--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{06ED0C7B-6FF1-463E-8453-51925E0CD421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C43DD094-A26C-4A35-81E2-0B1C355455CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2220" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2160" uniqueCount="579">
   <si>
     <t>Time</t>
   </si>
@@ -62,6 +62,183 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>04/16/2026 11:41:19 AM</t>
+  </si>
+  <si>
+    <t>680 - Medium</t>
+  </si>
+  <si>
+    <t>Jesus Carbajal</t>
+  </si>
+  <si>
+    <t>Active Drivers, Towing and Recovery</t>
+  </si>
+  <si>
+    <t>HAAS Alert, Towing and Recovery</t>
+  </si>
+  <si>
+    <t>Obstructed Camera</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>Tim Neff Jr.</t>
+  </si>
+  <si>
+    <t>Eastex Freeway Frontage Road, Beaumont, TX, 77702</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445972b-2023-520b-9311-2aa79edade29</t>
+  </si>
+  <si>
+    <t>04/15/2026 11:09:32 AM</t>
+  </si>
+  <si>
+    <t>669 - Heavy</t>
+  </si>
+  <si>
+    <t>Jason Walker</t>
+  </si>
+  <si>
+    <t>HAAS Alert, Heavy Haul</t>
+  </si>
+  <si>
+    <t>No Seat Belt</t>
+  </si>
+  <si>
+    <t>Construction, Light Traffic</t>
+  </si>
+  <si>
+    <t>I 10;US 69;US 96;US 287, Beaumont, TX, 77702</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544591e7-ac88-54d6-98a8-4bfe3fad16a5</t>
+  </si>
+  <si>
+    <t>04/14/2026 11:07:04 PM</t>
+  </si>
+  <si>
+    <t>658 - Medium</t>
+  </si>
+  <si>
+    <t>Paul Kunze Jr</t>
+  </si>
+  <si>
+    <t>Mobile Usage</t>
+  </si>
+  <si>
+    <t>Light Traffic, Night</t>
+  </si>
+  <si>
+    <t>Fannett Road, Beaumont, TX, 77705</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458f52-3b0b-50cb-bd6a-0400939c68f0</t>
+  </si>
+  <si>
+    <t>04/14/2026 5:40:17 PM</t>
+  </si>
+  <si>
+    <t>693 - Heavy</t>
+  </si>
+  <si>
+    <t>Drew Template</t>
+  </si>
+  <si>
+    <t>Active Drivers, Heavy Haul</t>
+  </si>
+  <si>
+    <t>Harsh Brake</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>401 Northeast Evangeline Thruway, Lafayette, LA, 70501</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0.58</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458e27-0eb3-5dba-85fd-a0dce64314bb</t>
+  </si>
+  <si>
+    <t>04/14/2026 5:19:07 PM</t>
+  </si>
+  <si>
+    <t>Coached</t>
+  </si>
+  <si>
+    <t>1193 US 90, Broussard, LA, 70518</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>0.65</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458e13-abfc-5546-ba17-feaf5efdc4dd</t>
+  </si>
+  <si>
+    <t>04/14/2026 11:46:08 AM</t>
+  </si>
+  <si>
+    <t>Eastex Freeway Frontage Road, Beaumont, TX, 77703</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458ce2-d409-5c3c-aecb-b998a858ebbd</t>
+  </si>
+  <si>
+    <t>04/13/2026 1:57:32 PM</t>
+  </si>
+  <si>
+    <t>21882 US 90, Nome, TX, 77713</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458834-c18f-5646-beeb-dec2a1a762b7</t>
+  </si>
+  <si>
+    <t>04/13/2026 10:43:50 AM</t>
+  </si>
+  <si>
+    <t>668 - Light</t>
+  </si>
+  <si>
+    <t>Dwayne Manuel</t>
+  </si>
+  <si>
+    <t>East Freeway, Houston, TX, 77020</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458783-6b27-5c61-8273-549c16680488</t>
+  </si>
+  <si>
     <t>04/11/2026 7:55:26 PM</t>
   </si>
   <si>
@@ -74,21 +251,6 @@
     <t>Towing and Recovery</t>
   </si>
   <si>
-    <t>HAAS Alert, Towing and Recovery</t>
-  </si>
-  <si>
-    <t>Mobile Usage</t>
-  </si>
-  <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
-    <t>Coached</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>FM 105, 7.6 mi ESE Silsbee, Jasper County, TX, 77615</t>
   </si>
   <si>
@@ -107,12 +269,6 @@
     <t xml:space="preserve">Jason Leleaux </t>
   </si>
   <si>
-    <t>HAAS Alert, Heavy Haul</t>
-  </si>
-  <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
     <t>TX 35, Alvin, TX, 77511</t>
   </si>
   <si>
@@ -125,12 +281,6 @@
     <t>04/10/2026 5:18:57 AM</t>
   </si>
   <si>
-    <t>No Seat Belt</t>
-  </si>
-  <si>
-    <t>Light Traffic, Night</t>
-  </si>
-  <si>
     <t>East Freeway, Baytown, TX, 77523</t>
   </si>
   <si>
@@ -149,12 +299,6 @@
     <t>Adam Johnson</t>
   </si>
   <si>
-    <t>Active Drivers, Heavy Haul</t>
-  </si>
-  <si>
-    <t>Obstructed Camera</t>
-  </si>
-  <si>
     <t>7360 Garth Street, Cheek, TX, 77705</t>
   </si>
   <si>
@@ -167,36 +311,15 @@
     <t>04/07/2026 10:15:48 PM</t>
   </si>
   <si>
-    <t>658 - Medium</t>
-  </si>
-  <si>
-    <t>Paul Kunze Jr</t>
-  </si>
-  <si>
-    <t>Active Drivers, Towing and Recovery</t>
-  </si>
-  <si>
-    <t>Tim Neff Jr.</t>
-  </si>
-  <si>
     <t>I 10, Beaumont, TX, 77705</t>
   </si>
   <si>
-    <t>57</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456b16-c772-5c6b-bb09-e92039e34f7c</t>
   </si>
   <si>
     <t>04/06/2026 5:30:46 PM</t>
   </si>
   <si>
-    <t>669 - Heavy</t>
-  </si>
-  <si>
-    <t>Jason Walker</t>
-  </si>
-  <si>
     <t>Following Distance</t>
   </si>
   <si>
@@ -212,15 +335,9 @@
     <t>04/06/2026 9:54:40 AM</t>
   </si>
   <si>
-    <t>668 - Light</t>
-  </si>
-  <si>
     <t>State Highway 124, Cheek, TX, 77705</t>
   </si>
   <si>
-    <t>37</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456349-e5b4-55ac-a43b-944299eef0c4</t>
   </si>
   <si>
@@ -230,9 +347,6 @@
     <t>Wet Road, Construction, Light Traffic, Raining</t>
   </si>
   <si>
-    <t>Eastex Freeway Frontage Road, Beaumont, TX, 77703</t>
-  </si>
-  <si>
     <t>25</t>
   </si>
   <si>
@@ -242,12 +356,6 @@
     <t>04/03/2026 8:23:50 AM</t>
   </si>
   <si>
-    <t>693 - Heavy</t>
-  </si>
-  <si>
-    <t>Drew Template</t>
-  </si>
-  <si>
     <t>Moderate Traffic</t>
   </si>
   <si>
@@ -338,9 +446,6 @@
     <t>04/01/2026 5:41:14 PM</t>
   </si>
   <si>
-    <t>Harsh Brake</t>
-  </si>
-  <si>
     <t>908 South Main Street, Vidor, TX, 77662</t>
   </si>
   <si>
@@ -383,12 +488,6 @@
     <t>03/31/2026 7:05:40 PM</t>
   </si>
   <si>
-    <t>Construction, Light Traffic</t>
-  </si>
-  <si>
-    <t>I 10;US 69;US 96;US 287, Beaumont, TX, 77702</t>
-  </si>
-  <si>
     <t>40</t>
   </si>
   <si>
@@ -455,12 +554,6 @@
     <t>03/25/2026 2:29:30 PM</t>
   </si>
   <si>
-    <t>680 - Medium</t>
-  </si>
-  <si>
-    <t>Jesus Carbajal</t>
-  </si>
-  <si>
     <t>Walden Road, Beaumont, TX, 77705</t>
   </si>
   <si>
@@ -551,9 +644,6 @@
     <t>10491 Old Sour Lake Road, 7.2 mi W Beaumont, Jefferson County, TX, 77713</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445187c-fcb2-50ce-aad8-1e15f2e9017e</t>
   </si>
   <si>
@@ -620,9 +710,6 @@
     <t>3029 TX 87, Newton, TX, 75966</t>
   </si>
   <si>
-    <t>38</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544502e8-358e-57ff-9d4c-94dbbff97f08</t>
   </si>
   <si>
@@ -653,9 +740,6 @@
     <t>South I-10 Frontage Road, Beaumont, TX, 77702</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>0.54</t>
   </si>
   <si>
@@ -938,9 +1022,6 @@
     <t>42308 TX 105, Batson, TX, 77519</t>
   </si>
   <si>
-    <t>42</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c9e3-685f-597b-b4d9-9b6891f4aba2</t>
   </si>
   <si>
@@ -1280,9 +1361,6 @@
     <t>02/21/2026 5:07:19 PM</t>
   </si>
   <si>
-    <t>Dwayne Manuel</t>
-  </si>
-  <si>
     <t>3692 Eastex Freeway, Beaumont, TX, 77706</t>
   </si>
   <si>
@@ -1674,114 +1752,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d8a3-4a9e-5da1-8727-16449fee6525</t>
-  </si>
-  <si>
-    <t>01/18/2026 12:42:39 PM</t>
-  </si>
-  <si>
-    <t>8317 Fannett Road, Beaumont, TX, 77705</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d26a-987e-5114-9b40-3b1eab196c91</t>
-  </si>
-  <si>
-    <t>01/16/2026 3:04:09 PM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c89f-6bf8-510b-83dc-18f40d6e8cf4</t>
-  </si>
-  <si>
-    <t>01/15/2026 6:22:20 PM</t>
-  </si>
-  <si>
-    <t>Phillip W Metz</t>
-  </si>
-  <si>
-    <t>1394 US 69;US 287, Lumberton, TX, 77625</t>
-  </si>
-  <si>
-    <t>0.73</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c42e-81da-55d0-a69c-5232a20ac30f</t>
-  </si>
-  <si>
-    <t>01/15/2026 11:33:21 AM</t>
-  </si>
-  <si>
-    <t>15192 East Freeway, Channelview, TX, 77530</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c2b8-12a7-5391-ac23-3065705d6392</t>
-  </si>
-  <si>
-    <t>01/14/2026 4:39:47 PM</t>
-  </si>
-  <si>
-    <t>28901 TX 124, Morey, TX, 77665</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445beaa-3f64-5c14-8e8f-1354075892d1</t>
-  </si>
-  <si>
-    <t>01/14/2026 12:51:13 PM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bdd8-feff-533a-81da-3dc9d25b46f8</t>
-  </si>
-  <si>
-    <t>01/14/2026 12:37:22 PM</t>
-  </si>
-  <si>
-    <t>5405 Walden Road, Beaumont, TX, 77705</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bdcc-4fff-5f93-b5f4-b05bc7bbaa05</t>
-  </si>
-  <si>
-    <t>01/14/2026 12:27:21 PM</t>
-  </si>
-  <si>
-    <t>Memorial Freeway, Port Arthur, TX, 77642</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bdc3-2526-52b4-9e5e-027756fd674b</t>
-  </si>
-  <si>
-    <t>01/14/2026 6:34:28 AM</t>
-  </si>
-  <si>
-    <t>4813 Fannett Road, Beaumont, TX, 77705</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bc80-11bf-5d60-a150-7dd13123decd</t>
-  </si>
-  <si>
-    <t>01/13/2026 2:53:53 PM</t>
-  </si>
-  <si>
-    <t>East Unit Road, 30.6 mi NE Galveston, Chambers County, TX, 77623</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b922-f26d-5fdb-9973-506530de9d2f</t>
-  </si>
-  <si>
-    <t>01/13/2026 12:28:32 PM</t>
-  </si>
-  <si>
-    <t>Berry Road, Houston, TX, 77022</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b89d-df16-5492-a318-c23d087f758a</t>
-  </si>
-  <si>
-    <t>01/13/2026 11:45:37 AM</t>
-  </si>
-  <si>
-    <t>5217 North Freeway, Houston, TX, 77022</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b876-9320-55ae-b8a2-d2d66a63fbd7</t>
   </si>
 </sst>
 </file>
@@ -2158,7 +2128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O148"/>
+  <dimension ref="A1:O144"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -2243,13 +2213,13 @@
         <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O2" t="s">
         <v>26</v>
@@ -2266,210 +2236,210 @@
         <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
         <v>23</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H4" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I4" t="s">
         <v>23</v>
       </c>
       <c r="J4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
         <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="H5" t="s">
         <v>22</v>
       </c>
       <c r="I5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N5" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="O5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" t="s">
         <v>49</v>
       </c>
-      <c r="B6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" t="s">
-        <v>37</v>
-      </c>
       <c r="H6" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I6" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N6" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="O6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="G7" t="s">
         <v>21</v>
       </c>
       <c r="H7" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I7" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J7" t="s">
         <v>61</v>
@@ -2478,13 +2448,13 @@
         <v>62</v>
       </c>
       <c r="L7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O7" t="s">
         <v>63</v>
@@ -2495,75 +2465,75 @@
         <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G8" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H8" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I8" t="s">
         <v>23</v>
       </c>
       <c r="J8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K8" t="s">
         <v>66</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" t="s">
+        <v>21</v>
+      </c>
+      <c r="O8" t="s">
         <v>67</v>
-      </c>
-      <c r="L8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M8" t="s">
-        <v>23</v>
-      </c>
-      <c r="N8" t="s">
-        <v>23</v>
-      </c>
-      <c r="O8" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" t="s">
         <v>69</v>
       </c>
-      <c r="B9" t="s">
-        <v>50</v>
-      </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
         <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="H9" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I9" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J9" t="s">
         <v>71</v>
@@ -2572,13 +2542,13 @@
         <v>72</v>
       </c>
       <c r="L9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O9" t="s">
         <v>73</v>
@@ -2595,22 +2565,22 @@
         <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="H10" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="I10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J10" t="s">
         <v>78</v>
@@ -2619,13 +2589,13 @@
         <v>79</v>
       </c>
       <c r="L10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O10" t="s">
         <v>80</v>
@@ -2636,107 +2606,107 @@
         <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="H11" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I11" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J11" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="K11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O11" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F12" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G12" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="H12" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I12" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="E13" t="s">
         <v>30</v>
@@ -2748,98 +2718,98 @@
         <v>21</v>
       </c>
       <c r="H13" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J13" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G14" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="H14" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I14" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J14" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K14" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="L14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O14" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B15" t="s">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
         <v>101</v>
       </c>
       <c r="G15" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="H15" t="s">
         <v>22</v>
@@ -2854,86 +2824,86 @@
         <v>103</v>
       </c>
       <c r="L15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" t="s">
+        <v>21</v>
+      </c>
+      <c r="O15" t="s">
         <v>104</v>
-      </c>
-      <c r="N15" t="s">
-        <v>23</v>
-      </c>
-      <c r="O15" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" t="s">
         <v>106</v>
       </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="K16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" t="s">
+        <v>21</v>
+      </c>
+      <c r="O16" t="s">
         <v>107</v>
-      </c>
-      <c r="G16" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" t="s">
-        <v>23</v>
-      </c>
-      <c r="J16" t="s">
-        <v>108</v>
-      </c>
-      <c r="K16" t="s">
-        <v>104</v>
-      </c>
-      <c r="L16" t="s">
-        <v>23</v>
-      </c>
-      <c r="M16" t="s">
-        <v>23</v>
-      </c>
-      <c r="N16" t="s">
-        <v>109</v>
-      </c>
-      <c r="O16" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B17" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E17" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G17" t="s">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="H17" t="s">
         <v>22</v>
@@ -2942,139 +2912,139 @@
         <v>23</v>
       </c>
       <c r="J17" t="s">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="K17" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="L17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O17" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E18" t="s">
         <v>30</v>
       </c>
       <c r="F18" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="G18" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="H18" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I18" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J18" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="K18" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L18" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M18" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N18" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O18" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G19" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="H19" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I19" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J19" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="K19" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="L19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O19" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B20" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E20" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G20" t="s">
-        <v>21</v>
+        <v>121</v>
       </c>
       <c r="H20" t="s">
         <v>22</v>
@@ -3083,92 +3053,92 @@
         <v>23</v>
       </c>
       <c r="J20" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="K20" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="L20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O20" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E21" t="s">
         <v>30</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G21" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="H21" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J21" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="K21" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="L21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O21" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B22" t="s">
-        <v>134</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E22" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="G22" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="H22" t="s">
         <v>22</v>
@@ -3177,583 +3147,583 @@
         <v>23</v>
       </c>
       <c r="J22" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="K22" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="L22" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M22" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="N22" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O22" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>134</v>
+      </c>
+      <c r="B23" t="s">
+        <v>135</v>
+      </c>
+      <c r="C23" t="s">
+        <v>136</v>
+      </c>
+      <c r="D23" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" t="s">
+        <v>137</v>
+      </c>
+      <c r="G23" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" t="s">
+        <v>55</v>
+      </c>
+      <c r="I23" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" t="s">
+        <v>138</v>
+      </c>
+      <c r="K23" t="s">
         <v>139</v>
       </c>
-      <c r="B23" t="s">
-        <v>99</v>
-      </c>
-      <c r="C23" t="s">
-        <v>100</v>
-      </c>
-      <c r="D23" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" t="s">
-        <v>107</v>
-      </c>
-      <c r="G23" t="s">
+      <c r="L23" t="s">
+        <v>21</v>
+      </c>
+      <c r="M23" t="s">
         <v>140</v>
       </c>
-      <c r="H23" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" t="s">
-        <v>23</v>
-      </c>
-      <c r="J23" t="s">
+      <c r="N23" t="s">
+        <v>21</v>
+      </c>
+      <c r="O23" t="s">
         <v>141</v>
-      </c>
-      <c r="K23" t="s">
-        <v>142</v>
-      </c>
-      <c r="L23" t="s">
-        <v>23</v>
-      </c>
-      <c r="M23" t="s">
-        <v>23</v>
-      </c>
-      <c r="N23" t="s">
-        <v>143</v>
-      </c>
-      <c r="O23" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>142</v>
+      </c>
+      <c r="B24" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" t="s">
+        <v>48</v>
+      </c>
+      <c r="G24" t="s">
+        <v>49</v>
+      </c>
+      <c r="H24" t="s">
+        <v>55</v>
+      </c>
+      <c r="I24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" t="s">
+        <v>143</v>
+      </c>
+      <c r="K24" t="s">
+        <v>140</v>
+      </c>
+      <c r="L24" t="s">
+        <v>21</v>
+      </c>
+      <c r="M24" t="s">
+        <v>21</v>
+      </c>
+      <c r="N24" t="s">
+        <v>144</v>
+      </c>
+      <c r="O24" t="s">
         <v>145</v>
-      </c>
-      <c r="B24" t="s">
-        <v>146</v>
-      </c>
-      <c r="C24" t="s">
-        <v>147</v>
-      </c>
-      <c r="D24" t="s">
-        <v>52</v>
-      </c>
-      <c r="E24" t="s">
-        <v>19</v>
-      </c>
-      <c r="F24" t="s">
-        <v>45</v>
-      </c>
-      <c r="G24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" t="s">
-        <v>53</v>
-      </c>
-      <c r="J24" t="s">
-        <v>148</v>
-      </c>
-      <c r="K24" t="s">
-        <v>119</v>
-      </c>
-      <c r="L24" t="s">
-        <v>23</v>
-      </c>
-      <c r="M24" t="s">
-        <v>23</v>
-      </c>
-      <c r="N24" t="s">
-        <v>23</v>
-      </c>
-      <c r="O24" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>146</v>
+      </c>
+      <c r="B25" t="s">
+        <v>147</v>
+      </c>
+      <c r="C25" t="s">
+        <v>148</v>
+      </c>
+      <c r="D25" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25" t="s">
+        <v>31</v>
+      </c>
+      <c r="G25" t="s">
+        <v>49</v>
+      </c>
+      <c r="H25" t="s">
+        <v>55</v>
+      </c>
+      <c r="I25" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" t="s">
+        <v>149</v>
+      </c>
+      <c r="K25" t="s">
         <v>150</v>
       </c>
-      <c r="B25" t="s">
-        <v>99</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="L25" t="s">
+        <v>21</v>
+      </c>
+      <c r="M25" t="s">
+        <v>21</v>
+      </c>
+      <c r="N25" t="s">
+        <v>21</v>
+      </c>
+      <c r="O25" t="s">
         <v>151</v>
-      </c>
-      <c r="D25" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" t="s">
-        <v>20</v>
-      </c>
-      <c r="G25" t="s">
-        <v>21</v>
-      </c>
-      <c r="H25" t="s">
-        <v>31</v>
-      </c>
-      <c r="I25" t="s">
-        <v>23</v>
-      </c>
-      <c r="J25" t="s">
-        <v>152</v>
-      </c>
-      <c r="K25" t="s">
-        <v>153</v>
-      </c>
-      <c r="L25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M25" t="s">
-        <v>23</v>
-      </c>
-      <c r="N25" t="s">
-        <v>23</v>
-      </c>
-      <c r="O25" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>152</v>
+      </c>
+      <c r="B26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" t="s">
+        <v>31</v>
+      </c>
+      <c r="G26" t="s">
+        <v>49</v>
+      </c>
+      <c r="H26" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" t="s">
+        <v>153</v>
+      </c>
+      <c r="K26" t="s">
+        <v>154</v>
+      </c>
+      <c r="L26" t="s">
+        <v>21</v>
+      </c>
+      <c r="M26" t="s">
+        <v>21</v>
+      </c>
+      <c r="N26" t="s">
+        <v>21</v>
+      </c>
+      <c r="O26" t="s">
         <v>155</v>
-      </c>
-      <c r="B26" t="s">
-        <v>156</v>
-      </c>
-      <c r="C26" t="s">
-        <v>157</v>
-      </c>
-      <c r="D26" t="s">
-        <v>52</v>
-      </c>
-      <c r="E26" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" t="s">
-        <v>20</v>
-      </c>
-      <c r="G26" t="s">
-        <v>158</v>
-      </c>
-      <c r="H26" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" t="s">
-        <v>53</v>
-      </c>
-      <c r="J26" t="s">
-        <v>159</v>
-      </c>
-      <c r="K26" t="s">
-        <v>160</v>
-      </c>
-      <c r="L26" t="s">
-        <v>23</v>
-      </c>
-      <c r="M26" t="s">
-        <v>23</v>
-      </c>
-      <c r="N26" t="s">
-        <v>23</v>
-      </c>
-      <c r="O26" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="C27" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="D27" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E27" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G27" t="s">
-        <v>136</v>
+        <v>32</v>
       </c>
       <c r="H27" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I27" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J27" t="s">
-        <v>163</v>
+        <v>33</v>
       </c>
       <c r="K27" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="L27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O27" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B28" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C28" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D28" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F28" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G28" t="s">
-        <v>167</v>
+        <v>49</v>
       </c>
       <c r="H28" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I28" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J28" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="K28" t="s">
-        <v>169</v>
+        <v>110</v>
       </c>
       <c r="L28" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M28" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N28" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O28" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B29" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C29" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="D29" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="E29" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F29" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G29" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H29" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I29" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J29" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="K29" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="L29" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M29" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N29" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O29" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>167</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
+        <v>168</v>
       </c>
       <c r="D30" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E30" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F30" t="s">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="G30" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="H30" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I30" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J30" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="K30" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="L30" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M30" t="s">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="N30" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O30" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B31" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="C31" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="D31" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G31" t="s">
-        <v>23</v>
+        <v>173</v>
       </c>
       <c r="H31" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I31" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J31" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="K31" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="L31" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M31" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N31" t="s">
-        <v>23</v>
+        <v>176</v>
       </c>
       <c r="O31" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="D32" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
       </c>
       <c r="F32" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="G32" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="H32" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I32" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J32" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="K32" t="s">
-        <v>67</v>
+        <v>154</v>
       </c>
       <c r="L32" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M32" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N32" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O32" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="C33" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="D33" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
       </c>
       <c r="F33" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G33" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="H33" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I33" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J33" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="K33" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="L33" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M33" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N33" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O33" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>186</v>
+      </c>
+      <c r="B34" t="s">
+        <v>187</v>
+      </c>
+      <c r="C34" t="s">
+        <v>188</v>
+      </c>
+      <c r="D34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" t="s">
+        <v>39</v>
+      </c>
+      <c r="G34" t="s">
+        <v>189</v>
+      </c>
+      <c r="H34" t="s">
+        <v>22</v>
+      </c>
+      <c r="I34" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" t="s">
         <v>190</v>
       </c>
-      <c r="B34" t="s">
-        <v>50</v>
-      </c>
-      <c r="C34" t="s">
-        <v>51</v>
-      </c>
-      <c r="D34" t="s">
-        <v>52</v>
-      </c>
-      <c r="E34" t="s">
-        <v>19</v>
-      </c>
-      <c r="F34" t="s">
-        <v>20</v>
-      </c>
-      <c r="G34" t="s">
-        <v>37</v>
-      </c>
-      <c r="H34" t="s">
-        <v>31</v>
-      </c>
-      <c r="I34" t="s">
-        <v>53</v>
-      </c>
-      <c r="J34" t="s">
+      <c r="K34" t="s">
         <v>191</v>
       </c>
-      <c r="K34" t="s">
-        <v>82</v>
-      </c>
       <c r="L34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O34" t="s">
         <v>192</v>
@@ -3764,104 +3734,104 @@
         <v>193</v>
       </c>
       <c r="B35" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="D35" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E35" t="s">
         <v>30</v>
       </c>
       <c r="F35" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G35" t="s">
-        <v>85</v>
+        <v>169</v>
       </c>
       <c r="H35" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I35" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J35" t="s">
         <v>194</v>
       </c>
       <c r="K35" t="s">
-        <v>115</v>
+        <v>195</v>
       </c>
       <c r="L35" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M35" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N35" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O35" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B36" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D36" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E36" t="s">
         <v>19</v>
       </c>
       <c r="F36" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G36" t="s">
-        <v>122</v>
+        <v>198</v>
       </c>
       <c r="H36" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I36" t="s">
         <v>23</v>
       </c>
       <c r="J36" t="s">
-        <v>123</v>
+        <v>199</v>
       </c>
       <c r="K36" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="L36" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M36" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N36" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O36" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B37" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="C37" t="s">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
@@ -3870,57 +3840,57 @@
         <v>19</v>
       </c>
       <c r="F37" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G37" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="H37" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I37" t="s">
         <v>23</v>
       </c>
       <c r="J37" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K37" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="L37" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M37" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N37" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O37" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>204</v>
+        <v>38</v>
       </c>
       <c r="D38" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E38" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F38" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G38" t="s">
-        <v>23</v>
+        <v>207</v>
       </c>
       <c r="H38" t="s">
         <v>22</v>
@@ -3929,33 +3899,33 @@
         <v>23</v>
       </c>
       <c r="J38" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="K38" t="s">
-        <v>206</v>
+        <v>25</v>
       </c>
       <c r="L38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O38" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B39" t="s">
-        <v>99</v>
+        <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>151</v>
+        <v>17</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
@@ -3964,13 +3934,13 @@
         <v>19</v>
       </c>
       <c r="F39" t="s">
-        <v>209</v>
+        <v>20</v>
       </c>
       <c r="G39" t="s">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="H39" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I39" t="s">
         <v>23</v>
@@ -3982,497 +3952,497 @@
         <v>212</v>
       </c>
       <c r="L39" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M39" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N39" t="s">
+        <v>21</v>
+      </c>
+      <c r="O39" t="s">
         <v>213</v>
-      </c>
-      <c r="O39" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>214</v>
+      </c>
+      <c r="B40" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" t="s">
+        <v>31</v>
+      </c>
+      <c r="G40" t="s">
+        <v>169</v>
+      </c>
+      <c r="H40" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" t="s">
+        <v>23</v>
+      </c>
+      <c r="J40" t="s">
         <v>215</v>
       </c>
-      <c r="B40" t="s">
-        <v>50</v>
-      </c>
-      <c r="C40" t="s">
-        <v>51</v>
-      </c>
-      <c r="D40" t="s">
-        <v>52</v>
-      </c>
-      <c r="E40" t="s">
-        <v>19</v>
-      </c>
-      <c r="F40" t="s">
-        <v>36</v>
-      </c>
-      <c r="G40" t="s">
+      <c r="K40" t="s">
+        <v>66</v>
+      </c>
+      <c r="L40" t="s">
+        <v>21</v>
+      </c>
+      <c r="M40" t="s">
+        <v>21</v>
+      </c>
+      <c r="N40" t="s">
+        <v>21</v>
+      </c>
+      <c r="O40" t="s">
         <v>216</v>
-      </c>
-      <c r="H40" t="s">
-        <v>31</v>
-      </c>
-      <c r="I40" t="s">
-        <v>53</v>
-      </c>
-      <c r="J40" t="s">
-        <v>217</v>
-      </c>
-      <c r="K40" t="s">
-        <v>218</v>
-      </c>
-      <c r="L40" t="s">
-        <v>23</v>
-      </c>
-      <c r="M40" t="s">
-        <v>23</v>
-      </c>
-      <c r="N40" t="s">
-        <v>23</v>
-      </c>
-      <c r="O40" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C41" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D41" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E41" t="s">
         <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G41" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H41" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I41" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J41" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="K41" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="L41" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M41" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N41" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O41" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B42" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="C42" t="s">
-        <v>147</v>
+        <v>38</v>
       </c>
       <c r="D42" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E42" t="s">
         <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>224</v>
+        <v>39</v>
       </c>
       <c r="G42" t="s">
-        <v>225</v>
+        <v>40</v>
       </c>
       <c r="H42" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I42" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J42" t="s">
-        <v>54</v>
+        <v>221</v>
       </c>
       <c r="K42" t="s">
-        <v>226</v>
+        <v>118</v>
       </c>
       <c r="L42" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M42" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N42" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O42" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B43" t="s">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="C43" t="s">
-        <v>151</v>
+        <v>29</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
       </c>
       <c r="E43" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F43" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G43" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="H43" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I43" t="s">
         <v>23</v>
       </c>
       <c r="J43" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="K43" t="s">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="L43" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M43" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N43" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O43" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B44" t="s">
-        <v>233</v>
+        <v>69</v>
       </c>
       <c r="C44" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="D44" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E44" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F44" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="G44" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H44" t="s">
         <v>22</v>
       </c>
       <c r="I44" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J44" t="s">
-        <v>163</v>
+        <v>33</v>
       </c>
       <c r="K44" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="L44" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M44" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N44" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O44" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="C45" t="s">
-        <v>59</v>
+        <v>182</v>
       </c>
       <c r="D45" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="E45" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G45" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="H45" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I45" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J45" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="K45" t="s">
-        <v>119</v>
+        <v>34</v>
       </c>
       <c r="L45" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M45" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N45" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O45" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C46" t="s">
-        <v>59</v>
+        <v>233</v>
       </c>
       <c r="D46" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E46" t="s">
         <v>30</v>
       </c>
       <c r="F46" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="G46" t="s">
         <v>21</v>
       </c>
       <c r="H46" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I46" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J46" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="K46" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="L46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O46" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B47" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="C47" t="s">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="D47" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="E47" t="s">
         <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>45</v>
+        <v>238</v>
       </c>
       <c r="G47" t="s">
-        <v>23</v>
+        <v>239</v>
       </c>
       <c r="H47" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I47" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J47" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="K47" t="s">
-        <v>169</v>
+        <v>42</v>
       </c>
       <c r="L47" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M47" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N47" t="s">
-        <v>23</v>
+        <v>241</v>
       </c>
       <c r="O47" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B48" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C48" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D48" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E48" t="s">
         <v>19</v>
       </c>
       <c r="F48" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="G48" t="s">
-        <v>77</v>
+        <v>244</v>
       </c>
       <c r="H48" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I48" t="s">
         <v>23</v>
       </c>
       <c r="J48" t="s">
+        <v>245</v>
+      </c>
+      <c r="K48" t="s">
+        <v>246</v>
+      </c>
+      <c r="L48" t="s">
+        <v>21</v>
+      </c>
+      <c r="M48" t="s">
+        <v>21</v>
+      </c>
+      <c r="N48" t="s">
+        <v>21</v>
+      </c>
+      <c r="O48" t="s">
         <v>247</v>
-      </c>
-      <c r="K48" t="s">
-        <v>248</v>
-      </c>
-      <c r="L48" t="s">
-        <v>23</v>
-      </c>
-      <c r="M48" t="s">
-        <v>23</v>
-      </c>
-      <c r="N48" t="s">
-        <v>23</v>
-      </c>
-      <c r="O48" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>248</v>
+      </c>
+      <c r="B49" t="s">
+        <v>37</v>
+      </c>
+      <c r="C49" t="s">
+        <v>38</v>
+      </c>
+      <c r="D49" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" t="s">
+        <v>19</v>
+      </c>
+      <c r="F49" t="s">
+        <v>39</v>
+      </c>
+      <c r="G49" t="s">
+        <v>40</v>
+      </c>
+      <c r="H49" t="s">
+        <v>22</v>
+      </c>
+      <c r="I49" t="s">
+        <v>23</v>
+      </c>
+      <c r="J49" t="s">
+        <v>249</v>
+      </c>
+      <c r="K49" t="s">
+        <v>118</v>
+      </c>
+      <c r="L49" t="s">
+        <v>21</v>
+      </c>
+      <c r="M49" t="s">
+        <v>21</v>
+      </c>
+      <c r="N49" t="s">
+        <v>21</v>
+      </c>
+      <c r="O49" t="s">
         <v>250</v>
-      </c>
-      <c r="B49" t="s">
-        <v>146</v>
-      </c>
-      <c r="C49" t="s">
-        <v>147</v>
-      </c>
-      <c r="D49" t="s">
-        <v>52</v>
-      </c>
-      <c r="E49" t="s">
-        <v>19</v>
-      </c>
-      <c r="F49" t="s">
-        <v>20</v>
-      </c>
-      <c r="G49" t="s">
-        <v>21</v>
-      </c>
-      <c r="H49" t="s">
-        <v>31</v>
-      </c>
-      <c r="I49" t="s">
-        <v>53</v>
-      </c>
-      <c r="J49" t="s">
-        <v>251</v>
-      </c>
-      <c r="K49" t="s">
-        <v>252</v>
-      </c>
-      <c r="L49" t="s">
-        <v>23</v>
-      </c>
-      <c r="M49" t="s">
-        <v>23</v>
-      </c>
-      <c r="N49" t="s">
-        <v>23</v>
-      </c>
-      <c r="O49" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>16</v>
       </c>
       <c r="C50" t="s">
-        <v>151</v>
+        <v>17</v>
       </c>
       <c r="D50" t="s">
         <v>18</v>
@@ -4481,10 +4451,10 @@
         <v>19</v>
       </c>
       <c r="F50" t="s">
-        <v>209</v>
+        <v>252</v>
       </c>
       <c r="G50" t="s">
-        <v>122</v>
+        <v>253</v>
       </c>
       <c r="H50" t="s">
         <v>22</v>
@@ -4493,606 +4463,606 @@
         <v>23</v>
       </c>
       <c r="J50" t="s">
+        <v>98</v>
+      </c>
+      <c r="K50" t="s">
+        <v>254</v>
+      </c>
+      <c r="L50" t="s">
+        <v>21</v>
+      </c>
+      <c r="M50" t="s">
+        <v>21</v>
+      </c>
+      <c r="N50" t="s">
+        <v>21</v>
+      </c>
+      <c r="O50" t="s">
         <v>255</v>
-      </c>
-      <c r="K50" t="s">
-        <v>256</v>
-      </c>
-      <c r="L50" t="s">
-        <v>23</v>
-      </c>
-      <c r="M50" t="s">
-        <v>23</v>
-      </c>
-      <c r="N50" t="s">
-        <v>257</v>
-      </c>
-      <c r="O50" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>256</v>
+      </c>
+      <c r="B51" t="s">
+        <v>135</v>
+      </c>
+      <c r="C51" t="s">
+        <v>182</v>
+      </c>
+      <c r="D51" t="s">
+        <v>77</v>
+      </c>
+      <c r="E51" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" t="s">
+        <v>31</v>
+      </c>
+      <c r="G51" t="s">
+        <v>40</v>
+      </c>
+      <c r="H51" t="s">
+        <v>22</v>
+      </c>
+      <c r="I51" t="s">
+        <v>21</v>
+      </c>
+      <c r="J51" t="s">
+        <v>257</v>
+      </c>
+      <c r="K51" t="s">
+        <v>258</v>
+      </c>
+      <c r="L51" t="s">
+        <v>21</v>
+      </c>
+      <c r="M51" t="s">
+        <v>21</v>
+      </c>
+      <c r="N51" t="s">
+        <v>21</v>
+      </c>
+      <c r="O51" t="s">
         <v>259</v>
-      </c>
-      <c r="B51" t="s">
-        <v>50</v>
-      </c>
-      <c r="C51" t="s">
-        <v>51</v>
-      </c>
-      <c r="D51" t="s">
-        <v>52</v>
-      </c>
-      <c r="E51" t="s">
-        <v>19</v>
-      </c>
-      <c r="F51" t="s">
-        <v>36</v>
-      </c>
-      <c r="G51" t="s">
-        <v>21</v>
-      </c>
-      <c r="H51" t="s">
-        <v>31</v>
-      </c>
-      <c r="I51" t="s">
-        <v>53</v>
-      </c>
-      <c r="J51" t="s">
-        <v>260</v>
-      </c>
-      <c r="K51" t="s">
-        <v>261</v>
-      </c>
-      <c r="L51" t="s">
-        <v>23</v>
-      </c>
-      <c r="M51" t="s">
-        <v>23</v>
-      </c>
-      <c r="N51" t="s">
-        <v>23</v>
-      </c>
-      <c r="O51" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>260</v>
+      </c>
+      <c r="B52" t="s">
+        <v>261</v>
+      </c>
+      <c r="C52" t="s">
+        <v>93</v>
+      </c>
+      <c r="D52" t="s">
+        <v>47</v>
+      </c>
+      <c r="E52" t="s">
+        <v>30</v>
+      </c>
+      <c r="F52" t="s">
+        <v>101</v>
+      </c>
+      <c r="G52" t="s">
+        <v>49</v>
+      </c>
+      <c r="H52" t="s">
+        <v>55</v>
+      </c>
+      <c r="I52" t="s">
+        <v>21</v>
+      </c>
+      <c r="J52" t="s">
+        <v>194</v>
+      </c>
+      <c r="K52" t="s">
+        <v>262</v>
+      </c>
+      <c r="L52" t="s">
+        <v>21</v>
+      </c>
+      <c r="M52" t="s">
+        <v>21</v>
+      </c>
+      <c r="N52" t="s">
+        <v>21</v>
+      </c>
+      <c r="O52" t="s">
         <v>263</v>
-      </c>
-      <c r="B52" t="s">
-        <v>50</v>
-      </c>
-      <c r="C52" t="s">
-        <v>51</v>
-      </c>
-      <c r="D52" t="s">
-        <v>52</v>
-      </c>
-      <c r="E52" t="s">
-        <v>19</v>
-      </c>
-      <c r="F52" t="s">
-        <v>20</v>
-      </c>
-      <c r="G52" t="s">
-        <v>37</v>
-      </c>
-      <c r="H52" t="s">
-        <v>31</v>
-      </c>
-      <c r="I52" t="s">
-        <v>53</v>
-      </c>
-      <c r="J52" t="s">
-        <v>264</v>
-      </c>
-      <c r="K52" t="s">
-        <v>62</v>
-      </c>
-      <c r="L52" t="s">
-        <v>23</v>
-      </c>
-      <c r="M52" t="s">
-        <v>23</v>
-      </c>
-      <c r="N52" t="s">
-        <v>23</v>
-      </c>
-      <c r="O52" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>264</v>
+      </c>
+      <c r="B53" t="s">
+        <v>28</v>
+      </c>
+      <c r="C53" t="s">
+        <v>29</v>
+      </c>
+      <c r="D53" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" t="s">
+        <v>30</v>
+      </c>
+      <c r="F53" t="s">
+        <v>31</v>
+      </c>
+      <c r="G53" t="s">
+        <v>121</v>
+      </c>
+      <c r="H53" t="s">
+        <v>22</v>
+      </c>
+      <c r="I53" t="s">
+        <v>23</v>
+      </c>
+      <c r="J53" t="s">
+        <v>265</v>
+      </c>
+      <c r="K53" t="s">
+        <v>154</v>
+      </c>
+      <c r="L53" t="s">
+        <v>21</v>
+      </c>
+      <c r="M53" t="s">
+        <v>21</v>
+      </c>
+      <c r="N53" t="s">
+        <v>21</v>
+      </c>
+      <c r="O53" t="s">
         <v>266</v>
-      </c>
-      <c r="B53" t="s">
-        <v>267</v>
-      </c>
-      <c r="C53" t="s">
-        <v>268</v>
-      </c>
-      <c r="D53" t="s">
-        <v>269</v>
-      </c>
-      <c r="E53" t="s">
-        <v>19</v>
-      </c>
-      <c r="F53" t="s">
-        <v>36</v>
-      </c>
-      <c r="G53" t="s">
-        <v>270</v>
-      </c>
-      <c r="H53" t="s">
-        <v>31</v>
-      </c>
-      <c r="I53" t="s">
-        <v>271</v>
-      </c>
-      <c r="J53" t="s">
-        <v>272</v>
-      </c>
-      <c r="K53" t="s">
-        <v>273</v>
-      </c>
-      <c r="L53" t="s">
-        <v>23</v>
-      </c>
-      <c r="M53" t="s">
-        <v>23</v>
-      </c>
-      <c r="N53" t="s">
-        <v>23</v>
-      </c>
-      <c r="O53" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="B54" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C54" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="D54" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E54" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F54" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G54" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="H54" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I54" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J54" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="K54" t="s">
-        <v>33</v>
+        <v>269</v>
       </c>
       <c r="L54" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M54" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N54" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O54" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="B55" t="s">
-        <v>146</v>
+        <v>16</v>
       </c>
       <c r="C55" t="s">
-        <v>147</v>
+        <v>17</v>
       </c>
       <c r="D55" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E55" t="s">
         <v>19</v>
       </c>
       <c r="F55" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G55" t="s">
+        <v>21</v>
+      </c>
+      <c r="H55" t="s">
+        <v>22</v>
+      </c>
+      <c r="I55" t="s">
         <v>23</v>
       </c>
-      <c r="H55" t="s">
-        <v>31</v>
-      </c>
-      <c r="I55" t="s">
-        <v>53</v>
-      </c>
       <c r="J55" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="K55" t="s">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="L55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O55" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="B56" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="C56" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D56" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E56" t="s">
         <v>19</v>
       </c>
       <c r="F56" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="G56" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="H56" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I56" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J56" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="K56" t="s">
-        <v>234</v>
+        <v>276</v>
       </c>
       <c r="L56" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M56" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N56" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O56" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B57" t="s">
         <v>16</v>
       </c>
       <c r="C57" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D57" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E57" t="s">
         <v>19</v>
       </c>
       <c r="F57" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G57" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="H57" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I57" t="s">
         <v>23</v>
       </c>
       <c r="J57" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="K57" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="L57" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M57" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N57" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O57" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B58" t="s">
-        <v>290</v>
+        <v>135</v>
       </c>
       <c r="C58" t="s">
-        <v>43</v>
+        <v>182</v>
       </c>
       <c r="D58" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="E58" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F58" t="s">
-        <v>60</v>
+        <v>238</v>
       </c>
       <c r="G58" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="H58" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="I58" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J58" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="K58" t="s">
-        <v>39</v>
+        <v>284</v>
       </c>
       <c r="L58" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M58" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N58" t="s">
-        <v>23</v>
+        <v>285</v>
       </c>
       <c r="O58" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="B59" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C59" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D59" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E59" t="s">
         <v>19</v>
       </c>
       <c r="F59" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G59" t="s">
-        <v>294</v>
+        <v>49</v>
       </c>
       <c r="H59" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I59" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J59" t="s">
-        <v>188</v>
+        <v>288</v>
       </c>
       <c r="K59" t="s">
-        <v>169</v>
+        <v>289</v>
       </c>
       <c r="L59" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M59" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N59" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O59" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B60" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C60" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D60" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E60" t="s">
         <v>19</v>
       </c>
       <c r="F60" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G60" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="H60" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I60" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J60" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="K60" t="s">
-        <v>206</v>
+        <v>103</v>
       </c>
       <c r="L60" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M60" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N60" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O60" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>294</v>
+      </c>
+      <c r="B61" t="s">
+        <v>295</v>
+      </c>
+      <c r="C61" t="s">
+        <v>296</v>
+      </c>
+      <c r="D61" t="s">
+        <v>297</v>
+      </c>
+      <c r="E61" t="s">
+        <v>19</v>
+      </c>
+      <c r="F61" t="s">
+        <v>31</v>
+      </c>
+      <c r="G61" t="s">
+        <v>298</v>
+      </c>
+      <c r="H61" t="s">
+        <v>22</v>
+      </c>
+      <c r="I61" t="s">
         <v>299</v>
-      </c>
-      <c r="B61" t="s">
-        <v>50</v>
-      </c>
-      <c r="C61" t="s">
-        <v>51</v>
-      </c>
-      <c r="D61" t="s">
-        <v>52</v>
-      </c>
-      <c r="E61" t="s">
-        <v>19</v>
-      </c>
-      <c r="F61" t="s">
-        <v>36</v>
-      </c>
-      <c r="G61" t="s">
-        <v>85</v>
-      </c>
-      <c r="H61" t="s">
-        <v>31</v>
-      </c>
-      <c r="I61" t="s">
-        <v>53</v>
       </c>
       <c r="J61" t="s">
         <v>300</v>
       </c>
       <c r="K61" t="s">
-        <v>124</v>
+        <v>301</v>
       </c>
       <c r="L61" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M61" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N61" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O61" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B62" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C62" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D62" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E62" t="s">
         <v>19</v>
       </c>
       <c r="F62" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G62" t="s">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="H62" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I62" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J62" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K62" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="L62" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M62" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N62" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O62" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B63" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="C63" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E63" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F63" t="s">
-        <v>101</v>
+        <v>20</v>
       </c>
       <c r="G63" t="s">
         <v>21</v>
@@ -5104,66 +5074,66 @@
         <v>23</v>
       </c>
       <c r="J63" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K63" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L63" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M63" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="N63" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O63" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B64" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="C64" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="D64" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="E64" t="s">
         <v>19</v>
       </c>
       <c r="F64" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G64" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="H64" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I64" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J64" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K64" t="s">
-        <v>311</v>
+        <v>262</v>
       </c>
       <c r="L64" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M64" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N64" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O64" t="s">
         <v>312</v>
@@ -5174,163 +5144,163 @@
         <v>313</v>
       </c>
       <c r="B65" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C65" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D65" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E65" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F65" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G65" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="H65" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I65" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J65" t="s">
         <v>314</v>
       </c>
       <c r="K65" t="s">
-        <v>67</v>
+        <v>315</v>
       </c>
       <c r="L65" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M65" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N65" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O65" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B66" t="s">
-        <v>50</v>
+        <v>318</v>
       </c>
       <c r="C66" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="D66" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E66" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F66" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="G66" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="H66" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I66" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J66" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K66" t="s">
-        <v>178</v>
+        <v>89</v>
       </c>
       <c r="L66" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M66" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N66" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O66" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B67" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C67" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D67" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E67" t="s">
         <v>19</v>
       </c>
       <c r="F67" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G67" t="s">
-        <v>37</v>
+        <v>322</v>
       </c>
       <c r="H67" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I67" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J67" t="s">
-        <v>320</v>
+        <v>218</v>
       </c>
       <c r="K67" t="s">
-        <v>321</v>
+        <v>200</v>
       </c>
       <c r="L67" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M67" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N67" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O67" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B68" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C68" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="D68" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E68" t="s">
         <v>19</v>
       </c>
       <c r="F68" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G68" t="s">
-        <v>21</v>
+        <v>121</v>
       </c>
       <c r="H68" t="s">
         <v>22</v>
@@ -5339,113 +5309,113 @@
         <v>23</v>
       </c>
       <c r="J68" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K68" t="s">
-        <v>39</v>
+        <v>235</v>
       </c>
       <c r="L68" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M68" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N68" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O68" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B69" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="C69" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="D69" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E69" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F69" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G69" t="s">
-        <v>21</v>
+        <v>121</v>
       </c>
       <c r="H69" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I69" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J69" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K69" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="L69" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M69" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N69" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O69" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B70" t="s">
-        <v>330</v>
+        <v>37</v>
       </c>
       <c r="C70" t="s">
-        <v>157</v>
+        <v>38</v>
       </c>
       <c r="D70" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E70" t="s">
         <v>19</v>
       </c>
       <c r="F70" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G70" t="s">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="H70" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I70" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J70" t="s">
-        <v>123</v>
+        <v>331</v>
       </c>
       <c r="K70" t="s">
-        <v>331</v>
+        <v>139</v>
       </c>
       <c r="L70" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M70" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N70" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O70" t="s">
         <v>332</v>
@@ -5456,231 +5426,231 @@
         <v>333</v>
       </c>
       <c r="B71" t="s">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="C71" t="s">
-        <v>151</v>
+        <v>83</v>
       </c>
       <c r="D71" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E71" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F71" t="s">
+        <v>137</v>
+      </c>
+      <c r="G71" t="s">
+        <v>49</v>
+      </c>
+      <c r="H71" t="s">
+        <v>55</v>
+      </c>
+      <c r="I71" t="s">
+        <v>21</v>
+      </c>
+      <c r="J71" t="s">
         <v>334</v>
       </c>
-      <c r="G71" t="s">
-        <v>21</v>
-      </c>
-      <c r="H71" t="s">
-        <v>22</v>
-      </c>
-      <c r="I71" t="s">
-        <v>23</v>
-      </c>
-      <c r="J71" t="s">
+      <c r="K71" t="s">
+        <v>62</v>
+      </c>
+      <c r="L71" t="s">
+        <v>21</v>
+      </c>
+      <c r="M71" t="s">
+        <v>140</v>
+      </c>
+      <c r="N71" t="s">
+        <v>21</v>
+      </c>
+      <c r="O71" t="s">
         <v>335</v>
-      </c>
-      <c r="K71" t="s">
-        <v>336</v>
-      </c>
-      <c r="L71" t="s">
-        <v>23</v>
-      </c>
-      <c r="M71" t="s">
-        <v>23</v>
-      </c>
-      <c r="N71" t="s">
-        <v>23</v>
-      </c>
-      <c r="O71" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>336</v>
+      </c>
+      <c r="B72" t="s">
+        <v>37</v>
+      </c>
+      <c r="C72" t="s">
+        <v>38</v>
+      </c>
+      <c r="D72" t="s">
+        <v>18</v>
+      </c>
+      <c r="E72" t="s">
+        <v>19</v>
+      </c>
+      <c r="F72" t="s">
+        <v>39</v>
+      </c>
+      <c r="G72" t="s">
+        <v>121</v>
+      </c>
+      <c r="H72" t="s">
+        <v>22</v>
+      </c>
+      <c r="I72" t="s">
+        <v>23</v>
+      </c>
+      <c r="J72" t="s">
+        <v>337</v>
+      </c>
+      <c r="K72" t="s">
         <v>338</v>
       </c>
-      <c r="B72" t="s">
-        <v>50</v>
-      </c>
-      <c r="C72" t="s">
-        <v>51</v>
-      </c>
-      <c r="D72" t="s">
-        <v>52</v>
-      </c>
-      <c r="E72" t="s">
-        <v>19</v>
-      </c>
-      <c r="F72" t="s">
-        <v>20</v>
-      </c>
-      <c r="G72" t="s">
-        <v>85</v>
-      </c>
-      <c r="H72" t="s">
-        <v>31</v>
-      </c>
-      <c r="I72" t="s">
-        <v>53</v>
-      </c>
-      <c r="J72" t="s">
+      <c r="L72" t="s">
+        <v>21</v>
+      </c>
+      <c r="M72" t="s">
+        <v>21</v>
+      </c>
+      <c r="N72" t="s">
+        <v>21</v>
+      </c>
+      <c r="O72" t="s">
         <v>339</v>
-      </c>
-      <c r="K72" t="s">
-        <v>124</v>
-      </c>
-      <c r="L72" t="s">
-        <v>23</v>
-      </c>
-      <c r="M72" t="s">
-        <v>23</v>
-      </c>
-      <c r="N72" t="s">
-        <v>23</v>
-      </c>
-      <c r="O72" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>340</v>
+      </c>
+      <c r="B73" t="s">
+        <v>126</v>
+      </c>
+      <c r="C73" t="s">
+        <v>21</v>
+      </c>
+      <c r="D73" t="s">
+        <v>21</v>
+      </c>
+      <c r="E73" t="s">
+        <v>30</v>
+      </c>
+      <c r="F73" t="s">
+        <v>31</v>
+      </c>
+      <c r="G73" t="s">
+        <v>49</v>
+      </c>
+      <c r="H73" t="s">
+        <v>22</v>
+      </c>
+      <c r="I73" t="s">
+        <v>21</v>
+      </c>
+      <c r="J73" t="s">
         <v>341</v>
       </c>
-      <c r="B73" t="s">
-        <v>50</v>
-      </c>
-      <c r="C73" t="s">
-        <v>51</v>
-      </c>
-      <c r="D73" t="s">
-        <v>52</v>
-      </c>
-      <c r="E73" t="s">
-        <v>19</v>
-      </c>
-      <c r="F73" t="s">
-        <v>20</v>
-      </c>
-      <c r="G73" t="s">
-        <v>21</v>
-      </c>
-      <c r="H73" t="s">
-        <v>31</v>
-      </c>
-      <c r="I73" t="s">
-        <v>53</v>
-      </c>
-      <c r="J73" t="s">
+      <c r="K73" t="s">
+        <v>66</v>
+      </c>
+      <c r="L73" t="s">
+        <v>21</v>
+      </c>
+      <c r="M73" t="s">
+        <v>21</v>
+      </c>
+      <c r="N73" t="s">
+        <v>21</v>
+      </c>
+      <c r="O73" t="s">
         <v>342</v>
-      </c>
-      <c r="K73" t="s">
-        <v>103</v>
-      </c>
-      <c r="L73" t="s">
-        <v>23</v>
-      </c>
-      <c r="M73" t="s">
-        <v>23</v>
-      </c>
-      <c r="N73" t="s">
-        <v>23</v>
-      </c>
-      <c r="O73" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>343</v>
+      </c>
+      <c r="B74" t="s">
+        <v>37</v>
+      </c>
+      <c r="C74" t="s">
+        <v>38</v>
+      </c>
+      <c r="D74" t="s">
+        <v>18</v>
+      </c>
+      <c r="E74" t="s">
+        <v>19</v>
+      </c>
+      <c r="F74" t="s">
+        <v>31</v>
+      </c>
+      <c r="G74" t="s">
+        <v>169</v>
+      </c>
+      <c r="H74" t="s">
+        <v>22</v>
+      </c>
+      <c r="I74" t="s">
+        <v>23</v>
+      </c>
+      <c r="J74" t="s">
         <v>344</v>
       </c>
-      <c r="B74" t="s">
-        <v>50</v>
-      </c>
-      <c r="C74" t="s">
-        <v>51</v>
-      </c>
-      <c r="D74" t="s">
-        <v>52</v>
-      </c>
-      <c r="E74" t="s">
-        <v>19</v>
-      </c>
-      <c r="F74" t="s">
-        <v>224</v>
-      </c>
-      <c r="G74" t="s">
+      <c r="K74" t="s">
+        <v>25</v>
+      </c>
+      <c r="L74" t="s">
+        <v>21</v>
+      </c>
+      <c r="M74" t="s">
+        <v>21</v>
+      </c>
+      <c r="N74" t="s">
+        <v>21</v>
+      </c>
+      <c r="O74" t="s">
         <v>345</v>
-      </c>
-      <c r="H74" t="s">
-        <v>31</v>
-      </c>
-      <c r="I74" t="s">
-        <v>53</v>
-      </c>
-      <c r="J74" t="s">
-        <v>66</v>
-      </c>
-      <c r="K74" t="s">
-        <v>206</v>
-      </c>
-      <c r="L74" t="s">
-        <v>23</v>
-      </c>
-      <c r="M74" t="s">
-        <v>23</v>
-      </c>
-      <c r="N74" t="s">
-        <v>23</v>
-      </c>
-      <c r="O74" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>346</v>
+      </c>
+      <c r="B75" t="s">
+        <v>37</v>
+      </c>
+      <c r="C75" t="s">
+        <v>38</v>
+      </c>
+      <c r="D75" t="s">
+        <v>18</v>
+      </c>
+      <c r="E75" t="s">
+        <v>19</v>
+      </c>
+      <c r="F75" t="s">
+        <v>39</v>
+      </c>
+      <c r="G75" t="s">
+        <v>40</v>
+      </c>
+      <c r="H75" t="s">
+        <v>22</v>
+      </c>
+      <c r="I75" t="s">
+        <v>23</v>
+      </c>
+      <c r="J75" t="s">
         <v>347</v>
-      </c>
-      <c r="B75" t="s">
-        <v>50</v>
-      </c>
-      <c r="C75" t="s">
-        <v>51</v>
-      </c>
-      <c r="D75" t="s">
-        <v>52</v>
-      </c>
-      <c r="E75" t="s">
-        <v>19</v>
-      </c>
-      <c r="F75" t="s">
-        <v>20</v>
-      </c>
-      <c r="G75" t="s">
-        <v>37</v>
-      </c>
-      <c r="H75" t="s">
-        <v>31</v>
-      </c>
-      <c r="I75" t="s">
-        <v>53</v>
-      </c>
-      <c r="J75" t="s">
-        <v>137</v>
       </c>
       <c r="K75" t="s">
         <v>348</v>
       </c>
       <c r="L75" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M75" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N75" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O75" t="s">
         <v>349</v>
@@ -5691,43 +5661,43 @@
         <v>350</v>
       </c>
       <c r="B76" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C76" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="D76" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E76" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F76" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G76" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="H76" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I76" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J76" t="s">
         <v>351</v>
       </c>
       <c r="K76" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="L76" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M76" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N76" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O76" t="s">
         <v>352</v>
@@ -5738,22 +5708,22 @@
         <v>353</v>
       </c>
       <c r="B77" t="s">
-        <v>354</v>
+        <v>28</v>
       </c>
       <c r="C77" t="s">
-        <v>355</v>
+        <v>29</v>
       </c>
       <c r="D77" t="s">
-        <v>356</v>
+        <v>18</v>
       </c>
       <c r="E77" t="s">
         <v>30</v>
       </c>
       <c r="F77" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G77" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="H77" t="s">
         <v>22</v>
@@ -5762,113 +5732,113 @@
         <v>23</v>
       </c>
       <c r="J77" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K77" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="L77" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M77" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N77" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O77" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B78" t="s">
-        <v>16</v>
+        <v>357</v>
       </c>
       <c r="C78" t="s">
-        <v>23</v>
+        <v>188</v>
       </c>
       <c r="D78" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E78" t="s">
         <v>19</v>
       </c>
       <c r="F78" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G78" t="s">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="H78" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I78" t="s">
         <v>23</v>
       </c>
       <c r="J78" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="K78" t="s">
+        <v>358</v>
+      </c>
+      <c r="L78" t="s">
+        <v>21</v>
+      </c>
+      <c r="M78" t="s">
+        <v>21</v>
+      </c>
+      <c r="N78" t="s">
+        <v>21</v>
+      </c>
+      <c r="O78" t="s">
         <v>359</v>
-      </c>
-      <c r="L78" t="s">
-        <v>23</v>
-      </c>
-      <c r="M78" t="s">
-        <v>23</v>
-      </c>
-      <c r="N78" t="s">
-        <v>23</v>
-      </c>
-      <c r="O78" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>360</v>
+      </c>
+      <c r="B79" t="s">
+        <v>135</v>
+      </c>
+      <c r="C79" t="s">
+        <v>182</v>
+      </c>
+      <c r="D79" t="s">
+        <v>77</v>
+      </c>
+      <c r="E79" t="s">
+        <v>19</v>
+      </c>
+      <c r="F79" t="s">
         <v>361</v>
       </c>
-      <c r="B79" t="s">
+      <c r="G79" t="s">
+        <v>49</v>
+      </c>
+      <c r="H79" t="s">
+        <v>55</v>
+      </c>
+      <c r="I79" t="s">
+        <v>21</v>
+      </c>
+      <c r="J79" t="s">
         <v>362</v>
       </c>
-      <c r="C79" t="s">
-        <v>29</v>
-      </c>
-      <c r="D79" t="s">
-        <v>30</v>
-      </c>
-      <c r="E79" t="s">
-        <v>30</v>
-      </c>
-      <c r="F79" t="s">
-        <v>45</v>
-      </c>
-      <c r="G79" t="s">
-        <v>23</v>
-      </c>
-      <c r="H79" t="s">
-        <v>22</v>
-      </c>
-      <c r="I79" t="s">
-        <v>23</v>
-      </c>
-      <c r="J79" t="s">
+      <c r="K79" t="s">
         <v>363</v>
       </c>
-      <c r="K79" t="s">
-        <v>311</v>
-      </c>
       <c r="L79" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M79" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N79" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O79" t="s">
         <v>364</v>
@@ -5879,22 +5849,22 @@
         <v>365</v>
       </c>
       <c r="B80" t="s">
-        <v>366</v>
+        <v>37</v>
       </c>
       <c r="C80" t="s">
-        <v>367</v>
+        <v>38</v>
       </c>
       <c r="D80" t="s">
-        <v>368</v>
+        <v>18</v>
       </c>
       <c r="E80" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F80" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G80" t="s">
-        <v>21</v>
+        <v>121</v>
       </c>
       <c r="H80" t="s">
         <v>22</v>
@@ -5903,139 +5873,139 @@
         <v>23</v>
       </c>
       <c r="J80" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="K80" t="s">
-        <v>370</v>
+        <v>157</v>
       </c>
       <c r="L80" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M80" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N80" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O80" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B81" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C81" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D81" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E81" t="s">
         <v>19</v>
       </c>
       <c r="F81" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G81" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="H81" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I81" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J81" t="s">
-        <v>123</v>
+        <v>369</v>
       </c>
       <c r="K81" t="s">
-        <v>182</v>
+        <v>139</v>
       </c>
       <c r="L81" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M81" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N81" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O81" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B82" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="C82" t="s">
-        <v>147</v>
+        <v>38</v>
       </c>
       <c r="D82" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E82" t="s">
         <v>19</v>
       </c>
       <c r="F82" t="s">
-        <v>20</v>
+        <v>252</v>
       </c>
       <c r="G82" t="s">
-        <v>21</v>
+        <v>372</v>
       </c>
       <c r="H82" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I82" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J82" t="s">
-        <v>375</v>
+        <v>106</v>
       </c>
       <c r="K82" t="s">
-        <v>115</v>
+        <v>235</v>
       </c>
       <c r="L82" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M82" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N82" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O82" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B83" t="s">
-        <v>378</v>
+        <v>37</v>
       </c>
       <c r="C83" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D83" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E83" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F83" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G83" t="s">
-        <v>294</v>
+        <v>40</v>
       </c>
       <c r="H83" t="s">
         <v>22</v>
@@ -6044,45 +6014,45 @@
         <v>23</v>
       </c>
       <c r="J83" t="s">
-        <v>379</v>
+        <v>170</v>
       </c>
       <c r="K83" t="s">
-        <v>348</v>
+        <v>375</v>
       </c>
       <c r="L83" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M83" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N83" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O83" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B84" t="s">
-        <v>366</v>
+        <v>28</v>
       </c>
       <c r="C84" t="s">
-        <v>382</v>
+        <v>29</v>
       </c>
       <c r="D84" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E84" t="s">
         <v>30</v>
       </c>
       <c r="F84" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G84" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="H84" t="s">
         <v>22</v>
@@ -6091,192 +6061,192 @@
         <v>23</v>
       </c>
       <c r="J84" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="K84" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="L84" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M84" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N84" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O84" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B85" t="s">
-        <v>50</v>
+        <v>381</v>
       </c>
       <c r="C85" t="s">
-        <v>51</v>
+        <v>382</v>
       </c>
       <c r="D85" t="s">
-        <v>52</v>
+        <v>383</v>
       </c>
       <c r="E85" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F85" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G85" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="H85" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I85" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J85" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="K85" t="s">
-        <v>124</v>
+        <v>200</v>
       </c>
       <c r="L85" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M85" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N85" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O85" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B86" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="C86" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="D86" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="E86" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F86" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G86" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H86" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I86" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J86" t="s">
-        <v>389</v>
+        <v>98</v>
       </c>
       <c r="K86" t="s">
-        <v>261</v>
+        <v>386</v>
       </c>
       <c r="L86" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M86" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N86" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O86" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B87" t="s">
-        <v>156</v>
+        <v>389</v>
       </c>
       <c r="C87" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="D87" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E87" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F87" t="s">
         <v>20</v>
       </c>
       <c r="G87" t="s">
-        <v>136</v>
+        <v>21</v>
       </c>
       <c r="H87" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I87" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J87" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="K87" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="L87" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M87" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N87" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O87" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>392</v>
+      </c>
+      <c r="B88" t="s">
+        <v>393</v>
+      </c>
+      <c r="C88" t="s">
         <v>394</v>
       </c>
-      <c r="B88" t="s">
-        <v>330</v>
-      </c>
-      <c r="C88" t="s">
-        <v>157</v>
-      </c>
       <c r="D88" t="s">
-        <v>52</v>
+        <v>395</v>
       </c>
       <c r="E88" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F88" t="s">
-        <v>224</v>
+        <v>39</v>
       </c>
       <c r="G88" t="s">
-        <v>395</v>
+        <v>49</v>
       </c>
       <c r="H88" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I88" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J88" t="s">
         <v>396</v>
@@ -6285,13 +6255,13 @@
         <v>397</v>
       </c>
       <c r="L88" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M88" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N88" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O88" t="s">
         <v>398</v>
@@ -6302,22 +6272,22 @@
         <v>399</v>
       </c>
       <c r="B89" t="s">
-        <v>400</v>
+        <v>37</v>
       </c>
       <c r="C89" t="s">
-        <v>204</v>
+        <v>38</v>
       </c>
       <c r="D89" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E89" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F89" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="G89" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="H89" t="s">
         <v>22</v>
@@ -6326,45 +6296,45 @@
         <v>23</v>
       </c>
       <c r="J89" t="s">
-        <v>163</v>
+        <v>33</v>
       </c>
       <c r="K89" t="s">
-        <v>359</v>
+        <v>212</v>
       </c>
       <c r="L89" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M89" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N89" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O89" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B90" t="s">
-        <v>366</v>
+        <v>16</v>
       </c>
       <c r="C90" t="s">
-        <v>382</v>
+        <v>17</v>
       </c>
       <c r="D90" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E90" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F90" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G90" t="s">
-        <v>403</v>
+        <v>49</v>
       </c>
       <c r="H90" t="s">
         <v>22</v>
@@ -6373,160 +6343,160 @@
         <v>23</v>
       </c>
       <c r="J90" t="s">
-        <v>54</v>
+        <v>402</v>
       </c>
       <c r="K90" t="s">
-        <v>404</v>
+        <v>150</v>
       </c>
       <c r="L90" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M90" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N90" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O90" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>404</v>
+      </c>
+      <c r="B91" t="s">
+        <v>405</v>
+      </c>
+      <c r="C91" t="s">
+        <v>83</v>
+      </c>
+      <c r="D91" t="s">
+        <v>30</v>
+      </c>
+      <c r="E91" t="s">
+        <v>30</v>
+      </c>
+      <c r="F91" t="s">
+        <v>31</v>
+      </c>
+      <c r="G91" t="s">
+        <v>322</v>
+      </c>
+      <c r="H91" t="s">
+        <v>55</v>
+      </c>
+      <c r="I91" t="s">
+        <v>21</v>
+      </c>
+      <c r="J91" t="s">
         <v>406</v>
       </c>
-      <c r="B91" t="s">
-        <v>99</v>
-      </c>
-      <c r="C91" t="s">
-        <v>151</v>
-      </c>
-      <c r="D91" t="s">
-        <v>18</v>
-      </c>
-      <c r="E91" t="s">
-        <v>19</v>
-      </c>
-      <c r="F91" t="s">
-        <v>334</v>
-      </c>
-      <c r="G91" t="s">
-        <v>21</v>
-      </c>
-      <c r="H91" t="s">
-        <v>22</v>
-      </c>
-      <c r="I91" t="s">
-        <v>23</v>
-      </c>
-      <c r="J91" t="s">
+      <c r="K91" t="s">
+        <v>375</v>
+      </c>
+      <c r="L91" t="s">
+        <v>21</v>
+      </c>
+      <c r="M91" t="s">
+        <v>21</v>
+      </c>
+      <c r="N91" t="s">
+        <v>21</v>
+      </c>
+      <c r="O91" t="s">
         <v>407</v>
-      </c>
-      <c r="K91" t="s">
-        <v>201</v>
-      </c>
-      <c r="L91" t="s">
-        <v>23</v>
-      </c>
-      <c r="M91" t="s">
-        <v>23</v>
-      </c>
-      <c r="N91" t="s">
-        <v>23</v>
-      </c>
-      <c r="O91" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>408</v>
+      </c>
+      <c r="B92" t="s">
+        <v>393</v>
+      </c>
+      <c r="C92" t="s">
         <v>409</v>
       </c>
-      <c r="B92" t="s">
+      <c r="D92" t="s">
+        <v>18</v>
+      </c>
+      <c r="E92" t="s">
+        <v>30</v>
+      </c>
+      <c r="F92" t="s">
+        <v>39</v>
+      </c>
+      <c r="G92" t="s">
+        <v>49</v>
+      </c>
+      <c r="H92" t="s">
+        <v>55</v>
+      </c>
+      <c r="I92" t="s">
+        <v>21</v>
+      </c>
+      <c r="J92" t="s">
         <v>410</v>
       </c>
-      <c r="C92" t="s">
-        <v>23</v>
-      </c>
-      <c r="D92" t="s">
-        <v>23</v>
-      </c>
-      <c r="E92" t="s">
-        <v>19</v>
-      </c>
-      <c r="F92" t="s">
-        <v>20</v>
-      </c>
-      <c r="G92" t="s">
-        <v>21</v>
-      </c>
-      <c r="H92" t="s">
-        <v>31</v>
-      </c>
-      <c r="I92" t="s">
-        <v>23</v>
-      </c>
-      <c r="J92" t="s">
+      <c r="K92" t="s">
+        <v>164</v>
+      </c>
+      <c r="L92" t="s">
+        <v>21</v>
+      </c>
+      <c r="M92" t="s">
+        <v>21</v>
+      </c>
+      <c r="N92" t="s">
+        <v>21</v>
+      </c>
+      <c r="O92" t="s">
         <v>411</v>
-      </c>
-      <c r="K92" t="s">
-        <v>261</v>
-      </c>
-      <c r="L92" t="s">
-        <v>23</v>
-      </c>
-      <c r="M92" t="s">
-        <v>23</v>
-      </c>
-      <c r="N92" t="s">
-        <v>23</v>
-      </c>
-      <c r="O92" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>412</v>
+      </c>
+      <c r="B93" t="s">
+        <v>37</v>
+      </c>
+      <c r="C93" t="s">
+        <v>38</v>
+      </c>
+      <c r="D93" t="s">
+        <v>18</v>
+      </c>
+      <c r="E93" t="s">
+        <v>19</v>
+      </c>
+      <c r="F93" t="s">
+        <v>39</v>
+      </c>
+      <c r="G93" t="s">
+        <v>121</v>
+      </c>
+      <c r="H93" t="s">
+        <v>22</v>
+      </c>
+      <c r="I93" t="s">
+        <v>23</v>
+      </c>
+      <c r="J93" t="s">
         <v>413</v>
       </c>
-      <c r="B93" t="s">
-        <v>50</v>
-      </c>
-      <c r="C93" t="s">
-        <v>51</v>
-      </c>
-      <c r="D93" t="s">
-        <v>52</v>
-      </c>
-      <c r="E93" t="s">
-        <v>19</v>
-      </c>
-      <c r="F93" t="s">
-        <v>20</v>
-      </c>
-      <c r="G93" t="s">
-        <v>85</v>
-      </c>
-      <c r="H93" t="s">
-        <v>31</v>
-      </c>
-      <c r="I93" t="s">
-        <v>53</v>
-      </c>
-      <c r="J93" t="s">
-        <v>66</v>
-      </c>
       <c r="K93" t="s">
-        <v>39</v>
+        <v>157</v>
       </c>
       <c r="L93" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M93" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N93" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O93" t="s">
         <v>414</v>
@@ -6537,43 +6507,43 @@
         <v>415</v>
       </c>
       <c r="B94" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C94" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="D94" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E94" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F94" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G94" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="H94" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I94" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J94" t="s">
         <v>416</v>
       </c>
       <c r="K94" t="s">
-        <v>178</v>
+        <v>289</v>
       </c>
       <c r="L94" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M94" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N94" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O94" t="s">
         <v>417</v>
@@ -6584,304 +6554,304 @@
         <v>418</v>
       </c>
       <c r="B95" t="s">
-        <v>50</v>
+        <v>187</v>
       </c>
       <c r="C95" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="D95" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="E95" t="s">
         <v>19</v>
       </c>
       <c r="F95" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G95" t="s">
-        <v>37</v>
+        <v>169</v>
       </c>
       <c r="H95" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I95" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J95" t="s">
-        <v>54</v>
+        <v>419</v>
       </c>
       <c r="K95" t="s">
-        <v>62</v>
+        <v>375</v>
       </c>
       <c r="L95" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M95" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N95" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O95" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B96" t="s">
-        <v>16</v>
+        <v>357</v>
       </c>
       <c r="C96" t="s">
-        <v>421</v>
+        <v>188</v>
       </c>
       <c r="D96" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E96" t="s">
         <v>19</v>
       </c>
       <c r="F96" t="s">
-        <v>20</v>
+        <v>252</v>
       </c>
       <c r="G96" t="s">
-        <v>21</v>
+        <v>422</v>
       </c>
       <c r="H96" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I96" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J96" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K96" t="s">
-        <v>104</v>
+        <v>424</v>
       </c>
       <c r="L96" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M96" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N96" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O96" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B97" t="s">
-        <v>16</v>
+        <v>427</v>
       </c>
       <c r="C97" t="s">
-        <v>421</v>
+        <v>233</v>
       </c>
       <c r="D97" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E97" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F97" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="G97" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="H97" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I97" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J97" t="s">
-        <v>425</v>
+        <v>194</v>
       </c>
       <c r="K97" t="s">
-        <v>234</v>
+        <v>386</v>
       </c>
       <c r="L97" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M97" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N97" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O97" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B98" t="s">
-        <v>50</v>
+        <v>393</v>
       </c>
       <c r="C98" t="s">
-        <v>51</v>
+        <v>409</v>
       </c>
       <c r="D98" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E98" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F98" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G98" t="s">
-        <v>37</v>
+        <v>430</v>
       </c>
       <c r="H98" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I98" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J98" t="s">
-        <v>428</v>
+        <v>98</v>
       </c>
       <c r="K98" t="s">
-        <v>321</v>
+        <v>431</v>
       </c>
       <c r="L98" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M98" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N98" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O98" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B99" t="s">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="C99" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="D99" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="E99" t="s">
         <v>19</v>
       </c>
       <c r="F99" t="s">
-        <v>20</v>
+        <v>361</v>
       </c>
       <c r="G99" t="s">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="H99" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I99" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J99" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="K99" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="L99" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M99" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N99" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O99" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B100" t="s">
-        <v>99</v>
+        <v>437</v>
       </c>
       <c r="C100" t="s">
-        <v>151</v>
+        <v>21</v>
       </c>
       <c r="D100" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E100" t="s">
         <v>19</v>
       </c>
       <c r="F100" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="G100" t="s">
-        <v>434</v>
+        <v>49</v>
       </c>
       <c r="H100" t="s">
         <v>22</v>
       </c>
       <c r="I100" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J100" t="s">
-        <v>123</v>
+        <v>438</v>
       </c>
       <c r="K100" t="s">
-        <v>103</v>
+        <v>289</v>
       </c>
       <c r="L100" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M100" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="N100" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O100" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B101" t="s">
-        <v>437</v>
+        <v>37</v>
       </c>
       <c r="C101" t="s">
-        <v>438</v>
+        <v>38</v>
       </c>
       <c r="D101" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E101" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F101" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G101" t="s">
-        <v>21</v>
+        <v>121</v>
       </c>
       <c r="H101" t="s">
         <v>22</v>
@@ -6890,113 +6860,113 @@
         <v>23</v>
       </c>
       <c r="J101" t="s">
-        <v>439</v>
+        <v>106</v>
       </c>
       <c r="K101" t="s">
-        <v>252</v>
+        <v>89</v>
       </c>
       <c r="L101" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M101" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N101" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O101" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B102" t="s">
-        <v>290</v>
+        <v>37</v>
       </c>
       <c r="C102" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D102" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E102" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F102" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G102" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="H102" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I102" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J102" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K102" t="s">
-        <v>234</v>
+        <v>25</v>
       </c>
       <c r="L102" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M102" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N102" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O102" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B103" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="C103" t="s">
-        <v>147</v>
+        <v>38</v>
       </c>
       <c r="D103" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E103" t="s">
         <v>19</v>
       </c>
       <c r="F103" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G103" t="s">
+        <v>40</v>
+      </c>
+      <c r="H103" t="s">
+        <v>22</v>
+      </c>
+      <c r="I103" t="s">
         <v>23</v>
       </c>
-      <c r="H103" t="s">
-        <v>31</v>
-      </c>
-      <c r="I103" t="s">
-        <v>53</v>
-      </c>
       <c r="J103" t="s">
-        <v>445</v>
+        <v>98</v>
       </c>
       <c r="K103" t="s">
-        <v>230</v>
+        <v>103</v>
       </c>
       <c r="L103" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M103" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N103" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O103" t="s">
         <v>446</v>
@@ -7007,43 +6977,43 @@
         <v>447</v>
       </c>
       <c r="B104" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="C104" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D104" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E104" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F104" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G104" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="H104" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I104" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J104" t="s">
         <v>448</v>
       </c>
       <c r="K104" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="L104" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M104" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N104" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O104" t="s">
         <v>449</v>
@@ -7054,13 +7024,13 @@
         <v>450</v>
       </c>
       <c r="B105" t="s">
-        <v>330</v>
+        <v>75</v>
       </c>
       <c r="C105" t="s">
-        <v>157</v>
+        <v>70</v>
       </c>
       <c r="D105" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E105" t="s">
         <v>19</v>
@@ -7069,54 +7039,54 @@
         <v>101</v>
       </c>
       <c r="G105" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="H105" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I105" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J105" t="s">
         <v>451</v>
       </c>
       <c r="K105" t="s">
+        <v>262</v>
+      </c>
+      <c r="L105" t="s">
+        <v>21</v>
+      </c>
+      <c r="M105" t="s">
+        <v>21</v>
+      </c>
+      <c r="N105" t="s">
+        <v>21</v>
+      </c>
+      <c r="O105" t="s">
         <v>452</v>
-      </c>
-      <c r="L105" t="s">
-        <v>23</v>
-      </c>
-      <c r="M105" t="s">
-        <v>104</v>
-      </c>
-      <c r="N105" t="s">
-        <v>23</v>
-      </c>
-      <c r="O105" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B106" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="C106" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="D106" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E106" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F106" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G106" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="H106" t="s">
         <v>22</v>
@@ -7125,33 +7095,33 @@
         <v>23</v>
       </c>
       <c r="J106" t="s">
+        <v>454</v>
+      </c>
+      <c r="K106" t="s">
+        <v>348</v>
+      </c>
+      <c r="L106" t="s">
+        <v>21</v>
+      </c>
+      <c r="M106" t="s">
+        <v>21</v>
+      </c>
+      <c r="N106" t="s">
+        <v>21</v>
+      </c>
+      <c r="O106" t="s">
         <v>455</v>
-      </c>
-      <c r="K106" t="s">
-        <v>115</v>
-      </c>
-      <c r="L106" t="s">
-        <v>23</v>
-      </c>
-      <c r="M106" t="s">
-        <v>23</v>
-      </c>
-      <c r="N106" t="s">
-        <v>23</v>
-      </c>
-      <c r="O106" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B107" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="C107" t="s">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="D107" t="s">
         <v>18</v>
@@ -7160,10 +7130,10 @@
         <v>19</v>
       </c>
       <c r="F107" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="G107" t="s">
-        <v>458</v>
+        <v>189</v>
       </c>
       <c r="H107" t="s">
         <v>22</v>
@@ -7172,113 +7142,113 @@
         <v>23</v>
       </c>
       <c r="J107" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="K107" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="L107" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M107" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N107" t="s">
-        <v>460</v>
+        <v>21</v>
       </c>
       <c r="O107" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B108" t="s">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="C108" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="D108" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="E108" t="s">
         <v>19</v>
       </c>
       <c r="F108" t="s">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="G108" t="s">
-        <v>122</v>
+        <v>460</v>
       </c>
       <c r="H108" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I108" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J108" t="s">
-        <v>463</v>
+        <v>33</v>
       </c>
       <c r="K108" t="s">
-        <v>178</v>
+        <v>139</v>
       </c>
       <c r="L108" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M108" t="s">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="N108" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O108" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>462</v>
+      </c>
+      <c r="B109" t="s">
+        <v>463</v>
+      </c>
+      <c r="C109" t="s">
+        <v>464</v>
+      </c>
+      <c r="D109" t="s">
+        <v>21</v>
+      </c>
+      <c r="E109" t="s">
+        <v>30</v>
+      </c>
+      <c r="F109" t="s">
+        <v>31</v>
+      </c>
+      <c r="G109" t="s">
+        <v>49</v>
+      </c>
+      <c r="H109" t="s">
+        <v>55</v>
+      </c>
+      <c r="I109" t="s">
+        <v>21</v>
+      </c>
+      <c r="J109" t="s">
         <v>465</v>
       </c>
-      <c r="B109" t="s">
-        <v>50</v>
-      </c>
-      <c r="C109" t="s">
-        <v>51</v>
-      </c>
-      <c r="D109" t="s">
-        <v>52</v>
-      </c>
-      <c r="E109" t="s">
-        <v>19</v>
-      </c>
-      <c r="F109" t="s">
-        <v>36</v>
-      </c>
-      <c r="G109" t="s">
-        <v>122</v>
-      </c>
-      <c r="H109" t="s">
-        <v>31</v>
-      </c>
-      <c r="I109" t="s">
-        <v>53</v>
-      </c>
-      <c r="J109" t="s">
-        <v>54</v>
-      </c>
       <c r="K109" t="s">
-        <v>115</v>
+        <v>280</v>
       </c>
       <c r="L109" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M109" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N109" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O109" t="s">
         <v>466</v>
@@ -7289,60 +7259,60 @@
         <v>467</v>
       </c>
       <c r="B110" t="s">
-        <v>146</v>
+        <v>318</v>
       </c>
       <c r="C110" t="s">
-        <v>147</v>
+        <v>93</v>
       </c>
       <c r="D110" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E110" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F110" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G110" t="s">
+        <v>49</v>
+      </c>
+      <c r="H110" t="s">
+        <v>22</v>
+      </c>
+      <c r="I110" t="s">
+        <v>23</v>
+      </c>
+      <c r="J110" t="s">
         <v>468</v>
       </c>
-      <c r="H110" t="s">
-        <v>31</v>
-      </c>
-      <c r="I110" t="s">
-        <v>53</v>
-      </c>
-      <c r="J110" t="s">
+      <c r="K110" t="s">
+        <v>262</v>
+      </c>
+      <c r="L110" t="s">
+        <v>21</v>
+      </c>
+      <c r="M110" t="s">
+        <v>21</v>
+      </c>
+      <c r="N110" t="s">
+        <v>21</v>
+      </c>
+      <c r="O110" t="s">
         <v>469</v>
-      </c>
-      <c r="K110" t="s">
-        <v>160</v>
-      </c>
-      <c r="L110" t="s">
-        <v>23</v>
-      </c>
-      <c r="M110" t="s">
-        <v>23</v>
-      </c>
-      <c r="N110" t="s">
-        <v>23</v>
-      </c>
-      <c r="O110" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B111" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="C111" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="D111" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E111" t="s">
         <v>19</v>
@@ -7351,122 +7321,122 @@
         <v>20</v>
       </c>
       <c r="G111" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="H111" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I111" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J111" t="s">
+        <v>471</v>
+      </c>
+      <c r="K111" t="s">
+        <v>258</v>
+      </c>
+      <c r="L111" t="s">
+        <v>21</v>
+      </c>
+      <c r="M111" t="s">
+        <v>21</v>
+      </c>
+      <c r="N111" t="s">
+        <v>21</v>
+      </c>
+      <c r="O111" t="s">
         <v>472</v>
-      </c>
-      <c r="K111" t="s">
-        <v>248</v>
-      </c>
-      <c r="L111" t="s">
-        <v>23</v>
-      </c>
-      <c r="M111" t="s">
-        <v>23</v>
-      </c>
-      <c r="N111" t="s">
-        <v>23</v>
-      </c>
-      <c r="O111" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>473</v>
+      </c>
+      <c r="B112" t="s">
+        <v>28</v>
+      </c>
+      <c r="C112" t="s">
+        <v>29</v>
+      </c>
+      <c r="D112" t="s">
+        <v>18</v>
+      </c>
+      <c r="E112" t="s">
+        <v>30</v>
+      </c>
+      <c r="F112" t="s">
+        <v>31</v>
+      </c>
+      <c r="G112" t="s">
+        <v>49</v>
+      </c>
+      <c r="H112" t="s">
+        <v>22</v>
+      </c>
+      <c r="I112" t="s">
+        <v>23</v>
+      </c>
+      <c r="J112" t="s">
         <v>474</v>
       </c>
-      <c r="B112" t="s">
-        <v>50</v>
-      </c>
-      <c r="C112" t="s">
-        <v>51</v>
-      </c>
-      <c r="D112" t="s">
-        <v>52</v>
-      </c>
-      <c r="E112" t="s">
-        <v>19</v>
-      </c>
-      <c r="F112" t="s">
-        <v>36</v>
-      </c>
-      <c r="G112" t="s">
-        <v>21</v>
-      </c>
-      <c r="H112" t="s">
-        <v>31</v>
-      </c>
-      <c r="I112" t="s">
-        <v>53</v>
-      </c>
-      <c r="J112" t="s">
+      <c r="K112" t="s">
+        <v>154</v>
+      </c>
+      <c r="L112" t="s">
+        <v>21</v>
+      </c>
+      <c r="M112" t="s">
+        <v>21</v>
+      </c>
+      <c r="N112" t="s">
+        <v>21</v>
+      </c>
+      <c r="O112" t="s">
         <v>475</v>
-      </c>
-      <c r="K112" t="s">
-        <v>201</v>
-      </c>
-      <c r="L112" t="s">
-        <v>23</v>
-      </c>
-      <c r="M112" t="s">
-        <v>23</v>
-      </c>
-      <c r="N112" t="s">
-        <v>23</v>
-      </c>
-      <c r="O112" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>476</v>
+      </c>
+      <c r="B113" t="s">
+        <v>357</v>
+      </c>
+      <c r="C113" t="s">
+        <v>188</v>
+      </c>
+      <c r="D113" t="s">
+        <v>18</v>
+      </c>
+      <c r="E113" t="s">
+        <v>19</v>
+      </c>
+      <c r="F113" t="s">
+        <v>137</v>
+      </c>
+      <c r="G113" t="s">
+        <v>49</v>
+      </c>
+      <c r="H113" t="s">
+        <v>22</v>
+      </c>
+      <c r="I113" t="s">
+        <v>23</v>
+      </c>
+      <c r="J113" t="s">
         <v>477</v>
       </c>
-      <c r="B113" t="s">
-        <v>50</v>
-      </c>
-      <c r="C113" t="s">
-        <v>51</v>
-      </c>
-      <c r="D113" t="s">
-        <v>52</v>
-      </c>
-      <c r="E113" t="s">
-        <v>19</v>
-      </c>
-      <c r="F113" t="s">
-        <v>107</v>
-      </c>
-      <c r="G113" t="s">
-        <v>77</v>
-      </c>
-      <c r="H113" t="s">
-        <v>31</v>
-      </c>
-      <c r="I113" t="s">
-        <v>53</v>
-      </c>
-      <c r="J113" t="s">
+      <c r="K113" t="s">
         <v>478</v>
       </c>
-      <c r="K113" t="s">
-        <v>47</v>
-      </c>
       <c r="L113" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M113" t="s">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="N113" t="s">
-        <v>213</v>
+        <v>21</v>
       </c>
       <c r="O113" t="s">
         <v>479</v>
@@ -7477,43 +7447,43 @@
         <v>480</v>
       </c>
       <c r="B114" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C114" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D114" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E114" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F114" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G114" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="H114" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I114" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J114" t="s">
         <v>481</v>
       </c>
       <c r="K114" t="s">
-        <v>103</v>
+        <v>150</v>
       </c>
       <c r="L114" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M114" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N114" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O114" t="s">
         <v>482</v>
@@ -7524,539 +7494,539 @@
         <v>483</v>
       </c>
       <c r="B115" t="s">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="C115" t="s">
-        <v>51</v>
+        <v>182</v>
       </c>
       <c r="D115" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="E115" t="s">
         <v>19</v>
       </c>
       <c r="F115" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G115" t="s">
         <v>484</v>
       </c>
       <c r="H115" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I115" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J115" t="s">
-        <v>303</v>
+        <v>485</v>
       </c>
       <c r="K115" t="s">
-        <v>397</v>
+        <v>110</v>
       </c>
       <c r="L115" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M115" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N115" t="s">
-        <v>23</v>
+        <v>486</v>
       </c>
       <c r="O115" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B116" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C116" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D116" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E116" t="s">
         <v>19</v>
       </c>
       <c r="F116" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G116" t="s">
-        <v>487</v>
+        <v>32</v>
       </c>
       <c r="H116" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I116" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J116" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="K116" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="L116" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M116" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N116" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O116" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B117" t="s">
-        <v>354</v>
+        <v>37</v>
       </c>
       <c r="C117" t="s">
-        <v>355</v>
+        <v>38</v>
       </c>
       <c r="D117" t="s">
-        <v>356</v>
+        <v>18</v>
       </c>
       <c r="E117" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F117" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="G117" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="H117" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I117" t="s">
-        <v>271</v>
+        <v>23</v>
       </c>
       <c r="J117" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="K117" t="s">
-        <v>359</v>
+        <v>150</v>
       </c>
       <c r="L117" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M117" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N117" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O117" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B118" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="C118" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="D118" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E118" t="s">
         <v>19</v>
       </c>
       <c r="F118" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G118" t="s">
-        <v>37</v>
+        <v>494</v>
       </c>
       <c r="H118" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I118" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J118" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="K118" t="s">
-        <v>119</v>
+        <v>191</v>
       </c>
       <c r="L118" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M118" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N118" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O118" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B119" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C119" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D119" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E119" t="s">
         <v>19</v>
       </c>
       <c r="F119" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G119" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H119" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I119" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J119" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="K119" t="s">
-        <v>72</v>
+        <v>276</v>
       </c>
       <c r="L119" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M119" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N119" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O119" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B120" t="s">
-        <v>330</v>
+        <v>37</v>
       </c>
       <c r="C120" t="s">
-        <v>157</v>
+        <v>38</v>
       </c>
       <c r="D120" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E120" t="s">
         <v>19</v>
       </c>
       <c r="F120" t="s">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="G120" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="H120" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I120" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J120" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="K120" t="s">
-        <v>234</v>
+        <v>34</v>
       </c>
       <c r="L120" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M120" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="N120" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O120" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B121" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C121" t="s">
-        <v>268</v>
+        <v>38</v>
       </c>
       <c r="D121" t="s">
-        <v>269</v>
+        <v>18</v>
       </c>
       <c r="E121" t="s">
         <v>19</v>
       </c>
       <c r="F121" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="G121" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="H121" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I121" t="s">
-        <v>271</v>
+        <v>23</v>
       </c>
       <c r="J121" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K121" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="L121" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M121" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N121" t="s">
-        <v>23</v>
+        <v>241</v>
       </c>
       <c r="O121" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B122" t="s">
-        <v>330</v>
+        <v>16</v>
       </c>
       <c r="C122" t="s">
-        <v>157</v>
+        <v>17</v>
       </c>
       <c r="D122" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E122" t="s">
         <v>19</v>
       </c>
       <c r="F122" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G122" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="H122" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I122" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J122" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="K122" t="s">
-        <v>307</v>
+        <v>139</v>
       </c>
       <c r="L122" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M122" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N122" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O122" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B123" t="s">
-        <v>330</v>
+        <v>37</v>
       </c>
       <c r="C123" t="s">
-        <v>157</v>
+        <v>38</v>
       </c>
       <c r="D123" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E123" t="s">
         <v>19</v>
       </c>
       <c r="F123" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G123" t="s">
-        <v>21</v>
+        <v>510</v>
       </c>
       <c r="H123" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I123" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J123" t="s">
-        <v>508</v>
+        <v>331</v>
       </c>
       <c r="K123" t="s">
-        <v>164</v>
+        <v>424</v>
       </c>
       <c r="L123" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M123" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N123" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O123" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B124" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="C124" t="s">
-        <v>147</v>
+        <v>38</v>
       </c>
       <c r="D124" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E124" t="s">
         <v>19</v>
       </c>
       <c r="F124" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G124" t="s">
-        <v>136</v>
+        <v>513</v>
       </c>
       <c r="H124" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I124" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J124" t="s">
-        <v>163</v>
+        <v>514</v>
       </c>
       <c r="K124" t="s">
-        <v>280</v>
+        <v>66</v>
       </c>
       <c r="L124" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M124" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N124" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O124" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B125" t="s">
-        <v>50</v>
+        <v>381</v>
       </c>
       <c r="C125" t="s">
-        <v>51</v>
+        <v>382</v>
       </c>
       <c r="D125" t="s">
-        <v>52</v>
+        <v>383</v>
       </c>
       <c r="E125" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F125" t="s">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="G125" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="H125" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I125" t="s">
-        <v>53</v>
+        <v>299</v>
       </c>
       <c r="J125" t="s">
-        <v>513</v>
+        <v>122</v>
       </c>
       <c r="K125" t="s">
-        <v>514</v>
+        <v>386</v>
       </c>
       <c r="L125" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M125" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N125" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O125" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B126" t="s">
-        <v>112</v>
+        <v>37</v>
       </c>
       <c r="C126" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="D126" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E126" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F126" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G126" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="H126" t="s">
         <v>22</v>
@@ -8065,33 +8035,33 @@
         <v>23</v>
       </c>
       <c r="J126" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="K126" t="s">
-        <v>67</v>
+        <v>154</v>
       </c>
       <c r="L126" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M126" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N126" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O126" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B127" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="C127" t="s">
-        <v>151</v>
+        <v>38</v>
       </c>
       <c r="D127" t="s">
         <v>18</v>
@@ -8100,78 +8070,78 @@
         <v>19</v>
       </c>
       <c r="F127" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G127" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="H127" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I127" t="s">
         <v>23</v>
       </c>
       <c r="J127" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="K127" t="s">
-        <v>521</v>
+        <v>110</v>
       </c>
       <c r="L127" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M127" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N127" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O127" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B128" t="s">
-        <v>90</v>
+        <v>357</v>
       </c>
       <c r="C128" t="s">
-        <v>524</v>
+        <v>188</v>
       </c>
       <c r="D128" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E128" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F128" t="s">
-        <v>36</v>
+        <v>137</v>
       </c>
       <c r="G128" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="H128" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I128" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J128" t="s">
         <v>525</v>
       </c>
       <c r="K128" t="s">
-        <v>115</v>
+        <v>262</v>
       </c>
       <c r="L128" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M128" t="s">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="N128" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O128" t="s">
         <v>526</v>
@@ -8182,43 +8152,43 @@
         <v>527</v>
       </c>
       <c r="B129" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="C129" t="s">
-        <v>151</v>
+        <v>296</v>
       </c>
       <c r="D129" t="s">
-        <v>18</v>
+        <v>297</v>
       </c>
       <c r="E129" t="s">
         <v>19</v>
       </c>
       <c r="F129" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G129" t="s">
-        <v>37</v>
+        <v>169</v>
       </c>
       <c r="H129" t="s">
         <v>22</v>
       </c>
       <c r="I129" t="s">
-        <v>23</v>
+        <v>299</v>
       </c>
       <c r="J129" t="s">
         <v>528</v>
       </c>
       <c r="K129" t="s">
-        <v>348</v>
+        <v>164</v>
       </c>
       <c r="L129" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M129" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N129" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O129" t="s">
         <v>529</v>
@@ -8229,10 +8199,10 @@
         <v>530</v>
       </c>
       <c r="B130" t="s">
-        <v>99</v>
+        <v>357</v>
       </c>
       <c r="C130" t="s">
-        <v>151</v>
+        <v>188</v>
       </c>
       <c r="D130" t="s">
         <v>18</v>
@@ -8241,13 +8211,13 @@
         <v>19</v>
       </c>
       <c r="F130" t="s">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="G130" t="s">
-        <v>21</v>
+        <v>169</v>
       </c>
       <c r="H130" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I130" t="s">
         <v>23</v>
@@ -8256,16 +8226,16 @@
         <v>531</v>
       </c>
       <c r="K130" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="L130" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M130" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="N130" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O130" t="s">
         <v>532</v>
@@ -8276,43 +8246,43 @@
         <v>533</v>
       </c>
       <c r="B131" t="s">
-        <v>267</v>
+        <v>357</v>
       </c>
       <c r="C131" t="s">
-        <v>51</v>
+        <v>188</v>
       </c>
       <c r="D131" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E131" t="s">
         <v>19</v>
       </c>
       <c r="F131" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G131" t="s">
+        <v>49</v>
+      </c>
+      <c r="H131" t="s">
+        <v>22</v>
+      </c>
+      <c r="I131" t="s">
+        <v>23</v>
+      </c>
+      <c r="J131" t="s">
         <v>534</v>
       </c>
-      <c r="H131" t="s">
-        <v>31</v>
-      </c>
-      <c r="I131" t="s">
-        <v>53</v>
-      </c>
-      <c r="J131" t="s">
-        <v>276</v>
-      </c>
       <c r="K131" t="s">
-        <v>280</v>
+        <v>195</v>
       </c>
       <c r="L131" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M131" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N131" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O131" t="s">
         <v>535</v>
@@ -8323,22 +8293,22 @@
         <v>536</v>
       </c>
       <c r="B132" t="s">
-        <v>330</v>
+        <v>16</v>
       </c>
       <c r="C132" t="s">
-        <v>157</v>
+        <v>17</v>
       </c>
       <c r="D132" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E132" t="s">
         <v>19</v>
       </c>
       <c r="F132" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G132" t="s">
-        <v>21</v>
+        <v>169</v>
       </c>
       <c r="H132" t="s">
         <v>22</v>
@@ -8347,45 +8317,45 @@
         <v>23</v>
       </c>
       <c r="J132" t="s">
+        <v>194</v>
+      </c>
+      <c r="K132" t="s">
+        <v>308</v>
+      </c>
+      <c r="L132" t="s">
+        <v>21</v>
+      </c>
+      <c r="M132" t="s">
+        <v>21</v>
+      </c>
+      <c r="N132" t="s">
+        <v>21</v>
+      </c>
+      <c r="O132" t="s">
         <v>537</v>
-      </c>
-      <c r="K132" t="s">
-        <v>119</v>
-      </c>
-      <c r="L132" t="s">
-        <v>23</v>
-      </c>
-      <c r="M132" t="s">
-        <v>23</v>
-      </c>
-      <c r="N132" t="s">
-        <v>23</v>
-      </c>
-      <c r="O132" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B133" t="s">
-        <v>354</v>
+        <v>37</v>
       </c>
       <c r="C133" t="s">
-        <v>355</v>
+        <v>38</v>
       </c>
       <c r="D133" t="s">
-        <v>356</v>
+        <v>18</v>
       </c>
       <c r="E133" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F133" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="G133" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="H133" t="s">
         <v>22</v>
@@ -8394,19 +8364,19 @@
         <v>23</v>
       </c>
       <c r="J133" t="s">
+        <v>539</v>
+      </c>
+      <c r="K133" t="s">
         <v>540</v>
       </c>
-      <c r="K133" t="s">
-        <v>234</v>
-      </c>
       <c r="L133" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M133" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N133" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O133" t="s">
         <v>541</v>
@@ -8417,43 +8387,43 @@
         <v>542</v>
       </c>
       <c r="B134" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="C134" t="s">
-        <v>524</v>
+        <v>148</v>
       </c>
       <c r="D134" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E134" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F134" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G134" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="H134" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I134" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J134" t="s">
         <v>543</v>
       </c>
       <c r="K134" t="s">
-        <v>241</v>
+        <v>66</v>
       </c>
       <c r="L134" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M134" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N134" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O134" t="s">
         <v>544</v>
@@ -8464,69 +8434,69 @@
         <v>545</v>
       </c>
       <c r="B135" t="s">
+        <v>135</v>
+      </c>
+      <c r="C135" t="s">
+        <v>182</v>
+      </c>
+      <c r="D135" t="s">
+        <v>77</v>
+      </c>
+      <c r="E135" t="s">
+        <v>19</v>
+      </c>
+      <c r="F135" t="s">
+        <v>31</v>
+      </c>
+      <c r="G135" t="s">
+        <v>49</v>
+      </c>
+      <c r="H135" t="s">
+        <v>22</v>
+      </c>
+      <c r="I135" t="s">
+        <v>21</v>
+      </c>
+      <c r="J135" t="s">
         <v>546</v>
       </c>
-      <c r="C135" t="s">
-        <v>135</v>
-      </c>
-      <c r="D135" t="s">
-        <v>52</v>
-      </c>
-      <c r="E135" t="s">
-        <v>30</v>
-      </c>
-      <c r="F135" t="s">
-        <v>36</v>
-      </c>
-      <c r="G135" t="s">
+      <c r="K135" t="s">
         <v>547</v>
       </c>
-      <c r="H135" t="s">
-        <v>22</v>
-      </c>
-      <c r="I135" t="s">
-        <v>23</v>
-      </c>
-      <c r="J135" t="s">
+      <c r="L135" t="s">
+        <v>21</v>
+      </c>
+      <c r="M135" t="s">
+        <v>21</v>
+      </c>
+      <c r="N135" t="s">
+        <v>21</v>
+      </c>
+      <c r="O135" t="s">
         <v>548</v>
-      </c>
-      <c r="K135" t="s">
-        <v>115</v>
-      </c>
-      <c r="L135" t="s">
-        <v>23</v>
-      </c>
-      <c r="M135" t="s">
-        <v>23</v>
-      </c>
-      <c r="N135" t="s">
-        <v>23</v>
-      </c>
-      <c r="O135" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>549</v>
+      </c>
+      <c r="B136" t="s">
+        <v>126</v>
+      </c>
+      <c r="C136" t="s">
         <v>550</v>
       </c>
-      <c r="B136" t="s">
-        <v>58</v>
-      </c>
-      <c r="C136" t="s">
-        <v>59</v>
-      </c>
       <c r="D136" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E136" t="s">
         <v>30</v>
       </c>
       <c r="F136" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G136" t="s">
-        <v>158</v>
+        <v>40</v>
       </c>
       <c r="H136" t="s">
         <v>22</v>
@@ -8538,16 +8508,16 @@
         <v>551</v>
       </c>
       <c r="K136" t="s">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="L136" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M136" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N136" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O136" t="s">
         <v>552</v>
@@ -8558,43 +8528,43 @@
         <v>553</v>
       </c>
       <c r="B137" t="s">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="C137" t="s">
-        <v>524</v>
+        <v>182</v>
       </c>
       <c r="D137" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="E137" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F137" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G137" t="s">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="H137" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I137" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="J137" t="s">
         <v>554</v>
       </c>
       <c r="K137" t="s">
-        <v>55</v>
+        <v>375</v>
       </c>
       <c r="L137" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M137" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N137" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O137" t="s">
         <v>555</v>
@@ -8605,231 +8575,231 @@
         <v>556</v>
       </c>
       <c r="B138" t="s">
-        <v>378</v>
+        <v>135</v>
       </c>
       <c r="C138" t="s">
-        <v>29</v>
+        <v>182</v>
       </c>
       <c r="D138" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="E138" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F138" t="s">
-        <v>36</v>
+        <v>137</v>
       </c>
       <c r="G138" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="H138" t="s">
         <v>22</v>
       </c>
       <c r="I138" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J138" t="s">
-        <v>66</v>
+        <v>557</v>
       </c>
       <c r="K138" t="s">
-        <v>230</v>
+        <v>72</v>
       </c>
       <c r="L138" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M138" t="s">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="N138" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O138" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B139" t="s">
-        <v>28</v>
+        <v>295</v>
       </c>
       <c r="C139" t="s">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="D139" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E139" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F139" t="s">
-        <v>107</v>
+        <v>31</v>
       </c>
       <c r="G139" t="s">
-        <v>294</v>
+        <v>560</v>
       </c>
       <c r="H139" t="s">
         <v>22</v>
       </c>
       <c r="I139" t="s">
-        <v>559</v>
+        <v>23</v>
       </c>
       <c r="J139" t="s">
-        <v>560</v>
+        <v>304</v>
       </c>
       <c r="K139" t="s">
-        <v>104</v>
+        <v>308</v>
       </c>
       <c r="L139" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M139" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N139" t="s">
+        <v>21</v>
+      </c>
+      <c r="O139" t="s">
         <v>561</v>
-      </c>
-      <c r="O139" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>562</v>
+      </c>
+      <c r="B140" t="s">
+        <v>357</v>
+      </c>
+      <c r="C140" t="s">
+        <v>188</v>
+      </c>
+      <c r="D140" t="s">
+        <v>18</v>
+      </c>
+      <c r="E140" t="s">
+        <v>19</v>
+      </c>
+      <c r="F140" t="s">
+        <v>39</v>
+      </c>
+      <c r="G140" t="s">
+        <v>49</v>
+      </c>
+      <c r="H140" t="s">
+        <v>55</v>
+      </c>
+      <c r="I140" t="s">
+        <v>21</v>
+      </c>
+      <c r="J140" t="s">
         <v>563</v>
       </c>
-      <c r="B140" t="s">
-        <v>112</v>
-      </c>
-      <c r="C140" t="s">
-        <v>113</v>
-      </c>
-      <c r="D140" t="s">
-        <v>44</v>
-      </c>
-      <c r="E140" t="s">
-        <v>30</v>
-      </c>
-      <c r="F140" t="s">
-        <v>36</v>
-      </c>
-      <c r="G140" t="s">
-        <v>77</v>
-      </c>
-      <c r="H140" t="s">
-        <v>22</v>
-      </c>
-      <c r="I140" t="s">
-        <v>23</v>
-      </c>
-      <c r="J140" t="s">
+      <c r="K140" t="s">
+        <v>154</v>
+      </c>
+      <c r="L140" t="s">
+        <v>21</v>
+      </c>
+      <c r="M140" t="s">
+        <v>21</v>
+      </c>
+      <c r="N140" t="s">
+        <v>21</v>
+      </c>
+      <c r="O140" t="s">
         <v>564</v>
-      </c>
-      <c r="K140" t="s">
-        <v>514</v>
-      </c>
-      <c r="L140" t="s">
-        <v>23</v>
-      </c>
-      <c r="M140" t="s">
-        <v>23</v>
-      </c>
-      <c r="N140" t="s">
-        <v>23</v>
-      </c>
-      <c r="O140" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B141" t="s">
-        <v>112</v>
+        <v>381</v>
       </c>
       <c r="C141" t="s">
-        <v>113</v>
+        <v>382</v>
       </c>
       <c r="D141" t="s">
-        <v>44</v>
+        <v>383</v>
       </c>
       <c r="E141" t="s">
         <v>30</v>
       </c>
       <c r="F141" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="G141" t="s">
-        <v>21</v>
+        <v>121</v>
       </c>
       <c r="H141" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="I141" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J141" t="s">
+        <v>566</v>
+      </c>
+      <c r="K141" t="s">
+        <v>262</v>
+      </c>
+      <c r="L141" t="s">
+        <v>21</v>
+      </c>
+      <c r="M141" t="s">
+        <v>21</v>
+      </c>
+      <c r="N141" t="s">
+        <v>21</v>
+      </c>
+      <c r="O141" t="s">
         <v>567</v>
-      </c>
-      <c r="K141" t="s">
-        <v>280</v>
-      </c>
-      <c r="L141" t="s">
-        <v>23</v>
-      </c>
-      <c r="M141" t="s">
-        <v>23</v>
-      </c>
-      <c r="N141" t="s">
-        <v>23</v>
-      </c>
-      <c r="O141" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>568</v>
+      </c>
+      <c r="B142" t="s">
+        <v>75</v>
+      </c>
+      <c r="C142" t="s">
+        <v>550</v>
+      </c>
+      <c r="D142" t="s">
+        <v>18</v>
+      </c>
+      <c r="E142" t="s">
+        <v>19</v>
+      </c>
+      <c r="F142" t="s">
+        <v>39</v>
+      </c>
+      <c r="G142" t="s">
+        <v>113</v>
+      </c>
+      <c r="H142" t="s">
+        <v>22</v>
+      </c>
+      <c r="I142" t="s">
+        <v>23</v>
+      </c>
+      <c r="J142" t="s">
         <v>569</v>
       </c>
-      <c r="B142" t="s">
-        <v>146</v>
-      </c>
-      <c r="C142" t="s">
-        <v>147</v>
-      </c>
-      <c r="D142" t="s">
-        <v>52</v>
-      </c>
-      <c r="E142" t="s">
-        <v>19</v>
-      </c>
-      <c r="F142" t="s">
-        <v>36</v>
-      </c>
-      <c r="G142" t="s">
-        <v>21</v>
-      </c>
-      <c r="H142" t="s">
-        <v>31</v>
-      </c>
-      <c r="I142" t="s">
-        <v>53</v>
-      </c>
-      <c r="J142" t="s">
-        <v>499</v>
-      </c>
       <c r="K142" t="s">
-        <v>201</v>
+        <v>269</v>
       </c>
       <c r="L142" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M142" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N142" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O142" t="s">
         <v>570</v>
@@ -8840,281 +8810,93 @@
         <v>571</v>
       </c>
       <c r="B143" t="s">
-        <v>330</v>
+        <v>572</v>
       </c>
       <c r="C143" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="D143" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E143" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F143" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G143" t="s">
-        <v>21</v>
+        <v>573</v>
       </c>
       <c r="H143" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="I143" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J143" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="K143" t="s">
-        <v>252</v>
+        <v>150</v>
       </c>
       <c r="L143" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M143" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N143" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O143" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B144" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="C144" t="s">
-        <v>421</v>
+        <v>29</v>
       </c>
       <c r="D144" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E144" t="s">
         <v>30</v>
       </c>
       <c r="F144" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G144" t="s">
-        <v>122</v>
+        <v>189</v>
       </c>
       <c r="H144" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="I144" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J144" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="K144" t="s">
-        <v>164</v>
+        <v>227</v>
       </c>
       <c r="L144" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M144" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N144" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O144" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>577</v>
-      </c>
-      <c r="B145" t="s">
-        <v>112</v>
-      </c>
-      <c r="C145" t="s">
-        <v>113</v>
-      </c>
-      <c r="D145" t="s">
-        <v>44</v>
-      </c>
-      <c r="E145" t="s">
-        <v>30</v>
-      </c>
-      <c r="F145" t="s">
-        <v>36</v>
-      </c>
-      <c r="G145" t="s">
-        <v>21</v>
-      </c>
-      <c r="H145" t="s">
-        <v>22</v>
-      </c>
-      <c r="I145" t="s">
-        <v>23</v>
-      </c>
-      <c r="J145" t="s">
         <v>578</v>
-      </c>
-      <c r="K145" t="s">
-        <v>206</v>
-      </c>
-      <c r="L145" t="s">
-        <v>23</v>
-      </c>
-      <c r="M145" t="s">
-        <v>23</v>
-      </c>
-      <c r="N145" t="s">
-        <v>23</v>
-      </c>
-      <c r="O145" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>580</v>
-      </c>
-      <c r="B146" t="s">
-        <v>362</v>
-      </c>
-      <c r="C146" t="s">
-        <v>29</v>
-      </c>
-      <c r="D146" t="s">
-        <v>30</v>
-      </c>
-      <c r="E146" t="s">
-        <v>30</v>
-      </c>
-      <c r="F146" t="s">
-        <v>45</v>
-      </c>
-      <c r="G146" t="s">
-        <v>23</v>
-      </c>
-      <c r="H146" t="s">
-        <v>22</v>
-      </c>
-      <c r="I146" t="s">
-        <v>23</v>
-      </c>
-      <c r="J146" t="s">
-        <v>581</v>
-      </c>
-      <c r="K146" t="s">
-        <v>178</v>
-      </c>
-      <c r="L146" t="s">
-        <v>23</v>
-      </c>
-      <c r="M146" t="s">
-        <v>23</v>
-      </c>
-      <c r="N146" t="s">
-        <v>23</v>
-      </c>
-      <c r="O146" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>583</v>
-      </c>
-      <c r="B147" t="s">
-        <v>58</v>
-      </c>
-      <c r="C147" t="s">
-        <v>59</v>
-      </c>
-      <c r="D147" t="s">
-        <v>52</v>
-      </c>
-      <c r="E147" t="s">
-        <v>30</v>
-      </c>
-      <c r="F147" t="s">
-        <v>36</v>
-      </c>
-      <c r="G147" t="s">
-        <v>85</v>
-      </c>
-      <c r="H147" t="s">
-        <v>22</v>
-      </c>
-      <c r="I147" t="s">
-        <v>23</v>
-      </c>
-      <c r="J147" t="s">
-        <v>584</v>
-      </c>
-      <c r="K147" t="s">
-        <v>169</v>
-      </c>
-      <c r="L147" t="s">
-        <v>23</v>
-      </c>
-      <c r="M147" t="s">
-        <v>23</v>
-      </c>
-      <c r="N147" t="s">
-        <v>23</v>
-      </c>
-      <c r="O147" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>586</v>
-      </c>
-      <c r="B148" t="s">
-        <v>58</v>
-      </c>
-      <c r="C148" t="s">
-        <v>59</v>
-      </c>
-      <c r="D148" t="s">
-        <v>52</v>
-      </c>
-      <c r="E148" t="s">
-        <v>30</v>
-      </c>
-      <c r="F148" t="s">
-        <v>20</v>
-      </c>
-      <c r="G148" t="s">
-        <v>85</v>
-      </c>
-      <c r="H148" t="s">
-        <v>31</v>
-      </c>
-      <c r="I148" t="s">
-        <v>53</v>
-      </c>
-      <c r="J148" t="s">
-        <v>587</v>
-      </c>
-      <c r="K148" t="s">
-        <v>307</v>
-      </c>
-      <c r="L148" t="s">
-        <v>23</v>
-      </c>
-      <c r="M148" t="s">
-        <v>23</v>
-      </c>
-      <c r="N148" t="s">
-        <v>23</v>
-      </c>
-      <c r="O148" t="s">
-        <v>588</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C43DD094-A26C-4A35-81E2-0B1C355455CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E48D0742-7A99-43DF-AAE7-D8FA55A52C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2550" yWindow="2550" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2160" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2160" uniqueCount="576">
   <si>
     <t>Time</t>
   </si>
@@ -62,33 +62,165 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>04/23/2026 1:47:25 PM</t>
+  </si>
+  <si>
+    <t>662 - Heavy</t>
+  </si>
+  <si>
+    <t>Drew Template</t>
+  </si>
+  <si>
+    <t>Active Drivers, Heavy Haul</t>
+  </si>
+  <si>
+    <t>HAAS Alert, Heavy Haul</t>
+  </si>
+  <si>
+    <t>Harsh Brake</t>
+  </si>
+  <si>
+    <t>Moderate Traffic</t>
+  </si>
+  <si>
+    <t>Coached</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>8401 Washington Boulevard, Beaumont, TX, 77707</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>0.61</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bbab-17ef-5346-9a45-c49e8341e9be</t>
+  </si>
+  <si>
+    <t>04/22/2026 6:29:50 AM</t>
+  </si>
+  <si>
+    <t>632 - Heavy</t>
+  </si>
+  <si>
+    <t>Gary Worley</t>
+  </si>
+  <si>
+    <t>No Seat Belt</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>Eddie Bowden</t>
+  </si>
+  <si>
+    <t>Fred Hartman Bridge, Baytown, TX</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b4f4-1f22-5ef3-9175-aee791790b8b</t>
+  </si>
+  <si>
+    <t>04/21/2026 5:20:10 PM</t>
+  </si>
+  <si>
+    <t>669 - Heavy</t>
+  </si>
+  <si>
+    <t>Jason Walker</t>
+  </si>
+  <si>
+    <t>Active Drivers, Towing and Recovery</t>
+  </si>
+  <si>
+    <t>Mobile Usage</t>
+  </si>
+  <si>
+    <t>Wet Road, Light Traffic, Raining</t>
+  </si>
+  <si>
+    <t>Tim Neff Jr.</t>
+  </si>
+  <si>
+    <t>I 10, Eminence, TX, 77597</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b221-27f0-520a-b7e1-6dca1413a74b</t>
+  </si>
+  <si>
+    <t>04/21/2026 2:19:20 PM</t>
+  </si>
+  <si>
+    <t>Wet Road, Light Traffic</t>
+  </si>
+  <si>
+    <t>West Cardinal Drive, Beaumont, TX, 77710</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b17b-997e-5ccd-9142-896d210e168f</t>
+  </si>
+  <si>
+    <t>04/20/2026 10:49:13 AM</t>
+  </si>
+  <si>
+    <t>680 - Medium</t>
+  </si>
+  <si>
+    <t>Jesus Carbajal</t>
+  </si>
+  <si>
+    <t>HAAS Alert, Towing and Recovery</t>
+  </si>
+  <si>
+    <t>Obstructed Camera</t>
+  </si>
+  <si>
+    <t>State Highway 124, Cheek, TX, 77705</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ab94-df4e-5e43-8f70-06189ab78268</t>
+  </si>
+  <si>
+    <t>04/18/2026 8:25:57 AM</t>
+  </si>
+  <si>
+    <t>658 - Medium</t>
+  </si>
+  <si>
+    <t>Paul Kunze Jr</t>
+  </si>
+  <si>
+    <t>Construction, Light Traffic</t>
+  </si>
+  <si>
+    <t>I 10, Beaumont, TX, 77702</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a0c4-fdcf-57c3-b241-7891a9a8e817</t>
+  </si>
+  <si>
     <t>04/16/2026 11:41:19 AM</t>
   </si>
   <si>
-    <t>680 - Medium</t>
-  </si>
-  <si>
-    <t>Jesus Carbajal</t>
-  </si>
-  <si>
-    <t>Active Drivers, Towing and Recovery</t>
-  </si>
-  <si>
-    <t>HAAS Alert, Towing and Recovery</t>
-  </si>
-  <si>
-    <t>Obstructed Camera</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
-    <t>Tim Neff Jr.</t>
-  </si>
-  <si>
     <t>Eastex Freeway Frontage Road, Beaumont, TX, 77702</t>
   </si>
   <si>
@@ -101,21 +233,6 @@
     <t>04/15/2026 11:09:32 AM</t>
   </si>
   <si>
-    <t>669 - Heavy</t>
-  </si>
-  <si>
-    <t>Jason Walker</t>
-  </si>
-  <si>
-    <t>HAAS Alert, Heavy Haul</t>
-  </si>
-  <si>
-    <t>No Seat Belt</t>
-  </si>
-  <si>
-    <t>Construction, Light Traffic</t>
-  </si>
-  <si>
     <t>I 10;US 69;US 96;US 287, Beaumont, TX, 77702</t>
   </si>
   <si>
@@ -128,15 +245,6 @@
     <t>04/14/2026 11:07:04 PM</t>
   </si>
   <si>
-    <t>658 - Medium</t>
-  </si>
-  <si>
-    <t>Paul Kunze Jr</t>
-  </si>
-  <si>
-    <t>Mobile Usage</t>
-  </si>
-  <si>
     <t>Light Traffic, Night</t>
   </si>
   <si>
@@ -155,15 +263,6 @@
     <t>693 - Heavy</t>
   </si>
   <si>
-    <t>Drew Template</t>
-  </si>
-  <si>
-    <t>Active Drivers, Heavy Haul</t>
-  </si>
-  <si>
-    <t>Harsh Brake</t>
-  </si>
-  <si>
     <t>Light Traffic</t>
   </si>
   <si>
@@ -182,9 +281,6 @@
     <t>04/14/2026 5:19:07 PM</t>
   </si>
   <si>
-    <t>Coached</t>
-  </si>
-  <si>
     <t>1193 US 90, Broussard, LA, 70518</t>
   </si>
   <si>
@@ -335,9 +431,6 @@
     <t>04/06/2026 9:54:40 AM</t>
   </si>
   <si>
-    <t>State Highway 124, Cheek, TX, 77705</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456349-e5b4-55ac-a43b-944299eef0c4</t>
   </si>
   <si>
@@ -356,12 +449,6 @@
     <t>04/03/2026 8:23:50 AM</t>
   </si>
   <si>
-    <t>Moderate Traffic</t>
-  </si>
-  <si>
-    <t>I 10, Eminence, TX, 77597</t>
-  </si>
-  <si>
     <t>74</t>
   </si>
   <si>
@@ -380,9 +467,6 @@
     <t>04/02/2026 10:12:18 AM</t>
   </si>
   <si>
-    <t>Wet Road, Light Traffic</t>
-  </si>
-  <si>
     <t>I 10;TX 130, Seguin, TX, 78156</t>
   </si>
   <si>
@@ -458,12 +542,6 @@
     <t>04/01/2026 12:52:39 PM</t>
   </si>
   <si>
-    <t>632 - Heavy</t>
-  </si>
-  <si>
-    <t>Gary Worley</t>
-  </si>
-  <si>
     <t>Folsom Drive, Beaumont, TX, 77706</t>
   </si>
   <si>
@@ -527,9 +605,6 @@
     <t>Passengers, Light Traffic</t>
   </si>
   <si>
-    <t>West Cardinal Drive, Beaumont, TX, 77710</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445443b-80c2-56be-a0b5-4ec2bfd564b2</t>
   </si>
   <si>
@@ -542,9 +617,6 @@
     <t>1399 Eastex Freeway, Beaumont, TX, 77706</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>0.66</t>
   </si>
   <si>
@@ -791,18 +863,12 @@
     <t>Farm to Market Road 363, Kirbyville, TX, 75956</t>
   </si>
   <si>
-    <t>63</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f97b-c1cc-5dd2-aafa-07cf63494074</t>
   </si>
   <si>
     <t>03/16/2026 6:25:17 PM</t>
   </si>
   <si>
-    <t>662 - Heavy</t>
-  </si>
-  <si>
     <t>62</t>
   </si>
   <si>
@@ -914,12 +980,6 @@
     <t>Construction, Passengers, Light Traffic</t>
   </si>
   <si>
-    <t>Eddie Bowden</t>
-  </si>
-  <si>
-    <t>I 10, Beaumont, TX, 77702</t>
-  </si>
-  <si>
     <t>49</t>
   </si>
   <si>
@@ -1031,9 +1091,6 @@
     <t>15303 State Highway 124, Fannett, TX, 77705</t>
   </si>
   <si>
-    <t>48</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c4f8-88db-5151-b3b9-552cfc8fbb82</t>
   </si>
   <si>
@@ -1061,9 +1118,6 @@
     <t>4362 Fannett Road, Beaumont, TX, 77705</t>
   </si>
   <si>
-    <t>31</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c103-aad0-52bd-972b-fc2503a6c1d1</t>
   </si>
   <si>
@@ -1208,9 +1262,6 @@
     <t>US 69;US 96;US 287, Beaumont, TX, 77710</t>
   </si>
   <si>
-    <t>56</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459c3a-1681-58e8-ab56-ffd196753d0d</t>
   </si>
   <si>
@@ -1692,66 +1743,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fa50-c3b4-52c1-896a-0cf878990d74</t>
-  </si>
-  <si>
-    <t>01/24/2026 7:00:47 PM</t>
-  </si>
-  <si>
-    <t>Wet Road, Light Traffic, Night</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f2aa-eeb0-5cc9-84ff-30906247e8c7</t>
-  </si>
-  <si>
-    <t>01/23/2026 2:46:39 PM</t>
-  </si>
-  <si>
-    <t>1584 Main Lane, Beaumont, TX, 77713</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ec9b-ea7b-5c5b-8cd4-f8d38216eab6</t>
-  </si>
-  <si>
-    <t>01/23/2026 8:26:01 AM</t>
-  </si>
-  <si>
-    <t>I 10, Baytown, TX, 77523</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445eb3f-6ea2-5300-9498-4fd2b0859d4a</t>
-  </si>
-  <si>
-    <t>01/22/2026 11:44:52 AM</t>
-  </si>
-  <si>
-    <t>East Freeway, 5.3 mi NNE Baytown, Harris County, TX, 77521</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e6cf-2141-5e7d-8736-9bfcfb2dddc0</t>
-  </si>
-  <si>
-    <t>01/21/2026 12:35:34 PM</t>
-  </si>
-  <si>
-    <t>629 - Heavy</t>
-  </si>
-  <si>
-    <t>Emergency Lights, Wet Road, Moderate Traffic, Raining</t>
-  </si>
-  <si>
-    <t>2740 Ruth Street, Sulphur, LA, 70665</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e1d7-2f05-54aa-a298-65e74a18b9d9</t>
-  </si>
-  <si>
-    <t>01/19/2026 5:42:18 PM</t>
-  </si>
-  <si>
-    <t>I 10, 11.6 mi SW Beaumont, Jefferson County, TX</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d8a3-4a9e-5da1-8727-16449fee6525</t>
   </si>
 </sst>
 </file>
@@ -2213,201 +2204,201 @@
         <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
         <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
         <v>31</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I4" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
         <v>48</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" t="s">
         <v>49</v>
       </c>
-      <c r="H5" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>50</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" t="s">
         <v>51</v>
-      </c>
-      <c r="L5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" t="s">
-        <v>21</v>
-      </c>
-      <c r="N5" t="s">
-        <v>52</v>
-      </c>
-      <c r="O5" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
         <v>54</v>
       </c>
-      <c r="B6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" t="s">
-        <v>46</v>
-      </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="H6" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="I6" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N6" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="O6" t="s">
         <v>59</v>
@@ -2418,231 +2409,231 @@
         <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G7" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I7" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H8" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I8" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
         <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G9" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="H9" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I9" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" t="s">
         <v>76</v>
       </c>
-      <c r="D10" t="s">
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>43</v>
+      </c>
+      <c r="J10" t="s">
         <v>77</v>
       </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" t="s">
-        <v>49</v>
-      </c>
-      <c r="H10" t="s">
-        <v>55</v>
-      </c>
-      <c r="I10" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>78</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O10" t="s">
         <v>79</v>
-      </c>
-      <c r="L10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" t="s">
-        <v>21</v>
-      </c>
-      <c r="N10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O10" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" t="s">
         <v>81</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" t="s">
         <v>82</v>
       </c>
-      <c r="C11" t="s">
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" t="s">
         <v>83</v>
       </c>
-      <c r="D11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" t="s">
-        <v>49</v>
-      </c>
-      <c r="H11" t="s">
-        <v>55</v>
-      </c>
-      <c r="I11" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>84</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" t="s">
+        <v>23</v>
+      </c>
+      <c r="N11" t="s">
         <v>85</v>
-      </c>
-      <c r="L11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" t="s">
-        <v>21</v>
-      </c>
-      <c r="N11" t="s">
-        <v>21</v>
       </c>
       <c r="O11" t="s">
         <v>86</v>
@@ -2653,28 +2644,28 @@
         <v>87</v>
       </c>
       <c r="B12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" t="s">
         <v>82</v>
       </c>
-      <c r="C12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" t="s">
-        <v>40</v>
-      </c>
       <c r="H12" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="I12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J12" t="s">
         <v>88</v>
@@ -2683,107 +2674,107 @@
         <v>89</v>
       </c>
       <c r="L12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N12" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="O12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" t="s">
+        <v>43</v>
+      </c>
+      <c r="J13" t="s">
         <v>93</v>
       </c>
-      <c r="D13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G13" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" t="s">
-        <v>55</v>
-      </c>
-      <c r="I13" t="s">
-        <v>21</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>94</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13" t="s">
+        <v>23</v>
+      </c>
+      <c r="N13" t="s">
+        <v>23</v>
+      </c>
+      <c r="O13" t="s">
         <v>95</v>
-      </c>
-      <c r="L13" t="s">
-        <v>21</v>
-      </c>
-      <c r="M13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N13" t="s">
-        <v>21</v>
-      </c>
-      <c r="O13" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G14" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="H14" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I14" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J14" t="s">
+        <v>97</v>
+      </c>
+      <c r="K14" t="s">
         <v>98</v>
       </c>
-      <c r="K14" t="s">
-        <v>72</v>
-      </c>
       <c r="L14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O14" t="s">
         <v>99</v>
@@ -2794,22 +2785,22 @@
         <v>100</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F15" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="G15" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="H15" t="s">
         <v>22</v>
@@ -2818,92 +2809,92 @@
         <v>23</v>
       </c>
       <c r="J15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L15" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M15" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N15" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>108</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G16" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s">
         <v>22</v>
       </c>
       <c r="I16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J16" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="K16" t="s">
-        <v>66</v>
+        <v>111</v>
       </c>
       <c r="L16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O16" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s">
         <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G17" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="H17" t="s">
         <v>22</v>
@@ -2912,80 +2903,80 @@
         <v>23</v>
       </c>
       <c r="J17" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="K17" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="L17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O17" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>114</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="E18" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="G18" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="H18" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="I18" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J18" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="K18" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="L18" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M18" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N18" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O18" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>124</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>125</v>
       </c>
       <c r="D19" t="s">
         <v>18</v>
@@ -2994,10 +2985,10 @@
         <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G19" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="H19" t="s">
         <v>22</v>
@@ -3006,254 +2997,254 @@
         <v>23</v>
       </c>
       <c r="J19" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="K19" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="L19" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M19" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N19" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O19" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F20" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G20" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="H20" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I20" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J20" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="K20" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="L20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O20" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B21" t="s">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="E21" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="G21" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I21" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J21" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K21" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="L21" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M21" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N21" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O21" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>101</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F22" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G22" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="H22" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I22" t="s">
         <v>23</v>
       </c>
       <c r="J22" t="s">
-        <v>131</v>
+        <v>57</v>
       </c>
       <c r="K22" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="L22" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M22" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N22" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O22" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B23" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E23" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F23" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="G23" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="H23" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="I23" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J23" t="s">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="K23" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="L23" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M23" t="s">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="N23" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O23" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="E24" t="s">
         <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>48</v>
+        <v>133</v>
       </c>
       <c r="G24" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="H24" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="I24" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J24" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="K24" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="L24" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M24" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N24" t="s">
-        <v>144</v>
+        <v>23</v>
       </c>
       <c r="O24" t="s">
         <v>145</v>
@@ -3264,184 +3255,184 @@
         <v>146</v>
       </c>
       <c r="B25" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25" t="s">
+        <v>41</v>
+      </c>
+      <c r="G25" t="s">
+        <v>82</v>
+      </c>
+      <c r="H25" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" t="s">
+        <v>43</v>
+      </c>
+      <c r="J25" t="s">
+        <v>130</v>
+      </c>
+      <c r="K25" t="s">
         <v>147</v>
       </c>
-      <c r="C25" t="s">
+      <c r="L25" t="s">
+        <v>23</v>
+      </c>
+      <c r="M25" t="s">
+        <v>23</v>
+      </c>
+      <c r="N25" t="s">
+        <v>23</v>
+      </c>
+      <c r="O25" t="s">
         <v>148</v>
-      </c>
-      <c r="D25" t="s">
-        <v>47</v>
-      </c>
-      <c r="E25" t="s">
-        <v>30</v>
-      </c>
-      <c r="F25" t="s">
-        <v>31</v>
-      </c>
-      <c r="G25" t="s">
-        <v>49</v>
-      </c>
-      <c r="H25" t="s">
-        <v>55</v>
-      </c>
-      <c r="I25" t="s">
-        <v>21</v>
-      </c>
-      <c r="J25" t="s">
-        <v>149</v>
-      </c>
-      <c r="K25" t="s">
-        <v>150</v>
-      </c>
-      <c r="L25" t="s">
-        <v>21</v>
-      </c>
-      <c r="M25" t="s">
-        <v>21</v>
-      </c>
-      <c r="N25" t="s">
-        <v>21</v>
-      </c>
-      <c r="O25" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="D26" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E26" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F26" t="s">
         <v>31</v>
       </c>
       <c r="G26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H26" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I26" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J26" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="K26" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="L26" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M26" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N26" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O26" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G27" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="H27" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I27" t="s">
         <v>23</v>
       </c>
       <c r="J27" t="s">
-        <v>33</v>
+        <v>155</v>
       </c>
       <c r="K27" t="s">
+        <v>156</v>
+      </c>
+      <c r="L27" t="s">
+        <v>23</v>
+      </c>
+      <c r="M27" t="s">
+        <v>23</v>
+      </c>
+      <c r="N27" t="s">
+        <v>23</v>
+      </c>
+      <c r="O27" t="s">
         <v>157</v>
-      </c>
-      <c r="L27" t="s">
-        <v>21</v>
-      </c>
-      <c r="M27" t="s">
-        <v>21</v>
-      </c>
-      <c r="N27" t="s">
-        <v>21</v>
-      </c>
-      <c r="O27" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B28" t="s">
-        <v>147</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c r="D28" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E28" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
         <v>31</v>
       </c>
       <c r="G28" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="H28" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="I28" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J28" t="s">
+        <v>159</v>
+      </c>
+      <c r="K28" t="s">
         <v>160</v>
       </c>
-      <c r="K28" t="s">
-        <v>110</v>
-      </c>
       <c r="L28" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M28" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N28" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O28" t="s">
         <v>161</v>
@@ -3452,104 +3443,104 @@
         <v>162</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>163</v>
       </c>
       <c r="C29" t="s">
-        <v>21</v>
+        <v>164</v>
       </c>
       <c r="D29" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="E29" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F29" t="s">
-        <v>39</v>
+        <v>165</v>
       </c>
       <c r="G29" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="H29" t="s">
         <v>22</v>
       </c>
       <c r="I29" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J29" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="K29" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="L29" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M29" t="s">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="N29" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O29" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B30" t="s">
-        <v>167</v>
+        <v>107</v>
       </c>
       <c r="C30" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" t="s">
+        <v>109</v>
+      </c>
+      <c r="E30" t="s">
+        <v>55</v>
+      </c>
+      <c r="F30" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" t="s">
+        <v>82</v>
+      </c>
+      <c r="H30" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" t="s">
+        <v>171</v>
+      </c>
+      <c r="K30" t="s">
         <v>168</v>
       </c>
-      <c r="D30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30" t="s">
-        <v>30</v>
-      </c>
-      <c r="F30" t="s">
-        <v>137</v>
-      </c>
-      <c r="G30" t="s">
-        <v>169</v>
-      </c>
-      <c r="H30" t="s">
-        <v>55</v>
-      </c>
-      <c r="I30" t="s">
-        <v>21</v>
-      </c>
-      <c r="J30" t="s">
-        <v>170</v>
-      </c>
-      <c r="K30" t="s">
-        <v>150</v>
-      </c>
       <c r="L30" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M30" t="s">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="N30" t="s">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="O30" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B31" t="s">
-        <v>135</v>
+        <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>136</v>
+        <v>30</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
@@ -3558,31 +3549,31 @@
         <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="G31" t="s">
-        <v>173</v>
+        <v>82</v>
       </c>
       <c r="H31" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="I31" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J31" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L31" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M31" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N31" t="s">
-        <v>176</v>
+        <v>23</v>
       </c>
       <c r="O31" t="s">
         <v>177</v>
@@ -3593,104 +3584,104 @@
         <v>178</v>
       </c>
       <c r="B32" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D32" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
       </c>
       <c r="F32" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G32" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="H32" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I32" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J32" t="s">
         <v>179</v>
       </c>
       <c r="K32" t="s">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="L32" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M32" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N32" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O32" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B33" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>182</v>
+        <v>62</v>
       </c>
       <c r="D33" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="E33" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F33" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G33" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="H33" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I33" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J33" t="s">
+        <v>72</v>
+      </c>
+      <c r="K33" t="s">
         <v>183</v>
       </c>
-      <c r="K33" t="s">
+      <c r="L33" t="s">
+        <v>23</v>
+      </c>
+      <c r="M33" t="s">
+        <v>23</v>
+      </c>
+      <c r="N33" t="s">
+        <v>23</v>
+      </c>
+      <c r="O33" t="s">
         <v>184</v>
-      </c>
-      <c r="L33" t="s">
-        <v>21</v>
-      </c>
-      <c r="M33" t="s">
-        <v>21</v>
-      </c>
-      <c r="N33" t="s">
-        <v>21</v>
-      </c>
-      <c r="O33" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B34" t="s">
-        <v>187</v>
+        <v>29</v>
       </c>
       <c r="C34" t="s">
-        <v>188</v>
+        <v>30</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
@@ -3699,10 +3690,10 @@
         <v>19</v>
       </c>
       <c r="F34" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G34" t="s">
-        <v>189</v>
+        <v>82</v>
       </c>
       <c r="H34" t="s">
         <v>22</v>
@@ -3711,92 +3702,92 @@
         <v>23</v>
       </c>
       <c r="J34" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="K34" t="s">
-        <v>191</v>
+        <v>141</v>
       </c>
       <c r="L34" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M34" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N34" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O34" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D35" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E35" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F35" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G35" t="s">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I35" t="s">
         <v>23</v>
       </c>
       <c r="J35" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="K35" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="L35" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M35" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N35" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O35" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B36" t="s">
-        <v>16</v>
+        <v>193</v>
       </c>
       <c r="C36" t="s">
-        <v>17</v>
+        <v>194</v>
       </c>
       <c r="D36" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E36" t="s">
         <v>19</v>
       </c>
       <c r="F36" t="s">
-        <v>31</v>
+        <v>165</v>
       </c>
       <c r="G36" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H36" t="s">
         <v>22</v>
@@ -3805,45 +3796,45 @@
         <v>23</v>
       </c>
       <c r="J36" t="s">
-        <v>199</v>
+        <v>49</v>
       </c>
       <c r="K36" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="L36" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M36" t="s">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="N36" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O36" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>163</v>
       </c>
       <c r="C37" t="s">
-        <v>38</v>
+        <v>164</v>
       </c>
       <c r="D37" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E37" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F37" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G37" t="s">
-        <v>40</v>
+        <v>198</v>
       </c>
       <c r="H37" t="s">
         <v>22</v>
@@ -3852,160 +3843,160 @@
         <v>23</v>
       </c>
       <c r="J37" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="K37" t="s">
-        <v>204</v>
+        <v>25</v>
       </c>
       <c r="L37" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M37" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N37" t="s">
-        <v>21</v>
+        <v>200</v>
       </c>
       <c r="O37" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C38" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D38" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E38" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F38" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G38" t="s">
-        <v>207</v>
+        <v>23</v>
       </c>
       <c r="H38" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I38" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J38" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="K38" t="s">
-        <v>25</v>
+        <v>180</v>
       </c>
       <c r="L38" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M38" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N38" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O38" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B39" t="s">
-        <v>16</v>
+        <v>163</v>
       </c>
       <c r="C39" t="s">
-        <v>17</v>
+        <v>206</v>
       </c>
       <c r="D39" t="s">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="E39" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F39" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G39" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="H39" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I39" t="s">
         <v>23</v>
       </c>
       <c r="J39" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="K39" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="L39" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M39" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N39" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O39" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>210</v>
+      </c>
+      <c r="B40" t="s">
+        <v>211</v>
+      </c>
+      <c r="C40" t="s">
+        <v>212</v>
+      </c>
+      <c r="D40" t="s">
+        <v>40</v>
+      </c>
+      <c r="E40" t="s">
+        <v>55</v>
+      </c>
+      <c r="F40" t="s">
+        <v>41</v>
+      </c>
+      <c r="G40" t="s">
+        <v>213</v>
+      </c>
+      <c r="H40" t="s">
+        <v>32</v>
+      </c>
+      <c r="I40" t="s">
+        <v>43</v>
+      </c>
+      <c r="J40" t="s">
         <v>214</v>
       </c>
-      <c r="B40" t="s">
-        <v>37</v>
-      </c>
-      <c r="C40" t="s">
-        <v>38</v>
-      </c>
-      <c r="D40" t="s">
-        <v>18</v>
-      </c>
-      <c r="E40" t="s">
-        <v>19</v>
-      </c>
-      <c r="F40" t="s">
-        <v>31</v>
-      </c>
-      <c r="G40" t="s">
-        <v>169</v>
-      </c>
-      <c r="H40" t="s">
-        <v>22</v>
-      </c>
-      <c r="I40" t="s">
-        <v>23</v>
-      </c>
-      <c r="J40" t="s">
+      <c r="K40" t="s">
         <v>215</v>
       </c>
-      <c r="K40" t="s">
-        <v>66</v>
-      </c>
       <c r="L40" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M40" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N40" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O40" t="s">
         <v>216</v>
@@ -4016,607 +4007,607 @@
         <v>217</v>
       </c>
       <c r="B41" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C41" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D41" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E41" t="s">
         <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G41" t="s">
-        <v>32</v>
+        <v>195</v>
       </c>
       <c r="H41" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I41" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J41" t="s">
         <v>218</v>
       </c>
       <c r="K41" t="s">
-        <v>25</v>
+        <v>219</v>
       </c>
       <c r="L41" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M41" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N41" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O41" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B42" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C42" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D42" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E42" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F42" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G42" t="s">
-        <v>40</v>
+        <v>222</v>
       </c>
       <c r="H42" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I42" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J42" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K42" t="s">
-        <v>118</v>
+        <v>224</v>
       </c>
       <c r="L42" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M42" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N42" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O42" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B43" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="D43" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E43" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F43" t="s">
         <v>31</v>
       </c>
       <c r="G43" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="H43" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I43" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J43" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="K43" t="s">
-        <v>150</v>
+        <v>228</v>
       </c>
       <c r="L43" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M43" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N43" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O43" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B44" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" t="s">
+        <v>62</v>
+      </c>
+      <c r="D44" t="s">
+        <v>40</v>
+      </c>
+      <c r="E44" t="s">
+        <v>55</v>
+      </c>
+      <c r="F44" t="s">
+        <v>41</v>
+      </c>
+      <c r="G44" t="s">
+        <v>231</v>
+      </c>
+      <c r="H44" t="s">
+        <v>32</v>
+      </c>
+      <c r="I44" t="s">
+        <v>43</v>
+      </c>
+      <c r="J44" t="s">
+        <v>232</v>
+      </c>
+      <c r="K44" t="s">
         <v>69</v>
       </c>
-      <c r="C44" t="s">
-        <v>21</v>
-      </c>
-      <c r="D44" t="s">
-        <v>21</v>
-      </c>
-      <c r="E44" t="s">
-        <v>19</v>
-      </c>
-      <c r="F44" t="s">
-        <v>39</v>
-      </c>
-      <c r="G44" t="s">
-        <v>32</v>
-      </c>
-      <c r="H44" t="s">
-        <v>22</v>
-      </c>
-      <c r="I44" t="s">
-        <v>21</v>
-      </c>
-      <c r="J44" t="s">
-        <v>33</v>
-      </c>
-      <c r="K44" t="s">
-        <v>227</v>
-      </c>
       <c r="L44" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M44" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N44" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O44" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B45" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="C45" t="s">
-        <v>182</v>
+        <v>54</v>
       </c>
       <c r="D45" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="E45" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F45" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G45" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="H45" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I45" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J45" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="K45" t="s">
-        <v>34</v>
+        <v>236</v>
       </c>
       <c r="L45" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M45" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N45" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O45" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B46" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="C46" t="s">
-        <v>233</v>
+        <v>62</v>
       </c>
       <c r="D46" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E46" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F46" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G46" t="s">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c r="H46" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="I46" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J46" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="K46" t="s">
-        <v>235</v>
+        <v>98</v>
       </c>
       <c r="L46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N46" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O46" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B47" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>182</v>
+        <v>62</v>
       </c>
       <c r="D47" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="E47" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F47" t="s">
-        <v>238</v>
+        <v>41</v>
       </c>
       <c r="G47" t="s">
-        <v>239</v>
+        <v>63</v>
       </c>
       <c r="H47" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I47" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J47" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K47" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="L47" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M47" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N47" t="s">
-        <v>241</v>
+        <v>23</v>
       </c>
       <c r="O47" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B48" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C48" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="D48" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E48" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F48" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G48" t="s">
-        <v>244</v>
+        <v>76</v>
       </c>
       <c r="H48" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I48" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J48" t="s">
         <v>245</v>
       </c>
       <c r="K48" t="s">
+        <v>147</v>
+      </c>
+      <c r="L48" t="s">
+        <v>23</v>
+      </c>
+      <c r="M48" t="s">
+        <v>23</v>
+      </c>
+      <c r="N48" t="s">
+        <v>23</v>
+      </c>
+      <c r="O48" t="s">
         <v>246</v>
-      </c>
-      <c r="L48" t="s">
-        <v>21</v>
-      </c>
-      <c r="M48" t="s">
-        <v>21</v>
-      </c>
-      <c r="N48" t="s">
-        <v>21</v>
-      </c>
-      <c r="O48" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B49" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D49" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E49" t="s">
         <v>19</v>
       </c>
       <c r="F49" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G49" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H49" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I49" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J49" t="s">
+        <v>248</v>
+      </c>
+      <c r="K49" t="s">
+        <v>176</v>
+      </c>
+      <c r="L49" t="s">
+        <v>23</v>
+      </c>
+      <c r="M49" t="s">
+        <v>23</v>
+      </c>
+      <c r="N49" t="s">
+        <v>23</v>
+      </c>
+      <c r="O49" t="s">
         <v>249</v>
-      </c>
-      <c r="K49" t="s">
-        <v>118</v>
-      </c>
-      <c r="L49" t="s">
-        <v>21</v>
-      </c>
-      <c r="M49" t="s">
-        <v>21</v>
-      </c>
-      <c r="N49" t="s">
-        <v>21</v>
-      </c>
-      <c r="O49" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>250</v>
+      </c>
+      <c r="B50" t="s">
+        <v>101</v>
+      </c>
+      <c r="C50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" t="s">
+        <v>23</v>
+      </c>
+      <c r="E50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F50" t="s">
+        <v>41</v>
+      </c>
+      <c r="G50" t="s">
+        <v>63</v>
+      </c>
+      <c r="H50" t="s">
+        <v>32</v>
+      </c>
+      <c r="I50" t="s">
+        <v>23</v>
+      </c>
+      <c r="J50" t="s">
+        <v>72</v>
+      </c>
+      <c r="K50" t="s">
         <v>251</v>
       </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="s">
-        <v>17</v>
-      </c>
-      <c r="D50" t="s">
-        <v>18</v>
-      </c>
-      <c r="E50" t="s">
-        <v>19</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="L50" t="s">
+        <v>23</v>
+      </c>
+      <c r="M50" t="s">
+        <v>23</v>
+      </c>
+      <c r="N50" t="s">
+        <v>23</v>
+      </c>
+      <c r="O50" t="s">
         <v>252</v>
-      </c>
-      <c r="G50" t="s">
-        <v>253</v>
-      </c>
-      <c r="H50" t="s">
-        <v>22</v>
-      </c>
-      <c r="I50" t="s">
-        <v>23</v>
-      </c>
-      <c r="J50" t="s">
-        <v>98</v>
-      </c>
-      <c r="K50" t="s">
-        <v>254</v>
-      </c>
-      <c r="L50" t="s">
-        <v>21</v>
-      </c>
-      <c r="M50" t="s">
-        <v>21</v>
-      </c>
-      <c r="N50" t="s">
-        <v>21</v>
-      </c>
-      <c r="O50" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B51" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="C51" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="D51" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="E51" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F51" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G51" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="H51" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I51" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J51" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="K51" t="s">
-        <v>258</v>
+        <v>73</v>
       </c>
       <c r="L51" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M51" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N51" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O51" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>256</v>
+      </c>
+      <c r="B52" t="s">
+        <v>81</v>
+      </c>
+      <c r="C52" t="s">
+        <v>257</v>
+      </c>
+      <c r="D52" t="s">
+        <v>19</v>
+      </c>
+      <c r="E52" t="s">
+        <v>19</v>
+      </c>
+      <c r="F52" t="s">
+        <v>56</v>
+      </c>
+      <c r="G52" t="s">
+        <v>23</v>
+      </c>
+      <c r="H52" t="s">
+        <v>22</v>
+      </c>
+      <c r="I52" t="s">
+        <v>23</v>
+      </c>
+      <c r="J52" t="s">
+        <v>258</v>
+      </c>
+      <c r="K52" t="s">
+        <v>259</v>
+      </c>
+      <c r="L52" t="s">
+        <v>23</v>
+      </c>
+      <c r="M52" t="s">
+        <v>23</v>
+      </c>
+      <c r="N52" t="s">
+        <v>23</v>
+      </c>
+      <c r="O52" t="s">
         <v>260</v>
-      </c>
-      <c r="B52" t="s">
-        <v>261</v>
-      </c>
-      <c r="C52" t="s">
-        <v>93</v>
-      </c>
-      <c r="D52" t="s">
-        <v>47</v>
-      </c>
-      <c r="E52" t="s">
-        <v>30</v>
-      </c>
-      <c r="F52" t="s">
-        <v>101</v>
-      </c>
-      <c r="G52" t="s">
-        <v>49</v>
-      </c>
-      <c r="H52" t="s">
-        <v>55</v>
-      </c>
-      <c r="I52" t="s">
-        <v>21</v>
-      </c>
-      <c r="J52" t="s">
-        <v>194</v>
-      </c>
-      <c r="K52" t="s">
-        <v>262</v>
-      </c>
-      <c r="L52" t="s">
-        <v>21</v>
-      </c>
-      <c r="M52" t="s">
-        <v>21</v>
-      </c>
-      <c r="N52" t="s">
-        <v>21</v>
-      </c>
-      <c r="O52" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>261</v>
+      </c>
+      <c r="B53" t="s">
+        <v>163</v>
+      </c>
+      <c r="C53" t="s">
+        <v>206</v>
+      </c>
+      <c r="D53" t="s">
+        <v>109</v>
+      </c>
+      <c r="E53" t="s">
+        <v>55</v>
+      </c>
+      <c r="F53" t="s">
+        <v>262</v>
+      </c>
+      <c r="G53" t="s">
+        <v>263</v>
+      </c>
+      <c r="H53" t="s">
+        <v>32</v>
+      </c>
+      <c r="I53" t="s">
+        <v>23</v>
+      </c>
+      <c r="J53" t="s">
         <v>264</v>
       </c>
-      <c r="B53" t="s">
-        <v>28</v>
-      </c>
-      <c r="C53" t="s">
-        <v>29</v>
-      </c>
-      <c r="D53" t="s">
-        <v>18</v>
-      </c>
-      <c r="E53" t="s">
-        <v>30</v>
-      </c>
-      <c r="F53" t="s">
-        <v>31</v>
-      </c>
-      <c r="G53" t="s">
-        <v>121</v>
-      </c>
-      <c r="H53" t="s">
-        <v>22</v>
-      </c>
-      <c r="I53" t="s">
-        <v>23</v>
-      </c>
-      <c r="J53" t="s">
+      <c r="K53" t="s">
+        <v>78</v>
+      </c>
+      <c r="L53" t="s">
+        <v>23</v>
+      </c>
+      <c r="M53" t="s">
+        <v>23</v>
+      </c>
+      <c r="N53" t="s">
         <v>265</v>
-      </c>
-      <c r="K53" t="s">
-        <v>154</v>
-      </c>
-      <c r="L53" t="s">
-        <v>21</v>
-      </c>
-      <c r="M53" t="s">
-        <v>21</v>
-      </c>
-      <c r="N53" t="s">
-        <v>21</v>
       </c>
       <c r="O53" t="s">
         <v>266</v>
@@ -4627,248 +4618,248 @@
         <v>267</v>
       </c>
       <c r="B54" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="D54" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E54" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F54" t="s">
         <v>31</v>
       </c>
       <c r="G54" t="s">
-        <v>49</v>
+        <v>268</v>
       </c>
       <c r="H54" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I54" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J54" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K54" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L54" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M54" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N54" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O54" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B55" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="D55" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E55" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F55" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G55" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="H55" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I55" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J55" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K55" t="s">
-        <v>200</v>
+        <v>147</v>
       </c>
       <c r="L55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N55" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O55" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B56" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="C56" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="D56" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="E56" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F56" t="s">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="G56" t="s">
-        <v>113</v>
+        <v>277</v>
       </c>
       <c r="H56" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I56" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J56" t="s">
-        <v>275</v>
+        <v>130</v>
       </c>
       <c r="K56" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="L56" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M56" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N56" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O56" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B57" t="s">
-        <v>16</v>
+        <v>163</v>
       </c>
       <c r="C57" t="s">
-        <v>17</v>
+        <v>206</v>
       </c>
       <c r="D57" t="s">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="E57" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F57" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G57" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="H57" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I57" t="s">
         <v>23</v>
       </c>
       <c r="J57" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K57" t="s">
-        <v>280</v>
+        <v>45</v>
       </c>
       <c r="L57" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M57" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N57" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O57" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B58" t="s">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="C58" t="s">
-        <v>182</v>
+        <v>125</v>
       </c>
       <c r="D58" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="E58" t="s">
         <v>19</v>
       </c>
       <c r="F58" t="s">
-        <v>238</v>
+        <v>133</v>
       </c>
       <c r="G58" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="H58" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="I58" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J58" t="s">
-        <v>283</v>
+        <v>218</v>
       </c>
       <c r="K58" t="s">
         <v>284</v>
       </c>
       <c r="L58" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M58" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N58" t="s">
+        <v>23</v>
+      </c>
+      <c r="O58" t="s">
         <v>285</v>
-      </c>
-      <c r="O58" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B59" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C59" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D59" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E59" t="s">
         <v>19</v>
@@ -4877,498 +4868,498 @@
         <v>31</v>
       </c>
       <c r="G59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H59" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I59" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J59" t="s">
+        <v>287</v>
+      </c>
+      <c r="K59" t="s">
+        <v>180</v>
+      </c>
+      <c r="L59" t="s">
+        <v>23</v>
+      </c>
+      <c r="M59" t="s">
+        <v>23</v>
+      </c>
+      <c r="N59" t="s">
+        <v>23</v>
+      </c>
+      <c r="O59" t="s">
         <v>288</v>
-      </c>
-      <c r="K59" t="s">
-        <v>289</v>
-      </c>
-      <c r="L59" t="s">
-        <v>21</v>
-      </c>
-      <c r="M59" t="s">
-        <v>21</v>
-      </c>
-      <c r="N59" t="s">
-        <v>21</v>
-      </c>
-      <c r="O59" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B60" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C60" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D60" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E60" t="s">
         <v>19</v>
       </c>
       <c r="F60" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G60" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="H60" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I60" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J60" t="s">
+        <v>290</v>
+      </c>
+      <c r="K60" t="s">
+        <v>291</v>
+      </c>
+      <c r="L60" t="s">
+        <v>23</v>
+      </c>
+      <c r="M60" t="s">
+        <v>23</v>
+      </c>
+      <c r="N60" t="s">
+        <v>23</v>
+      </c>
+      <c r="O60" t="s">
         <v>292</v>
-      </c>
-      <c r="K60" t="s">
-        <v>103</v>
-      </c>
-      <c r="L60" t="s">
-        <v>21</v>
-      </c>
-      <c r="M60" t="s">
-        <v>21</v>
-      </c>
-      <c r="N60" t="s">
-        <v>21</v>
-      </c>
-      <c r="O60" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>293</v>
+      </c>
+      <c r="B61" t="s">
+        <v>53</v>
+      </c>
+      <c r="C61" t="s">
+        <v>54</v>
+      </c>
+      <c r="D61" t="s">
+        <v>40</v>
+      </c>
+      <c r="E61" t="s">
+        <v>55</v>
+      </c>
+      <c r="F61" t="s">
+        <v>56</v>
+      </c>
+      <c r="G61" t="s">
+        <v>23</v>
+      </c>
+      <c r="H61" t="s">
+        <v>32</v>
+      </c>
+      <c r="I61" t="s">
+        <v>43</v>
+      </c>
+      <c r="J61" t="s">
         <v>294</v>
       </c>
-      <c r="B61" t="s">
+      <c r="K61" t="s">
+        <v>224</v>
+      </c>
+      <c r="L61" t="s">
+        <v>23</v>
+      </c>
+      <c r="M61" t="s">
+        <v>23</v>
+      </c>
+      <c r="N61" t="s">
+        <v>23</v>
+      </c>
+      <c r="O61" t="s">
         <v>295</v>
-      </c>
-      <c r="C61" t="s">
-        <v>296</v>
-      </c>
-      <c r="D61" t="s">
-        <v>297</v>
-      </c>
-      <c r="E61" t="s">
-        <v>19</v>
-      </c>
-      <c r="F61" t="s">
-        <v>31</v>
-      </c>
-      <c r="G61" t="s">
-        <v>298</v>
-      </c>
-      <c r="H61" t="s">
-        <v>22</v>
-      </c>
-      <c r="I61" t="s">
-        <v>299</v>
-      </c>
-      <c r="J61" t="s">
-        <v>300</v>
-      </c>
-      <c r="K61" t="s">
-        <v>301</v>
-      </c>
-      <c r="L61" t="s">
-        <v>21</v>
-      </c>
-      <c r="M61" t="s">
-        <v>21</v>
-      </c>
-      <c r="N61" t="s">
-        <v>21</v>
-      </c>
-      <c r="O61" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B62" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="C62" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D62" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E62" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F62" t="s">
-        <v>31</v>
+        <v>133</v>
       </c>
       <c r="G62" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H62" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I62" t="s">
         <v>23</v>
       </c>
       <c r="J62" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="K62" t="s">
-        <v>85</v>
+        <v>298</v>
       </c>
       <c r="L62" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M62" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N62" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O62" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="B63" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="C63" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="D63" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E63" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F63" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G63" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="H63" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I63" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J63" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="K63" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="L63" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M63" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N63" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O63" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B64" t="s">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="C64" t="s">
-        <v>21</v>
+        <v>206</v>
       </c>
       <c r="D64" t="s">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="E64" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F64" t="s">
-        <v>39</v>
+        <v>262</v>
       </c>
       <c r="G64" t="s">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="H64" t="s">
         <v>22</v>
       </c>
       <c r="I64" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J64" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="K64" t="s">
-        <v>262</v>
+        <v>306</v>
       </c>
       <c r="L64" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M64" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N64" t="s">
-        <v>21</v>
+        <v>307</v>
       </c>
       <c r="O64" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B65" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C65" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="D65" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="E65" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F65" t="s">
         <v>31</v>
       </c>
       <c r="G65" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="H65" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I65" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J65" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K65" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="L65" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M65" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N65" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O65" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B66" t="s">
-        <v>318</v>
+        <v>61</v>
       </c>
       <c r="C66" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="D66" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E66" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F66" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="G66" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="H66" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="I66" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J66" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="K66" t="s">
-        <v>89</v>
+        <v>135</v>
       </c>
       <c r="L66" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M66" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N66" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O66" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>316</v>
+      </c>
+      <c r="B67" t="s">
+        <v>317</v>
+      </c>
+      <c r="C67" t="s">
+        <v>318</v>
+      </c>
+      <c r="D67" t="s">
+        <v>319</v>
+      </c>
+      <c r="E67" t="s">
+        <v>55</v>
+      </c>
+      <c r="F67" t="s">
+        <v>31</v>
+      </c>
+      <c r="G67" t="s">
+        <v>320</v>
+      </c>
+      <c r="H67" t="s">
+        <v>32</v>
+      </c>
+      <c r="I67" t="s">
+        <v>33</v>
+      </c>
+      <c r="J67" t="s">
+        <v>64</v>
+      </c>
+      <c r="K67" t="s">
         <v>321</v>
       </c>
-      <c r="B67" t="s">
-        <v>37</v>
-      </c>
-      <c r="C67" t="s">
-        <v>38</v>
-      </c>
-      <c r="D67" t="s">
-        <v>18</v>
-      </c>
-      <c r="E67" t="s">
-        <v>19</v>
-      </c>
-      <c r="F67" t="s">
-        <v>39</v>
-      </c>
-      <c r="G67" t="s">
+      <c r="L67" t="s">
+        <v>23</v>
+      </c>
+      <c r="M67" t="s">
+        <v>23</v>
+      </c>
+      <c r="N67" t="s">
+        <v>23</v>
+      </c>
+      <c r="O67" t="s">
         <v>322</v>
-      </c>
-      <c r="H67" t="s">
-        <v>22</v>
-      </c>
-      <c r="I67" t="s">
-        <v>23</v>
-      </c>
-      <c r="J67" t="s">
-        <v>218</v>
-      </c>
-      <c r="K67" t="s">
-        <v>200</v>
-      </c>
-      <c r="L67" t="s">
-        <v>21</v>
-      </c>
-      <c r="M67" t="s">
-        <v>21</v>
-      </c>
-      <c r="N67" t="s">
-        <v>21</v>
-      </c>
-      <c r="O67" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>323</v>
+      </c>
+      <c r="B68" t="s">
+        <v>61</v>
+      </c>
+      <c r="C68" t="s">
+        <v>62</v>
+      </c>
+      <c r="D68" t="s">
+        <v>40</v>
+      </c>
+      <c r="E68" t="s">
+        <v>55</v>
+      </c>
+      <c r="F68" t="s">
+        <v>31</v>
+      </c>
+      <c r="G68" t="s">
+        <v>63</v>
+      </c>
+      <c r="H68" t="s">
+        <v>32</v>
+      </c>
+      <c r="I68" t="s">
+        <v>43</v>
+      </c>
+      <c r="J68" t="s">
         <v>324</v>
       </c>
-      <c r="B68" t="s">
-        <v>37</v>
-      </c>
-      <c r="C68" t="s">
-        <v>38</v>
-      </c>
-      <c r="D68" t="s">
-        <v>18</v>
-      </c>
-      <c r="E68" t="s">
-        <v>19</v>
-      </c>
-      <c r="F68" t="s">
-        <v>39</v>
-      </c>
-      <c r="G68" t="s">
-        <v>121</v>
-      </c>
-      <c r="H68" t="s">
-        <v>22</v>
-      </c>
-      <c r="I68" t="s">
-        <v>23</v>
-      </c>
-      <c r="J68" t="s">
+      <c r="K68" t="s">
+        <v>117</v>
+      </c>
+      <c r="L68" t="s">
+        <v>23</v>
+      </c>
+      <c r="M68" t="s">
+        <v>23</v>
+      </c>
+      <c r="N68" t="s">
+        <v>23</v>
+      </c>
+      <c r="O68" t="s">
         <v>325</v>
-      </c>
-      <c r="K68" t="s">
-        <v>235</v>
-      </c>
-      <c r="L68" t="s">
-        <v>21</v>
-      </c>
-      <c r="M68" t="s">
-        <v>21</v>
-      </c>
-      <c r="N68" t="s">
-        <v>21</v>
-      </c>
-      <c r="O68" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>326</v>
+      </c>
+      <c r="B69" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" t="s">
+        <v>54</v>
+      </c>
+      <c r="D69" t="s">
+        <v>40</v>
+      </c>
+      <c r="E69" t="s">
+        <v>55</v>
+      </c>
+      <c r="F69" t="s">
+        <v>56</v>
+      </c>
+      <c r="G69" t="s">
+        <v>23</v>
+      </c>
+      <c r="H69" t="s">
+        <v>32</v>
+      </c>
+      <c r="I69" t="s">
+        <v>43</v>
+      </c>
+      <c r="J69" t="s">
         <v>327</v>
       </c>
-      <c r="B69" t="s">
-        <v>37</v>
-      </c>
-      <c r="C69" t="s">
-        <v>38</v>
-      </c>
-      <c r="D69" t="s">
-        <v>18</v>
-      </c>
-      <c r="E69" t="s">
-        <v>19</v>
-      </c>
-      <c r="F69" t="s">
-        <v>31</v>
-      </c>
-      <c r="G69" t="s">
-        <v>121</v>
-      </c>
-      <c r="H69" t="s">
-        <v>22</v>
-      </c>
-      <c r="I69" t="s">
-        <v>23</v>
-      </c>
-      <c r="J69" t="s">
+      <c r="K69" t="s">
         <v>328</v>
       </c>
-      <c r="K69" t="s">
-        <v>157</v>
-      </c>
       <c r="L69" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M69" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N69" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O69" t="s">
         <v>329</v>
@@ -5379,25 +5370,25 @@
         <v>330</v>
       </c>
       <c r="B70" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="C70" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D70" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E70" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F70" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G70" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H70" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I70" t="s">
         <v>23</v>
@@ -5406,16 +5397,16 @@
         <v>331</v>
       </c>
       <c r="K70" t="s">
-        <v>139</v>
+        <v>284</v>
       </c>
       <c r="L70" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M70" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N70" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O70" t="s">
         <v>332</v>
@@ -5426,57 +5417,57 @@
         <v>333</v>
       </c>
       <c r="B71" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="C71" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="D71" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E71" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F71" t="s">
-        <v>137</v>
+        <v>31</v>
       </c>
       <c r="G71" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="H71" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="I71" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J71" t="s">
         <v>334</v>
       </c>
       <c r="K71" t="s">
-        <v>62</v>
+        <v>335</v>
       </c>
       <c r="L71" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M71" t="s">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="N71" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O71" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B72" t="s">
-        <v>37</v>
+        <v>338</v>
       </c>
       <c r="C72" t="s">
-        <v>38</v>
+        <v>125</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
@@ -5485,10 +5476,10 @@
         <v>19</v>
       </c>
       <c r="F72" t="s">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="G72" t="s">
-        <v>121</v>
+        <v>21</v>
       </c>
       <c r="H72" t="s">
         <v>22</v>
@@ -5497,160 +5488,160 @@
         <v>23</v>
       </c>
       <c r="J72" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K72" t="s">
-        <v>338</v>
+        <v>121</v>
       </c>
       <c r="L72" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M72" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N72" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O72" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B73" t="s">
-        <v>126</v>
+        <v>61</v>
       </c>
       <c r="C73" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="D73" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="E73" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F73" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G73" t="s">
-        <v>49</v>
+        <v>342</v>
       </c>
       <c r="H73" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I73" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J73" t="s">
-        <v>341</v>
+        <v>242</v>
       </c>
       <c r="K73" t="s">
-        <v>66</v>
+        <v>224</v>
       </c>
       <c r="L73" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M73" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N73" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O73" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B74" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C74" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="D74" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E74" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F74" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G74" t="s">
-        <v>169</v>
+        <v>48</v>
       </c>
       <c r="H74" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I74" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J74" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K74" t="s">
-        <v>25</v>
+        <v>259</v>
       </c>
       <c r="L74" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M74" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N74" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O74" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B75" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C75" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="D75" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E75" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F75" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G75" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H75" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I75" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J75" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K75" t="s">
-        <v>348</v>
+        <v>183</v>
       </c>
       <c r="L75" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M75" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N75" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O75" t="s">
         <v>349</v>
@@ -5661,43 +5652,43 @@
         <v>350</v>
       </c>
       <c r="B76" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C76" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="D76" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E76" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F76" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G76" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="H76" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="I76" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J76" t="s">
         <v>351</v>
       </c>
       <c r="K76" t="s">
-        <v>89</v>
+        <v>167</v>
       </c>
       <c r="L76" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M76" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N76" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O76" t="s">
         <v>352</v>
@@ -5708,22 +5699,22 @@
         <v>353</v>
       </c>
       <c r="B77" t="s">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="C77" t="s">
-        <v>29</v>
+        <v>115</v>
       </c>
       <c r="D77" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E77" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F77" t="s">
-        <v>31</v>
+        <v>165</v>
       </c>
       <c r="G77" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="H77" t="s">
         <v>22</v>
@@ -5735,16 +5726,16 @@
         <v>354</v>
       </c>
       <c r="K77" t="s">
-        <v>195</v>
+        <v>94</v>
       </c>
       <c r="L77" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M77" t="s">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="N77" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O77" t="s">
         <v>355</v>
@@ -5755,210 +5746,210 @@
         <v>356</v>
       </c>
       <c r="B78" t="s">
+        <v>61</v>
+      </c>
+      <c r="C78" t="s">
+        <v>62</v>
+      </c>
+      <c r="D78" t="s">
+        <v>40</v>
+      </c>
+      <c r="E78" t="s">
+        <v>55</v>
+      </c>
+      <c r="F78" t="s">
+        <v>41</v>
+      </c>
+      <c r="G78" t="s">
+        <v>48</v>
+      </c>
+      <c r="H78" t="s">
+        <v>32</v>
+      </c>
+      <c r="I78" t="s">
+        <v>43</v>
+      </c>
+      <c r="J78" t="s">
         <v>357</v>
       </c>
-      <c r="C78" t="s">
-        <v>188</v>
-      </c>
-      <c r="D78" t="s">
-        <v>18</v>
-      </c>
-      <c r="E78" t="s">
-        <v>19</v>
-      </c>
-      <c r="F78" t="s">
-        <v>39</v>
-      </c>
-      <c r="G78" t="s">
-        <v>32</v>
-      </c>
-      <c r="H78" t="s">
-        <v>22</v>
-      </c>
-      <c r="I78" t="s">
-        <v>23</v>
-      </c>
-      <c r="J78" t="s">
-        <v>33</v>
-      </c>
       <c r="K78" t="s">
+        <v>65</v>
+      </c>
+      <c r="L78" t="s">
+        <v>23</v>
+      </c>
+      <c r="M78" t="s">
+        <v>23</v>
+      </c>
+      <c r="N78" t="s">
+        <v>23</v>
+      </c>
+      <c r="O78" t="s">
         <v>358</v>
-      </c>
-      <c r="L78" t="s">
-        <v>21</v>
-      </c>
-      <c r="M78" t="s">
-        <v>21</v>
-      </c>
-      <c r="N78" t="s">
-        <v>21</v>
-      </c>
-      <c r="O78" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B79" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="C79" t="s">
-        <v>182</v>
+        <v>23</v>
       </c>
       <c r="D79" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="E79" t="s">
         <v>19</v>
       </c>
       <c r="F79" t="s">
+        <v>31</v>
+      </c>
+      <c r="G79" t="s">
+        <v>82</v>
+      </c>
+      <c r="H79" t="s">
+        <v>32</v>
+      </c>
+      <c r="I79" t="s">
+        <v>23</v>
+      </c>
+      <c r="J79" t="s">
+        <v>360</v>
+      </c>
+      <c r="K79" t="s">
+        <v>98</v>
+      </c>
+      <c r="L79" t="s">
+        <v>23</v>
+      </c>
+      <c r="M79" t="s">
+        <v>23</v>
+      </c>
+      <c r="N79" t="s">
+        <v>23</v>
+      </c>
+      <c r="O79" t="s">
         <v>361</v>
-      </c>
-      <c r="G79" t="s">
-        <v>49</v>
-      </c>
-      <c r="H79" t="s">
-        <v>55</v>
-      </c>
-      <c r="I79" t="s">
-        <v>21</v>
-      </c>
-      <c r="J79" t="s">
-        <v>362</v>
-      </c>
-      <c r="K79" t="s">
-        <v>363</v>
-      </c>
-      <c r="L79" t="s">
-        <v>21</v>
-      </c>
-      <c r="M79" t="s">
-        <v>21</v>
-      </c>
-      <c r="N79" t="s">
-        <v>21</v>
-      </c>
-      <c r="O79" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B80" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C80" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="D80" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E80" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F80" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G80" t="s">
-        <v>121</v>
+        <v>195</v>
       </c>
       <c r="H80" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I80" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J80" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="K80" t="s">
-        <v>157</v>
+        <v>69</v>
       </c>
       <c r="L80" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M80" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N80" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O80" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B81" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C81" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="D81" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E81" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F81" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G81" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="H81" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I81" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J81" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="K81" t="s">
-        <v>139</v>
+        <v>50</v>
       </c>
       <c r="L81" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M81" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N81" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O81" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B82" t="s">
-        <v>37</v>
+        <v>101</v>
       </c>
       <c r="C82" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D82" t="s">
         <v>18</v>
       </c>
       <c r="E82" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F82" t="s">
-        <v>252</v>
+        <v>41</v>
       </c>
       <c r="G82" t="s">
-        <v>372</v>
+        <v>82</v>
       </c>
       <c r="H82" t="s">
         <v>22</v>
@@ -5967,515 +5958,515 @@
         <v>23</v>
       </c>
       <c r="J82" t="s">
-        <v>106</v>
+        <v>369</v>
       </c>
       <c r="K82" t="s">
-        <v>235</v>
+        <v>121</v>
       </c>
       <c r="L82" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M82" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N82" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O82" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B83" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C83" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D83" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E83" t="s">
         <v>19</v>
       </c>
       <c r="F83" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G83" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="H83" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I83" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J83" t="s">
-        <v>170</v>
+        <v>372</v>
       </c>
       <c r="K83" t="s">
-        <v>375</v>
+        <v>219</v>
       </c>
       <c r="L83" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M83" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N83" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O83" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>374</v>
+      </c>
+      <c r="B84" t="s">
+        <v>375</v>
+      </c>
+      <c r="C84" t="s">
+        <v>212</v>
+      </c>
+      <c r="D84" t="s">
+        <v>40</v>
+      </c>
+      <c r="E84" t="s">
+        <v>55</v>
+      </c>
+      <c r="F84" t="s">
+        <v>41</v>
+      </c>
+      <c r="G84" t="s">
+        <v>63</v>
+      </c>
+      <c r="H84" t="s">
+        <v>32</v>
+      </c>
+      <c r="I84" t="s">
+        <v>43</v>
+      </c>
+      <c r="J84" t="s">
+        <v>72</v>
+      </c>
+      <c r="K84" t="s">
+        <v>376</v>
+      </c>
+      <c r="L84" t="s">
+        <v>23</v>
+      </c>
+      <c r="M84" t="s">
+        <v>23</v>
+      </c>
+      <c r="N84" t="s">
+        <v>23</v>
+      </c>
+      <c r="O84" t="s">
         <v>377</v>
-      </c>
-      <c r="B84" t="s">
-        <v>28</v>
-      </c>
-      <c r="C84" t="s">
-        <v>29</v>
-      </c>
-      <c r="D84" t="s">
-        <v>18</v>
-      </c>
-      <c r="E84" t="s">
-        <v>30</v>
-      </c>
-      <c r="F84" t="s">
-        <v>31</v>
-      </c>
-      <c r="G84" t="s">
-        <v>113</v>
-      </c>
-      <c r="H84" t="s">
-        <v>22</v>
-      </c>
-      <c r="I84" t="s">
-        <v>23</v>
-      </c>
-      <c r="J84" t="s">
-        <v>378</v>
-      </c>
-      <c r="K84" t="s">
-        <v>154</v>
-      </c>
-      <c r="L84" t="s">
-        <v>21</v>
-      </c>
-      <c r="M84" t="s">
-        <v>21</v>
-      </c>
-      <c r="N84" t="s">
-        <v>21</v>
-      </c>
-      <c r="O84" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>378</v>
+      </c>
+      <c r="B85" t="s">
+        <v>163</v>
+      </c>
+      <c r="C85" t="s">
+        <v>206</v>
+      </c>
+      <c r="D85" t="s">
+        <v>109</v>
+      </c>
+      <c r="E85" t="s">
+        <v>55</v>
+      </c>
+      <c r="F85" t="s">
+        <v>379</v>
+      </c>
+      <c r="G85" t="s">
+        <v>82</v>
+      </c>
+      <c r="H85" t="s">
+        <v>22</v>
+      </c>
+      <c r="I85" t="s">
+        <v>23</v>
+      </c>
+      <c r="J85" t="s">
         <v>380</v>
       </c>
-      <c r="B85" t="s">
+      <c r="K85" t="s">
         <v>381</v>
       </c>
-      <c r="C85" t="s">
+      <c r="L85" t="s">
+        <v>23</v>
+      </c>
+      <c r="M85" t="s">
+        <v>23</v>
+      </c>
+      <c r="N85" t="s">
+        <v>23</v>
+      </c>
+      <c r="O85" t="s">
         <v>382</v>
-      </c>
-      <c r="D85" t="s">
-        <v>383</v>
-      </c>
-      <c r="E85" t="s">
-        <v>30</v>
-      </c>
-      <c r="F85" t="s">
-        <v>31</v>
-      </c>
-      <c r="G85" t="s">
-        <v>49</v>
-      </c>
-      <c r="H85" t="s">
-        <v>55</v>
-      </c>
-      <c r="I85" t="s">
-        <v>21</v>
-      </c>
-      <c r="J85" t="s">
-        <v>378</v>
-      </c>
-      <c r="K85" t="s">
-        <v>200</v>
-      </c>
-      <c r="L85" t="s">
-        <v>21</v>
-      </c>
-      <c r="M85" t="s">
-        <v>21</v>
-      </c>
-      <c r="N85" t="s">
-        <v>21</v>
-      </c>
-      <c r="O85" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>383</v>
+      </c>
+      <c r="B86" t="s">
+        <v>61</v>
+      </c>
+      <c r="C86" t="s">
+        <v>62</v>
+      </c>
+      <c r="D86" t="s">
+        <v>40</v>
+      </c>
+      <c r="E86" t="s">
+        <v>55</v>
+      </c>
+      <c r="F86" t="s">
+        <v>41</v>
+      </c>
+      <c r="G86" t="s">
+        <v>48</v>
+      </c>
+      <c r="H86" t="s">
+        <v>32</v>
+      </c>
+      <c r="I86" t="s">
+        <v>43</v>
+      </c>
+      <c r="J86" t="s">
+        <v>384</v>
+      </c>
+      <c r="K86" t="s">
+        <v>183</v>
+      </c>
+      <c r="L86" t="s">
+        <v>23</v>
+      </c>
+      <c r="M86" t="s">
+        <v>23</v>
+      </c>
+      <c r="N86" t="s">
+        <v>23</v>
+      </c>
+      <c r="O86" t="s">
         <v>385</v>
-      </c>
-      <c r="B86" t="s">
-        <v>75</v>
-      </c>
-      <c r="C86" t="s">
-        <v>21</v>
-      </c>
-      <c r="D86" t="s">
-        <v>21</v>
-      </c>
-      <c r="E86" t="s">
-        <v>19</v>
-      </c>
-      <c r="F86" t="s">
-        <v>39</v>
-      </c>
-      <c r="G86" t="s">
-        <v>32</v>
-      </c>
-      <c r="H86" t="s">
-        <v>22</v>
-      </c>
-      <c r="I86" t="s">
-        <v>21</v>
-      </c>
-      <c r="J86" t="s">
-        <v>98</v>
-      </c>
-      <c r="K86" t="s">
-        <v>386</v>
-      </c>
-      <c r="L86" t="s">
-        <v>21</v>
-      </c>
-      <c r="M86" t="s">
-        <v>21</v>
-      </c>
-      <c r="N86" t="s">
-        <v>21</v>
-      </c>
-      <c r="O86" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>386</v>
+      </c>
+      <c r="B87" t="s">
+        <v>61</v>
+      </c>
+      <c r="C87" t="s">
+        <v>62</v>
+      </c>
+      <c r="D87" t="s">
+        <v>40</v>
+      </c>
+      <c r="E87" t="s">
+        <v>55</v>
+      </c>
+      <c r="F87" t="s">
+        <v>41</v>
+      </c>
+      <c r="G87" t="s">
+        <v>82</v>
+      </c>
+      <c r="H87" t="s">
+        <v>32</v>
+      </c>
+      <c r="I87" t="s">
+        <v>43</v>
+      </c>
+      <c r="J87" t="s">
+        <v>387</v>
+      </c>
+      <c r="K87" t="s">
+        <v>167</v>
+      </c>
+      <c r="L87" t="s">
+        <v>23</v>
+      </c>
+      <c r="M87" t="s">
+        <v>23</v>
+      </c>
+      <c r="N87" t="s">
+        <v>23</v>
+      </c>
+      <c r="O87" t="s">
         <v>388</v>
-      </c>
-      <c r="B87" t="s">
-        <v>389</v>
-      </c>
-      <c r="C87" t="s">
-        <v>83</v>
-      </c>
-      <c r="D87" t="s">
-        <v>30</v>
-      </c>
-      <c r="E87" t="s">
-        <v>30</v>
-      </c>
-      <c r="F87" t="s">
-        <v>20</v>
-      </c>
-      <c r="G87" t="s">
-        <v>21</v>
-      </c>
-      <c r="H87" t="s">
-        <v>55</v>
-      </c>
-      <c r="I87" t="s">
-        <v>21</v>
-      </c>
-      <c r="J87" t="s">
-        <v>390</v>
-      </c>
-      <c r="K87" t="s">
-        <v>338</v>
-      </c>
-      <c r="L87" t="s">
-        <v>21</v>
-      </c>
-      <c r="M87" t="s">
-        <v>21</v>
-      </c>
-      <c r="N87" t="s">
-        <v>21</v>
-      </c>
-      <c r="O87" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B88" t="s">
-        <v>393</v>
+        <v>61</v>
       </c>
       <c r="C88" t="s">
-        <v>394</v>
+        <v>62</v>
       </c>
       <c r="D88" t="s">
-        <v>395</v>
+        <v>40</v>
       </c>
       <c r="E88" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F88" t="s">
-        <v>39</v>
+        <v>276</v>
       </c>
       <c r="G88" t="s">
-        <v>49</v>
+        <v>390</v>
       </c>
       <c r="H88" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="I88" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J88" t="s">
-        <v>396</v>
+        <v>57</v>
       </c>
       <c r="K88" t="s">
-        <v>397</v>
+        <v>259</v>
       </c>
       <c r="L88" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M88" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N88" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O88" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="B89" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C89" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="D89" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E89" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F89" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G89" t="s">
+        <v>76</v>
+      </c>
+      <c r="H89" t="s">
+        <v>32</v>
+      </c>
+      <c r="I89" t="s">
+        <v>43</v>
+      </c>
+      <c r="J89" t="s">
         <v>49</v>
       </c>
-      <c r="H89" t="s">
-        <v>22</v>
-      </c>
-      <c r="I89" t="s">
-        <v>23</v>
-      </c>
-      <c r="J89" t="s">
-        <v>33</v>
-      </c>
       <c r="K89" t="s">
-        <v>212</v>
+        <v>393</v>
       </c>
       <c r="L89" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M89" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N89" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O89" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B90" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C90" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D90" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E90" t="s">
         <v>19</v>
       </c>
       <c r="F90" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G90" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="H90" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I90" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J90" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="K90" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="L90" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M90" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N90" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O90" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="B91" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="C91" t="s">
-        <v>83</v>
+        <v>400</v>
       </c>
       <c r="D91" t="s">
-        <v>30</v>
+        <v>401</v>
       </c>
       <c r="E91" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F91" t="s">
         <v>31</v>
       </c>
       <c r="G91" t="s">
-        <v>322</v>
+        <v>82</v>
       </c>
       <c r="H91" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="I91" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J91" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="K91" t="s">
-        <v>375</v>
+        <v>224</v>
       </c>
       <c r="L91" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M91" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N91" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O91" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B92" t="s">
-        <v>393</v>
+        <v>107</v>
       </c>
       <c r="C92" t="s">
-        <v>409</v>
+        <v>23</v>
       </c>
       <c r="D92" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E92" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F92" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G92" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="H92" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="I92" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J92" t="s">
-        <v>410</v>
+        <v>130</v>
       </c>
       <c r="K92" t="s">
-        <v>164</v>
+        <v>404</v>
       </c>
       <c r="L92" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M92" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N92" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O92" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B93" t="s">
-        <v>37</v>
+        <v>407</v>
       </c>
       <c r="C93" t="s">
-        <v>38</v>
+        <v>115</v>
       </c>
       <c r="D93" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E93" t="s">
         <v>19</v>
       </c>
       <c r="F93" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="G93" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="H93" t="s">
         <v>22</v>
@@ -6484,45 +6475,45 @@
         <v>23</v>
       </c>
       <c r="J93" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="K93" t="s">
-        <v>157</v>
+        <v>65</v>
       </c>
       <c r="L93" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M93" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N93" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O93" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B94" t="s">
-        <v>28</v>
+        <v>411</v>
       </c>
       <c r="C94" t="s">
-        <v>29</v>
+        <v>412</v>
       </c>
       <c r="D94" t="s">
-        <v>18</v>
+        <v>413</v>
       </c>
       <c r="E94" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F94" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G94" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="H94" t="s">
         <v>22</v>
@@ -6531,421 +6522,421 @@
         <v>23</v>
       </c>
       <c r="J94" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="K94" t="s">
-        <v>289</v>
+        <v>58</v>
       </c>
       <c r="L94" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M94" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N94" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O94" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B95" t="s">
-        <v>187</v>
+        <v>61</v>
       </c>
       <c r="C95" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="D95" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="E95" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F95" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G95" t="s">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="H95" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I95" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J95" t="s">
-        <v>419</v>
+        <v>72</v>
       </c>
       <c r="K95" t="s">
-        <v>375</v>
+        <v>236</v>
       </c>
       <c r="L95" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M95" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N95" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O95" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B96" t="s">
-        <v>357</v>
+        <v>53</v>
       </c>
       <c r="C96" t="s">
-        <v>188</v>
+        <v>54</v>
       </c>
       <c r="D96" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E96" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F96" t="s">
-        <v>252</v>
+        <v>41</v>
       </c>
       <c r="G96" t="s">
-        <v>422</v>
+        <v>82</v>
       </c>
       <c r="H96" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I96" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J96" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="K96" t="s">
-        <v>424</v>
+        <v>176</v>
       </c>
       <c r="L96" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M96" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N96" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O96" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B97" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C97" t="s">
-        <v>233</v>
+        <v>115</v>
       </c>
       <c r="D97" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="E97" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F97" t="s">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="G97" t="s">
-        <v>113</v>
+        <v>342</v>
       </c>
       <c r="H97" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="I97" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J97" t="s">
-        <v>194</v>
+        <v>423</v>
       </c>
       <c r="K97" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="L97" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M97" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N97" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O97" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B98" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C98" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="D98" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E98" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F98" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G98" t="s">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="H98" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="I98" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J98" t="s">
-        <v>98</v>
+        <v>427</v>
       </c>
       <c r="K98" t="s">
-        <v>431</v>
+        <v>190</v>
       </c>
       <c r="L98" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M98" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N98" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O98" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B99" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="C99" t="s">
-        <v>182</v>
+        <v>62</v>
       </c>
       <c r="D99" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="E99" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F99" t="s">
-        <v>361</v>
+        <v>41</v>
       </c>
       <c r="G99" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H99" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="I99" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J99" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="K99" t="s">
-        <v>34</v>
+        <v>183</v>
       </c>
       <c r="L99" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M99" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N99" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O99" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B100" t="s">
-        <v>437</v>
+        <v>38</v>
       </c>
       <c r="C100" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="D100" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="E100" t="s">
         <v>19</v>
       </c>
       <c r="F100" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G100" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="H100" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I100" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J100" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="K100" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="L100" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M100" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N100" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O100" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="B101" t="s">
-        <v>37</v>
+        <v>211</v>
       </c>
       <c r="C101" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D101" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E101" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F101" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G101" t="s">
-        <v>121</v>
+        <v>195</v>
       </c>
       <c r="H101" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I101" t="s">
         <v>23</v>
       </c>
       <c r="J101" t="s">
-        <v>106</v>
+        <v>436</v>
       </c>
       <c r="K101" t="s">
-        <v>89</v>
+        <v>393</v>
       </c>
       <c r="L101" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M101" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N101" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O101" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>438</v>
+      </c>
+      <c r="B102" t="s">
+        <v>375</v>
+      </c>
+      <c r="C102" t="s">
+        <v>212</v>
+      </c>
+      <c r="D102" t="s">
+        <v>40</v>
+      </c>
+      <c r="E102" t="s">
+        <v>55</v>
+      </c>
+      <c r="F102" t="s">
+        <v>276</v>
+      </c>
+      <c r="G102" t="s">
+        <v>439</v>
+      </c>
+      <c r="H102" t="s">
+        <v>32</v>
+      </c>
+      <c r="I102" t="s">
+        <v>43</v>
+      </c>
+      <c r="J102" t="s">
+        <v>440</v>
+      </c>
+      <c r="K102" t="s">
+        <v>441</v>
+      </c>
+      <c r="L102" t="s">
+        <v>23</v>
+      </c>
+      <c r="M102" t="s">
+        <v>23</v>
+      </c>
+      <c r="N102" t="s">
+        <v>23</v>
+      </c>
+      <c r="O102" t="s">
         <v>442</v>
-      </c>
-      <c r="B102" t="s">
-        <v>37</v>
-      </c>
-      <c r="C102" t="s">
-        <v>38</v>
-      </c>
-      <c r="D102" t="s">
-        <v>18</v>
-      </c>
-      <c r="E102" t="s">
-        <v>19</v>
-      </c>
-      <c r="F102" t="s">
-        <v>31</v>
-      </c>
-      <c r="G102" t="s">
-        <v>40</v>
-      </c>
-      <c r="H102" t="s">
-        <v>22</v>
-      </c>
-      <c r="I102" t="s">
-        <v>23</v>
-      </c>
-      <c r="J102" t="s">
-        <v>443</v>
-      </c>
-      <c r="K102" t="s">
-        <v>25</v>
-      </c>
-      <c r="L102" t="s">
-        <v>21</v>
-      </c>
-      <c r="M102" t="s">
-        <v>21</v>
-      </c>
-      <c r="N102" t="s">
-        <v>21</v>
-      </c>
-      <c r="O102" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B103" t="s">
-        <v>37</v>
+        <v>444</v>
       </c>
       <c r="C103" t="s">
-        <v>38</v>
+        <v>257</v>
       </c>
       <c r="D103" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E103" t="s">
         <v>19</v>
       </c>
       <c r="F103" t="s">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="G103" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="H103" t="s">
         <v>22</v>
@@ -6954,45 +6945,45 @@
         <v>23</v>
       </c>
       <c r="J103" t="s">
-        <v>98</v>
+        <v>218</v>
       </c>
       <c r="K103" t="s">
-        <v>103</v>
+        <v>404</v>
       </c>
       <c r="L103" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M103" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N103" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O103" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B104" t="s">
-        <v>75</v>
+        <v>411</v>
       </c>
       <c r="C104" t="s">
-        <v>70</v>
+        <v>426</v>
       </c>
       <c r="D104" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E104" t="s">
         <v>19</v>
       </c>
       <c r="F104" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G104" t="s">
-        <v>49</v>
+        <v>447</v>
       </c>
       <c r="H104" t="s">
         <v>22</v>
@@ -7001,19 +6992,19 @@
         <v>23</v>
       </c>
       <c r="J104" t="s">
+        <v>130</v>
+      </c>
+      <c r="K104" t="s">
         <v>448</v>
       </c>
-      <c r="K104" t="s">
-        <v>140</v>
-      </c>
       <c r="L104" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M104" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N104" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O104" t="s">
         <v>449</v>
@@ -7024,22 +7015,22 @@
         <v>450</v>
       </c>
       <c r="B105" t="s">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="C105" t="s">
-        <v>70</v>
+        <v>206</v>
       </c>
       <c r="D105" t="s">
-        <v>47</v>
+        <v>109</v>
       </c>
       <c r="E105" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F105" t="s">
-        <v>101</v>
+        <v>379</v>
       </c>
       <c r="G105" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="H105" t="s">
         <v>22</v>
@@ -7051,16 +7042,16 @@
         <v>451</v>
       </c>
       <c r="K105" t="s">
-        <v>262</v>
+        <v>73</v>
       </c>
       <c r="L105" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M105" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N105" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O105" t="s">
         <v>452</v>
@@ -7071,90 +7062,90 @@
         <v>453</v>
       </c>
       <c r="B106" t="s">
-        <v>37</v>
+        <v>454</v>
       </c>
       <c r="C106" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D106" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E106" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F106" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G106" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="H106" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I106" t="s">
         <v>23</v>
       </c>
       <c r="J106" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K106" t="s">
-        <v>348</v>
+        <v>311</v>
       </c>
       <c r="L106" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M106" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N106" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O106" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B107" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C107" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="D107" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E107" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F107" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G107" t="s">
-        <v>189</v>
+        <v>48</v>
       </c>
       <c r="H107" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I107" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J107" t="s">
-        <v>457</v>
+        <v>57</v>
       </c>
       <c r="K107" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="L107" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M107" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N107" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O107" t="s">
         <v>458</v>
@@ -7165,43 +7156,43 @@
         <v>459</v>
       </c>
       <c r="B108" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="C108" t="s">
-        <v>182</v>
+        <v>62</v>
       </c>
       <c r="D108" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="E108" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F108" t="s">
-        <v>137</v>
+        <v>31</v>
       </c>
       <c r="G108" t="s">
+        <v>76</v>
+      </c>
+      <c r="H108" t="s">
+        <v>32</v>
+      </c>
+      <c r="I108" t="s">
+        <v>43</v>
+      </c>
+      <c r="J108" t="s">
         <v>460</v>
       </c>
-      <c r="H108" t="s">
-        <v>55</v>
-      </c>
-      <c r="I108" t="s">
-        <v>21</v>
-      </c>
-      <c r="J108" t="s">
-        <v>33</v>
-      </c>
       <c r="K108" t="s">
-        <v>139</v>
+        <v>69</v>
       </c>
       <c r="L108" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M108" t="s">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="N108" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O108" t="s">
         <v>461</v>
@@ -7212,69 +7203,69 @@
         <v>462</v>
       </c>
       <c r="B109" t="s">
+        <v>61</v>
+      </c>
+      <c r="C109" t="s">
+        <v>62</v>
+      </c>
+      <c r="D109" t="s">
+        <v>40</v>
+      </c>
+      <c r="E109" t="s">
+        <v>55</v>
+      </c>
+      <c r="F109" t="s">
+        <v>41</v>
+      </c>
+      <c r="G109" t="s">
+        <v>76</v>
+      </c>
+      <c r="H109" t="s">
+        <v>32</v>
+      </c>
+      <c r="I109" t="s">
+        <v>43</v>
+      </c>
+      <c r="J109" t="s">
+        <v>130</v>
+      </c>
+      <c r="K109" t="s">
+        <v>135</v>
+      </c>
+      <c r="L109" t="s">
+        <v>23</v>
+      </c>
+      <c r="M109" t="s">
+        <v>23</v>
+      </c>
+      <c r="N109" t="s">
+        <v>23</v>
+      </c>
+      <c r="O109" t="s">
         <v>463</v>
-      </c>
-      <c r="C109" t="s">
-        <v>464</v>
-      </c>
-      <c r="D109" t="s">
-        <v>21</v>
-      </c>
-      <c r="E109" t="s">
-        <v>30</v>
-      </c>
-      <c r="F109" t="s">
-        <v>31</v>
-      </c>
-      <c r="G109" t="s">
-        <v>49</v>
-      </c>
-      <c r="H109" t="s">
-        <v>55</v>
-      </c>
-      <c r="I109" t="s">
-        <v>21</v>
-      </c>
-      <c r="J109" t="s">
-        <v>465</v>
-      </c>
-      <c r="K109" t="s">
-        <v>280</v>
-      </c>
-      <c r="L109" t="s">
-        <v>21</v>
-      </c>
-      <c r="M109" t="s">
-        <v>21</v>
-      </c>
-      <c r="N109" t="s">
-        <v>21</v>
-      </c>
-      <c r="O109" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B110" t="s">
-        <v>318</v>
+        <v>107</v>
       </c>
       <c r="C110" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="D110" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="E110" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F110" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G110" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="H110" t="s">
         <v>22</v>
@@ -7283,45 +7274,45 @@
         <v>23</v>
       </c>
       <c r="J110" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="K110" t="s">
-        <v>262</v>
+        <v>168</v>
       </c>
       <c r="L110" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M110" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N110" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O110" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B111" t="s">
-        <v>16</v>
+        <v>107</v>
       </c>
       <c r="C111" t="s">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="D111" t="s">
         <v>18</v>
       </c>
       <c r="E111" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F111" t="s">
-        <v>20</v>
+        <v>133</v>
       </c>
       <c r="G111" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="H111" t="s">
         <v>22</v>
@@ -7330,221 +7321,221 @@
         <v>23</v>
       </c>
       <c r="J111" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="K111" t="s">
-        <v>258</v>
+        <v>284</v>
       </c>
       <c r="L111" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M111" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N111" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O111" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B112" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="C112" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="D112" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E112" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F112" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G112" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="H112" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I112" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J112" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="K112" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="L112" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M112" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N112" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O112" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B113" t="s">
-        <v>357</v>
+        <v>61</v>
       </c>
       <c r="C113" t="s">
-        <v>188</v>
+        <v>62</v>
       </c>
       <c r="D113" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E113" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F113" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="G113" t="s">
-        <v>49</v>
+        <v>213</v>
       </c>
       <c r="H113" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I113" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J113" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="K113" t="s">
-        <v>478</v>
+        <v>98</v>
       </c>
       <c r="L113" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M113" t="s">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="N113" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O113" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B114" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="C114" t="s">
-        <v>148</v>
+        <v>206</v>
       </c>
       <c r="D114" t="s">
-        <v>47</v>
+        <v>109</v>
       </c>
       <c r="E114" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F114" t="s">
-        <v>31</v>
+        <v>165</v>
       </c>
       <c r="G114" t="s">
-        <v>49</v>
+        <v>477</v>
       </c>
       <c r="H114" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="I114" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J114" t="s">
-        <v>481</v>
+        <v>72</v>
       </c>
       <c r="K114" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="L114" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M114" t="s">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="N114" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O114" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B115" t="s">
-        <v>135</v>
+        <v>480</v>
       </c>
       <c r="C115" t="s">
-        <v>182</v>
+        <v>481</v>
       </c>
       <c r="D115" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="E115" t="s">
         <v>19</v>
       </c>
       <c r="F115" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="G115" t="s">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="H115" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="I115" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J115" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="K115" t="s">
-        <v>110</v>
+        <v>302</v>
       </c>
       <c r="L115" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M115" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N115" t="s">
-        <v>486</v>
+        <v>23</v>
       </c>
       <c r="O115" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="B116" t="s">
-        <v>37</v>
+        <v>338</v>
       </c>
       <c r="C116" t="s">
-        <v>38</v>
+        <v>125</v>
       </c>
       <c r="D116" t="s">
         <v>18</v>
@@ -7553,95 +7544,95 @@
         <v>19</v>
       </c>
       <c r="F116" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G116" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="H116" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I116" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J116" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="K116" t="s">
-        <v>25</v>
+        <v>284</v>
       </c>
       <c r="L116" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M116" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N116" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O116" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B117" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C117" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D117" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E117" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F117" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="G117" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H117" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I117" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J117" t="s">
-        <v>98</v>
+        <v>488</v>
       </c>
       <c r="K117" t="s">
-        <v>150</v>
+        <v>45</v>
       </c>
       <c r="L117" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M117" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N117" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O117" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B118" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C118" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D118" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E118" t="s">
         <v>19</v>
@@ -7650,89 +7641,89 @@
         <v>31</v>
       </c>
       <c r="G118" t="s">
-        <v>494</v>
+        <v>82</v>
       </c>
       <c r="H118" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I118" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J118" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="K118" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="L118" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M118" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N118" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O118" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B119" t="s">
-        <v>37</v>
+        <v>375</v>
       </c>
       <c r="C119" t="s">
-        <v>38</v>
+        <v>212</v>
       </c>
       <c r="D119" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E119" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F119" t="s">
-        <v>39</v>
+        <v>165</v>
       </c>
       <c r="G119" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="H119" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I119" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J119" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="K119" t="s">
-        <v>276</v>
+        <v>495</v>
       </c>
       <c r="L119" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M119" t="s">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="N119" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O119" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B120" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C120" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D120" t="s">
         <v>18</v>
@@ -7744,7 +7735,7 @@
         <v>31</v>
       </c>
       <c r="G120" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="H120" t="s">
         <v>22</v>
@@ -7753,45 +7744,45 @@
         <v>23</v>
       </c>
       <c r="J120" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="K120" t="s">
-        <v>34</v>
+        <v>176</v>
       </c>
       <c r="L120" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M120" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N120" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O120" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B121" t="s">
-        <v>37</v>
+        <v>163</v>
       </c>
       <c r="C121" t="s">
-        <v>38</v>
+        <v>206</v>
       </c>
       <c r="D121" t="s">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="E121" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F121" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="G121" t="s">
-        <v>113</v>
+        <v>501</v>
       </c>
       <c r="H121" t="s">
         <v>22</v>
@@ -7800,442 +7791,442 @@
         <v>23</v>
       </c>
       <c r="J121" t="s">
+        <v>502</v>
+      </c>
+      <c r="K121" t="s">
+        <v>141</v>
+      </c>
+      <c r="L121" t="s">
+        <v>23</v>
+      </c>
+      <c r="M121" t="s">
+        <v>23</v>
+      </c>
+      <c r="N121" t="s">
+        <v>503</v>
+      </c>
+      <c r="O121" t="s">
         <v>504</v>
-      </c>
-      <c r="K121" t="s">
-        <v>95</v>
-      </c>
-      <c r="L121" t="s">
-        <v>21</v>
-      </c>
-      <c r="M121" t="s">
-        <v>21</v>
-      </c>
-      <c r="N121" t="s">
-        <v>241</v>
-      </c>
-      <c r="O121" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>505</v>
+      </c>
+      <c r="B122" t="s">
+        <v>61</v>
+      </c>
+      <c r="C122" t="s">
+        <v>62</v>
+      </c>
+      <c r="D122" t="s">
+        <v>40</v>
+      </c>
+      <c r="E122" t="s">
+        <v>55</v>
+      </c>
+      <c r="F122" t="s">
+        <v>41</v>
+      </c>
+      <c r="G122" t="s">
+        <v>63</v>
+      </c>
+      <c r="H122" t="s">
+        <v>32</v>
+      </c>
+      <c r="I122" t="s">
+        <v>43</v>
+      </c>
+      <c r="J122" t="s">
         <v>506</v>
       </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="s">
-        <v>17</v>
-      </c>
-      <c r="D122" t="s">
-        <v>18</v>
-      </c>
-      <c r="E122" t="s">
-        <v>19</v>
-      </c>
-      <c r="F122" t="s">
-        <v>39</v>
-      </c>
-      <c r="G122" t="s">
-        <v>169</v>
-      </c>
-      <c r="H122" t="s">
-        <v>22</v>
-      </c>
-      <c r="I122" t="s">
-        <v>23</v>
-      </c>
-      <c r="J122" t="s">
+      <c r="K122" t="s">
+        <v>69</v>
+      </c>
+      <c r="L122" t="s">
+        <v>23</v>
+      </c>
+      <c r="M122" t="s">
+        <v>23</v>
+      </c>
+      <c r="N122" t="s">
+        <v>23</v>
+      </c>
+      <c r="O122" t="s">
         <v>507</v>
-      </c>
-      <c r="K122" t="s">
-        <v>139</v>
-      </c>
-      <c r="L122" t="s">
-        <v>21</v>
-      </c>
-      <c r="M122" t="s">
-        <v>21</v>
-      </c>
-      <c r="N122" t="s">
-        <v>21</v>
-      </c>
-      <c r="O122" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>508</v>
+      </c>
+      <c r="B123" t="s">
+        <v>61</v>
+      </c>
+      <c r="C123" t="s">
+        <v>62</v>
+      </c>
+      <c r="D123" t="s">
+        <v>40</v>
+      </c>
+      <c r="E123" t="s">
+        <v>55</v>
+      </c>
+      <c r="F123" t="s">
+        <v>31</v>
+      </c>
+      <c r="G123" t="s">
+        <v>63</v>
+      </c>
+      <c r="H123" t="s">
+        <v>32</v>
+      </c>
+      <c r="I123" t="s">
+        <v>43</v>
+      </c>
+      <c r="J123" t="s">
+        <v>130</v>
+      </c>
+      <c r="K123" t="s">
+        <v>176</v>
+      </c>
+      <c r="L123" t="s">
+        <v>23</v>
+      </c>
+      <c r="M123" t="s">
+        <v>23</v>
+      </c>
+      <c r="N123" t="s">
+        <v>23</v>
+      </c>
+      <c r="O123" t="s">
         <v>509</v>
-      </c>
-      <c r="B123" t="s">
-        <v>37</v>
-      </c>
-      <c r="C123" t="s">
-        <v>38</v>
-      </c>
-      <c r="D123" t="s">
-        <v>18</v>
-      </c>
-      <c r="E123" t="s">
-        <v>19</v>
-      </c>
-      <c r="F123" t="s">
-        <v>39</v>
-      </c>
-      <c r="G123" t="s">
-        <v>510</v>
-      </c>
-      <c r="H123" t="s">
-        <v>22</v>
-      </c>
-      <c r="I123" t="s">
-        <v>23</v>
-      </c>
-      <c r="J123" t="s">
-        <v>331</v>
-      </c>
-      <c r="K123" t="s">
-        <v>424</v>
-      </c>
-      <c r="L123" t="s">
-        <v>21</v>
-      </c>
-      <c r="M123" t="s">
-        <v>21</v>
-      </c>
-      <c r="N123" t="s">
-        <v>21</v>
-      </c>
-      <c r="O123" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B124" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C124" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D124" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E124" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F124" t="s">
         <v>31</v>
       </c>
       <c r="G124" t="s">
+        <v>511</v>
+      </c>
+      <c r="H124" t="s">
+        <v>32</v>
+      </c>
+      <c r="I124" t="s">
+        <v>43</v>
+      </c>
+      <c r="J124" t="s">
+        <v>512</v>
+      </c>
+      <c r="K124" t="s">
+        <v>215</v>
+      </c>
+      <c r="L124" t="s">
+        <v>23</v>
+      </c>
+      <c r="M124" t="s">
+        <v>23</v>
+      </c>
+      <c r="N124" t="s">
+        <v>23</v>
+      </c>
+      <c r="O124" t="s">
         <v>513</v>
-      </c>
-      <c r="H124" t="s">
-        <v>22</v>
-      </c>
-      <c r="I124" t="s">
-        <v>23</v>
-      </c>
-      <c r="J124" t="s">
-        <v>514</v>
-      </c>
-      <c r="K124" t="s">
-        <v>66</v>
-      </c>
-      <c r="L124" t="s">
-        <v>21</v>
-      </c>
-      <c r="M124" t="s">
-        <v>21</v>
-      </c>
-      <c r="N124" t="s">
-        <v>21</v>
-      </c>
-      <c r="O124" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>514</v>
+      </c>
+      <c r="B125" t="s">
+        <v>61</v>
+      </c>
+      <c r="C125" t="s">
+        <v>62</v>
+      </c>
+      <c r="D125" t="s">
+        <v>40</v>
+      </c>
+      <c r="E125" t="s">
+        <v>55</v>
+      </c>
+      <c r="F125" t="s">
+        <v>41</v>
+      </c>
+      <c r="G125" t="s">
+        <v>76</v>
+      </c>
+      <c r="H125" t="s">
+        <v>32</v>
+      </c>
+      <c r="I125" t="s">
+        <v>43</v>
+      </c>
+      <c r="J125" t="s">
+        <v>515</v>
+      </c>
+      <c r="K125" t="s">
+        <v>298</v>
+      </c>
+      <c r="L125" t="s">
+        <v>23</v>
+      </c>
+      <c r="M125" t="s">
+        <v>23</v>
+      </c>
+      <c r="N125" t="s">
+        <v>23</v>
+      </c>
+      <c r="O125" t="s">
         <v>516</v>
-      </c>
-      <c r="B125" t="s">
-        <v>381</v>
-      </c>
-      <c r="C125" t="s">
-        <v>382</v>
-      </c>
-      <c r="D125" t="s">
-        <v>383</v>
-      </c>
-      <c r="E125" t="s">
-        <v>30</v>
-      </c>
-      <c r="F125" t="s">
-        <v>101</v>
-      </c>
-      <c r="G125" t="s">
-        <v>113</v>
-      </c>
-      <c r="H125" t="s">
-        <v>22</v>
-      </c>
-      <c r="I125" t="s">
-        <v>299</v>
-      </c>
-      <c r="J125" t="s">
-        <v>122</v>
-      </c>
-      <c r="K125" t="s">
-        <v>386</v>
-      </c>
-      <c r="L125" t="s">
-        <v>21</v>
-      </c>
-      <c r="M125" t="s">
-        <v>21</v>
-      </c>
-      <c r="N125" t="s">
-        <v>21</v>
-      </c>
-      <c r="O125" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B126" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C126" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="D126" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E126" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F126" t="s">
         <v>31</v>
       </c>
       <c r="G126" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="H126" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I126" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J126" t="s">
+        <v>518</v>
+      </c>
+      <c r="K126" t="s">
+        <v>73</v>
+      </c>
+      <c r="L126" t="s">
+        <v>23</v>
+      </c>
+      <c r="M126" t="s">
+        <v>23</v>
+      </c>
+      <c r="N126" t="s">
+        <v>23</v>
+      </c>
+      <c r="O126" t="s">
         <v>519</v>
-      </c>
-      <c r="K126" t="s">
-        <v>154</v>
-      </c>
-      <c r="L126" t="s">
-        <v>21</v>
-      </c>
-      <c r="M126" t="s">
-        <v>21</v>
-      </c>
-      <c r="N126" t="s">
-        <v>21</v>
-      </c>
-      <c r="O126" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>520</v>
+      </c>
+      <c r="B127" t="s">
+        <v>61</v>
+      </c>
+      <c r="C127" t="s">
+        <v>62</v>
+      </c>
+      <c r="D127" t="s">
+        <v>40</v>
+      </c>
+      <c r="E127" t="s">
+        <v>55</v>
+      </c>
+      <c r="F127" t="s">
+        <v>20</v>
+      </c>
+      <c r="G127" t="s">
+        <v>21</v>
+      </c>
+      <c r="H127" t="s">
+        <v>32</v>
+      </c>
+      <c r="I127" t="s">
+        <v>43</v>
+      </c>
+      <c r="J127" t="s">
         <v>521</v>
       </c>
-      <c r="B127" t="s">
-        <v>37</v>
-      </c>
-      <c r="C127" t="s">
-        <v>38</v>
-      </c>
-      <c r="D127" t="s">
-        <v>18</v>
-      </c>
-      <c r="E127" t="s">
-        <v>19</v>
-      </c>
-      <c r="F127" t="s">
-        <v>39</v>
-      </c>
-      <c r="G127" t="s">
-        <v>40</v>
-      </c>
-      <c r="H127" t="s">
-        <v>22</v>
-      </c>
-      <c r="I127" t="s">
-        <v>23</v>
-      </c>
-      <c r="J127" t="s">
+      <c r="K127" t="s">
+        <v>127</v>
+      </c>
+      <c r="L127" t="s">
+        <v>23</v>
+      </c>
+      <c r="M127" t="s">
+        <v>23</v>
+      </c>
+      <c r="N127" t="s">
+        <v>265</v>
+      </c>
+      <c r="O127" t="s">
         <v>522</v>
-      </c>
-      <c r="K127" t="s">
-        <v>110</v>
-      </c>
-      <c r="L127" t="s">
-        <v>21</v>
-      </c>
-      <c r="M127" t="s">
-        <v>21</v>
-      </c>
-      <c r="N127" t="s">
-        <v>21</v>
-      </c>
-      <c r="O127" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>523</v>
+      </c>
+      <c r="B128" t="s">
+        <v>53</v>
+      </c>
+      <c r="C128" t="s">
+        <v>54</v>
+      </c>
+      <c r="D128" t="s">
+        <v>40</v>
+      </c>
+      <c r="E128" t="s">
+        <v>55</v>
+      </c>
+      <c r="F128" t="s">
+        <v>41</v>
+      </c>
+      <c r="G128" t="s">
+        <v>195</v>
+      </c>
+      <c r="H128" t="s">
+        <v>32</v>
+      </c>
+      <c r="I128" t="s">
+        <v>43</v>
+      </c>
+      <c r="J128" t="s">
         <v>524</v>
       </c>
-      <c r="B128" t="s">
-        <v>357</v>
-      </c>
-      <c r="C128" t="s">
-        <v>188</v>
-      </c>
-      <c r="D128" t="s">
-        <v>18</v>
-      </c>
-      <c r="E128" t="s">
-        <v>19</v>
-      </c>
-      <c r="F128" t="s">
-        <v>137</v>
-      </c>
-      <c r="G128" t="s">
-        <v>113</v>
-      </c>
-      <c r="H128" t="s">
-        <v>22</v>
-      </c>
-      <c r="I128" t="s">
-        <v>23</v>
-      </c>
-      <c r="J128" t="s">
+      <c r="K128" t="s">
+        <v>167</v>
+      </c>
+      <c r="L128" t="s">
+        <v>23</v>
+      </c>
+      <c r="M128" t="s">
+        <v>23</v>
+      </c>
+      <c r="N128" t="s">
+        <v>23</v>
+      </c>
+      <c r="O128" t="s">
         <v>525</v>
-      </c>
-      <c r="K128" t="s">
-        <v>262</v>
-      </c>
-      <c r="L128" t="s">
-        <v>21</v>
-      </c>
-      <c r="M128" t="s">
-        <v>140</v>
-      </c>
-      <c r="N128" t="s">
-        <v>21</v>
-      </c>
-      <c r="O128" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>526</v>
+      </c>
+      <c r="B129" t="s">
+        <v>61</v>
+      </c>
+      <c r="C129" t="s">
+        <v>62</v>
+      </c>
+      <c r="D129" t="s">
+        <v>40</v>
+      </c>
+      <c r="E129" t="s">
+        <v>55</v>
+      </c>
+      <c r="F129" t="s">
+        <v>41</v>
+      </c>
+      <c r="G129" t="s">
         <v>527</v>
       </c>
-      <c r="B129" t="s">
-        <v>75</v>
-      </c>
-      <c r="C129" t="s">
-        <v>296</v>
-      </c>
-      <c r="D129" t="s">
-        <v>297</v>
-      </c>
-      <c r="E129" t="s">
-        <v>19</v>
-      </c>
-      <c r="F129" t="s">
-        <v>39</v>
-      </c>
-      <c r="G129" t="s">
-        <v>169</v>
-      </c>
       <c r="H129" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I129" t="s">
-        <v>299</v>
+        <v>43</v>
       </c>
       <c r="J129" t="s">
+        <v>351</v>
+      </c>
+      <c r="K129" t="s">
+        <v>441</v>
+      </c>
+      <c r="L129" t="s">
+        <v>23</v>
+      </c>
+      <c r="M129" t="s">
+        <v>23</v>
+      </c>
+      <c r="N129" t="s">
+        <v>23</v>
+      </c>
+      <c r="O129" t="s">
         <v>528</v>
-      </c>
-      <c r="K129" t="s">
-        <v>164</v>
-      </c>
-      <c r="L129" t="s">
-        <v>21</v>
-      </c>
-      <c r="M129" t="s">
-        <v>21</v>
-      </c>
-      <c r="N129" t="s">
-        <v>21</v>
-      </c>
-      <c r="O129" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B130" t="s">
-        <v>357</v>
+        <v>61</v>
       </c>
       <c r="C130" t="s">
-        <v>188</v>
+        <v>62</v>
       </c>
       <c r="D130" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E130" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F130" t="s">
         <v>31</v>
       </c>
       <c r="G130" t="s">
-        <v>169</v>
+        <v>530</v>
       </c>
       <c r="H130" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I130" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J130" t="s">
         <v>531</v>
       </c>
       <c r="K130" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="L130" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M130" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N130" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O130" t="s">
         <v>532</v>
@@ -8246,90 +8237,90 @@
         <v>533</v>
       </c>
       <c r="B131" t="s">
-        <v>357</v>
+        <v>399</v>
       </c>
       <c r="C131" t="s">
-        <v>188</v>
+        <v>400</v>
       </c>
       <c r="D131" t="s">
-        <v>18</v>
+        <v>401</v>
       </c>
       <c r="E131" t="s">
         <v>19</v>
       </c>
       <c r="F131" t="s">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="G131" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="H131" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I131" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J131" t="s">
+        <v>150</v>
+      </c>
+      <c r="K131" t="s">
+        <v>404</v>
+      </c>
+      <c r="L131" t="s">
+        <v>23</v>
+      </c>
+      <c r="M131" t="s">
+        <v>23</v>
+      </c>
+      <c r="N131" t="s">
+        <v>23</v>
+      </c>
+      <c r="O131" t="s">
         <v>534</v>
-      </c>
-      <c r="K131" t="s">
-        <v>195</v>
-      </c>
-      <c r="L131" t="s">
-        <v>21</v>
-      </c>
-      <c r="M131" t="s">
-        <v>21</v>
-      </c>
-      <c r="N131" t="s">
-        <v>21</v>
-      </c>
-      <c r="O131" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B132" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="C132" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="D132" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E132" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F132" t="s">
         <v>31</v>
       </c>
       <c r="G132" t="s">
-        <v>169</v>
+        <v>76</v>
       </c>
       <c r="H132" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I132" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J132" t="s">
-        <v>194</v>
+        <v>536</v>
       </c>
       <c r="K132" t="s">
-        <v>308</v>
+        <v>180</v>
       </c>
       <c r="L132" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M132" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N132" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O132" t="s">
         <v>537</v>
@@ -8340,339 +8331,339 @@
         <v>538</v>
       </c>
       <c r="B133" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C133" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="D133" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E133" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F133" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G133" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="H133" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I133" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J133" t="s">
         <v>539</v>
       </c>
       <c r="K133" t="s">
+        <v>141</v>
+      </c>
+      <c r="L133" t="s">
+        <v>23</v>
+      </c>
+      <c r="M133" t="s">
+        <v>23</v>
+      </c>
+      <c r="N133" t="s">
+        <v>23</v>
+      </c>
+      <c r="O133" t="s">
         <v>540</v>
-      </c>
-      <c r="L133" t="s">
-        <v>21</v>
-      </c>
-      <c r="M133" t="s">
-        <v>21</v>
-      </c>
-      <c r="N133" t="s">
-        <v>21</v>
-      </c>
-      <c r="O133" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>541</v>
+      </c>
+      <c r="B134" t="s">
+        <v>375</v>
+      </c>
+      <c r="C134" t="s">
+        <v>212</v>
+      </c>
+      <c r="D134" t="s">
+        <v>40</v>
+      </c>
+      <c r="E134" t="s">
+        <v>55</v>
+      </c>
+      <c r="F134" t="s">
+        <v>165</v>
+      </c>
+      <c r="G134" t="s">
+        <v>21</v>
+      </c>
+      <c r="H134" t="s">
+        <v>32</v>
+      </c>
+      <c r="I134" t="s">
+        <v>43</v>
+      </c>
+      <c r="J134" t="s">
         <v>542</v>
       </c>
-      <c r="B134" t="s">
-        <v>147</v>
-      </c>
-      <c r="C134" t="s">
-        <v>148</v>
-      </c>
-      <c r="D134" t="s">
-        <v>47</v>
-      </c>
-      <c r="E134" t="s">
-        <v>30</v>
-      </c>
-      <c r="F134" t="s">
-        <v>31</v>
-      </c>
-      <c r="G134" t="s">
-        <v>113</v>
-      </c>
-      <c r="H134" t="s">
-        <v>55</v>
-      </c>
-      <c r="I134" t="s">
-        <v>21</v>
-      </c>
-      <c r="J134" t="s">
+      <c r="K134" t="s">
+        <v>284</v>
+      </c>
+      <c r="L134" t="s">
+        <v>23</v>
+      </c>
+      <c r="M134" t="s">
+        <v>168</v>
+      </c>
+      <c r="N134" t="s">
+        <v>23</v>
+      </c>
+      <c r="O134" t="s">
         <v>543</v>
-      </c>
-      <c r="K134" t="s">
-        <v>66</v>
-      </c>
-      <c r="L134" t="s">
-        <v>21</v>
-      </c>
-      <c r="M134" t="s">
-        <v>21</v>
-      </c>
-      <c r="N134" t="s">
-        <v>21</v>
-      </c>
-      <c r="O134" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>544</v>
+      </c>
+      <c r="B135" t="s">
+        <v>107</v>
+      </c>
+      <c r="C135" t="s">
+        <v>318</v>
+      </c>
+      <c r="D135" t="s">
+        <v>319</v>
+      </c>
+      <c r="E135" t="s">
+        <v>55</v>
+      </c>
+      <c r="F135" t="s">
+        <v>41</v>
+      </c>
+      <c r="G135" t="s">
+        <v>195</v>
+      </c>
+      <c r="H135" t="s">
+        <v>32</v>
+      </c>
+      <c r="I135" t="s">
+        <v>33</v>
+      </c>
+      <c r="J135" t="s">
         <v>545</v>
       </c>
-      <c r="B135" t="s">
-        <v>135</v>
-      </c>
-      <c r="C135" t="s">
-        <v>182</v>
-      </c>
-      <c r="D135" t="s">
-        <v>77</v>
-      </c>
-      <c r="E135" t="s">
-        <v>19</v>
-      </c>
-      <c r="F135" t="s">
-        <v>31</v>
-      </c>
-      <c r="G135" t="s">
-        <v>49</v>
-      </c>
-      <c r="H135" t="s">
-        <v>22</v>
-      </c>
-      <c r="I135" t="s">
-        <v>21</v>
-      </c>
-      <c r="J135" t="s">
+      <c r="K135" t="s">
+        <v>190</v>
+      </c>
+      <c r="L135" t="s">
+        <v>23</v>
+      </c>
+      <c r="M135" t="s">
+        <v>23</v>
+      </c>
+      <c r="N135" t="s">
+        <v>23</v>
+      </c>
+      <c r="O135" t="s">
         <v>546</v>
-      </c>
-      <c r="K135" t="s">
-        <v>547</v>
-      </c>
-      <c r="L135" t="s">
-        <v>21</v>
-      </c>
-      <c r="M135" t="s">
-        <v>21</v>
-      </c>
-      <c r="N135" t="s">
-        <v>21</v>
-      </c>
-      <c r="O135" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B136" t="s">
-        <v>126</v>
+        <v>375</v>
       </c>
       <c r="C136" t="s">
-        <v>550</v>
+        <v>212</v>
       </c>
       <c r="D136" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E136" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F136" t="s">
         <v>31</v>
       </c>
       <c r="G136" t="s">
-        <v>40</v>
+        <v>195</v>
       </c>
       <c r="H136" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I136" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J136" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="K136" t="s">
-        <v>150</v>
+        <v>94</v>
       </c>
       <c r="L136" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M136" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N136" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O136" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B137" t="s">
-        <v>135</v>
+        <v>375</v>
       </c>
       <c r="C137" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="D137" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="E137" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F137" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G137" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="H137" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="I137" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J137" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="K137" t="s">
-        <v>375</v>
+        <v>219</v>
       </c>
       <c r="L137" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M137" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N137" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O137" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B138" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="C138" t="s">
-        <v>182</v>
+        <v>54</v>
       </c>
       <c r="D138" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="E138" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F138" t="s">
-        <v>137</v>
+        <v>31</v>
       </c>
       <c r="G138" t="s">
-        <v>49</v>
+        <v>195</v>
       </c>
       <c r="H138" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I138" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J138" t="s">
-        <v>557</v>
+        <v>218</v>
       </c>
       <c r="K138" t="s">
-        <v>72</v>
+        <v>328</v>
       </c>
       <c r="L138" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M138" t="s">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="N138" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O138" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="B139" t="s">
-        <v>295</v>
+        <v>61</v>
       </c>
       <c r="C139" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="D139" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E139" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F139" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G139" t="s">
-        <v>560</v>
+        <v>82</v>
       </c>
       <c r="H139" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I139" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J139" t="s">
-        <v>304</v>
+        <v>556</v>
       </c>
       <c r="K139" t="s">
-        <v>308</v>
+        <v>557</v>
       </c>
       <c r="L139" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M139" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N139" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O139" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B140" t="s">
-        <v>357</v>
+        <v>29</v>
       </c>
       <c r="C140" t="s">
-        <v>188</v>
+        <v>30</v>
       </c>
       <c r="D140" t="s">
         <v>18</v>
@@ -8681,222 +8672,222 @@
         <v>19</v>
       </c>
       <c r="F140" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G140" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="H140" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="I140" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J140" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="K140" t="s">
-        <v>154</v>
+        <v>98</v>
       </c>
       <c r="L140" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M140" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N140" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O140" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>562</v>
+      </c>
+      <c r="B141" t="s">
+        <v>163</v>
+      </c>
+      <c r="C141" t="s">
+        <v>206</v>
+      </c>
+      <c r="D141" t="s">
+        <v>109</v>
+      </c>
+      <c r="E141" t="s">
+        <v>55</v>
+      </c>
+      <c r="F141" t="s">
+        <v>31</v>
+      </c>
+      <c r="G141" t="s">
+        <v>82</v>
+      </c>
+      <c r="H141" t="s">
+        <v>32</v>
+      </c>
+      <c r="I141" t="s">
+        <v>23</v>
+      </c>
+      <c r="J141" t="s">
+        <v>563</v>
+      </c>
+      <c r="K141" t="s">
+        <v>564</v>
+      </c>
+      <c r="L141" t="s">
+        <v>23</v>
+      </c>
+      <c r="M141" t="s">
+        <v>23</v>
+      </c>
+      <c r="N141" t="s">
+        <v>23</v>
+      </c>
+      <c r="O141" t="s">
         <v>565</v>
-      </c>
-      <c r="B141" t="s">
-        <v>381</v>
-      </c>
-      <c r="C141" t="s">
-        <v>382</v>
-      </c>
-      <c r="D141" t="s">
-        <v>383</v>
-      </c>
-      <c r="E141" t="s">
-        <v>30</v>
-      </c>
-      <c r="F141" t="s">
-        <v>101</v>
-      </c>
-      <c r="G141" t="s">
-        <v>121</v>
-      </c>
-      <c r="H141" t="s">
-        <v>55</v>
-      </c>
-      <c r="I141" t="s">
-        <v>21</v>
-      </c>
-      <c r="J141" t="s">
-        <v>566</v>
-      </c>
-      <c r="K141" t="s">
-        <v>262</v>
-      </c>
-      <c r="L141" t="s">
-        <v>21</v>
-      </c>
-      <c r="M141" t="s">
-        <v>21</v>
-      </c>
-      <c r="N141" t="s">
-        <v>21</v>
-      </c>
-      <c r="O141" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B142" t="s">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="C142" t="s">
-        <v>550</v>
+        <v>567</v>
       </c>
       <c r="D142" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E142" t="s">
         <v>19</v>
       </c>
       <c r="F142" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G142" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="H142" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I142" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="J142" t="s">
+        <v>568</v>
+      </c>
+      <c r="K142" t="s">
+        <v>176</v>
+      </c>
+      <c r="L142" t="s">
+        <v>23</v>
+      </c>
+      <c r="M142" t="s">
+        <v>23</v>
+      </c>
+      <c r="N142" t="s">
+        <v>23</v>
+      </c>
+      <c r="O142" t="s">
         <v>569</v>
-      </c>
-      <c r="K142" t="s">
-        <v>269</v>
-      </c>
-      <c r="L142" t="s">
-        <v>21</v>
-      </c>
-      <c r="M142" t="s">
-        <v>21</v>
-      </c>
-      <c r="N142" t="s">
-        <v>21</v>
-      </c>
-      <c r="O142" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B143" t="s">
-        <v>572</v>
+        <v>163</v>
       </c>
       <c r="C143" t="s">
-        <v>168</v>
+        <v>206</v>
       </c>
       <c r="D143" t="s">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="E143" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F143" t="s">
         <v>31</v>
       </c>
       <c r="G143" t="s">
-        <v>573</v>
+        <v>76</v>
       </c>
       <c r="H143" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="I143" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J143" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="K143" t="s">
-        <v>150</v>
+        <v>393</v>
       </c>
       <c r="L143" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M143" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N143" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O143" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B144" t="s">
-        <v>28</v>
+        <v>163</v>
       </c>
       <c r="C144" t="s">
-        <v>29</v>
+        <v>206</v>
       </c>
       <c r="D144" t="s">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="E144" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="F144" t="s">
-        <v>31</v>
+        <v>165</v>
       </c>
       <c r="G144" t="s">
-        <v>189</v>
+        <v>82</v>
       </c>
       <c r="H144" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="I144" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J144" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="K144" t="s">
-        <v>227</v>
+        <v>104</v>
       </c>
       <c r="L144" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M144" t="s">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="N144" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O144" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB58F288-1A6A-44D3-8AA3-E99DE1893A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{852F700C-A3A5-4B44-8E39-52D873C202AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="1635" windowWidth="16920" windowHeight="14565" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2190" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2145" uniqueCount="569">
   <si>
     <t>Time</t>
   </si>
@@ -62,6 +62,150 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>05/06/2026 6:15:28 PM</t>
+  </si>
+  <si>
+    <t>680 - Medium</t>
+  </si>
+  <si>
+    <t>Jesus Carbajal</t>
+  </si>
+  <si>
+    <t>Active Drivers, Towing and Recovery</t>
+  </si>
+  <si>
+    <t>HAAS Alert, Towing and Recovery</t>
+  </si>
+  <si>
+    <t>Inattentive Driving</t>
+  </si>
+  <si>
+    <t>Wet Road, Light Traffic</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>Tim Neff Jr.</t>
+  </si>
+  <si>
+    <t>Professional Drive, Port Arthur, TX, 77627</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ff93-2bc8-5ff4-87de-ffed8bce9121</t>
+  </si>
+  <si>
+    <t>05/06/2026 10:49:01 AM</t>
+  </si>
+  <si>
+    <t>673 - Heavy</t>
+  </si>
+  <si>
+    <t>Kyle Ray</t>
+  </si>
+  <si>
+    <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
+  </si>
+  <si>
+    <t>HAAS Alert, Heavy Haul</t>
+  </si>
+  <si>
+    <t>Drowsiness</t>
+  </si>
+  <si>
+    <t>Very Drowsy, Light Traffic</t>
+  </si>
+  <si>
+    <t>Coached</t>
+  </si>
+  <si>
+    <t>Eddie Bowden</t>
+  </si>
+  <si>
+    <t>I 10, Eminence, TX, 77597</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fdfa-6df8-54f7-bf4a-fab794afbe08</t>
+  </si>
+  <si>
+    <t>05/04/2026 2:55:02 PM</t>
+  </si>
+  <si>
+    <t>669 - Heavy</t>
+  </si>
+  <si>
+    <t>Jason Walker</t>
+  </si>
+  <si>
+    <t>No Seat Belt</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>West Cardinal Drive, Beaumont, TX, 77710</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f48e-f389-50f8-87be-6562e2798e54</t>
+  </si>
+  <si>
+    <t>05/04/2026 11:04:48 AM</t>
+  </si>
+  <si>
+    <t>632 - Heavy</t>
+  </si>
+  <si>
+    <t>Gary Worley</t>
+  </si>
+  <si>
+    <t>Active Drivers, Heavy Haul</t>
+  </si>
+  <si>
+    <t>5269 Mustang-Chocolate Bayou Road, Liverpool, TX, 77511</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f3bc-29ec-5cbd-8282-0b221781d62e</t>
+  </si>
+  <si>
+    <t>05/03/2026 7:49:58 PM</t>
+  </si>
+  <si>
+    <t>667 - Medium</t>
+  </si>
+  <si>
+    <t>Jeremy Myers</t>
+  </si>
+  <si>
+    <t>Towing and Recovery</t>
+  </si>
+  <si>
+    <t>362 Simmons Road, 1.9 mi N Vidor, Orange County, TX, 77662</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f076-9dc7-55a8-867a-6a41fd2b62ac</t>
+  </si>
+  <si>
     <t>05/02/2026 7:49:16 AM</t>
   </si>
   <si>
@@ -71,33 +215,12 @@
     <t>Paul Kunze Jr</t>
   </si>
   <si>
-    <t>Active Drivers, Towing and Recovery</t>
-  </si>
-  <si>
-    <t>HAAS Alert, Towing and Recovery</t>
-  </si>
-  <si>
     <t>Mobile Usage</t>
   </si>
   <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
-    <t>Tim Neff Jr.</t>
-  </si>
-  <si>
-    <t>West Cardinal Drive, Beaumont, TX, 77710</t>
-  </si>
-  <si>
     <t>44</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e8bc-6e70-5526-87d9-b05bb8910029</t>
   </si>
   <si>
@@ -110,9 +233,6 @@
     <t>Phillip Metz</t>
   </si>
   <si>
-    <t>Wet Road, Light Traffic</t>
-  </si>
-  <si>
     <t>6425 Highway 347, Beaumont, TX, 77705</t>
   </si>
   <si>
@@ -125,9 +245,6 @@
     <t>05/01/2026 6:20:21 PM</t>
   </si>
   <si>
-    <t>No Seat Belt</t>
-  </si>
-  <si>
     <t>Wet Road, Light Traffic, Raining</t>
   </si>
   <si>
@@ -143,24 +260,9 @@
     <t>05/01/2026 9:24:31 AM</t>
   </si>
   <si>
-    <t>632 - Heavy</t>
-  </si>
-  <si>
-    <t>Gary Worley</t>
-  </si>
-  <si>
-    <t>Active Drivers, Heavy Haul</t>
-  </si>
-  <si>
-    <t>HAAS Alert, Heavy Haul</t>
-  </si>
-  <si>
     <t>Wet Road, Construction, Light Traffic</t>
   </si>
   <si>
-    <t>Eddie Bowden</t>
-  </si>
-  <si>
     <t>State Highway 124, Cheek, TX, 77705</t>
   </si>
   <si>
@@ -173,9 +275,6 @@
     <t>04/30/2026 10:24:39 PM</t>
   </si>
   <si>
-    <t>Drowsiness</t>
-  </si>
-  <si>
     <t>Very Drowsy, Wet Road, Light Traffic, Night</t>
   </si>
   <si>
@@ -206,21 +305,12 @@
     <t>04/28/2026 10:39:38 AM</t>
   </si>
   <si>
-    <t>680 - Medium</t>
-  </si>
-  <si>
-    <t>Jesus Carbajal</t>
-  </si>
-  <si>
     <t>Passengers, Light Traffic</t>
   </si>
   <si>
     <t>I 10, Vinton, LA, 70668</t>
   </si>
   <si>
-    <t>36</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d4be-f767-5552-9776-eea7c53edc2d</t>
   </si>
   <si>
@@ -239,12 +329,6 @@
     <t>04/27/2026 8:54:16 AM</t>
   </si>
   <si>
-    <t>669 - Heavy</t>
-  </si>
-  <si>
-    <t>Jason Walker</t>
-  </si>
-  <si>
     <t>272 5th Street, Sour Lake, TX, 77659</t>
   </si>
   <si>
@@ -269,12 +353,6 @@
     <t>04/24/2026 8:06:44 PM</t>
   </si>
   <si>
-    <t>Kyle Ray</t>
-  </si>
-  <si>
-    <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
-  </si>
-  <si>
     <t>7838 Fannett Road, Beaumont, TX, 77705</t>
   </si>
   <si>
@@ -308,9 +386,6 @@
     <t>Moderate Traffic</t>
   </si>
   <si>
-    <t>Coached</t>
-  </si>
-  <si>
     <t>8401 Washington Boulevard, Beaumont, TX, 77707</t>
   </si>
   <si>
@@ -338,9 +413,6 @@
     <t>04/21/2026 5:20:10 PM</t>
   </si>
   <si>
-    <t>I 10, Eminence, TX, 77597</t>
-  </si>
-  <si>
     <t>63</t>
   </si>
   <si>
@@ -401,9 +473,6 @@
     <t>I 10;US 69;US 96;US 287, Beaumont, TX, 77702</t>
   </si>
   <si>
-    <t>38</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544591e7-ac88-54d6-98a8-4bfe3fad16a5</t>
   </si>
   <si>
@@ -494,15 +563,6 @@
     <t>04/11/2026 7:55:26 PM</t>
   </si>
   <si>
-    <t>667 - Medium</t>
-  </si>
-  <si>
-    <t>Jeremy Myers</t>
-  </si>
-  <si>
-    <t>Towing and Recovery</t>
-  </si>
-  <si>
     <t>FM 105, 7.6 mi ESE Silsbee, Jasper County, TX, 77615</t>
   </si>
   <si>
@@ -593,9 +653,6 @@
     <t>Wet Road, Construction, Light Traffic, Raining</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455a30-e5ca-5116-bf04-94e46dcd707c</t>
   </si>
   <si>
@@ -659,18 +716,12 @@
     <t>04/01/2026 6:31:15 PM</t>
   </si>
   <si>
-    <t>Inattentive Driving</t>
-  </si>
-  <si>
     <t>Highway 69 Frontage Road, Loeb, TX, 77567</t>
   </si>
   <si>
     <t>52</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454b63-0bf8-539f-a255-8c9b76b7b752</t>
   </si>
   <si>
@@ -731,9 +782,6 @@
     <t>US 96, Zion Hill, TX</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454587-d024-5358-89a5-f14a9b756111</t>
   </si>
   <si>
@@ -1073,9 +1121,6 @@
     <t>5343 Fannett Road, Beaumont, TX, 77705</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e71e-bb7e-5153-af24-78b0ff3c67c3</t>
   </si>
   <si>
@@ -1331,9 +1376,6 @@
     <t>02/27/2026 5:00:26 PM</t>
   </si>
   <si>
-    <t>673 - Heavy</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a154-f86c-5a77-bfd0-38b1ffa99ee1</t>
   </si>
   <si>
@@ -1445,9 +1487,6 @@
     <t>02/25/2026 12:35:25 PM</t>
   </si>
   <si>
-    <t>Very Drowsy, Light Traffic</t>
-  </si>
-  <si>
     <t>2630 South Major Drive, Beaumont, TX, 77707</t>
   </si>
   <si>
@@ -1683,78 +1722,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453f60-1815-52c5-9ba5-709af6712cc5</t>
-  </si>
-  <si>
-    <t>02/07/2026 12:07:29 PM</t>
-  </si>
-  <si>
-    <t>5101 Walden Road, Beaumont, TX, 77707</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453949-9472-5875-8dd7-7620f2caacdf</t>
-  </si>
-  <si>
-    <t>02/07/2026 11:24:39 AM</t>
-  </si>
-  <si>
-    <t>Eastex Freeway Frontage Road, Beaumont, TX, 77708</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453922-5f06-592c-937b-73c8034648ee</t>
-  </si>
-  <si>
-    <t>02/06/2026 7:35:07 PM</t>
-  </si>
-  <si>
-    <t>Moderate Traffic, Night</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544535bd-0cbc-5bb0-aaca-092bfae4060f</t>
-  </si>
-  <si>
-    <t>02/06/2026 6:55:33 PM</t>
-  </si>
-  <si>
-    <t>Construction, Light Traffic, Night</t>
-  </si>
-  <si>
-    <t>1150 South I-10 Frontage Road, Beaumont, TX, 77707</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453598-d335-51f3-8722-6bec0547209c</t>
-  </si>
-  <si>
-    <t>02/06/2026 10:15:04 AM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544533bc-4ce7-5452-ace0-d23b84c600bc</t>
-  </si>
-  <si>
-    <t>02/05/2026 11:21:47 PM</t>
-  </si>
-  <si>
-    <t>2285 10th Street, Port Arthur, TX, 77640</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453166-3266-558d-b5f1-c88dd47eea71</t>
-  </si>
-  <si>
-    <t>02/05/2026 10:14:41 PM</t>
-  </si>
-  <si>
-    <t>1790 East Cardinal Drive, Beaumont, TX, 77705</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453128-c721-5368-8463-df616ba2eaa3</t>
-  </si>
-  <si>
-    <t>02/03/2026 7:13:44 AM</t>
-  </si>
-  <si>
-    <t>Eastex Freeway, Beaumont, TX, 77708</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544523a3-36a7-52a7-8f6a-3fbacaa889ac</t>
   </si>
 </sst>
 </file>
@@ -2131,7 +2098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O146"/>
+  <dimension ref="A1:O143"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -2219,48 +2186,48 @@
         <v>26</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2" t="s">
         <v>26</v>
       </c>
       <c r="O2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -2272,30 +2239,30 @@
         <v>26</v>
       </c>
       <c r="O3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
         <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H4" t="s">
         <v>22</v>
@@ -2304,10 +2271,10 @@
         <v>23</v>
       </c>
       <c r="J4" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="K4" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -2319,42 +2286,42 @@
         <v>26</v>
       </c>
       <c r="O4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
         <v>44</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>45</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>36</v>
       </c>
-      <c r="G5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" t="s">
-        <v>22</v>
-      </c>
       <c r="I5" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="J5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -2366,42 +2333,42 @@
         <v>26</v>
       </c>
       <c r="O5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G6" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="H6" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J6" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K6" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -2413,31 +2380,31 @@
         <v>26</v>
       </c>
       <c r="O6" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
       </c>
       <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G7" t="s">
         <v>45</v>
       </c>
-      <c r="F7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" t="s">
-        <v>21</v>
-      </c>
       <c r="H7" t="s">
         <v>22</v>
       </c>
@@ -2445,10 +2412,10 @@
         <v>23</v>
       </c>
       <c r="J7" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="K7" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="L7" t="s">
         <v>26</v>
@@ -2460,18 +2427,18 @@
         <v>26</v>
       </c>
       <c r="O7" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
         <v>18</v>
@@ -2480,10 +2447,10 @@
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="G8" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="H8" t="s">
         <v>22</v>
@@ -2492,10 +2459,10 @@
         <v>23</v>
       </c>
       <c r="J8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K8" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="L8" t="s">
         <v>26</v>
@@ -2507,18 +2474,18 @@
         <v>26</v>
       </c>
       <c r="O8" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D9" t="s">
         <v>18</v>
@@ -2527,10 +2494,10 @@
         <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="H9" t="s">
         <v>22</v>
@@ -2539,10 +2506,10 @@
         <v>23</v>
       </c>
       <c r="J9" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K9" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="L9" t="s">
         <v>26</v>
@@ -2554,42 +2521,42 @@
         <v>26</v>
       </c>
       <c r="O9" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H10" t="s">
         <v>36</v>
       </c>
-      <c r="G10" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" t="s">
-        <v>22</v>
-      </c>
       <c r="I10" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J10" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K10" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="L10" t="s">
         <v>26</v>
@@ -2601,30 +2568,30 @@
         <v>26</v>
       </c>
       <c r="O10" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="H11" t="s">
         <v>22</v>
@@ -2633,10 +2600,10 @@
         <v>23</v>
       </c>
       <c r="J11" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="K11" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="L11" t="s">
         <v>26</v>
@@ -2648,42 +2615,42 @@
         <v>26</v>
       </c>
       <c r="O11" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" t="s">
         <v>45</v>
       </c>
-      <c r="F12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12" t="s">
-        <v>31</v>
-      </c>
       <c r="H12" t="s">
         <v>22</v>
       </c>
       <c r="I12" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="J12" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="K12" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="L12" t="s">
         <v>26</v>
@@ -2695,30 +2662,30 @@
         <v>26</v>
       </c>
       <c r="O12" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G13" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
@@ -2727,10 +2694,10 @@
         <v>23</v>
       </c>
       <c r="J13" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="K13" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="L13" t="s">
         <v>26</v>
@@ -2742,42 +2709,42 @@
         <v>26</v>
       </c>
       <c r="O13" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s">
         <v>44</v>
       </c>
-      <c r="E14" t="s">
+      <c r="G14" t="s">
         <v>45</v>
       </c>
-      <c r="F14" t="s">
-        <v>95</v>
-      </c>
-      <c r="G14" t="s">
-        <v>96</v>
-      </c>
       <c r="H14" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="I14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J14" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K14" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L14" t="s">
         <v>26</v>
@@ -2786,15 +2753,15 @@
         <v>26</v>
       </c>
       <c r="N14" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="O14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B15" t="s">
         <v>42</v>
@@ -2803,28 +2770,28 @@
         <v>43</v>
       </c>
       <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" t="s">
         <v>44</v>
       </c>
-      <c r="E15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" t="s">
-        <v>36</v>
-      </c>
       <c r="G15" t="s">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="H15" t="s">
         <v>22</v>
       </c>
       <c r="I15" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="J15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L15" t="s">
         <v>26</v>
@@ -2836,31 +2803,31 @@
         <v>26</v>
       </c>
       <c r="O15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
       </c>
       <c r="E16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" t="s">
         <v>45</v>
       </c>
-      <c r="F16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G16" t="s">
-        <v>37</v>
-      </c>
       <c r="H16" t="s">
         <v>22</v>
       </c>
@@ -2868,10 +2835,10 @@
         <v>23</v>
       </c>
       <c r="J16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L16" t="s">
         <v>26</v>
@@ -2883,42 +2850,42 @@
         <v>26</v>
       </c>
       <c r="O16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="G17" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H17" t="s">
         <v>22</v>
       </c>
       <c r="I17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="J17" t="s">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="K17" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="L17" t="s">
         <v>26</v>
@@ -2930,30 +2897,30 @@
         <v>26</v>
       </c>
       <c r="O17" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
       </c>
       <c r="E18" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="G18" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H18" t="s">
         <v>22</v>
@@ -2962,10 +2929,10 @@
         <v>23</v>
       </c>
       <c r="J18" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="K18" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="L18" t="s">
         <v>26</v>
@@ -2977,42 +2944,42 @@
         <v>26</v>
       </c>
       <c r="O18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>119</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="E19" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>121</v>
       </c>
       <c r="G19" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H19" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I19" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J19" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K19" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="L19" t="s">
         <v>26</v>
@@ -3021,45 +2988,45 @@
         <v>26</v>
       </c>
       <c r="N19" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="O19" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>127</v>
+      </c>
+      <c r="B20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" t="s">
         <v>122</v>
       </c>
-      <c r="B20" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" t="s">
-        <v>114</v>
-      </c>
-      <c r="G20" t="s">
-        <v>26</v>
-      </c>
       <c r="H20" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I20" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J20" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K20" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="L20" t="s">
         <v>26</v>
@@ -3071,30 +3038,30 @@
         <v>26</v>
       </c>
       <c r="O20" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="F21" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="G21" t="s">
-        <v>118</v>
+        <v>76</v>
       </c>
       <c r="H21" t="s">
         <v>22</v>
@@ -3103,10 +3070,10 @@
         <v>23</v>
       </c>
       <c r="J21" t="s">
-        <v>127</v>
+        <v>38</v>
       </c>
       <c r="K21" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="L21" t="s">
         <v>26</v>
@@ -3118,42 +3085,42 @@
         <v>26</v>
       </c>
       <c r="O21" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G22" t="s">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="H22" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I22" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J22" t="s">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="K22" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="L22" t="s">
         <v>26</v>
@@ -3165,42 +3132,42 @@
         <v>26</v>
       </c>
       <c r="O22" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B23" t="s">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="G23" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H23" t="s">
         <v>22</v>
       </c>
       <c r="I23" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J23" t="s">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L23" t="s">
         <v>26</v>
@@ -3209,45 +3176,45 @@
         <v>26</v>
       </c>
       <c r="N23" t="s">
-        <v>138</v>
+        <v>26</v>
       </c>
       <c r="O23" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B24" t="s">
-        <v>135</v>
+        <v>64</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E24" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="G24" t="s">
-        <v>21</v>
+        <v>142</v>
       </c>
       <c r="H24" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="I24" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J24" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="K24" t="s">
-        <v>55</v>
+        <v>144</v>
       </c>
       <c r="L24" t="s">
         <v>26</v>
@@ -3256,21 +3223,21 @@
         <v>26</v>
       </c>
       <c r="N24" t="s">
-        <v>142</v>
+        <v>26</v>
       </c>
       <c r="O24" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
@@ -3279,7 +3246,7 @@
         <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="G25" t="s">
         <v>26</v>
@@ -3291,10 +3258,10 @@
         <v>23</v>
       </c>
       <c r="J25" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K25" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="L25" t="s">
         <v>26</v>
@@ -3306,30 +3273,30 @@
         <v>26</v>
       </c>
       <c r="O25" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
       </c>
       <c r="E26" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="F26" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G26" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="H26" t="s">
         <v>22</v>
@@ -3338,10 +3305,10 @@
         <v>23</v>
       </c>
       <c r="J26" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K26" t="s">
-        <v>150</v>
+        <v>47</v>
       </c>
       <c r="L26" t="s">
         <v>26</v>
@@ -3353,33 +3320,33 @@
         <v>26</v>
       </c>
       <c r="O26" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B27" t="s">
-        <v>153</v>
+        <v>64</v>
       </c>
       <c r="C27" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" t="s">
+        <v>66</v>
+      </c>
+      <c r="G27" t="s">
         <v>154</v>
       </c>
-      <c r="D27" t="s">
-        <v>44</v>
-      </c>
-      <c r="E27" t="s">
-        <v>19</v>
-      </c>
-      <c r="F27" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" t="s">
-        <v>21</v>
-      </c>
       <c r="H27" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="I27" t="s">
         <v>23</v>
@@ -3388,336 +3355,336 @@
         <v>155</v>
       </c>
       <c r="K27" t="s">
+        <v>101</v>
+      </c>
+      <c r="L27" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" t="s">
+        <v>26</v>
+      </c>
+      <c r="N27" t="s">
+        <v>26</v>
+      </c>
+      <c r="O27" t="s">
         <v>156</v>
-      </c>
-      <c r="L27" t="s">
-        <v>26</v>
-      </c>
-      <c r="M27" t="s">
-        <v>26</v>
-      </c>
-      <c r="N27" t="s">
-        <v>26</v>
-      </c>
-      <c r="O27" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>157</v>
+      </c>
+      <c r="B28" t="s">
         <v>158</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
+        <v>120</v>
+      </c>
+      <c r="D28" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" t="s">
+        <v>121</v>
+      </c>
+      <c r="G28" t="s">
+        <v>45</v>
+      </c>
+      <c r="H28" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" t="s">
+        <v>26</v>
+      </c>
+      <c r="J28" t="s">
         <v>159</v>
       </c>
-      <c r="C28" t="s">
+      <c r="K28" t="s">
         <v>160</v>
       </c>
-      <c r="D28" t="s">
+      <c r="L28" t="s">
+        <v>26</v>
+      </c>
+      <c r="M28" t="s">
+        <v>26</v>
+      </c>
+      <c r="N28" t="s">
         <v>161</v>
       </c>
-      <c r="E28" t="s">
-        <v>19</v>
-      </c>
-      <c r="F28" t="s">
-        <v>20</v>
-      </c>
-      <c r="G28" t="s">
-        <v>21</v>
-      </c>
-      <c r="H28" t="s">
-        <v>97</v>
-      </c>
-      <c r="I28" t="s">
-        <v>26</v>
-      </c>
-      <c r="J28" t="s">
+      <c r="O28" t="s">
         <v>162</v>
-      </c>
-      <c r="K28" t="s">
-        <v>163</v>
-      </c>
-      <c r="L28" t="s">
-        <v>26</v>
-      </c>
-      <c r="M28" t="s">
-        <v>26</v>
-      </c>
-      <c r="N28" t="s">
-        <v>26</v>
-      </c>
-      <c r="O28" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>163</v>
+      </c>
+      <c r="B29" t="s">
+        <v>158</v>
+      </c>
+      <c r="C29" t="s">
+        <v>120</v>
+      </c>
+      <c r="D29" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" t="s">
+        <v>33</v>
+      </c>
+      <c r="F29" t="s">
+        <v>121</v>
+      </c>
+      <c r="G29" t="s">
+        <v>45</v>
+      </c>
+      <c r="H29" t="s">
+        <v>36</v>
+      </c>
+      <c r="I29" t="s">
+        <v>26</v>
+      </c>
+      <c r="J29" t="s">
+        <v>164</v>
+      </c>
+      <c r="K29" t="s">
+        <v>88</v>
+      </c>
+      <c r="L29" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" t="s">
+        <v>26</v>
+      </c>
+      <c r="N29" t="s">
         <v>165</v>
       </c>
-      <c r="B29" t="s">
+      <c r="O29" t="s">
         <v>166</v>
-      </c>
-      <c r="C29" t="s">
-        <v>167</v>
-      </c>
-      <c r="D29" t="s">
-        <v>45</v>
-      </c>
-      <c r="E29" t="s">
-        <v>45</v>
-      </c>
-      <c r="F29" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" t="s">
-        <v>21</v>
-      </c>
-      <c r="H29" t="s">
-        <v>97</v>
-      </c>
-      <c r="I29" t="s">
-        <v>26</v>
-      </c>
-      <c r="J29" t="s">
-        <v>168</v>
-      </c>
-      <c r="K29" t="s">
-        <v>49</v>
-      </c>
-      <c r="L29" t="s">
-        <v>26</v>
-      </c>
-      <c r="M29" t="s">
-        <v>26</v>
-      </c>
-      <c r="N29" t="s">
-        <v>26</v>
-      </c>
-      <c r="O29" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>167</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" t="s">
+        <v>138</v>
+      </c>
+      <c r="G30" t="s">
+        <v>26</v>
+      </c>
+      <c r="H30" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" t="s">
+        <v>168</v>
+      </c>
+      <c r="K30" t="s">
+        <v>169</v>
+      </c>
+      <c r="L30" t="s">
+        <v>26</v>
+      </c>
+      <c r="M30" t="s">
+        <v>26</v>
+      </c>
+      <c r="N30" t="s">
+        <v>26</v>
+      </c>
+      <c r="O30" t="s">
         <v>170</v>
-      </c>
-      <c r="B30" t="s">
-        <v>166</v>
-      </c>
-      <c r="C30" t="s">
-        <v>167</v>
-      </c>
-      <c r="D30" t="s">
-        <v>45</v>
-      </c>
-      <c r="E30" t="s">
-        <v>45</v>
-      </c>
-      <c r="F30" t="s">
-        <v>36</v>
-      </c>
-      <c r="G30" t="s">
-        <v>131</v>
-      </c>
-      <c r="H30" t="s">
-        <v>97</v>
-      </c>
-      <c r="I30" t="s">
-        <v>26</v>
-      </c>
-      <c r="J30" t="s">
-        <v>171</v>
-      </c>
-      <c r="K30" t="s">
-        <v>172</v>
-      </c>
-      <c r="L30" t="s">
-        <v>26</v>
-      </c>
-      <c r="M30" t="s">
-        <v>26</v>
-      </c>
-      <c r="N30" t="s">
-        <v>26</v>
-      </c>
-      <c r="O30" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>171</v>
+      </c>
+      <c r="B31" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" t="s">
+        <v>44</v>
+      </c>
+      <c r="G31" t="s">
+        <v>142</v>
+      </c>
+      <c r="H31" t="s">
+        <v>22</v>
+      </c>
+      <c r="I31" t="s">
+        <v>23</v>
+      </c>
+      <c r="J31" t="s">
+        <v>172</v>
+      </c>
+      <c r="K31" t="s">
+        <v>173</v>
+      </c>
+      <c r="L31" t="s">
+        <v>26</v>
+      </c>
+      <c r="M31" t="s">
+        <v>26</v>
+      </c>
+      <c r="N31" t="s">
+        <v>26</v>
+      </c>
+      <c r="O31" t="s">
         <v>174</v>
-      </c>
-      <c r="B31" t="s">
-        <v>175</v>
-      </c>
-      <c r="C31" t="s">
-        <v>176</v>
-      </c>
-      <c r="D31" t="s">
-        <v>44</v>
-      </c>
-      <c r="E31" t="s">
-        <v>45</v>
-      </c>
-      <c r="F31" t="s">
-        <v>114</v>
-      </c>
-      <c r="G31" t="s">
-        <v>26</v>
-      </c>
-      <c r="H31" t="s">
-        <v>97</v>
-      </c>
-      <c r="I31" t="s">
-        <v>23</v>
-      </c>
-      <c r="J31" t="s">
-        <v>177</v>
-      </c>
-      <c r="K31" t="s">
-        <v>178</v>
-      </c>
-      <c r="L31" t="s">
-        <v>26</v>
-      </c>
-      <c r="M31" t="s">
-        <v>26</v>
-      </c>
-      <c r="N31" t="s">
-        <v>26</v>
-      </c>
-      <c r="O31" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>175</v>
+      </c>
+      <c r="B32" t="s">
+        <v>176</v>
+      </c>
+      <c r="C32" t="s">
+        <v>177</v>
+      </c>
+      <c r="D32" t="s">
+        <v>52</v>
+      </c>
+      <c r="E32" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" t="s">
+        <v>66</v>
+      </c>
+      <c r="G32" t="s">
+        <v>45</v>
+      </c>
+      <c r="H32" t="s">
+        <v>36</v>
+      </c>
+      <c r="I32" t="s">
+        <v>23</v>
+      </c>
+      <c r="J32" t="s">
+        <v>178</v>
+      </c>
+      <c r="K32" t="s">
+        <v>179</v>
+      </c>
+      <c r="L32" t="s">
+        <v>26</v>
+      </c>
+      <c r="M32" t="s">
+        <v>26</v>
+      </c>
+      <c r="N32" t="s">
+        <v>26</v>
+      </c>
+      <c r="O32" t="s">
         <v>180</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" t="s">
-        <v>19</v>
-      </c>
-      <c r="F32" t="s">
-        <v>20</v>
-      </c>
-      <c r="G32" t="s">
-        <v>131</v>
-      </c>
-      <c r="H32" t="s">
-        <v>22</v>
-      </c>
-      <c r="I32" t="s">
-        <v>23</v>
-      </c>
-      <c r="J32" t="s">
-        <v>181</v>
-      </c>
-      <c r="K32" t="s">
-        <v>156</v>
-      </c>
-      <c r="L32" t="s">
-        <v>26</v>
-      </c>
-      <c r="M32" t="s">
-        <v>26</v>
-      </c>
-      <c r="N32" t="s">
-        <v>26</v>
-      </c>
-      <c r="O32" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>181</v>
+      </c>
+      <c r="B33" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" t="s">
+        <v>59</v>
+      </c>
+      <c r="E33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" t="s">
+        <v>66</v>
+      </c>
+      <c r="G33" t="s">
+        <v>45</v>
+      </c>
+      <c r="H33" t="s">
+        <v>36</v>
+      </c>
+      <c r="I33" t="s">
+        <v>26</v>
+      </c>
+      <c r="J33" t="s">
+        <v>182</v>
+      </c>
+      <c r="K33" t="s">
         <v>183</v>
       </c>
-      <c r="B33" t="s">
-        <v>74</v>
-      </c>
-      <c r="C33" t="s">
-        <v>75</v>
-      </c>
-      <c r="D33" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" t="s">
-        <v>45</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="L33" t="s">
+        <v>26</v>
+      </c>
+      <c r="M33" t="s">
+        <v>26</v>
+      </c>
+      <c r="N33" t="s">
+        <v>26</v>
+      </c>
+      <c r="O33" t="s">
         <v>184</v>
-      </c>
-      <c r="G33" t="s">
-        <v>21</v>
-      </c>
-      <c r="H33" t="s">
-        <v>22</v>
-      </c>
-      <c r="I33" t="s">
-        <v>23</v>
-      </c>
-      <c r="J33" t="s">
-        <v>185</v>
-      </c>
-      <c r="K33" t="s">
-        <v>186</v>
-      </c>
-      <c r="L33" t="s">
-        <v>26</v>
-      </c>
-      <c r="M33" t="s">
-        <v>26</v>
-      </c>
-      <c r="N33" t="s">
-        <v>26</v>
-      </c>
-      <c r="O33" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>185</v>
+      </c>
+      <c r="B34" t="s">
+        <v>186</v>
+      </c>
+      <c r="C34" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" t="s">
+        <v>33</v>
+      </c>
+      <c r="E34" t="s">
+        <v>33</v>
+      </c>
+      <c r="F34" t="s">
+        <v>66</v>
+      </c>
+      <c r="G34" t="s">
+        <v>45</v>
+      </c>
+      <c r="H34" t="s">
+        <v>36</v>
+      </c>
+      <c r="I34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J34" t="s">
         <v>188</v>
       </c>
-      <c r="B34" t="s">
-        <v>153</v>
-      </c>
-      <c r="C34" t="s">
-        <v>26</v>
-      </c>
-      <c r="D34" t="s">
-        <v>26</v>
-      </c>
-      <c r="E34" t="s">
-        <v>19</v>
-      </c>
-      <c r="F34" t="s">
-        <v>20</v>
-      </c>
-      <c r="G34" t="s">
-        <v>21</v>
-      </c>
-      <c r="H34" t="s">
-        <v>22</v>
-      </c>
-      <c r="I34" t="s">
-        <v>26</v>
-      </c>
-      <c r="J34" t="s">
-        <v>48</v>
-      </c>
       <c r="K34" t="s">
-        <v>150</v>
+        <v>83</v>
       </c>
       <c r="L34" t="s">
         <v>26</v>
@@ -3737,31 +3704,31 @@
         <v>190</v>
       </c>
       <c r="B35" t="s">
-        <v>16</v>
+        <v>186</v>
       </c>
       <c r="C35" t="s">
-        <v>17</v>
+        <v>187</v>
       </c>
       <c r="D35" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E35" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F35" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G35" t="s">
+        <v>154</v>
+      </c>
+      <c r="H35" t="s">
+        <v>36</v>
+      </c>
+      <c r="I35" t="s">
+        <v>26</v>
+      </c>
+      <c r="J35" t="s">
         <v>191</v>
-      </c>
-      <c r="H35" t="s">
-        <v>22</v>
-      </c>
-      <c r="I35" t="s">
-        <v>23</v>
-      </c>
-      <c r="J35" t="s">
-        <v>145</v>
       </c>
       <c r="K35" t="s">
         <v>192</v>
@@ -3784,34 +3751,34 @@
         <v>194</v>
       </c>
       <c r="B36" t="s">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="C36" t="s">
-        <v>94</v>
+        <v>196</v>
       </c>
       <c r="D36" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E36" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="F36" t="s">
-        <v>184</v>
+        <v>138</v>
       </c>
       <c r="G36" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="H36" t="s">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="I36" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J36" t="s">
-        <v>107</v>
+        <v>197</v>
       </c>
       <c r="K36" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="L36" t="s">
         <v>26</v>
@@ -3823,18 +3790,18 @@
         <v>26</v>
       </c>
       <c r="O36" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B37" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C37" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
@@ -3843,10 +3810,10 @@
         <v>19</v>
       </c>
       <c r="F37" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="G37" t="s">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="H37" t="s">
         <v>22</v>
@@ -3855,10 +3822,10 @@
         <v>23</v>
       </c>
       <c r="J37" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="K37" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="L37" t="s">
         <v>26</v>
@@ -3870,30 +3837,30 @@
         <v>26</v>
       </c>
       <c r="O37" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
       </c>
       <c r="E38" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F38" t="s">
-        <v>36</v>
+        <v>204</v>
       </c>
       <c r="G38" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="H38" t="s">
         <v>22</v>
@@ -3902,10 +3869,10 @@
         <v>23</v>
       </c>
       <c r="J38" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="K38" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="L38" t="s">
         <v>26</v>
@@ -3917,15 +3884,15 @@
         <v>26</v>
       </c>
       <c r="O38" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B39" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="C39" t="s">
         <v>26</v>
@@ -3934,14 +3901,14 @@
         <v>26</v>
       </c>
       <c r="E39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" t="s">
+        <v>66</v>
+      </c>
+      <c r="G39" t="s">
         <v>45</v>
       </c>
-      <c r="F39" t="s">
-        <v>20</v>
-      </c>
-      <c r="G39" t="s">
-        <v>21</v>
-      </c>
       <c r="H39" t="s">
         <v>22</v>
       </c>
@@ -3949,10 +3916,10 @@
         <v>26</v>
       </c>
       <c r="J39" t="s">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="L39" t="s">
         <v>26</v>
@@ -3964,18 +3931,18 @@
         <v>26</v>
       </c>
       <c r="O39" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B40" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C40" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
@@ -3984,10 +3951,10 @@
         <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="G40" t="s">
-        <v>21</v>
+        <v>211</v>
       </c>
       <c r="H40" t="s">
         <v>22</v>
@@ -3996,10 +3963,10 @@
         <v>23</v>
       </c>
       <c r="J40" t="s">
-        <v>210</v>
+        <v>168</v>
       </c>
       <c r="K40" t="s">
-        <v>211</v>
+        <v>61</v>
       </c>
       <c r="L40" t="s">
         <v>26</v>
@@ -4019,78 +3986,78 @@
         <v>213</v>
       </c>
       <c r="B41" t="s">
-        <v>29</v>
+        <v>158</v>
       </c>
       <c r="C41" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="D41" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="E41" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F41" t="s">
+        <v>204</v>
+      </c>
+      <c r="G41" t="s">
+        <v>122</v>
+      </c>
+      <c r="H41" t="s">
+        <v>36</v>
+      </c>
+      <c r="I41" t="s">
+        <v>26</v>
+      </c>
+      <c r="J41" t="s">
+        <v>38</v>
+      </c>
+      <c r="K41" t="s">
         <v>214</v>
       </c>
-      <c r="G41" t="s">
-        <v>21</v>
-      </c>
-      <c r="H41" t="s">
-        <v>97</v>
-      </c>
-      <c r="I41" t="s">
-        <v>23</v>
-      </c>
-      <c r="J41" t="s">
+      <c r="L41" t="s">
+        <v>26</v>
+      </c>
+      <c r="M41" t="s">
+        <v>26</v>
+      </c>
+      <c r="N41" t="s">
+        <v>26</v>
+      </c>
+      <c r="O41" t="s">
         <v>215</v>
-      </c>
-      <c r="K41" t="s">
-        <v>216</v>
-      </c>
-      <c r="L41" t="s">
-        <v>26</v>
-      </c>
-      <c r="M41" t="s">
-        <v>217</v>
-      </c>
-      <c r="N41" t="s">
-        <v>26</v>
-      </c>
-      <c r="O41" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B42" t="s">
-        <v>159</v>
+        <v>64</v>
       </c>
       <c r="C42" t="s">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="D42" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="E42" t="s">
         <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="G42" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H42" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="I42" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J42" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="K42" t="s">
         <v>217</v>
@@ -4102,45 +4069,45 @@
         <v>26</v>
       </c>
       <c r="N42" t="s">
-        <v>221</v>
+        <v>26</v>
       </c>
       <c r="O42" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="C43" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="D43" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43" t="s">
         <v>44</v>
-      </c>
-      <c r="E43" t="s">
-        <v>45</v>
-      </c>
-      <c r="F43" t="s">
-        <v>36</v>
       </c>
       <c r="G43" t="s">
         <v>21</v>
       </c>
       <c r="H43" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="I43" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="J43" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="K43" t="s">
-        <v>77</v>
+        <v>221</v>
       </c>
       <c r="L43" t="s">
         <v>26</v>
@@ -4152,65 +4119,65 @@
         <v>26</v>
       </c>
       <c r="O43" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>223</v>
+      </c>
+      <c r="B44" t="s">
+        <v>224</v>
+      </c>
+      <c r="C44" t="s">
+        <v>26</v>
+      </c>
+      <c r="D44" t="s">
+        <v>26</v>
+      </c>
+      <c r="E44" t="s">
+        <v>33</v>
+      </c>
+      <c r="F44" t="s">
+        <v>66</v>
+      </c>
+      <c r="G44" t="s">
+        <v>45</v>
+      </c>
+      <c r="H44" t="s">
+        <v>22</v>
+      </c>
+      <c r="I44" t="s">
+        <v>26</v>
+      </c>
+      <c r="J44" t="s">
+        <v>225</v>
+      </c>
+      <c r="K44" t="s">
         <v>226</v>
       </c>
-      <c r="B44" t="s">
-        <v>74</v>
-      </c>
-      <c r="C44" t="s">
-        <v>75</v>
-      </c>
-      <c r="D44" t="s">
-        <v>18</v>
-      </c>
-      <c r="E44" t="s">
-        <v>45</v>
-      </c>
-      <c r="F44" t="s">
-        <v>36</v>
-      </c>
-      <c r="G44" t="s">
-        <v>21</v>
-      </c>
-      <c r="H44" t="s">
-        <v>22</v>
-      </c>
-      <c r="I44" t="s">
-        <v>23</v>
-      </c>
-      <c r="J44" t="s">
+      <c r="L44" t="s">
+        <v>26</v>
+      </c>
+      <c r="M44" t="s">
+        <v>26</v>
+      </c>
+      <c r="N44" t="s">
+        <v>26</v>
+      </c>
+      <c r="O44" t="s">
         <v>227</v>
-      </c>
-      <c r="K44" t="s">
-        <v>228</v>
-      </c>
-      <c r="L44" t="s">
-        <v>26</v>
-      </c>
-      <c r="M44" t="s">
-        <v>26</v>
-      </c>
-      <c r="N44" t="s">
-        <v>26</v>
-      </c>
-      <c r="O44" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B45" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C45" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
@@ -4219,10 +4186,10 @@
         <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G45" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="H45" t="s">
         <v>22</v>
@@ -4231,63 +4198,63 @@
         <v>23</v>
       </c>
       <c r="J45" t="s">
-        <v>127</v>
+        <v>229</v>
       </c>
       <c r="K45" t="s">
+        <v>230</v>
+      </c>
+      <c r="L45" t="s">
+        <v>26</v>
+      </c>
+      <c r="M45" t="s">
+        <v>26</v>
+      </c>
+      <c r="N45" t="s">
+        <v>26</v>
+      </c>
+      <c r="O45" t="s">
         <v>231</v>
-      </c>
-      <c r="L45" t="s">
-        <v>26</v>
-      </c>
-      <c r="M45" t="s">
-        <v>26</v>
-      </c>
-      <c r="N45" t="s">
-        <v>26</v>
-      </c>
-      <c r="O45" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>232</v>
+      </c>
+      <c r="B46" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" t="s">
+        <v>71</v>
+      </c>
+      <c r="D46" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" t="s">
+        <v>20</v>
+      </c>
+      <c r="G46" t="s">
+        <v>45</v>
+      </c>
+      <c r="H46" t="s">
+        <v>36</v>
+      </c>
+      <c r="I46" t="s">
+        <v>23</v>
+      </c>
+      <c r="J46" t="s">
         <v>233</v>
       </c>
-      <c r="B46" t="s">
-        <v>42</v>
-      </c>
-      <c r="C46" t="s">
-        <v>43</v>
-      </c>
-      <c r="D46" t="s">
-        <v>44</v>
-      </c>
-      <c r="E46" t="s">
-        <v>45</v>
-      </c>
-      <c r="F46" t="s">
-        <v>36</v>
-      </c>
-      <c r="G46" t="s">
-        <v>21</v>
-      </c>
-      <c r="H46" t="s">
-        <v>97</v>
-      </c>
-      <c r="I46" t="s">
-        <v>47</v>
-      </c>
-      <c r="J46" t="s">
+      <c r="K46" t="s">
         <v>234</v>
       </c>
-      <c r="K46" t="s">
-        <v>192</v>
-      </c>
       <c r="L46" t="s">
         <v>26</v>
       </c>
       <c r="M46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N46" t="s">
         <v>26</v>
@@ -4301,25 +4268,25 @@
         <v>236</v>
       </c>
       <c r="B47" t="s">
-        <v>135</v>
+        <v>57</v>
       </c>
       <c r="C47" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="D47" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="E47" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" t="s">
+        <v>121</v>
+      </c>
+      <c r="G47" t="s">
         <v>45</v>
       </c>
-      <c r="F47" t="s">
-        <v>20</v>
-      </c>
-      <c r="G47" t="s">
-        <v>21</v>
-      </c>
       <c r="H47" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I47" t="s">
         <v>26</v>
@@ -4328,16 +4295,16 @@
         <v>237</v>
       </c>
       <c r="K47" t="s">
+        <v>27</v>
+      </c>
+      <c r="L47" t="s">
+        <v>26</v>
+      </c>
+      <c r="M47" t="s">
+        <v>26</v>
+      </c>
+      <c r="N47" t="s">
         <v>238</v>
-      </c>
-      <c r="L47" t="s">
-        <v>26</v>
-      </c>
-      <c r="M47" t="s">
-        <v>26</v>
-      </c>
-      <c r="N47" t="s">
-        <v>26</v>
       </c>
       <c r="O47" t="s">
         <v>239</v>
@@ -4348,104 +4315,104 @@
         <v>240</v>
       </c>
       <c r="B48" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48" t="s">
+        <v>51</v>
+      </c>
+      <c r="D48" t="s">
+        <v>52</v>
+      </c>
+      <c r="E48" t="s">
+        <v>33</v>
+      </c>
+      <c r="F48" t="s">
+        <v>44</v>
+      </c>
+      <c r="G48" t="s">
+        <v>45</v>
+      </c>
+      <c r="H48" t="s">
+        <v>36</v>
+      </c>
+      <c r="I48" t="s">
+        <v>37</v>
+      </c>
+      <c r="J48" t="s">
         <v>241</v>
       </c>
-      <c r="C48" t="s">
+      <c r="K48" t="s">
+        <v>105</v>
+      </c>
+      <c r="L48" t="s">
+        <v>26</v>
+      </c>
+      <c r="M48" t="s">
+        <v>26</v>
+      </c>
+      <c r="N48" t="s">
+        <v>26</v>
+      </c>
+      <c r="O48" t="s">
         <v>242</v>
-      </c>
-      <c r="D48" t="s">
-        <v>18</v>
-      </c>
-      <c r="E48" t="s">
-        <v>45</v>
-      </c>
-      <c r="F48" t="s">
-        <v>214</v>
-      </c>
-      <c r="G48" t="s">
-        <v>65</v>
-      </c>
-      <c r="H48" t="s">
-        <v>97</v>
-      </c>
-      <c r="I48" t="s">
-        <v>26</v>
-      </c>
-      <c r="J48" t="s">
-        <v>24</v>
-      </c>
-      <c r="K48" t="s">
-        <v>77</v>
-      </c>
-      <c r="L48" t="s">
-        <v>26</v>
-      </c>
-      <c r="M48" t="s">
-        <v>217</v>
-      </c>
-      <c r="N48" t="s">
-        <v>26</v>
-      </c>
-      <c r="O48" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B49" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C49" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="D49" t="s">
         <v>18</v>
       </c>
       <c r="E49" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F49" t="s">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="G49" t="s">
+        <v>45</v>
+      </c>
+      <c r="H49" t="s">
+        <v>22</v>
+      </c>
+      <c r="I49" t="s">
+        <v>23</v>
+      </c>
+      <c r="J49" t="s">
+        <v>244</v>
+      </c>
+      <c r="K49" t="s">
         <v>245</v>
       </c>
-      <c r="H49" t="s">
-        <v>97</v>
-      </c>
-      <c r="I49" t="s">
-        <v>23</v>
-      </c>
-      <c r="J49" t="s">
+      <c r="L49" t="s">
+        <v>26</v>
+      </c>
+      <c r="M49" t="s">
+        <v>26</v>
+      </c>
+      <c r="N49" t="s">
+        <v>26</v>
+      </c>
+      <c r="O49" t="s">
         <v>246</v>
-      </c>
-      <c r="K49" t="s">
-        <v>99</v>
-      </c>
-      <c r="L49" t="s">
-        <v>26</v>
-      </c>
-      <c r="M49" t="s">
-        <v>26</v>
-      </c>
-      <c r="N49" t="s">
-        <v>247</v>
-      </c>
-      <c r="O49" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B50" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D50" t="s">
         <v>18</v>
@@ -4454,10 +4421,10 @@
         <v>19</v>
       </c>
       <c r="F50" t="s">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="G50" t="s">
-        <v>26</v>
+        <v>142</v>
       </c>
       <c r="H50" t="s">
         <v>22</v>
@@ -4466,10 +4433,10 @@
         <v>23</v>
       </c>
       <c r="J50" t="s">
-        <v>250</v>
+        <v>151</v>
       </c>
       <c r="K50" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="L50" t="s">
         <v>26</v>
@@ -4481,89 +4448,89 @@
         <v>26</v>
       </c>
       <c r="O50" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>250</v>
+      </c>
+      <c r="B51" t="s">
+        <v>50</v>
+      </c>
+      <c r="C51" t="s">
+        <v>51</v>
+      </c>
+      <c r="D51" t="s">
+        <v>52</v>
+      </c>
+      <c r="E51" t="s">
+        <v>33</v>
+      </c>
+      <c r="F51" t="s">
+        <v>44</v>
+      </c>
+      <c r="G51" t="s">
+        <v>45</v>
+      </c>
+      <c r="H51" t="s">
+        <v>36</v>
+      </c>
+      <c r="I51" t="s">
+        <v>37</v>
+      </c>
+      <c r="J51" t="s">
+        <v>251</v>
+      </c>
+      <c r="K51" t="s">
+        <v>61</v>
+      </c>
+      <c r="L51" t="s">
+        <v>26</v>
+      </c>
+      <c r="M51" t="s">
+        <v>26</v>
+      </c>
+      <c r="N51" t="s">
+        <v>26</v>
+      </c>
+      <c r="O51" t="s">
         <v>252</v>
-      </c>
-      <c r="B51" t="s">
-        <v>29</v>
-      </c>
-      <c r="C51" t="s">
-        <v>253</v>
-      </c>
-      <c r="D51" t="s">
-        <v>161</v>
-      </c>
-      <c r="E51" t="s">
-        <v>19</v>
-      </c>
-      <c r="F51" t="s">
-        <v>20</v>
-      </c>
-      <c r="G51" t="s">
-        <v>21</v>
-      </c>
-      <c r="H51" t="s">
-        <v>22</v>
-      </c>
-      <c r="I51" t="s">
-        <v>26</v>
-      </c>
-      <c r="J51" t="s">
-        <v>254</v>
-      </c>
-      <c r="K51" t="s">
-        <v>255</v>
-      </c>
-      <c r="L51" t="s">
-        <v>26</v>
-      </c>
-      <c r="M51" t="s">
-        <v>26</v>
-      </c>
-      <c r="N51" t="s">
-        <v>26</v>
-      </c>
-      <c r="O51" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B52" t="s">
-        <v>258</v>
+        <v>158</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>26</v>
       </c>
       <c r="D52" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E52" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F52" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="G52" t="s">
-        <v>260</v>
+        <v>45</v>
       </c>
       <c r="H52" t="s">
         <v>22</v>
       </c>
       <c r="I52" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J52" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="K52" t="s">
-        <v>262</v>
+        <v>39</v>
       </c>
       <c r="L52" t="s">
         <v>26</v>
@@ -4575,65 +4542,65 @@
         <v>26</v>
       </c>
       <c r="O52" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="B53" t="s">
-        <v>74</v>
+        <v>257</v>
       </c>
       <c r="C53" t="s">
-        <v>75</v>
+        <v>258</v>
       </c>
       <c r="D53" t="s">
         <v>18</v>
       </c>
       <c r="E53" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="F53" t="s">
+        <v>20</v>
+      </c>
+      <c r="G53" t="s">
+        <v>96</v>
+      </c>
+      <c r="H53" t="s">
         <v>36</v>
       </c>
-      <c r="G53" t="s">
-        <v>65</v>
-      </c>
-      <c r="H53" t="s">
-        <v>22</v>
-      </c>
       <c r="I53" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J53" t="s">
-        <v>265</v>
+        <v>46</v>
       </c>
       <c r="K53" t="s">
-        <v>39</v>
+        <v>105</v>
       </c>
       <c r="L53" t="s">
         <v>26</v>
       </c>
       <c r="M53" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N53" t="s">
         <v>26</v>
       </c>
       <c r="O53" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="B54" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C54" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D54" t="s">
         <v>18</v>
@@ -4642,22 +4609,22 @@
         <v>19</v>
       </c>
       <c r="F54" t="s">
+        <v>121</v>
+      </c>
+      <c r="G54" t="s">
+        <v>261</v>
+      </c>
+      <c r="H54" t="s">
         <v>36</v>
       </c>
-      <c r="G54" t="s">
-        <v>268</v>
-      </c>
-      <c r="H54" t="s">
-        <v>22</v>
-      </c>
       <c r="I54" t="s">
         <v>23</v>
       </c>
       <c r="J54" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="K54" t="s">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="L54" t="s">
         <v>26</v>
@@ -4666,15 +4633,15 @@
         <v>26</v>
       </c>
       <c r="N54" t="s">
-        <v>26</v>
+        <v>263</v>
       </c>
       <c r="O54" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B55" t="s">
         <v>16</v>
@@ -4689,10 +4656,10 @@
         <v>19</v>
       </c>
       <c r="F55" t="s">
-        <v>36</v>
+        <v>138</v>
       </c>
       <c r="G55" t="s">
-        <v>131</v>
+        <v>26</v>
       </c>
       <c r="H55" t="s">
         <v>22</v>
@@ -4701,10 +4668,10 @@
         <v>23</v>
       </c>
       <c r="J55" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="K55" t="s">
-        <v>67</v>
+        <v>245</v>
       </c>
       <c r="L55" t="s">
         <v>26</v>
@@ -4716,42 +4683,42 @@
         <v>26</v>
       </c>
       <c r="O55" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B56" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C56" t="s">
-        <v>17</v>
+        <v>269</v>
       </c>
       <c r="D56" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="E56" t="s">
         <v>19</v>
       </c>
       <c r="F56" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="G56" t="s">
-        <v>275</v>
+        <v>45</v>
       </c>
       <c r="H56" t="s">
         <v>22</v>
       </c>
       <c r="I56" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J56" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="K56" t="s">
-        <v>124</v>
+        <v>271</v>
       </c>
       <c r="L56" t="s">
         <v>26</v>
@@ -4763,18 +4730,18 @@
         <v>26</v>
       </c>
       <c r="O56" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B57" t="s">
-        <v>63</v>
+        <v>274</v>
       </c>
       <c r="C57" t="s">
-        <v>64</v>
+        <v>275</v>
       </c>
       <c r="D57" t="s">
         <v>18</v>
@@ -4783,10 +4750,10 @@
         <v>19</v>
       </c>
       <c r="F57" t="s">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="G57" t="s">
-        <v>26</v>
+        <v>276</v>
       </c>
       <c r="H57" t="s">
         <v>22</v>
@@ -4795,45 +4762,45 @@
         <v>23</v>
       </c>
       <c r="J57" t="s">
+        <v>277</v>
+      </c>
+      <c r="K57" t="s">
+        <v>278</v>
+      </c>
+      <c r="L57" t="s">
+        <v>26</v>
+      </c>
+      <c r="M57" t="s">
+        <v>26</v>
+      </c>
+      <c r="N57" t="s">
+        <v>26</v>
+      </c>
+      <c r="O57" t="s">
         <v>279</v>
-      </c>
-      <c r="K57" t="s">
-        <v>280</v>
-      </c>
-      <c r="L57" t="s">
-        <v>26</v>
-      </c>
-      <c r="M57" t="s">
-        <v>26</v>
-      </c>
-      <c r="N57" t="s">
-        <v>26</v>
-      </c>
-      <c r="O57" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B58" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C58" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
       </c>
       <c r="E58" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F58" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G58" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="H58" t="s">
         <v>22</v>
@@ -4842,10 +4809,10 @@
         <v>23</v>
       </c>
       <c r="J58" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="K58" t="s">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="L58" t="s">
         <v>26</v>
@@ -4857,12 +4824,12 @@
         <v>26</v>
       </c>
       <c r="O58" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B59" t="s">
         <v>16</v>
@@ -4877,10 +4844,10 @@
         <v>19</v>
       </c>
       <c r="F59" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G59" t="s">
-        <v>118</v>
+        <v>284</v>
       </c>
       <c r="H59" t="s">
         <v>22</v>
@@ -4889,33 +4856,33 @@
         <v>23</v>
       </c>
       <c r="J59" t="s">
+        <v>285</v>
+      </c>
+      <c r="K59" t="s">
+        <v>93</v>
+      </c>
+      <c r="L59" t="s">
+        <v>26</v>
+      </c>
+      <c r="M59" t="s">
+        <v>26</v>
+      </c>
+      <c r="N59" t="s">
+        <v>26</v>
+      </c>
+      <c r="O59" t="s">
         <v>286</v>
-      </c>
-      <c r="K59" t="s">
-        <v>124</v>
-      </c>
-      <c r="L59" t="s">
-        <v>26</v>
-      </c>
-      <c r="M59" t="s">
-        <v>26</v>
-      </c>
-      <c r="N59" t="s">
-        <v>26</v>
-      </c>
-      <c r="O59" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B60" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C60" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D60" t="s">
         <v>18</v>
@@ -4924,10 +4891,10 @@
         <v>19</v>
       </c>
       <c r="F60" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G60" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="H60" t="s">
         <v>22</v>
@@ -4936,45 +4903,45 @@
         <v>23</v>
       </c>
       <c r="J60" t="s">
+        <v>288</v>
+      </c>
+      <c r="K60" t="s">
+        <v>54</v>
+      </c>
+      <c r="L60" t="s">
+        <v>26</v>
+      </c>
+      <c r="M60" t="s">
+        <v>26</v>
+      </c>
+      <c r="N60" t="s">
+        <v>26</v>
+      </c>
+      <c r="O60" t="s">
         <v>289</v>
-      </c>
-      <c r="K60" t="s">
-        <v>198</v>
-      </c>
-      <c r="L60" t="s">
-        <v>26</v>
-      </c>
-      <c r="M60" t="s">
-        <v>26</v>
-      </c>
-      <c r="N60" t="s">
-        <v>26</v>
-      </c>
-      <c r="O60" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B61" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C61" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D61" t="s">
         <v>18</v>
       </c>
       <c r="E61" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F61" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="G61" t="s">
-        <v>31</v>
+        <v>291</v>
       </c>
       <c r="H61" t="s">
         <v>22</v>
@@ -4986,7 +4953,7 @@
         <v>292</v>
       </c>
       <c r="K61" t="s">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="L61" t="s">
         <v>26</v>
@@ -5006,34 +4973,34 @@
         <v>294</v>
       </c>
       <c r="B62" t="s">
-        <v>153</v>
+        <v>16</v>
       </c>
       <c r="C62" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E62" t="s">
         <v>19</v>
       </c>
       <c r="F62" t="s">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="G62" t="s">
-        <v>118</v>
+        <v>26</v>
       </c>
       <c r="H62" t="s">
         <v>22</v>
       </c>
       <c r="I62" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J62" t="s">
-        <v>127</v>
+        <v>295</v>
       </c>
       <c r="K62" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L62" t="s">
         <v>26</v>
@@ -5045,42 +5012,42 @@
         <v>26</v>
       </c>
       <c r="O62" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B63" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="C63" t="s">
-        <v>253</v>
+        <v>65</v>
       </c>
       <c r="D63" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="E63" t="s">
         <v>19</v>
       </c>
       <c r="F63" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G63" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="H63" t="s">
         <v>22</v>
       </c>
       <c r="I63" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J63" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K63" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="L63" t="s">
         <v>26</v>
@@ -5092,124 +5059,124 @@
         <v>26</v>
       </c>
       <c r="O63" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B64" t="s">
-        <v>135</v>
+        <v>64</v>
       </c>
       <c r="C64" t="s">
-        <v>301</v>
+        <v>65</v>
       </c>
       <c r="D64" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="E64" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F64" t="s">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="G64" t="s">
-        <v>26</v>
+        <v>142</v>
       </c>
       <c r="H64" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="I64" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J64" t="s">
         <v>302</v>
       </c>
       <c r="K64" t="s">
+        <v>148</v>
+      </c>
+      <c r="L64" t="s">
+        <v>26</v>
+      </c>
+      <c r="M64" t="s">
+        <v>26</v>
+      </c>
+      <c r="N64" t="s">
+        <v>26</v>
+      </c>
+      <c r="O64" t="s">
         <v>303</v>
-      </c>
-      <c r="L64" t="s">
-        <v>26</v>
-      </c>
-      <c r="M64" t="s">
-        <v>26</v>
-      </c>
-      <c r="N64" t="s">
-        <v>26</v>
-      </c>
-      <c r="O64" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>304</v>
+      </c>
+      <c r="B65" t="s">
+        <v>64</v>
+      </c>
+      <c r="C65" t="s">
+        <v>65</v>
+      </c>
+      <c r="D65" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65" t="s">
+        <v>19</v>
+      </c>
+      <c r="F65" t="s">
+        <v>66</v>
+      </c>
+      <c r="G65" t="s">
+        <v>154</v>
+      </c>
+      <c r="H65" t="s">
+        <v>22</v>
+      </c>
+      <c r="I65" t="s">
+        <v>23</v>
+      </c>
+      <c r="J65" t="s">
         <v>305</v>
       </c>
-      <c r="B65" t="s">
-        <v>29</v>
-      </c>
-      <c r="C65" t="s">
-        <v>253</v>
-      </c>
-      <c r="D65" t="s">
-        <v>161</v>
-      </c>
-      <c r="E65" t="s">
-        <v>19</v>
-      </c>
-      <c r="F65" t="s">
+      <c r="K65" t="s">
+        <v>217</v>
+      </c>
+      <c r="L65" t="s">
+        <v>26</v>
+      </c>
+      <c r="M65" t="s">
+        <v>26</v>
+      </c>
+      <c r="N65" t="s">
+        <v>26</v>
+      </c>
+      <c r="O65" t="s">
         <v>306</v>
-      </c>
-      <c r="G65" t="s">
-        <v>307</v>
-      </c>
-      <c r="H65" t="s">
-        <v>22</v>
-      </c>
-      <c r="I65" t="s">
-        <v>26</v>
-      </c>
-      <c r="J65" t="s">
-        <v>308</v>
-      </c>
-      <c r="K65" t="s">
-        <v>71</v>
-      </c>
-      <c r="L65" t="s">
-        <v>26</v>
-      </c>
-      <c r="M65" t="s">
-        <v>26</v>
-      </c>
-      <c r="N65" t="s">
-        <v>309</v>
-      </c>
-      <c r="O65" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B66" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C66" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D66" t="s">
         <v>18</v>
       </c>
       <c r="E66" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F66" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G66" t="s">
-        <v>312</v>
+        <v>21</v>
       </c>
       <c r="H66" t="s">
         <v>22</v>
@@ -5218,10 +5185,10 @@
         <v>23</v>
       </c>
       <c r="J66" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="K66" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="L66" t="s">
         <v>26</v>
@@ -5233,42 +5200,42 @@
         <v>26</v>
       </c>
       <c r="O66" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B67" t="s">
-        <v>16</v>
+        <v>176</v>
       </c>
       <c r="C67" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D67" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E67" t="s">
         <v>19</v>
       </c>
       <c r="F67" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="G67" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H67" t="s">
         <v>22</v>
       </c>
       <c r="I67" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J67" t="s">
-        <v>316</v>
+        <v>151</v>
       </c>
       <c r="K67" t="s">
-        <v>198</v>
+        <v>311</v>
       </c>
       <c r="L67" t="s">
         <v>26</v>
@@ -5280,42 +5247,42 @@
         <v>26</v>
       </c>
       <c r="O67" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B68" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C68" t="s">
-        <v>64</v>
+        <v>269</v>
       </c>
       <c r="D68" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="E68" t="s">
         <v>19</v>
       </c>
       <c r="F68" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G68" t="s">
-        <v>319</v>
+        <v>45</v>
       </c>
       <c r="H68" t="s">
         <v>22</v>
       </c>
       <c r="I68" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J68" t="s">
-        <v>181</v>
+        <v>314</v>
       </c>
       <c r="K68" t="s">
-        <v>320</v>
+        <v>47</v>
       </c>
       <c r="L68" t="s">
         <v>26</v>
@@ -5327,42 +5294,42 @@
         <v>26</v>
       </c>
       <c r="O68" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B69" t="s">
-        <v>29</v>
+        <v>158</v>
       </c>
       <c r="C69" t="s">
-        <v>253</v>
+        <v>317</v>
       </c>
       <c r="D69" t="s">
-        <v>161</v>
+        <v>33</v>
       </c>
       <c r="E69" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F69" t="s">
+        <v>138</v>
+      </c>
+      <c r="G69" t="s">
+        <v>26</v>
+      </c>
+      <c r="H69" t="s">
         <v>36</v>
       </c>
-      <c r="G69" t="s">
-        <v>131</v>
-      </c>
-      <c r="H69" t="s">
-        <v>22</v>
-      </c>
       <c r="I69" t="s">
         <v>26</v>
       </c>
       <c r="J69" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="K69" t="s">
-        <v>108</v>
+        <v>319</v>
       </c>
       <c r="L69" t="s">
         <v>26</v>
@@ -5374,77 +5341,77 @@
         <v>26</v>
       </c>
       <c r="O69" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>321</v>
+      </c>
+      <c r="B70" t="s">
+        <v>70</v>
+      </c>
+      <c r="C70" t="s">
+        <v>269</v>
+      </c>
+      <c r="D70" t="s">
+        <v>59</v>
+      </c>
+      <c r="E70" t="s">
+        <v>19</v>
+      </c>
+      <c r="F70" t="s">
+        <v>322</v>
+      </c>
+      <c r="G70" t="s">
+        <v>323</v>
+      </c>
+      <c r="H70" t="s">
+        <v>22</v>
+      </c>
+      <c r="I70" t="s">
+        <v>26</v>
+      </c>
+      <c r="J70" t="s">
+        <v>324</v>
+      </c>
+      <c r="K70" t="s">
+        <v>101</v>
+      </c>
+      <c r="L70" t="s">
+        <v>26</v>
+      </c>
+      <c r="M70" t="s">
+        <v>26</v>
+      </c>
+      <c r="N70" t="s">
         <v>325</v>
       </c>
-      <c r="B70" t="s">
-        <v>93</v>
-      </c>
-      <c r="C70" t="s">
-        <v>176</v>
-      </c>
-      <c r="D70" t="s">
-        <v>44</v>
-      </c>
-      <c r="E70" t="s">
-        <v>45</v>
-      </c>
-      <c r="F70" t="s">
-        <v>184</v>
-      </c>
-      <c r="G70" t="s">
-        <v>21</v>
-      </c>
-      <c r="H70" t="s">
-        <v>97</v>
-      </c>
-      <c r="I70" t="s">
-        <v>23</v>
-      </c>
-      <c r="J70" t="s">
-        <v>265</v>
-      </c>
-      <c r="K70" t="s">
+      <c r="O70" t="s">
         <v>326</v>
-      </c>
-      <c r="L70" t="s">
-        <v>26</v>
-      </c>
-      <c r="M70" t="s">
-        <v>26</v>
-      </c>
-      <c r="N70" t="s">
-        <v>26</v>
-      </c>
-      <c r="O70" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B71" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C71" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D71" t="s">
         <v>18</v>
       </c>
       <c r="E71" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F71" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G71" t="s">
-        <v>31</v>
+        <v>328</v>
       </c>
       <c r="H71" t="s">
         <v>22</v>
@@ -5456,7 +5423,7 @@
         <v>329</v>
       </c>
       <c r="K71" t="s">
-        <v>228</v>
+        <v>67</v>
       </c>
       <c r="L71" t="s">
         <v>26</v>
@@ -5476,22 +5443,22 @@
         <v>331</v>
       </c>
       <c r="B72" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C72" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
       </c>
       <c r="E72" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F72" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="G72" t="s">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="H72" t="s">
         <v>22</v>
@@ -5503,30 +5470,30 @@
         <v>332</v>
       </c>
       <c r="K72" t="s">
+        <v>217</v>
+      </c>
+      <c r="L72" t="s">
+        <v>26</v>
+      </c>
+      <c r="M72" t="s">
+        <v>26</v>
+      </c>
+      <c r="N72" t="s">
+        <v>26</v>
+      </c>
+      <c r="O72" t="s">
         <v>333</v>
-      </c>
-      <c r="L72" t="s">
-        <v>26</v>
-      </c>
-      <c r="M72" t="s">
-        <v>26</v>
-      </c>
-      <c r="N72" t="s">
-        <v>26</v>
-      </c>
-      <c r="O72" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B73" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="C73" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="D73" t="s">
         <v>18</v>
@@ -5535,10 +5502,10 @@
         <v>19</v>
       </c>
       <c r="F73" t="s">
-        <v>114</v>
+        <v>34</v>
       </c>
       <c r="G73" t="s">
-        <v>26</v>
+        <v>335</v>
       </c>
       <c r="H73" t="s">
         <v>22</v>
@@ -5547,10 +5514,10 @@
         <v>23</v>
       </c>
       <c r="J73" t="s">
+        <v>201</v>
+      </c>
+      <c r="K73" t="s">
         <v>336</v>
-      </c>
-      <c r="K73" t="s">
-        <v>60</v>
       </c>
       <c r="L73" t="s">
         <v>26</v>
@@ -5570,22 +5537,22 @@
         <v>338</v>
       </c>
       <c r="B74" t="s">
-        <v>159</v>
+        <v>70</v>
       </c>
       <c r="C74" t="s">
-        <v>26</v>
+        <v>269</v>
       </c>
       <c r="D74" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="E74" t="s">
         <v>19</v>
       </c>
       <c r="F74" t="s">
-        <v>184</v>
+        <v>44</v>
       </c>
       <c r="G74" t="s">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="H74" t="s">
         <v>22</v>
@@ -5597,136 +5564,136 @@
         <v>339</v>
       </c>
       <c r="K74" t="s">
+        <v>132</v>
+      </c>
+      <c r="L74" t="s">
+        <v>26</v>
+      </c>
+      <c r="M74" t="s">
+        <v>26</v>
+      </c>
+      <c r="N74" t="s">
+        <v>26</v>
+      </c>
+      <c r="O74" t="s">
         <v>340</v>
-      </c>
-      <c r="L74" t="s">
-        <v>26</v>
-      </c>
-      <c r="M74" t="s">
-        <v>26</v>
-      </c>
-      <c r="N74" t="s">
-        <v>26</v>
-      </c>
-      <c r="O74" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>341</v>
+      </c>
+      <c r="B75" t="s">
+        <v>119</v>
+      </c>
+      <c r="C75" t="s">
+        <v>196</v>
+      </c>
+      <c r="D75" t="s">
+        <v>52</v>
+      </c>
+      <c r="E75" t="s">
+        <v>33</v>
+      </c>
+      <c r="F75" t="s">
+        <v>204</v>
+      </c>
+      <c r="G75" t="s">
+        <v>45</v>
+      </c>
+      <c r="H75" t="s">
+        <v>36</v>
+      </c>
+      <c r="I75" t="s">
+        <v>23</v>
+      </c>
+      <c r="J75" t="s">
+        <v>281</v>
+      </c>
+      <c r="K75" t="s">
         <v>342</v>
       </c>
-      <c r="B75" t="s">
-        <v>63</v>
-      </c>
-      <c r="C75" t="s">
-        <v>64</v>
-      </c>
-      <c r="D75" t="s">
-        <v>18</v>
-      </c>
-      <c r="E75" t="s">
-        <v>19</v>
-      </c>
-      <c r="F75" t="s">
-        <v>20</v>
-      </c>
-      <c r="G75" t="s">
-        <v>21</v>
-      </c>
-      <c r="H75" t="s">
-        <v>22</v>
-      </c>
-      <c r="I75" t="s">
-        <v>23</v>
-      </c>
-      <c r="J75" t="s">
-        <v>70</v>
-      </c>
-      <c r="K75" t="s">
+      <c r="L75" t="s">
+        <v>26</v>
+      </c>
+      <c r="M75" t="s">
+        <v>26</v>
+      </c>
+      <c r="N75" t="s">
+        <v>26</v>
+      </c>
+      <c r="O75" t="s">
         <v>343</v>
-      </c>
-      <c r="L75" t="s">
-        <v>26</v>
-      </c>
-      <c r="M75" t="s">
-        <v>26</v>
-      </c>
-      <c r="N75" t="s">
-        <v>26</v>
-      </c>
-      <c r="O75" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>344</v>
+      </c>
+      <c r="B76" t="s">
+        <v>42</v>
+      </c>
+      <c r="C76" t="s">
+        <v>43</v>
+      </c>
+      <c r="D76" t="s">
+        <v>18</v>
+      </c>
+      <c r="E76" t="s">
+        <v>33</v>
+      </c>
+      <c r="F76" t="s">
+        <v>44</v>
+      </c>
+      <c r="G76" t="s">
+        <v>21</v>
+      </c>
+      <c r="H76" t="s">
+        <v>22</v>
+      </c>
+      <c r="I76" t="s">
+        <v>23</v>
+      </c>
+      <c r="J76" t="s">
         <v>345</v>
       </c>
-      <c r="B76" t="s">
-        <v>29</v>
-      </c>
-      <c r="C76" t="s">
-        <v>253</v>
-      </c>
-      <c r="D76" t="s">
-        <v>161</v>
-      </c>
-      <c r="E76" t="s">
-        <v>19</v>
-      </c>
-      <c r="F76" t="s">
-        <v>306</v>
-      </c>
-      <c r="G76" t="s">
-        <v>118</v>
-      </c>
-      <c r="H76" t="s">
-        <v>97</v>
-      </c>
-      <c r="I76" t="s">
-        <v>26</v>
-      </c>
-      <c r="J76" t="s">
+      <c r="K76" t="s">
+        <v>245</v>
+      </c>
+      <c r="L76" t="s">
+        <v>26</v>
+      </c>
+      <c r="M76" t="s">
+        <v>26</v>
+      </c>
+      <c r="N76" t="s">
+        <v>26</v>
+      </c>
+      <c r="O76" t="s">
         <v>346</v>
-      </c>
-      <c r="K76" t="s">
-        <v>347</v>
-      </c>
-      <c r="L76" t="s">
-        <v>26</v>
-      </c>
-      <c r="M76" t="s">
-        <v>26</v>
-      </c>
-      <c r="N76" t="s">
-        <v>348</v>
-      </c>
-      <c r="O76" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B77" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C77" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D77" t="s">
         <v>18</v>
       </c>
       <c r="E77" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F77" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G77" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H77" t="s">
         <v>22</v>
@@ -5735,10 +5702,10 @@
         <v>23</v>
       </c>
       <c r="J77" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="K77" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="L77" t="s">
         <v>26</v>
@@ -5750,12 +5717,12 @@
         <v>26</v>
       </c>
       <c r="O77" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B78" t="s">
         <v>16</v>
@@ -5770,10 +5737,10 @@
         <v>19</v>
       </c>
       <c r="F78" t="s">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="G78" t="s">
-        <v>131</v>
+        <v>26</v>
       </c>
       <c r="H78" t="s">
         <v>22</v>
@@ -5782,10 +5749,10 @@
         <v>23</v>
       </c>
       <c r="J78" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="K78" t="s">
-        <v>186</v>
+        <v>93</v>
       </c>
       <c r="L78" t="s">
         <v>26</v>
@@ -5797,59 +5764,59 @@
         <v>26</v>
       </c>
       <c r="O78" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>354</v>
+      </c>
+      <c r="B79" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" t="s">
+        <v>26</v>
+      </c>
+      <c r="D79" t="s">
+        <v>26</v>
+      </c>
+      <c r="E79" t="s">
+        <v>19</v>
+      </c>
+      <c r="F79" t="s">
+        <v>204</v>
+      </c>
+      <c r="G79" t="s">
+        <v>122</v>
+      </c>
+      <c r="H79" t="s">
+        <v>22</v>
+      </c>
+      <c r="I79" t="s">
+        <v>26</v>
+      </c>
+      <c r="J79" t="s">
+        <v>355</v>
+      </c>
+      <c r="K79" t="s">
+        <v>356</v>
+      </c>
+      <c r="L79" t="s">
+        <v>26</v>
+      </c>
+      <c r="M79" t="s">
+        <v>26</v>
+      </c>
+      <c r="N79" t="s">
+        <v>26</v>
+      </c>
+      <c r="O79" t="s">
         <v>357</v>
-      </c>
-      <c r="B79" t="s">
-        <v>358</v>
-      </c>
-      <c r="C79" t="s">
-        <v>359</v>
-      </c>
-      <c r="D79" t="s">
-        <v>360</v>
-      </c>
-      <c r="E79" t="s">
-        <v>19</v>
-      </c>
-      <c r="F79" t="s">
-        <v>36</v>
-      </c>
-      <c r="G79" t="s">
-        <v>361</v>
-      </c>
-      <c r="H79" t="s">
-        <v>22</v>
-      </c>
-      <c r="I79" t="s">
-        <v>47</v>
-      </c>
-      <c r="J79" t="s">
-        <v>119</v>
-      </c>
-      <c r="K79" t="s">
-        <v>362</v>
-      </c>
-      <c r="L79" t="s">
-        <v>26</v>
-      </c>
-      <c r="M79" t="s">
-        <v>26</v>
-      </c>
-      <c r="N79" t="s">
-        <v>26</v>
-      </c>
-      <c r="O79" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B80" t="s">
         <v>16</v>
@@ -5864,10 +5831,10 @@
         <v>19</v>
       </c>
       <c r="F80" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="G80" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="H80" t="s">
         <v>22</v>
@@ -5876,10 +5843,10 @@
         <v>23</v>
       </c>
       <c r="J80" t="s">
-        <v>365</v>
+        <v>100</v>
       </c>
       <c r="K80" t="s">
-        <v>49</v>
+        <v>359</v>
       </c>
       <c r="L80" t="s">
         <v>26</v>
@@ -5891,42 +5858,42 @@
         <v>26</v>
       </c>
       <c r="O80" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="B81" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C81" t="s">
-        <v>64</v>
+        <v>269</v>
       </c>
       <c r="D81" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="E81" t="s">
         <v>19</v>
       </c>
       <c r="F81" t="s">
-        <v>114</v>
+        <v>322</v>
       </c>
       <c r="G81" t="s">
-        <v>26</v>
+        <v>142</v>
       </c>
       <c r="H81" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I81" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J81" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="K81" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="L81" t="s">
         <v>26</v>
@@ -5935,45 +5902,45 @@
         <v>26</v>
       </c>
       <c r="N81" t="s">
-        <v>26</v>
+        <v>364</v>
       </c>
       <c r="O81" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B82" t="s">
-        <v>159</v>
+        <v>64</v>
       </c>
       <c r="C82" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="D82" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E82" t="s">
         <v>19</v>
       </c>
       <c r="F82" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G82" t="s">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="H82" t="s">
         <v>22</v>
       </c>
       <c r="I82" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J82" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="K82" t="s">
-        <v>326</v>
+        <v>25</v>
       </c>
       <c r="L82" t="s">
         <v>26</v>
@@ -5985,42 +5952,42 @@
         <v>26</v>
       </c>
       <c r="O82" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B83" t="s">
-        <v>159</v>
+        <v>64</v>
       </c>
       <c r="C83" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="D83" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E83" t="s">
         <v>19</v>
       </c>
       <c r="F83" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="G83" t="s">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="H83" t="s">
         <v>22</v>
       </c>
       <c r="I83" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J83" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="K83" t="s">
-        <v>376</v>
+        <v>206</v>
       </c>
       <c r="L83" t="s">
         <v>26</v>
@@ -6032,65 +5999,65 @@
         <v>26</v>
       </c>
       <c r="O83" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>372</v>
+      </c>
+      <c r="B84" t="s">
+        <v>373</v>
+      </c>
+      <c r="C84" t="s">
+        <v>374</v>
+      </c>
+      <c r="D84" t="s">
+        <v>375</v>
+      </c>
+      <c r="E84" t="s">
+        <v>19</v>
+      </c>
+      <c r="F84" t="s">
+        <v>44</v>
+      </c>
+      <c r="G84" t="s">
+        <v>376</v>
+      </c>
+      <c r="H84" t="s">
+        <v>22</v>
+      </c>
+      <c r="I84" t="s">
+        <v>37</v>
+      </c>
+      <c r="J84" t="s">
+        <v>143</v>
+      </c>
+      <c r="K84" t="s">
+        <v>377</v>
+      </c>
+      <c r="L84" t="s">
+        <v>26</v>
+      </c>
+      <c r="M84" t="s">
+        <v>26</v>
+      </c>
+      <c r="N84" t="s">
+        <v>26</v>
+      </c>
+      <c r="O84" t="s">
         <v>378</v>
-      </c>
-      <c r="B84" t="s">
-        <v>379</v>
-      </c>
-      <c r="C84" t="s">
-        <v>176</v>
-      </c>
-      <c r="D84" t="s">
-        <v>44</v>
-      </c>
-      <c r="E84" t="s">
-        <v>45</v>
-      </c>
-      <c r="F84" t="s">
-        <v>184</v>
-      </c>
-      <c r="G84" t="s">
-        <v>96</v>
-      </c>
-      <c r="H84" t="s">
-        <v>97</v>
-      </c>
-      <c r="I84" t="s">
-        <v>23</v>
-      </c>
-      <c r="J84" t="s">
-        <v>380</v>
-      </c>
-      <c r="K84" t="s">
-        <v>172</v>
-      </c>
-      <c r="L84" t="s">
-        <v>26</v>
-      </c>
-      <c r="M84" t="s">
-        <v>26</v>
-      </c>
-      <c r="N84" t="s">
-        <v>26</v>
-      </c>
-      <c r="O84" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B85" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C85" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D85" t="s">
         <v>18</v>
@@ -6099,10 +6066,10 @@
         <v>19</v>
       </c>
       <c r="F85" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G85" t="s">
-        <v>46</v>
+        <v>142</v>
       </c>
       <c r="H85" t="s">
         <v>22</v>
@@ -6111,10 +6078,10 @@
         <v>23</v>
       </c>
       <c r="J85" t="s">
-        <v>286</v>
+        <v>380</v>
       </c>
       <c r="K85" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="L85" t="s">
         <v>26</v>
@@ -6126,12 +6093,12 @@
         <v>26</v>
       </c>
       <c r="O85" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B86" t="s">
         <v>16</v>
@@ -6146,10 +6113,10 @@
         <v>19</v>
       </c>
       <c r="F86" t="s">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="G86" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H86" t="s">
         <v>22</v>
@@ -6158,104 +6125,104 @@
         <v>23</v>
       </c>
       <c r="J86" t="s">
+        <v>383</v>
+      </c>
+      <c r="K86" t="s">
+        <v>384</v>
+      </c>
+      <c r="L86" t="s">
+        <v>26</v>
+      </c>
+      <c r="M86" t="s">
+        <v>26</v>
+      </c>
+      <c r="N86" t="s">
+        <v>26</v>
+      </c>
+      <c r="O86" t="s">
         <v>385</v>
-      </c>
-      <c r="K86" t="s">
-        <v>303</v>
-      </c>
-      <c r="L86" t="s">
-        <v>26</v>
-      </c>
-      <c r="M86" t="s">
-        <v>26</v>
-      </c>
-      <c r="N86" t="s">
-        <v>26</v>
-      </c>
-      <c r="O86" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>386</v>
+      </c>
+      <c r="B87" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" t="s">
+        <v>26</v>
+      </c>
+      <c r="D87" t="s">
+        <v>26</v>
+      </c>
+      <c r="E87" t="s">
+        <v>19</v>
+      </c>
+      <c r="F87" t="s">
+        <v>66</v>
+      </c>
+      <c r="G87" t="s">
+        <v>122</v>
+      </c>
+      <c r="H87" t="s">
+        <v>22</v>
+      </c>
+      <c r="I87" t="s">
+        <v>26</v>
+      </c>
+      <c r="J87" t="s">
         <v>387</v>
       </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="s">
-        <v>17</v>
-      </c>
-      <c r="D87" t="s">
-        <v>18</v>
-      </c>
-      <c r="E87" t="s">
-        <v>19</v>
-      </c>
-      <c r="F87" t="s">
-        <v>36</v>
-      </c>
-      <c r="G87" t="s">
-        <v>31</v>
-      </c>
-      <c r="H87" t="s">
-        <v>22</v>
-      </c>
-      <c r="I87" t="s">
-        <v>23</v>
-      </c>
-      <c r="J87" t="s">
+      <c r="K87" t="s">
+        <v>342</v>
+      </c>
+      <c r="L87" t="s">
+        <v>26</v>
+      </c>
+      <c r="M87" t="s">
+        <v>26</v>
+      </c>
+      <c r="N87" t="s">
+        <v>26</v>
+      </c>
+      <c r="O87" t="s">
         <v>388</v>
-      </c>
-      <c r="K87" t="s">
-        <v>231</v>
-      </c>
-      <c r="L87" t="s">
-        <v>26</v>
-      </c>
-      <c r="M87" t="s">
-        <v>26</v>
-      </c>
-      <c r="N87" t="s">
-        <v>26</v>
-      </c>
-      <c r="O87" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>389</v>
+      </c>
+      <c r="B88" t="s">
+        <v>57</v>
+      </c>
+      <c r="C88" t="s">
+        <v>26</v>
+      </c>
+      <c r="D88" t="s">
+        <v>26</v>
+      </c>
+      <c r="E88" t="s">
+        <v>19</v>
+      </c>
+      <c r="F88" t="s">
+        <v>44</v>
+      </c>
+      <c r="G88" t="s">
+        <v>45</v>
+      </c>
+      <c r="H88" t="s">
+        <v>22</v>
+      </c>
+      <c r="I88" t="s">
+        <v>26</v>
+      </c>
+      <c r="J88" t="s">
         <v>390</v>
       </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="s">
-        <v>17</v>
-      </c>
-      <c r="D88" t="s">
-        <v>18</v>
-      </c>
-      <c r="E88" t="s">
-        <v>19</v>
-      </c>
-      <c r="F88" t="s">
-        <v>20</v>
-      </c>
-      <c r="G88" t="s">
-        <v>118</v>
-      </c>
-      <c r="H88" t="s">
-        <v>22</v>
-      </c>
-      <c r="I88" t="s">
-        <v>23</v>
-      </c>
-      <c r="J88" t="s">
+      <c r="K88" t="s">
         <v>391</v>
-      </c>
-      <c r="K88" t="s">
-        <v>216</v>
       </c>
       <c r="L88" t="s">
         <v>26</v>
@@ -6275,57 +6242,57 @@
         <v>393</v>
       </c>
       <c r="B89" t="s">
-        <v>135</v>
+        <v>394</v>
       </c>
       <c r="C89" t="s">
-        <v>167</v>
+        <v>196</v>
       </c>
       <c r="D89" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E89" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="F89" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="G89" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="H89" t="s">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="I89" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J89" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K89" t="s">
-        <v>146</v>
+        <v>192</v>
       </c>
       <c r="L89" t="s">
         <v>26</v>
       </c>
       <c r="M89" t="s">
-        <v>217</v>
+        <v>26</v>
       </c>
       <c r="N89" t="s">
         <v>26</v>
       </c>
       <c r="O89" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B90" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C90" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D90" t="s">
         <v>18</v>
@@ -6334,10 +6301,10 @@
         <v>19</v>
       </c>
       <c r="F90" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="G90" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="H90" t="s">
         <v>22</v>
@@ -6346,10 +6313,10 @@
         <v>23</v>
       </c>
       <c r="J90" t="s">
-        <v>397</v>
+        <v>302</v>
       </c>
       <c r="K90" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="L90" t="s">
         <v>26</v>
@@ -6369,19 +6336,19 @@
         <v>399</v>
       </c>
       <c r="B91" t="s">
-        <v>205</v>
+        <v>64</v>
       </c>
       <c r="C91" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="D91" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E91" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F91" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="G91" t="s">
         <v>21</v>
@@ -6390,13 +6357,13 @@
         <v>22</v>
       </c>
       <c r="I91" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J91" t="s">
         <v>400</v>
       </c>
       <c r="K91" t="s">
-        <v>150</v>
+        <v>319</v>
       </c>
       <c r="L91" t="s">
         <v>26</v>
@@ -6416,10 +6383,10 @@
         <v>402</v>
       </c>
       <c r="B92" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C92" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D92" t="s">
         <v>18</v>
@@ -6428,10 +6395,10 @@
         <v>19</v>
       </c>
       <c r="F92" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G92" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="H92" t="s">
         <v>22</v>
@@ -6443,7 +6410,7 @@
         <v>403</v>
       </c>
       <c r="K92" t="s">
-        <v>124</v>
+        <v>248</v>
       </c>
       <c r="L92" t="s">
         <v>26</v>
@@ -6463,10 +6430,10 @@
         <v>405</v>
       </c>
       <c r="B93" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C93" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D93" t="s">
         <v>18</v>
@@ -6475,10 +6442,10 @@
         <v>19</v>
       </c>
       <c r="F93" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="G93" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H93" t="s">
         <v>22</v>
@@ -6490,7 +6457,7 @@
         <v>406</v>
       </c>
       <c r="K93" t="s">
-        <v>111</v>
+        <v>234</v>
       </c>
       <c r="L93" t="s">
         <v>26</v>
@@ -6510,25 +6477,25 @@
         <v>408</v>
       </c>
       <c r="B94" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C94" t="s">
-        <v>94</v>
+        <v>187</v>
       </c>
       <c r="D94" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E94" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F94" t="s">
         <v>20</v>
       </c>
       <c r="G94" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H94" t="s">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="I94" t="s">
         <v>26</v>
@@ -6537,13 +6504,13 @@
         <v>409</v>
       </c>
       <c r="K94" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L94" t="s">
         <v>26</v>
       </c>
       <c r="M94" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N94" t="s">
         <v>26</v>
@@ -6557,19 +6524,19 @@
         <v>411</v>
       </c>
       <c r="B95" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C95" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D95" t="s">
         <v>18</v>
       </c>
       <c r="E95" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F95" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="G95" t="s">
         <v>21</v>
@@ -6584,7 +6551,7 @@
         <v>412</v>
       </c>
       <c r="K95" t="s">
-        <v>39</v>
+        <v>144</v>
       </c>
       <c r="L95" t="s">
         <v>26</v>
@@ -6604,104 +6571,104 @@
         <v>414</v>
       </c>
       <c r="B96" t="s">
+        <v>224</v>
+      </c>
+      <c r="C96" t="s">
+        <v>26</v>
+      </c>
+      <c r="D96" t="s">
+        <v>26</v>
+      </c>
+      <c r="E96" t="s">
+        <v>33</v>
+      </c>
+      <c r="F96" t="s">
+        <v>44</v>
+      </c>
+      <c r="G96" t="s">
+        <v>45</v>
+      </c>
+      <c r="H96" t="s">
+        <v>22</v>
+      </c>
+      <c r="I96" t="s">
+        <v>26</v>
+      </c>
+      <c r="J96" t="s">
         <v>415</v>
       </c>
-      <c r="C96" t="s">
-        <v>259</v>
-      </c>
-      <c r="D96" t="s">
-        <v>18</v>
-      </c>
-      <c r="E96" t="s">
-        <v>19</v>
-      </c>
-      <c r="F96" t="s">
-        <v>20</v>
-      </c>
-      <c r="G96" t="s">
-        <v>118</v>
-      </c>
-      <c r="H96" t="s">
-        <v>22</v>
-      </c>
-      <c r="I96" t="s">
-        <v>23</v>
-      </c>
-      <c r="J96" t="s">
-        <v>127</v>
-      </c>
       <c r="K96" t="s">
+        <v>173</v>
+      </c>
+      <c r="L96" t="s">
+        <v>26</v>
+      </c>
+      <c r="M96" t="s">
+        <v>26</v>
+      </c>
+      <c r="N96" t="s">
+        <v>26</v>
+      </c>
+      <c r="O96" t="s">
         <v>416</v>
-      </c>
-      <c r="L96" t="s">
-        <v>26</v>
-      </c>
-      <c r="M96" t="s">
-        <v>26</v>
-      </c>
-      <c r="N96" t="s">
-        <v>26</v>
-      </c>
-      <c r="O96" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>417</v>
+      </c>
+      <c r="B97" t="s">
+        <v>64</v>
+      </c>
+      <c r="C97" t="s">
+        <v>65</v>
+      </c>
+      <c r="D97" t="s">
+        <v>18</v>
+      </c>
+      <c r="E97" t="s">
+        <v>19</v>
+      </c>
+      <c r="F97" t="s">
+        <v>44</v>
+      </c>
+      <c r="G97" t="s">
+        <v>96</v>
+      </c>
+      <c r="H97" t="s">
+        <v>22</v>
+      </c>
+      <c r="I97" t="s">
+        <v>23</v>
+      </c>
+      <c r="J97" t="s">
         <v>418</v>
       </c>
-      <c r="B97" t="s">
-        <v>29</v>
-      </c>
-      <c r="C97" t="s">
-        <v>253</v>
-      </c>
-      <c r="D97" t="s">
-        <v>161</v>
-      </c>
-      <c r="E97" t="s">
-        <v>19</v>
-      </c>
-      <c r="F97" t="s">
+      <c r="K97" t="s">
+        <v>148</v>
+      </c>
+      <c r="L97" t="s">
+        <v>26</v>
+      </c>
+      <c r="M97" t="s">
+        <v>26</v>
+      </c>
+      <c r="N97" t="s">
+        <v>26</v>
+      </c>
+      <c r="O97" t="s">
         <v>419</v>
-      </c>
-      <c r="G97" t="s">
-        <v>21</v>
-      </c>
-      <c r="H97" t="s">
-        <v>97</v>
-      </c>
-      <c r="I97" t="s">
-        <v>26</v>
-      </c>
-      <c r="J97" t="s">
-        <v>420</v>
-      </c>
-      <c r="K97" t="s">
-        <v>421</v>
-      </c>
-      <c r="L97" t="s">
-        <v>26</v>
-      </c>
-      <c r="M97" t="s">
-        <v>26</v>
-      </c>
-      <c r="N97" t="s">
-        <v>26</v>
-      </c>
-      <c r="O97" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B98" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C98" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D98" t="s">
         <v>18</v>
@@ -6710,10 +6677,10 @@
         <v>19</v>
       </c>
       <c r="F98" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="G98" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
       <c r="H98" t="s">
         <v>22</v>
@@ -6722,10 +6689,10 @@
         <v>23</v>
       </c>
       <c r="J98" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="K98" t="s">
-        <v>231</v>
+        <v>135</v>
       </c>
       <c r="L98" t="s">
         <v>26</v>
@@ -6737,42 +6704,42 @@
         <v>26</v>
       </c>
       <c r="O98" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B99" t="s">
-        <v>16</v>
+        <v>176</v>
       </c>
       <c r="C99" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
       <c r="D99" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="E99" t="s">
         <v>19</v>
       </c>
       <c r="F99" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="G99" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H99" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I99" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J99" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="K99" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="L99" t="s">
         <v>26</v>
@@ -6784,30 +6751,30 @@
         <v>26</v>
       </c>
       <c r="O99" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B100" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C100" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D100" t="s">
         <v>18</v>
       </c>
       <c r="E100" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F100" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G100" t="s">
-        <v>430</v>
+        <v>45</v>
       </c>
       <c r="H100" t="s">
         <v>22</v>
@@ -6816,10 +6783,10 @@
         <v>23</v>
       </c>
       <c r="J100" t="s">
-        <v>48</v>
+        <v>427</v>
       </c>
       <c r="K100" t="s">
-        <v>303</v>
+        <v>78</v>
       </c>
       <c r="L100" t="s">
         <v>26</v>
@@ -6831,18 +6798,18 @@
         <v>26</v>
       </c>
       <c r="O100" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B101" t="s">
-        <v>16</v>
+        <v>430</v>
       </c>
       <c r="C101" t="s">
-        <v>17</v>
+        <v>275</v>
       </c>
       <c r="D101" t="s">
         <v>18</v>
@@ -6851,10 +6818,10 @@
         <v>19</v>
       </c>
       <c r="F101" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="G101" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H101" t="s">
         <v>22</v>
@@ -6863,10 +6830,10 @@
         <v>23</v>
       </c>
       <c r="J101" t="s">
-        <v>24</v>
+        <v>151</v>
       </c>
       <c r="K101" t="s">
-        <v>81</v>
+        <v>431</v>
       </c>
       <c r="L101" t="s">
         <v>26</v>
@@ -6878,42 +6845,42 @@
         <v>26</v>
       </c>
       <c r="O101" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>433</v>
+      </c>
+      <c r="B102" t="s">
+        <v>70</v>
+      </c>
+      <c r="C102" t="s">
+        <v>269</v>
+      </c>
+      <c r="D102" t="s">
+        <v>59</v>
+      </c>
+      <c r="E102" t="s">
+        <v>19</v>
+      </c>
+      <c r="F102" t="s">
         <v>434</v>
       </c>
-      <c r="B102" t="s">
-        <v>74</v>
-      </c>
-      <c r="C102" t="s">
-        <v>75</v>
-      </c>
-      <c r="D102" t="s">
-        <v>18</v>
-      </c>
-      <c r="E102" t="s">
+      <c r="G102" t="s">
         <v>45</v>
       </c>
-      <c r="F102" t="s">
+      <c r="H102" t="s">
         <v>36</v>
       </c>
-      <c r="G102" t="s">
-        <v>96</v>
-      </c>
-      <c r="H102" t="s">
-        <v>22</v>
-      </c>
       <c r="I102" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J102" t="s">
         <v>435</v>
       </c>
       <c r="K102" t="s">
-        <v>228</v>
+        <v>436</v>
       </c>
       <c r="L102" t="s">
         <v>26</v>
@@ -6925,42 +6892,42 @@
         <v>26</v>
       </c>
       <c r="O102" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B103" t="s">
-        <v>438</v>
+        <v>64</v>
       </c>
       <c r="C103" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="D103" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="E103" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F103" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="G103" t="s">
         <v>21</v>
       </c>
       <c r="H103" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="I103" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="J103" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="K103" t="s">
-        <v>60</v>
+        <v>248</v>
       </c>
       <c r="L103" t="s">
         <v>26</v>
@@ -6972,42 +6939,42 @@
         <v>26</v>
       </c>
       <c r="O103" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B104" t="s">
-        <v>159</v>
+        <v>64</v>
       </c>
       <c r="C104" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="D104" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E104" t="s">
         <v>19</v>
       </c>
       <c r="F104" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="G104" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="H104" t="s">
         <v>22</v>
       </c>
       <c r="I104" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J104" t="s">
-        <v>181</v>
+        <v>442</v>
       </c>
       <c r="K104" t="s">
-        <v>441</v>
+        <v>234</v>
       </c>
       <c r="L104" t="s">
         <v>26</v>
@@ -7019,42 +6986,42 @@
         <v>26</v>
       </c>
       <c r="O104" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B105" t="s">
-        <v>444</v>
+        <v>64</v>
       </c>
       <c r="C105" t="s">
-        <v>167</v>
+        <v>65</v>
       </c>
       <c r="D105" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="E105" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F105" t="s">
-        <v>114</v>
+        <v>34</v>
       </c>
       <c r="G105" t="s">
-        <v>26</v>
+        <v>445</v>
       </c>
       <c r="H105" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="I105" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J105" t="s">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="K105" t="s">
-        <v>120</v>
+        <v>319</v>
       </c>
       <c r="L105" t="s">
         <v>26</v>
@@ -7074,69 +7041,69 @@
         <v>447</v>
       </c>
       <c r="B106" t="s">
+        <v>64</v>
+      </c>
+      <c r="C106" t="s">
+        <v>65</v>
+      </c>
+      <c r="D106" t="s">
+        <v>18</v>
+      </c>
+      <c r="E106" t="s">
+        <v>19</v>
+      </c>
+      <c r="F106" t="s">
+        <v>66</v>
+      </c>
+      <c r="G106" t="s">
+        <v>154</v>
+      </c>
+      <c r="H106" t="s">
+        <v>22</v>
+      </c>
+      <c r="I106" t="s">
+        <v>23</v>
+      </c>
+      <c r="J106" t="s">
+        <v>46</v>
+      </c>
+      <c r="K106" t="s">
+        <v>109</v>
+      </c>
+      <c r="L106" t="s">
+        <v>26</v>
+      </c>
+      <c r="M106" t="s">
+        <v>26</v>
+      </c>
+      <c r="N106" t="s">
+        <v>26</v>
+      </c>
+      <c r="O106" t="s">
         <v>448</v>
-      </c>
-      <c r="C106" t="s">
-        <v>449</v>
-      </c>
-      <c r="D106" t="s">
-        <v>450</v>
-      </c>
-      <c r="E106" t="s">
-        <v>45</v>
-      </c>
-      <c r="F106" t="s">
-        <v>20</v>
-      </c>
-      <c r="G106" t="s">
-        <v>21</v>
-      </c>
-      <c r="H106" t="s">
-        <v>97</v>
-      </c>
-      <c r="I106" t="s">
-        <v>23</v>
-      </c>
-      <c r="J106" t="s">
-        <v>451</v>
-      </c>
-      <c r="K106" t="s">
-        <v>115</v>
-      </c>
-      <c r="L106" t="s">
-        <v>26</v>
-      </c>
-      <c r="M106" t="s">
-        <v>26</v>
-      </c>
-      <c r="N106" t="s">
-        <v>26</v>
-      </c>
-      <c r="O106" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B107" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C107" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D107" t="s">
         <v>18</v>
       </c>
       <c r="E107" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F107" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G107" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="H107" t="s">
         <v>22</v>
@@ -7145,10 +7112,10 @@
         <v>23</v>
       </c>
       <c r="J107" t="s">
-        <v>127</v>
+        <v>450</v>
       </c>
       <c r="K107" t="s">
-        <v>280</v>
+        <v>245</v>
       </c>
       <c r="L107" t="s">
         <v>26</v>
@@ -7160,42 +7127,42 @@
         <v>26</v>
       </c>
       <c r="O107" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B108" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="C108" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D108" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E108" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F108" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G108" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H108" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I108" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J108" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="K108" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="L108" t="s">
         <v>26</v>
@@ -7207,42 +7174,42 @@
         <v>26</v>
       </c>
       <c r="O108" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B109" t="s">
-        <v>459</v>
+        <v>57</v>
       </c>
       <c r="C109" t="s">
-        <v>167</v>
+        <v>26</v>
       </c>
       <c r="D109" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="E109" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F109" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="G109" t="s">
-        <v>46</v>
+        <v>142</v>
       </c>
       <c r="H109" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="I109" t="s">
         <v>26</v>
       </c>
       <c r="J109" t="s">
-        <v>460</v>
+        <v>201</v>
       </c>
       <c r="K109" t="s">
-        <v>81</v>
+        <v>455</v>
       </c>
       <c r="L109" t="s">
         <v>26</v>
@@ -7254,42 +7221,42 @@
         <v>26</v>
       </c>
       <c r="O109" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="B110" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="C110" t="s">
-        <v>463</v>
+        <v>187</v>
       </c>
       <c r="D110" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="E110" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="F110" t="s">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="G110" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H110" t="s">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="I110" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J110" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="K110" t="s">
-        <v>238</v>
+        <v>144</v>
       </c>
       <c r="L110" t="s">
         <v>26</v>
@@ -7301,78 +7268,78 @@
         <v>26</v>
       </c>
       <c r="O110" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>461</v>
+      </c>
+      <c r="B111" t="s">
+        <v>462</v>
+      </c>
+      <c r="C111" t="s">
+        <v>463</v>
+      </c>
+      <c r="D111" t="s">
+        <v>464</v>
+      </c>
+      <c r="E111" t="s">
+        <v>33</v>
+      </c>
+      <c r="F111" t="s">
+        <v>66</v>
+      </c>
+      <c r="G111" t="s">
+        <v>45</v>
+      </c>
+      <c r="H111" t="s">
+        <v>36</v>
+      </c>
+      <c r="I111" t="s">
+        <v>23</v>
+      </c>
+      <c r="J111" t="s">
+        <v>465</v>
+      </c>
+      <c r="K111" t="s">
+        <v>139</v>
+      </c>
+      <c r="L111" t="s">
+        <v>26</v>
+      </c>
+      <c r="M111" t="s">
+        <v>26</v>
+      </c>
+      <c r="N111" t="s">
+        <v>26</v>
+      </c>
+      <c r="O111" t="s">
         <v>466</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="s">
-        <v>17</v>
-      </c>
-      <c r="D111" t="s">
-        <v>18</v>
-      </c>
-      <c r="E111" t="s">
-        <v>19</v>
-      </c>
-      <c r="F111" t="s">
-        <v>20</v>
-      </c>
-      <c r="G111" t="s">
-        <v>31</v>
-      </c>
-      <c r="H111" t="s">
-        <v>22</v>
-      </c>
-      <c r="I111" t="s">
-        <v>23</v>
-      </c>
-      <c r="J111" t="s">
-        <v>467</v>
-      </c>
-      <c r="K111" t="s">
-        <v>231</v>
-      </c>
-      <c r="L111" t="s">
-        <v>26</v>
-      </c>
-      <c r="M111" t="s">
-        <v>26</v>
-      </c>
-      <c r="N111" t="s">
-        <v>26</v>
-      </c>
-      <c r="O111" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B112" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C112" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D112" t="s">
         <v>18</v>
       </c>
       <c r="E112" t="s">
+        <v>19</v>
+      </c>
+      <c r="F112" t="s">
+        <v>66</v>
+      </c>
+      <c r="G112" t="s">
         <v>45</v>
       </c>
-      <c r="F112" t="s">
-        <v>36</v>
-      </c>
-      <c r="G112" t="s">
-        <v>21</v>
-      </c>
       <c r="H112" t="s">
         <v>22</v>
       </c>
@@ -7380,10 +7347,10 @@
         <v>23</v>
       </c>
       <c r="J112" t="s">
-        <v>470</v>
+        <v>151</v>
       </c>
       <c r="K112" t="s">
-        <v>352</v>
+        <v>296</v>
       </c>
       <c r="L112" t="s">
         <v>26</v>
@@ -7395,42 +7362,42 @@
         <v>26</v>
       </c>
       <c r="O112" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B113" t="s">
-        <v>258</v>
+        <v>16</v>
       </c>
       <c r="C113" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D113" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E113" t="s">
         <v>19</v>
       </c>
       <c r="F113" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="G113" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H113" t="s">
         <v>22</v>
       </c>
       <c r="I113" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J113" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="K113" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="L113" t="s">
         <v>26</v>
@@ -7442,89 +7409,89 @@
         <v>26</v>
       </c>
       <c r="O113" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>472</v>
+      </c>
+      <c r="B114" t="s">
+        <v>473</v>
+      </c>
+      <c r="C114" t="s">
+        <v>187</v>
+      </c>
+      <c r="D114" t="s">
+        <v>33</v>
+      </c>
+      <c r="E114" t="s">
+        <v>33</v>
+      </c>
+      <c r="F114" t="s">
+        <v>44</v>
+      </c>
+      <c r="G114" t="s">
+        <v>81</v>
+      </c>
+      <c r="H114" t="s">
+        <v>36</v>
+      </c>
+      <c r="I114" t="s">
+        <v>26</v>
+      </c>
+      <c r="J114" t="s">
+        <v>474</v>
+      </c>
+      <c r="K114" t="s">
+        <v>109</v>
+      </c>
+      <c r="L114" t="s">
+        <v>26</v>
+      </c>
+      <c r="M114" t="s">
+        <v>26</v>
+      </c>
+      <c r="N114" t="s">
+        <v>26</v>
+      </c>
+      <c r="O114" t="s">
         <v>475</v>
-      </c>
-      <c r="B114" t="s">
-        <v>415</v>
-      </c>
-      <c r="C114" t="s">
-        <v>259</v>
-      </c>
-      <c r="D114" t="s">
-        <v>18</v>
-      </c>
-      <c r="E114" t="s">
-        <v>19</v>
-      </c>
-      <c r="F114" t="s">
-        <v>52</v>
-      </c>
-      <c r="G114" t="s">
-        <v>476</v>
-      </c>
-      <c r="H114" t="s">
-        <v>22</v>
-      </c>
-      <c r="I114" t="s">
-        <v>23</v>
-      </c>
-      <c r="J114" t="s">
-        <v>477</v>
-      </c>
-      <c r="K114" t="s">
-        <v>478</v>
-      </c>
-      <c r="L114" t="s">
-        <v>26</v>
-      </c>
-      <c r="M114" t="s">
-        <v>26</v>
-      </c>
-      <c r="N114" t="s">
-        <v>26</v>
-      </c>
-      <c r="O114" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B115" t="s">
-        <v>481</v>
+        <v>462</v>
       </c>
       <c r="C115" t="s">
-        <v>301</v>
+        <v>477</v>
       </c>
       <c r="D115" t="s">
+        <v>18</v>
+      </c>
+      <c r="E115" t="s">
+        <v>33</v>
+      </c>
+      <c r="F115" t="s">
+        <v>66</v>
+      </c>
+      <c r="G115" t="s">
         <v>45</v>
       </c>
-      <c r="E115" t="s">
-        <v>45</v>
-      </c>
-      <c r="F115" t="s">
-        <v>184</v>
-      </c>
-      <c r="G115" t="s">
-        <v>96</v>
-      </c>
       <c r="H115" t="s">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="I115" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J115" t="s">
-        <v>265</v>
+        <v>478</v>
       </c>
       <c r="K115" t="s">
-        <v>441</v>
+        <v>39</v>
       </c>
       <c r="L115" t="s">
         <v>26</v>
@@ -7536,42 +7503,42 @@
         <v>26</v>
       </c>
       <c r="O115" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B116" t="s">
-        <v>448</v>
+        <v>64</v>
       </c>
       <c r="C116" t="s">
-        <v>463</v>
+        <v>65</v>
       </c>
       <c r="D116" t="s">
         <v>18</v>
       </c>
       <c r="E116" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F116" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="G116" t="s">
-        <v>484</v>
+        <v>21</v>
       </c>
       <c r="H116" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="I116" t="s">
         <v>23</v>
       </c>
       <c r="J116" t="s">
-        <v>181</v>
+        <v>481</v>
       </c>
       <c r="K116" t="s">
-        <v>33</v>
+        <v>248</v>
       </c>
       <c r="L116" t="s">
         <v>26</v>
@@ -7583,42 +7550,42 @@
         <v>26</v>
       </c>
       <c r="O116" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B117" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C117" t="s">
-        <v>253</v>
+        <v>43</v>
       </c>
       <c r="D117" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="E117" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F117" t="s">
-        <v>419</v>
+        <v>44</v>
       </c>
       <c r="G117" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H117" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="I117" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J117" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="K117" t="s">
-        <v>128</v>
+        <v>25</v>
       </c>
       <c r="L117" t="s">
         <v>26</v>
@@ -7630,15 +7597,15 @@
         <v>26</v>
       </c>
       <c r="O117" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B118" t="s">
-        <v>490</v>
+        <v>274</v>
       </c>
       <c r="C118" t="s">
         <v>26</v>
@@ -7650,10 +7617,10 @@
         <v>19</v>
       </c>
       <c r="F118" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="G118" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="H118" t="s">
         <v>22</v>
@@ -7662,10 +7629,10 @@
         <v>26</v>
       </c>
       <c r="J118" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="K118" t="s">
-        <v>352</v>
+        <v>109</v>
       </c>
       <c r="L118" t="s">
         <v>26</v>
@@ -7677,18 +7644,18 @@
         <v>26</v>
       </c>
       <c r="O118" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B119" t="s">
-        <v>16</v>
+        <v>430</v>
       </c>
       <c r="C119" t="s">
-        <v>17</v>
+        <v>275</v>
       </c>
       <c r="D119" t="s">
         <v>18</v>
@@ -7697,10 +7664,10 @@
         <v>19</v>
       </c>
       <c r="F119" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="G119" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H119" t="s">
         <v>22</v>
@@ -7709,10 +7676,10 @@
         <v>23</v>
       </c>
       <c r="J119" t="s">
-        <v>48</v>
+        <v>490</v>
       </c>
       <c r="K119" t="s">
-        <v>172</v>
+        <v>491</v>
       </c>
       <c r="L119" t="s">
         <v>26</v>
@@ -7724,89 +7691,89 @@
         <v>26</v>
       </c>
       <c r="O119" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>493</v>
+      </c>
+      <c r="B120" t="s">
+        <v>494</v>
+      </c>
+      <c r="C120" t="s">
+        <v>317</v>
+      </c>
+      <c r="D120" t="s">
+        <v>33</v>
+      </c>
+      <c r="E120" t="s">
+        <v>33</v>
+      </c>
+      <c r="F120" t="s">
+        <v>204</v>
+      </c>
+      <c r="G120" t="s">
+        <v>122</v>
+      </c>
+      <c r="H120" t="s">
+        <v>36</v>
+      </c>
+      <c r="I120" t="s">
+        <v>26</v>
+      </c>
+      <c r="J120" t="s">
+        <v>281</v>
+      </c>
+      <c r="K120" t="s">
+        <v>455</v>
+      </c>
+      <c r="L120" t="s">
+        <v>26</v>
+      </c>
+      <c r="M120" t="s">
+        <v>26</v>
+      </c>
+      <c r="N120" t="s">
+        <v>26</v>
+      </c>
+      <c r="O120" t="s">
         <v>495</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="s">
-        <v>17</v>
-      </c>
-      <c r="D120" t="s">
-        <v>18</v>
-      </c>
-      <c r="E120" t="s">
-        <v>19</v>
-      </c>
-      <c r="F120" t="s">
-        <v>36</v>
-      </c>
-      <c r="G120" t="s">
-        <v>131</v>
-      </c>
-      <c r="H120" t="s">
-        <v>22</v>
-      </c>
-      <c r="I120" t="s">
-        <v>23</v>
-      </c>
-      <c r="J120" t="s">
-        <v>496</v>
-      </c>
-      <c r="K120" t="s">
-        <v>124</v>
-      </c>
-      <c r="L120" t="s">
-        <v>26</v>
-      </c>
-      <c r="M120" t="s">
-        <v>26</v>
-      </c>
-      <c r="N120" t="s">
-        <v>26</v>
-      </c>
-      <c r="O120" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B121" t="s">
-        <v>16</v>
+        <v>462</v>
       </c>
       <c r="C121" t="s">
-        <v>17</v>
+        <v>477</v>
       </c>
       <c r="D121" t="s">
         <v>18</v>
       </c>
       <c r="E121" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F121" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="G121" t="s">
-        <v>131</v>
+        <v>497</v>
       </c>
       <c r="H121" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I121" t="s">
         <v>23</v>
       </c>
       <c r="J121" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="K121" t="s">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="L121" t="s">
         <v>26</v>
@@ -7818,89 +7785,89 @@
         <v>26</v>
       </c>
       <c r="O121" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>499</v>
+      </c>
+      <c r="B122" t="s">
+        <v>70</v>
+      </c>
+      <c r="C122" t="s">
+        <v>269</v>
+      </c>
+      <c r="D122" t="s">
+        <v>59</v>
+      </c>
+      <c r="E122" t="s">
+        <v>19</v>
+      </c>
+      <c r="F122" t="s">
+        <v>434</v>
+      </c>
+      <c r="G122" t="s">
+        <v>45</v>
+      </c>
+      <c r="H122" t="s">
+        <v>36</v>
+      </c>
+      <c r="I122" t="s">
+        <v>26</v>
+      </c>
+      <c r="J122" t="s">
         <v>500</v>
       </c>
-      <c r="B122" t="s">
-        <v>159</v>
-      </c>
-      <c r="C122" t="s">
-        <v>154</v>
-      </c>
-      <c r="D122" t="s">
-        <v>44</v>
-      </c>
-      <c r="E122" t="s">
-        <v>19</v>
-      </c>
-      <c r="F122" t="s">
-        <v>20</v>
-      </c>
-      <c r="G122" t="s">
-        <v>21</v>
-      </c>
-      <c r="H122" t="s">
-        <v>97</v>
-      </c>
-      <c r="I122" t="s">
-        <v>23</v>
-      </c>
-      <c r="J122" t="s">
+      <c r="K122" t="s">
+        <v>47</v>
+      </c>
+      <c r="L122" t="s">
+        <v>26</v>
+      </c>
+      <c r="M122" t="s">
+        <v>26</v>
+      </c>
+      <c r="N122" t="s">
+        <v>26</v>
+      </c>
+      <c r="O122" t="s">
         <v>501</v>
-      </c>
-      <c r="K122" t="s">
-        <v>217</v>
-      </c>
-      <c r="L122" t="s">
-        <v>26</v>
-      </c>
-      <c r="M122" t="s">
-        <v>26</v>
-      </c>
-      <c r="N122" t="s">
-        <v>26</v>
-      </c>
-      <c r="O122" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>502</v>
+      </c>
+      <c r="B123" t="s">
         <v>503</v>
       </c>
-      <c r="B123" t="s">
-        <v>159</v>
-      </c>
       <c r="C123" t="s">
-        <v>154</v>
+        <v>26</v>
       </c>
       <c r="D123" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="E123" t="s">
         <v>19</v>
       </c>
       <c r="F123" t="s">
-        <v>184</v>
+        <v>66</v>
       </c>
       <c r="G123" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="H123" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="I123" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J123" t="s">
         <v>504</v>
       </c>
       <c r="K123" t="s">
-        <v>326</v>
+        <v>25</v>
       </c>
       <c r="L123" t="s">
         <v>26</v>
@@ -7920,10 +7887,10 @@
         <v>506</v>
       </c>
       <c r="B124" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C124" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D124" t="s">
         <v>18</v>
@@ -7932,10 +7899,10 @@
         <v>19</v>
       </c>
       <c r="F124" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="G124" t="s">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="H124" t="s">
         <v>22</v>
@@ -7944,33 +7911,33 @@
         <v>23</v>
       </c>
       <c r="J124" t="s">
+        <v>82</v>
+      </c>
+      <c r="K124" t="s">
+        <v>192</v>
+      </c>
+      <c r="L124" t="s">
+        <v>26</v>
+      </c>
+      <c r="M124" t="s">
+        <v>26</v>
+      </c>
+      <c r="N124" t="s">
+        <v>26</v>
+      </c>
+      <c r="O124" t="s">
         <v>507</v>
-      </c>
-      <c r="K124" t="s">
-        <v>111</v>
-      </c>
-      <c r="L124" t="s">
-        <v>26</v>
-      </c>
-      <c r="M124" t="s">
-        <v>26</v>
-      </c>
-      <c r="N124" t="s">
-        <v>26</v>
-      </c>
-      <c r="O124" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B125" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C125" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D125" t="s">
         <v>18</v>
@@ -7979,10 +7946,10 @@
         <v>19</v>
       </c>
       <c r="F125" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G125" t="s">
-        <v>260</v>
+        <v>154</v>
       </c>
       <c r="H125" t="s">
         <v>22</v>
@@ -7991,151 +7958,151 @@
         <v>23</v>
       </c>
       <c r="J125" t="s">
+        <v>509</v>
+      </c>
+      <c r="K125" t="s">
+        <v>148</v>
+      </c>
+      <c r="L125" t="s">
+        <v>26</v>
+      </c>
+      <c r="M125" t="s">
+        <v>26</v>
+      </c>
+      <c r="N125" t="s">
+        <v>26</v>
+      </c>
+      <c r="O125" t="s">
         <v>510</v>
-      </c>
-      <c r="K125" t="s">
-        <v>150</v>
-      </c>
-      <c r="L125" t="s">
-        <v>26</v>
-      </c>
-      <c r="M125" t="s">
-        <v>26</v>
-      </c>
-      <c r="N125" t="s">
-        <v>26</v>
-      </c>
-      <c r="O125" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>511</v>
+      </c>
+      <c r="B126" t="s">
+        <v>64</v>
+      </c>
+      <c r="C126" t="s">
+        <v>65</v>
+      </c>
+      <c r="D126" t="s">
+        <v>18</v>
+      </c>
+      <c r="E126" t="s">
+        <v>19</v>
+      </c>
+      <c r="F126" t="s">
+        <v>66</v>
+      </c>
+      <c r="G126" t="s">
+        <v>154</v>
+      </c>
+      <c r="H126" t="s">
+        <v>22</v>
+      </c>
+      <c r="I126" t="s">
+        <v>23</v>
+      </c>
+      <c r="J126" t="s">
+        <v>201</v>
+      </c>
+      <c r="K126" t="s">
+        <v>206</v>
+      </c>
+      <c r="L126" t="s">
+        <v>26</v>
+      </c>
+      <c r="M126" t="s">
+        <v>26</v>
+      </c>
+      <c r="N126" t="s">
+        <v>26</v>
+      </c>
+      <c r="O126" t="s">
         <v>512</v>
-      </c>
-      <c r="B126" t="s">
-        <v>29</v>
-      </c>
-      <c r="C126" t="s">
-        <v>253</v>
-      </c>
-      <c r="D126" t="s">
-        <v>161</v>
-      </c>
-      <c r="E126" t="s">
-        <v>19</v>
-      </c>
-      <c r="F126" t="s">
-        <v>214</v>
-      </c>
-      <c r="G126" t="s">
-        <v>513</v>
-      </c>
-      <c r="H126" t="s">
-        <v>97</v>
-      </c>
-      <c r="I126" t="s">
-        <v>26</v>
-      </c>
-      <c r="J126" t="s">
-        <v>127</v>
-      </c>
-      <c r="K126" t="s">
-        <v>216</v>
-      </c>
-      <c r="L126" t="s">
-        <v>26</v>
-      </c>
-      <c r="M126" t="s">
-        <v>217</v>
-      </c>
-      <c r="N126" t="s">
-        <v>26</v>
-      </c>
-      <c r="O126" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>513</v>
+      </c>
+      <c r="B127" t="s">
+        <v>57</v>
+      </c>
+      <c r="C127" t="s">
+        <v>177</v>
+      </c>
+      <c r="D127" t="s">
+        <v>52</v>
+      </c>
+      <c r="E127" t="s">
+        <v>19</v>
+      </c>
+      <c r="F127" t="s">
+        <v>66</v>
+      </c>
+      <c r="G127" t="s">
+        <v>45</v>
+      </c>
+      <c r="H127" t="s">
+        <v>36</v>
+      </c>
+      <c r="I127" t="s">
+        <v>23</v>
+      </c>
+      <c r="J127" t="s">
+        <v>514</v>
+      </c>
+      <c r="K127" t="s">
+        <v>27</v>
+      </c>
+      <c r="L127" t="s">
+        <v>26</v>
+      </c>
+      <c r="M127" t="s">
+        <v>26</v>
+      </c>
+      <c r="N127" t="s">
+        <v>26</v>
+      </c>
+      <c r="O127" t="s">
         <v>515</v>
-      </c>
-      <c r="B127" t="s">
-        <v>516</v>
-      </c>
-      <c r="C127" t="s">
-        <v>517</v>
-      </c>
-      <c r="D127" t="s">
-        <v>26</v>
-      </c>
-      <c r="E127" t="s">
-        <v>45</v>
-      </c>
-      <c r="F127" t="s">
-        <v>36</v>
-      </c>
-      <c r="G127" t="s">
-        <v>21</v>
-      </c>
-      <c r="H127" t="s">
-        <v>97</v>
-      </c>
-      <c r="I127" t="s">
-        <v>47</v>
-      </c>
-      <c r="J127" t="s">
-        <v>518</v>
-      </c>
-      <c r="K127" t="s">
-        <v>343</v>
-      </c>
-      <c r="L127" t="s">
-        <v>26</v>
-      </c>
-      <c r="M127" t="s">
-        <v>26</v>
-      </c>
-      <c r="N127" t="s">
-        <v>26</v>
-      </c>
-      <c r="O127" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B128" t="s">
-        <v>379</v>
+        <v>57</v>
       </c>
       <c r="C128" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D128" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E128" t="s">
+        <v>19</v>
+      </c>
+      <c r="F128" t="s">
+        <v>204</v>
+      </c>
+      <c r="G128" t="s">
         <v>45</v>
       </c>
-      <c r="F128" t="s">
-        <v>20</v>
-      </c>
-      <c r="G128" t="s">
-        <v>21</v>
-      </c>
       <c r="H128" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I128" t="s">
         <v>23</v>
       </c>
       <c r="J128" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="K128" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="L128" t="s">
         <v>26</v>
@@ -8147,18 +8114,18 @@
         <v>26</v>
       </c>
       <c r="O128" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B129" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C129" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D129" t="s">
         <v>18</v>
@@ -8167,10 +8134,10 @@
         <v>19</v>
       </c>
       <c r="F129" t="s">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="G129" t="s">
-        <v>26</v>
+        <v>154</v>
       </c>
       <c r="H129" t="s">
         <v>22</v>
@@ -8179,10 +8146,10 @@
         <v>23</v>
       </c>
       <c r="J129" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="K129" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="L129" t="s">
         <v>26</v>
@@ -8194,30 +8161,30 @@
         <v>26</v>
       </c>
       <c r="O129" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="B130" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C130" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D130" t="s">
         <v>18</v>
       </c>
       <c r="E130" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F130" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="G130" t="s">
-        <v>21</v>
+        <v>276</v>
       </c>
       <c r="H130" t="s">
         <v>22</v>
@@ -8226,10 +8193,10 @@
         <v>23</v>
       </c>
       <c r="J130" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="K130" t="s">
-        <v>228</v>
+        <v>173</v>
       </c>
       <c r="L130" t="s">
         <v>26</v>
@@ -8241,89 +8208,89 @@
         <v>26</v>
       </c>
       <c r="O130" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="B131" t="s">
-        <v>415</v>
+        <v>70</v>
       </c>
       <c r="C131" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="D131" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="E131" t="s">
         <v>19</v>
       </c>
       <c r="F131" t="s">
-        <v>214</v>
+        <v>20</v>
       </c>
       <c r="G131" t="s">
-        <v>21</v>
+        <v>526</v>
       </c>
       <c r="H131" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I131" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J131" t="s">
-        <v>530</v>
+        <v>151</v>
       </c>
       <c r="K131" t="s">
-        <v>531</v>
+        <v>234</v>
       </c>
       <c r="L131" t="s">
         <v>26</v>
       </c>
       <c r="M131" t="s">
-        <v>217</v>
+        <v>27</v>
       </c>
       <c r="N131" t="s">
         <v>26</v>
       </c>
       <c r="O131" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="B132" t="s">
-        <v>42</v>
+        <v>529</v>
       </c>
       <c r="C132" t="s">
-        <v>43</v>
+        <v>530</v>
       </c>
       <c r="D132" t="s">
+        <v>26</v>
+      </c>
+      <c r="E132" t="s">
+        <v>33</v>
+      </c>
+      <c r="F132" t="s">
         <v>44</v>
       </c>
-      <c r="E132" t="s">
+      <c r="G132" t="s">
         <v>45</v>
       </c>
-      <c r="F132" t="s">
+      <c r="H132" t="s">
         <v>36</v>
       </c>
-      <c r="G132" t="s">
-        <v>21</v>
-      </c>
-      <c r="H132" t="s">
-        <v>97</v>
-      </c>
       <c r="I132" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="J132" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="K132" t="s">
-        <v>77</v>
+        <v>359</v>
       </c>
       <c r="L132" t="s">
         <v>26</v>
@@ -8335,42 +8302,42 @@
         <v>26</v>
       </c>
       <c r="O132" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B133" t="s">
-        <v>29</v>
+        <v>394</v>
       </c>
       <c r="C133" t="s">
-        <v>253</v>
+        <v>196</v>
       </c>
       <c r="D133" t="s">
-        <v>161</v>
+        <v>52</v>
       </c>
       <c r="E133" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F133" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="G133" t="s">
-        <v>537</v>
+        <v>45</v>
       </c>
       <c r="H133" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="I133" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J133" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="K133" t="s">
-        <v>192</v>
+        <v>342</v>
       </c>
       <c r="L133" t="s">
         <v>26</v>
@@ -8379,15 +8346,15 @@
         <v>26</v>
       </c>
       <c r="N133" t="s">
-        <v>539</v>
+        <v>26</v>
       </c>
       <c r="O133" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="B134" t="s">
         <v>16</v>
@@ -8402,10 +8369,10 @@
         <v>19</v>
       </c>
       <c r="F134" t="s">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="G134" t="s">
-        <v>118</v>
+        <v>26</v>
       </c>
       <c r="H134" t="s">
         <v>22</v>
@@ -8414,10 +8381,10 @@
         <v>23</v>
       </c>
       <c r="J134" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="K134" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="L134" t="s">
         <v>26</v>
@@ -8429,30 +8396,30 @@
         <v>26</v>
       </c>
       <c r="O134" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="B135" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C135" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D135" t="s">
         <v>18</v>
       </c>
       <c r="E135" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F135" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G135" t="s">
-        <v>118</v>
+        <v>45</v>
       </c>
       <c r="H135" t="s">
         <v>22</v>
@@ -8461,10 +8428,10 @@
         <v>23</v>
       </c>
       <c r="J135" t="s">
-        <v>181</v>
+        <v>540</v>
       </c>
       <c r="K135" t="s">
-        <v>77</v>
+        <v>245</v>
       </c>
       <c r="L135" t="s">
         <v>26</v>
@@ -8476,18 +8443,18 @@
         <v>26</v>
       </c>
       <c r="O135" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="B136" t="s">
-        <v>63</v>
+        <v>430</v>
       </c>
       <c r="C136" t="s">
-        <v>64</v>
+        <v>275</v>
       </c>
       <c r="D136" t="s">
         <v>18</v>
@@ -8496,10 +8463,10 @@
         <v>19</v>
       </c>
       <c r="F136" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="G136" t="s">
-        <v>547</v>
+        <v>45</v>
       </c>
       <c r="H136" t="s">
         <v>22</v>
@@ -8508,57 +8475,57 @@
         <v>23</v>
       </c>
       <c r="J136" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="K136" t="s">
-        <v>262</v>
+        <v>544</v>
       </c>
       <c r="L136" t="s">
         <v>26</v>
       </c>
       <c r="M136" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N136" t="s">
         <v>26</v>
       </c>
       <c r="O136" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B137" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="C137" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="D137" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="E137" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="F137" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G137" t="s">
-        <v>131</v>
+        <v>45</v>
       </c>
       <c r="H137" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I137" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J137" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="K137" t="s">
-        <v>340</v>
+        <v>105</v>
       </c>
       <c r="L137" t="s">
         <v>26</v>
@@ -8570,65 +8537,65 @@
         <v>26</v>
       </c>
       <c r="O137" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>549</v>
+      </c>
+      <c r="B138" t="s">
+        <v>70</v>
+      </c>
+      <c r="C138" t="s">
+        <v>269</v>
+      </c>
+      <c r="D138" t="s">
+        <v>59</v>
+      </c>
+      <c r="E138" t="s">
+        <v>19</v>
+      </c>
+      <c r="F138" t="s">
+        <v>121</v>
+      </c>
+      <c r="G138" t="s">
+        <v>550</v>
+      </c>
+      <c r="H138" t="s">
+        <v>36</v>
+      </c>
+      <c r="I138" t="s">
+        <v>26</v>
+      </c>
+      <c r="J138" t="s">
+        <v>551</v>
+      </c>
+      <c r="K138" t="s">
+        <v>61</v>
+      </c>
+      <c r="L138" t="s">
+        <v>26</v>
+      </c>
+      <c r="M138" t="s">
+        <v>26</v>
+      </c>
+      <c r="N138" t="s">
+        <v>552</v>
+      </c>
+      <c r="O138" t="s">
         <v>553</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="s">
-        <v>17</v>
-      </c>
-      <c r="D138" t="s">
-        <v>18</v>
-      </c>
-      <c r="E138" t="s">
-        <v>19</v>
-      </c>
-      <c r="F138" t="s">
-        <v>36</v>
-      </c>
-      <c r="G138" t="s">
-        <v>21</v>
-      </c>
-      <c r="H138" t="s">
-        <v>22</v>
-      </c>
-      <c r="I138" t="s">
-        <v>23</v>
-      </c>
-      <c r="J138" t="s">
-        <v>554</v>
-      </c>
-      <c r="K138" t="s">
-        <v>128</v>
-      </c>
-      <c r="L138" t="s">
-        <v>26</v>
-      </c>
-      <c r="M138" t="s">
-        <v>26</v>
-      </c>
-      <c r="N138" t="s">
-        <v>26</v>
-      </c>
-      <c r="O138" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B139" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C139" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D139" t="s">
         <v>18</v>
@@ -8637,10 +8604,10 @@
         <v>19</v>
       </c>
       <c r="F139" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="G139" t="s">
-        <v>96</v>
+        <v>142</v>
       </c>
       <c r="H139" t="s">
         <v>22</v>
@@ -8649,10 +8616,10 @@
         <v>23</v>
       </c>
       <c r="J139" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="K139" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="L139" t="s">
         <v>26</v>
@@ -8661,21 +8628,21 @@
         <v>26</v>
       </c>
       <c r="N139" t="s">
-        <v>309</v>
+        <v>26</v>
       </c>
       <c r="O139" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B140" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C140" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D140" t="s">
         <v>18</v>
@@ -8684,10 +8651,10 @@
         <v>19</v>
       </c>
       <c r="F140" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G140" t="s">
-        <v>65</v>
+        <v>142</v>
       </c>
       <c r="H140" t="s">
         <v>22</v>
@@ -8696,10 +8663,10 @@
         <v>23</v>
       </c>
       <c r="J140" t="s">
-        <v>560</v>
+        <v>201</v>
       </c>
       <c r="K140" t="s">
-        <v>216</v>
+        <v>105</v>
       </c>
       <c r="L140" t="s">
         <v>26</v>
@@ -8711,12 +8678,12 @@
         <v>26</v>
       </c>
       <c r="O140" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B141" t="s">
         <v>16</v>
@@ -8731,10 +8698,10 @@
         <v>19</v>
       </c>
       <c r="F141" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G141" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="H141" t="s">
         <v>22</v>
@@ -8743,10 +8710,10 @@
         <v>23</v>
       </c>
       <c r="J141" t="s">
-        <v>391</v>
+        <v>561</v>
       </c>
       <c r="K141" t="s">
-        <v>478</v>
+        <v>278</v>
       </c>
       <c r="L141" t="s">
         <v>26</v>
@@ -8758,18 +8725,18 @@
         <v>26</v>
       </c>
       <c r="O141" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B142" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C142" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D142" t="s">
         <v>18</v>
@@ -8778,10 +8745,10 @@
         <v>19</v>
       </c>
       <c r="F142" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="G142" t="s">
-        <v>566</v>
+        <v>154</v>
       </c>
       <c r="H142" t="s">
         <v>22</v>
@@ -8790,10 +8757,10 @@
         <v>23</v>
       </c>
       <c r="J142" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="K142" t="s">
-        <v>150</v>
+        <v>356</v>
       </c>
       <c r="L142" t="s">
         <v>26</v>
@@ -8805,43 +8772,43 @@
         <v>26</v>
       </c>
       <c r="O142" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B143" t="s">
-        <v>438</v>
+        <v>64</v>
       </c>
       <c r="C143" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="D143" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="E143" t="s">
+        <v>19</v>
+      </c>
+      <c r="F143" t="s">
+        <v>44</v>
+      </c>
+      <c r="G143" t="s">
         <v>45</v>
       </c>
-      <c r="F143" t="s">
-        <v>184</v>
-      </c>
-      <c r="G143" t="s">
-        <v>96</v>
-      </c>
       <c r="H143" t="s">
         <v>22</v>
       </c>
       <c r="I143" t="s">
+        <v>23</v>
+      </c>
+      <c r="J143" t="s">
+        <v>567</v>
+      </c>
+      <c r="K143" t="s">
         <v>47</v>
       </c>
-      <c r="J143" t="s">
-        <v>201</v>
-      </c>
-      <c r="K143" t="s">
-        <v>441</v>
-      </c>
       <c r="L143" t="s">
         <v>26</v>
       </c>
@@ -8852,148 +8819,7 @@
         <v>26</v>
       </c>
       <c r="O143" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>571</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="s">
-        <v>17</v>
-      </c>
-      <c r="D144" t="s">
-        <v>18</v>
-      </c>
-      <c r="E144" t="s">
-        <v>19</v>
-      </c>
-      <c r="F144" t="s">
-        <v>36</v>
-      </c>
-      <c r="G144" t="s">
-        <v>131</v>
-      </c>
-      <c r="H144" t="s">
-        <v>22</v>
-      </c>
-      <c r="I144" t="s">
-        <v>23</v>
-      </c>
-      <c r="J144" t="s">
-        <v>572</v>
-      </c>
-      <c r="K144" t="s">
-        <v>228</v>
-      </c>
-      <c r="L144" t="s">
-        <v>26</v>
-      </c>
-      <c r="M144" t="s">
-        <v>26</v>
-      </c>
-      <c r="N144" t="s">
-        <v>26</v>
-      </c>
-      <c r="O144" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>574</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="s">
-        <v>17</v>
-      </c>
-      <c r="D145" t="s">
-        <v>18</v>
-      </c>
-      <c r="E145" t="s">
-        <v>19</v>
-      </c>
-      <c r="F145" t="s">
-        <v>20</v>
-      </c>
-      <c r="G145" t="s">
-        <v>131</v>
-      </c>
-      <c r="H145" t="s">
-        <v>22</v>
-      </c>
-      <c r="I145" t="s">
-        <v>23</v>
-      </c>
-      <c r="J145" t="s">
-        <v>575</v>
-      </c>
-      <c r="K145" t="s">
-        <v>192</v>
-      </c>
-      <c r="L145" t="s">
-        <v>26</v>
-      </c>
-      <c r="M145" t="s">
-        <v>26</v>
-      </c>
-      <c r="N145" t="s">
-        <v>26</v>
-      </c>
-      <c r="O145" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>577</v>
-      </c>
-      <c r="B146" t="s">
-        <v>415</v>
-      </c>
-      <c r="C146" t="s">
-        <v>259</v>
-      </c>
-      <c r="D146" t="s">
-        <v>18</v>
-      </c>
-      <c r="E146" t="s">
-        <v>19</v>
-      </c>
-      <c r="F146" t="s">
-        <v>214</v>
-      </c>
-      <c r="G146" t="s">
-        <v>96</v>
-      </c>
-      <c r="H146" t="s">
-        <v>22</v>
-      </c>
-      <c r="I146" t="s">
-        <v>23</v>
-      </c>
-      <c r="J146" t="s">
-        <v>578</v>
-      </c>
-      <c r="K146" t="s">
-        <v>326</v>
-      </c>
-      <c r="L146" t="s">
-        <v>26</v>
-      </c>
-      <c r="M146" t="s">
-        <v>217</v>
-      </c>
-      <c r="N146" t="s">
-        <v>26</v>
-      </c>
-      <c r="O146" t="s">
-        <v>579</v>
+        <v>568</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,19 +3,22 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB747A4E-0E6D-4B4F-8377-B0F5DD9922ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F055D839-0866-4C3D-ABA3-ED83842D6C90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sheet1!$A$1:$O$97</definedName>
+  </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="425">
   <si>
     <t>Time</t>
   </si>
@@ -62,9 +65,6 @@
     <t>Event URL</t>
   </si>
   <si>
-    <t>06/04/2026 2:15:03 PM</t>
-  </si>
-  <si>
     <t>644 - Medium</t>
   </si>
   <si>
@@ -83,15 +83,9 @@
     <t>Needs Coaching</t>
   </si>
   <si>
-    <t>Fannett Road, Beaumont, TX, 77701</t>
-  </si>
-  <si>
     <t>32</t>
   </si>
   <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445940f-7e14-5c0f-aa68-07d221d9e214</t>
-  </si>
-  <si>
     <t>06/03/2026 4:48:22 PM</t>
   </si>
   <si>
@@ -812,12 +806,6 @@
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544564eb-79d0-5e02-bdcb-46a38e6bc3b1</t>
   </si>
   <si>
-    <t>04/06/2026 9:54:40 AM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456349-e5b4-55ac-a43b-944299eef0c4</t>
-  </si>
-  <si>
     <t>04/04/2026 3:30:47 PM</t>
   </si>
   <si>
@@ -857,18 +845,6 @@
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454ec0-9872-5236-a722-8479419e97c6</t>
   </si>
   <si>
-    <t>04/02/2026 8:23:33 AM</t>
-  </si>
-  <si>
-    <t>I 10, 7.4 mi NW Kerrville, Kerr County, TX, 78025:78631</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454e5d-0a80-52f2-800d-6d1920f58de1</t>
-  </si>
-  <si>
     <t>04/01/2026 6:33:25 PM</t>
   </si>
   <si>
@@ -941,15 +917,6 @@
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454599-fd4e-5fc8-b9a7-5a6d8fc02784</t>
   </si>
   <si>
-    <t>03/31/2026 3:13:41 PM</t>
-  </si>
-  <si>
-    <t>US 96, Zion Hill, TX</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454587-d024-5358-89a5-f14a9b756111</t>
-  </si>
-  <si>
     <t>03/31/2026 9:10:43 AM</t>
   </si>
   <si>
@@ -1109,15 +1076,6 @@
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450893-aabf-5818-9db3-afc50f70f5ed</t>
   </si>
   <si>
-    <t>03/19/2026 11:18:44 AM</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544506e4-630c-59b3-88ae-741798ff874c</t>
-  </si>
-  <si>
     <t>03/18/2026 4:44:25 PM</t>
   </si>
   <si>
@@ -1241,18 +1199,6 @@
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e8e3-b6e9-523c-814d-c3175795ade0</t>
   </si>
   <si>
-    <t>03/13/2026 1:36:23 PM</t>
-  </si>
-  <si>
-    <t>I 10, Cove, TX, 77523</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e87c-411e-5c77-80c8-2b39bf713eb3</t>
-  </si>
-  <si>
     <t>03/13/2026 8:26:45 AM</t>
   </si>
   <si>
@@ -1332,27 +1278,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445de0d-2536-552e-a3db-af775cdc7d20</t>
-  </si>
-  <si>
-    <t>03/11/2026 10:58:07 AM</t>
-  </si>
-  <si>
-    <t>10986 Eastex Freeway, Aldine, TX, 77093</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445dd9e-a59c-54c0-9aad-0915937a3ec0</t>
-  </si>
-  <si>
-    <t>03/11/2026 10:56:40 AM</t>
-  </si>
-  <si>
-    <t>Eastex Freeway Frontage Road, Houston, TX, 77093</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445dd9d-5163-5221-bfbc-3057a3e4dbb3</t>
   </si>
   <si>
     <t>03/10/2026 2:44:40 PM</t>
@@ -1744,7 +1669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O105"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -1796,1788 +1721,1788 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>249</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>250</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>251</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J2" t="s">
-        <v>22</v>
+        <v>252</v>
       </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>253</v>
       </c>
       <c r="L2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O2" t="s">
-        <v>24</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>380</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="C3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s">
-        <v>30</v>
-      </c>
       <c r="J3" t="s">
-        <v>31</v>
+        <v>323</v>
       </c>
       <c r="K3" t="s">
-        <v>32</v>
+        <v>381</v>
       </c>
       <c r="L3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O3" t="s">
-        <v>33</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>420</v>
+      </c>
+      <c r="B4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D4" t="s">
         <v>34</v>
       </c>
-      <c r="B4" t="s">
+      <c r="E4" t="s">
         <v>35</v>
       </c>
-      <c r="C4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="G4" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="I4" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="J4" t="s">
-        <v>42</v>
+        <v>421</v>
       </c>
       <c r="K4" t="s">
-        <v>43</v>
+        <v>247</v>
       </c>
       <c r="L4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O4" t="s">
-        <v>44</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>407</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>408</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>409</v>
       </c>
       <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" t="s">
+        <v>410</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
         <v>38</v>
       </c>
-      <c r="F5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" t="s">
-        <v>50</v>
-      </c>
-      <c r="I5" t="s">
-        <v>41</v>
-      </c>
       <c r="J5" t="s">
-        <v>51</v>
+        <v>202</v>
       </c>
       <c r="K5" t="s">
-        <v>52</v>
+        <v>411</v>
       </c>
       <c r="L5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O5" t="s">
-        <v>53</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" t="s">
         <v>35</v>
       </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" t="s">
         <v>37</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" t="s">
-        <v>55</v>
-      </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="I6" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="J6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="L6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O6" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="G7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" t="s">
+        <v>69</v>
+      </c>
+      <c r="K7" t="s">
         <v>40</v>
       </c>
-      <c r="H7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" t="s">
-        <v>64</v>
-      </c>
-      <c r="K7" t="s">
-        <v>65</v>
-      </c>
       <c r="L7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" t="s">
         <v>67</v>
       </c>
-      <c r="B8" t="s">
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
         <v>68</v>
       </c>
-      <c r="C8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" t="s">
-        <v>71</v>
-      </c>
       <c r="H8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J8" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="K8" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="L8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O8" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="H9" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="I9" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J9" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K9" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="L9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M9" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="N9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O9" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="H10" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J10" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K10" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="L10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O10" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G11" t="s">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="H11" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="I11" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J11" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="K11" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="L11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O11" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>311</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>312</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" t="s">
         <v>18</v>
       </c>
-      <c r="F12" t="s">
-        <v>49</v>
-      </c>
       <c r="G12" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="H12" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J12" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="K12" t="s">
-        <v>32</v>
+        <v>313</v>
       </c>
       <c r="L12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M12" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="N12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O12" t="s">
-        <v>93</v>
+        <v>314</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>352</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>312</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" t="s">
         <v>18</v>
       </c>
-      <c r="F13" t="s">
-        <v>39</v>
-      </c>
       <c r="G13" t="s">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="H13" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J13" t="s">
-        <v>96</v>
+        <v>353</v>
       </c>
       <c r="K13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O13" t="s">
-        <v>98</v>
+        <v>354</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>99</v>
+        <v>360</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>312</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>361</v>
       </c>
       <c r="G14" t="s">
-        <v>100</v>
+        <v>362</v>
       </c>
       <c r="H14" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J14" t="s">
-        <v>101</v>
+        <v>363</v>
       </c>
       <c r="K14" t="s">
-        <v>102</v>
+        <v>165</v>
       </c>
       <c r="L14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N14" t="s">
-        <v>17</v>
+        <v>364</v>
       </c>
       <c r="O14" t="s">
-        <v>103</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>104</v>
+        <v>377</v>
       </c>
       <c r="B15" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
+        <v>312</v>
+      </c>
+      <c r="D15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" t="s">
         <v>36</v>
       </c>
-      <c r="D15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" t="s">
-        <v>39</v>
-      </c>
       <c r="G15" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="H15" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I15" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="J15" t="s">
-        <v>106</v>
+        <v>378</v>
       </c>
       <c r="K15" t="s">
-        <v>107</v>
+        <v>193</v>
       </c>
       <c r="L15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O15" t="s">
-        <v>108</v>
+        <v>379</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>109</v>
+        <v>396</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>312</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>361</v>
       </c>
       <c r="G16" t="s">
-        <v>71</v>
+        <v>201</v>
       </c>
       <c r="H16" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="I16" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J16" t="s">
-        <v>110</v>
+        <v>397</v>
       </c>
       <c r="K16" t="s">
-        <v>111</v>
+        <v>398</v>
       </c>
       <c r="L16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M16" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="N16" t="s">
-        <v>17</v>
+        <v>399</v>
       </c>
       <c r="O16" t="s">
-        <v>112</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>113</v>
+        <v>180</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="D17" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F17" t="s">
-        <v>49</v>
+        <v>183</v>
       </c>
       <c r="G17" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="H17" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="I17" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J17" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="K17" t="s">
-        <v>97</v>
+        <v>185</v>
       </c>
       <c r="L17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M17" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="N17" t="s">
-        <v>17</v>
+        <v>186</v>
       </c>
       <c r="O17" t="s">
-        <v>115</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>116</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s">
-        <v>117</v>
+        <v>214</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>182</v>
       </c>
       <c r="D18" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F18" t="s">
-        <v>118</v>
+        <v>183</v>
       </c>
       <c r="G18" t="s">
-        <v>119</v>
+        <v>37</v>
       </c>
       <c r="H18" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I18" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="J18" t="s">
-        <v>120</v>
+        <v>215</v>
       </c>
       <c r="K18" t="s">
-        <v>65</v>
+        <v>216</v>
       </c>
       <c r="L18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N18" t="s">
-        <v>17</v>
+        <v>217</v>
       </c>
       <c r="O18" t="s">
-        <v>121</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>122</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>214</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>182</v>
       </c>
       <c r="D19" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F19" t="s">
-        <v>39</v>
+        <v>183</v>
       </c>
       <c r="G19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H19" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="I19" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J19" t="s">
-        <v>123</v>
+        <v>220</v>
       </c>
       <c r="K19" t="s">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="L19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N19" t="s">
-        <v>17</v>
+        <v>221</v>
       </c>
       <c r="O19" t="s">
-        <v>124</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>125</v>
+        <v>265</v>
       </c>
       <c r="B20" t="s">
+        <v>214</v>
+      </c>
+      <c r="C20" t="s">
+        <v>182</v>
+      </c>
+      <c r="D20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" t="s">
         <v>35</v>
       </c>
-      <c r="C20" t="s">
-        <v>36</v>
-      </c>
-      <c r="D20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E20" t="s">
-        <v>38</v>
-      </c>
       <c r="F20" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="G20" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H20" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I20" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="J20" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="K20" t="s">
-        <v>32</v>
+        <v>266</v>
       </c>
       <c r="L20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O20" t="s">
-        <v>127</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>128</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s">
-        <v>129</v>
+        <v>232</v>
       </c>
       <c r="C21" t="s">
-        <v>130</v>
+        <v>233</v>
       </c>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="E21" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" t="s">
         <v>18</v>
       </c>
-      <c r="F21" t="s">
-        <v>39</v>
-      </c>
       <c r="G21" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H21" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I21" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J21" t="s">
-        <v>131</v>
+        <v>234</v>
       </c>
       <c r="K21" t="s">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="L21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O21" t="s">
-        <v>133</v>
+        <v>235</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>136</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F22" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G22" t="s">
+        <v>37</v>
+      </c>
+      <c r="H22" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" t="s">
+        <v>38</v>
+      </c>
+      <c r="J22" t="s">
+        <v>39</v>
+      </c>
+      <c r="K22" t="s">
         <v>40</v>
       </c>
-      <c r="H22" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" t="s">
-        <v>30</v>
-      </c>
-      <c r="J22" t="s">
-        <v>123</v>
-      </c>
-      <c r="K22" t="s">
-        <v>137</v>
-      </c>
       <c r="L22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O22" t="s">
-        <v>138</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>139</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>140</v>
+        <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F23" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G23" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="H23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I23" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="J23" t="s">
-        <v>141</v>
+        <v>53</v>
       </c>
       <c r="K23" t="s">
-        <v>142</v>
+        <v>54</v>
       </c>
       <c r="L23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O23" t="s">
-        <v>143</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>144</v>
+        <v>101</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="C24" t="s">
-        <v>140</v>
+        <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F24" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G24" t="s">
-        <v>145</v>
+        <v>37</v>
       </c>
       <c r="H24" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="I24" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="J24" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="K24" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="L24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O24" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" t="s">
         <v>35</v>
       </c>
-      <c r="C25" t="s">
+      <c r="F25" t="s">
         <v>36</v>
       </c>
-      <c r="D25" t="s">
+      <c r="G25" t="s">
         <v>37</v>
       </c>
-      <c r="E25" t="s">
+      <c r="H25" t="s">
+        <v>47</v>
+      </c>
+      <c r="I25" t="s">
         <v>38</v>
       </c>
-      <c r="F25" t="s">
-        <v>39</v>
-      </c>
-      <c r="G25" t="s">
-        <v>150</v>
-      </c>
-      <c r="H25" t="s">
-        <v>50</v>
-      </c>
-      <c r="I25" t="s">
-        <v>41</v>
-      </c>
       <c r="J25" t="s">
-        <v>151</v>
+        <v>123</v>
       </c>
       <c r="K25" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="L25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O25" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B26" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>136</v>
+        <v>33</v>
       </c>
       <c r="D26" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E26" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F26" t="s">
-        <v>118</v>
+        <v>36</v>
       </c>
       <c r="G26" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="H26" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="I26" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="J26" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="K26" t="s">
-        <v>156</v>
+        <v>79</v>
       </c>
       <c r="L26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O26" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="B27" t="s">
-        <v>159</v>
+        <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>140</v>
+        <v>33</v>
       </c>
       <c r="D27" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E27" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" t="s">
+        <v>36</v>
+      </c>
+      <c r="G27" t="s">
+        <v>52</v>
+      </c>
+      <c r="H27" t="s">
+        <v>47</v>
+      </c>
+      <c r="I27" t="s">
         <v>38</v>
       </c>
-      <c r="F27" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" t="s">
-        <v>40</v>
-      </c>
-      <c r="H27" t="s">
-        <v>21</v>
-      </c>
-      <c r="I27" t="s">
-        <v>30</v>
-      </c>
       <c r="J27" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="K27" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="L27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O27" t="s">
-        <v>162</v>
+        <v>191</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D28" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E28" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F28" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G28" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="H28" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="I28" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="J28" t="s">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="K28" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O28" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>166</v>
+        <v>287</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D29" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E29" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F29" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G29" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H29" t="s">
+        <v>47</v>
+      </c>
+      <c r="I29" t="s">
+        <v>38</v>
+      </c>
+      <c r="J29" t="s">
+        <v>288</v>
+      </c>
+      <c r="K29" t="s">
         <v>21</v>
       </c>
-      <c r="I29" t="s">
-        <v>30</v>
-      </c>
-      <c r="J29" t="s">
-        <v>167</v>
-      </c>
-      <c r="K29" t="s">
-        <v>168</v>
-      </c>
       <c r="L29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O29" t="s">
-        <v>169</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>170</v>
+        <v>296</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="C30" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="D30" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E30" t="s">
+        <v>35</v>
+      </c>
+      <c r="F30" t="s">
+        <v>36</v>
+      </c>
+      <c r="G30" t="s">
+        <v>37</v>
+      </c>
+      <c r="H30" t="s">
+        <v>47</v>
+      </c>
+      <c r="I30" t="s">
         <v>38</v>
       </c>
-      <c r="F30" t="s">
-        <v>39</v>
-      </c>
-      <c r="G30" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" t="s">
-        <v>21</v>
-      </c>
-      <c r="I30" t="s">
-        <v>30</v>
-      </c>
       <c r="J30" t="s">
-        <v>171</v>
+        <v>297</v>
       </c>
       <c r="K30" t="s">
-        <v>23</v>
+        <v>129</v>
       </c>
       <c r="L30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O30" t="s">
-        <v>172</v>
+        <v>298</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>173</v>
+        <v>315</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>316</v>
       </c>
       <c r="C31" t="s">
-        <v>76</v>
+        <v>317</v>
       </c>
       <c r="D31" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E31" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F31" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="G31" t="s">
-        <v>40</v>
+        <v>318</v>
       </c>
       <c r="H31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I31" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J31" t="s">
-        <v>174</v>
+        <v>319</v>
       </c>
       <c r="K31" t="s">
-        <v>175</v>
+        <v>320</v>
       </c>
       <c r="L31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O31" t="s">
-        <v>176</v>
+        <v>321</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>177</v>
+        <v>240</v>
       </c>
       <c r="B32" t="s">
-        <v>159</v>
+        <v>241</v>
       </c>
       <c r="C32" t="s">
+        <v>242</v>
+      </c>
+      <c r="D32" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" t="s">
+        <v>35</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>37</v>
+      </c>
+      <c r="H32" t="s">
         <v>47</v>
       </c>
-      <c r="D32" t="s">
-        <v>48</v>
-      </c>
-      <c r="E32" t="s">
-        <v>38</v>
-      </c>
-      <c r="F32" t="s">
-        <v>19</v>
-      </c>
-      <c r="G32" t="s">
-        <v>20</v>
-      </c>
-      <c r="H32" t="s">
-        <v>21</v>
-      </c>
       <c r="I32" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="J32" t="s">
-        <v>178</v>
+        <v>243</v>
       </c>
       <c r="K32" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="L32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O32" t="s">
-        <v>179</v>
+        <v>244</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>180</v>
+        <v>245</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>241</v>
       </c>
       <c r="C33" t="s">
-        <v>76</v>
+        <v>242</v>
       </c>
       <c r="D33" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E33" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F33" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G33" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="H33" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="I33" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J33" t="s">
-        <v>181</v>
+        <v>246</v>
       </c>
       <c r="K33" t="s">
-        <v>107</v>
+        <v>247</v>
       </c>
       <c r="L33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O33" t="s">
-        <v>182</v>
+        <v>248</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>183</v>
+        <v>71</v>
       </c>
       <c r="B34" t="s">
-        <v>184</v>
+        <v>72</v>
       </c>
       <c r="C34" t="s">
-        <v>185</v>
+        <v>73</v>
       </c>
       <c r="D34" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E34" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F34" t="s">
-        <v>186</v>
+        <v>36</v>
       </c>
       <c r="G34" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H34" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I34" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J34" t="s">
-        <v>187</v>
+        <v>74</v>
       </c>
       <c r="K34" t="s">
-        <v>188</v>
+        <v>75</v>
       </c>
       <c r="L34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N34" t="s">
-        <v>189</v>
+        <v>16</v>
       </c>
       <c r="O34" t="s">
-        <v>190</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>191</v>
+        <v>119</v>
       </c>
       <c r="B35" t="s">
+        <v>72</v>
+      </c>
+      <c r="C35" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" t="s">
         <v>35</v>
       </c>
-      <c r="C35" t="s">
+      <c r="F35" t="s">
         <v>36</v>
       </c>
-      <c r="D35" t="s">
+      <c r="G35" t="s">
         <v>37</v>
       </c>
-      <c r="E35" t="s">
-        <v>38</v>
-      </c>
-      <c r="F35" t="s">
-        <v>39</v>
-      </c>
-      <c r="G35" t="s">
-        <v>55</v>
-      </c>
       <c r="H35" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I35" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="J35" t="s">
-        <v>192</v>
+        <v>120</v>
       </c>
       <c r="K35" t="s">
-        <v>193</v>
+        <v>99</v>
       </c>
       <c r="L35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O35" t="s">
-        <v>194</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D36" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E36" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F36" t="s">
+        <v>36</v>
+      </c>
+      <c r="G36" t="s">
         <v>19</v>
       </c>
-      <c r="G36" t="s">
-        <v>145</v>
-      </c>
       <c r="H36" t="s">
+        <v>20</v>
+      </c>
+      <c r="I36" t="s">
+        <v>27</v>
+      </c>
+      <c r="J36" t="s">
+        <v>168</v>
+      </c>
+      <c r="K36" t="s">
         <v>21</v>
       </c>
-      <c r="I36" t="s">
-        <v>30</v>
-      </c>
-      <c r="J36" t="s">
-        <v>120</v>
-      </c>
-      <c r="K36" t="s">
-        <v>196</v>
-      </c>
       <c r="L36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O36" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="B37" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" t="s">
+        <v>73</v>
+      </c>
+      <c r="D37" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" t="s">
         <v>35</v>
       </c>
-      <c r="C37" t="s">
+      <c r="F37" t="s">
         <v>36</v>
       </c>
-      <c r="D37" t="s">
+      <c r="G37" t="s">
         <v>37</v>
       </c>
-      <c r="E37" t="s">
-        <v>38</v>
-      </c>
-      <c r="F37" t="s">
-        <v>39</v>
-      </c>
-      <c r="G37" t="s">
-        <v>20</v>
-      </c>
       <c r="H37" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I37" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="J37" t="s">
-        <v>123</v>
+        <v>171</v>
       </c>
       <c r="K37" t="s">
-        <v>43</v>
+        <v>172</v>
       </c>
       <c r="L37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O37" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="C38" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" t="s">
+        <v>35</v>
+      </c>
+      <c r="F38" t="s">
+        <v>36</v>
+      </c>
+      <c r="G38" t="s">
+        <v>37</v>
+      </c>
+      <c r="H38" t="s">
+        <v>20</v>
+      </c>
+      <c r="I38" t="s">
         <v>27</v>
       </c>
-      <c r="D38" t="s">
-        <v>28</v>
-      </c>
-      <c r="E38" t="s">
-        <v>18</v>
-      </c>
-      <c r="F38" t="s">
-        <v>29</v>
-      </c>
-      <c r="G38" t="s">
-        <v>17</v>
-      </c>
-      <c r="H38" t="s">
-        <v>21</v>
-      </c>
-      <c r="I38" t="s">
-        <v>30</v>
-      </c>
       <c r="J38" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="K38" t="s">
-        <v>201</v>
+        <v>104</v>
       </c>
       <c r="L38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O38" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="B39" t="s">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="D39" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E39" t="s">
+        <v>35</v>
+      </c>
+      <c r="F39" t="s">
         <v>18</v>
       </c>
-      <c r="F39" t="s">
-        <v>19</v>
-      </c>
       <c r="G39" t="s">
-        <v>204</v>
+        <v>142</v>
       </c>
       <c r="H39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I39" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J39" t="s">
-        <v>205</v>
+        <v>117</v>
       </c>
       <c r="K39" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="L39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O39" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
@@ -3585,43 +3510,43 @@
         <v>208</v>
       </c>
       <c r="B40" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="C40" t="s">
+        <v>73</v>
+      </c>
+      <c r="D40" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F40" t="s">
+        <v>36</v>
+      </c>
+      <c r="G40" t="s">
+        <v>201</v>
+      </c>
+      <c r="H40" t="s">
+        <v>20</v>
+      </c>
+      <c r="I40" t="s">
         <v>27</v>
-      </c>
-      <c r="D40" t="s">
-        <v>28</v>
-      </c>
-      <c r="E40" t="s">
-        <v>18</v>
-      </c>
-      <c r="F40" t="s">
-        <v>29</v>
-      </c>
-      <c r="G40" t="s">
-        <v>17</v>
-      </c>
-      <c r="H40" t="s">
-        <v>21</v>
-      </c>
-      <c r="I40" t="s">
-        <v>30</v>
       </c>
       <c r="J40" t="s">
         <v>209</v>
       </c>
       <c r="K40" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="L40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O40" t="s">
         <v>210</v>
@@ -3629,3060 +3554,2689 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C41" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D41" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E41" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F41" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G41" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H41" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I41" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J41" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="K41" t="s">
-        <v>102</v>
+        <v>229</v>
       </c>
       <c r="L41" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M41" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N41" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O41" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>214</v>
+        <v>258</v>
       </c>
       <c r="B42" t="s">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="C42" t="s">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="D42" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E42" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F42" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="G42" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="H42" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I42" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J42" t="s">
-        <v>77</v>
+        <v>259</v>
       </c>
       <c r="K42" t="s">
-        <v>168</v>
+        <v>260</v>
       </c>
       <c r="L42" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M42" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N42" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O42" t="s">
-        <v>215</v>
+        <v>261</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>216</v>
+        <v>290</v>
       </c>
       <c r="B43" t="s">
-        <v>217</v>
+        <v>72</v>
       </c>
       <c r="C43" t="s">
-        <v>185</v>
+        <v>73</v>
       </c>
       <c r="D43" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" t="s">
+        <v>35</v>
+      </c>
+      <c r="F43" t="s">
+        <v>36</v>
+      </c>
+      <c r="G43" t="s">
         <v>37</v>
       </c>
-      <c r="E43" t="s">
-        <v>38</v>
-      </c>
-      <c r="F43" t="s">
-        <v>186</v>
-      </c>
-      <c r="G43" t="s">
-        <v>40</v>
-      </c>
       <c r="H43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I43" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J43" t="s">
-        <v>218</v>
+        <v>291</v>
       </c>
       <c r="K43" t="s">
-        <v>219</v>
+        <v>54</v>
       </c>
       <c r="L43" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M43" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N43" t="s">
-        <v>220</v>
+        <v>16</v>
       </c>
       <c r="O43" t="s">
-        <v>221</v>
+        <v>292</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>222</v>
+        <v>322</v>
       </c>
       <c r="B44" t="s">
-        <v>217</v>
+        <v>72</v>
       </c>
       <c r="C44" t="s">
-        <v>185</v>
+        <v>73</v>
       </c>
       <c r="D44" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E44" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F44" t="s">
-        <v>186</v>
+        <v>36</v>
       </c>
       <c r="G44" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="H44" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I44" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J44" t="s">
-        <v>223</v>
+        <v>323</v>
       </c>
       <c r="K44" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="L44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N44" t="s">
-        <v>224</v>
+        <v>16</v>
       </c>
       <c r="O44" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>226</v>
+        <v>349</v>
       </c>
       <c r="B45" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="C45" t="s">
+        <v>73</v>
+      </c>
+      <c r="D45" t="s">
+        <v>25</v>
+      </c>
+      <c r="E45" t="s">
+        <v>35</v>
+      </c>
+      <c r="F45" t="s">
+        <v>36</v>
+      </c>
+      <c r="G45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" t="s">
+        <v>20</v>
+      </c>
+      <c r="I45" t="s">
         <v>27</v>
       </c>
-      <c r="D45" t="s">
-        <v>28</v>
-      </c>
-      <c r="E45" t="s">
-        <v>18</v>
-      </c>
-      <c r="F45" t="s">
-        <v>29</v>
-      </c>
-      <c r="G45" t="s">
-        <v>17</v>
-      </c>
-      <c r="H45" t="s">
+      <c r="J45" t="s">
+        <v>350</v>
+      </c>
+      <c r="K45" t="s">
         <v>21</v>
       </c>
-      <c r="I45" t="s">
-        <v>30</v>
-      </c>
-      <c r="J45" t="s">
-        <v>227</v>
-      </c>
-      <c r="K45" t="s">
-        <v>228</v>
-      </c>
       <c r="L45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O45" t="s">
-        <v>229</v>
+        <v>351</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>230</v>
+        <v>383</v>
       </c>
       <c r="B46" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C46" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D46" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E46" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F46" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G46" t="s">
-        <v>204</v>
+        <v>19</v>
       </c>
       <c r="H46" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I46" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J46" t="s">
-        <v>231</v>
+        <v>384</v>
       </c>
       <c r="K46" t="s">
-        <v>232</v>
+        <v>54</v>
       </c>
       <c r="L46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O46" t="s">
-        <v>233</v>
+        <v>385</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>234</v>
+        <v>386</v>
       </c>
       <c r="B47" t="s">
-        <v>235</v>
+        <v>72</v>
       </c>
       <c r="C47" t="s">
-        <v>236</v>
+        <v>73</v>
       </c>
       <c r="D47" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" t="s">
+        <v>35</v>
+      </c>
+      <c r="F47" t="s">
+        <v>36</v>
+      </c>
+      <c r="G47" t="s">
         <v>37</v>
       </c>
-      <c r="E47" t="s">
-        <v>18</v>
-      </c>
-      <c r="F47" t="s">
-        <v>19</v>
-      </c>
-      <c r="G47" t="s">
-        <v>40</v>
-      </c>
       <c r="H47" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I47" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J47" t="s">
-        <v>237</v>
+        <v>387</v>
       </c>
       <c r="K47" t="s">
-        <v>78</v>
+        <v>388</v>
       </c>
       <c r="L47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O47" t="s">
-        <v>238</v>
+        <v>389</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>239</v>
+        <v>125</v>
       </c>
       <c r="B48" t="s">
+        <v>126</v>
+      </c>
+      <c r="C48" t="s">
+        <v>127</v>
+      </c>
+      <c r="D48" t="s">
+        <v>67</v>
+      </c>
+      <c r="E48" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48" t="s">
+        <v>36</v>
+      </c>
+      <c r="G48" t="s">
+        <v>37</v>
+      </c>
+      <c r="H48" t="s">
+        <v>47</v>
+      </c>
+      <c r="I48" t="s">
+        <v>16</v>
+      </c>
+      <c r="J48" t="s">
+        <v>128</v>
+      </c>
+      <c r="K48" t="s">
         <v>129</v>
       </c>
-      <c r="C48" t="s">
+      <c r="L48" t="s">
+        <v>16</v>
+      </c>
+      <c r="M48" t="s">
+        <v>16</v>
+      </c>
+      <c r="N48" t="s">
+        <v>16</v>
+      </c>
+      <c r="O48" t="s">
         <v>130</v>
-      </c>
-      <c r="D48" t="s">
-        <v>70</v>
-      </c>
-      <c r="E48" t="s">
-        <v>18</v>
-      </c>
-      <c r="F48" t="s">
-        <v>19</v>
-      </c>
-      <c r="G48" t="s">
-        <v>40</v>
-      </c>
-      <c r="H48" t="s">
-        <v>50</v>
-      </c>
-      <c r="I48" t="s">
-        <v>17</v>
-      </c>
-      <c r="J48" t="s">
-        <v>240</v>
-      </c>
-      <c r="K48" t="s">
-        <v>241</v>
-      </c>
-      <c r="L48" t="s">
-        <v>17</v>
-      </c>
-      <c r="M48" t="s">
-        <v>17</v>
-      </c>
-      <c r="N48" t="s">
-        <v>17</v>
-      </c>
-      <c r="O48" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="B49" t="s">
-        <v>244</v>
+        <v>126</v>
       </c>
       <c r="C49" t="s">
-        <v>245</v>
+        <v>127</v>
       </c>
       <c r="D49" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="E49" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F49" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G49" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H49" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J49" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="K49" t="s">
-        <v>82</v>
+        <v>238</v>
       </c>
       <c r="L49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O49" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>248</v>
+        <v>283</v>
       </c>
       <c r="B50" t="s">
-        <v>244</v>
+        <v>126</v>
       </c>
       <c r="C50" t="s">
-        <v>245</v>
+        <v>127</v>
       </c>
       <c r="D50" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="E50" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F50" t="s">
-        <v>39</v>
+        <v>183</v>
       </c>
       <c r="G50" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="H50" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I50" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J50" t="s">
-        <v>249</v>
+        <v>284</v>
       </c>
       <c r="K50" t="s">
-        <v>250</v>
+        <v>89</v>
       </c>
       <c r="L50" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M50" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N50" t="s">
-        <v>17</v>
+        <v>285</v>
       </c>
       <c r="O50" t="s">
-        <v>251</v>
+        <v>286</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>252</v>
+        <v>22</v>
       </c>
       <c r="B51" t="s">
-        <v>253</v>
+        <v>23</v>
       </c>
       <c r="C51" t="s">
-        <v>254</v>
+        <v>24</v>
       </c>
       <c r="D51" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E51" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F51" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" t="s">
+        <v>16</v>
+      </c>
+      <c r="H51" t="s">
+        <v>20</v>
+      </c>
+      <c r="I51" t="s">
+        <v>27</v>
+      </c>
+      <c r="J51" t="s">
+        <v>28</v>
+      </c>
+      <c r="K51" t="s">
         <v>29</v>
       </c>
-      <c r="G51" t="s">
-        <v>17</v>
-      </c>
-      <c r="H51" t="s">
-        <v>50</v>
-      </c>
-      <c r="I51" t="s">
+      <c r="L51" t="s">
+        <v>16</v>
+      </c>
+      <c r="M51" t="s">
+        <v>16</v>
+      </c>
+      <c r="N51" t="s">
+        <v>16</v>
+      </c>
+      <c r="O51" t="s">
         <v>30</v>
-      </c>
-      <c r="J51" t="s">
-        <v>255</v>
-      </c>
-      <c r="K51" t="s">
-        <v>256</v>
-      </c>
-      <c r="L51" t="s">
-        <v>17</v>
-      </c>
-      <c r="M51" t="s">
-        <v>17</v>
-      </c>
-      <c r="N51" t="s">
-        <v>17</v>
-      </c>
-      <c r="O51" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>258</v>
+        <v>106</v>
       </c>
       <c r="B52" t="s">
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="C52" t="s">
-        <v>136</v>
+        <v>24</v>
       </c>
       <c r="D52" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F52" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="G52" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H52" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I52" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J52" t="s">
-        <v>259</v>
+        <v>107</v>
       </c>
       <c r="K52" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="L52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M52" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="N52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O52" t="s">
-        <v>260</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>261</v>
+        <v>110</v>
       </c>
       <c r="B53" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="C53" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="D53" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E53" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F53" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="G53" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="H53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I53" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J53" t="s">
-        <v>262</v>
+        <v>111</v>
       </c>
       <c r="K53" t="s">
-        <v>263</v>
+        <v>94</v>
       </c>
       <c r="L53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M53" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="N53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O53" t="s">
-        <v>264</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>265</v>
+        <v>160</v>
       </c>
       <c r="B54" t="s">
-        <v>235</v>
+        <v>23</v>
       </c>
       <c r="C54" t="s">
+        <v>24</v>
+      </c>
+      <c r="D54" t="s">
+        <v>25</v>
+      </c>
+      <c r="E54" t="s">
         <v>17</v>
       </c>
-      <c r="D54" t="s">
-        <v>17</v>
-      </c>
-      <c r="E54" t="s">
-        <v>18</v>
-      </c>
       <c r="F54" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G54" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="H54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I54" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J54" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="K54" t="s">
-        <v>232</v>
+        <v>29</v>
       </c>
       <c r="L54" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M54" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N54" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O54" t="s">
-        <v>266</v>
+        <v>162</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>267</v>
+        <v>163</v>
       </c>
       <c r="B55" t="s">
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="C55" t="s">
-        <v>136</v>
+        <v>24</v>
       </c>
       <c r="D55" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E55" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F55" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G55" t="s">
-        <v>268</v>
+        <v>37</v>
       </c>
       <c r="H55" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I55" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J55" t="s">
-        <v>227</v>
+        <v>164</v>
       </c>
       <c r="K55" t="s">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="L55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O55" t="s">
-        <v>269</v>
+        <v>166</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>270</v>
+        <v>197</v>
       </c>
       <c r="B56" t="s">
-        <v>217</v>
+        <v>23</v>
       </c>
       <c r="C56" t="s">
-        <v>185</v>
+        <v>24</v>
       </c>
       <c r="D56" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E56" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F56" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="G56" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="H56" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I56" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J56" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="K56" t="s">
-        <v>271</v>
+        <v>198</v>
       </c>
       <c r="L56" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M56" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N56" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O56" t="s">
-        <v>272</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>273</v>
+        <v>205</v>
       </c>
       <c r="B57" t="s">
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="C57" t="s">
-        <v>136</v>
+        <v>24</v>
       </c>
       <c r="D57" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E57" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F57" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G57" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="H57" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I57" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J57" t="s">
-        <v>259</v>
+        <v>206</v>
       </c>
       <c r="K57" t="s">
-        <v>274</v>
+        <v>85</v>
       </c>
       <c r="L57" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M57" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N57" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O57" t="s">
-        <v>275</v>
+        <v>207</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>276</v>
+        <v>223</v>
       </c>
       <c r="B58" t="s">
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="C58" t="s">
-        <v>136</v>
+        <v>24</v>
       </c>
       <c r="D58" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E58" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F58" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G58" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H58" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I58" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J58" t="s">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="K58" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
       <c r="L58" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M58" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N58" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O58" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>280</v>
+        <v>308</v>
       </c>
       <c r="B59" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="C59" t="s">
+        <v>24</v>
+      </c>
+      <c r="D59" t="s">
+        <v>25</v>
+      </c>
+      <c r="E59" t="s">
         <v>17</v>
       </c>
-      <c r="D59" t="s">
-        <v>17</v>
-      </c>
-      <c r="E59" t="s">
-        <v>38</v>
-      </c>
       <c r="F59" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G59" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="H59" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I59" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J59" t="s">
-        <v>281</v>
+        <v>309</v>
       </c>
       <c r="K59" t="s">
-        <v>282</v>
+        <v>54</v>
       </c>
       <c r="L59" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M59" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N59" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O59" t="s">
-        <v>283</v>
+        <v>310</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="B60" t="s">
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="C60" t="s">
-        <v>136</v>
+        <v>24</v>
       </c>
       <c r="D60" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E60" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F60" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G60" t="s">
-        <v>40</v>
+        <v>326</v>
       </c>
       <c r="H60" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I60" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J60" t="s">
-        <v>285</v>
+        <v>327</v>
       </c>
       <c r="K60" t="s">
-        <v>286</v>
+        <v>158</v>
       </c>
       <c r="L60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O60" t="s">
-        <v>287</v>
+        <v>328</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>288</v>
+        <v>336</v>
       </c>
       <c r="B61" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="C61" t="s">
-        <v>140</v>
+        <v>24</v>
       </c>
       <c r="D61" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E61" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F61" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="G61" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="H61" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I61" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J61" t="s">
-        <v>289</v>
+        <v>337</v>
       </c>
       <c r="K61" t="s">
-        <v>290</v>
+        <v>338</v>
       </c>
       <c r="L61" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M61" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="N61" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O61" t="s">
-        <v>291</v>
+        <v>339</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>292</v>
+        <v>373</v>
       </c>
       <c r="B62" t="s">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="C62" t="s">
-        <v>130</v>
+        <v>24</v>
       </c>
       <c r="D62" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="E62" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F62" t="s">
-        <v>186</v>
+        <v>115</v>
       </c>
       <c r="G62" t="s">
-        <v>40</v>
+        <v>374</v>
       </c>
       <c r="H62" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I62" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J62" t="s">
-        <v>293</v>
+        <v>256</v>
       </c>
       <c r="K62" t="s">
-        <v>92</v>
+        <v>375</v>
       </c>
       <c r="L62" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M62" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N62" t="s">
-        <v>294</v>
+        <v>16</v>
       </c>
       <c r="O62" t="s">
-        <v>295</v>
+        <v>376</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>296</v>
+        <v>390</v>
       </c>
       <c r="B63" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C63" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D63" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E63" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F63" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G63" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="H63" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I63" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="J63" t="s">
-        <v>297</v>
+        <v>391</v>
       </c>
       <c r="K63" t="s">
-        <v>23</v>
+        <v>158</v>
       </c>
       <c r="L63" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M63" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N63" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O63" t="s">
-        <v>298</v>
+        <v>392</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>299</v>
+        <v>393</v>
       </c>
       <c r="B64" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="C64" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="D64" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E64" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F64" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="G64" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H64" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I64" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J64" t="s">
-        <v>300</v>
+        <v>164</v>
       </c>
       <c r="K64" t="s">
-        <v>57</v>
+        <v>394</v>
       </c>
       <c r="L64" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M64" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N64" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O64" t="s">
-        <v>301</v>
+        <v>395</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>302</v>
+        <v>416</v>
       </c>
       <c r="B65" t="s">
-        <v>135</v>
+        <v>23</v>
       </c>
       <c r="C65" t="s">
-        <v>136</v>
+        <v>24</v>
       </c>
       <c r="D65" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E65" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F65" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G65" t="s">
-        <v>204</v>
+        <v>16</v>
       </c>
       <c r="H65" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I65" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J65" t="s">
-        <v>212</v>
+        <v>417</v>
       </c>
       <c r="K65" t="s">
-        <v>303</v>
+        <v>418</v>
       </c>
       <c r="L65" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M65" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N65" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O65" t="s">
-        <v>304</v>
+        <v>419</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>305</v>
+        <v>355</v>
       </c>
       <c r="B66" t="s">
+        <v>214</v>
+      </c>
+      <c r="C66" t="s">
+        <v>356</v>
+      </c>
+      <c r="D66" t="s">
         <v>35</v>
       </c>
-      <c r="C66" t="s">
-        <v>36</v>
-      </c>
-      <c r="D66" t="s">
-        <v>37</v>
-      </c>
       <c r="E66" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F66" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G66" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="H66" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I66" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="J66" t="s">
-        <v>306</v>
+        <v>357</v>
       </c>
       <c r="K66" t="s">
-        <v>132</v>
+        <v>358</v>
       </c>
       <c r="L66" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M66" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N66" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O66" t="s">
-        <v>307</v>
+        <v>359</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>308</v>
+        <v>42</v>
       </c>
       <c r="B67" t="s">
-        <v>217</v>
+        <v>43</v>
       </c>
       <c r="C67" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D67" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="E67" t="s">
+        <v>35</v>
+      </c>
+      <c r="F67" t="s">
+        <v>46</v>
+      </c>
+      <c r="G67" t="s">
+        <v>37</v>
+      </c>
+      <c r="H67" t="s">
+        <v>47</v>
+      </c>
+      <c r="I67" t="s">
         <v>38</v>
       </c>
-      <c r="F67" t="s">
-        <v>19</v>
-      </c>
-      <c r="G67" t="s">
-        <v>40</v>
-      </c>
-      <c r="H67" t="s">
-        <v>21</v>
-      </c>
-      <c r="I67" t="s">
-        <v>17</v>
-      </c>
       <c r="J67" t="s">
-        <v>309</v>
+        <v>48</v>
       </c>
       <c r="K67" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="L67" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M67" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N67" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O67" t="s">
-        <v>310</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>311</v>
+        <v>113</v>
       </c>
       <c r="B68" t="s">
-        <v>312</v>
+        <v>114</v>
       </c>
       <c r="C68" t="s">
-        <v>313</v>
+        <v>44</v>
       </c>
       <c r="D68" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E68" t="s">
+        <v>35</v>
+      </c>
+      <c r="F68" t="s">
+        <v>115</v>
+      </c>
+      <c r="G68" t="s">
+        <v>116</v>
+      </c>
+      <c r="H68" t="s">
+        <v>47</v>
+      </c>
+      <c r="I68" t="s">
         <v>38</v>
       </c>
-      <c r="F68" t="s">
-        <v>49</v>
-      </c>
-      <c r="G68" t="s">
-        <v>95</v>
-      </c>
-      <c r="H68" t="s">
-        <v>50</v>
-      </c>
-      <c r="I68" t="s">
-        <v>17</v>
-      </c>
       <c r="J68" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="K68" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="L68" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M68" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="N68" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O68" t="s">
-        <v>314</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>315</v>
+        <v>174</v>
       </c>
       <c r="B69" t="s">
-        <v>68</v>
+        <v>156</v>
       </c>
       <c r="C69" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="D69" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E69" t="s">
+        <v>35</v>
+      </c>
+      <c r="F69" t="s">
         <v>18</v>
       </c>
-      <c r="F69" t="s">
-        <v>186</v>
-      </c>
       <c r="G69" t="s">
-        <v>316</v>
+        <v>19</v>
       </c>
       <c r="H69" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I69" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="J69" t="s">
-        <v>317</v>
+        <v>175</v>
       </c>
       <c r="K69" t="s">
-        <v>188</v>
+        <v>104</v>
       </c>
       <c r="L69" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M69" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N69" t="s">
-        <v>318</v>
+        <v>16</v>
       </c>
       <c r="O69" t="s">
-        <v>319</v>
+        <v>176</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>320</v>
+        <v>131</v>
       </c>
       <c r="B70" t="s">
-        <v>26</v>
+        <v>132</v>
       </c>
       <c r="C70" t="s">
+        <v>133</v>
+      </c>
+      <c r="D70" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" t="s">
+        <v>17</v>
+      </c>
+      <c r="F70" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" t="s">
+        <v>37</v>
+      </c>
+      <c r="H70" t="s">
+        <v>20</v>
+      </c>
+      <c r="I70" t="s">
         <v>27</v>
       </c>
-      <c r="D70" t="s">
-        <v>28</v>
-      </c>
-      <c r="E70" t="s">
-        <v>18</v>
-      </c>
-      <c r="F70" t="s">
-        <v>29</v>
-      </c>
-      <c r="G70" t="s">
-        <v>17</v>
-      </c>
-      <c r="H70" t="s">
-        <v>21</v>
-      </c>
-      <c r="I70" t="s">
-        <v>30</v>
-      </c>
       <c r="J70" t="s">
-        <v>321</v>
+        <v>120</v>
       </c>
       <c r="K70" t="s">
-        <v>57</v>
+        <v>134</v>
       </c>
       <c r="L70" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M70" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N70" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O70" t="s">
-        <v>322</v>
+        <v>135</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>323</v>
+        <v>150</v>
       </c>
       <c r="B71" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="C71" t="s">
-        <v>324</v>
+        <v>133</v>
       </c>
       <c r="D71" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="E71" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F71" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="G71" t="s">
-        <v>40</v>
+        <v>151</v>
       </c>
       <c r="H71" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I71" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J71" t="s">
-        <v>101</v>
+        <v>152</v>
       </c>
       <c r="K71" t="s">
-        <v>325</v>
+        <v>153</v>
       </c>
       <c r="L71" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M71" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N71" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O71" t="s">
-        <v>326</v>
+        <v>154</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>327</v>
+        <v>200</v>
       </c>
       <c r="B72" t="s">
-        <v>328</v>
+        <v>132</v>
       </c>
       <c r="C72" t="s">
-        <v>329</v>
+        <v>133</v>
       </c>
       <c r="D72" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E72" t="s">
+        <v>17</v>
+      </c>
+      <c r="F72" t="s">
         <v>18</v>
       </c>
-      <c r="F72" t="s">
-        <v>19</v>
-      </c>
       <c r="G72" t="s">
-        <v>330</v>
+        <v>201</v>
       </c>
       <c r="H72" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I72" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J72" t="s">
-        <v>331</v>
+        <v>202</v>
       </c>
       <c r="K72" t="s">
-        <v>332</v>
+        <v>203</v>
       </c>
       <c r="L72" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M72" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N72" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O72" t="s">
-        <v>333</v>
+        <v>204</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>334</v>
+        <v>211</v>
       </c>
       <c r="B73" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="C73" t="s">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="D73" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E73" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F73" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="G73" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="H73" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I73" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J73" t="s">
-        <v>335</v>
+        <v>74</v>
       </c>
       <c r="K73" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="L73" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M73" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N73" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O73" t="s">
-        <v>336</v>
+        <v>212</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>337</v>
+        <v>255</v>
       </c>
       <c r="B74" t="s">
-        <v>26</v>
+        <v>132</v>
       </c>
       <c r="C74" t="s">
+        <v>133</v>
+      </c>
+      <c r="D74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E74" t="s">
+        <v>17</v>
+      </c>
+      <c r="F74" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" t="s">
+        <v>68</v>
+      </c>
+      <c r="H74" t="s">
+        <v>20</v>
+      </c>
+      <c r="I74" t="s">
         <v>27</v>
       </c>
-      <c r="D74" t="s">
-        <v>28</v>
-      </c>
-      <c r="E74" t="s">
-        <v>18</v>
-      </c>
-      <c r="F74" t="s">
-        <v>39</v>
-      </c>
-      <c r="G74" t="s">
-        <v>338</v>
-      </c>
-      <c r="H74" t="s">
-        <v>21</v>
-      </c>
-      <c r="I74" t="s">
-        <v>30</v>
-      </c>
       <c r="J74" t="s">
-        <v>339</v>
+        <v>256</v>
       </c>
       <c r="K74" t="s">
-        <v>161</v>
+        <v>75</v>
       </c>
       <c r="L74" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M74" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N74" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O74" t="s">
-        <v>340</v>
+        <v>257</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>341</v>
+        <v>262</v>
       </c>
       <c r="B75" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C75" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D75" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E75" t="s">
+        <v>17</v>
+      </c>
+      <c r="F75" t="s">
         <v>18</v>
       </c>
-      <c r="F75" t="s">
-        <v>39</v>
-      </c>
       <c r="G75" t="s">
-        <v>71</v>
+        <v>263</v>
       </c>
       <c r="H75" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I75" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J75" t="s">
-        <v>342</v>
+        <v>224</v>
       </c>
       <c r="K75" t="s">
-        <v>32</v>
+        <v>129</v>
       </c>
       <c r="L75" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M75" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N75" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O75" t="s">
-        <v>343</v>
+        <v>264</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>344</v>
+        <v>268</v>
       </c>
       <c r="B76" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C76" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D76" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E76" t="s">
+        <v>17</v>
+      </c>
+      <c r="F76" t="s">
         <v>18</v>
       </c>
-      <c r="F76" t="s">
-        <v>19</v>
-      </c>
       <c r="G76" t="s">
-        <v>345</v>
+        <v>37</v>
       </c>
       <c r="H76" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I76" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J76" t="s">
-        <v>346</v>
+        <v>256</v>
       </c>
       <c r="K76" t="s">
-        <v>88</v>
+        <v>269</v>
       </c>
       <c r="L76" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M76" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N76" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O76" t="s">
-        <v>347</v>
+        <v>270</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>348</v>
+        <v>271</v>
       </c>
       <c r="B77" t="s">
-        <v>26</v>
+        <v>132</v>
       </c>
       <c r="C77" t="s">
+        <v>133</v>
+      </c>
+      <c r="D77" t="s">
+        <v>25</v>
+      </c>
+      <c r="E77" t="s">
+        <v>17</v>
+      </c>
+      <c r="F77" t="s">
+        <v>36</v>
+      </c>
+      <c r="G77" t="s">
+        <v>19</v>
+      </c>
+      <c r="H77" t="s">
+        <v>20</v>
+      </c>
+      <c r="I77" t="s">
         <v>27</v>
       </c>
-      <c r="D77" t="s">
-        <v>28</v>
-      </c>
-      <c r="E77" t="s">
-        <v>18</v>
-      </c>
-      <c r="F77" t="s">
-        <v>29</v>
-      </c>
-      <c r="G77" t="s">
-        <v>17</v>
-      </c>
-      <c r="H77" t="s">
-        <v>21</v>
-      </c>
-      <c r="I77" t="s">
-        <v>30</v>
-      </c>
       <c r="J77" t="s">
-        <v>349</v>
+        <v>272</v>
       </c>
       <c r="K77" t="s">
-        <v>350</v>
+        <v>273</v>
       </c>
       <c r="L77" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M77" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N77" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O77" t="s">
-        <v>351</v>
+        <v>274</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>352</v>
+        <v>275</v>
       </c>
       <c r="B78" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C78" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D78" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E78" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F78" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G78" t="s">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="H78" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I78" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J78" t="s">
-        <v>353</v>
+        <v>276</v>
       </c>
       <c r="K78" t="s">
-        <v>232</v>
+        <v>277</v>
       </c>
       <c r="L78" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M78" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N78" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O78" t="s">
-        <v>354</v>
+        <v>278</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>355</v>
+        <v>293</v>
       </c>
       <c r="B79" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C79" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D79" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E79" t="s">
+        <v>17</v>
+      </c>
+      <c r="F79" t="s">
         <v>18</v>
       </c>
-      <c r="F79" t="s">
-        <v>19</v>
-      </c>
       <c r="G79" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H79" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I79" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J79" t="s">
-        <v>356</v>
+        <v>209</v>
       </c>
       <c r="K79" t="s">
-        <v>88</v>
+        <v>294</v>
       </c>
       <c r="L79" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M79" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N79" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O79" t="s">
-        <v>357</v>
+        <v>295</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="B80" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C80" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D80" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E80" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F80" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G80" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H80" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I80" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J80" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="K80" t="s">
-        <v>274</v>
+        <v>29</v>
       </c>
       <c r="L80" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M80" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N80" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O80" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>361</v>
+        <v>332</v>
       </c>
       <c r="B81" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="C81" t="s">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="D81" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E81" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F81" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="G81" t="s">
-        <v>20</v>
+        <v>333</v>
       </c>
       <c r="H81" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I81" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J81" t="s">
-        <v>362</v>
+        <v>334</v>
       </c>
       <c r="K81" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="L81" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M81" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N81" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O81" t="s">
-        <v>363</v>
+        <v>335</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="B82" t="s">
-        <v>235</v>
+        <v>132</v>
       </c>
       <c r="C82" t="s">
+        <v>133</v>
+      </c>
+      <c r="D82" t="s">
+        <v>25</v>
+      </c>
+      <c r="E82" t="s">
         <v>17</v>
       </c>
-      <c r="D82" t="s">
-        <v>17</v>
-      </c>
-      <c r="E82" t="s">
-        <v>18</v>
-      </c>
       <c r="F82" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G82" t="s">
-        <v>204</v>
+        <v>92</v>
       </c>
       <c r="H82" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I82" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J82" t="s">
-        <v>212</v>
+        <v>341</v>
       </c>
       <c r="K82" t="s">
-        <v>365</v>
+        <v>229</v>
       </c>
       <c r="L82" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M82" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N82" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O82" t="s">
-        <v>366</v>
+        <v>342</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="B83" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="C83" t="s">
-        <v>324</v>
+        <v>133</v>
       </c>
       <c r="D83" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="E83" t="s">
+        <v>17</v>
+      </c>
+      <c r="F83" t="s">
         <v>18</v>
       </c>
-      <c r="F83" t="s">
-        <v>19</v>
-      </c>
       <c r="G83" t="s">
-        <v>40</v>
+        <v>201</v>
       </c>
       <c r="H83" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I83" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J83" t="s">
-        <v>368</v>
+        <v>344</v>
       </c>
       <c r="K83" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L83" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M83" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N83" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O83" t="s">
-        <v>369</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="B84" t="s">
-        <v>217</v>
+        <v>132</v>
       </c>
       <c r="C84" t="s">
-        <v>371</v>
+        <v>133</v>
       </c>
       <c r="D84" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="E84" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F84" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G84" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="H84" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I84" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J84" t="s">
-        <v>372</v>
+        <v>347</v>
       </c>
       <c r="K84" t="s">
-        <v>373</v>
+        <v>269</v>
       </c>
       <c r="L84" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M84" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N84" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O84" t="s">
-        <v>374</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="B85" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="C85" t="s">
-        <v>324</v>
+        <v>133</v>
       </c>
       <c r="D85" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="E85" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F85" t="s">
-        <v>376</v>
+        <v>36</v>
       </c>
       <c r="G85" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="H85" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I85" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J85" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="K85" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="L85" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M85" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N85" t="s">
-        <v>379</v>
+        <v>16</v>
       </c>
       <c r="O85" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="B86" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C86" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D86" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E86" t="s">
+        <v>17</v>
+      </c>
+      <c r="F86" t="s">
         <v>18</v>
       </c>
-      <c r="F86" t="s">
-        <v>39</v>
-      </c>
       <c r="G86" t="s">
-        <v>382</v>
+        <v>68</v>
       </c>
       <c r="H86" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I86" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J86" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="K86" t="s">
-        <v>137</v>
+        <v>269</v>
       </c>
       <c r="L86" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M86" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N86" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O86" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="B87" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C87" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D87" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E87" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F87" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G87" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="H87" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I87" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J87" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="K87" t="s">
-        <v>274</v>
+        <v>94</v>
       </c>
       <c r="L87" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M87" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N87" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O87" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="B88" t="s">
-        <v>26</v>
+        <v>132</v>
       </c>
       <c r="C88" t="s">
+        <v>133</v>
+      </c>
+      <c r="D88" t="s">
+        <v>25</v>
+      </c>
+      <c r="E88" t="s">
+        <v>17</v>
+      </c>
+      <c r="F88" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" t="s">
+        <v>68</v>
+      </c>
+      <c r="H88" t="s">
+        <v>20</v>
+      </c>
+      <c r="I88" t="s">
         <v>27</v>
       </c>
-      <c r="D88" t="s">
-        <v>28</v>
-      </c>
-      <c r="E88" t="s">
-        <v>18</v>
-      </c>
-      <c r="F88" t="s">
-        <v>118</v>
-      </c>
-      <c r="G88" t="s">
-        <v>389</v>
-      </c>
-      <c r="H88" t="s">
-        <v>21</v>
-      </c>
-      <c r="I88" t="s">
-        <v>30</v>
-      </c>
       <c r="J88" t="s">
-        <v>259</v>
+        <v>405</v>
       </c>
       <c r="K88" t="s">
-        <v>390</v>
+        <v>260</v>
       </c>
       <c r="L88" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M88" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N88" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O88" t="s">
-        <v>391</v>
+        <v>406</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="B89" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="C89" t="s">
-        <v>324</v>
+        <v>133</v>
       </c>
       <c r="D89" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="E89" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F89" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G89" t="s">
-        <v>71</v>
+        <v>201</v>
       </c>
       <c r="H89" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I89" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J89" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="K89" t="s">
-        <v>196</v>
+        <v>79</v>
       </c>
       <c r="L89" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M89" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N89" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O89" t="s">
-        <v>394</v>
+        <v>415</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="B90" t="s">
-        <v>184</v>
+        <v>132</v>
       </c>
       <c r="C90" t="s">
-        <v>254</v>
+        <v>133</v>
       </c>
       <c r="D90" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E90" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F90" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="G90" t="s">
-        <v>40</v>
+        <v>147</v>
       </c>
       <c r="H90" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I90" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J90" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="K90" t="s">
-        <v>396</v>
+        <v>158</v>
       </c>
       <c r="L90" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M90" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N90" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O90" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>398</v>
+        <v>136</v>
       </c>
       <c r="B91" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C91" t="s">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="D91" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E91" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F91" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="G91" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H91" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I91" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J91" t="s">
-        <v>399</v>
+        <v>138</v>
       </c>
       <c r="K91" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="L91" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M91" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N91" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O91" t="s">
-        <v>400</v>
+        <v>140</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>401</v>
+        <v>141</v>
       </c>
       <c r="B92" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C92" t="s">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="D92" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E92" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="F92" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G92" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="H92" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I92" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J92" t="s">
-        <v>402</v>
+        <v>143</v>
       </c>
       <c r="K92" t="s">
-        <v>403</v>
+        <v>144</v>
       </c>
       <c r="L92" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M92" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N92" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O92" t="s">
-        <v>404</v>
+        <v>145</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>405</v>
+        <v>155</v>
       </c>
       <c r="B93" t="s">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="C93" t="s">
+        <v>137</v>
+      </c>
+      <c r="D93" t="s">
+        <v>25</v>
+      </c>
+      <c r="E93" t="s">
+        <v>35</v>
+      </c>
+      <c r="F93" t="s">
+        <v>18</v>
+      </c>
+      <c r="G93" t="s">
+        <v>37</v>
+      </c>
+      <c r="H93" t="s">
+        <v>20</v>
+      </c>
+      <c r="I93" t="s">
         <v>27</v>
       </c>
-      <c r="D93" t="s">
-        <v>28</v>
-      </c>
-      <c r="E93" t="s">
-        <v>18</v>
-      </c>
-      <c r="F93" t="s">
-        <v>29</v>
-      </c>
-      <c r="G93" t="s">
-        <v>17</v>
-      </c>
-      <c r="H93" t="s">
-        <v>21</v>
-      </c>
-      <c r="I93" t="s">
-        <v>30</v>
-      </c>
       <c r="J93" t="s">
-        <v>406</v>
+        <v>157</v>
       </c>
       <c r="K93" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="L93" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M93" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N93" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O93" t="s">
-        <v>407</v>
+        <v>159</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>408</v>
+        <v>279</v>
       </c>
       <c r="B94" t="s">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="C94" t="s">
+        <v>137</v>
+      </c>
+      <c r="D94" t="s">
+        <v>25</v>
+      </c>
+      <c r="E94" t="s">
         <v>17</v>
       </c>
-      <c r="D94" t="s">
-        <v>17</v>
-      </c>
-      <c r="E94" t="s">
-        <v>18</v>
-      </c>
       <c r="F94" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="G94" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="H94" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="I94" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J94" t="s">
-        <v>409</v>
+        <v>280</v>
       </c>
       <c r="K94" t="s">
-        <v>410</v>
+        <v>281</v>
       </c>
       <c r="L94" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M94" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="N94" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O94" t="s">
-        <v>411</v>
+        <v>282</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>412</v>
+        <v>303</v>
       </c>
       <c r="B95" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="C95" t="s">
+        <v>137</v>
+      </c>
+      <c r="D95" t="s">
+        <v>25</v>
+      </c>
+      <c r="E95" t="s">
+        <v>17</v>
+      </c>
+      <c r="F95" t="s">
+        <v>183</v>
+      </c>
+      <c r="G95" t="s">
+        <v>304</v>
+      </c>
+      <c r="H95" t="s">
+        <v>47</v>
+      </c>
+      <c r="I95" t="s">
         <v>27</v>
       </c>
-      <c r="D95" t="s">
-        <v>28</v>
-      </c>
-      <c r="E95" t="s">
-        <v>18</v>
-      </c>
-      <c r="F95" t="s">
-        <v>19</v>
-      </c>
-      <c r="G95" t="s">
-        <v>40</v>
-      </c>
-      <c r="H95" t="s">
-        <v>21</v>
-      </c>
-      <c r="I95" t="s">
-        <v>30</v>
-      </c>
       <c r="J95" t="s">
-        <v>167</v>
+        <v>305</v>
       </c>
       <c r="K95" t="s">
-        <v>413</v>
+        <v>185</v>
       </c>
       <c r="L95" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M95" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N95" t="s">
-        <v>17</v>
+        <v>306</v>
       </c>
       <c r="O95" t="s">
-        <v>414</v>
+        <v>307</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>415</v>
+        <v>81</v>
       </c>
       <c r="B96" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C96" t="s">
-        <v>324</v>
+        <v>83</v>
       </c>
       <c r="D96" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="E96" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F96" t="s">
-        <v>376</v>
+        <v>36</v>
       </c>
       <c r="G96" t="s">
-        <v>204</v>
+        <v>19</v>
       </c>
       <c r="H96" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I96" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J96" t="s">
-        <v>416</v>
+        <v>84</v>
       </c>
       <c r="K96" t="s">
-        <v>417</v>
+        <v>85</v>
       </c>
       <c r="L96" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M96" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N96" t="s">
-        <v>418</v>
+        <v>16</v>
       </c>
       <c r="O96" t="s">
-        <v>419</v>
+        <v>86</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>420</v>
+        <v>299</v>
       </c>
       <c r="B97" t="s">
-        <v>135</v>
+        <v>300</v>
       </c>
       <c r="C97" t="s">
-        <v>136</v>
+        <v>301</v>
       </c>
       <c r="D97" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E97" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F97" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G97" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="H97" t="s">
+        <v>47</v>
+      </c>
+      <c r="I97" t="s">
+        <v>16</v>
+      </c>
+      <c r="J97" t="s">
+        <v>120</v>
+      </c>
+      <c r="K97" t="s">
         <v>21</v>
       </c>
-      <c r="I97" t="s">
-        <v>30</v>
-      </c>
-      <c r="J97" t="s">
-        <v>421</v>
-      </c>
-      <c r="K97" t="s">
-        <v>97</v>
-      </c>
       <c r="L97" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M97" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="N97" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O97" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>423</v>
-      </c>
-      <c r="B98" t="s">
-        <v>135</v>
-      </c>
-      <c r="C98" t="s">
-        <v>136</v>
-      </c>
-      <c r="D98" t="s">
-        <v>28</v>
-      </c>
-      <c r="E98" t="s">
-        <v>18</v>
-      </c>
-      <c r="F98" t="s">
-        <v>19</v>
-      </c>
-      <c r="G98" t="s">
-        <v>71</v>
-      </c>
-      <c r="H98" t="s">
-        <v>21</v>
-      </c>
-      <c r="I98" t="s">
-        <v>30</v>
-      </c>
-      <c r="J98" t="s">
-        <v>424</v>
-      </c>
-      <c r="K98" t="s">
-        <v>263</v>
-      </c>
-      <c r="L98" t="s">
-        <v>17</v>
-      </c>
-      <c r="M98" t="s">
-        <v>17</v>
-      </c>
-      <c r="N98" t="s">
-        <v>17</v>
-      </c>
-      <c r="O98" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>426</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="s">
-        <v>427</v>
-      </c>
-      <c r="D99" t="s">
-        <v>428</v>
-      </c>
-      <c r="E99" t="s">
-        <v>18</v>
-      </c>
-      <c r="F99" t="s">
-        <v>39</v>
-      </c>
-      <c r="G99" t="s">
-        <v>429</v>
-      </c>
-      <c r="H99" t="s">
-        <v>21</v>
-      </c>
-      <c r="I99" t="s">
-        <v>41</v>
-      </c>
-      <c r="J99" t="s">
-        <v>205</v>
-      </c>
-      <c r="K99" t="s">
-        <v>430</v>
-      </c>
-      <c r="L99" t="s">
-        <v>17</v>
-      </c>
-      <c r="M99" t="s">
-        <v>17</v>
-      </c>
-      <c r="N99" t="s">
-        <v>17</v>
-      </c>
-      <c r="O99" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>432</v>
-      </c>
-      <c r="B100" t="s">
-        <v>135</v>
-      </c>
-      <c r="C100" t="s">
-        <v>136</v>
-      </c>
-      <c r="D100" t="s">
-        <v>28</v>
-      </c>
-      <c r="E100" t="s">
-        <v>18</v>
-      </c>
-      <c r="F100" t="s">
-        <v>39</v>
-      </c>
-      <c r="G100" t="s">
-        <v>204</v>
-      </c>
-      <c r="H100" t="s">
-        <v>21</v>
-      </c>
-      <c r="I100" t="s">
-        <v>30</v>
-      </c>
-      <c r="J100" t="s">
-        <v>433</v>
-      </c>
-      <c r="K100" t="s">
-        <v>82</v>
-      </c>
-      <c r="L100" t="s">
-        <v>17</v>
-      </c>
-      <c r="M100" t="s">
-        <v>17</v>
-      </c>
-      <c r="N100" t="s">
-        <v>17</v>
-      </c>
-      <c r="O100" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>435</v>
-      </c>
-      <c r="B101" t="s">
-        <v>26</v>
-      </c>
-      <c r="C101" t="s">
-        <v>27</v>
-      </c>
-      <c r="D101" t="s">
-        <v>28</v>
-      </c>
-      <c r="E101" t="s">
-        <v>18</v>
-      </c>
-      <c r="F101" t="s">
-        <v>29</v>
-      </c>
-      <c r="G101" t="s">
-        <v>17</v>
-      </c>
-      <c r="H101" t="s">
-        <v>21</v>
-      </c>
-      <c r="I101" t="s">
-        <v>30</v>
-      </c>
-      <c r="J101" t="s">
-        <v>436</v>
-      </c>
-      <c r="K101" t="s">
-        <v>437</v>
-      </c>
-      <c r="L101" t="s">
-        <v>17</v>
-      </c>
-      <c r="M101" t="s">
-        <v>17</v>
-      </c>
-      <c r="N101" t="s">
-        <v>17</v>
-      </c>
-      <c r="O101" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>439</v>
-      </c>
-      <c r="B102" t="s">
-        <v>129</v>
-      </c>
-      <c r="C102" t="s">
-        <v>17</v>
-      </c>
-      <c r="D102" t="s">
-        <v>17</v>
-      </c>
-      <c r="E102" t="s">
-        <v>18</v>
-      </c>
-      <c r="F102" t="s">
-        <v>19</v>
-      </c>
-      <c r="G102" t="s">
-        <v>55</v>
-      </c>
-      <c r="H102" t="s">
-        <v>21</v>
-      </c>
-      <c r="I102" t="s">
-        <v>17</v>
-      </c>
-      <c r="J102" t="s">
-        <v>440</v>
-      </c>
-      <c r="K102" t="s">
-        <v>396</v>
-      </c>
-      <c r="L102" t="s">
-        <v>17</v>
-      </c>
-      <c r="M102" t="s">
-        <v>17</v>
-      </c>
-      <c r="N102" t="s">
-        <v>17</v>
-      </c>
-      <c r="O102" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>442</v>
-      </c>
-      <c r="B103" t="s">
-        <v>129</v>
-      </c>
-      <c r="C103" t="s">
-        <v>17</v>
-      </c>
-      <c r="D103" t="s">
-        <v>17</v>
-      </c>
-      <c r="E103" t="s">
-        <v>18</v>
-      </c>
-      <c r="F103" t="s">
-        <v>39</v>
-      </c>
-      <c r="G103" t="s">
-        <v>40</v>
-      </c>
-      <c r="H103" t="s">
-        <v>21</v>
-      </c>
-      <c r="I103" t="s">
-        <v>17</v>
-      </c>
-      <c r="J103" t="s">
-        <v>443</v>
-      </c>
-      <c r="K103" t="s">
-        <v>444</v>
-      </c>
-      <c r="L103" t="s">
-        <v>17</v>
-      </c>
-      <c r="M103" t="s">
-        <v>17</v>
-      </c>
-      <c r="N103" t="s">
-        <v>17</v>
-      </c>
-      <c r="O103" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>446</v>
-      </c>
-      <c r="B104" t="s">
-        <v>105</v>
-      </c>
-      <c r="C104" t="s">
-        <v>254</v>
-      </c>
-      <c r="D104" t="s">
-        <v>37</v>
-      </c>
-      <c r="E104" t="s">
-        <v>38</v>
-      </c>
-      <c r="F104" t="s">
-        <v>63</v>
-      </c>
-      <c r="G104" t="s">
-        <v>55</v>
-      </c>
-      <c r="H104" t="s">
-        <v>50</v>
-      </c>
-      <c r="I104" t="s">
-        <v>30</v>
-      </c>
-      <c r="J104" t="s">
-        <v>447</v>
-      </c>
-      <c r="K104" t="s">
-        <v>250</v>
-      </c>
-      <c r="L104" t="s">
-        <v>17</v>
-      </c>
-      <c r="M104" t="s">
-        <v>17</v>
-      </c>
-      <c r="N104" t="s">
-        <v>17</v>
-      </c>
-      <c r="O104" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>449</v>
-      </c>
-      <c r="B105" t="s">
-        <v>135</v>
-      </c>
-      <c r="C105" t="s">
-        <v>136</v>
-      </c>
-      <c r="D105" t="s">
-        <v>28</v>
-      </c>
-      <c r="E105" t="s">
-        <v>18</v>
-      </c>
-      <c r="F105" t="s">
-        <v>19</v>
-      </c>
-      <c r="G105" t="s">
-        <v>150</v>
-      </c>
-      <c r="H105" t="s">
-        <v>21</v>
-      </c>
-      <c r="I105" t="s">
-        <v>30</v>
-      </c>
-      <c r="J105" t="s">
-        <v>356</v>
-      </c>
-      <c r="K105" t="s">
-        <v>161</v>
-      </c>
-      <c r="L105" t="s">
-        <v>17</v>
-      </c>
-      <c r="M105" t="s">
-        <v>17</v>
-      </c>
-      <c r="N105" t="s">
-        <v>17</v>
-      </c>
-      <c r="O105" t="s">
-        <v>450</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O97" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O97">
+      <sortCondition ref="C1:C97"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B1D9237-FE97-4204-AE7C-F101DB284119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDA9FD5D-BD47-47DB-B8B0-B7CA35DA114D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1215" windowWidth="21930" windowHeight="14985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3330" yWindow="3330" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="401">
   <si>
     <t>Time</t>
   </si>
@@ -62,51 +62,273 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>06/18/2026 4:34:01 PM</t>
+  </si>
+  <si>
+    <t>680 - Medium</t>
+  </si>
+  <si>
+    <t>Jesus Carbajal</t>
+  </si>
+  <si>
+    <t>Active Drivers, Towing and Recovery</t>
+  </si>
+  <si>
+    <t>HAAS Alert, Towing and Recovery</t>
+  </si>
+  <si>
+    <t>Obstructed Camera</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>Tim Neff Jr.</t>
+  </si>
+  <si>
+    <t>Interstate 10 South Frontage Road, Beaumont, TX, 77702</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445dca7-bd7e-50f6-b2da-d0e7f3669228</t>
+  </si>
+  <si>
+    <t>06/18/2026 8:05:45 AM</t>
+  </si>
+  <si>
+    <t>685 - Medium</t>
+  </si>
+  <si>
+    <t>Christopher Marcantel</t>
+  </si>
+  <si>
+    <t>Towing and Recovery</t>
+  </si>
+  <si>
+    <t>Severe Speeding</t>
+  </si>
+  <si>
+    <t>Speed Sign Verified</t>
+  </si>
+  <si>
+    <t>I 10, Winnie, TX</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445dad6-6838-50e1-a08f-721a3f1f36df</t>
+  </si>
+  <si>
+    <t>06/17/2026 5:02:17 PM</t>
+  </si>
+  <si>
+    <t>683 - Heavy</t>
+  </si>
+  <si>
+    <t>Dwayne Manuel</t>
+  </si>
+  <si>
+    <t>Active Drivers, Heavy Haul</t>
+  </si>
+  <si>
+    <t>HAAS Alert, Heavy Haul</t>
+  </si>
+  <si>
+    <t>Mobile Usage</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>H O Mills Highway, Port Arthur, TX</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d79b-44e0-5b5f-afa1-10741c645e86</t>
+  </si>
+  <si>
+    <t>06/17/2026 11:28:09 AM</t>
+  </si>
+  <si>
+    <t>Inattentive Driving</t>
+  </si>
+  <si>
+    <t>College Street, Beaumont, TX, 77702</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d669-5d00-570d-892c-3b3bcb44e34d</t>
+  </si>
+  <si>
+    <t>06/15/2026 5:53:31 PM</t>
+  </si>
+  <si>
+    <t>5230 North Major Drive, Beaumont, TX, 77705</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cd7d-73a6-51c3-baf6-41a38469fe10</t>
+  </si>
+  <si>
+    <t>06/15/2026 1:23:54 PM</t>
+  </si>
+  <si>
+    <t>669 - Heavy</t>
+  </si>
+  <si>
+    <t>Jason Walker</t>
+  </si>
+  <si>
+    <t>Wet Road, Light Traffic, Raining</t>
+  </si>
+  <si>
+    <t>State Highway 326, Sour Lake, TX, 77659</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cc86-9c64-5c62-a497-759c62f256a9</t>
+  </si>
+  <si>
+    <t>06/14/2026 11:39:04 AM</t>
+  </si>
+  <si>
+    <t>Coached</t>
+  </si>
+  <si>
+    <t>State Highway 124, Hamshire, TX, 77622</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c700-47f3-56b1-b136-8c61392947bb</t>
+  </si>
+  <si>
+    <t>06/14/2026 9:48:42 AM</t>
+  </si>
+  <si>
+    <t>644 - Medium</t>
+  </si>
+  <si>
+    <t>Paul Kunze Jr</t>
+  </si>
+  <si>
+    <t>Fannett Road, Beaumont, TX, 77705</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c69b-3b3b-50b6-9299-c5f9408304d6</t>
+  </si>
+  <si>
+    <t>06/14/2026 12:03:26 AM</t>
+  </si>
+  <si>
+    <t>FM 365, 9.6 mi WSW Nederland, Jefferson County, TX</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c483-6560-5f24-a5a4-1196fcf0710d</t>
+  </si>
+  <si>
+    <t>06/13/2026 5:24:44 PM</t>
+  </si>
+  <si>
+    <t>Fannett Road, Beaumont, TX, 77701</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c316-622e-5089-9af0-e3644e669122</t>
+  </si>
+  <si>
+    <t>06/13/2026 4:18:06 PM</t>
+  </si>
+  <si>
+    <t>Moderate Traffic</t>
+  </si>
+  <si>
+    <t>East Freeway, Channelview, TX, 77530</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c2d9-604f-59f0-87e5-6a5c05c198bc</t>
+  </si>
+  <si>
+    <t>06/12/2026 9:27:53 AM</t>
+  </si>
+  <si>
+    <t>North Dorman Road, 4.8 mi NNE Bridge City, Orange County, TX, 77630</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bc3b-756c-5d9e-9d81-2830d4d259b7</t>
+  </si>
+  <si>
+    <t>06/12/2026 7:39:02 AM</t>
+  </si>
+  <si>
+    <t>Dupont Drive, West Orange, TX, 77630</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bbd7-ce4d-5d05-b19f-5787bf9d3e6c</t>
+  </si>
+  <si>
+    <t>06/12/2026 7:17:24 AM</t>
+  </si>
+  <si>
+    <t>TX 73, Port Arthur, TX, 77640</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bbc3-fc20-5357-b19e-8917e5854b0b</t>
+  </si>
+  <si>
+    <t>06/12/2026 2:36:49 AM</t>
+  </si>
+  <si>
+    <t>I 10, Beaumont, TX, 77705</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bac3-1a90-5376-b4c0-879059363b9a</t>
+  </si>
+  <si>
     <t>06/11/2026 10:09:35 PM</t>
   </si>
   <si>
-    <t>680 - Medium</t>
-  </si>
-  <si>
-    <t>Jesus Carbajal</t>
-  </si>
-  <si>
-    <t>Active Drivers, Towing and Recovery</t>
-  </si>
-  <si>
-    <t>HAAS Alert, Towing and Recovery</t>
-  </si>
-  <si>
     <t>Drowsiness</t>
   </si>
   <si>
     <t>Moderately Drowsy, Light Traffic, Night</t>
   </si>
   <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
-    <t>Tim Neff Jr.</t>
-  </si>
-  <si>
-    <t>Fannett Road, Beaumont, TX, 77705</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b9ce-7522-5e34-bee1-b027d6f0c003</t>
   </si>
   <si>
     <t>06/10/2026 4:50:31 PM</t>
   </si>
   <si>
-    <t>Severe Speeding</t>
-  </si>
-  <si>
     <t>State Route 109, Starks, LA</t>
   </si>
   <si>
@@ -116,9 +338,6 @@
     <t>19</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b383-f8ee-57b2-b3a2-576df0f3920d</t>
   </si>
   <si>
@@ -131,15 +350,6 @@
     <t>Thomas Neff III</t>
   </si>
   <si>
-    <t>HAAS Alert, Heavy Haul</t>
-  </si>
-  <si>
-    <t>Mobile Usage</t>
-  </si>
-  <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
     <t>5020 Fannett Road, Beaumont, TX, 77705</t>
   </si>
   <si>
@@ -164,12 +374,6 @@
     <t>Following Distance</t>
   </si>
   <si>
-    <t>Moderate Traffic</t>
-  </si>
-  <si>
-    <t>Coached</t>
-  </si>
-  <si>
     <t>Eddie Bowden</t>
   </si>
   <si>
@@ -203,18 +407,9 @@
     <t>06/04/2026 2:15:03 PM</t>
   </si>
   <si>
-    <t>644 - Medium</t>
-  </si>
-  <si>
     <t>Wet Road, Light Traffic</t>
   </si>
   <si>
-    <t>Fannett Road, Beaumont, TX, 77701</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445940f-7e14-5c0f-aa68-07d221d9e214</t>
   </si>
   <si>
@@ -227,9 +422,6 @@
     <t>Gary Worley</t>
   </si>
   <si>
-    <t>Active Drivers, Heavy Haul</t>
-  </si>
-  <si>
     <t>No Seat Belt</t>
   </si>
   <si>
@@ -245,9 +437,6 @@
     <t>692 - Heavy</t>
   </si>
   <si>
-    <t>Inattentive Driving</t>
-  </si>
-  <si>
     <t>I 10, Seguin, TX, 78638</t>
   </si>
   <si>
@@ -260,9 +449,6 @@
     <t>05/28/2026 4:24:20 PM</t>
   </si>
   <si>
-    <t>College Street, Beaumont, TX, 77702</t>
-  </si>
-  <si>
     <t>30</t>
   </si>
   <si>
@@ -290,15 +476,6 @@
     <t>05/28/2026 12:14:01 AM</t>
   </si>
   <si>
-    <t>685 - Medium</t>
-  </si>
-  <si>
-    <t>Christopher Marcantel</t>
-  </si>
-  <si>
-    <t>Towing and Recovery</t>
-  </si>
-  <si>
     <t>Light Traffic, Night</t>
   </si>
   <si>
@@ -311,15 +488,6 @@
     <t>05/23/2026 10:35:24 AM</t>
   </si>
   <si>
-    <t>669 - Heavy</t>
-  </si>
-  <si>
-    <t>Jason Walker</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445557a-13c8-58c7-91dd-c320f5c8cfc4</t>
   </si>
   <si>
@@ -329,9 +497,6 @@
     <t>2706 Irving Avenue, Beaumont, TX, 77701</t>
   </si>
   <si>
-    <t>39</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445487c-7266-58c3-95b0-bb9b5182787c</t>
   </si>
   <si>
@@ -356,9 +521,6 @@
     <t>36</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445432b-c0f7-5407-ab0e-1be086171464</t>
   </si>
   <si>
@@ -482,9 +644,6 @@
     <t>658 - Medium</t>
   </si>
   <si>
-    <t>Paul Kunze Jr</t>
-  </si>
-  <si>
     <t>44</t>
   </si>
   <si>
@@ -509,15 +668,9 @@
     <t>05/01/2026 6:20:21 PM</t>
   </si>
   <si>
-    <t>Wet Road, Light Traffic, Raining</t>
-  </si>
-  <si>
     <t>FM 366, Groves, TX, 77651</t>
   </si>
   <si>
-    <t>35</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e5d7-d728-50d0-8a79-285ccb21062a</t>
   </si>
   <si>
@@ -575,9 +728,6 @@
     <t>12.8 mi SW Beaumont, Jefferson County, TX</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d13d-b4f6-5a82-bd3b-3d99bfc16a01</t>
   </si>
   <si>
@@ -671,9 +821,6 @@
     <t>04/20/2026 10:49:13 AM</t>
   </si>
   <si>
-    <t>Obstructed Camera</t>
-  </si>
-  <si>
     <t>56</t>
   </si>
   <si>
@@ -776,9 +923,6 @@
     <t>668 - Light</t>
   </si>
   <si>
-    <t>Dwayne Manuel</t>
-  </si>
-  <si>
     <t>East Freeway, Houston, TX, 77020</t>
   </si>
   <si>
@@ -800,9 +944,6 @@
     <t>04/10/2026 6:09:04 AM</t>
   </si>
   <si>
-    <t>683 - Heavy</t>
-  </si>
-  <si>
     <t>Jason Leleaux</t>
   </si>
   <si>
@@ -845,9 +986,6 @@
     <t>04/07/2026 10:15:48 PM</t>
   </si>
   <si>
-    <t>I 10, Beaumont, TX, 77705</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456b16-c772-5c6b-bb09-e92039e34f7c</t>
   </si>
   <si>
@@ -974,9 +1112,6 @@
     <t>03/31/2026 7:05:40 PM</t>
   </si>
   <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445465c-3230-53bd-9134-409c7545bd21</t>
   </si>
   <si>
@@ -1083,183 +1218,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451fd5-3fbc-5ac1-96f4-67459813149f</t>
-  </si>
-  <si>
-    <t>03/22/2026 9:37:51 PM</t>
-  </si>
-  <si>
-    <t>214 Patna Drive, 10.4 mi W Beaumont, Jefferson County, TX, 77713</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445188e-4a89-5038-95c0-80ab04e32fd7</t>
-  </si>
-  <si>
-    <t>03/22/2026 9:18:57 PM</t>
-  </si>
-  <si>
-    <t>Passengers, Light Traffic, Night</t>
-  </si>
-  <si>
-    <t>10491 Old Sour Lake Road, 7.2 mi W Beaumont, Jefferson County, TX, 77713</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445187c-fcb2-50ce-aad8-1e15f2e9017e</t>
-  </si>
-  <si>
-    <t>03/21/2026 6:27:09 PM</t>
-  </si>
-  <si>
-    <t>2420 Wescalder Road, Beaumont, TX, 77707</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544512b9-5827-53fe-b13d-86d6ba6f8bfb</t>
-  </si>
-  <si>
-    <t>03/20/2026 12:33:43 PM</t>
-  </si>
-  <si>
-    <t>7184 Fannett Road, Beaumont, TX, 77705</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450c4f-680f-5b6f-afb9-ccfcd3041935</t>
-  </si>
-  <si>
-    <t>03/20/2026 8:57:34 AM</t>
-  </si>
-  <si>
-    <t>South I-10 Frontage Road, Beaumont, TX, 77705</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450b89-838e-5be0-bf1d-8df08398544a</t>
-  </si>
-  <si>
-    <t>03/19/2026 10:53:11 PM</t>
-  </si>
-  <si>
-    <t>East Freeway, Channelview, TX, 77530</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450960-2e19-5128-bc45-73715420fda0</t>
-  </si>
-  <si>
-    <t>03/19/2026 7:09:48 PM</t>
-  </si>
-  <si>
-    <t>Pinewood Boulevard, 11.1 mi SW Lumberton, Hardin County, TX, 77659</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450893-aabf-5818-9db3-afc50f70f5ed</t>
-  </si>
-  <si>
-    <t>03/19/2026 11:18:44 AM</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544506e4-630c-59b3-88ae-741798ff874c</t>
-  </si>
-  <si>
-    <t>03/18/2026 4:44:25 PM</t>
-  </si>
-  <si>
-    <t>3029 TX 87, Newton, TX, 75966</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544502e8-358e-57ff-9d4c-94dbbff97f08</t>
-  </si>
-  <si>
-    <t>03/18/2026 2:16:22 PM</t>
-  </si>
-  <si>
-    <t>Jonathan Walters</t>
-  </si>
-  <si>
-    <t>5205 South Boudoin Road, Calcasieu Parish, LA, 70665</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450260-a909-53ce-9d38-d69da7866e49</t>
-  </si>
-  <si>
-    <t>03/18/2026 1:23:19 PM</t>
-  </si>
-  <si>
-    <t>Harsh Turn</t>
-  </si>
-  <si>
-    <t>Pedestrians, Moderate Traffic</t>
-  </si>
-  <si>
-    <t>South I-10 Frontage Road, Beaumont, TX, 77702</t>
-  </si>
-  <si>
-    <t>0.54</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450230-1977-56d5-aef9-6acd8216bfbc</t>
-  </si>
-  <si>
-    <t>03/18/2026 6:09:02 AM</t>
-  </si>
-  <si>
-    <t>Parking Lot, Light Traffic, Night</t>
-  </si>
-  <si>
-    <t>5321 Walden Road, Beaumont, TX, 77705</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544500a2-8018-5d6f-ae1d-56e0df4523b7</t>
-  </si>
-  <si>
-    <t>03/17/2026 8:39:10 PM</t>
-  </si>
-  <si>
-    <t>South Sam Houston Tollway East, Houston, TX, 77048</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fe98-c2e1-53c7-af85-7ddd56e544e9</t>
-  </si>
-  <si>
-    <t>03/17/2026 3:42:27 AM</t>
-  </si>
-  <si>
-    <t>Slightly Drowsy, Light Traffic, Night</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445faf5-ef7a-5cf8-8c44-9a03e9e68ec3</t>
-  </si>
-  <si>
-    <t>03/16/2026 8:49:23 PM</t>
-  </si>
-  <si>
-    <t>Farm to Market Road 363, Kirbyville, TX, 75956</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f97b-c1cc-5dd2-aafa-07cf63494074</t>
-  </si>
-  <si>
-    <t>03/16/2026 6:25:17 PM</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f8f7-d4ef-526d-9093-4b7be0bae0b0</t>
-  </si>
-  <si>
-    <t>03/16/2026 7:41:03 AM</t>
-  </si>
-  <si>
-    <t>I-10 Frontage Road, 23.5 mi SW Beaumont, Jefferson County, TX, 77665</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f6aa-0357-54bc-82c3-ffcf0eb0e5df</t>
   </si>
 </sst>
 </file>
@@ -1636,7 +1594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O95"/>
+  <dimension ref="A1:O93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1721,86 +1679,86 @@
         <v>25</v>
       </c>
       <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2" t="s">
         <v>26</v>
-      </c>
-      <c r="M2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H3" t="s">
         <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H4" t="s">
         <v>22</v>
@@ -1809,80 +1767,80 @@
         <v>23</v>
       </c>
       <c r="J4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
         <v>44</v>
       </c>
-      <c r="B5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G5" t="s">
-        <v>49</v>
-      </c>
       <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" t="s">
         <v>50</v>
       </c>
-      <c r="I5" t="s">
+      <c r="K5" t="s">
         <v>51</v>
       </c>
-      <c r="J5" t="s">
+      <c r="L5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" t="s">
         <v>52</v>
       </c>
-      <c r="K5" t="s">
+      <c r="N5" t="s">
+        <v>21</v>
+      </c>
+      <c r="O5" t="s">
         <v>53</v>
-      </c>
-      <c r="L5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" t="s">
-        <v>26</v>
-      </c>
-      <c r="O5" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
@@ -1891,10 +1849,10 @@
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H6" t="s">
         <v>22</v>
@@ -1903,327 +1861,327 @@
         <v>23</v>
       </c>
       <c r="J6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="K6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" t="s">
         <v>61</v>
-      </c>
-      <c r="B7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" t="s">
-        <v>63</v>
       </c>
       <c r="H7" t="s">
         <v>22</v>
       </c>
       <c r="I7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K7" t="s">
+        <v>63</v>
+      </c>
+      <c r="L7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7" t="s">
         <v>64</v>
-      </c>
-      <c r="K7" t="s">
-        <v>65</v>
-      </c>
-      <c r="L7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" t="s">
         <v>67</v>
       </c>
-      <c r="B8" t="s">
+      <c r="K8" t="s">
         <v>68</v>
       </c>
-      <c r="C8" t="s">
+      <c r="L8" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" t="s">
+        <v>21</v>
+      </c>
+      <c r="N8" t="s">
+        <v>21</v>
+      </c>
+      <c r="O8" t="s">
         <v>69</v>
-      </c>
-      <c r="D8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" t="s">
-        <v>51</v>
-      </c>
-      <c r="J8" t="s">
-        <v>72</v>
-      </c>
-      <c r="K8" t="s">
-        <v>42</v>
-      </c>
-      <c r="L8" t="s">
-        <v>26</v>
-      </c>
-      <c r="M8" t="s">
-        <v>26</v>
-      </c>
-      <c r="N8" t="s">
-        <v>26</v>
-      </c>
-      <c r="O8" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" t="s">
+        <v>73</v>
+      </c>
+      <c r="K9" t="s">
+        <v>46</v>
+      </c>
+      <c r="L9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O9" t="s">
         <v>74</v>
-      </c>
-      <c r="B9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9" t="s">
-        <v>51</v>
-      </c>
-      <c r="J9" t="s">
-        <v>77</v>
-      </c>
-      <c r="K9" t="s">
-        <v>78</v>
-      </c>
-      <c r="L9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O9" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="G10" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="H10" t="s">
         <v>22</v>
       </c>
       <c r="I10" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="J10" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="K10" t="s">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="L10" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M10" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O10" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H11" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I11" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J11" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="K11" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="L11" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M11" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N11" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O11" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G12" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H12" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I12" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J12" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K12" t="s">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="L12" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M12" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="N12" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O12" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="G13" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
@@ -2232,92 +2190,92 @@
         <v>23</v>
       </c>
       <c r="J13" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="K13" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="L13" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M13" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N13" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O13" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>94</v>
+        <v>21</v>
       </c>
       <c r="H14" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="I14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J14" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="K14" t="s">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="L14" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M14" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N14" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O14" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="G15" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="H15" t="s">
         <v>22</v>
@@ -2326,268 +2284,268 @@
         <v>23</v>
       </c>
       <c r="J15" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="K15" t="s">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="L15" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M15" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N15" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O15" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="G16" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="H16" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="I16" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J16" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="K16" t="s">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="L16" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M16" t="s">
-        <v>113</v>
+        <v>36</v>
       </c>
       <c r="N16" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O16" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="E17" t="s">
         <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="G17" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="H17" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="I17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J17" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="K17" t="s">
-        <v>118</v>
+        <v>51</v>
       </c>
       <c r="L17" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M17" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N17" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O17" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="E18" t="s">
         <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="G18" t="s">
-        <v>121</v>
+        <v>21</v>
       </c>
       <c r="H18" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="I18" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J18" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="K18" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="L18" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="M18" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N18" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O18" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="B19" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F19" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="G19" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H19" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="I19" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="J19" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="K19" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="L19" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M19" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N19" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O19" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>115</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>116</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="G20" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I20" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
       <c r="J20" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="K20" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="L20" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M20" t="s">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="N20" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O20" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>125</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
@@ -2596,10 +2554,10 @@
         <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="G21" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="H21" t="s">
         <v>22</v>
@@ -2608,327 +2566,327 @@
         <v>23</v>
       </c>
       <c r="J21" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="K21" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="L21" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M21" t="s">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="N21" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O21" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" t="s">
+        <v>130</v>
+      </c>
+      <c r="H22" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s">
+        <v>79</v>
+      </c>
+      <c r="K22" t="s">
         <v>46</v>
       </c>
-      <c r="D22" t="s">
-        <v>47</v>
-      </c>
-      <c r="E22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" t="s">
-        <v>138</v>
-      </c>
-      <c r="H22" t="s">
-        <v>50</v>
-      </c>
-      <c r="I22" t="s">
-        <v>51</v>
-      </c>
-      <c r="J22" t="s">
-        <v>139</v>
-      </c>
-      <c r="K22" t="s">
-        <v>88</v>
-      </c>
       <c r="L22" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M22" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N22" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O22" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="D23" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="E23" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F23" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="G23" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H23" t="s">
         <v>22</v>
       </c>
       <c r="I23" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
       <c r="J23" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="K23" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="L23" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M23" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N23" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O23" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>139</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="D24" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="E24" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F24" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="G24" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H24" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I24" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="J24" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="K24" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="L24" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M24" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N24" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O24" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B25" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C25" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="D25" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="E25" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F25" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="G25" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="H25" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" t="s">
+        <v>119</v>
+      </c>
+      <c r="J25" t="s">
         <v>50</v>
       </c>
-      <c r="I25" t="s">
-        <v>26</v>
-      </c>
-      <c r="J25" t="s">
-        <v>150</v>
-      </c>
       <c r="K25" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="L25" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M25" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N25" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O25" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B26" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C26" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D26" t="s">
-        <v>18</v>
+        <v>149</v>
       </c>
       <c r="E26" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F26" t="s">
-        <v>39</v>
+        <v>118</v>
       </c>
       <c r="G26" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H26" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J26" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="K26" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="L26" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M26" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N26" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O26" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="C27" t="s">
-        <v>159</v>
+        <v>29</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G27" t="s">
-        <v>63</v>
+        <v>153</v>
       </c>
       <c r="H27" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J27" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="K27" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="L27" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M27" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N27" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O27" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="C28" t="s">
-        <v>159</v>
+        <v>60</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
       </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F28" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="G28" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="H28" t="s">
         <v>22</v>
@@ -2937,92 +2895,92 @@
         <v>23</v>
       </c>
       <c r="J28" t="s">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="K28" t="s">
-        <v>166</v>
+        <v>84</v>
       </c>
       <c r="L28" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M28" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N28" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O28" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="D29" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="E29" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F29" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="G29" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="H29" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I29" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="J29" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="K29" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="L29" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M29" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N29" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O29" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="B30" t="s">
-        <v>154</v>
+        <v>109</v>
       </c>
       <c r="C30" t="s">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
       </c>
       <c r="E30" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F30" t="s">
-        <v>20</v>
+        <v>135</v>
       </c>
       <c r="G30" t="s">
-        <v>173</v>
+        <v>130</v>
       </c>
       <c r="H30" t="s">
         <v>22</v>
@@ -3031,233 +2989,233 @@
         <v>23</v>
       </c>
       <c r="J30" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="K30" t="s">
-        <v>32</v>
+        <v>163</v>
       </c>
       <c r="L30" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M30" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N30" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O30" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="B31" t="s">
-        <v>177</v>
+        <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>159</v>
+        <v>29</v>
       </c>
       <c r="D31" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E31" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G31" t="s">
-        <v>40</v>
+        <v>153</v>
       </c>
       <c r="H31" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I31" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J31" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="K31" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="L31" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M31" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="N31" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O31" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="B32" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D32" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
       </c>
       <c r="F32" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="G32" t="s">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="H32" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I32" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J32" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="K32" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
       <c r="L32" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M32" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N32" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O32" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="B33" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C33" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D33" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
       </c>
       <c r="F33" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="G33" t="s">
-        <v>40</v>
+        <v>175</v>
       </c>
       <c r="H33" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I33" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J33" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="K33" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="L33" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M33" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N33" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O33" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>180</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="D34" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="E34" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F34" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="G34" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="H34" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I34" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
       <c r="J34" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="K34" t="s">
-        <v>65</v>
+        <v>182</v>
       </c>
       <c r="L34" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M34" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N34" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O34" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
       </c>
       <c r="E35" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F35" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="G35" t="s">
-        <v>40</v>
+        <v>153</v>
       </c>
       <c r="H35" t="s">
         <v>22</v>
@@ -3266,315 +3224,315 @@
         <v>23</v>
       </c>
       <c r="J35" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="K35" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="L35" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M35" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="N35" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O35" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B36" t="s">
-        <v>177</v>
+        <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="D36" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="E36" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F36" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G36" t="s">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="H36" t="s">
         <v>22</v>
       </c>
       <c r="I36" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="J36" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="K36" t="s">
-        <v>128</v>
+        <v>172</v>
       </c>
       <c r="L36" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M36" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="N36" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O36" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C37" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D37" t="s">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="E37" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F37" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="G37" t="s">
-        <v>40</v>
+        <v>192</v>
       </c>
       <c r="H37" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I37" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
       <c r="J37" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="K37" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="L37" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M37" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N37" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O37" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B38" t="s">
-        <v>202</v>
+        <v>59</v>
       </c>
       <c r="C38" t="s">
-        <v>203</v>
+        <v>60</v>
       </c>
       <c r="D38" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E38" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F38" t="s">
-        <v>204</v>
+        <v>135</v>
       </c>
       <c r="G38" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H38" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="I38" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J38" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="K38" t="s">
-        <v>206</v>
+        <v>177</v>
       </c>
       <c r="L38" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M38" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N38" t="s">
-        <v>207</v>
+        <v>21</v>
       </c>
       <c r="O38" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="B39" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="C39" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
       <c r="D39" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="E39" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F39" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="G39" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H39" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I39" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="J39" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="K39" t="s">
-        <v>53</v>
+        <v>167</v>
       </c>
       <c r="L39" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M39" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N39" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O39" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B40" t="s">
-        <v>98</v>
+        <v>202</v>
       </c>
       <c r="C40" t="s">
-        <v>99</v>
+        <v>203</v>
       </c>
       <c r="D40" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E40" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>39</v>
+        <v>135</v>
       </c>
       <c r="G40" t="s">
-        <v>164</v>
+        <v>44</v>
       </c>
       <c r="H40" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I40" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J40" t="s">
-        <v>139</v>
+        <v>204</v>
       </c>
       <c r="K40" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="L40" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M40" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N40" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O40" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B41" t="s">
-        <v>68</v>
+        <v>208</v>
       </c>
       <c r="C41" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D41" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E41" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="G41" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="H41" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="I41" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="J41" t="s">
-        <v>142</v>
+        <v>196</v>
       </c>
       <c r="K41" t="s">
-        <v>42</v>
+        <v>209</v>
       </c>
       <c r="L41" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M41" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N41" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O41" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B42" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C42" t="s">
-        <v>17</v>
+        <v>212</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -3583,10 +3541,10 @@
         <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>218</v>
+        <v>43</v>
       </c>
       <c r="G42" t="s">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="H42" t="s">
         <v>22</v>
@@ -3595,33 +3553,33 @@
         <v>23</v>
       </c>
       <c r="J42" t="s">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="K42" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="L42" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M42" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N42" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O42" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B43" t="s">
-        <v>154</v>
+        <v>28</v>
       </c>
       <c r="C43" t="s">
-        <v>155</v>
+        <v>212</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -3630,10 +3588,10 @@
         <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>39</v>
+        <v>135</v>
       </c>
       <c r="G43" t="s">
-        <v>222</v>
+        <v>61</v>
       </c>
       <c r="H43" t="s">
         <v>22</v>
@@ -3642,92 +3600,92 @@
         <v>23</v>
       </c>
       <c r="J43" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="K43" t="s">
-        <v>224</v>
+        <v>56</v>
       </c>
       <c r="L43" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M43" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N43" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O43" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B44" t="s">
-        <v>16</v>
+        <v>133</v>
       </c>
       <c r="C44" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="D44" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="E44" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F44" t="s">
-        <v>218</v>
+        <v>135</v>
       </c>
       <c r="G44" t="s">
-        <v>26</v>
+        <v>220</v>
       </c>
       <c r="H44" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I44" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
       <c r="J44" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="K44" t="s">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="L44" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M44" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N44" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O44" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B45" t="s">
-        <v>98</v>
+        <v>208</v>
       </c>
       <c r="C45" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
       </c>
       <c r="E45" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="G45" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H45" t="s">
         <v>22</v>
@@ -3736,45 +3694,45 @@
         <v>23</v>
       </c>
       <c r="J45" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="K45" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="L45" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M45" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N45" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O45" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B46" t="s">
-        <v>154</v>
+        <v>228</v>
       </c>
       <c r="C46" t="s">
-        <v>155</v>
+        <v>212</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
       </c>
       <c r="E46" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F46" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G46" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="H46" t="s">
         <v>22</v>
@@ -3783,139 +3741,139 @@
         <v>23</v>
       </c>
       <c r="J46" t="s">
-        <v>24</v>
+        <v>229</v>
       </c>
       <c r="K46" t="s">
-        <v>186</v>
+        <v>230</v>
       </c>
       <c r="L46" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M46" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N46" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O46" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B47" t="s">
-        <v>235</v>
+        <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>203</v>
+        <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E47" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>204</v>
+        <v>135</v>
       </c>
       <c r="G47" t="s">
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="H47" t="s">
         <v>22</v>
       </c>
       <c r="I47" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J47" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="K47" t="s">
-        <v>33</v>
+        <v>167</v>
       </c>
       <c r="L47" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M47" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N47" t="s">
-        <v>237</v>
+        <v>21</v>
       </c>
       <c r="O47" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B48" t="s">
-        <v>235</v>
+        <v>16</v>
       </c>
       <c r="C48" t="s">
-        <v>203</v>
+        <v>17</v>
       </c>
       <c r="D48" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E48" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F48" t="s">
-        <v>204</v>
+        <v>135</v>
       </c>
       <c r="G48" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H48" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="I48" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J48" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="K48" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L48" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M48" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N48" t="s">
-        <v>241</v>
+        <v>21</v>
       </c>
       <c r="O48" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B49" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="C49" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="D49" t="s">
         <v>18</v>
       </c>
       <c r="E49" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F49" t="s">
-        <v>218</v>
+        <v>135</v>
       </c>
       <c r="G49" t="s">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="H49" t="s">
         <v>22</v>
@@ -3924,45 +3882,45 @@
         <v>23</v>
       </c>
       <c r="J49" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="K49" t="s">
-        <v>245</v>
+        <v>46</v>
       </c>
       <c r="L49" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M49" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N49" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O49" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B50" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="C50" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="D50" t="s">
         <v>18</v>
       </c>
       <c r="E50" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F50" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="G50" t="s">
-        <v>222</v>
+        <v>44</v>
       </c>
       <c r="H50" t="s">
         <v>22</v>
@@ -3971,327 +3929,327 @@
         <v>23</v>
       </c>
       <c r="J50" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="K50" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="L50" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M50" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N50" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O50" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B51" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="C51" t="s">
-        <v>253</v>
+        <v>116</v>
       </c>
       <c r="D51" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="E51" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F51" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G51" t="s">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="H51" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="I51" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
       <c r="J51" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="K51" t="s">
-        <v>100</v>
+        <v>182</v>
       </c>
       <c r="L51" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M51" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N51" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O51" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B52" t="s">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="C52" t="s">
-        <v>149</v>
+        <v>60</v>
       </c>
       <c r="D52" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="E52" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F52" t="s">
-        <v>39</v>
+        <v>135</v>
       </c>
       <c r="G52" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H52" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="I52" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J52" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="K52" t="s">
-        <v>258</v>
+        <v>182</v>
       </c>
       <c r="L52" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M52" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N52" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O52" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="B53" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="C53" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="D53" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E53" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F53" t="s">
-        <v>39</v>
+        <v>254</v>
       </c>
       <c r="G53" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I53" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J53" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="K53" t="s">
-        <v>104</v>
+        <v>256</v>
       </c>
       <c r="L53" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M53" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N53" t="s">
-        <v>26</v>
+        <v>257</v>
       </c>
       <c r="O53" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B54" t="s">
+        <v>133</v>
+      </c>
+      <c r="C54" t="s">
+        <v>134</v>
+      </c>
+      <c r="D54" t="s">
+        <v>41</v>
+      </c>
+      <c r="E54" t="s">
+        <v>42</v>
+      </c>
+      <c r="F54" t="s">
+        <v>135</v>
+      </c>
+      <c r="G54" t="s">
+        <v>82</v>
+      </c>
+      <c r="H54" t="s">
+        <v>66</v>
+      </c>
+      <c r="I54" t="s">
+        <v>119</v>
+      </c>
+      <c r="J54" t="s">
+        <v>260</v>
+      </c>
+      <c r="K54" t="s">
+        <v>121</v>
+      </c>
+      <c r="L54" t="s">
+        <v>21</v>
+      </c>
+      <c r="M54" t="s">
+        <v>21</v>
+      </c>
+      <c r="N54" t="s">
+        <v>21</v>
+      </c>
+      <c r="O54" t="s">
         <v>261</v>
-      </c>
-      <c r="C54" t="s">
-        <v>262</v>
-      </c>
-      <c r="D54" t="s">
-        <v>38</v>
-      </c>
-      <c r="E54" t="s">
-        <v>38</v>
-      </c>
-      <c r="F54" t="s">
-        <v>71</v>
-      </c>
-      <c r="G54" t="s">
-        <v>94</v>
-      </c>
-      <c r="H54" t="s">
-        <v>50</v>
-      </c>
-      <c r="I54" t="s">
-        <v>26</v>
-      </c>
-      <c r="J54" t="s">
-        <v>266</v>
-      </c>
-      <c r="K54" t="s">
-        <v>267</v>
-      </c>
-      <c r="L54" t="s">
-        <v>26</v>
-      </c>
-      <c r="M54" t="s">
-        <v>26</v>
-      </c>
-      <c r="N54" t="s">
-        <v>26</v>
-      </c>
-      <c r="O54" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B55" t="s">
-        <v>270</v>
+        <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>271</v>
+        <v>60</v>
       </c>
       <c r="D55" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E55" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F55" t="s">
-        <v>218</v>
+        <v>43</v>
       </c>
       <c r="G55" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="H55" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="I55" t="s">
         <v>23</v>
       </c>
       <c r="J55" t="s">
-        <v>272</v>
+        <v>193</v>
       </c>
       <c r="K55" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="L55" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M55" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N55" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O55" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="B56" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="C56" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="D56" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="E56" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F56" t="s">
-        <v>39</v>
+        <v>135</v>
       </c>
       <c r="G56" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="H56" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I56" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
       <c r="J56" t="s">
-        <v>276</v>
+        <v>196</v>
       </c>
       <c r="K56" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="L56" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M56" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N56" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O56" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="B57" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C57" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="D57" t="s">
         <v>18</v>
       </c>
       <c r="E57" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F57" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="G57" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="H57" t="s">
         <v>22</v>
@@ -4300,80 +4258,80 @@
         <v>23</v>
       </c>
       <c r="J57" t="s">
-        <v>279</v>
+        <v>221</v>
       </c>
       <c r="K57" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="L57" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M57" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N57" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O57" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="B58" t="s">
-        <v>252</v>
+        <v>208</v>
       </c>
       <c r="C58" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="D58" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E58" t="s">
         <v>19</v>
       </c>
       <c r="F58" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G58" t="s">
-        <v>40</v>
+        <v>271</v>
       </c>
       <c r="H58" t="s">
         <v>22</v>
       </c>
       <c r="I58" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J58" t="s">
-        <v>170</v>
+        <v>272</v>
       </c>
       <c r="K58" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="L58" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M58" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N58" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O58" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B59" t="s">
-        <v>154</v>
+        <v>16</v>
       </c>
       <c r="C59" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -4382,10 +4340,10 @@
         <v>19</v>
       </c>
       <c r="F59" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="G59" t="s">
-        <v>285</v>
+        <v>21</v>
       </c>
       <c r="H59" t="s">
         <v>22</v>
@@ -4394,80 +4352,80 @@
         <v>23</v>
       </c>
       <c r="J59" t="s">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="K59" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="L59" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M59" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N59" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O59" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="B60" t="s">
-        <v>235</v>
+        <v>59</v>
       </c>
       <c r="C60" t="s">
-        <v>203</v>
+        <v>60</v>
       </c>
       <c r="D60" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E60" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F60" t="s">
-        <v>48</v>
+        <v>135</v>
       </c>
       <c r="G60" t="s">
-        <v>49</v>
+        <v>271</v>
       </c>
       <c r="H60" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="I60" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J60" t="s">
-        <v>139</v>
+        <v>279</v>
       </c>
       <c r="K60" t="s">
-        <v>31</v>
+        <v>177</v>
       </c>
       <c r="L60" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M60" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N60" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O60" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="B61" t="s">
-        <v>154</v>
+        <v>208</v>
       </c>
       <c r="C61" t="s">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="D61" t="s">
         <v>18</v>
@@ -4476,10 +4434,10 @@
         <v>19</v>
       </c>
       <c r="F61" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G61" t="s">
-        <v>40</v>
+        <v>153</v>
       </c>
       <c r="H61" t="s">
         <v>22</v>
@@ -4488,127 +4446,127 @@
         <v>23</v>
       </c>
       <c r="J61" t="s">
-        <v>276</v>
+        <v>73</v>
       </c>
       <c r="K61" t="s">
-        <v>290</v>
+        <v>35</v>
       </c>
       <c r="L61" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M61" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N61" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O61" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B62" t="s">
-        <v>154</v>
+        <v>284</v>
       </c>
       <c r="C62" t="s">
-        <v>155</v>
+        <v>253</v>
       </c>
       <c r="D62" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="E62" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F62" t="s">
-        <v>71</v>
+        <v>254</v>
       </c>
       <c r="G62" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="H62" t="s">
         <v>22</v>
       </c>
       <c r="I62" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J62" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="K62" t="s">
-        <v>294</v>
+        <v>36</v>
       </c>
       <c r="L62" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M62" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N62" t="s">
-        <v>26</v>
+        <v>286</v>
       </c>
       <c r="O62" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="B63" t="s">
-        <v>36</v>
+        <v>284</v>
       </c>
       <c r="C63" t="s">
-        <v>26</v>
+        <v>253</v>
       </c>
       <c r="D63" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="E63" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F63" t="s">
-        <v>39</v>
+        <v>254</v>
       </c>
       <c r="G63" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H63" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I63" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J63" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="K63" t="s">
-        <v>298</v>
+        <v>106</v>
       </c>
       <c r="L63" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M63" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N63" t="s">
-        <v>26</v>
+        <v>290</v>
       </c>
       <c r="O63" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="B64" t="s">
-        <v>154</v>
+        <v>16</v>
       </c>
       <c r="C64" t="s">
-        <v>155</v>
+        <v>17</v>
       </c>
       <c r="D64" t="s">
         <v>18</v>
@@ -4617,10 +4575,10 @@
         <v>19</v>
       </c>
       <c r="F64" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="G64" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="H64" t="s">
         <v>22</v>
@@ -4629,456 +4587,456 @@
         <v>23</v>
       </c>
       <c r="J64" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="K64" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="L64" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M64" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N64" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O64" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="B65" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="C65" t="s">
-        <v>159</v>
+        <v>60</v>
       </c>
       <c r="D65" t="s">
         <v>18</v>
       </c>
       <c r="E65" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F65" t="s">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="G65" t="s">
-        <v>40</v>
+        <v>271</v>
       </c>
       <c r="H65" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="I65" t="s">
         <v>23</v>
       </c>
       <c r="J65" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="K65" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="L65" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M65" t="s">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="N65" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O65" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="B66" t="s">
-        <v>148</v>
+        <v>301</v>
       </c>
       <c r="C66" t="s">
-        <v>149</v>
+        <v>40</v>
       </c>
       <c r="D66" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="E66" t="s">
         <v>19</v>
       </c>
       <c r="F66" t="s">
-        <v>204</v>
+        <v>43</v>
       </c>
       <c r="G66" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H66" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I66" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J66" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="K66" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="L66" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M66" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N66" t="s">
-        <v>310</v>
+        <v>21</v>
       </c>
       <c r="O66" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="B67" t="s">
-        <v>68</v>
+        <v>202</v>
       </c>
       <c r="C67" t="s">
-        <v>69</v>
+        <v>203</v>
       </c>
       <c r="D67" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="E67" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F67" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="G67" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H67" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I67" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="J67" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="K67" t="s">
-        <v>65</v>
+        <v>306</v>
       </c>
       <c r="L67" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M67" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N67" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O67" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B68" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="C68" t="s">
-        <v>99</v>
+        <v>309</v>
       </c>
       <c r="D68" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="E68" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F68" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="G68" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H68" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I68" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J68" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="K68" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="L68" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M68" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N68" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O68" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B69" t="s">
-        <v>154</v>
+        <v>39</v>
       </c>
       <c r="C69" t="s">
-        <v>155</v>
+        <v>309</v>
       </c>
       <c r="D69" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="E69" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F69" t="s">
-        <v>39</v>
+        <v>135</v>
       </c>
       <c r="G69" t="s">
-        <v>222</v>
+        <v>153</v>
       </c>
       <c r="H69" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I69" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J69" t="s">
-        <v>230</v>
+        <v>313</v>
       </c>
       <c r="K69" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="L69" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M69" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N69" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O69" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>316</v>
+      </c>
+      <c r="B70" t="s">
+        <v>317</v>
+      </c>
+      <c r="C70" t="s">
+        <v>318</v>
+      </c>
+      <c r="D70" t="s">
+        <v>41</v>
+      </c>
+      <c r="E70" t="s">
+        <v>42</v>
+      </c>
+      <c r="F70" t="s">
+        <v>20</v>
+      </c>
+      <c r="G70" t="s">
+        <v>21</v>
+      </c>
+      <c r="H70" t="s">
+        <v>66</v>
+      </c>
+      <c r="I70" t="s">
+        <v>23</v>
+      </c>
+      <c r="J70" t="s">
+        <v>319</v>
+      </c>
+      <c r="K70" t="s">
+        <v>320</v>
+      </c>
+      <c r="L70" t="s">
+        <v>21</v>
+      </c>
+      <c r="M70" t="s">
+        <v>21</v>
+      </c>
+      <c r="N70" t="s">
+        <v>21</v>
+      </c>
+      <c r="O70" t="s">
         <v>321</v>
-      </c>
-      <c r="B70" t="s">
-        <v>68</v>
-      </c>
-      <c r="C70" t="s">
-        <v>69</v>
-      </c>
-      <c r="D70" t="s">
-        <v>70</v>
-      </c>
-      <c r="E70" t="s">
-        <v>38</v>
-      </c>
-      <c r="F70" t="s">
-        <v>71</v>
-      </c>
-      <c r="G70" t="s">
-        <v>40</v>
-      </c>
-      <c r="H70" t="s">
-        <v>50</v>
-      </c>
-      <c r="I70" t="s">
-        <v>51</v>
-      </c>
-      <c r="J70" t="s">
-        <v>322</v>
-      </c>
-      <c r="K70" t="s">
-        <v>151</v>
-      </c>
-      <c r="L70" t="s">
-        <v>26</v>
-      </c>
-      <c r="M70" t="s">
-        <v>26</v>
-      </c>
-      <c r="N70" t="s">
-        <v>26</v>
-      </c>
-      <c r="O70" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B71" t="s">
-        <v>235</v>
+        <v>208</v>
       </c>
       <c r="C71" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="D71" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E71" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F71" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G71" t="s">
-        <v>40</v>
+        <v>153</v>
       </c>
       <c r="H71" t="s">
         <v>22</v>
       </c>
       <c r="I71" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J71" t="s">
-        <v>325</v>
+        <v>97</v>
       </c>
       <c r="K71" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L71" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M71" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N71" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O71" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B72" t="s">
-        <v>328</v>
+        <v>59</v>
       </c>
       <c r="C72" t="s">
-        <v>329</v>
+        <v>60</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
       </c>
       <c r="E72" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F72" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="G72" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="H72" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="I72" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J72" t="s">
-        <v>142</v>
+        <v>325</v>
       </c>
       <c r="K72" t="s">
-        <v>65</v>
+        <v>326</v>
       </c>
       <c r="L72" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M72" t="s">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="N72" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O72" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B73" t="s">
-        <v>91</v>
+        <v>301</v>
       </c>
       <c r="C73" t="s">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="D73" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E73" t="s">
         <v>19</v>
       </c>
       <c r="F73" t="s">
-        <v>204</v>
+        <v>43</v>
       </c>
       <c r="G73" t="s">
-        <v>332</v>
+        <v>44</v>
       </c>
       <c r="H73" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="I73" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J73" t="s">
-        <v>333</v>
+        <v>221</v>
       </c>
       <c r="K73" t="s">
-        <v>206</v>
+        <v>298</v>
       </c>
       <c r="L73" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M73" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N73" t="s">
-        <v>334</v>
+        <v>21</v>
       </c>
       <c r="O73" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B74" t="s">
-        <v>16</v>
+        <v>208</v>
       </c>
       <c r="C74" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
@@ -5087,10 +5045,10 @@
         <v>19</v>
       </c>
       <c r="F74" t="s">
-        <v>218</v>
+        <v>43</v>
       </c>
       <c r="G74" t="s">
-        <v>26</v>
+        <v>331</v>
       </c>
       <c r="H74" t="s">
         <v>22</v>
@@ -5099,80 +5057,80 @@
         <v>23</v>
       </c>
       <c r="J74" t="s">
-        <v>337</v>
+        <v>293</v>
       </c>
       <c r="K74" t="s">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="L74" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M74" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N74" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O74" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B75" t="s">
-        <v>91</v>
+        <v>284</v>
       </c>
       <c r="C75" t="s">
-        <v>340</v>
+        <v>253</v>
       </c>
       <c r="D75" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="E75" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F75" t="s">
-        <v>39</v>
+        <v>118</v>
       </c>
       <c r="G75" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="H75" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I75" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J75" t="s">
-        <v>122</v>
+        <v>193</v>
       </c>
       <c r="K75" t="s">
-        <v>341</v>
+        <v>105</v>
       </c>
       <c r="L75" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M75" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N75" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O75" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B76" t="s">
-        <v>344</v>
+        <v>208</v>
       </c>
       <c r="C76" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="D76" t="s">
         <v>18</v>
@@ -5181,10 +5139,10 @@
         <v>19</v>
       </c>
       <c r="F76" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G76" t="s">
-        <v>345</v>
+        <v>44</v>
       </c>
       <c r="H76" t="s">
         <v>22</v>
@@ -5193,45 +5151,45 @@
         <v>23</v>
       </c>
       <c r="J76" t="s">
-        <v>346</v>
+        <v>97</v>
       </c>
       <c r="K76" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="L76" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M76" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N76" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O76" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="B77" t="s">
-        <v>98</v>
+        <v>208</v>
       </c>
       <c r="C77" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="D77" t="s">
         <v>18</v>
       </c>
       <c r="E77" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F77" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="G77" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="H77" t="s">
         <v>22</v>
@@ -5240,80 +5198,80 @@
         <v>23</v>
       </c>
       <c r="J77" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="K77" t="s">
-        <v>166</v>
+        <v>340</v>
       </c>
       <c r="L77" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M77" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N77" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O77" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="B78" t="s">
-        <v>16</v>
+        <v>109</v>
       </c>
       <c r="C78" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D78" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E78" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F78" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="G78" t="s">
-        <v>353</v>
+        <v>44</v>
       </c>
       <c r="H78" t="s">
         <v>22</v>
       </c>
       <c r="I78" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J78" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="K78" t="s">
-        <v>179</v>
+        <v>344</v>
       </c>
       <c r="L78" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M78" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N78" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O78" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="B79" t="s">
-        <v>154</v>
+        <v>208</v>
       </c>
       <c r="C79" t="s">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="D79" t="s">
         <v>18</v>
@@ -5322,10 +5280,10 @@
         <v>19</v>
       </c>
       <c r="F79" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="G79" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="H79" t="s">
         <v>22</v>
@@ -5334,33 +5292,33 @@
         <v>23</v>
       </c>
       <c r="J79" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="K79" t="s">
-        <v>112</v>
+        <v>348</v>
       </c>
       <c r="L79" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M79" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N79" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O79" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B80" t="s">
-        <v>154</v>
+        <v>28</v>
       </c>
       <c r="C80" t="s">
-        <v>155</v>
+        <v>212</v>
       </c>
       <c r="D80" t="s">
         <v>18</v>
@@ -5369,151 +5327,151 @@
         <v>19</v>
       </c>
       <c r="F80" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G80" t="s">
-        <v>360</v>
+        <v>44</v>
       </c>
       <c r="H80" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I80" t="s">
         <v>23</v>
       </c>
       <c r="J80" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="K80" t="s">
-        <v>108</v>
+        <v>352</v>
       </c>
       <c r="L80" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M80" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="N80" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O80" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="B81" t="s">
-        <v>16</v>
+        <v>202</v>
       </c>
       <c r="C81" t="s">
-        <v>17</v>
+        <v>203</v>
       </c>
       <c r="D81" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E81" t="s">
         <v>19</v>
       </c>
       <c r="F81" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="G81" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="H81" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I81" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J81" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="K81" t="s">
-        <v>365</v>
+        <v>52</v>
       </c>
       <c r="L81" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M81" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N81" t="s">
-        <v>26</v>
+        <v>356</v>
       </c>
       <c r="O81" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="B82" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="C82" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="D82" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="E82" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F82" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="G82" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="H82" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I82" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
       <c r="J82" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="K82" t="s">
-        <v>249</v>
+        <v>46</v>
       </c>
       <c r="L82" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M82" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N82" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O82" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="B83" t="s">
-        <v>154</v>
+        <v>59</v>
       </c>
       <c r="C83" t="s">
-        <v>155</v>
+        <v>60</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
       </c>
       <c r="E83" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F83" t="s">
-        <v>39</v>
+        <v>135</v>
       </c>
       <c r="G83" t="s">
-        <v>222</v>
+        <v>44</v>
       </c>
       <c r="H83" t="s">
         <v>22</v>
@@ -5522,33 +5480,33 @@
         <v>23</v>
       </c>
       <c r="J83" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="K83" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="L83" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M83" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N83" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O83" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="B84" t="s">
-        <v>154</v>
+        <v>208</v>
       </c>
       <c r="C84" t="s">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="D84" t="s">
         <v>18</v>
@@ -5557,10 +5515,10 @@
         <v>19</v>
       </c>
       <c r="F84" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G84" t="s">
-        <v>94</v>
+        <v>271</v>
       </c>
       <c r="H84" t="s">
         <v>22</v>
@@ -5569,315 +5527,315 @@
         <v>23</v>
       </c>
       <c r="J84" t="s">
-        <v>374</v>
+        <v>279</v>
       </c>
       <c r="K84" t="s">
-        <v>290</v>
+        <v>25</v>
       </c>
       <c r="L84" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M84" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N84" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O84" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="B85" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="C85" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="D85" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="E85" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F85" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="G85" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="H85" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I85" t="s">
-        <v>23</v>
+        <v>119</v>
       </c>
       <c r="J85" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="K85" t="s">
-        <v>65</v>
+        <v>205</v>
       </c>
       <c r="L85" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M85" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N85" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O85" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="B86" t="s">
-        <v>252</v>
+        <v>284</v>
       </c>
       <c r="C86" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D86" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E86" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F86" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G86" t="s">
-        <v>222</v>
+        <v>44</v>
       </c>
       <c r="H86" t="s">
         <v>22</v>
       </c>
       <c r="I86" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J86" t="s">
-        <v>230</v>
+        <v>370</v>
       </c>
       <c r="K86" t="s">
-        <v>380</v>
+        <v>150</v>
       </c>
       <c r="L86" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M86" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N86" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O86" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="B87" t="s">
-        <v>91</v>
+        <v>373</v>
       </c>
       <c r="C87" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="D87" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="E87" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F87" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G87" t="s">
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="H87" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="I87" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J87" t="s">
-        <v>383</v>
+        <v>196</v>
       </c>
       <c r="K87" t="s">
-        <v>123</v>
+        <v>46</v>
       </c>
       <c r="L87" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M87" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="N87" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O87" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="B88" t="s">
-        <v>235</v>
+        <v>28</v>
       </c>
       <c r="C88" t="s">
-        <v>386</v>
+        <v>212</v>
       </c>
       <c r="D88" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E88" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F88" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="G88" t="s">
-        <v>26</v>
+        <v>377</v>
       </c>
       <c r="H88" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I88" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J88" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="K88" t="s">
-        <v>25</v>
+        <v>256</v>
       </c>
       <c r="L88" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M88" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N88" t="s">
-        <v>26</v>
+        <v>379</v>
       </c>
       <c r="O88" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="B89" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="C89" t="s">
-        <v>340</v>
+        <v>17</v>
       </c>
       <c r="D89" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="E89" t="s">
         <v>19</v>
       </c>
       <c r="F89" t="s">
-        <v>390</v>
+        <v>20</v>
       </c>
       <c r="G89" t="s">
-        <v>391</v>
+        <v>21</v>
       </c>
       <c r="H89" t="s">
         <v>22</v>
       </c>
       <c r="I89" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J89" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="K89" t="s">
-        <v>186</v>
+        <v>144</v>
       </c>
       <c r="L89" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M89" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N89" t="s">
-        <v>393</v>
+        <v>21</v>
       </c>
       <c r="O89" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="B90" t="s">
-        <v>154</v>
+        <v>28</v>
       </c>
       <c r="C90" t="s">
-        <v>155</v>
+        <v>385</v>
       </c>
       <c r="D90" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E90" t="s">
         <v>19</v>
       </c>
       <c r="F90" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="G90" t="s">
-        <v>396</v>
+        <v>44</v>
       </c>
       <c r="H90" t="s">
         <v>22</v>
       </c>
       <c r="I90" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J90" t="s">
-        <v>397</v>
+        <v>176</v>
       </c>
       <c r="K90" t="s">
-        <v>156</v>
+        <v>386</v>
       </c>
       <c r="L90" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M90" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N90" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O90" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="B91" t="s">
-        <v>154</v>
+        <v>389</v>
       </c>
       <c r="C91" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="D91" t="s">
         <v>18</v>
@@ -5886,10 +5844,10 @@
         <v>19</v>
       </c>
       <c r="F91" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G91" t="s">
-        <v>94</v>
+        <v>390</v>
       </c>
       <c r="H91" t="s">
         <v>22</v>
@@ -5898,45 +5856,45 @@
         <v>23</v>
       </c>
       <c r="J91" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="K91" t="s">
-        <v>290</v>
+        <v>392</v>
       </c>
       <c r="L91" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M91" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N91" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O91" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="B92" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="C92" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="D92" t="s">
         <v>18</v>
       </c>
       <c r="E92" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="F92" t="s">
-        <v>20</v>
+        <v>135</v>
       </c>
       <c r="G92" t="s">
-        <v>403</v>
+        <v>170</v>
       </c>
       <c r="H92" t="s">
         <v>22</v>
@@ -5945,163 +5903,69 @@
         <v>23</v>
       </c>
       <c r="J92" t="s">
-        <v>276</v>
+        <v>395</v>
       </c>
       <c r="K92" t="s">
-        <v>404</v>
+        <v>56</v>
       </c>
       <c r="L92" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M92" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N92" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O92" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="B93" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="C93" t="s">
-        <v>340</v>
+        <v>17</v>
       </c>
       <c r="D93" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="E93" t="s">
         <v>19</v>
       </c>
       <c r="F93" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="G93" t="s">
-        <v>94</v>
+        <v>398</v>
       </c>
       <c r="H93" t="s">
         <v>22</v>
       </c>
       <c r="I93" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J93" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="K93" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="L93" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M93" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N93" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O93" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>409</v>
-      </c>
-      <c r="B94" t="s">
-        <v>202</v>
-      </c>
-      <c r="C94" t="s">
-        <v>271</v>
-      </c>
-      <c r="D94" t="s">
-        <v>70</v>
-      </c>
-      <c r="E94" t="s">
-        <v>38</v>
-      </c>
-      <c r="F94" t="s">
-        <v>48</v>
-      </c>
-      <c r="G94" t="s">
-        <v>40</v>
-      </c>
-      <c r="H94" t="s">
-        <v>50</v>
-      </c>
-      <c r="I94" t="s">
-        <v>23</v>
-      </c>
-      <c r="J94" t="s">
-        <v>350</v>
-      </c>
-      <c r="K94" t="s">
-        <v>410</v>
-      </c>
-      <c r="L94" t="s">
-        <v>26</v>
-      </c>
-      <c r="M94" t="s">
-        <v>26</v>
-      </c>
-      <c r="N94" t="s">
-        <v>26</v>
-      </c>
-      <c r="O94" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>412</v>
-      </c>
-      <c r="B95" t="s">
-        <v>98</v>
-      </c>
-      <c r="C95" t="s">
-        <v>99</v>
-      </c>
-      <c r="D95" t="s">
-        <v>18</v>
-      </c>
-      <c r="E95" t="s">
-        <v>38</v>
-      </c>
-      <c r="F95" t="s">
-        <v>71</v>
-      </c>
-      <c r="G95" t="s">
-        <v>63</v>
-      </c>
-      <c r="H95" t="s">
-        <v>22</v>
-      </c>
-      <c r="I95" t="s">
-        <v>23</v>
-      </c>
-      <c r="J95" t="s">
-        <v>413</v>
-      </c>
-      <c r="K95" t="s">
-        <v>82</v>
-      </c>
-      <c r="L95" t="s">
-        <v>26</v>
-      </c>
-      <c r="M95" t="s">
-        <v>26</v>
-      </c>
-      <c r="N95" t="s">
-        <v>26</v>
-      </c>
-      <c r="O95" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDA9FD5D-BD47-47DB-B8B0-B7CA35DA114D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEA9338F-6BCA-45F9-BC62-13CB330C2C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3330" yWindow="3330" windowWidth="43200" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1395" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="410">
   <si>
     <t>Time</t>
   </si>
@@ -62,33 +62,186 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>06/25/2026 4:56:43 PM</t>
+  </si>
+  <si>
+    <t>694 - Heavy</t>
+  </si>
+  <si>
+    <t>Dwayne Manuel</t>
+  </si>
+  <si>
+    <t>Active Drivers, Heavy Haul</t>
+  </si>
+  <si>
+    <t>HAAS Alert, Heavy Haul</t>
+  </si>
+  <si>
+    <t>Heavy Speeding</t>
+  </si>
+  <si>
+    <t>Speed Sign Verified</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>Tim Neff Jr.</t>
+  </si>
+  <si>
+    <t>I 10, Winnie, TX</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544500c9-09b5-5d26-bf1c-4f5a5e59e627</t>
+  </si>
+  <si>
+    <t>06/25/2026 4:46:02 PM</t>
+  </si>
+  <si>
+    <t>629 - Heavy</t>
+  </si>
+  <si>
+    <t>Mobile Usage</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>Fannett Road, Beaumont, TX, 77705</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544500bf-4275-5ded-85e2-3ee8f4e6d92b</t>
+  </si>
+  <si>
+    <t>06/25/2026 12:16:55 PM</t>
+  </si>
+  <si>
+    <t>680 - Medium</t>
+  </si>
+  <si>
+    <t>Jesus Carbajal</t>
+  </si>
+  <si>
+    <t>Active Drivers, Towing and Recovery</t>
+  </si>
+  <si>
+    <t>HAAS Alert, Towing and Recovery</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ffc8-df6a-5dea-9370-f13b79e392c6</t>
+  </si>
+  <si>
+    <t>06/25/2026 11:15:11 AM</t>
+  </si>
+  <si>
+    <t>Harsh Brake</t>
+  </si>
+  <si>
+    <t>East Freeway Frontage Road, Houston, TX, 77020</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>0.67</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ff90-5d57-5dc0-a571-4d8c6dcde945</t>
+  </si>
+  <si>
+    <t>06/24/2026 1:15:17 PM</t>
+  </si>
+  <si>
+    <t>669 - Heavy</t>
+  </si>
+  <si>
+    <t>Jason Walker</t>
+  </si>
+  <si>
+    <t>Following Distance</t>
+  </si>
+  <si>
+    <t>Moderate Traffic</t>
+  </si>
+  <si>
+    <t>Creole Nature Trail All-American Road, Calcasieu Parish, LA</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fad7-f51b-528d-8ce9-9658a4c0b9e5</t>
+  </si>
+  <si>
+    <t>06/23/2026 11:02:05 AM</t>
+  </si>
+  <si>
+    <t>I 10 Frontage Road, 24.6 mi SE Liberty, Chambers County, TX</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>0.55</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f537-a7f7-5b50-be7d-fcffb700b16d</t>
+  </si>
+  <si>
+    <t>06/22/2026 11:26:05 AM</t>
+  </si>
+  <si>
+    <t>692 - Heavy</t>
+  </si>
+  <si>
+    <t>William Foley</t>
+  </si>
+  <si>
+    <t>I 45, Madisonville, TX, 77864</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f027-4165-5f24-8d32-d9f65658b1d2</t>
+  </si>
+  <si>
+    <t>06/19/2026 4:15:44 PM</t>
+  </si>
+  <si>
+    <t>658 - Medium</t>
+  </si>
+  <si>
+    <t>Paul Kunze Jr</t>
+  </si>
+  <si>
+    <t>US 69;US 96;US 287, Beaumont, TX, 77701</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e1bd-5e83-597e-995e-9c0f9e74b244</t>
+  </si>
+  <si>
     <t>06/18/2026 4:34:01 PM</t>
   </si>
   <si>
-    <t>680 - Medium</t>
-  </si>
-  <si>
-    <t>Jesus Carbajal</t>
-  </si>
-  <si>
-    <t>Active Drivers, Towing and Recovery</t>
-  </si>
-  <si>
-    <t>HAAS Alert, Towing and Recovery</t>
-  </si>
-  <si>
     <t>Obstructed Camera</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
-    <t>Tim Neff Jr.</t>
-  </si>
-  <si>
     <t>Interstate 10 South Frontage Road, Beaumont, TX, 77702</t>
   </si>
   <si>
@@ -113,18 +266,9 @@
     <t>Severe Speeding</t>
   </si>
   <si>
-    <t>Speed Sign Verified</t>
-  </si>
-  <si>
-    <t>I 10, Winnie, TX</t>
-  </si>
-  <si>
     <t>85</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -137,19 +281,7 @@
     <t>683 - Heavy</t>
   </si>
   <si>
-    <t>Dwayne Manuel</t>
-  </si>
-  <si>
-    <t>Active Drivers, Heavy Haul</t>
-  </si>
-  <si>
-    <t>HAAS Alert, Heavy Haul</t>
-  </si>
-  <si>
-    <t>Mobile Usage</t>
-  </si>
-  <si>
-    <t>Light Traffic</t>
+    <t>Coached</t>
   </si>
   <si>
     <t>H O Mills Highway, Port Arthur, TX</t>
@@ -194,12 +326,6 @@
     <t>06/15/2026 1:23:54 PM</t>
   </si>
   <si>
-    <t>669 - Heavy</t>
-  </si>
-  <si>
-    <t>Jason Walker</t>
-  </si>
-  <si>
     <t>Wet Road, Light Traffic, Raining</t>
   </si>
   <si>
@@ -215,9 +341,6 @@
     <t>06/14/2026 11:39:04 AM</t>
   </si>
   <si>
-    <t>Coached</t>
-  </si>
-  <si>
     <t>State Highway 124, Hamshire, TX, 77622</t>
   </si>
   <si>
@@ -233,12 +356,6 @@
     <t>644 - Medium</t>
   </si>
   <si>
-    <t>Paul Kunze Jr</t>
-  </si>
-  <si>
-    <t>Fannett Road, Beaumont, TX, 77705</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c69b-3b3b-50b6-9299-c5f9408304d6</t>
   </si>
   <si>
@@ -263,15 +380,9 @@
     <t>06/13/2026 4:18:06 PM</t>
   </si>
   <si>
-    <t>Moderate Traffic</t>
-  </si>
-  <si>
     <t>East Freeway, Channelview, TX, 77530</t>
   </si>
   <si>
-    <t>57</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c2d9-604f-59f0-87e5-6a5c05c198bc</t>
   </si>
   <si>
@@ -371,18 +482,12 @@
     <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
   </si>
   <si>
-    <t>Following Distance</t>
-  </si>
-  <si>
     <t>Eddie Bowden</t>
   </si>
   <si>
     <t>I 10, Welsh, LA, 70581</t>
   </si>
   <si>
-    <t>65</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a382-4d73-5bb1-b5db-a39ca69f4b45</t>
   </si>
   <si>
@@ -434,9 +539,6 @@
     <t>05/29/2026 12:42:54 PM</t>
   </si>
   <si>
-    <t>692 - Heavy</t>
-  </si>
-  <si>
     <t>I 10, Seguin, TX, 78638</t>
   </si>
   <si>
@@ -641,9 +743,6 @@
     <t>05/02/2026 7:49:16 AM</t>
   </si>
   <si>
-    <t>658 - Medium</t>
-  </si>
-  <si>
     <t>44</t>
   </si>
   <si>
@@ -701,9 +800,6 @@
     <t>04/28/2026 2:56:41 PM</t>
   </si>
   <si>
-    <t>629 - Heavy</t>
-  </si>
-  <si>
     <t>South Major Drive, Beaumont, TX, 77705</t>
   </si>
   <si>
@@ -779,9 +875,6 @@
     <t>Drew Template</t>
   </si>
   <si>
-    <t>Harsh Brake</t>
-  </si>
-  <si>
     <t>8401 Washington Boulevard, Beaumont, TX, 77707</t>
   </si>
   <si>
@@ -935,9 +1028,6 @@
     <t>FM 105, 7.6 mi ESE Silsbee, Jasper County, TX, 77615</t>
   </si>
   <si>
-    <t>59</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457f2f-b767-58bc-a524-ffc617afdb32</t>
   </si>
   <si>
@@ -995,9 +1085,6 @@
     <t>East Freeway, 5.0 mi N Baytown, Harris County, TX, 77521</t>
   </si>
   <si>
-    <t>58</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544564eb-79d0-5e02-bdcb-46a38e6bc3b1</t>
   </si>
   <si>
@@ -1158,66 +1245,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544543df-906f-58b3-859c-3234287075ec</t>
-  </si>
-  <si>
-    <t>03/25/2026 2:29:30 PM</t>
-  </si>
-  <si>
-    <t>Walden Road, Beaumont, TX, 77705</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452679-31fa-5ba3-b440-2e874ac5ae9f</t>
-  </si>
-  <si>
-    <t>03/25/2026 2:01:32 PM</t>
-  </si>
-  <si>
-    <t>Corey Boyett</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445265f-97a1-58d6-85fc-f99cb35e4840</t>
-  </si>
-  <si>
-    <t>03/24/2026 5:06:47 PM</t>
-  </si>
-  <si>
-    <t>646 - Medium</t>
-  </si>
-  <si>
-    <t>Construction, Moderate Traffic</t>
-  </si>
-  <si>
-    <t>2059 I 10, Beaumont, TX, 77703</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544521e2-d62e-5675-8fd7-978f4ed5d73a</t>
-  </si>
-  <si>
-    <t>03/24/2026 8:21:25 AM</t>
-  </si>
-  <si>
-    <t>I 10, Winnie, TX, 77580</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452001-db24-56b8-a3cb-576425192e90</t>
-  </si>
-  <si>
-    <t>03/24/2026 7:32:42 AM</t>
-  </si>
-  <si>
-    <t>Wet Road, Passengers, Light Traffic</t>
-  </si>
-  <si>
-    <t>TX 73, 15.3 mi SW Nederland, Jefferson County, TX</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451fd5-3fbc-5ac1-96f4-67459813149f</t>
   </si>
 </sst>
 </file>
@@ -1594,7 +1621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O93"/>
+  <dimension ref="A1:O96"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -1679,86 +1706,86 @@
         <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
         <v>31</v>
-      </c>
-      <c r="G3" t="s">
-        <v>32</v>
       </c>
       <c r="H3" t="s">
         <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" t="s">
         <v>33</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" t="s">
         <v>34</v>
-      </c>
-      <c r="L3" t="s">
-        <v>35</v>
-      </c>
-      <c r="M3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N3" t="s">
-        <v>21</v>
-      </c>
-      <c r="O3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s">
         <v>38</v>
       </c>
-      <c r="B4" t="s">
+      <c r="E4" t="s">
         <v>39</v>
       </c>
-      <c r="C4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" t="s">
-        <v>42</v>
-      </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="H4" t="s">
         <v>22</v>
@@ -1767,45 +1794,45 @@
         <v>23</v>
       </c>
       <c r="J4" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="K4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G5" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H5" t="s">
         <v>22</v>
@@ -1814,45 +1841,45 @@
         <v>23</v>
       </c>
       <c r="J5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="K5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="L5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="N5" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="O5" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G6" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H6" t="s">
         <v>22</v>
@@ -1861,45 +1888,45 @@
         <v>23</v>
       </c>
       <c r="J6" t="s">
+        <v>53</v>
+      </c>
+      <c r="K6" t="s">
+        <v>54</v>
+      </c>
+      <c r="L6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O6" t="s">
         <v>55</v>
-      </c>
-      <c r="K6" t="s">
-        <v>56</v>
-      </c>
-      <c r="L6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O6" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
         <v>43</v>
       </c>
       <c r="G7" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="H7" t="s">
         <v>22</v>
@@ -1908,92 +1935,92 @@
         <v>23</v>
       </c>
       <c r="J7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="K7" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="L7" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M7" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N7" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="O7" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G8" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" t="s">
+        <v>64</v>
+      </c>
+      <c r="K8" t="s">
+        <v>65</v>
+      </c>
+      <c r="L8" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" t="s">
+        <v>26</v>
+      </c>
+      <c r="O8" t="s">
         <v>66</v>
-      </c>
-      <c r="I8" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" t="s">
-        <v>21</v>
-      </c>
-      <c r="O8" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H9" t="s">
         <v>22</v>
@@ -2002,45 +2029,45 @@
         <v>23</v>
       </c>
       <c r="J9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K9" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="L9" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M9" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N9" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="G10" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H10" t="s">
         <v>22</v>
@@ -2049,19 +2076,19 @@
         <v>23</v>
       </c>
       <c r="J10" t="s">
+        <v>75</v>
+      </c>
+      <c r="K10" t="s">
         <v>76</v>
       </c>
-      <c r="K10" t="s">
-        <v>34</v>
-      </c>
       <c r="L10" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="M10" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="N10" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O10" t="s">
         <v>77</v>
@@ -2072,116 +2099,116 @@
         <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="G11" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="H11" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I11" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J11" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="K11" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="L11" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="M11" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="N11" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O11" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="G12" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="H12" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="I12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J12" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="K12" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L12" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M12" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="N12" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O12" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="G13" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
@@ -2190,45 +2217,45 @@
         <v>23</v>
       </c>
       <c r="J13" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="K13" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L13" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M13" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="N13" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O13" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F14" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G14" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H14" t="s">
         <v>22</v>
@@ -2237,45 +2264,45 @@
         <v>23</v>
       </c>
       <c r="J14" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="K14" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="L14" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M14" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N14" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O14" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G15" t="s">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="H15" t="s">
         <v>22</v>
@@ -2284,92 +2311,92 @@
         <v>23</v>
       </c>
       <c r="J15" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="K15" t="s">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="L15" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="M15" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="N15" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O15" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="E16" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" t="s">
         <v>31</v>
       </c>
-      <c r="G16" t="s">
-        <v>32</v>
-      </c>
       <c r="H16" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="I16" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J16" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="K16" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="L16" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="M16" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="N16" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O16" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E17" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F17" t="s">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="G17" t="s">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="H17" t="s">
         <v>22</v>
@@ -2378,45 +2405,45 @@
         <v>23</v>
       </c>
       <c r="J17" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="K17" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="L17" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M17" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N17" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O17" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E18" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F18" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="G18" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H18" t="s">
         <v>22</v>
@@ -2425,113 +2452,113 @@
         <v>23</v>
       </c>
       <c r="J18" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="K18" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="L18" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="M18" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="N18" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O18" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F19" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G19" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H19" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="I19" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J19" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="K19" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="L19" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M19" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N19" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O19" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B20" t="s">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F20" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="G20" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="H20" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="I20" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="J20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K20" t="s">
-        <v>121</v>
+        <v>33</v>
       </c>
       <c r="L20" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M20" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="N20" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O20" t="s">
         <v>122</v>
@@ -2542,22 +2569,22 @@
         <v>123</v>
       </c>
       <c r="B21" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F21" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G21" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H21" t="s">
         <v>22</v>
@@ -2566,348 +2593,348 @@
         <v>23</v>
       </c>
       <c r="J21" t="s">
+        <v>124</v>
+      </c>
+      <c r="K21" t="s">
+        <v>125</v>
+      </c>
+      <c r="L21" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" t="s">
+        <v>26</v>
+      </c>
+      <c r="N21" t="s">
+        <v>26</v>
+      </c>
+      <c r="O21" t="s">
         <v>126</v>
-      </c>
-      <c r="K21" t="s">
-        <v>127</v>
-      </c>
-      <c r="L21" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" t="s">
-        <v>21</v>
-      </c>
-      <c r="N21" t="s">
-        <v>21</v>
-      </c>
-      <c r="O21" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D22" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F22" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="G22" t="s">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="H22" t="s">
         <v>22</v>
       </c>
       <c r="I22" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J22" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="K22" t="s">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="L22" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M22" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N22" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O22" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B23" t="s">
-        <v>133</v>
+        <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>134</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E23" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F23" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="G23" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="H23" t="s">
         <v>22</v>
       </c>
       <c r="I23" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="J23" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="K23" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="L23" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="M23" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="N23" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O23" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B24" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s">
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="D24" t="s">
-        <v>117</v>
+        <v>26</v>
       </c>
       <c r="E24" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F24" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="G24" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="H24" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I24" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="J24" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="K24" t="s">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="L24" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="M24" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="N24" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O24" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B25" t="s">
-        <v>133</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>134</v>
+        <v>37</v>
       </c>
       <c r="D25" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E25" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F25" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G25" t="s">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="H25" t="s">
         <v>22</v>
       </c>
       <c r="I25" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="J25" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="K25" t="s">
-        <v>144</v>
+        <v>95</v>
       </c>
       <c r="L25" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M25" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N25" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O25" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B26" t="s">
-        <v>147</v>
+        <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>148</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>149</v>
+        <v>38</v>
       </c>
       <c r="E26" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F26" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="G26" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="H26" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I26" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J26" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="K26" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="L26" t="s">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="M26" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="N26" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O26" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>147</v>
       </c>
       <c r="D27" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G27" t="s">
-        <v>153</v>
+        <v>31</v>
       </c>
       <c r="H27" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J27" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="K27" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="L27" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M27" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N27" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O27" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>151</v>
+      </c>
+      <c r="B28" t="s">
+        <v>152</v>
+      </c>
+      <c r="C28" t="s">
+        <v>153</v>
+      </c>
+      <c r="D28" t="s">
+        <v>154</v>
+      </c>
+      <c r="E28" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" t="s">
+        <v>51</v>
+      </c>
+      <c r="G28" t="s">
+        <v>52</v>
+      </c>
+      <c r="H28" t="s">
+        <v>88</v>
+      </c>
+      <c r="I28" t="s">
+        <v>155</v>
+      </c>
+      <c r="J28" t="s">
         <v>156</v>
       </c>
-      <c r="B28" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" t="s">
-        <v>60</v>
-      </c>
-      <c r="D28" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28" t="s">
-        <v>42</v>
-      </c>
-      <c r="F28" t="s">
-        <v>135</v>
-      </c>
-      <c r="G28" t="s">
-        <v>130</v>
-      </c>
-      <c r="H28" t="s">
-        <v>22</v>
-      </c>
-      <c r="I28" t="s">
-        <v>23</v>
-      </c>
-      <c r="J28" t="s">
-        <v>73</v>
-      </c>
       <c r="K28" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="L28" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M28" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N28" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O28" t="s">
         <v>157</v>
@@ -2918,351 +2945,351 @@
         <v>158</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>159</v>
       </c>
       <c r="C29" t="s">
-        <v>29</v>
+        <v>160</v>
       </c>
       <c r="D29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" t="s">
+        <v>39</v>
+      </c>
+      <c r="F29" t="s">
         <v>30</v>
       </c>
-      <c r="E29" t="s">
-        <v>19</v>
-      </c>
-      <c r="F29" t="s">
-        <v>43</v>
-      </c>
       <c r="G29" t="s">
-        <v>153</v>
+        <v>31</v>
       </c>
       <c r="H29" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I29" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J29" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K29" t="s">
-        <v>63</v>
+        <v>162</v>
       </c>
       <c r="L29" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M29" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N29" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O29" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B30" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c r="D30" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E30" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F30" t="s">
-        <v>135</v>
+        <v>30</v>
       </c>
       <c r="G30" t="s">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="H30" t="s">
         <v>22</v>
       </c>
       <c r="I30" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J30" t="s">
-        <v>162</v>
+        <v>118</v>
       </c>
       <c r="K30" t="s">
-        <v>163</v>
+        <v>90</v>
       </c>
       <c r="L30" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M30" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N30" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O30" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="C31" t="s">
-        <v>29</v>
+        <v>169</v>
       </c>
       <c r="D31" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="G31" t="s">
-        <v>153</v>
+        <v>31</v>
       </c>
       <c r="H31" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I31" t="s">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="J31" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="K31" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="L31" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M31" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="N31" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O31" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="C32" t="s">
-        <v>29</v>
+        <v>153</v>
       </c>
       <c r="D32" t="s">
-        <v>30</v>
+        <v>154</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
       </c>
       <c r="F32" t="s">
-        <v>135</v>
+        <v>93</v>
       </c>
       <c r="G32" t="s">
-        <v>170</v>
+        <v>31</v>
       </c>
       <c r="H32" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="I32" t="s">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="J32" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K32" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="L32" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M32" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N32" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O32" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="C33" t="s">
-        <v>29</v>
+        <v>169</v>
       </c>
       <c r="D33" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
       </c>
       <c r="F33" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="G33" t="s">
-        <v>175</v>
+        <v>52</v>
       </c>
       <c r="H33" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I33" t="s">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="J33" t="s">
-        <v>176</v>
+        <v>94</v>
       </c>
       <c r="K33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L33" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M33" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B34" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C34" t="s">
-        <v>134</v>
+        <v>182</v>
       </c>
       <c r="D34" t="s">
-        <v>41</v>
+        <v>183</v>
       </c>
       <c r="E34" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F34" t="s">
-        <v>135</v>
+        <v>51</v>
       </c>
       <c r="G34" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H34" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="I34" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="J34" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="K34" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="L34" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M34" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N34" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O34" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B35" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="C35" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="E35" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F35" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="G35" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="H35" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="I35" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J35" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K35" t="s">
-        <v>186</v>
+        <v>149</v>
       </c>
       <c r="L35" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M35" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="N35" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O35" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B36" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="D36" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E36" t="s">
         <v>19</v>
       </c>
       <c r="F36" t="s">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="G36" t="s">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="H36" t="s">
         <v>22</v>
@@ -3271,66 +3298,66 @@
         <v>23</v>
       </c>
       <c r="J36" t="s">
-        <v>189</v>
+        <v>32</v>
       </c>
       <c r="K36" t="s">
-        <v>172</v>
+        <v>33</v>
       </c>
       <c r="L36" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M36" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="N36" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O36" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B37" t="s">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="C37" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="D37" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="E37" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F37" t="s">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="G37" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="H37" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="I37" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="J37" t="s">
         <v>193</v>
       </c>
       <c r="K37" t="s">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="L37" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M37" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N37" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O37" t="s">
         <v>194</v>
@@ -3341,22 +3368,22 @@
         <v>195</v>
       </c>
       <c r="B38" t="s">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="C38" t="s">
-        <v>60</v>
+        <v>147</v>
       </c>
       <c r="D38" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E38" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F38" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="G38" t="s">
-        <v>44</v>
+        <v>165</v>
       </c>
       <c r="H38" t="s">
         <v>22</v>
@@ -3368,171 +3395,171 @@
         <v>196</v>
       </c>
       <c r="K38" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="L38" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M38" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N38" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O38" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B39" t="s">
-        <v>133</v>
+        <v>79</v>
       </c>
       <c r="C39" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="D39" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="E39" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F39" t="s">
-        <v>135</v>
+        <v>93</v>
       </c>
       <c r="G39" t="s">
-        <v>44</v>
+        <v>187</v>
       </c>
       <c r="H39" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="I39" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="J39" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K39" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="L39" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M39" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="N39" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O39" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B40" t="s">
-        <v>202</v>
+        <v>79</v>
       </c>
       <c r="C40" t="s">
-        <v>203</v>
+        <v>80</v>
       </c>
       <c r="D40" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E40" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F40" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="G40" t="s">
-        <v>44</v>
+        <v>204</v>
       </c>
       <c r="H40" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="I40" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J40" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K40" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L40" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M40" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N40" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O40" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B41" t="s">
-        <v>208</v>
+        <v>79</v>
       </c>
       <c r="C41" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D41" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="E41" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F41" t="s">
-        <v>43</v>
+        <v>170</v>
       </c>
       <c r="G41" t="s">
-        <v>44</v>
+        <v>209</v>
       </c>
       <c r="H41" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="I41" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J41" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="K41" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L41" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M41" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N41" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O41" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B42" t="s">
-        <v>28</v>
+        <v>214</v>
       </c>
       <c r="C42" t="s">
-        <v>212</v>
+        <v>169</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -3541,57 +3568,57 @@
         <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>43</v>
+        <v>170</v>
       </c>
       <c r="G42" t="s">
-        <v>130</v>
+        <v>31</v>
       </c>
       <c r="H42" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="I42" t="s">
-        <v>23</v>
+        <v>155</v>
       </c>
       <c r="J42" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K42" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L42" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M42" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N42" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O42" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B43" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C43" t="s">
-        <v>212</v>
+        <v>37</v>
       </c>
       <c r="D43" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E43" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F43" t="s">
-        <v>135</v>
+        <v>93</v>
       </c>
       <c r="G43" t="s">
-        <v>61</v>
+        <v>187</v>
       </c>
       <c r="H43" t="s">
         <v>22</v>
@@ -3600,139 +3627,139 @@
         <v>23</v>
       </c>
       <c r="J43" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="K43" t="s">
-        <v>56</v>
+        <v>220</v>
       </c>
       <c r="L43" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M43" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="N43" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O43" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B44" t="s">
-        <v>133</v>
+        <v>36</v>
       </c>
       <c r="C44" t="s">
-        <v>134</v>
+        <v>37</v>
       </c>
       <c r="D44" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E44" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F44" t="s">
-        <v>135</v>
+        <v>93</v>
       </c>
       <c r="G44" t="s">
-        <v>220</v>
+        <v>165</v>
       </c>
       <c r="H44" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I44" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="J44" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K44" t="s">
-        <v>63</v>
+        <v>206</v>
       </c>
       <c r="L44" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M44" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="N44" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O44" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B45" t="s">
-        <v>208</v>
+        <v>152</v>
       </c>
       <c r="C45" t="s">
-        <v>72</v>
+        <v>153</v>
       </c>
       <c r="D45" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="E45" t="s">
         <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="G45" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H45" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="I45" t="s">
-        <v>23</v>
+        <v>155</v>
       </c>
       <c r="J45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K45" t="s">
-        <v>106</v>
+        <v>184</v>
       </c>
       <c r="L45" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M45" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N45" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O45" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B46" t="s">
-        <v>228</v>
+        <v>49</v>
       </c>
       <c r="C46" t="s">
-        <v>212</v>
+        <v>50</v>
       </c>
       <c r="D46" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E46" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F46" t="s">
-        <v>43</v>
+        <v>170</v>
       </c>
       <c r="G46" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H46" t="s">
         <v>22</v>
@@ -3741,19 +3768,19 @@
         <v>23</v>
       </c>
       <c r="J46" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K46" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="L46" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M46" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N46" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O46" t="s">
         <v>231</v>
@@ -3764,10 +3791,10 @@
         <v>232</v>
       </c>
       <c r="B47" t="s">
-        <v>16</v>
+        <v>168</v>
       </c>
       <c r="C47" t="s">
-        <v>17</v>
+        <v>169</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
@@ -3776,31 +3803,31 @@
         <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="G47" t="s">
-        <v>170</v>
+        <v>31</v>
       </c>
       <c r="H47" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="I47" t="s">
-        <v>23</v>
+        <v>155</v>
       </c>
       <c r="J47" t="s">
         <v>233</v>
       </c>
       <c r="K47" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="L47" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M47" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N47" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O47" t="s">
         <v>234</v>
@@ -3811,69 +3838,69 @@
         <v>235</v>
       </c>
       <c r="B48" t="s">
-        <v>16</v>
+        <v>236</v>
       </c>
       <c r="C48" t="s">
-        <v>17</v>
+        <v>237</v>
       </c>
       <c r="D48" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="E48" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F48" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="G48" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H48" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="I48" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J48" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K48" t="s">
-        <v>35</v>
+        <v>239</v>
       </c>
       <c r="L48" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M48" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N48" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O48" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D49" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E49" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F49" t="s">
-        <v>135</v>
+        <v>30</v>
       </c>
       <c r="G49" t="s">
-        <v>130</v>
+        <v>31</v>
       </c>
       <c r="H49" t="s">
         <v>22</v>
@@ -3882,45 +3909,45 @@
         <v>23</v>
       </c>
       <c r="J49" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="K49" t="s">
-        <v>46</v>
+        <v>242</v>
       </c>
       <c r="L49" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M49" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N49" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O49" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B50" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="C50" t="s">
-        <v>60</v>
+        <v>245</v>
       </c>
       <c r="D50" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E50" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F50" t="s">
-        <v>135</v>
+        <v>30</v>
       </c>
       <c r="G50" t="s">
-        <v>44</v>
+        <v>165</v>
       </c>
       <c r="H50" t="s">
         <v>22</v>
@@ -3929,233 +3956,233 @@
         <v>23</v>
       </c>
       <c r="J50" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="K50" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="L50" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M50" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N50" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O50" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>249</v>
+      </c>
+      <c r="B51" t="s">
+        <v>79</v>
+      </c>
+      <c r="C51" t="s">
         <v>245</v>
       </c>
-      <c r="B51" t="s">
-        <v>228</v>
-      </c>
-      <c r="C51" t="s">
-        <v>116</v>
-      </c>
       <c r="D51" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="E51" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F51" t="s">
-        <v>43</v>
+        <v>170</v>
       </c>
       <c r="G51" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="H51" t="s">
         <v>22</v>
       </c>
       <c r="I51" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="J51" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K51" t="s">
-        <v>182</v>
+        <v>100</v>
       </c>
       <c r="L51" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M51" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N51" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O51" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B52" t="s">
-        <v>59</v>
+        <v>168</v>
       </c>
       <c r="C52" t="s">
-        <v>60</v>
+        <v>169</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
       </c>
       <c r="E52" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F52" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="G52" t="s">
-        <v>44</v>
+        <v>253</v>
       </c>
       <c r="H52" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="I52" t="s">
-        <v>23</v>
+        <v>155</v>
       </c>
       <c r="J52" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="K52" t="s">
-        <v>182</v>
+        <v>105</v>
       </c>
       <c r="L52" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M52" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N52" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O52" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B53" t="s">
-        <v>252</v>
+        <v>68</v>
       </c>
       <c r="C53" t="s">
-        <v>253</v>
+        <v>69</v>
       </c>
       <c r="D53" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E53" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F53" t="s">
-        <v>254</v>
+        <v>137</v>
       </c>
       <c r="G53" t="s">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="H53" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I53" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J53" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="K53" t="s">
-        <v>256</v>
+        <v>143</v>
       </c>
       <c r="L53" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M53" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N53" t="s">
-        <v>257</v>
+        <v>26</v>
       </c>
       <c r="O53" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B54" t="s">
-        <v>133</v>
+        <v>29</v>
       </c>
       <c r="C54" t="s">
-        <v>134</v>
+        <v>245</v>
       </c>
       <c r="D54" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E54" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F54" t="s">
-        <v>135</v>
+        <v>30</v>
       </c>
       <c r="G54" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="H54" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I54" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="J54" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K54" t="s">
-        <v>121</v>
+        <v>262</v>
       </c>
       <c r="L54" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M54" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N54" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O54" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="C55" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="D55" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E55" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F55" t="s">
-        <v>43</v>
+        <v>170</v>
       </c>
       <c r="G55" t="s">
-        <v>61</v>
+        <v>204</v>
       </c>
       <c r="H55" t="s">
         <v>22</v>
@@ -4164,92 +4191,92 @@
         <v>23</v>
       </c>
       <c r="J55" t="s">
-        <v>193</v>
+        <v>265</v>
       </c>
       <c r="K55" t="s">
-        <v>263</v>
+        <v>201</v>
       </c>
       <c r="L55" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M55" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N55" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O55" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B56" t="s">
-        <v>133</v>
+        <v>36</v>
       </c>
       <c r="C56" t="s">
-        <v>134</v>
+        <v>37</v>
       </c>
       <c r="D56" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E56" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F56" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="G56" t="s">
-        <v>130</v>
+        <v>31</v>
       </c>
       <c r="H56" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I56" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="J56" t="s">
-        <v>196</v>
+        <v>268</v>
       </c>
       <c r="K56" t="s">
-        <v>112</v>
+        <v>45</v>
       </c>
       <c r="L56" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M56" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N56" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O56" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B57" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C57" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="D57" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E57" t="s">
         <v>19</v>
       </c>
       <c r="F57" t="s">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="G57" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="H57" t="s">
         <v>22</v>
@@ -4258,45 +4285,45 @@
         <v>23</v>
       </c>
       <c r="J57" t="s">
-        <v>221</v>
+        <v>271</v>
       </c>
       <c r="K57" t="s">
-        <v>268</v>
+        <v>90</v>
       </c>
       <c r="L57" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M57" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N57" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O57" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B58" t="s">
-        <v>208</v>
+        <v>49</v>
       </c>
       <c r="C58" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="D58" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E58" t="s">
         <v>19</v>
       </c>
       <c r="F58" t="s">
-        <v>43</v>
+        <v>170</v>
       </c>
       <c r="G58" t="s">
-        <v>271</v>
+        <v>31</v>
       </c>
       <c r="H58" t="s">
         <v>22</v>
@@ -4305,92 +4332,92 @@
         <v>23</v>
       </c>
       <c r="J58" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K58" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="L58" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M58" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N58" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O58" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B59" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C59" t="s">
-        <v>17</v>
+        <v>153</v>
       </c>
       <c r="D59" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="E59" t="s">
         <v>19</v>
       </c>
       <c r="F59" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G59" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="H59" t="s">
         <v>22</v>
       </c>
       <c r="I59" t="s">
-        <v>23</v>
+        <v>155</v>
       </c>
       <c r="J59" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="K59" t="s">
-        <v>163</v>
+        <v>216</v>
       </c>
       <c r="L59" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M59" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N59" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O59" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B60" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C60" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D60" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E60" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F60" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="G60" t="s">
-        <v>271</v>
+        <v>31</v>
       </c>
       <c r="H60" t="s">
         <v>22</v>
@@ -4399,33 +4426,33 @@
         <v>23</v>
       </c>
       <c r="J60" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K60" t="s">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="L60" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M60" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N60" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O60" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B61" t="s">
-        <v>208</v>
+        <v>284</v>
       </c>
       <c r="C61" t="s">
-        <v>72</v>
+        <v>285</v>
       </c>
       <c r="D61" t="s">
         <v>18</v>
@@ -4437,136 +4464,136 @@
         <v>43</v>
       </c>
       <c r="G61" t="s">
-        <v>153</v>
+        <v>52</v>
       </c>
       <c r="H61" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="I61" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J61" t="s">
-        <v>73</v>
+        <v>286</v>
       </c>
       <c r="K61" t="s">
-        <v>35</v>
+        <v>287</v>
       </c>
       <c r="L61" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M61" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N61" t="s">
-        <v>21</v>
+        <v>288</v>
       </c>
       <c r="O61" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="B62" t="s">
-        <v>284</v>
+        <v>168</v>
       </c>
       <c r="C62" t="s">
-        <v>253</v>
+        <v>169</v>
       </c>
       <c r="D62" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="E62" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F62" t="s">
-        <v>254</v>
+        <v>170</v>
       </c>
       <c r="G62" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H62" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="I62" t="s">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="J62" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="K62" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="L62" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M62" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N62" t="s">
-        <v>286</v>
+        <v>26</v>
       </c>
       <c r="O62" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B63" t="s">
-        <v>284</v>
+        <v>49</v>
       </c>
       <c r="C63" t="s">
-        <v>253</v>
+        <v>50</v>
       </c>
       <c r="D63" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E63" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F63" t="s">
-        <v>254</v>
+        <v>30</v>
       </c>
       <c r="G63" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="H63" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I63" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J63" t="s">
-        <v>289</v>
+        <v>227</v>
       </c>
       <c r="K63" t="s">
-        <v>106</v>
+        <v>294</v>
       </c>
       <c r="L63" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M63" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N63" t="s">
-        <v>290</v>
+        <v>26</v>
       </c>
       <c r="O63" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B64" t="s">
-        <v>16</v>
+        <v>168</v>
       </c>
       <c r="C64" t="s">
-        <v>17</v>
+        <v>169</v>
       </c>
       <c r="D64" t="s">
         <v>18</v>
@@ -4575,57 +4602,57 @@
         <v>19</v>
       </c>
       <c r="F64" t="s">
-        <v>20</v>
+        <v>170</v>
       </c>
       <c r="G64" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
       <c r="H64" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="I64" t="s">
-        <v>23</v>
+        <v>155</v>
       </c>
       <c r="J64" t="s">
-        <v>293</v>
+        <v>230</v>
       </c>
       <c r="K64" t="s">
-        <v>294</v>
+        <v>149</v>
       </c>
       <c r="L64" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M64" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N64" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O64" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B65" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="C65" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="D65" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E65" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F65" t="s">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="G65" t="s">
-        <v>271</v>
+        <v>26</v>
       </c>
       <c r="H65" t="s">
         <v>22</v>
@@ -4634,160 +4661,160 @@
         <v>23</v>
       </c>
       <c r="J65" t="s">
-        <v>297</v>
+        <v>254</v>
       </c>
       <c r="K65" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L65" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M65" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N65" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O65" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B66" t="s">
-        <v>301</v>
+        <v>68</v>
       </c>
       <c r="C66" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D66" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E66" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F66" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G66" t="s">
-        <v>44</v>
+        <v>302</v>
       </c>
       <c r="H66" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I66" t="s">
         <v>23</v>
       </c>
       <c r="J66" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K66" t="s">
-        <v>84</v>
+        <v>304</v>
       </c>
       <c r="L66" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M66" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N66" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O66" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B67" t="s">
-        <v>202</v>
+        <v>36</v>
       </c>
       <c r="C67" t="s">
-        <v>203</v>
+        <v>37</v>
       </c>
       <c r="D67" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E67" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F67" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="G67" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="H67" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I67" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J67" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K67" t="s">
-        <v>306</v>
+        <v>197</v>
       </c>
       <c r="L67" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M67" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N67" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O67" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B68" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C68" t="s">
-        <v>309</v>
+        <v>50</v>
       </c>
       <c r="D68" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E68" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F68" t="s">
-        <v>43</v>
+        <v>170</v>
       </c>
       <c r="G68" t="s">
-        <v>44</v>
+        <v>302</v>
       </c>
       <c r="H68" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I68" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J68" t="s">
         <v>310</v>
       </c>
       <c r="K68" t="s">
-        <v>63</v>
+        <v>211</v>
       </c>
       <c r="L68" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M68" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N68" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O68" t="s">
         <v>311</v>
@@ -4798,104 +4825,104 @@
         <v>312</v>
       </c>
       <c r="B69" t="s">
+        <v>68</v>
+      </c>
+      <c r="C69" t="s">
+        <v>69</v>
+      </c>
+      <c r="D69" t="s">
+        <v>38</v>
+      </c>
+      <c r="E69" t="s">
         <v>39</v>
       </c>
-      <c r="C69" t="s">
-        <v>309</v>
-      </c>
-      <c r="D69" t="s">
-        <v>42</v>
-      </c>
-      <c r="E69" t="s">
-        <v>42</v>
-      </c>
       <c r="F69" t="s">
-        <v>135</v>
+        <v>30</v>
       </c>
       <c r="G69" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="H69" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I69" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J69" t="s">
+        <v>32</v>
+      </c>
+      <c r="K69" t="s">
+        <v>45</v>
+      </c>
+      <c r="L69" t="s">
+        <v>26</v>
+      </c>
+      <c r="M69" t="s">
+        <v>26</v>
+      </c>
+      <c r="N69" t="s">
+        <v>26</v>
+      </c>
+      <c r="O69" t="s">
         <v>313</v>
-      </c>
-      <c r="K69" t="s">
-        <v>314</v>
-      </c>
-      <c r="L69" t="s">
-        <v>21</v>
-      </c>
-      <c r="M69" t="s">
-        <v>21</v>
-      </c>
-      <c r="N69" t="s">
-        <v>21</v>
-      </c>
-      <c r="O69" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>314</v>
+      </c>
+      <c r="B70" t="s">
+        <v>315</v>
+      </c>
+      <c r="C70" t="s">
+        <v>285</v>
+      </c>
+      <c r="D70" t="s">
+        <v>18</v>
+      </c>
+      <c r="E70" t="s">
+        <v>19</v>
+      </c>
+      <c r="F70" t="s">
+        <v>43</v>
+      </c>
+      <c r="G70" t="s">
+        <v>31</v>
+      </c>
+      <c r="H70" t="s">
+        <v>22</v>
+      </c>
+      <c r="I70" t="s">
+        <v>26</v>
+      </c>
+      <c r="J70" t="s">
         <v>316</v>
       </c>
-      <c r="B70" t="s">
+      <c r="K70" t="s">
+        <v>84</v>
+      </c>
+      <c r="L70" t="s">
+        <v>26</v>
+      </c>
+      <c r="M70" t="s">
+        <v>26</v>
+      </c>
+      <c r="N70" t="s">
         <v>317</v>
       </c>
-      <c r="C70" t="s">
+      <c r="O70" t="s">
         <v>318</v>
-      </c>
-      <c r="D70" t="s">
-        <v>41</v>
-      </c>
-      <c r="E70" t="s">
-        <v>42</v>
-      </c>
-      <c r="F70" t="s">
-        <v>20</v>
-      </c>
-      <c r="G70" t="s">
-        <v>21</v>
-      </c>
-      <c r="H70" t="s">
-        <v>66</v>
-      </c>
-      <c r="I70" t="s">
-        <v>23</v>
-      </c>
-      <c r="J70" t="s">
-        <v>319</v>
-      </c>
-      <c r="K70" t="s">
-        <v>320</v>
-      </c>
-      <c r="L70" t="s">
-        <v>21</v>
-      </c>
-      <c r="M70" t="s">
-        <v>21</v>
-      </c>
-      <c r="N70" t="s">
-        <v>21</v>
-      </c>
-      <c r="O70" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B71" t="s">
-        <v>208</v>
+        <v>315</v>
       </c>
       <c r="C71" t="s">
-        <v>72</v>
+        <v>285</v>
       </c>
       <c r="D71" t="s">
         <v>18</v>
@@ -4907,54 +4934,54 @@
         <v>43</v>
       </c>
       <c r="G71" t="s">
-        <v>153</v>
+        <v>31</v>
       </c>
       <c r="H71" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="I71" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J71" t="s">
-        <v>97</v>
+        <v>320</v>
       </c>
       <c r="K71" t="s">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="L71" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M71" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N71" t="s">
-        <v>21</v>
+        <v>321</v>
       </c>
       <c r="O71" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B72" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="C72" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="D72" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E72" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F72" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="G72" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="H72" t="s">
         <v>22</v>
@@ -4963,327 +4990,327 @@
         <v>23</v>
       </c>
       <c r="J72" t="s">
+        <v>324</v>
+      </c>
+      <c r="K72" t="s">
         <v>325</v>
       </c>
-      <c r="K72" t="s">
+      <c r="L72" t="s">
+        <v>26</v>
+      </c>
+      <c r="M72" t="s">
+        <v>26</v>
+      </c>
+      <c r="N72" t="s">
+        <v>26</v>
+      </c>
+      <c r="O72" t="s">
         <v>326</v>
-      </c>
-      <c r="L72" t="s">
-        <v>21</v>
-      </c>
-      <c r="M72" t="s">
-        <v>21</v>
-      </c>
-      <c r="N72" t="s">
-        <v>21</v>
-      </c>
-      <c r="O72" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B73" t="s">
-        <v>301</v>
+        <v>49</v>
       </c>
       <c r="C73" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="D73" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E73" t="s">
         <v>19</v>
       </c>
       <c r="F73" t="s">
-        <v>43</v>
+        <v>170</v>
       </c>
       <c r="G73" t="s">
-        <v>44</v>
+        <v>302</v>
       </c>
       <c r="H73" t="s">
         <v>22</v>
       </c>
       <c r="I73" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J73" t="s">
-        <v>221</v>
+        <v>328</v>
       </c>
       <c r="K73" t="s">
-        <v>298</v>
+        <v>329</v>
       </c>
       <c r="L73" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M73" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N73" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O73" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B74" t="s">
-        <v>208</v>
+        <v>332</v>
       </c>
       <c r="C74" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
       </c>
       <c r="E74" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F74" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G74" t="s">
-        <v>331</v>
+        <v>31</v>
       </c>
       <c r="H74" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="I74" t="s">
         <v>23</v>
       </c>
       <c r="J74" t="s">
-        <v>293</v>
+        <v>333</v>
       </c>
       <c r="K74" t="s">
-        <v>205</v>
+        <v>33</v>
       </c>
       <c r="L74" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M74" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N74" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O74" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B75" t="s">
-        <v>284</v>
+        <v>236</v>
       </c>
       <c r="C75" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="D75" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="E75" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F75" t="s">
-        <v>118</v>
+        <v>30</v>
       </c>
       <c r="G75" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="H75" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="I75" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J75" t="s">
-        <v>193</v>
+        <v>336</v>
       </c>
       <c r="K75" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="L75" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M75" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N75" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O75" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B76" t="s">
-        <v>208</v>
+        <v>87</v>
       </c>
       <c r="C76" t="s">
-        <v>72</v>
+        <v>339</v>
       </c>
       <c r="D76" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E76" t="s">
         <v>19</v>
       </c>
       <c r="F76" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G76" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H76" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="I76" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J76" t="s">
-        <v>97</v>
+        <v>340</v>
       </c>
       <c r="K76" t="s">
-        <v>336</v>
+        <v>105</v>
       </c>
       <c r="L76" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M76" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N76" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O76" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B77" t="s">
-        <v>208</v>
+        <v>87</v>
       </c>
       <c r="C77" t="s">
-        <v>72</v>
+        <v>339</v>
       </c>
       <c r="D77" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E77" t="s">
         <v>19</v>
       </c>
       <c r="F77" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="G77" t="s">
-        <v>130</v>
+        <v>187</v>
       </c>
       <c r="H77" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="I77" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J77" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="K77" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="L77" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M77" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N77" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O77" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B78" t="s">
-        <v>109</v>
+        <v>347</v>
       </c>
       <c r="C78" t="s">
-        <v>21</v>
+        <v>348</v>
       </c>
       <c r="D78" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E78" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F78" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="G78" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="H78" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="I78" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J78" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="K78" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="L78" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M78" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N78" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O78" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B79" t="s">
-        <v>208</v>
+        <v>68</v>
       </c>
       <c r="C79" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D79" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E79" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F79" t="s">
-        <v>135</v>
+        <v>30</v>
       </c>
       <c r="G79" t="s">
-        <v>44</v>
+        <v>187</v>
       </c>
       <c r="H79" t="s">
         <v>22</v>
@@ -5292,207 +5319,207 @@
         <v>23</v>
       </c>
       <c r="J79" t="s">
-        <v>347</v>
+        <v>134</v>
       </c>
       <c r="K79" t="s">
-        <v>348</v>
+        <v>33</v>
       </c>
       <c r="L79" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M79" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N79" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O79" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B80" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C80" t="s">
-        <v>212</v>
+        <v>50</v>
       </c>
       <c r="D80" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E80" t="s">
         <v>19</v>
       </c>
       <c r="F80" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G80" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H80" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I80" t="s">
         <v>23</v>
       </c>
       <c r="J80" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="K80" t="s">
-        <v>352</v>
+        <v>71</v>
       </c>
       <c r="L80" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M80" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="N80" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O80" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B81" t="s">
-        <v>202</v>
+        <v>332</v>
       </c>
       <c r="C81" t="s">
-        <v>203</v>
+        <v>26</v>
       </c>
       <c r="D81" t="s">
+        <v>26</v>
+      </c>
+      <c r="E81" t="s">
+        <v>39</v>
+      </c>
+      <c r="F81" t="s">
         <v>30</v>
       </c>
-      <c r="E81" t="s">
-        <v>19</v>
-      </c>
-      <c r="F81" t="s">
+      <c r="G81" t="s">
+        <v>31</v>
+      </c>
+      <c r="H81" t="s">
+        <v>22</v>
+      </c>
+      <c r="I81" t="s">
+        <v>26</v>
+      </c>
+      <c r="J81" t="s">
         <v>254</v>
       </c>
-      <c r="G81" t="s">
-        <v>44</v>
-      </c>
-      <c r="H81" t="s">
-        <v>66</v>
-      </c>
-      <c r="I81" t="s">
-        <v>21</v>
-      </c>
-      <c r="J81" t="s">
-        <v>355</v>
-      </c>
       <c r="K81" t="s">
-        <v>52</v>
+        <v>329</v>
       </c>
       <c r="L81" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M81" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N81" t="s">
-        <v>356</v>
+        <v>26</v>
       </c>
       <c r="O81" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B82" t="s">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c r="C82" t="s">
-        <v>134</v>
+        <v>69</v>
       </c>
       <c r="D82" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E82" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F82" t="s">
-        <v>135</v>
+        <v>30</v>
       </c>
       <c r="G82" t="s">
-        <v>44</v>
+        <v>360</v>
       </c>
       <c r="H82" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I82" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="J82" t="s">
-        <v>359</v>
+        <v>324</v>
       </c>
       <c r="K82" t="s">
-        <v>46</v>
+        <v>239</v>
       </c>
       <c r="L82" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M82" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N82" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O82" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B83" t="s">
-        <v>59</v>
+        <v>315</v>
       </c>
       <c r="C83" t="s">
-        <v>60</v>
+        <v>285</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
       </c>
       <c r="E83" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F83" t="s">
-        <v>135</v>
+        <v>51</v>
       </c>
       <c r="G83" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H83" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="I83" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J83" t="s">
-        <v>362</v>
+        <v>227</v>
       </c>
       <c r="K83" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L83" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M83" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N83" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O83" t="s">
         <v>363</v>
@@ -5503,22 +5530,22 @@
         <v>364</v>
       </c>
       <c r="B84" t="s">
-        <v>208</v>
+        <v>68</v>
       </c>
       <c r="C84" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D84" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E84" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F84" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G84" t="s">
-        <v>271</v>
+        <v>31</v>
       </c>
       <c r="H84" t="s">
         <v>22</v>
@@ -5527,327 +5554,327 @@
         <v>23</v>
       </c>
       <c r="J84" t="s">
-        <v>279</v>
+        <v>134</v>
       </c>
       <c r="K84" t="s">
-        <v>25</v>
+        <v>365</v>
       </c>
       <c r="L84" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M84" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N84" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O84" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B85" t="s">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c r="C85" t="s">
-        <v>134</v>
+        <v>69</v>
       </c>
       <c r="D85" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E85" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F85" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="G85" t="s">
-        <v>44</v>
+        <v>165</v>
       </c>
       <c r="H85" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I85" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="J85" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K85" t="s">
-        <v>205</v>
+        <v>369</v>
       </c>
       <c r="L85" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M85" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N85" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O85" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B86" t="s">
-        <v>284</v>
+        <v>146</v>
       </c>
       <c r="C86" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D86" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E86" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F86" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G86" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H86" t="s">
         <v>22</v>
       </c>
       <c r="I86" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J86" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K86" t="s">
-        <v>150</v>
+        <v>373</v>
       </c>
       <c r="L86" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M86" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N86" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O86" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B87" t="s">
-        <v>373</v>
+        <v>68</v>
       </c>
       <c r="C87" t="s">
-        <v>374</v>
+        <v>69</v>
       </c>
       <c r="D87" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E87" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F87" t="s">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="G87" t="s">
-        <v>170</v>
+        <v>31</v>
       </c>
       <c r="H87" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="I87" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J87" t="s">
-        <v>196</v>
+        <v>376</v>
       </c>
       <c r="K87" t="s">
-        <v>46</v>
+        <v>377</v>
       </c>
       <c r="L87" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M87" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="N87" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O87" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B88" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="C88" t="s">
-        <v>212</v>
+        <v>245</v>
       </c>
       <c r="D88" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E88" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F88" t="s">
-        <v>254</v>
+        <v>93</v>
       </c>
       <c r="G88" t="s">
-        <v>377</v>
+        <v>31</v>
       </c>
       <c r="H88" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="I88" t="s">
         <v>23</v>
       </c>
       <c r="J88" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K88" t="s">
-        <v>256</v>
+        <v>381</v>
       </c>
       <c r="L88" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M88" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="N88" t="s">
-        <v>379</v>
+        <v>26</v>
       </c>
       <c r="O88" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B89" t="s">
-        <v>16</v>
+        <v>236</v>
       </c>
       <c r="C89" t="s">
-        <v>17</v>
+        <v>237</v>
       </c>
       <c r="D89" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="E89" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F89" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="G89" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H89" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="I89" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J89" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="K89" t="s">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="L89" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M89" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N89" t="s">
-        <v>21</v>
+        <v>385</v>
       </c>
       <c r="O89" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B90" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="C90" t="s">
-        <v>385</v>
+        <v>169</v>
       </c>
       <c r="D90" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E90" t="s">
         <v>19</v>
       </c>
       <c r="F90" t="s">
-        <v>43</v>
+        <v>170</v>
       </c>
       <c r="G90" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H90" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="I90" t="s">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="J90" t="s">
-        <v>176</v>
+        <v>388</v>
       </c>
       <c r="K90" t="s">
-        <v>386</v>
+        <v>90</v>
       </c>
       <c r="L90" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M90" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N90" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O90" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B91" t="s">
-        <v>389</v>
+        <v>49</v>
       </c>
       <c r="C91" t="s">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="D91" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E91" t="s">
         <v>19</v>
       </c>
       <c r="F91" t="s">
-        <v>43</v>
+        <v>170</v>
       </c>
       <c r="G91" t="s">
-        <v>390</v>
+        <v>31</v>
       </c>
       <c r="H91" t="s">
         <v>22</v>
@@ -5859,42 +5886,42 @@
         <v>391</v>
       </c>
       <c r="K91" t="s">
+        <v>178</v>
+      </c>
+      <c r="L91" t="s">
+        <v>26</v>
+      </c>
+      <c r="M91" t="s">
+        <v>26</v>
+      </c>
+      <c r="N91" t="s">
+        <v>26</v>
+      </c>
+      <c r="O91" t="s">
         <v>392</v>
-      </c>
-      <c r="L91" t="s">
-        <v>21</v>
-      </c>
-      <c r="M91" t="s">
-        <v>21</v>
-      </c>
-      <c r="N91" t="s">
-        <v>21</v>
-      </c>
-      <c r="O91" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B92" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C92" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D92" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E92" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F92" t="s">
-        <v>135</v>
+        <v>30</v>
       </c>
       <c r="G92" t="s">
-        <v>170</v>
+        <v>302</v>
       </c>
       <c r="H92" t="s">
         <v>22</v>
@@ -5903,33 +5930,33 @@
         <v>23</v>
       </c>
       <c r="J92" t="s">
-        <v>395</v>
+        <v>310</v>
       </c>
       <c r="K92" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="L92" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="M92" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N92" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O92" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B93" t="s">
-        <v>16</v>
+        <v>168</v>
       </c>
       <c r="C93" t="s">
-        <v>17</v>
+        <v>169</v>
       </c>
       <c r="D93" t="s">
         <v>18</v>
@@ -5938,34 +5965,175 @@
         <v>19</v>
       </c>
       <c r="F93" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="G93" t="s">
+        <v>31</v>
+      </c>
+      <c r="H93" t="s">
+        <v>88</v>
+      </c>
+      <c r="I93" t="s">
+        <v>155</v>
+      </c>
+      <c r="J93" t="s">
+        <v>396</v>
+      </c>
+      <c r="K93" t="s">
+        <v>239</v>
+      </c>
+      <c r="L93" t="s">
+        <v>26</v>
+      </c>
+      <c r="M93" t="s">
+        <v>26</v>
+      </c>
+      <c r="N93" t="s">
+        <v>26</v>
+      </c>
+      <c r="O93" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>398</v>
       </c>
-      <c r="H93" t="s">
+      <c r="B94" t="s">
+        <v>315</v>
+      </c>
+      <c r="C94" t="s">
+        <v>26</v>
+      </c>
+      <c r="D94" t="s">
+        <v>26</v>
+      </c>
+      <c r="E94" t="s">
+        <v>19</v>
+      </c>
+      <c r="F94" t="s">
+        <v>30</v>
+      </c>
+      <c r="G94" t="s">
+        <v>31</v>
+      </c>
+      <c r="H94" t="s">
         <v>22</v>
       </c>
-      <c r="I93" t="s">
+      <c r="I94" t="s">
+        <v>26</v>
+      </c>
+      <c r="J94" t="s">
+        <v>399</v>
+      </c>
+      <c r="K94" t="s">
+        <v>184</v>
+      </c>
+      <c r="L94" t="s">
+        <v>26</v>
+      </c>
+      <c r="M94" t="s">
+        <v>26</v>
+      </c>
+      <c r="N94" t="s">
+        <v>26</v>
+      </c>
+      <c r="O94" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>401</v>
+      </c>
+      <c r="B95" t="s">
+        <v>402</v>
+      </c>
+      <c r="C95" t="s">
+        <v>403</v>
+      </c>
+      <c r="D95" t="s">
+        <v>38</v>
+      </c>
+      <c r="E95" t="s">
+        <v>19</v>
+      </c>
+      <c r="F95" t="s">
+        <v>93</v>
+      </c>
+      <c r="G95" t="s">
+        <v>204</v>
+      </c>
+      <c r="H95" t="s">
+        <v>88</v>
+      </c>
+      <c r="I95" t="s">
+        <v>26</v>
+      </c>
+      <c r="J95" t="s">
+        <v>230</v>
+      </c>
+      <c r="K95" t="s">
+        <v>90</v>
+      </c>
+      <c r="L95" t="s">
+        <v>26</v>
+      </c>
+      <c r="M95" t="s">
+        <v>96</v>
+      </c>
+      <c r="N95" t="s">
+        <v>26</v>
+      </c>
+      <c r="O95" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>405</v>
+      </c>
+      <c r="B96" t="s">
+        <v>79</v>
+      </c>
+      <c r="C96" t="s">
+        <v>245</v>
+      </c>
+      <c r="D96" t="s">
+        <v>38</v>
+      </c>
+      <c r="E96" t="s">
+        <v>39</v>
+      </c>
+      <c r="F96" t="s">
+        <v>43</v>
+      </c>
+      <c r="G96" t="s">
+        <v>406</v>
+      </c>
+      <c r="H96" t="s">
+        <v>88</v>
+      </c>
+      <c r="I96" t="s">
         <v>23</v>
       </c>
-      <c r="J93" t="s">
-        <v>399</v>
-      </c>
-      <c r="K93" t="s">
-        <v>230</v>
-      </c>
-      <c r="L93" t="s">
-        <v>21</v>
-      </c>
-      <c r="M93" t="s">
-        <v>21</v>
-      </c>
-      <c r="N93" t="s">
-        <v>21</v>
-      </c>
-      <c r="O93" t="s">
-        <v>400</v>
+      <c r="J96" t="s">
+        <v>407</v>
+      </c>
+      <c r="K96" t="s">
+        <v>287</v>
+      </c>
+      <c r="L96" t="s">
+        <v>26</v>
+      </c>
+      <c r="M96" t="s">
+        <v>26</v>
+      </c>
+      <c r="N96" t="s">
+        <v>408</v>
+      </c>
+      <c r="O96" t="s">
+        <v>409</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEA9338F-6BCA-45F9-BC62-13CB330C2C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DFE0660-B827-4326-96FE-B28A784C4592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="420">
   <si>
     <t>Time</t>
   </si>
@@ -62,252 +62,510 @@
     <t>Event URL</t>
   </si>
   <si>
-    <t>06/25/2026 4:56:43 PM</t>
-  </si>
-  <si>
-    <t>694 - Heavy</t>
+    <t>07/02/2026 5:12:33 PM</t>
+  </si>
+  <si>
+    <t>629 - Heavy</t>
+  </si>
+  <si>
+    <t>Harley Tidwell</t>
+  </si>
+  <si>
+    <t>Active Drivers, Towing and Recovery</t>
+  </si>
+  <si>
+    <t>HAAS Alert, Heavy Haul</t>
+  </si>
+  <si>
+    <t>Heavy Speeding</t>
+  </si>
+  <si>
+    <t>Speed Sign Verified</t>
+  </si>
+  <si>
+    <t>Coached</t>
+  </si>
+  <si>
+    <t>Tim Neff Jr.</t>
+  </si>
+  <si>
+    <t>Creole Nature Trail All-American Road, Sulphur, LA, 70663</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544524e4-0e81-5c5c-a460-ff689cc97daf</t>
+  </si>
+  <si>
+    <t>07/02/2026 4:49:00 PM</t>
+  </si>
+  <si>
+    <t>669 - Heavy</t>
+  </si>
+  <si>
+    <t>Jason Walker</t>
+  </si>
+  <si>
+    <t>Mobile Usage</t>
+  </si>
+  <si>
+    <t>Wet Road, Light Traffic</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>Walden Road, Beaumont, TX, 77705</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544524ce-7fa8-58dd-910f-84869b9ab43f</t>
+  </si>
+  <si>
+    <t>07/02/2026 2:57:58 PM</t>
+  </si>
+  <si>
+    <t>641 - Heavy</t>
+  </si>
+  <si>
+    <t>Adam Johnson</t>
+  </si>
+  <si>
+    <t>Active Drivers, Heavy Haul</t>
+  </si>
+  <si>
+    <t>Following Distance</t>
+  </si>
+  <si>
+    <t>Moderate Traffic</t>
+  </si>
+  <si>
+    <t>I 10;US 90, Rose City, TX, 77662</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452468-d67a-595f-9e91-90e100223163</t>
+  </si>
+  <si>
+    <t>07/01/2026 12:35:29 PM</t>
+  </si>
+  <si>
+    <t>658 - Medium</t>
+  </si>
+  <si>
+    <t>Phillip Metz</t>
+  </si>
+  <si>
+    <t>HAAS Alert, Towing and Recovery</t>
+  </si>
+  <si>
+    <t>East Freeway, Channelview, TX, 77530</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451ec0-085f-56a4-bd8c-a28cd6a152aa</t>
+  </si>
+  <si>
+    <t>07/01/2026 12:08:06 PM</t>
+  </si>
+  <si>
+    <t>Obstructed Camera</t>
+  </si>
+  <si>
+    <t>North Main Street, Lumberton, TX, 77657</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451ea6-f54f-5727-9c92-1efb2075136e</t>
+  </si>
+  <si>
+    <t>07/01/2026 11:01:54 AM</t>
+  </si>
+  <si>
+    <t>680 - Medium</t>
+  </si>
+  <si>
+    <t>Jesus Carbajal</t>
+  </si>
+  <si>
+    <t>Parking Lot, Light Traffic</t>
+  </si>
+  <si>
+    <t>6155 Eastex Freeway Frontage Road, Beaumont, TX, 77706</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451e6a-5c5f-58a9-ae02-c239247de4e5</t>
+  </si>
+  <si>
+    <t>06/30/2026 6:33:35 PM</t>
+  </si>
+  <si>
+    <t>No Seat Belt</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>46733 I-10 Frontage Road, Winnie, TX, 77665</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451ae1-87c2-5135-b4f0-eab364728ee4</t>
+  </si>
+  <si>
+    <t>06/30/2026 3:45:32 PM</t>
+  </si>
+  <si>
+    <t>659 - Heavy</t>
+  </si>
+  <si>
+    <t>Thomas Neff III</t>
+  </si>
+  <si>
+    <t>I 10, Beaumont, TX, 77705</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451a47-ad87-5fb7-a6d7-1bf798bc9f48</t>
+  </si>
+  <si>
+    <t>06/30/2026 1:43:51 PM</t>
+  </si>
+  <si>
+    <t>Emergency Lights, Speed Sign Verified</t>
+  </si>
+  <si>
+    <t>Port Arthur Road, Port Arthur, TX, 77705</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544519d8-4452-5ca8-a5d4-202c1c203857</t>
+  </si>
+  <si>
+    <t>06/30/2026 2:25:53 AM</t>
+  </si>
+  <si>
+    <t>667 - Medium</t>
+  </si>
+  <si>
+    <t>Jeremy Myers</t>
+  </si>
+  <si>
+    <t>Towing and Recovery</t>
+  </si>
+  <si>
+    <t>Drowsiness</t>
+  </si>
+  <si>
+    <t>Moderately Drowsy, Construction, Light Traffic, Night</t>
+  </si>
+  <si>
+    <t>US 69;US 96;US 287, Loeb, TX, 77657</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445176b-900a-5030-9c5c-f45149ae21dc</t>
+  </si>
+  <si>
+    <t>06/29/2026 6:45:25 PM</t>
+  </si>
+  <si>
+    <t>Severe Speeding</t>
+  </si>
+  <si>
+    <t>TX 124, Stowell, TX, 77661</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544515c6-0006-56ad-b973-19cc55a23aac</t>
+  </si>
+  <si>
+    <t>06/29/2026 11:23:34 AM</t>
+  </si>
+  <si>
+    <t>646 - Medium</t>
+  </si>
+  <si>
+    <t>US 69;US 96;US 287, Loeb, TX</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451431-78bb-5436-96d6-3c70d67fb881</t>
+  </si>
+  <si>
+    <t>06/29/2026 10:19:27 AM</t>
+  </si>
+  <si>
+    <t>Construction, Light Traffic</t>
+  </si>
+  <si>
+    <t>North Dorman Road, 4.8 mi NNE Bridge City, Orange County, TX, 77630</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544513f6-c68b-542c-9f35-22427550e8bd</t>
+  </si>
+  <si>
+    <t>06/29/2026 9:38:44 AM</t>
+  </si>
+  <si>
+    <t>Decker Drive, Baytown, TX, 77562</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544513d1-8033-5ca3-8ee4-f53cff58f76b</t>
+  </si>
+  <si>
+    <t>06/29/2026 8:54:50 AM</t>
+  </si>
+  <si>
+    <t>US 90, Nome, TX, 77629</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544513a9-4e6a-5777-b020-ae490b0ad885</t>
+  </si>
+  <si>
+    <t>06/28/2026 8:19:03 PM</t>
+  </si>
+  <si>
+    <t>683 - Heavy</t>
+  </si>
+  <si>
+    <t>Gary Worley</t>
+  </si>
+  <si>
+    <t>Eddie Bowden</t>
+  </si>
+  <si>
+    <t>US 90, China, TX, 77613</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544510f5-5d50-549b-869b-bddc80251d19</t>
+  </si>
+  <si>
+    <t>06/27/2026 5:25:06 PM</t>
+  </si>
+  <si>
+    <t>685 - Medium</t>
+  </si>
+  <si>
+    <t>Paul Kunze Jr</t>
+  </si>
+  <si>
+    <t>Inattentive Driving</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450b2f-be05-543b-acec-2c7c24ae13ce</t>
+  </si>
+  <si>
+    <t>06/26/2026 3:30:01 PM</t>
+  </si>
+  <si>
+    <t>US 69;US 96;US 287, Beaumont, TX, 77701</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544505a0-0548-52df-90bb-6baf18f84b57</t>
+  </si>
+  <si>
+    <t>06/26/2026 3:27:58 PM</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445059e-2881-5100-83b4-1f5b093312d4</t>
+  </si>
+  <si>
+    <t>06/25/2026 4:46:02 PM</t>
+  </si>
+  <si>
+    <t>Fannett Road, Beaumont, TX, 77705</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544500bf-4275-5ded-85e2-3ee8f4e6d92b</t>
+  </si>
+  <si>
+    <t>06/25/2026 12:16:55 PM</t>
+  </si>
+  <si>
+    <t>I 10, Winnie, TX</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ffc8-df6a-5dea-9370-f13b79e392c6</t>
+  </si>
+  <si>
+    <t>06/25/2026 11:15:11 AM</t>
+  </si>
+  <si>
+    <t>Harsh Brake</t>
+  </si>
+  <si>
+    <t>East Freeway Frontage Road, Houston, TX, 77020</t>
+  </si>
+  <si>
+    <t>0.67</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ff90-5d57-5dc0-a571-4d8c6dcde945</t>
+  </si>
+  <si>
+    <t>06/25/2026 10:09:43 AM</t>
+  </si>
+  <si>
+    <t>668 - Light</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ff54-6b07-5d1d-8dc0-8053502f47ef</t>
+  </si>
+  <si>
+    <t>06/24/2026 1:15:17 PM</t>
+  </si>
+  <si>
+    <t>Creole Nature Trail All-American Road, Calcasieu Parish, LA</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fad7-f51b-528d-8ce9-9658a4c0b9e5</t>
+  </si>
+  <si>
+    <t>06/23/2026 11:02:05 AM</t>
+  </si>
+  <si>
+    <t>I 10 Frontage Road, 24.6 mi SE Liberty, Chambers County, TX</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>0.55</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f537-a7f7-5b50-be7d-fcffb700b16d</t>
+  </si>
+  <si>
+    <t>06/22/2026 11:26:05 AM</t>
+  </si>
+  <si>
+    <t>692 - Heavy</t>
+  </si>
+  <si>
+    <t>William Foley</t>
+  </si>
+  <si>
+    <t>I 45, Madisonville, TX, 77864</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f027-4165-5f24-8d32-d9f65658b1d2</t>
+  </si>
+  <si>
+    <t>06/19/2026 4:15:44 PM</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e1bd-5e83-597e-995e-9c0f9e74b244</t>
+  </si>
+  <si>
+    <t>06/18/2026 4:34:01 PM</t>
+  </si>
+  <si>
+    <t>Interstate 10 South Frontage Road, Beaumont, TX, 77702</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445dca7-bd7e-50f6-b2da-d0e7f3669228</t>
+  </si>
+  <si>
+    <t>06/18/2026 8:05:45 AM</t>
+  </si>
+  <si>
+    <t>Christopher Marcantel</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445dad6-6838-50e1-a08f-721a3f1f36df</t>
+  </si>
+  <si>
+    <t>06/17/2026 5:02:17 PM</t>
   </si>
   <si>
     <t>Dwayne Manuel</t>
   </si>
   <si>
-    <t>Active Drivers, Heavy Haul</t>
-  </si>
-  <si>
-    <t>HAAS Alert, Heavy Haul</t>
-  </si>
-  <si>
-    <t>Heavy Speeding</t>
-  </si>
-  <si>
-    <t>Speed Sign Verified</t>
-  </si>
-  <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
-    <t>Tim Neff Jr.</t>
-  </si>
-  <si>
-    <t>I 10, Winnie, TX</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544500c9-09b5-5d26-bf1c-4f5a5e59e627</t>
-  </si>
-  <si>
-    <t>06/25/2026 4:46:02 PM</t>
-  </si>
-  <si>
-    <t>629 - Heavy</t>
-  </si>
-  <si>
-    <t>Mobile Usage</t>
-  </si>
-  <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
-    <t>Fannett Road, Beaumont, TX, 77705</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544500bf-4275-5ded-85e2-3ee8f4e6d92b</t>
-  </si>
-  <si>
-    <t>06/25/2026 12:16:55 PM</t>
-  </si>
-  <si>
-    <t>680 - Medium</t>
-  </si>
-  <si>
-    <t>Jesus Carbajal</t>
-  </si>
-  <si>
-    <t>Active Drivers, Towing and Recovery</t>
-  </si>
-  <si>
-    <t>HAAS Alert, Towing and Recovery</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ffc8-df6a-5dea-9370-f13b79e392c6</t>
-  </si>
-  <si>
-    <t>06/25/2026 11:15:11 AM</t>
-  </si>
-  <si>
-    <t>Harsh Brake</t>
-  </si>
-  <si>
-    <t>East Freeway Frontage Road, Houston, TX, 77020</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>0.67</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ff90-5d57-5dc0-a571-4d8c6dcde945</t>
-  </si>
-  <si>
-    <t>06/24/2026 1:15:17 PM</t>
-  </si>
-  <si>
-    <t>669 - Heavy</t>
-  </si>
-  <si>
-    <t>Jason Walker</t>
-  </si>
-  <si>
-    <t>Following Distance</t>
-  </si>
-  <si>
-    <t>Moderate Traffic</t>
-  </si>
-  <si>
-    <t>Creole Nature Trail All-American Road, Calcasieu Parish, LA</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fad7-f51b-528d-8ce9-9658a4c0b9e5</t>
-  </si>
-  <si>
-    <t>06/23/2026 11:02:05 AM</t>
-  </si>
-  <si>
-    <t>I 10 Frontage Road, 24.6 mi SE Liberty, Chambers County, TX</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>0.55</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f537-a7f7-5b50-be7d-fcffb700b16d</t>
-  </si>
-  <si>
-    <t>06/22/2026 11:26:05 AM</t>
-  </si>
-  <si>
-    <t>692 - Heavy</t>
-  </si>
-  <si>
-    <t>William Foley</t>
-  </si>
-  <si>
-    <t>I 45, Madisonville, TX, 77864</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f027-4165-5f24-8d32-d9f65658b1d2</t>
-  </si>
-  <si>
-    <t>06/19/2026 4:15:44 PM</t>
-  </si>
-  <si>
-    <t>658 - Medium</t>
-  </si>
-  <si>
-    <t>Paul Kunze Jr</t>
-  </si>
-  <si>
-    <t>US 69;US 96;US 287, Beaumont, TX, 77701</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e1bd-5e83-597e-995e-9c0f9e74b244</t>
-  </si>
-  <si>
-    <t>06/18/2026 4:34:01 PM</t>
-  </si>
-  <si>
-    <t>Obstructed Camera</t>
-  </si>
-  <si>
-    <t>Interstate 10 South Frontage Road, Beaumont, TX, 77702</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445dca7-bd7e-50f6-b2da-d0e7f3669228</t>
-  </si>
-  <si>
-    <t>06/18/2026 8:05:45 AM</t>
-  </si>
-  <si>
-    <t>685 - Medium</t>
-  </si>
-  <si>
-    <t>Christopher Marcantel</t>
-  </si>
-  <si>
-    <t>Towing and Recovery</t>
-  </si>
-  <si>
-    <t>Severe Speeding</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445dad6-6838-50e1-a08f-721a3f1f36df</t>
-  </si>
-  <si>
-    <t>06/17/2026 5:02:17 PM</t>
-  </si>
-  <si>
-    <t>683 - Heavy</t>
-  </si>
-  <si>
-    <t>Coached</t>
-  </si>
-  <si>
     <t>H O Mills Highway, Port Arthur, TX</t>
   </si>
   <si>
-    <t>32</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d79b-44e0-5b5f-afa1-10741c645e86</t>
   </si>
   <si>
     <t>06/17/2026 11:28:09 AM</t>
   </si>
   <si>
-    <t>Inattentive Driving</t>
-  </si>
-  <si>
     <t>College Street, Beaumont, TX, 77702</t>
   </si>
   <si>
     <t>45</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d669-5d00-570d-892c-3b3bcb44e34d</t>
   </si>
   <si>
@@ -317,9 +575,6 @@
     <t>5230 North Major Drive, Beaumont, TX, 77705</t>
   </si>
   <si>
-    <t>35</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cd7d-73a6-51c3-baf6-41a38469fe10</t>
   </si>
   <si>
@@ -380,21 +635,12 @@
     <t>06/13/2026 4:18:06 PM</t>
   </si>
   <si>
-    <t>East Freeway, Channelview, TX, 77530</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c2d9-604f-59f0-87e5-6a5c05c198bc</t>
   </si>
   <si>
     <t>06/12/2026 9:27:53 AM</t>
   </si>
   <si>
-    <t>North Dorman Road, 4.8 mi NNE Bridge City, Orange County, TX, 77630</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bc3b-756c-5d9e-9d81-2830d4d259b7</t>
   </si>
   <si>
@@ -419,18 +665,12 @@
     <t>06/12/2026 2:36:49 AM</t>
   </si>
   <si>
-    <t>I 10, Beaumont, TX, 77705</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bac3-1a90-5376-b4c0-879059363b9a</t>
   </si>
   <si>
     <t>06/11/2026 10:09:35 PM</t>
   </si>
   <si>
-    <t>Drowsiness</t>
-  </si>
-  <si>
     <t>Moderately Drowsy, Light Traffic, Night</t>
   </si>
   <si>
@@ -455,12 +695,6 @@
     <t>06/10/2026 10:04:03 AM</t>
   </si>
   <si>
-    <t>659 - Heavy</t>
-  </si>
-  <si>
-    <t>Thomas Neff III</t>
-  </si>
-  <si>
     <t>5020 Fannett Road, Beaumont, TX, 77705</t>
   </si>
   <si>
@@ -482,9 +716,6 @@
     <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
   </si>
   <si>
-    <t>Eddie Bowden</t>
-  </si>
-  <si>
     <t>I 10, Welsh, LA, 70581</t>
   </si>
   <si>
@@ -512,9 +743,6 @@
     <t>06/04/2026 2:15:03 PM</t>
   </si>
   <si>
-    <t>Wet Road, Light Traffic</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445940f-7e14-5c0f-aa68-07d221d9e214</t>
   </si>
   <si>
@@ -524,12 +752,6 @@
     <t>632 - Heavy</t>
   </si>
   <si>
-    <t>Gary Worley</t>
-  </si>
-  <si>
-    <t>No Seat Belt</t>
-  </si>
-  <si>
     <t>Hufsmith Kohrville Road, 4.1 mi SSE Tomball, Harris County, TX, 77375</t>
   </si>
   <si>
@@ -542,9 +764,6 @@
     <t>I 10, Seguin, TX, 78638</t>
   </si>
   <si>
-    <t>69</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544574d4-f86a-51ab-8240-5abf48d2eb45</t>
   </si>
   <si>
@@ -569,9 +788,6 @@
     <t>Active Drivers, HAAS Alert, Heavy Haul, Towing and Recovery</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456fea-dac1-5b56-beb5-7a334db4549a</t>
   </si>
   <si>
@@ -650,9 +866,6 @@
     <t>I 10;US 90, Vidor, TX, 77662</t>
   </si>
   <si>
-    <t>38</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544533bc-e027-5557-b78e-89930845d14b</t>
   </si>
   <si>
@@ -662,9 +875,6 @@
     <t>634 - Heavy</t>
   </si>
   <si>
-    <t>US 90, China, TX, 77613</t>
-  </si>
-  <si>
     <t>33</t>
   </si>
   <si>
@@ -725,12 +935,6 @@
     <t>05/03/2026 7:49:58 PM</t>
   </si>
   <si>
-    <t>667 - Medium</t>
-  </si>
-  <si>
-    <t>Jeremy Myers</t>
-  </si>
-  <si>
     <t>362 Simmons Road, 1.9 mi N Vidor, Orange County, TX, 77662</t>
   </si>
   <si>
@@ -752,9 +956,6 @@
     <t>05/01/2026 6:35:06 PM</t>
   </si>
   <si>
-    <t>Phillip Metz</t>
-  </si>
-  <si>
     <t>6425 Highway 347, Beaumont, TX, 77705</t>
   </si>
   <si>
@@ -803,9 +1004,6 @@
     <t>South Major Drive, Beaumont, TX, 77705</t>
   </si>
   <si>
-    <t>27</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d5aa-4dd2-5073-adcd-a728d6e756c6</t>
   </si>
   <si>
@@ -914,18 +1112,12 @@
     <t>04/20/2026 10:49:13 AM</t>
   </si>
   <si>
-    <t>56</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ab94-df4e-5e43-8f70-06189ab78268</t>
   </si>
   <si>
     <t>04/18/2026 8:25:57 AM</t>
   </si>
   <si>
-    <t>Construction, Light Traffic</t>
-  </si>
-  <si>
     <t>I 10, Beaumont, TX, 77702</t>
   </si>
   <si>
@@ -1013,9 +1205,6 @@
     <t>04/13/2026 10:43:50 AM</t>
   </si>
   <si>
-    <t>668 - Light</t>
-  </si>
-  <si>
     <t>East Freeway, Houston, TX, 77020</t>
   </si>
   <si>
@@ -1058,12 +1247,6 @@
     <t>04/09/2026 2:37:19 PM</t>
   </si>
   <si>
-    <t>641 - Heavy</t>
-  </si>
-  <si>
-    <t>Adam Johnson</t>
-  </si>
-  <si>
     <t>7360 Garth Street, Cheek, TX, 77705</t>
   </si>
   <si>
@@ -1092,159 +1275,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456349-e5b4-55ac-a43b-944299eef0c4</t>
-  </si>
-  <si>
-    <t>04/04/2026 3:30:47 PM</t>
-  </si>
-  <si>
-    <t>Wet Road, Construction, Light Traffic, Raining</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455a30-e5ca-5116-bf04-94e46dcd707c</t>
-  </si>
-  <si>
-    <t>04/03/2026 8:23:50 AM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455383-a777-5e06-acea-9d6c785bb48e</t>
-  </si>
-  <si>
-    <t>04/02/2026 7:07:15 PM</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544550aa-5eec-5d3f-ba8e-58709543895d</t>
-  </si>
-  <si>
-    <t>04/02/2026 10:12:18 AM</t>
-  </si>
-  <si>
-    <t>I 10;TX 130, Seguin, TX, 78156</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454ec0-9872-5236-a722-8479419e97c6</t>
-  </si>
-  <si>
-    <t>04/02/2026 8:23:33 AM</t>
-  </si>
-  <si>
-    <t>I 10, 7.4 mi NW Kerrville, Kerr County, TX, 78025:78631</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454e5d-0a80-52f2-800d-6d1920f58de1</t>
-  </si>
-  <si>
-    <t>04/01/2026 6:33:25 PM</t>
-  </si>
-  <si>
-    <t>I 10, 66.6 mi S San Angelo, Sutton County, TX, 76950</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454b65-05b1-5dfd-b7bd-526bc0c582eb</t>
-  </si>
-  <si>
-    <t>04/01/2026 6:31:15 PM</t>
-  </si>
-  <si>
-    <t>Highway 69 Frontage Road, Loeb, TX, 77567</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454b63-0bf8-539f-a255-8c9b76b7b752</t>
-  </si>
-  <si>
-    <t>04/01/2026 5:41:14 PM</t>
-  </si>
-  <si>
-    <t>908 South Main Street, Vidor, TX, 77662</t>
-  </si>
-  <si>
-    <t>0.52</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454b35-3f81-5af1-ac81-e3f9afda2747</t>
-  </si>
-  <si>
-    <t>04/01/2026 12:52:39 PM</t>
-  </si>
-  <si>
-    <t>Folsom Drive, Beaumont, TX, 77706</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454a2d-0b87-5fb5-a920-705c56a6731e</t>
-  </si>
-  <si>
-    <t>04/01/2026 11:14:43 AM</t>
-  </si>
-  <si>
-    <t>299 3rd Street, Kountze, TX, 77625</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544549d3-61b9-58db-9eab-8eb3fed34996</t>
-  </si>
-  <si>
-    <t>03/31/2026 7:05:40 PM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445465c-3230-53bd-9134-409c7545bd21</t>
-  </si>
-  <si>
-    <t>03/31/2026 3:33:33 PM</t>
-  </si>
-  <si>
-    <t>9263 Hasting Field Road North, Pearland, TX, 77511</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454599-fd4e-5fc8-b9a7-5a6d8fc02784</t>
-  </si>
-  <si>
-    <t>03/31/2026 3:13:41 PM</t>
-  </si>
-  <si>
-    <t>US 96, Zion Hill, TX</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454587-d024-5358-89a5-f14a9b756111</t>
-  </si>
-  <si>
-    <t>03/31/2026 9:10:43 AM</t>
-  </si>
-  <si>
-    <t>607 - Heavy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tommy Scott </t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445443b-80c2-56be-a0b5-4ec2bfd564b2</t>
-  </si>
-  <si>
-    <t>03/31/2026 7:30:18 AM</t>
-  </si>
-  <si>
-    <t>Construction, Congested</t>
-  </si>
-  <si>
-    <t>1399 Eastex Freeway, Beaumont, TX, 77706</t>
-  </si>
-  <si>
-    <t>0.66</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544543df-906f-58b3-859c-3234287075ec</t>
   </si>
 </sst>
 </file>
@@ -1621,10 +1651,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O96"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O100"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1671,7 +1701,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -1718,7 +1748,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -1726,31 +1756,31 @@
         <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L3" t="s">
         <v>26</v>
@@ -1762,42 +1792,42 @@
         <v>26</v>
       </c>
       <c r="O3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I4" t="s">
         <v>23</v>
       </c>
       <c r="J4" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="K4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L4" t="s">
         <v>26</v>
@@ -1809,42 +1839,42 @@
         <v>26</v>
       </c>
       <c r="O4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
         <v>42</v>
       </c>
-      <c r="B5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I5" t="s">
         <v>23</v>
       </c>
       <c r="J5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="K5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L5" t="s">
         <v>26</v>
@@ -1853,45 +1883,45 @@
         <v>26</v>
       </c>
       <c r="N5" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="O5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G6" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I6" t="s">
         <v>23</v>
       </c>
       <c r="J6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L6" t="s">
         <v>26</v>
@@ -1903,42 +1933,42 @@
         <v>26</v>
       </c>
       <c r="O6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I7" t="s">
         <v>23</v>
       </c>
       <c r="J7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K7" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="L7" t="s">
         <v>26</v>
@@ -1947,21 +1977,21 @@
         <v>26</v>
       </c>
       <c r="N7" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="O7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
         <v>18</v>
@@ -1970,22 +2000,22 @@
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="G8" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="H8" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I8" t="s">
         <v>23</v>
       </c>
       <c r="J8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L8" t="s">
         <v>26</v>
@@ -1997,42 +2027,42 @@
         <v>26</v>
       </c>
       <c r="O8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G9" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H9" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I9" t="s">
         <v>23</v>
       </c>
       <c r="J9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="L9" t="s">
         <v>26</v>
@@ -2044,42 +2074,42 @@
         <v>26</v>
       </c>
       <c r="O9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="H10" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L10" t="s">
         <v>26</v>
@@ -2091,183 +2121,183 @@
         <v>26</v>
       </c>
       <c r="O10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G11" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="H11" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I11" t="s">
         <v>26</v>
       </c>
       <c r="J11" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="K11" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="L11" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="M11" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="N11" t="s">
         <v>26</v>
       </c>
       <c r="O11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="G12" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H12" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="I12" t="s">
         <v>23</v>
       </c>
       <c r="J12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K12" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="L12" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="M12" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="N12" t="s">
         <v>26</v>
       </c>
       <c r="O12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F13" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="G13" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="H13" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I13" t="s">
         <v>23</v>
       </c>
       <c r="J13" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="K13" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="L13" t="s">
         <v>26</v>
       </c>
       <c r="M13" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="N13" t="s">
         <v>26</v>
       </c>
       <c r="O13" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="G14" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="H14" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I14" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="K14" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L14" t="s">
         <v>26</v>
@@ -2279,42 +2309,42 @@
         <v>26</v>
       </c>
       <c r="O14" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="G15" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="H15" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I15" t="s">
         <v>23</v>
       </c>
       <c r="J15" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="K15" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L15" t="s">
         <v>26</v>
@@ -2326,89 +2356,89 @@
         <v>26</v>
       </c>
       <c r="O15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F16" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="G16" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" t="s">
+        <v>33</v>
+      </c>
+      <c r="I16" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L16" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" t="s">
+        <v>26</v>
+      </c>
+      <c r="N16" t="s">
+        <v>26</v>
+      </c>
+      <c r="O16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" t="s">
         <v>31</v>
       </c>
-      <c r="H16" t="s">
-        <v>88</v>
-      </c>
-      <c r="I16" t="s">
-        <v>26</v>
-      </c>
-      <c r="J16" t="s">
-        <v>108</v>
-      </c>
-      <c r="K16" t="s">
-        <v>109</v>
-      </c>
-      <c r="L16" t="s">
-        <v>26</v>
-      </c>
-      <c r="M16" t="s">
-        <v>26</v>
-      </c>
-      <c r="N16" t="s">
-        <v>26</v>
-      </c>
-      <c r="O16" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>111</v>
-      </c>
-      <c r="B17" t="s">
-        <v>112</v>
-      </c>
-      <c r="C17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" t="s">
-        <v>30</v>
-      </c>
       <c r="G17" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I17" t="s">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="J17" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="K17" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="L17" t="s">
         <v>26</v>
@@ -2420,183 +2450,183 @@
         <v>26</v>
       </c>
       <c r="O17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E18" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F18" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="G18" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="H18" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I18" t="s">
         <v>23</v>
       </c>
       <c r="J18" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="K18" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="L18" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="M18" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="N18" t="s">
         <v>26</v>
       </c>
       <c r="O18" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="E19" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F19" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" t="s">
+        <v>33</v>
+      </c>
+      <c r="I19" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" t="s">
+        <v>129</v>
+      </c>
+      <c r="K19" t="s">
+        <v>130</v>
+      </c>
+      <c r="L19" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" t="s">
+        <v>26</v>
+      </c>
+      <c r="N19" t="s">
+        <v>26</v>
+      </c>
+      <c r="O19" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>132</v>
+      </c>
+      <c r="B20" t="s">
+        <v>122</v>
+      </c>
+      <c r="C20" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F20" t="s">
         <v>31</v>
       </c>
-      <c r="H19" t="s">
-        <v>88</v>
-      </c>
-      <c r="I19" t="s">
-        <v>26</v>
-      </c>
-      <c r="J19" t="s">
-        <v>118</v>
-      </c>
-      <c r="K19" t="s">
-        <v>76</v>
-      </c>
-      <c r="L19" t="s">
-        <v>26</v>
-      </c>
-      <c r="M19" t="s">
-        <v>26</v>
-      </c>
-      <c r="N19" t="s">
-        <v>26</v>
-      </c>
-      <c r="O19" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>120</v>
-      </c>
-      <c r="B20" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" t="s">
-        <v>39</v>
-      </c>
-      <c r="F20" t="s">
-        <v>93</v>
-      </c>
       <c r="G20" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="H20" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="I20" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J20" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="K20" t="s">
-        <v>33</v>
+        <v>133</v>
       </c>
       <c r="L20" t="s">
         <v>26</v>
       </c>
       <c r="M20" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="N20" t="s">
         <v>26</v>
       </c>
       <c r="O20" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B21" t="s">
-        <v>112</v>
+        <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E21" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G21" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="H21" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I21" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J21" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="K21" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="L21" t="s">
         <v>26</v>
@@ -2608,42 +2638,42 @@
         <v>26</v>
       </c>
       <c r="O21" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E22" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="G22" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H22" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I22" t="s">
         <v>23</v>
       </c>
       <c r="J22" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="K22" t="s">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="L22" t="s">
         <v>26</v>
@@ -2655,62 +2685,62 @@
         <v>26</v>
       </c>
       <c r="O22" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="D23" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E23" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F23" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="G23" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="H23" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I23" t="s">
         <v>23</v>
       </c>
       <c r="J23" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="K23" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="L23" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="M23" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="N23" t="s">
-        <v>26</v>
+        <v>146</v>
       </c>
       <c r="O23" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="C24" t="s">
         <v>26</v>
@@ -2719,72 +2749,72 @@
         <v>26</v>
       </c>
       <c r="E24" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F24" t="s">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="G24" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H24" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I24" t="s">
         <v>26</v>
       </c>
       <c r="J24" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K24" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="L24" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="M24" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="N24" t="s">
         <v>26</v>
       </c>
       <c r="O24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E25" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="G25" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="H25" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I25" t="s">
         <v>23</v>
       </c>
       <c r="J25" t="s">
-        <v>32</v>
+        <v>152</v>
       </c>
       <c r="K25" t="s">
-        <v>95</v>
+        <v>153</v>
       </c>
       <c r="L25" t="s">
         <v>26</v>
@@ -2796,77 +2826,77 @@
         <v>26</v>
       </c>
       <c r="O25" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C26" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E26" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F26" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="G26" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="H26" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I26" t="s">
         <v>23</v>
       </c>
       <c r="J26" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="K26" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="L26" t="s">
-        <v>143</v>
+        <v>26</v>
       </c>
       <c r="M26" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="N26" t="s">
-        <v>26</v>
+        <v>158</v>
       </c>
       <c r="O26" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="B27" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="C27" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G27" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="H27" t="s">
         <v>22</v>
@@ -2875,10 +2905,10 @@
         <v>23</v>
       </c>
       <c r="J27" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="K27" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="L27" t="s">
         <v>26</v>
@@ -2890,42 +2920,42 @@
         <v>26</v>
       </c>
       <c r="O27" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B28" t="s">
-        <v>152</v>
+        <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="D28" t="s">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="F28" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="G28" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="H28" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="I28" t="s">
-        <v>155</v>
+        <v>23</v>
       </c>
       <c r="J28" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="K28" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="L28" t="s">
         <v>26</v>
@@ -2937,42 +2967,42 @@
         <v>26</v>
       </c>
       <c r="O28" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="B29" t="s">
-        <v>159</v>
+        <v>59</v>
       </c>
       <c r="C29" t="s">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E29" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F29" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="G29" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H29" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I29" t="s">
         <v>23</v>
       </c>
       <c r="J29" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="K29" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="L29" t="s">
         <v>26</v>
@@ -2984,89 +3014,89 @@
         <v>26</v>
       </c>
       <c r="O29" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="B30" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C30" t="s">
-        <v>26</v>
+        <v>173</v>
       </c>
       <c r="D30" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="E30" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F30" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="G30" t="s">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="H30" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I30" t="s">
         <v>26</v>
       </c>
       <c r="J30" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="K30" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="L30" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="M30" t="s">
-        <v>26</v>
+        <v>174</v>
       </c>
       <c r="N30" t="s">
         <v>26</v>
       </c>
       <c r="O30" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B31" t="s">
-        <v>168</v>
+        <v>115</v>
       </c>
       <c r="C31" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="D31" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>170</v>
+        <v>31</v>
       </c>
       <c r="G31" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="H31" t="s">
         <v>22</v>
       </c>
       <c r="I31" t="s">
-        <v>155</v>
+        <v>23</v>
       </c>
       <c r="J31" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="K31" t="s">
-        <v>149</v>
+        <v>68</v>
       </c>
       <c r="L31" t="s">
         <v>26</v>
@@ -3078,89 +3108,89 @@
         <v>26</v>
       </c>
       <c r="O31" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
       <c r="C32" t="s">
-        <v>153</v>
+        <v>60</v>
       </c>
       <c r="D32" t="s">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="E32" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="F32" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="G32" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="H32" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="I32" t="s">
-        <v>155</v>
+        <v>23</v>
       </c>
       <c r="J32" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="K32" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="L32" t="s">
         <v>26</v>
       </c>
       <c r="M32" t="s">
-        <v>26</v>
+        <v>126</v>
       </c>
       <c r="N32" t="s">
         <v>26</v>
       </c>
       <c r="O32" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B33" t="s">
-        <v>168</v>
+        <v>59</v>
       </c>
       <c r="C33" t="s">
-        <v>169</v>
+        <v>60</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
       </c>
       <c r="E33" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="F33" t="s">
-        <v>170</v>
+        <v>31</v>
       </c>
       <c r="G33" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="H33" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I33" t="s">
-        <v>155</v>
+        <v>23</v>
       </c>
       <c r="J33" t="s">
-        <v>94</v>
+        <v>185</v>
       </c>
       <c r="K33" t="s">
-        <v>178</v>
+        <v>35</v>
       </c>
       <c r="L33" t="s">
         <v>26</v>
@@ -3172,89 +3202,89 @@
         <v>26</v>
       </c>
       <c r="O33" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="B34" t="s">
-        <v>181</v>
+        <v>29</v>
       </c>
       <c r="C34" t="s">
-        <v>182</v>
+        <v>30</v>
       </c>
       <c r="D34" t="s">
-        <v>183</v>
+        <v>18</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
       </c>
       <c r="F34" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="G34" t="s">
+        <v>188</v>
+      </c>
+      <c r="H34" t="s">
+        <v>33</v>
+      </c>
+      <c r="I34" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" t="s">
+        <v>189</v>
+      </c>
+      <c r="K34" t="s">
+        <v>190</v>
+      </c>
+      <c r="L34" t="s">
+        <v>26</v>
+      </c>
+      <c r="M34" t="s">
+        <v>26</v>
+      </c>
+      <c r="N34" t="s">
+        <v>26</v>
+      </c>
+      <c r="O34" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>192</v>
+      </c>
+      <c r="B35" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" t="s">
+        <v>173</v>
+      </c>
+      <c r="D35" t="s">
+        <v>84</v>
+      </c>
+      <c r="E35" t="s">
+        <v>49</v>
+      </c>
+      <c r="F35" t="s">
         <v>31</v>
       </c>
-      <c r="H34" t="s">
-        <v>88</v>
-      </c>
-      <c r="I34" t="s">
-        <v>26</v>
-      </c>
-      <c r="J34" t="s">
-        <v>156</v>
-      </c>
-      <c r="K34" t="s">
-        <v>184</v>
-      </c>
-      <c r="L34" t="s">
-        <v>26</v>
-      </c>
-      <c r="M34" t="s">
-        <v>26</v>
-      </c>
-      <c r="N34" t="s">
-        <v>26</v>
-      </c>
-      <c r="O34" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>186</v>
-      </c>
-      <c r="B35" t="s">
-        <v>79</v>
-      </c>
-      <c r="C35" t="s">
-        <v>80</v>
-      </c>
-      <c r="D35" t="s">
-        <v>81</v>
-      </c>
-      <c r="E35" t="s">
-        <v>39</v>
-      </c>
-      <c r="F35" t="s">
-        <v>30</v>
-      </c>
       <c r="G35" t="s">
-        <v>187</v>
+        <v>66</v>
       </c>
       <c r="H35" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="I35" t="s">
         <v>26</v>
       </c>
       <c r="J35" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="K35" t="s">
-        <v>149</v>
+        <v>194</v>
       </c>
       <c r="L35" t="s">
         <v>26</v>
@@ -3266,42 +3296,42 @@
         <v>26</v>
       </c>
       <c r="O35" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B36" t="s">
+        <v>197</v>
+      </c>
+      <c r="C36" t="s">
+        <v>123</v>
+      </c>
+      <c r="D36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" t="s">
         <v>49</v>
       </c>
-      <c r="C36" t="s">
-        <v>50</v>
-      </c>
-      <c r="D36" t="s">
-        <v>38</v>
-      </c>
-      <c r="E36" t="s">
-        <v>19</v>
-      </c>
       <c r="F36" t="s">
-        <v>170</v>
+        <v>31</v>
       </c>
       <c r="G36" t="s">
-        <v>165</v>
+        <v>66</v>
       </c>
       <c r="H36" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I36" t="s">
         <v>23</v>
       </c>
       <c r="J36" t="s">
-        <v>32</v>
+        <v>136</v>
       </c>
       <c r="K36" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="L36" t="s">
         <v>26</v>
@@ -3313,183 +3343,183 @@
         <v>26</v>
       </c>
       <c r="O36" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="C37" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D37" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="E37" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F37" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="G37" t="s">
-        <v>187</v>
+        <v>26</v>
       </c>
       <c r="H37" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="I37" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J37" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="K37" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="L37" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="M37" t="s">
-        <v>26</v>
+        <v>174</v>
       </c>
       <c r="N37" t="s">
         <v>26</v>
       </c>
       <c r="O37" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="B38" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="C38" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="D38" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="E38" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="F38" t="s">
-        <v>170</v>
+        <v>31</v>
       </c>
       <c r="G38" t="s">
-        <v>165</v>
+        <v>66</v>
       </c>
       <c r="H38" t="s">
         <v>22</v>
       </c>
       <c r="I38" t="s">
+        <v>26</v>
+      </c>
+      <c r="J38" t="s">
+        <v>203</v>
+      </c>
+      <c r="K38" t="s">
+        <v>170</v>
+      </c>
+      <c r="L38" t="s">
+        <v>26</v>
+      </c>
+      <c r="M38" t="s">
+        <v>26</v>
+      </c>
+      <c r="N38" t="s">
+        <v>26</v>
+      </c>
+      <c r="O38" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>205</v>
+      </c>
+      <c r="B39" t="s">
+        <v>122</v>
+      </c>
+      <c r="C39" t="s">
+        <v>173</v>
+      </c>
+      <c r="D39" t="s">
+        <v>84</v>
+      </c>
+      <c r="E39" t="s">
+        <v>49</v>
+      </c>
+      <c r="F39" t="s">
+        <v>124</v>
+      </c>
+      <c r="G39" t="s">
+        <v>42</v>
+      </c>
+      <c r="H39" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" t="s">
+        <v>26</v>
+      </c>
+      <c r="J39" t="s">
+        <v>50</v>
+      </c>
+      <c r="K39" t="s">
+        <v>137</v>
+      </c>
+      <c r="L39" t="s">
+        <v>26</v>
+      </c>
+      <c r="M39" t="s">
+        <v>126</v>
+      </c>
+      <c r="N39" t="s">
+        <v>26</v>
+      </c>
+      <c r="O39" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>207</v>
+      </c>
+      <c r="B40" t="s">
+        <v>197</v>
+      </c>
+      <c r="C40" t="s">
+        <v>123</v>
+      </c>
+      <c r="D40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" t="s">
+        <v>49</v>
+      </c>
+      <c r="F40" t="s">
+        <v>31</v>
+      </c>
+      <c r="G40" t="s">
+        <v>66</v>
+      </c>
+      <c r="H40" t="s">
+        <v>33</v>
+      </c>
+      <c r="I40" t="s">
         <v>23</v>
       </c>
-      <c r="J38" t="s">
-        <v>196</v>
-      </c>
-      <c r="K38" t="s">
-        <v>197</v>
-      </c>
-      <c r="L38" t="s">
-        <v>26</v>
-      </c>
-      <c r="M38" t="s">
-        <v>26</v>
-      </c>
-      <c r="N38" t="s">
-        <v>26</v>
-      </c>
-      <c r="O38" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>199</v>
-      </c>
-      <c r="B39" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" t="s">
-        <v>80</v>
-      </c>
-      <c r="D39" t="s">
-        <v>81</v>
-      </c>
-      <c r="E39" t="s">
-        <v>39</v>
-      </c>
-      <c r="F39" t="s">
-        <v>93</v>
-      </c>
-      <c r="G39" t="s">
-        <v>187</v>
-      </c>
-      <c r="H39" t="s">
-        <v>88</v>
-      </c>
-      <c r="I39" t="s">
-        <v>26</v>
-      </c>
-      <c r="J39" t="s">
-        <v>200</v>
-      </c>
-      <c r="K39" t="s">
-        <v>201</v>
-      </c>
-      <c r="L39" t="s">
-        <v>26</v>
-      </c>
-      <c r="M39" t="s">
-        <v>96</v>
-      </c>
-      <c r="N39" t="s">
-        <v>26</v>
-      </c>
-      <c r="O39" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>203</v>
-      </c>
-      <c r="B40" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" t="s">
-        <v>80</v>
-      </c>
-      <c r="D40" t="s">
-        <v>81</v>
-      </c>
-      <c r="E40" t="s">
-        <v>39</v>
-      </c>
-      <c r="F40" t="s">
-        <v>170</v>
-      </c>
-      <c r="G40" t="s">
-        <v>204</v>
-      </c>
-      <c r="H40" t="s">
-        <v>88</v>
-      </c>
-      <c r="I40" t="s">
-        <v>26</v>
-      </c>
       <c r="J40" t="s">
-        <v>205</v>
+        <v>104</v>
       </c>
       <c r="K40" t="s">
-        <v>206</v>
+        <v>56</v>
       </c>
       <c r="L40" t="s">
         <v>26</v>
@@ -3501,324 +3531,324 @@
         <v>26</v>
       </c>
       <c r="O40" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="C41" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D41" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="E41" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F41" t="s">
-        <v>170</v>
+        <v>54</v>
       </c>
       <c r="G41" t="s">
-        <v>209</v>
+        <v>26</v>
       </c>
       <c r="H41" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="I41" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J41" t="s">
         <v>210</v>
       </c>
       <c r="K41" t="s">
+        <v>35</v>
+      </c>
+      <c r="L41" t="s">
+        <v>26</v>
+      </c>
+      <c r="M41" t="s">
+        <v>26</v>
+      </c>
+      <c r="N41" t="s">
+        <v>26</v>
+      </c>
+      <c r="O41" t="s">
         <v>211</v>
       </c>
-      <c r="L41" t="s">
-        <v>26</v>
-      </c>
-      <c r="M41" t="s">
-        <v>26</v>
-      </c>
-      <c r="N41" t="s">
-        <v>26</v>
-      </c>
-      <c r="O41" t="s">
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>213</v>
-      </c>
       <c r="B42" t="s">
-        <v>214</v>
+        <v>59</v>
       </c>
       <c r="C42" t="s">
-        <v>169</v>
+        <v>60</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
       </c>
       <c r="E42" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="F42" t="s">
-        <v>170</v>
+        <v>91</v>
       </c>
       <c r="G42" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H42" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="I42" t="s">
-        <v>155</v>
+        <v>23</v>
       </c>
       <c r="J42" t="s">
+        <v>213</v>
+      </c>
+      <c r="K42" t="s">
+        <v>93</v>
+      </c>
+      <c r="L42" t="s">
+        <v>94</v>
+      </c>
+      <c r="M42" t="s">
+        <v>174</v>
+      </c>
+      <c r="N42" t="s">
+        <v>26</v>
+      </c>
+      <c r="O42" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>215</v>
       </c>
-      <c r="K42" t="s">
+      <c r="B43" t="s">
+        <v>197</v>
+      </c>
+      <c r="C43" t="s">
+        <v>26</v>
+      </c>
+      <c r="D43" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" t="s">
+        <v>49</v>
+      </c>
+      <c r="F43" t="s">
+        <v>91</v>
+      </c>
+      <c r="G43" t="s">
+        <v>21</v>
+      </c>
+      <c r="H43" t="s">
+        <v>33</v>
+      </c>
+      <c r="I43" t="s">
+        <v>26</v>
+      </c>
+      <c r="J43" t="s">
+        <v>73</v>
+      </c>
+      <c r="K43" t="s">
+        <v>93</v>
+      </c>
+      <c r="L43" t="s">
+        <v>94</v>
+      </c>
+      <c r="M43" t="s">
+        <v>174</v>
+      </c>
+      <c r="N43" t="s">
+        <v>26</v>
+      </c>
+      <c r="O43" t="s">
         <v>216</v>
       </c>
-      <c r="L42" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" t="s">
-        <v>26</v>
-      </c>
-      <c r="N42" t="s">
-        <v>26</v>
-      </c>
-      <c r="O42" t="s">
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="B44" t="s">
+        <v>59</v>
+      </c>
+      <c r="C44" t="s">
+        <v>60</v>
+      </c>
+      <c r="D44" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" t="s">
+        <v>49</v>
+      </c>
+      <c r="F44" t="s">
+        <v>85</v>
+      </c>
+      <c r="G44" t="s">
         <v>218</v>
       </c>
-      <c r="B43" t="s">
-        <v>36</v>
-      </c>
-      <c r="C43" t="s">
-        <v>37</v>
-      </c>
-      <c r="D43" t="s">
-        <v>38</v>
-      </c>
-      <c r="E43" t="s">
-        <v>39</v>
-      </c>
-      <c r="F43" t="s">
-        <v>93</v>
-      </c>
-      <c r="G43" t="s">
-        <v>187</v>
-      </c>
-      <c r="H43" t="s">
-        <v>22</v>
-      </c>
-      <c r="I43" t="s">
-        <v>23</v>
-      </c>
-      <c r="J43" t="s">
-        <v>219</v>
-      </c>
-      <c r="K43" t="s">
-        <v>220</v>
-      </c>
-      <c r="L43" t="s">
-        <v>26</v>
-      </c>
-      <c r="M43" t="s">
-        <v>96</v>
-      </c>
-      <c r="N43" t="s">
-        <v>26</v>
-      </c>
-      <c r="O43" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>222</v>
-      </c>
-      <c r="B44" t="s">
-        <v>36</v>
-      </c>
-      <c r="C44" t="s">
-        <v>37</v>
-      </c>
-      <c r="D44" t="s">
-        <v>38</v>
-      </c>
-      <c r="E44" t="s">
-        <v>39</v>
-      </c>
-      <c r="F44" t="s">
-        <v>93</v>
-      </c>
-      <c r="G44" t="s">
-        <v>165</v>
-      </c>
       <c r="H44" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I44" t="s">
         <v>23</v>
       </c>
       <c r="J44" t="s">
+        <v>136</v>
+      </c>
+      <c r="K44" t="s">
+        <v>182</v>
+      </c>
+      <c r="L44" t="s">
+        <v>26</v>
+      </c>
+      <c r="M44" t="s">
+        <v>26</v>
+      </c>
+      <c r="N44" t="s">
+        <v>26</v>
+      </c>
+      <c r="O44" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>220</v>
+      </c>
+      <c r="B45" t="s">
+        <v>59</v>
+      </c>
+      <c r="C45" t="s">
+        <v>60</v>
+      </c>
+      <c r="D45" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" t="s">
+        <v>49</v>
+      </c>
+      <c r="F45" t="s">
+        <v>91</v>
+      </c>
+      <c r="G45" t="s">
+        <v>26</v>
+      </c>
+      <c r="H45" t="s">
+        <v>33</v>
+      </c>
+      <c r="I45" t="s">
+        <v>23</v>
+      </c>
+      <c r="J45" t="s">
+        <v>221</v>
+      </c>
+      <c r="K45" t="s">
+        <v>222</v>
+      </c>
+      <c r="L45" t="s">
         <v>223</v>
       </c>
-      <c r="K44" t="s">
-        <v>206</v>
-      </c>
-      <c r="L44" t="s">
-        <v>26</v>
-      </c>
-      <c r="M44" t="s">
-        <v>96</v>
-      </c>
-      <c r="N44" t="s">
-        <v>26</v>
-      </c>
-      <c r="O44" t="s">
+      <c r="M45" t="s">
+        <v>174</v>
+      </c>
+      <c r="N45" t="s">
+        <v>26</v>
+      </c>
+      <c r="O45" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
         <v>225</v>
       </c>
-      <c r="B45" t="s">
-        <v>152</v>
-      </c>
-      <c r="C45" t="s">
-        <v>153</v>
-      </c>
-      <c r="D45" t="s">
-        <v>154</v>
-      </c>
-      <c r="E45" t="s">
-        <v>19</v>
-      </c>
-      <c r="F45" t="s">
-        <v>137</v>
-      </c>
-      <c r="G45" t="s">
-        <v>226</v>
-      </c>
-      <c r="H45" t="s">
-        <v>88</v>
-      </c>
-      <c r="I45" t="s">
-        <v>155</v>
-      </c>
-      <c r="J45" t="s">
-        <v>227</v>
-      </c>
-      <c r="K45" t="s">
-        <v>184</v>
-      </c>
-      <c r="L45" t="s">
-        <v>26</v>
-      </c>
-      <c r="M45" t="s">
-        <v>26</v>
-      </c>
-      <c r="N45" t="s">
-        <v>26</v>
-      </c>
-      <c r="O45" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>229</v>
-      </c>
       <c r="B46" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="C46" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="D46" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E46" t="s">
         <v>19</v>
       </c>
       <c r="F46" t="s">
-        <v>170</v>
+        <v>31</v>
       </c>
       <c r="G46" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="H46" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I46" t="s">
         <v>23</v>
       </c>
       <c r="J46" t="s">
+        <v>226</v>
+      </c>
+      <c r="K46" t="s">
+        <v>227</v>
+      </c>
+      <c r="L46" t="s">
+        <v>26</v>
+      </c>
+      <c r="M46" t="s">
+        <v>26</v>
+      </c>
+      <c r="N46" t="s">
+        <v>26</v>
+      </c>
+      <c r="O46" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>229</v>
+      </c>
+      <c r="B47" t="s">
         <v>230</v>
       </c>
-      <c r="K46" t="s">
-        <v>211</v>
-      </c>
-      <c r="L46" t="s">
-        <v>26</v>
-      </c>
-      <c r="M46" t="s">
-        <v>26</v>
-      </c>
-      <c r="N46" t="s">
-        <v>26</v>
-      </c>
-      <c r="O46" t="s">
+      <c r="C47" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="D47" t="s">
         <v>232</v>
-      </c>
-      <c r="B47" t="s">
-        <v>168</v>
-      </c>
-      <c r="C47" t="s">
-        <v>169</v>
-      </c>
-      <c r="D47" t="s">
-        <v>18</v>
       </c>
       <c r="E47" t="s">
         <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>170</v>
+        <v>41</v>
       </c>
       <c r="G47" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="H47" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="I47" t="s">
-        <v>155</v>
+        <v>117</v>
       </c>
       <c r="J47" t="s">
         <v>233</v>
       </c>
       <c r="K47" t="s">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="L47" t="s">
         <v>26</v>
@@ -3833,7 +3863,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>235</v>
       </c>
@@ -3844,22 +3874,22 @@
         <v>237</v>
       </c>
       <c r="D48" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="E48" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F48" t="s">
-        <v>170</v>
+        <v>31</v>
       </c>
       <c r="G48" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="H48" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="I48" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J48" t="s">
         <v>238</v>
@@ -3880,321 +3910,321 @@
         <v>240</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>241</v>
       </c>
       <c r="B49" t="s">
+        <v>197</v>
+      </c>
+      <c r="C49" t="s">
+        <v>26</v>
+      </c>
+      <c r="D49" t="s">
+        <v>26</v>
+      </c>
+      <c r="E49" t="s">
+        <v>49</v>
+      </c>
+      <c r="F49" t="s">
+        <v>31</v>
+      </c>
+      <c r="G49" t="s">
+        <v>32</v>
+      </c>
+      <c r="H49" t="s">
+        <v>33</v>
+      </c>
+      <c r="I49" t="s">
+        <v>26</v>
+      </c>
+      <c r="J49" t="s">
+        <v>203</v>
+      </c>
+      <c r="K49" t="s">
         <v>68</v>
       </c>
-      <c r="C49" t="s">
-        <v>69</v>
-      </c>
-      <c r="D49" t="s">
-        <v>38</v>
-      </c>
-      <c r="E49" t="s">
-        <v>39</v>
-      </c>
-      <c r="F49" t="s">
-        <v>30</v>
-      </c>
-      <c r="G49" t="s">
-        <v>31</v>
-      </c>
-      <c r="H49" t="s">
-        <v>22</v>
-      </c>
-      <c r="I49" t="s">
-        <v>23</v>
-      </c>
-      <c r="J49" t="s">
-        <v>230</v>
-      </c>
-      <c r="K49" t="s">
+      <c r="L49" t="s">
+        <v>26</v>
+      </c>
+      <c r="M49" t="s">
+        <v>26</v>
+      </c>
+      <c r="N49" t="s">
+        <v>26</v>
+      </c>
+      <c r="O49" t="s">
         <v>242</v>
       </c>
-      <c r="L49" t="s">
-        <v>26</v>
-      </c>
-      <c r="M49" t="s">
-        <v>26</v>
-      </c>
-      <c r="N49" t="s">
-        <v>26</v>
-      </c>
-      <c r="O49" t="s">
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="B50" t="s">
         <v>244</v>
       </c>
-      <c r="B50" t="s">
-        <v>79</v>
-      </c>
       <c r="C50" t="s">
+        <v>116</v>
+      </c>
+      <c r="D50" t="s">
+        <v>40</v>
+      </c>
+      <c r="E50" t="s">
+        <v>19</v>
+      </c>
+      <c r="F50" t="s">
+        <v>65</v>
+      </c>
+      <c r="G50" t="s">
+        <v>66</v>
+      </c>
+      <c r="H50" t="s">
+        <v>33</v>
+      </c>
+      <c r="I50" t="s">
+        <v>117</v>
+      </c>
+      <c r="J50" t="s">
         <v>245</v>
       </c>
-      <c r="D50" t="s">
-        <v>38</v>
-      </c>
-      <c r="E50" t="s">
-        <v>39</v>
-      </c>
-      <c r="F50" t="s">
-        <v>30</v>
-      </c>
-      <c r="G50" t="s">
-        <v>165</v>
-      </c>
-      <c r="H50" t="s">
-        <v>22</v>
-      </c>
-      <c r="I50" t="s">
-        <v>23</v>
-      </c>
-      <c r="J50" t="s">
+      <c r="K50" t="s">
+        <v>227</v>
+      </c>
+      <c r="L50" t="s">
+        <v>26</v>
+      </c>
+      <c r="M50" t="s">
+        <v>26</v>
+      </c>
+      <c r="N50" t="s">
+        <v>26</v>
+      </c>
+      <c r="O50" t="s">
         <v>246</v>
       </c>
-      <c r="K50" t="s">
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
         <v>247</v>
       </c>
-      <c r="L50" t="s">
-        <v>26</v>
-      </c>
-      <c r="M50" t="s">
-        <v>26</v>
-      </c>
-      <c r="N50" t="s">
-        <v>26</v>
-      </c>
-      <c r="O50" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>249</v>
-      </c>
       <c r="B51" t="s">
-        <v>79</v>
+        <v>161</v>
       </c>
       <c r="C51" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="D51" t="s">
-        <v>38</v>
+        <v>232</v>
       </c>
       <c r="E51" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F51" t="s">
-        <v>170</v>
+        <v>124</v>
       </c>
       <c r="G51" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="H51" t="s">
         <v>22</v>
       </c>
       <c r="I51" t="s">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="J51" t="s">
+        <v>248</v>
+      </c>
+      <c r="K51" t="s">
+        <v>133</v>
+      </c>
+      <c r="L51" t="s">
+        <v>26</v>
+      </c>
+      <c r="M51" t="s">
+        <v>26</v>
+      </c>
+      <c r="N51" t="s">
+        <v>26</v>
+      </c>
+      <c r="O51" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
         <v>250</v>
       </c>
-      <c r="K51" t="s">
-        <v>100</v>
-      </c>
-      <c r="L51" t="s">
-        <v>26</v>
-      </c>
-      <c r="M51" t="s">
-        <v>26</v>
-      </c>
-      <c r="N51" t="s">
-        <v>26</v>
-      </c>
-      <c r="O51" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>252</v>
-      </c>
       <c r="B52" t="s">
-        <v>168</v>
+        <v>244</v>
       </c>
       <c r="C52" t="s">
-        <v>169</v>
+        <v>116</v>
       </c>
       <c r="D52" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E52" t="s">
         <v>19</v>
       </c>
       <c r="F52" t="s">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="G52" t="s">
+        <v>42</v>
+      </c>
+      <c r="H52" t="s">
+        <v>33</v>
+      </c>
+      <c r="I52" t="s">
+        <v>117</v>
+      </c>
+      <c r="J52" t="s">
+        <v>181</v>
+      </c>
+      <c r="K52" t="s">
+        <v>251</v>
+      </c>
+      <c r="L52" t="s">
+        <v>26</v>
+      </c>
+      <c r="M52" t="s">
+        <v>26</v>
+      </c>
+      <c r="N52" t="s">
+        <v>26</v>
+      </c>
+      <c r="O52" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
         <v>253</v>
       </c>
-      <c r="H52" t="s">
-        <v>88</v>
-      </c>
-      <c r="I52" t="s">
-        <v>155</v>
-      </c>
-      <c r="J52" t="s">
+      <c r="B53" t="s">
         <v>254</v>
       </c>
-      <c r="K52" t="s">
-        <v>105</v>
-      </c>
-      <c r="L52" t="s">
-        <v>26</v>
-      </c>
-      <c r="M52" t="s">
-        <v>26</v>
-      </c>
-      <c r="N52" t="s">
-        <v>26</v>
-      </c>
-      <c r="O52" t="s">
+      <c r="C53" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="D53" t="s">
         <v>256</v>
       </c>
-      <c r="B53" t="s">
-        <v>68</v>
-      </c>
-      <c r="C53" t="s">
-        <v>69</v>
-      </c>
-      <c r="D53" t="s">
-        <v>38</v>
-      </c>
       <c r="E53" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F53" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="G53" t="s">
-        <v>257</v>
+        <v>66</v>
       </c>
       <c r="H53" t="s">
         <v>22</v>
       </c>
       <c r="I53" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J53" t="s">
+        <v>233</v>
+      </c>
+      <c r="K53" t="s">
+        <v>44</v>
+      </c>
+      <c r="L53" t="s">
+        <v>26</v>
+      </c>
+      <c r="M53" t="s">
+        <v>26</v>
+      </c>
+      <c r="N53" t="s">
+        <v>26</v>
+      </c>
+      <c r="O53" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
         <v>258</v>
       </c>
-      <c r="K53" t="s">
-        <v>143</v>
-      </c>
-      <c r="L53" t="s">
-        <v>26</v>
-      </c>
-      <c r="M53" t="s">
-        <v>26</v>
-      </c>
-      <c r="N53" t="s">
-        <v>26</v>
-      </c>
-      <c r="O53" t="s">
+      <c r="B54" t="s">
+        <v>122</v>
+      </c>
+      <c r="C54" t="s">
+        <v>173</v>
+      </c>
+      <c r="D54" t="s">
+        <v>84</v>
+      </c>
+      <c r="E54" t="s">
+        <v>49</v>
+      </c>
+      <c r="F54" t="s">
+        <v>31</v>
+      </c>
+      <c r="G54" t="s">
         <v>259</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>260</v>
-      </c>
-      <c r="B54" t="s">
-        <v>29</v>
-      </c>
-      <c r="C54" t="s">
-        <v>245</v>
-      </c>
-      <c r="D54" t="s">
-        <v>38</v>
-      </c>
-      <c r="E54" t="s">
-        <v>19</v>
-      </c>
-      <c r="F54" t="s">
-        <v>30</v>
-      </c>
-      <c r="G54" t="s">
-        <v>31</v>
       </c>
       <c r="H54" t="s">
         <v>22</v>
       </c>
       <c r="I54" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J54" t="s">
+        <v>260</v>
+      </c>
+      <c r="K54" t="s">
+        <v>227</v>
+      </c>
+      <c r="L54" t="s">
+        <v>26</v>
+      </c>
+      <c r="M54" t="s">
+        <v>26</v>
+      </c>
+      <c r="N54" t="s">
+        <v>26</v>
+      </c>
+      <c r="O54" t="s">
         <v>261</v>
       </c>
-      <c r="K54" t="s">
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
         <v>262</v>
       </c>
-      <c r="L54" t="s">
-        <v>26</v>
-      </c>
-      <c r="M54" t="s">
-        <v>26</v>
-      </c>
-      <c r="N54" t="s">
-        <v>26</v>
-      </c>
-      <c r="O54" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>264</v>
-      </c>
       <c r="B55" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C55" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D55" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E55" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F55" t="s">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="G55" t="s">
-        <v>204</v>
+        <v>32</v>
       </c>
       <c r="H55" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I55" t="s">
         <v>23</v>
       </c>
       <c r="J55" t="s">
-        <v>265</v>
+        <v>136</v>
       </c>
       <c r="K55" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="L55" t="s">
         <v>26</v>
@@ -4206,42 +4236,42 @@
         <v>26</v>
       </c>
       <c r="O55" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B56" t="s">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="C56" t="s">
-        <v>37</v>
+        <v>173</v>
       </c>
       <c r="D56" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="E56" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F56" t="s">
-        <v>170</v>
+        <v>31</v>
       </c>
       <c r="G56" t="s">
-        <v>31</v>
+        <v>259</v>
       </c>
       <c r="H56" t="s">
         <v>22</v>
       </c>
       <c r="I56" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J56" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="K56" t="s">
-        <v>45</v>
+        <v>190</v>
       </c>
       <c r="L56" t="s">
         <v>26</v>
@@ -4253,136 +4283,136 @@
         <v>26</v>
       </c>
       <c r="O56" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B57" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="C57" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="D57" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E57" t="s">
         <v>19</v>
       </c>
       <c r="F57" t="s">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="G57" t="s">
-        <v>165</v>
+        <v>32</v>
       </c>
       <c r="H57" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I57" t="s">
         <v>23</v>
       </c>
       <c r="J57" t="s">
+        <v>268</v>
+      </c>
+      <c r="K57" t="s">
+        <v>269</v>
+      </c>
+      <c r="L57" t="s">
+        <v>26</v>
+      </c>
+      <c r="M57" t="s">
+        <v>26</v>
+      </c>
+      <c r="N57" t="s">
+        <v>26</v>
+      </c>
+      <c r="O57" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
         <v>271</v>
       </c>
-      <c r="K57" t="s">
-        <v>90</v>
-      </c>
-      <c r="L57" t="s">
-        <v>26</v>
-      </c>
-      <c r="M57" t="s">
-        <v>26</v>
-      </c>
-      <c r="N57" t="s">
-        <v>26</v>
-      </c>
-      <c r="O57" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>273</v>
-      </c>
       <c r="B58" t="s">
+        <v>122</v>
+      </c>
+      <c r="C58" t="s">
+        <v>173</v>
+      </c>
+      <c r="D58" t="s">
+        <v>84</v>
+      </c>
+      <c r="E58" t="s">
         <v>49</v>
       </c>
-      <c r="C58" t="s">
-        <v>50</v>
-      </c>
-      <c r="D58" t="s">
-        <v>38</v>
-      </c>
-      <c r="E58" t="s">
-        <v>19</v>
-      </c>
       <c r="F58" t="s">
-        <v>170</v>
+        <v>124</v>
       </c>
       <c r="G58" t="s">
-        <v>31</v>
+        <v>259</v>
       </c>
       <c r="H58" t="s">
         <v>22</v>
       </c>
       <c r="I58" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J58" t="s">
+        <v>272</v>
+      </c>
+      <c r="K58" t="s">
+        <v>273</v>
+      </c>
+      <c r="L58" t="s">
+        <v>26</v>
+      </c>
+      <c r="M58" t="s">
+        <v>126</v>
+      </c>
+      <c r="N58" t="s">
+        <v>26</v>
+      </c>
+      <c r="O58" t="s">
         <v>274</v>
       </c>
-      <c r="K58" t="s">
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>275</v>
       </c>
-      <c r="L58" t="s">
-        <v>26</v>
-      </c>
-      <c r="M58" t="s">
-        <v>26</v>
-      </c>
-      <c r="N58" t="s">
-        <v>26</v>
-      </c>
-      <c r="O58" t="s">
+      <c r="B59" t="s">
+        <v>122</v>
+      </c>
+      <c r="C59" t="s">
+        <v>173</v>
+      </c>
+      <c r="D59" t="s">
+        <v>84</v>
+      </c>
+      <c r="E59" t="s">
+        <v>49</v>
+      </c>
+      <c r="F59" t="s">
+        <v>65</v>
+      </c>
+      <c r="G59" t="s">
         <v>276</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>277</v>
-      </c>
-      <c r="B59" t="s">
-        <v>29</v>
-      </c>
-      <c r="C59" t="s">
-        <v>153</v>
-      </c>
-      <c r="D59" t="s">
-        <v>154</v>
-      </c>
-      <c r="E59" t="s">
-        <v>19</v>
-      </c>
-      <c r="F59" t="s">
-        <v>30</v>
-      </c>
-      <c r="G59" t="s">
-        <v>165</v>
       </c>
       <c r="H59" t="s">
         <v>22</v>
       </c>
       <c r="I59" t="s">
-        <v>155</v>
+        <v>26</v>
       </c>
       <c r="J59" t="s">
+        <v>277</v>
+      </c>
+      <c r="K59" t="s">
         <v>278</v>
-      </c>
-      <c r="K59" t="s">
-        <v>216</v>
       </c>
       <c r="L59" t="s">
         <v>26</v>
@@ -4397,39 +4427,39 @@
         <v>279</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>280</v>
       </c>
       <c r="B60" t="s">
+        <v>122</v>
+      </c>
+      <c r="C60" t="s">
+        <v>173</v>
+      </c>
+      <c r="D60" t="s">
+        <v>84</v>
+      </c>
+      <c r="E60" t="s">
         <v>49</v>
       </c>
-      <c r="C60" t="s">
-        <v>50</v>
-      </c>
-      <c r="D60" t="s">
-        <v>38</v>
-      </c>
-      <c r="E60" t="s">
-        <v>19</v>
-      </c>
       <c r="F60" t="s">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="G60" t="s">
-        <v>31</v>
+        <v>281</v>
       </c>
       <c r="H60" t="s">
         <v>22</v>
       </c>
       <c r="I60" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J60" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K60" t="s">
-        <v>216</v>
+        <v>109</v>
       </c>
       <c r="L60" t="s">
         <v>26</v>
@@ -4441,183 +4471,183 @@
         <v>26</v>
       </c>
       <c r="O60" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B61" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C61" t="s">
-        <v>285</v>
+        <v>116</v>
       </c>
       <c r="D61" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E61" t="s">
         <v>19</v>
       </c>
       <c r="F61" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="G61" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="H61" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="I61" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="J61" t="s">
+        <v>118</v>
+      </c>
+      <c r="K61" t="s">
         <v>286</v>
       </c>
-      <c r="K61" t="s">
+      <c r="L61" t="s">
+        <v>26</v>
+      </c>
+      <c r="M61" t="s">
+        <v>26</v>
+      </c>
+      <c r="N61" t="s">
+        <v>26</v>
+      </c>
+      <c r="O61" t="s">
         <v>287</v>
       </c>
-      <c r="L61" t="s">
-        <v>26</v>
-      </c>
-      <c r="M61" t="s">
-        <v>26</v>
-      </c>
-      <c r="N61" t="s">
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
         <v>288</v>
       </c>
-      <c r="O61" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>290</v>
-      </c>
       <c r="B62" t="s">
-        <v>168</v>
+        <v>59</v>
       </c>
       <c r="C62" t="s">
-        <v>169</v>
+        <v>60</v>
       </c>
       <c r="D62" t="s">
         <v>18</v>
       </c>
       <c r="E62" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="F62" t="s">
-        <v>170</v>
+        <v>124</v>
       </c>
       <c r="G62" t="s">
-        <v>52</v>
+        <v>259</v>
       </c>
       <c r="H62" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="I62" t="s">
-        <v>155</v>
+        <v>23</v>
       </c>
       <c r="J62" t="s">
+        <v>289</v>
+      </c>
+      <c r="K62" t="s">
+        <v>290</v>
+      </c>
+      <c r="L62" t="s">
+        <v>26</v>
+      </c>
+      <c r="M62" t="s">
+        <v>126</v>
+      </c>
+      <c r="N62" t="s">
+        <v>26</v>
+      </c>
+      <c r="O62" t="s">
         <v>291</v>
       </c>
-      <c r="K62" t="s">
-        <v>65</v>
-      </c>
-      <c r="L62" t="s">
-        <v>26</v>
-      </c>
-      <c r="M62" t="s">
-        <v>26</v>
-      </c>
-      <c r="N62" t="s">
-        <v>26</v>
-      </c>
-      <c r="O62" t="s">
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>293</v>
-      </c>
       <c r="B63" t="s">
+        <v>59</v>
+      </c>
+      <c r="C63" t="s">
+        <v>60</v>
+      </c>
+      <c r="D63" t="s">
+        <v>18</v>
+      </c>
+      <c r="E63" t="s">
         <v>49</v>
       </c>
-      <c r="C63" t="s">
-        <v>50</v>
-      </c>
-      <c r="D63" t="s">
-        <v>38</v>
-      </c>
-      <c r="E63" t="s">
-        <v>19</v>
-      </c>
       <c r="F63" t="s">
-        <v>30</v>
+        <v>124</v>
       </c>
       <c r="G63" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="H63" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I63" t="s">
         <v>23</v>
       </c>
       <c r="J63" t="s">
-        <v>227</v>
+        <v>293</v>
       </c>
       <c r="K63" t="s">
+        <v>278</v>
+      </c>
+      <c r="L63" t="s">
+        <v>26</v>
+      </c>
+      <c r="M63" t="s">
+        <v>126</v>
+      </c>
+      <c r="N63" t="s">
+        <v>26</v>
+      </c>
+      <c r="O63" t="s">
         <v>294</v>
       </c>
-      <c r="L63" t="s">
-        <v>26</v>
-      </c>
-      <c r="M63" t="s">
-        <v>26</v>
-      </c>
-      <c r="N63" t="s">
-        <v>26</v>
-      </c>
-      <c r="O63" t="s">
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>296</v>
-      </c>
       <c r="B64" t="s">
-        <v>168</v>
+        <v>230</v>
       </c>
       <c r="C64" t="s">
-        <v>169</v>
+        <v>231</v>
       </c>
       <c r="D64" t="s">
-        <v>18</v>
+        <v>232</v>
       </c>
       <c r="E64" t="s">
         <v>19</v>
       </c>
       <c r="F64" t="s">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="G64" t="s">
-        <v>165</v>
+        <v>296</v>
       </c>
       <c r="H64" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="I64" t="s">
-        <v>155</v>
+        <v>117</v>
       </c>
       <c r="J64" t="s">
-        <v>230</v>
+        <v>297</v>
       </c>
       <c r="K64" t="s">
-        <v>149</v>
+        <v>44</v>
       </c>
       <c r="L64" t="s">
         <v>26</v>
@@ -4629,42 +4659,42 @@
         <v>26</v>
       </c>
       <c r="O64" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B65" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C65" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D65" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E65" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F65" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="G65" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="H65" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I65" t="s">
         <v>23</v>
       </c>
       <c r="J65" t="s">
-        <v>254</v>
+        <v>300</v>
       </c>
       <c r="K65" t="s">
-        <v>299</v>
+        <v>109</v>
       </c>
       <c r="L65" t="s">
         <v>26</v>
@@ -4676,89 +4706,89 @@
         <v>26</v>
       </c>
       <c r="O65" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B66" t="s">
-        <v>68</v>
+        <v>244</v>
       </c>
       <c r="C66" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="D66" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E66" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F66" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="G66" t="s">
-        <v>302</v>
+        <v>66</v>
       </c>
       <c r="H66" t="s">
         <v>22</v>
       </c>
       <c r="I66" t="s">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="J66" t="s">
         <v>303</v>
       </c>
       <c r="K66" t="s">
+        <v>273</v>
+      </c>
+      <c r="L66" t="s">
+        <v>26</v>
+      </c>
+      <c r="M66" t="s">
+        <v>26</v>
+      </c>
+      <c r="N66" t="s">
+        <v>26</v>
+      </c>
+      <c r="O66" t="s">
         <v>304</v>
       </c>
-      <c r="L66" t="s">
-        <v>26</v>
-      </c>
-      <c r="M66" t="s">
-        <v>26</v>
-      </c>
-      <c r="N66" t="s">
-        <v>26</v>
-      </c>
-      <c r="O66" t="s">
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>306</v>
-      </c>
       <c r="B67" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="C67" t="s">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="D67" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="E67" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F67" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="G67" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="H67" t="s">
         <v>22</v>
       </c>
       <c r="I67" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J67" t="s">
+        <v>306</v>
+      </c>
+      <c r="K67" t="s">
         <v>307</v>
-      </c>
-      <c r="K67" t="s">
-        <v>197</v>
       </c>
       <c r="L67" t="s">
         <v>26</v>
@@ -4773,39 +4803,39 @@
         <v>308</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>309</v>
       </c>
       <c r="B68" t="s">
+        <v>47</v>
+      </c>
+      <c r="C68" t="s">
+        <v>123</v>
+      </c>
+      <c r="D68" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68" t="s">
         <v>49</v>
       </c>
-      <c r="C68" t="s">
-        <v>50</v>
-      </c>
-      <c r="D68" t="s">
-        <v>38</v>
-      </c>
-      <c r="E68" t="s">
-        <v>19</v>
-      </c>
       <c r="F68" t="s">
-        <v>170</v>
+        <v>31</v>
       </c>
       <c r="G68" t="s">
-        <v>302</v>
+        <v>66</v>
       </c>
       <c r="H68" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I68" t="s">
         <v>23</v>
       </c>
       <c r="J68" t="s">
+        <v>300</v>
+      </c>
+      <c r="K68" t="s">
         <v>310</v>
-      </c>
-      <c r="K68" t="s">
-        <v>211</v>
       </c>
       <c r="L68" t="s">
         <v>26</v>
@@ -4820,39 +4850,39 @@
         <v>311</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>312</v>
       </c>
       <c r="B69" t="s">
-        <v>68</v>
+        <v>122</v>
       </c>
       <c r="C69" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="D69" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E69" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F69" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G69" t="s">
-        <v>187</v>
+        <v>32</v>
       </c>
       <c r="H69" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I69" t="s">
         <v>23</v>
       </c>
       <c r="J69" t="s">
-        <v>32</v>
+        <v>313</v>
       </c>
       <c r="K69" t="s">
-        <v>45</v>
+        <v>314</v>
       </c>
       <c r="L69" t="s">
         <v>26</v>
@@ -4864,42 +4894,42 @@
         <v>26</v>
       </c>
       <c r="O69" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B70" t="s">
-        <v>315</v>
+        <v>122</v>
       </c>
       <c r="C70" t="s">
-        <v>285</v>
+        <v>48</v>
       </c>
       <c r="D70" t="s">
         <v>18</v>
       </c>
       <c r="E70" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="F70" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="G70" t="s">
-        <v>31</v>
+        <v>188</v>
       </c>
       <c r="H70" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I70" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J70" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K70" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="L70" t="s">
         <v>26</v>
@@ -4908,45 +4938,45 @@
         <v>26</v>
       </c>
       <c r="N70" t="s">
-        <v>317</v>
+        <v>26</v>
       </c>
       <c r="O70" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>319</v>
       </c>
       <c r="B71" t="s">
-        <v>315</v>
+        <v>244</v>
       </c>
       <c r="C71" t="s">
-        <v>285</v>
+        <v>116</v>
       </c>
       <c r="D71" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E71" t="s">
         <v>19</v>
       </c>
       <c r="F71" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="G71" t="s">
-        <v>31</v>
+        <v>320</v>
       </c>
       <c r="H71" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="I71" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="J71" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K71" t="s">
-        <v>143</v>
+        <v>190</v>
       </c>
       <c r="L71" t="s">
         <v>26</v>
@@ -4955,45 +4985,45 @@
         <v>26</v>
       </c>
       <c r="N71" t="s">
-        <v>321</v>
+        <v>26</v>
       </c>
       <c r="O71" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>323</v>
       </c>
       <c r="B72" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C72" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="D72" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E72" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F72" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="G72" t="s">
-        <v>26</v>
+        <v>324</v>
       </c>
       <c r="H72" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I72" t="s">
         <v>23</v>
       </c>
       <c r="J72" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K72" t="s">
-        <v>325</v>
+        <v>223</v>
       </c>
       <c r="L72" t="s">
         <v>26</v>
@@ -5008,30 +5038,30 @@
         <v>326</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>327</v>
       </c>
       <c r="B73" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C73" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D73" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E73" t="s">
         <v>19</v>
       </c>
       <c r="F73" t="s">
-        <v>170</v>
+        <v>31</v>
       </c>
       <c r="G73" t="s">
-        <v>302</v>
+        <v>66</v>
       </c>
       <c r="H73" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I73" t="s">
         <v>23</v>
@@ -5040,242 +5070,242 @@
         <v>328</v>
       </c>
       <c r="K73" t="s">
+        <v>51</v>
+      </c>
+      <c r="L73" t="s">
+        <v>26</v>
+      </c>
+      <c r="M73" t="s">
+        <v>26</v>
+      </c>
+      <c r="N73" t="s">
+        <v>26</v>
+      </c>
+      <c r="O73" t="s">
         <v>329</v>
       </c>
-      <c r="L73" t="s">
-        <v>26</v>
-      </c>
-      <c r="M73" t="s">
-        <v>26</v>
-      </c>
-      <c r="N73" t="s">
-        <v>26</v>
-      </c>
-      <c r="O73" t="s">
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>331</v>
-      </c>
       <c r="B74" t="s">
-        <v>332</v>
+        <v>59</v>
       </c>
       <c r="C74" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
       </c>
       <c r="E74" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F74" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="G74" t="s">
-        <v>31</v>
+        <v>276</v>
       </c>
       <c r="H74" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="I74" t="s">
         <v>23</v>
       </c>
       <c r="J74" t="s">
+        <v>331</v>
+      </c>
+      <c r="K74" t="s">
+        <v>273</v>
+      </c>
+      <c r="L74" t="s">
+        <v>26</v>
+      </c>
+      <c r="M74" t="s">
+        <v>26</v>
+      </c>
+      <c r="N74" t="s">
+        <v>26</v>
+      </c>
+      <c r="O74" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>333</v>
       </c>
-      <c r="K74" t="s">
-        <v>33</v>
-      </c>
-      <c r="L74" t="s">
-        <v>26</v>
-      </c>
-      <c r="M74" t="s">
-        <v>26</v>
-      </c>
-      <c r="N74" t="s">
-        <v>26</v>
-      </c>
-      <c r="O74" t="s">
+      <c r="B75" t="s">
+        <v>59</v>
+      </c>
+      <c r="C75" t="s">
+        <v>60</v>
+      </c>
+      <c r="D75" t="s">
+        <v>18</v>
+      </c>
+      <c r="E75" t="s">
+        <v>49</v>
+      </c>
+      <c r="F75" t="s">
+        <v>65</v>
+      </c>
+      <c r="G75" t="s">
+        <v>66</v>
+      </c>
+      <c r="H75" t="s">
+        <v>33</v>
+      </c>
+      <c r="I75" t="s">
+        <v>23</v>
+      </c>
+      <c r="J75" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+      <c r="K75" t="s">
+        <v>94</v>
+      </c>
+      <c r="L75" t="s">
+        <v>26</v>
+      </c>
+      <c r="M75" t="s">
+        <v>26</v>
+      </c>
+      <c r="N75" t="s">
+        <v>26</v>
+      </c>
+      <c r="O75" t="s">
         <v>335</v>
       </c>
-      <c r="B75" t="s">
-        <v>236</v>
-      </c>
-      <c r="C75" t="s">
-        <v>237</v>
-      </c>
-      <c r="D75" t="s">
-        <v>81</v>
-      </c>
-      <c r="E75" t="s">
-        <v>39</v>
-      </c>
-      <c r="F75" t="s">
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>336</v>
+      </c>
+      <c r="B76" t="s">
+        <v>29</v>
+      </c>
+      <c r="C76" t="s">
         <v>30</v>
       </c>
-      <c r="G75" t="s">
-        <v>31</v>
-      </c>
-      <c r="H75" t="s">
-        <v>88</v>
-      </c>
-      <c r="I75" t="s">
-        <v>26</v>
-      </c>
-      <c r="J75" t="s">
-        <v>336</v>
-      </c>
-      <c r="K75" t="s">
-        <v>54</v>
-      </c>
-      <c r="L75" t="s">
-        <v>26</v>
-      </c>
-      <c r="M75" t="s">
-        <v>26</v>
-      </c>
-      <c r="N75" t="s">
-        <v>26</v>
-      </c>
-      <c r="O75" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>338</v>
-      </c>
-      <c r="B76" t="s">
-        <v>87</v>
-      </c>
-      <c r="C76" t="s">
-        <v>339</v>
-      </c>
       <c r="D76" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E76" t="s">
         <v>19</v>
       </c>
       <c r="F76" t="s">
+        <v>65</v>
+      </c>
+      <c r="G76" t="s">
+        <v>32</v>
+      </c>
+      <c r="H76" t="s">
+        <v>33</v>
+      </c>
+      <c r="I76" t="s">
+        <v>23</v>
+      </c>
+      <c r="J76" t="s">
+        <v>337</v>
+      </c>
+      <c r="K76" t="s">
+        <v>68</v>
+      </c>
+      <c r="L76" t="s">
+        <v>26</v>
+      </c>
+      <c r="M76" t="s">
+        <v>26</v>
+      </c>
+      <c r="N76" t="s">
+        <v>26</v>
+      </c>
+      <c r="O76" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>339</v>
+      </c>
+      <c r="B77" t="s">
+        <v>29</v>
+      </c>
+      <c r="C77" t="s">
         <v>30</v>
       </c>
-      <c r="G76" t="s">
-        <v>31</v>
-      </c>
-      <c r="H76" t="s">
-        <v>88</v>
-      </c>
-      <c r="I76" t="s">
-        <v>26</v>
-      </c>
-      <c r="J76" t="s">
-        <v>340</v>
-      </c>
-      <c r="K76" t="s">
-        <v>105</v>
-      </c>
-      <c r="L76" t="s">
-        <v>26</v>
-      </c>
-      <c r="M76" t="s">
-        <v>26</v>
-      </c>
-      <c r="N76" t="s">
-        <v>26</v>
-      </c>
-      <c r="O76" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>342</v>
-      </c>
-      <c r="B77" t="s">
-        <v>87</v>
-      </c>
-      <c r="C77" t="s">
-        <v>339</v>
-      </c>
       <c r="D77" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E77" t="s">
         <v>19</v>
       </c>
       <c r="F77" t="s">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="G77" t="s">
-        <v>187</v>
+        <v>66</v>
       </c>
       <c r="H77" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="I77" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J77" t="s">
+        <v>340</v>
+      </c>
+      <c r="K77" t="s">
+        <v>341</v>
+      </c>
+      <c r="L77" t="s">
+        <v>26</v>
+      </c>
+      <c r="M77" t="s">
+        <v>26</v>
+      </c>
+      <c r="N77" t="s">
+        <v>26</v>
+      </c>
+      <c r="O77" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>343</v>
       </c>
-      <c r="K77" t="s">
-        <v>344</v>
-      </c>
-      <c r="L77" t="s">
-        <v>26</v>
-      </c>
-      <c r="M77" t="s">
-        <v>26</v>
-      </c>
-      <c r="N77" t="s">
-        <v>26</v>
-      </c>
-      <c r="O77" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>346</v>
-      </c>
       <c r="B78" t="s">
-        <v>347</v>
+        <v>16</v>
       </c>
       <c r="C78" t="s">
-        <v>348</v>
+        <v>231</v>
       </c>
       <c r="D78" t="s">
-        <v>18</v>
+        <v>232</v>
       </c>
       <c r="E78" t="s">
         <v>19</v>
       </c>
       <c r="F78" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="G78" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H78" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="I78" t="s">
-        <v>23</v>
+        <v>117</v>
       </c>
       <c r="J78" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="K78" t="s">
-        <v>350</v>
+        <v>286</v>
       </c>
       <c r="L78" t="s">
         <v>26</v>
@@ -5287,42 +5317,42 @@
         <v>26</v>
       </c>
       <c r="O78" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B79" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="C79" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="D79" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E79" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F79" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="G79" t="s">
-        <v>187</v>
+        <v>66</v>
       </c>
       <c r="H79" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I79" t="s">
         <v>23</v>
       </c>
       <c r="J79" t="s">
-        <v>134</v>
+        <v>347</v>
       </c>
       <c r="K79" t="s">
-        <v>33</v>
+        <v>286</v>
       </c>
       <c r="L79" t="s">
         <v>26</v>
@@ -5334,89 +5364,89 @@
         <v>26</v>
       </c>
       <c r="O79" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B80" t="s">
-        <v>49</v>
+        <v>350</v>
       </c>
       <c r="C80" t="s">
-        <v>50</v>
+        <v>351</v>
       </c>
       <c r="D80" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E80" t="s">
         <v>19</v>
       </c>
       <c r="F80" t="s">
-        <v>51</v>
+        <v>144</v>
       </c>
       <c r="G80" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="H80" t="s">
         <v>22</v>
       </c>
       <c r="I80" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J80" t="s">
+        <v>352</v>
+      </c>
+      <c r="K80" t="s">
+        <v>353</v>
+      </c>
+      <c r="L80" t="s">
+        <v>26</v>
+      </c>
+      <c r="M80" t="s">
+        <v>26</v>
+      </c>
+      <c r="N80" t="s">
+        <v>354</v>
+      </c>
+      <c r="O80" t="s">
         <v>355</v>
       </c>
-      <c r="K80" t="s">
-        <v>71</v>
-      </c>
-      <c r="L80" t="s">
-        <v>26</v>
-      </c>
-      <c r="M80" t="s">
-        <v>26</v>
-      </c>
-      <c r="N80" t="s">
-        <v>26</v>
-      </c>
-      <c r="O80" t="s">
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>357</v>
-      </c>
       <c r="B81" t="s">
-        <v>332</v>
+        <v>244</v>
       </c>
       <c r="C81" t="s">
-        <v>26</v>
+        <v>116</v>
       </c>
       <c r="D81" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E81" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F81" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="G81" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="H81" t="s">
         <v>22</v>
       </c>
       <c r="I81" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="J81" t="s">
-        <v>254</v>
+        <v>357</v>
       </c>
       <c r="K81" t="s">
-        <v>329</v>
+        <v>164</v>
       </c>
       <c r="L81" t="s">
         <v>26</v>
@@ -5431,39 +5461,39 @@
         <v>358</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>359</v>
       </c>
       <c r="B82" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="C82" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="D82" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E82" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F82" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G82" t="s">
-        <v>360</v>
+        <v>188</v>
       </c>
       <c r="H82" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I82" t="s">
         <v>23</v>
       </c>
       <c r="J82" t="s">
-        <v>324</v>
+        <v>297</v>
       </c>
       <c r="K82" t="s">
-        <v>239</v>
+        <v>360</v>
       </c>
       <c r="L82" t="s">
         <v>26</v>
@@ -5478,39 +5508,39 @@
         <v>361</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>362</v>
       </c>
       <c r="B83" t="s">
-        <v>315</v>
+        <v>244</v>
       </c>
       <c r="C83" t="s">
-        <v>285</v>
+        <v>116</v>
       </c>
       <c r="D83" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E83" t="s">
         <v>19</v>
       </c>
       <c r="F83" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="G83" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H83" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="I83" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="J83" t="s">
+        <v>300</v>
+      </c>
+      <c r="K83" t="s">
         <v>227</v>
-      </c>
-      <c r="K83" t="s">
-        <v>142</v>
       </c>
       <c r="L83" t="s">
         <v>26</v>
@@ -5525,321 +5555,321 @@
         <v>363</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>364</v>
       </c>
       <c r="B84" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C84" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D84" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E84" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F84" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="G84" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H84" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I84" t="s">
         <v>23</v>
       </c>
       <c r="J84" t="s">
-        <v>134</v>
+        <v>321</v>
       </c>
       <c r="K84" t="s">
+        <v>79</v>
+      </c>
+      <c r="L84" t="s">
+        <v>26</v>
+      </c>
+      <c r="M84" t="s">
+        <v>26</v>
+      </c>
+      <c r="N84" t="s">
+        <v>26</v>
+      </c>
+      <c r="O84" t="s">
         <v>365</v>
       </c>
-      <c r="L84" t="s">
-        <v>26</v>
-      </c>
-      <c r="M84" t="s">
-        <v>26</v>
-      </c>
-      <c r="N84" t="s">
-        <v>26</v>
-      </c>
-      <c r="O84" t="s">
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>367</v>
-      </c>
       <c r="B85" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="C85" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="D85" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E85" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F85" t="s">
-        <v>170</v>
+        <v>31</v>
       </c>
       <c r="G85" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="H85" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I85" t="s">
         <v>23</v>
       </c>
       <c r="J85" t="s">
+        <v>367</v>
+      </c>
+      <c r="K85" t="s">
         <v>368</v>
       </c>
-      <c r="K85" t="s">
+      <c r="L85" t="s">
+        <v>26</v>
+      </c>
+      <c r="M85" t="s">
+        <v>26</v>
+      </c>
+      <c r="N85" t="s">
+        <v>26</v>
+      </c>
+      <c r="O85" t="s">
         <v>369</v>
       </c>
-      <c r="L85" t="s">
-        <v>26</v>
-      </c>
-      <c r="M85" t="s">
-        <v>26</v>
-      </c>
-      <c r="N85" t="s">
-        <v>26</v>
-      </c>
-      <c r="O85" t="s">
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+      <c r="B86" t="s">
+        <v>59</v>
+      </c>
+      <c r="C86" t="s">
+        <v>60</v>
+      </c>
+      <c r="D86" t="s">
+        <v>18</v>
+      </c>
+      <c r="E86" t="s">
+        <v>49</v>
+      </c>
+      <c r="F86" t="s">
+        <v>54</v>
+      </c>
+      <c r="G86" t="s">
+        <v>26</v>
+      </c>
+      <c r="H86" t="s">
+        <v>33</v>
+      </c>
+      <c r="I86" t="s">
+        <v>23</v>
+      </c>
+      <c r="J86" t="s">
         <v>371</v>
       </c>
-      <c r="B86" t="s">
-        <v>146</v>
-      </c>
-      <c r="C86" t="s">
-        <v>26</v>
-      </c>
-      <c r="D86" t="s">
-        <v>26</v>
-      </c>
-      <c r="E86" t="s">
+      <c r="K86" t="s">
+        <v>269</v>
+      </c>
+      <c r="L86" t="s">
+        <v>26</v>
+      </c>
+      <c r="M86" t="s">
+        <v>26</v>
+      </c>
+      <c r="N86" t="s">
+        <v>26</v>
+      </c>
+      <c r="O86" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>373</v>
+      </c>
+      <c r="B87" t="s">
+        <v>29</v>
+      </c>
+      <c r="C87" t="s">
+        <v>30</v>
+      </c>
+      <c r="D87" t="s">
+        <v>18</v>
+      </c>
+      <c r="E87" t="s">
         <v>19</v>
       </c>
-      <c r="F86" t="s">
-        <v>30</v>
-      </c>
-      <c r="G86" t="s">
-        <v>31</v>
-      </c>
-      <c r="H86" t="s">
-        <v>22</v>
-      </c>
-      <c r="I86" t="s">
-        <v>26</v>
-      </c>
-      <c r="J86" t="s">
-        <v>372</v>
-      </c>
-      <c r="K86" t="s">
-        <v>373</v>
-      </c>
-      <c r="L86" t="s">
-        <v>26</v>
-      </c>
-      <c r="M86" t="s">
-        <v>26</v>
-      </c>
-      <c r="N86" t="s">
-        <v>26</v>
-      </c>
-      <c r="O86" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>375</v>
-      </c>
-      <c r="B87" t="s">
-        <v>68</v>
-      </c>
-      <c r="C87" t="s">
-        <v>69</v>
-      </c>
-      <c r="D87" t="s">
-        <v>38</v>
-      </c>
-      <c r="E87" t="s">
-        <v>39</v>
-      </c>
       <c r="F87" t="s">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="G87" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="H87" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I87" t="s">
         <v>23</v>
       </c>
       <c r="J87" t="s">
+        <v>374</v>
+      </c>
+      <c r="K87" t="s">
+        <v>109</v>
+      </c>
+      <c r="L87" t="s">
+        <v>26</v>
+      </c>
+      <c r="M87" t="s">
+        <v>26</v>
+      </c>
+      <c r="N87" t="s">
+        <v>26</v>
+      </c>
+      <c r="O87" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
         <v>376</v>
       </c>
-      <c r="K87" t="s">
-        <v>377</v>
-      </c>
-      <c r="L87" t="s">
-        <v>26</v>
-      </c>
-      <c r="M87" t="s">
-        <v>26</v>
-      </c>
-      <c r="N87" t="s">
-        <v>26</v>
-      </c>
-      <c r="O87" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>379</v>
-      </c>
       <c r="B88" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="C88" t="s">
-        <v>245</v>
+        <v>123</v>
       </c>
       <c r="D88" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E88" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F88" t="s">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="G88" t="s">
-        <v>31</v>
+        <v>259</v>
       </c>
       <c r="H88" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="I88" t="s">
         <v>23</v>
       </c>
       <c r="J88" t="s">
+        <v>136</v>
+      </c>
+      <c r="K88" t="s">
+        <v>94</v>
+      </c>
+      <c r="L88" t="s">
+        <v>26</v>
+      </c>
+      <c r="M88" t="s">
+        <v>26</v>
+      </c>
+      <c r="N88" t="s">
+        <v>26</v>
+      </c>
+      <c r="O88" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>378</v>
+      </c>
+      <c r="B89" t="s">
+        <v>379</v>
+      </c>
+      <c r="C89" t="s">
+        <v>351</v>
+      </c>
+      <c r="D89" t="s">
+        <v>40</v>
+      </c>
+      <c r="E89" t="s">
+        <v>19</v>
+      </c>
+      <c r="F89" t="s">
+        <v>144</v>
+      </c>
+      <c r="G89" t="s">
+        <v>66</v>
+      </c>
+      <c r="H89" t="s">
+        <v>33</v>
+      </c>
+      <c r="I89" t="s">
+        <v>26</v>
+      </c>
+      <c r="J89" t="s">
         <v>380</v>
       </c>
-      <c r="K88" t="s">
+      <c r="K89" t="s">
+        <v>174</v>
+      </c>
+      <c r="L89" t="s">
+        <v>26</v>
+      </c>
+      <c r="M89" t="s">
+        <v>26</v>
+      </c>
+      <c r="N89" t="s">
         <v>381</v>
       </c>
-      <c r="L88" t="s">
-        <v>26</v>
-      </c>
-      <c r="M88" t="s">
-        <v>96</v>
-      </c>
-      <c r="N88" t="s">
-        <v>26</v>
-      </c>
-      <c r="O88" t="s">
+      <c r="O89" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
         <v>383</v>
       </c>
-      <c r="B89" t="s">
-        <v>236</v>
-      </c>
-      <c r="C89" t="s">
-        <v>237</v>
-      </c>
-      <c r="D89" t="s">
-        <v>81</v>
-      </c>
-      <c r="E89" t="s">
-        <v>39</v>
-      </c>
-      <c r="F89" t="s">
-        <v>43</v>
-      </c>
-      <c r="G89" t="s">
-        <v>31</v>
-      </c>
-      <c r="H89" t="s">
-        <v>88</v>
-      </c>
-      <c r="I89" t="s">
-        <v>26</v>
-      </c>
-      <c r="J89" t="s">
-        <v>384</v>
-      </c>
-      <c r="K89" t="s">
-        <v>96</v>
-      </c>
-      <c r="L89" t="s">
-        <v>26</v>
-      </c>
-      <c r="M89" t="s">
-        <v>26</v>
-      </c>
-      <c r="N89" t="s">
-        <v>385</v>
-      </c>
-      <c r="O89" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>387</v>
-      </c>
       <c r="B90" t="s">
-        <v>168</v>
+        <v>379</v>
       </c>
       <c r="C90" t="s">
-        <v>169</v>
+        <v>351</v>
       </c>
       <c r="D90" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E90" t="s">
         <v>19</v>
       </c>
       <c r="F90" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="G90" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="H90" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="I90" t="s">
-        <v>155</v>
+        <v>26</v>
       </c>
       <c r="J90" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="K90" t="s">
-        <v>90</v>
+        <v>223</v>
       </c>
       <c r="L90" t="s">
         <v>26</v>
@@ -5848,92 +5878,92 @@
         <v>26</v>
       </c>
       <c r="N90" t="s">
-        <v>26</v>
+        <v>385</v>
       </c>
       <c r="O90" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B91" t="s">
+        <v>59</v>
+      </c>
+      <c r="C91" t="s">
+        <v>60</v>
+      </c>
+      <c r="D91" t="s">
+        <v>18</v>
+      </c>
+      <c r="E91" t="s">
         <v>49</v>
       </c>
-      <c r="C91" t="s">
-        <v>50</v>
-      </c>
-      <c r="D91" t="s">
-        <v>38</v>
-      </c>
-      <c r="E91" t="s">
-        <v>19</v>
-      </c>
       <c r="F91" t="s">
-        <v>170</v>
+        <v>54</v>
       </c>
       <c r="G91" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H91" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I91" t="s">
         <v>23</v>
       </c>
       <c r="J91" t="s">
+        <v>388</v>
+      </c>
+      <c r="K91" t="s">
+        <v>389</v>
+      </c>
+      <c r="L91" t="s">
+        <v>26</v>
+      </c>
+      <c r="M91" t="s">
+        <v>26</v>
+      </c>
+      <c r="N91" t="s">
+        <v>26</v>
+      </c>
+      <c r="O91" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
         <v>391</v>
       </c>
-      <c r="K91" t="s">
-        <v>178</v>
-      </c>
-      <c r="L91" t="s">
-        <v>26</v>
-      </c>
-      <c r="M91" t="s">
-        <v>26</v>
-      </c>
-      <c r="N91" t="s">
-        <v>26</v>
-      </c>
-      <c r="O91" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>393</v>
-      </c>
       <c r="B92" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="C92" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="D92" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E92" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F92" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="G92" t="s">
-        <v>302</v>
+        <v>103</v>
       </c>
       <c r="H92" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I92" t="s">
         <v>23</v>
       </c>
       <c r="J92" t="s">
-        <v>310</v>
+        <v>392</v>
       </c>
       <c r="K92" t="s">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="L92" t="s">
         <v>26</v>
@@ -5948,39 +5978,39 @@
         <v>394</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>395</v>
       </c>
       <c r="B93" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="C93" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="D93" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E93" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="F93" t="s">
-        <v>170</v>
+        <v>31</v>
       </c>
       <c r="G93" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="H93" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="I93" t="s">
-        <v>155</v>
+        <v>23</v>
       </c>
       <c r="J93" t="s">
         <v>396</v>
       </c>
       <c r="K93" t="s">
-        <v>239</v>
+        <v>137</v>
       </c>
       <c r="L93" t="s">
         <v>26</v>
@@ -5995,27 +6025,27 @@
         <v>397</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>398</v>
       </c>
       <c r="B94" t="s">
-        <v>315</v>
+        <v>82</v>
       </c>
       <c r="C94" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="D94" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="E94" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="F94" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G94" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="H94" t="s">
         <v>22</v>
@@ -6027,7 +6057,7 @@
         <v>399</v>
       </c>
       <c r="K94" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="L94" t="s">
         <v>26</v>
@@ -6042,45 +6072,45 @@
         <v>400</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>401</v>
       </c>
       <c r="B95" t="s">
+        <v>115</v>
+      </c>
+      <c r="C95" t="s">
         <v>402</v>
       </c>
-      <c r="C95" t="s">
-        <v>403</v>
-      </c>
       <c r="D95" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E95" t="s">
         <v>19</v>
       </c>
       <c r="F95" t="s">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="G95" t="s">
-        <v>204</v>
+        <v>66</v>
       </c>
       <c r="H95" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="I95" t="s">
         <v>26</v>
       </c>
       <c r="J95" t="s">
-        <v>230</v>
+        <v>403</v>
       </c>
       <c r="K95" t="s">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="L95" t="s">
         <v>26</v>
       </c>
       <c r="M95" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="N95" t="s">
         <v>26</v>
@@ -6089,51 +6119,239 @@
         <v>404</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>405</v>
       </c>
       <c r="B96" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="C96" t="s">
-        <v>245</v>
+        <v>402</v>
       </c>
       <c r="D96" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96" t="s">
+        <v>19</v>
+      </c>
+      <c r="F96" t="s">
+        <v>65</v>
+      </c>
+      <c r="G96" t="s">
+        <v>259</v>
+      </c>
+      <c r="H96" t="s">
+        <v>22</v>
+      </c>
+      <c r="I96" t="s">
+        <v>26</v>
+      </c>
+      <c r="J96" t="s">
+        <v>406</v>
+      </c>
+      <c r="K96" t="s">
+        <v>407</v>
+      </c>
+      <c r="L96" t="s">
+        <v>26</v>
+      </c>
+      <c r="M96" t="s">
+        <v>26</v>
+      </c>
+      <c r="N96" t="s">
+        <v>26</v>
+      </c>
+      <c r="O96" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>409</v>
+      </c>
+      <c r="B97" t="s">
         <v>38</v>
       </c>
-      <c r="E96" t="s">
+      <c r="C97" t="s">
         <v>39</v>
       </c>
-      <c r="F96" t="s">
-        <v>43</v>
-      </c>
-      <c r="G96" t="s">
-        <v>406</v>
-      </c>
-      <c r="H96" t="s">
-        <v>88</v>
-      </c>
-      <c r="I96" t="s">
+      <c r="D97" t="s">
+        <v>40</v>
+      </c>
+      <c r="E97" t="s">
+        <v>19</v>
+      </c>
+      <c r="F97" t="s">
+        <v>54</v>
+      </c>
+      <c r="G97" t="s">
+        <v>26</v>
+      </c>
+      <c r="H97" t="s">
+        <v>22</v>
+      </c>
+      <c r="I97" t="s">
         <v>23</v>
       </c>
-      <c r="J96" t="s">
-        <v>407</v>
-      </c>
-      <c r="K96" t="s">
-        <v>287</v>
-      </c>
-      <c r="L96" t="s">
-        <v>26</v>
-      </c>
-      <c r="M96" t="s">
-        <v>26</v>
-      </c>
-      <c r="N96" t="s">
-        <v>408</v>
-      </c>
-      <c r="O96" t="s">
-        <v>409</v>
+      <c r="J97" t="s">
+        <v>410</v>
+      </c>
+      <c r="K97" t="s">
+        <v>411</v>
+      </c>
+      <c r="L97" t="s">
+        <v>26</v>
+      </c>
+      <c r="M97" t="s">
+        <v>26</v>
+      </c>
+      <c r="N97" t="s">
+        <v>26</v>
+      </c>
+      <c r="O97" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>413</v>
+      </c>
+      <c r="B98" t="s">
+        <v>47</v>
+      </c>
+      <c r="C98" t="s">
+        <v>123</v>
+      </c>
+      <c r="D98" t="s">
+        <v>18</v>
+      </c>
+      <c r="E98" t="s">
+        <v>49</v>
+      </c>
+      <c r="F98" t="s">
+        <v>31</v>
+      </c>
+      <c r="G98" t="s">
+        <v>259</v>
+      </c>
+      <c r="H98" t="s">
+        <v>33</v>
+      </c>
+      <c r="I98" t="s">
+        <v>23</v>
+      </c>
+      <c r="J98" t="s">
+        <v>73</v>
+      </c>
+      <c r="K98" t="s">
+        <v>137</v>
+      </c>
+      <c r="L98" t="s">
+        <v>26</v>
+      </c>
+      <c r="M98" t="s">
+        <v>26</v>
+      </c>
+      <c r="N98" t="s">
+        <v>26</v>
+      </c>
+      <c r="O98" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>415</v>
+      </c>
+      <c r="B99" t="s">
+        <v>29</v>
+      </c>
+      <c r="C99" t="s">
+        <v>30</v>
+      </c>
+      <c r="D99" t="s">
+        <v>18</v>
+      </c>
+      <c r="E99" t="s">
+        <v>19</v>
+      </c>
+      <c r="F99" t="s">
+        <v>41</v>
+      </c>
+      <c r="G99" t="s">
+        <v>66</v>
+      </c>
+      <c r="H99" t="s">
+        <v>33</v>
+      </c>
+      <c r="I99" t="s">
+        <v>23</v>
+      </c>
+      <c r="J99" t="s">
+        <v>416</v>
+      </c>
+      <c r="K99" t="s">
+        <v>74</v>
+      </c>
+      <c r="L99" t="s">
+        <v>26</v>
+      </c>
+      <c r="M99" t="s">
+        <v>26</v>
+      </c>
+      <c r="N99" t="s">
+        <v>26</v>
+      </c>
+      <c r="O99" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>418</v>
+      </c>
+      <c r="B100" t="s">
+        <v>149</v>
+      </c>
+      <c r="C100" t="s">
+        <v>26</v>
+      </c>
+      <c r="D100" t="s">
+        <v>26</v>
+      </c>
+      <c r="E100" t="s">
+        <v>49</v>
+      </c>
+      <c r="F100" t="s">
+        <v>31</v>
+      </c>
+      <c r="G100" t="s">
+        <v>66</v>
+      </c>
+      <c r="H100" t="s">
+        <v>33</v>
+      </c>
+      <c r="I100" t="s">
+        <v>26</v>
+      </c>
+      <c r="J100" t="s">
+        <v>321</v>
+      </c>
+      <c r="K100" t="s">
+        <v>393</v>
+      </c>
+      <c r="L100" t="s">
+        <v>26</v>
+      </c>
+      <c r="M100" t="s">
+        <v>26</v>
+      </c>
+      <c r="N100" t="s">
+        <v>26</v>
+      </c>
+      <c r="O100" t="s">
+        <v>419</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DFE0660-B827-4326-96FE-B28A784C4592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE101934-9FA6-4A56-803A-2DD22EA1927E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1680" uniqueCount="459">
   <si>
     <t>Time</t>
   </si>
@@ -62,7 +62,373 @@
     <t>Event URL</t>
   </si>
   <si>
-    <t>07/02/2026 5:12:33 PM</t>
+    <t>07/09/2026 8:14:20 PM</t>
+  </si>
+  <si>
+    <t>658 - Medium</t>
+  </si>
+  <si>
+    <t>Paul Kunze Jr</t>
+  </si>
+  <si>
+    <t>Active Drivers, Towing and Recovery</t>
+  </si>
+  <si>
+    <t>HAAS Alert, Towing and Recovery</t>
+  </si>
+  <si>
+    <t>Mobile Usage</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>Tim Neff Jr.</t>
+  </si>
+  <si>
+    <t>Martin Luther King Junior Parkway, Beaumont, TX, 77701</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544549cd-f00d-52ad-bb3e-9c69ddab7b28</t>
+  </si>
+  <si>
+    <t>07/09/2026 6:39:52 PM</t>
+  </si>
+  <si>
+    <t>646 - Medium</t>
+  </si>
+  <si>
+    <t>Heavy Speeding</t>
+  </si>
+  <si>
+    <t>Speed Sign Verified</t>
+  </si>
+  <si>
+    <t>US 69;US 96;US 287, Beaumont, TX, 77710</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454977-71c3-5f5a-bf2e-b3c5aa74eb3b</t>
+  </si>
+  <si>
+    <t>07/09/2026 12:48:10 PM</t>
+  </si>
+  <si>
+    <t>649 - Heavy</t>
+  </si>
+  <si>
+    <t>Juan Ramirez</t>
+  </si>
+  <si>
+    <t>HAAS Alert, Heavy Haul</t>
+  </si>
+  <si>
+    <t>Rolling Stop</t>
+  </si>
+  <si>
+    <t>Wet Road, Parking Lot, Light Traffic</t>
+  </si>
+  <si>
+    <t>Coached</t>
+  </si>
+  <si>
+    <t>East Cardinal Drive, Beaumont, TX, 77710</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454835-75ef-50af-9cc5-ddbc6ec0876d</t>
+  </si>
+  <si>
+    <t>07/09/2026 8:25:14 AM</t>
+  </si>
+  <si>
+    <t>680 - Medium</t>
+  </si>
+  <si>
+    <t>Jesus Carbajal</t>
+  </si>
+  <si>
+    <t>Severe Speeding</t>
+  </si>
+  <si>
+    <t>I 10, Winnie, TX</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454744-bb1a-5daa-9bcb-7e498329e50f</t>
+  </si>
+  <si>
+    <t>07/09/2026 8:21:14 AM</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454741-119c-5c13-bbb1-f4cc40c3ab18</t>
+  </si>
+  <si>
+    <t>07/08/2026 7:35:24 PM</t>
+  </si>
+  <si>
+    <t>Construction, Light Traffic</t>
+  </si>
+  <si>
+    <t>Interstate 10 South Frontage Road, Beaumont, TX, 77702</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>0.52</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454483-ec91-5665-aed8-abe284d1a541</t>
+  </si>
+  <si>
+    <t>07/08/2026 3:35:11 PM</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544543a8-00dc-586d-92c6-afc9fa51f693</t>
+  </si>
+  <si>
+    <t>07/08/2026 10:54:22 AM</t>
+  </si>
+  <si>
+    <t>641 - Heavy</t>
+  </si>
+  <si>
+    <t>Adam Johnson</t>
+  </si>
+  <si>
+    <t>Active Drivers, Heavy Haul</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544542a6-e822-5dfd-960f-d9a17ff69650</t>
+  </si>
+  <si>
+    <t>07/08/2026 9:10:13 AM</t>
+  </si>
+  <si>
+    <t>685 - Medium</t>
+  </si>
+  <si>
+    <t>Jammie Singleton</t>
+  </si>
+  <si>
+    <t>Following Distance</t>
+  </si>
+  <si>
+    <t>Moderate Traffic</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454247-8d4f-5875-9229-50054cf58c0e</t>
+  </si>
+  <si>
+    <t>07/07/2026 10:08:17 PM</t>
+  </si>
+  <si>
+    <t>667 - Medium</t>
+  </si>
+  <si>
+    <t>Jeremy Myers</t>
+  </si>
+  <si>
+    <t>Towing and Recovery</t>
+  </si>
+  <si>
+    <t>US 69;US 287, Lumberton, TX, 77657</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453fe9-896a-5edb-bea5-59308595e899</t>
+  </si>
+  <si>
+    <t>07/07/2026 8:40:51 PM</t>
+  </si>
+  <si>
+    <t>625 - Heavy</t>
+  </si>
+  <si>
+    <t>I 10, 18.8 mi SE Liberty, Chambers County, TX</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453f99-7d2f-53e3-befe-f1791d246378</t>
+  </si>
+  <si>
+    <t>07/07/2026 8:21:33 PM</t>
+  </si>
+  <si>
+    <t>US Highway 90, Felicia, TX</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453f87-d216-5e0f-a6e4-fa3a620e8365</t>
+  </si>
+  <si>
+    <t>07/07/2026 6:49:42 PM</t>
+  </si>
+  <si>
+    <t>Passengers, Light Traffic</t>
+  </si>
+  <si>
+    <t>I 10, 19.7 mi SE Liberty, Chambers County, TX</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453f33-bb61-5847-8f5f-91a6e4c42900</t>
+  </si>
+  <si>
+    <t>07/07/2026 6:36:21 PM</t>
+  </si>
+  <si>
+    <t>Wet Road, Congested</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453f27-8226-5bb4-8ef8-dcd03d721cba</t>
+  </si>
+  <si>
+    <t>07/07/2026 6:26:13 PM</t>
+  </si>
+  <si>
+    <t>683 - Heavy</t>
+  </si>
+  <si>
+    <t>Jonathan Walters</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453f1e-3a9d-576e-965e-f8c65f3564b0</t>
+  </si>
+  <si>
+    <t>07/07/2026 12:55:40 PM</t>
+  </si>
+  <si>
+    <t>659 - Heavy</t>
+  </si>
+  <si>
+    <t>Thomas Neff III</t>
+  </si>
+  <si>
+    <t>Fannett Road, Beaumont, TX, 77705</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453def-98ff-502f-8ca7-7264394e93f7</t>
+  </si>
+  <si>
+    <t>07/07/2026 12:13:12 PM</t>
+  </si>
+  <si>
+    <t>Creole Nature Trail All-American Road, Calcasieu Parish, LA</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453dc8-b8e9-5241-9c46-807d0ae54e01</t>
+  </si>
+  <si>
+    <t>07/07/2026 6:55:34 AM</t>
+  </si>
+  <si>
+    <t>662 - Heavy</t>
+  </si>
+  <si>
+    <t>Drew Template</t>
+  </si>
+  <si>
+    <t>I 10, 14.1 mi ENE Baytown, Chambers County, TX, 77580</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453ca5-eb68-52ed-befe-9a727facddbe</t>
+  </si>
+  <si>
+    <t>07/06/2026 6:03:50 PM</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544539e3-6084-5ae3-bb67-44dcf860c866</t>
+  </si>
+  <si>
+    <t>07/05/2026 10:41:08 PM</t>
+  </si>
+  <si>
+    <t>Atchafalaya Basin Bridge, Henderson, LA</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544535ba-e48d-50fe-9c3d-bd2b5092e628</t>
+  </si>
+  <si>
+    <t>07/03/2026 1:40:22 PM</t>
+  </si>
+  <si>
+    <t>669 - Heavy</t>
+  </si>
+  <si>
+    <t>Jason Walker</t>
+  </si>
+  <si>
+    <t>No Seat Belt</t>
+  </si>
+  <si>
+    <t>Dowling Road, Port Arthur, TX</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445297f-152b-5754-9e25-40e4e4ae62e9</t>
+  </si>
+  <si>
+    <t>07/03/2026 11:57:24 AM</t>
+  </si>
+  <si>
+    <t>Port Arthur Road, Port Arthur, TX, 77705</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452920-d1d8-59eb-b096-728d2ee5d607</t>
+  </si>
+  <si>
+    <t>07/02/2026 4:12:33 PM</t>
   </si>
   <si>
     <t>629 - Heavy</t>
@@ -71,54 +437,21 @@
     <t>Harley Tidwell</t>
   </si>
   <si>
-    <t>Active Drivers, Towing and Recovery</t>
-  </si>
-  <si>
-    <t>HAAS Alert, Heavy Haul</t>
-  </si>
-  <si>
-    <t>Heavy Speeding</t>
-  </si>
-  <si>
-    <t>Speed Sign Verified</t>
-  </si>
-  <si>
-    <t>Coached</t>
-  </si>
-  <si>
-    <t>Tim Neff Jr.</t>
-  </si>
-  <si>
     <t>Creole Nature Trail All-American Road, Sulphur, LA, 70663</t>
   </si>
   <si>
     <t>73</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544524e4-0e81-5c5c-a460-ff689cc97daf</t>
   </si>
   <si>
-    <t>07/02/2026 4:49:00 PM</t>
-  </si>
-  <si>
-    <t>669 - Heavy</t>
-  </si>
-  <si>
-    <t>Jason Walker</t>
-  </si>
-  <si>
-    <t>Mobile Usage</t>
+    <t>07/02/2026 3:49:00 PM</t>
   </si>
   <si>
     <t>Wet Road, Light Traffic</t>
   </si>
   <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
     <t>Walden Road, Beaumont, TX, 77705</t>
   </si>
   <si>
@@ -128,43 +461,22 @@
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544524ce-7fa8-58dd-910f-84869b9ab43f</t>
   </si>
   <si>
-    <t>07/02/2026 2:57:58 PM</t>
-  </si>
-  <si>
-    <t>641 - Heavy</t>
-  </si>
-  <si>
-    <t>Adam Johnson</t>
-  </si>
-  <si>
-    <t>Active Drivers, Heavy Haul</t>
-  </si>
-  <si>
-    <t>Following Distance</t>
-  </si>
-  <si>
-    <t>Moderate Traffic</t>
+    <t>07/02/2026 1:57:58 PM</t>
   </si>
   <si>
     <t>I 10;US 90, Rose City, TX, 77662</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452468-d67a-595f-9e91-90e100223163</t>
   </si>
   <si>
-    <t>07/01/2026 12:35:29 PM</t>
-  </si>
-  <si>
-    <t>658 - Medium</t>
+    <t>07/01/2026 11:35:29 AM</t>
   </si>
   <si>
     <t>Phillip Metz</t>
   </si>
   <si>
-    <t>HAAS Alert, Towing and Recovery</t>
+    <t>Phillip W Metz</t>
   </si>
   <si>
     <t>East Freeway, Channelview, TX, 77530</t>
@@ -176,946 +488,817 @@
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451ec0-085f-56a4-bd8c-a28cd6a152aa</t>
   </si>
   <si>
-    <t>07/01/2026 12:08:06 PM</t>
+    <t>07/01/2026 10:01:54 AM</t>
+  </si>
+  <si>
+    <t>Parking Lot, Light Traffic</t>
+  </si>
+  <si>
+    <t>6155 Eastex Freeway Frontage Road, Beaumont, TX, 77706</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451e6a-5c5f-58a9-ae02-c239247de4e5</t>
+  </si>
+  <si>
+    <t>06/30/2026 5:33:35 PM</t>
+  </si>
+  <si>
+    <t>46733 I-10 Frontage Road, Winnie, TX, 77665</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451ae1-87c2-5135-b4f0-eab364728ee4</t>
+  </si>
+  <si>
+    <t>06/30/2026 2:45:32 PM</t>
+  </si>
+  <si>
+    <t>I 10, Beaumont, TX, 77705</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451a47-ad87-5fb7-a6d7-1bf798bc9f48</t>
+  </si>
+  <si>
+    <t>06/30/2026 1:25:53 AM</t>
+  </si>
+  <si>
+    <t>Drowsiness</t>
+  </si>
+  <si>
+    <t>Moderately Drowsy, Construction, Light Traffic, Night</t>
+  </si>
+  <si>
+    <t>US 69;US 96;US 287, Loeb, TX, 77657</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445176b-900a-5030-9c5c-f45149ae21dc</t>
+  </si>
+  <si>
+    <t>06/29/2026 5:45:25 PM</t>
+  </si>
+  <si>
+    <t>TX 124, Stowell, TX, 77661</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544515c6-0006-56ad-b973-19cc55a23aac</t>
+  </si>
+  <si>
+    <t>06/29/2026 10:23:34 AM</t>
+  </si>
+  <si>
+    <t>US 69;US 96;US 287, Loeb, TX</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451431-78bb-5436-96d6-3c70d67fb881</t>
+  </si>
+  <si>
+    <t>06/29/2026 9:19:27 AM</t>
+  </si>
+  <si>
+    <t>North Dorman Road, 4.8 mi NNE Bridge City, Orange County, TX, 77630</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544513f6-c68b-542c-9f35-22427550e8bd</t>
+  </si>
+  <si>
+    <t>06/29/2026 7:54:50 AM</t>
+  </si>
+  <si>
+    <t>US 90, Nome, TX, 77629</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544513a9-4e6a-5777-b020-ae490b0ad885</t>
+  </si>
+  <si>
+    <t>06/28/2026 7:19:03 PM</t>
+  </si>
+  <si>
+    <t>Gary Worley</t>
+  </si>
+  <si>
+    <t>Eddie Bowden</t>
+  </si>
+  <si>
+    <t>US 90, China, TX, 77613</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544510f5-5d50-549b-869b-bddc80251d19</t>
+  </si>
+  <si>
+    <t>06/27/2026 4:25:06 PM</t>
+  </si>
+  <si>
+    <t>Inattentive Driving</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450b2f-be05-543b-acec-2c7c24ae13ce</t>
+  </si>
+  <si>
+    <t>06/26/2026 2:30:01 PM</t>
+  </si>
+  <si>
+    <t>US 69;US 96;US 287, Beaumont, TX, 77701</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544505a0-0548-52df-90bb-6baf18f84b57</t>
+  </si>
+  <si>
+    <t>06/26/2026 2:27:58 PM</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445059e-2881-5100-83b4-1f5b093312d4</t>
+  </si>
+  <si>
+    <t>06/25/2026 3:46:02 PM</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544500bf-4275-5ded-85e2-3ee8f4e6d92b</t>
+  </si>
+  <si>
+    <t>06/25/2026 11:16:55 AM</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ffc8-df6a-5dea-9370-f13b79e392c6</t>
+  </si>
+  <si>
+    <t>06/25/2026 10:15:11 AM</t>
+  </si>
+  <si>
+    <t>Harsh Brake</t>
+  </si>
+  <si>
+    <t>East Freeway Frontage Road, Houston, TX, 77020</t>
+  </si>
+  <si>
+    <t>0.67</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ff90-5d57-5dc0-a571-4d8c6dcde945</t>
+  </si>
+  <si>
+    <t>06/25/2026 9:09:43 AM</t>
+  </si>
+  <si>
+    <t>668 - Light</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ff54-6b07-5d1d-8dc0-8053502f47ef</t>
+  </si>
+  <si>
+    <t>06/24/2026 12:15:17 PM</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fad7-f51b-528d-8ce9-9658a4c0b9e5</t>
+  </si>
+  <si>
+    <t>06/23/2026 10:02:05 AM</t>
+  </si>
+  <si>
+    <t>I 10 Frontage Road, 24.6 mi SE Liberty, Chambers County, TX</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>0.55</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f537-a7f7-5b50-be7d-fcffb700b16d</t>
+  </si>
+  <si>
+    <t>06/22/2026 10:26:05 AM</t>
+  </si>
+  <si>
+    <t>692 - Heavy</t>
+  </si>
+  <si>
+    <t>William Foley</t>
+  </si>
+  <si>
+    <t>I 45, Madisonville, TX, 77864</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f027-4165-5f24-8d32-d9f65658b1d2</t>
+  </si>
+  <si>
+    <t>06/19/2026 3:15:44 PM</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e1bd-5e83-597e-995e-9c0f9e74b244</t>
+  </si>
+  <si>
+    <t>06/18/2026 3:34:01 PM</t>
   </si>
   <si>
     <t>Obstructed Camera</t>
   </si>
   <si>
-    <t>North Main Street, Lumberton, TX, 77657</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451ea6-f54f-5727-9c92-1efb2075136e</t>
-  </si>
-  <si>
-    <t>07/01/2026 11:01:54 AM</t>
-  </si>
-  <si>
-    <t>680 - Medium</t>
-  </si>
-  <si>
-    <t>Jesus Carbajal</t>
-  </si>
-  <si>
-    <t>Parking Lot, Light Traffic</t>
-  </si>
-  <si>
-    <t>6155 Eastex Freeway Frontage Road, Beaumont, TX, 77706</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451e6a-5c5f-58a9-ae02-c239247de4e5</t>
-  </si>
-  <si>
-    <t>06/30/2026 6:33:35 PM</t>
-  </si>
-  <si>
-    <t>No Seat Belt</t>
-  </si>
-  <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
-    <t>46733 I-10 Frontage Road, Winnie, TX, 77665</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451ae1-87c2-5135-b4f0-eab364728ee4</t>
-  </si>
-  <si>
-    <t>06/30/2026 3:45:32 PM</t>
-  </si>
-  <si>
-    <t>659 - Heavy</t>
-  </si>
-  <si>
-    <t>Thomas Neff III</t>
-  </si>
-  <si>
-    <t>I 10, Beaumont, TX, 77705</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451a47-ad87-5fb7-a6d7-1bf798bc9f48</t>
-  </si>
-  <si>
-    <t>06/30/2026 1:43:51 PM</t>
-  </si>
-  <si>
-    <t>Emergency Lights, Speed Sign Verified</t>
-  </si>
-  <si>
-    <t>Port Arthur Road, Port Arthur, TX, 77705</t>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445dca7-bd7e-50f6-b2da-d0e7f3669228</t>
+  </si>
+  <si>
+    <t>06/18/2026 7:05:45 AM</t>
+  </si>
+  <si>
+    <t>Christopher Marcantel</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445dad6-6838-50e1-a08f-721a3f1f36df</t>
+  </si>
+  <si>
+    <t>06/17/2026 4:02:17 PM</t>
+  </si>
+  <si>
+    <t>Dwayne Manuel</t>
+  </si>
+  <si>
+    <t>H O Mills Highway, Port Arthur, TX</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d79b-44e0-5b5f-afa1-10741c645e86</t>
+  </si>
+  <si>
+    <t>06/17/2026 10:28:09 AM</t>
+  </si>
+  <si>
+    <t>College Street, Beaumont, TX, 77702</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d669-5d00-570d-892c-3b3bcb44e34d</t>
+  </si>
+  <si>
+    <t>06/15/2026 4:53:31 PM</t>
+  </si>
+  <si>
+    <t>5230 North Major Drive, Beaumont, TX, 77705</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cd7d-73a6-51c3-baf6-41a38469fe10</t>
+  </si>
+  <si>
+    <t>06/15/2026 12:23:54 PM</t>
+  </si>
+  <si>
+    <t>Wet Road, Light Traffic, Raining</t>
+  </si>
+  <si>
+    <t>State Highway 326, Sour Lake, TX, 77659</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cc86-9c64-5c62-a497-759c62f256a9</t>
+  </si>
+  <si>
+    <t>06/14/2026 10:39:04 AM</t>
+  </si>
+  <si>
+    <t>State Highway 124, Hamshire, TX, 77622</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c700-47f3-56b1-b136-8c61392947bb</t>
+  </si>
+  <si>
+    <t>06/14/2026 8:48:42 AM</t>
+  </si>
+  <si>
+    <t>644 - Medium</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c69b-3b3b-50b6-9299-c5f9408304d6</t>
+  </si>
+  <si>
+    <t>06/13/2026 11:03:26 PM</t>
+  </si>
+  <si>
+    <t>FM 365, 9.6 mi WSW Nederland, Jefferson County, TX</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c483-6560-5f24-a5a4-1196fcf0710d</t>
+  </si>
+  <si>
+    <t>06/13/2026 4:24:44 PM</t>
+  </si>
+  <si>
+    <t>Fannett Road, Beaumont, TX, 77701</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c316-622e-5089-9af0-e3644e669122</t>
+  </si>
+  <si>
+    <t>06/13/2026 3:18:06 PM</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c2d9-604f-59f0-87e5-6a5c05c198bc</t>
+  </si>
+  <si>
+    <t>06/12/2026 8:27:53 AM</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bc3b-756c-5d9e-9d81-2830d4d259b7</t>
+  </si>
+  <si>
+    <t>06/12/2026 6:39:02 AM</t>
+  </si>
+  <si>
+    <t>Dupont Drive, West Orange, TX, 77630</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bbd7-ce4d-5d05-b19f-5787bf9d3e6c</t>
+  </si>
+  <si>
+    <t>06/12/2026 6:17:24 AM</t>
+  </si>
+  <si>
+    <t>TX 73, Port Arthur, TX, 77640</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bbc3-fc20-5357-b19e-8917e5854b0b</t>
+  </si>
+  <si>
+    <t>06/12/2026 1:36:49 AM</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bac3-1a90-5376-b4c0-879059363b9a</t>
+  </si>
+  <si>
+    <t>06/11/2026 9:09:35 PM</t>
+  </si>
+  <si>
+    <t>Moderately Drowsy, Light Traffic, Night</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b9ce-7522-5e34-bee1-b027d6f0c003</t>
+  </si>
+  <si>
+    <t>06/10/2026 3:50:31 PM</t>
+  </si>
+  <si>
+    <t>State Route 109, Starks, LA</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b383-f8ee-57b2-b3a2-576df0f3920d</t>
+  </si>
+  <si>
+    <t>06/10/2026 9:04:03 AM</t>
+  </si>
+  <si>
+    <t>5020 Fannett Road, Beaumont, TX, 77705</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b20f-d7d1-559a-a6fe-1633a24b3ed4</t>
+  </si>
+  <si>
+    <t>06/07/2026 1:14:46 PM</t>
+  </si>
+  <si>
+    <t>673 - Heavy</t>
+  </si>
+  <si>
+    <t>Kyle Ray</t>
+  </si>
+  <si>
+    <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
+  </si>
+  <si>
+    <t>I 10, Welsh, LA, 70581</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a382-4d73-5bb1-b5db-a39ca69f4b45</t>
+  </si>
+  <si>
+    <t>06/06/2026 7:18:21 AM</t>
+  </si>
+  <si>
+    <t>696 - Medium</t>
+  </si>
+  <si>
+    <t>5225 Fannett Road, Beaumont, TX, 77705</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459d15-a3c3-5e99-83f7-c781117f27a0</t>
+  </si>
+  <si>
+    <t>06/04/2026 1:15:03 PM</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445940f-7e14-5c0f-aa68-07d221d9e214</t>
+  </si>
+  <si>
+    <t>06/03/2026 9:10:14 AM</t>
+  </si>
+  <si>
+    <t>632 - Heavy</t>
+  </si>
+  <si>
+    <t>Hufsmith Kohrville Road, 4.1 mi SSE Tomball, Harris County, TX, 77375</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458e08-fce4-50c2-a0a6-5143a8afefc2</t>
+  </si>
+  <si>
+    <t>05/29/2026 11:42:54 AM</t>
+  </si>
+  <si>
+    <t>I 10, Seguin, TX, 78638</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544574d4-f86a-51ab-8240-5abf48d2eb45</t>
+  </si>
+  <si>
+    <t>05/28/2026 3:24:20 PM</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457079-5686-54e8-8a42-3ea1c6f860e5</t>
+  </si>
+  <si>
+    <t>05/28/2026 12:48:42 PM</t>
+  </si>
+  <si>
+    <t>660 - Heavy</t>
+  </si>
+  <si>
+    <t>Billy Johnson</t>
+  </si>
+  <si>
+    <t>Active Drivers, HAAS Alert, Heavy Haul, Towing and Recovery</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456fea-dac1-5b56-beb5-7a334db4549a</t>
+  </si>
+  <si>
+    <t>05/27/2026 11:14:01 PM</t>
+  </si>
+  <si>
+    <t>Light Traffic, Night</t>
+  </si>
+  <si>
+    <t>East Parkway Street, Groves, TX, 77619</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456d00-fb6e-5da8-9ac8-5b4748eeabcb</t>
+  </si>
+  <si>
+    <t>05/23/2026 9:35:24 AM</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445557a-13c8-58c7-91dd-c320f5c8cfc4</t>
+  </si>
+  <si>
+    <t>05/20/2026 9:02:55 PM</t>
+  </si>
+  <si>
+    <t>2706 Irving Avenue, Beaumont, TX, 77701</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445487c-7266-58c3-95b0-bb9b5182787c</t>
+  </si>
+  <si>
+    <t>05/20/2026 4:13:08 PM</t>
+  </si>
+  <si>
+    <t>I 10, 11.5 mi SW Beaumont, Jefferson County, TX</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454773-2263-5caf-9487-742896f74a00</t>
+  </si>
+  <si>
+    <t>05/19/2026 8:16:41 PM</t>
+  </si>
+  <si>
+    <t>3777 South 11th Street, Beaumont, TX, 77705</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445432b-c0f7-5407-ab0e-1be086171464</t>
+  </si>
+  <si>
+    <t>05/17/2026 11:48:35 AM</t>
+  </si>
+  <si>
+    <t>959 South 4th Street, Beaumont, TX, 77701</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445370d-dcb1-54d0-9764-b9756c5f4a28</t>
+  </si>
+  <si>
+    <t>05/16/2026 8:21:16 PM</t>
+  </si>
+  <si>
+    <t>Construction, Moderate Traffic, Night</t>
+  </si>
+  <si>
+    <t>I 10;US 90, Vidor, TX, 77662</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544533bc-e027-5557-b78e-89930845d14b</t>
+  </si>
+  <si>
+    <t>05/15/2026 10:50:46 AM</t>
+  </si>
+  <si>
+    <t>634 - Heavy</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452c8c-35cb-5042-8396-5318d3f2fd79</t>
+  </si>
+  <si>
+    <t>05/08/2026 12:47:14 AM</t>
+  </si>
+  <si>
+    <t>7282 Garth Street, Cheek, TX, 77705</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450657-2264-540c-a356-04b8b65790a7</t>
+  </si>
+  <si>
+    <t>05/06/2026 5:15:28 PM</t>
+  </si>
+  <si>
+    <t>Professional Drive, Port Arthur, TX, 77627</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ff93-2bc8-5ff4-87de-ffed8bce9121</t>
+  </si>
+  <si>
+    <t>05/06/2026 9:49:01 AM</t>
+  </si>
+  <si>
+    <t>Very Drowsy, Light Traffic</t>
+  </si>
+  <si>
+    <t>I 10, Eminence, TX, 77597</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fdfa-6df8-54f7-bf4a-fab794afbe08</t>
+  </si>
+  <si>
+    <t>05/04/2026 1:55:02 PM</t>
+  </si>
+  <si>
+    <t>West Cardinal Drive, Beaumont, TX, 77710</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f48e-f389-50f8-87be-6562e2798e54</t>
+  </si>
+  <si>
+    <t>05/04/2026 10:04:48 AM</t>
+  </si>
+  <si>
+    <t>5269 Mustang-Chocolate Bayou Road, Liverpool, TX, 77511</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f3bc-29ec-5cbd-8282-0b221781d62e</t>
+  </si>
+  <si>
+    <t>05/03/2026 6:49:58 PM</t>
+  </si>
+  <si>
+    <t>362 Simmons Road, 1.9 mi N Vidor, Orange County, TX, 77662</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f076-9dc7-55a8-867a-6a41fd2b62ac</t>
+  </si>
+  <si>
+    <t>05/02/2026 6:49:16 AM</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e8bc-6e70-5526-87d9-b05bb8910029</t>
+  </si>
+  <si>
+    <t>05/01/2026 5:35:06 PM</t>
+  </si>
+  <si>
+    <t>6425 Highway 347, Beaumont, TX, 77705</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e5e5-5b1b-523d-ab9c-a26f380cefef</t>
+  </si>
+  <si>
+    <t>05/01/2026 5:20:21 PM</t>
+  </si>
+  <si>
+    <t>FM 366, Groves, TX, 77651</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e5d7-d728-50d0-8a79-285ccb21062a</t>
+  </si>
+  <si>
+    <t>05/01/2026 8:24:31 AM</t>
+  </si>
+  <si>
+    <t>Wet Road, Construction, Light Traffic</t>
+  </si>
+  <si>
+    <t>State Highway 124, Cheek, TX, 77705</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e3ed-47e7-5957-ba13-b0bea3bf1b0d</t>
+  </si>
+  <si>
+    <t>04/30/2026 9:24:39 PM</t>
+  </si>
+  <si>
+    <t>Very Drowsy, Wet Road, Light Traffic, Night</t>
+  </si>
+  <si>
+    <t>7743 TX 105, Beaumont, TX, 77713</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e191-28b2-53d4-beb2-41c48d1673bc</t>
+  </si>
+  <si>
+    <t>04/28/2026 1:56:41 PM</t>
+  </si>
+  <si>
+    <t>South Major Drive, Beaumont, TX, 77705</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d5aa-4dd2-5073-adcd-a728d6e756c6</t>
+  </si>
+  <si>
+    <t>04/28/2026 9:39:38 AM</t>
+  </si>
+  <si>
+    <t>I 10, Vinton, LA, 70668</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d4be-f767-5552-9776-eea7c53edc2d</t>
+  </si>
+  <si>
+    <t>04/27/2026 5:19:35 PM</t>
+  </si>
+  <si>
+    <t>12.8 mi SW Beaumont, Jefferson County, TX</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d13d-b4f6-5a82-bd3b-3d99bfc16a01</t>
+  </si>
+  <si>
+    <t>04/27/2026 7:54:16 AM</t>
+  </si>
+  <si>
+    <t>272 5th Street, Sour Lake, TX, 77659</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cf38-25f0-54ef-8b24-354e43be286d</t>
+  </si>
+  <si>
+    <t>04/26/2026 2:30:04 PM</t>
+  </si>
+  <si>
+    <t>State Highway 73, Winnie, TX, 77665</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cb7c-286d-5c30-82b5-a900c5aaf727</t>
+  </si>
+  <si>
+    <t>04/24/2026 7:06:44 PM</t>
+  </si>
+  <si>
+    <t>7838 Fannett Road, Beaumont, TX, 77705</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c22c-b8a8-56e7-91dd-e75155840d5d</t>
+  </si>
+  <si>
+    <t>04/24/2026 12:19:55 PM</t>
+  </si>
+  <si>
+    <t>4039 Washington Boulevard, Beaumont, TX, 77705</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c0b8-4808-566d-a30c-abb96659aacf</t>
+  </si>
+  <si>
+    <t>04/23/2026 12:47:25 PM</t>
+  </si>
+  <si>
+    <t>8401 Washington Boulevard, Beaumont, TX, 77707</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>0.61</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bbab-17ef-5346-9a45-c49e8341e9be</t>
+  </si>
+  <si>
+    <t>04/22/2026 5:29:50 AM</t>
+  </si>
+  <si>
+    <t>Fred Hartman Bridge, Baytown, TX</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b4f4-1f22-5ef3-9175-aee791790b8b</t>
+  </si>
+  <si>
+    <t>04/21/2026 4:20:10 PM</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b221-27f0-520a-b7e1-6dca1413a74b</t>
+  </si>
+  <si>
+    <t>04/21/2026 1:19:20 PM</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b17b-997e-5ccd-9142-896d210e168f</t>
+  </si>
+  <si>
+    <t>04/20/2026 9:49:13 AM</t>
   </si>
   <si>
     <t>56</t>
   </si>
   <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544519d8-4452-5ca8-a5d4-202c1c203857</t>
-  </si>
-  <si>
-    <t>06/30/2026 2:25:53 AM</t>
-  </si>
-  <si>
-    <t>667 - Medium</t>
-  </si>
-  <si>
-    <t>Jeremy Myers</t>
-  </si>
-  <si>
-    <t>Towing and Recovery</t>
-  </si>
-  <si>
-    <t>Drowsiness</t>
-  </si>
-  <si>
-    <t>Moderately Drowsy, Construction, Light Traffic, Night</t>
-  </si>
-  <si>
-    <t>US 69;US 96;US 287, Loeb, TX, 77657</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445176b-900a-5030-9c5c-f45149ae21dc</t>
-  </si>
-  <si>
-    <t>06/29/2026 6:45:25 PM</t>
-  </si>
-  <si>
-    <t>Severe Speeding</t>
-  </si>
-  <si>
-    <t>TX 124, Stowell, TX, 77661</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544515c6-0006-56ad-b973-19cc55a23aac</t>
-  </si>
-  <si>
-    <t>06/29/2026 11:23:34 AM</t>
-  </si>
-  <si>
-    <t>646 - Medium</t>
-  </si>
-  <si>
-    <t>US 69;US 96;US 287, Loeb, TX</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451431-78bb-5436-96d6-3c70d67fb881</t>
-  </si>
-  <si>
-    <t>06/29/2026 10:19:27 AM</t>
-  </si>
-  <si>
-    <t>Construction, Light Traffic</t>
-  </si>
-  <si>
-    <t>North Dorman Road, 4.8 mi NNE Bridge City, Orange County, TX, 77630</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544513f6-c68b-542c-9f35-22427550e8bd</t>
-  </si>
-  <si>
-    <t>06/29/2026 9:38:44 AM</t>
-  </si>
-  <si>
-    <t>Decker Drive, Baytown, TX, 77562</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544513d1-8033-5ca3-8ee4-f53cff58f76b</t>
-  </si>
-  <si>
-    <t>06/29/2026 8:54:50 AM</t>
-  </si>
-  <si>
-    <t>US 90, Nome, TX, 77629</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544513a9-4e6a-5777-b020-ae490b0ad885</t>
-  </si>
-  <si>
-    <t>06/28/2026 8:19:03 PM</t>
-  </si>
-  <si>
-    <t>683 - Heavy</t>
-  </si>
-  <si>
-    <t>Gary Worley</t>
-  </si>
-  <si>
-    <t>Eddie Bowden</t>
-  </si>
-  <si>
-    <t>US 90, China, TX, 77613</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544510f5-5d50-549b-869b-bddc80251d19</t>
-  </si>
-  <si>
-    <t>06/27/2026 5:25:06 PM</t>
-  </si>
-  <si>
-    <t>685 - Medium</t>
-  </si>
-  <si>
-    <t>Paul Kunze Jr</t>
-  </si>
-  <si>
-    <t>Inattentive Driving</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450b2f-be05-543b-acec-2c7c24ae13ce</t>
-  </si>
-  <si>
-    <t>06/26/2026 3:30:01 PM</t>
-  </si>
-  <si>
-    <t>US 69;US 96;US 287, Beaumont, TX, 77701</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544505a0-0548-52df-90bb-6baf18f84b57</t>
-  </si>
-  <si>
-    <t>06/26/2026 3:27:58 PM</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445059e-2881-5100-83b4-1f5b093312d4</t>
-  </si>
-  <si>
-    <t>06/25/2026 4:46:02 PM</t>
-  </si>
-  <si>
-    <t>Fannett Road, Beaumont, TX, 77705</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544500bf-4275-5ded-85e2-3ee8f4e6d92b</t>
-  </si>
-  <si>
-    <t>06/25/2026 12:16:55 PM</t>
-  </si>
-  <si>
-    <t>I 10, Winnie, TX</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ffc8-df6a-5dea-9370-f13b79e392c6</t>
-  </si>
-  <si>
-    <t>06/25/2026 11:15:11 AM</t>
-  </si>
-  <si>
-    <t>Harsh Brake</t>
-  </si>
-  <si>
-    <t>East Freeway Frontage Road, Houston, TX, 77020</t>
-  </si>
-  <si>
-    <t>0.67</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ff90-5d57-5dc0-a571-4d8c6dcde945</t>
-  </si>
-  <si>
-    <t>06/25/2026 10:09:43 AM</t>
-  </si>
-  <si>
-    <t>668 - Light</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ff54-6b07-5d1d-8dc0-8053502f47ef</t>
-  </si>
-  <si>
-    <t>06/24/2026 1:15:17 PM</t>
-  </si>
-  <si>
-    <t>Creole Nature Trail All-American Road, Calcasieu Parish, LA</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fad7-f51b-528d-8ce9-9658a4c0b9e5</t>
-  </si>
-  <si>
-    <t>06/23/2026 11:02:05 AM</t>
-  </si>
-  <si>
-    <t>I 10 Frontage Road, 24.6 mi SE Liberty, Chambers County, TX</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>0.55</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f537-a7f7-5b50-be7d-fcffb700b16d</t>
-  </si>
-  <si>
-    <t>06/22/2026 11:26:05 AM</t>
-  </si>
-  <si>
-    <t>692 - Heavy</t>
-  </si>
-  <si>
-    <t>William Foley</t>
-  </si>
-  <si>
-    <t>I 45, Madisonville, TX, 77864</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f027-4165-5f24-8d32-d9f65658b1d2</t>
-  </si>
-  <si>
-    <t>06/19/2026 4:15:44 PM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e1bd-5e83-597e-995e-9c0f9e74b244</t>
-  </si>
-  <si>
-    <t>06/18/2026 4:34:01 PM</t>
-  </si>
-  <si>
-    <t>Interstate 10 South Frontage Road, Beaumont, TX, 77702</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445dca7-bd7e-50f6-b2da-d0e7f3669228</t>
-  </si>
-  <si>
-    <t>06/18/2026 8:05:45 AM</t>
-  </si>
-  <si>
-    <t>Christopher Marcantel</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445dad6-6838-50e1-a08f-721a3f1f36df</t>
-  </si>
-  <si>
-    <t>06/17/2026 5:02:17 PM</t>
-  </si>
-  <si>
-    <t>Dwayne Manuel</t>
-  </si>
-  <si>
-    <t>H O Mills Highway, Port Arthur, TX</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d79b-44e0-5b5f-afa1-10741c645e86</t>
-  </si>
-  <si>
-    <t>06/17/2026 11:28:09 AM</t>
-  </si>
-  <si>
-    <t>College Street, Beaumont, TX, 77702</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d669-5d00-570d-892c-3b3bcb44e34d</t>
-  </si>
-  <si>
-    <t>06/15/2026 5:53:31 PM</t>
-  </si>
-  <si>
-    <t>5230 North Major Drive, Beaumont, TX, 77705</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cd7d-73a6-51c3-baf6-41a38469fe10</t>
-  </si>
-  <si>
-    <t>06/15/2026 1:23:54 PM</t>
-  </si>
-  <si>
-    <t>Wet Road, Light Traffic, Raining</t>
-  </si>
-  <si>
-    <t>State Highway 326, Sour Lake, TX, 77659</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cc86-9c64-5c62-a497-759c62f256a9</t>
-  </si>
-  <si>
-    <t>06/14/2026 11:39:04 AM</t>
-  </si>
-  <si>
-    <t>State Highway 124, Hamshire, TX, 77622</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c700-47f3-56b1-b136-8c61392947bb</t>
-  </si>
-  <si>
-    <t>06/14/2026 9:48:42 AM</t>
-  </si>
-  <si>
-    <t>644 - Medium</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c69b-3b3b-50b6-9299-c5f9408304d6</t>
-  </si>
-  <si>
-    <t>06/14/2026 12:03:26 AM</t>
-  </si>
-  <si>
-    <t>FM 365, 9.6 mi WSW Nederland, Jefferson County, TX</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c483-6560-5f24-a5a4-1196fcf0710d</t>
-  </si>
-  <si>
-    <t>06/13/2026 5:24:44 PM</t>
-  </si>
-  <si>
-    <t>Fannett Road, Beaumont, TX, 77701</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c316-622e-5089-9af0-e3644e669122</t>
-  </si>
-  <si>
-    <t>06/13/2026 4:18:06 PM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c2d9-604f-59f0-87e5-6a5c05c198bc</t>
-  </si>
-  <si>
-    <t>06/12/2026 9:27:53 AM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bc3b-756c-5d9e-9d81-2830d4d259b7</t>
-  </si>
-  <si>
-    <t>06/12/2026 7:39:02 AM</t>
-  </si>
-  <si>
-    <t>Dupont Drive, West Orange, TX, 77630</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bbd7-ce4d-5d05-b19f-5787bf9d3e6c</t>
-  </si>
-  <si>
-    <t>06/12/2026 7:17:24 AM</t>
-  </si>
-  <si>
-    <t>TX 73, Port Arthur, TX, 77640</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bbc3-fc20-5357-b19e-8917e5854b0b</t>
-  </si>
-  <si>
-    <t>06/12/2026 2:36:49 AM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bac3-1a90-5376-b4c0-879059363b9a</t>
-  </si>
-  <si>
-    <t>06/11/2026 10:09:35 PM</t>
-  </si>
-  <si>
-    <t>Moderately Drowsy, Light Traffic, Night</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b9ce-7522-5e34-bee1-b027d6f0c003</t>
-  </si>
-  <si>
-    <t>06/10/2026 4:50:31 PM</t>
-  </si>
-  <si>
-    <t>State Route 109, Starks, LA</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b383-f8ee-57b2-b3a2-576df0f3920d</t>
-  </si>
-  <si>
-    <t>06/10/2026 10:04:03 AM</t>
-  </si>
-  <si>
-    <t>5020 Fannett Road, Beaumont, TX, 77705</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b20f-d7d1-559a-a6fe-1633a24b3ed4</t>
-  </si>
-  <si>
-    <t>06/07/2026 2:14:46 PM</t>
-  </si>
-  <si>
-    <t>673 - Heavy</t>
-  </si>
-  <si>
-    <t>Kyle Ray</t>
-  </si>
-  <si>
-    <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
-  </si>
-  <si>
-    <t>I 10, Welsh, LA, 70581</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a382-4d73-5bb1-b5db-a39ca69f4b45</t>
-  </si>
-  <si>
-    <t>06/06/2026 8:18:21 AM</t>
-  </si>
-  <si>
-    <t>696 - Medium</t>
-  </si>
-  <si>
-    <t>Jammie Singleton</t>
-  </si>
-  <si>
-    <t>5225 Fannett Road, Beaumont, TX, 77705</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54459d15-a3c3-5e99-83f7-c781117f27a0</t>
-  </si>
-  <si>
-    <t>06/04/2026 2:15:03 PM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445940f-7e14-5c0f-aa68-07d221d9e214</t>
-  </si>
-  <si>
-    <t>06/03/2026 10:10:14 AM</t>
-  </si>
-  <si>
-    <t>632 - Heavy</t>
-  </si>
-  <si>
-    <t>Hufsmith Kohrville Road, 4.1 mi SSE Tomball, Harris County, TX, 77375</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458e08-fce4-50c2-a0a6-5143a8afefc2</t>
-  </si>
-  <si>
-    <t>05/29/2026 12:42:54 PM</t>
-  </si>
-  <si>
-    <t>I 10, Seguin, TX, 78638</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544574d4-f86a-51ab-8240-5abf48d2eb45</t>
-  </si>
-  <si>
-    <t>05/28/2026 4:24:20 PM</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457079-5686-54e8-8a42-3ea1c6f860e5</t>
-  </si>
-  <si>
-    <t>05/28/2026 1:48:42 PM</t>
-  </si>
-  <si>
-    <t>660 - Heavy</t>
-  </si>
-  <si>
-    <t>Billy Johnson</t>
-  </si>
-  <si>
-    <t>Active Drivers, HAAS Alert, Heavy Haul, Towing and Recovery</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456fea-dac1-5b56-beb5-7a334db4549a</t>
-  </si>
-  <si>
-    <t>05/28/2026 12:14:01 AM</t>
-  </si>
-  <si>
-    <t>Light Traffic, Night</t>
-  </si>
-  <si>
-    <t>East Parkway Street, Groves, TX, 77619</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456d00-fb6e-5da8-9ac8-5b4748eeabcb</t>
-  </si>
-  <si>
-    <t>05/23/2026 10:35:24 AM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445557a-13c8-58c7-91dd-c320f5c8cfc4</t>
-  </si>
-  <si>
-    <t>05/20/2026 10:02:55 PM</t>
-  </si>
-  <si>
-    <t>2706 Irving Avenue, Beaumont, TX, 77701</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445487c-7266-58c3-95b0-bb9b5182787c</t>
-  </si>
-  <si>
-    <t>05/20/2026 5:13:08 PM</t>
-  </si>
-  <si>
-    <t>I 10, 11.5 mi SW Beaumont, Jefferson County, TX</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454773-2263-5caf-9487-742896f74a00</t>
-  </si>
-  <si>
-    <t>05/19/2026 9:16:41 PM</t>
-  </si>
-  <si>
-    <t>3777 South 11th Street, Beaumont, TX, 77705</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445432b-c0f7-5407-ab0e-1be086171464</t>
-  </si>
-  <si>
-    <t>05/17/2026 12:48:35 PM</t>
-  </si>
-  <si>
-    <t>Passengers, Light Traffic</t>
-  </si>
-  <si>
-    <t>959 South 4th Street, Beaumont, TX, 77701</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445370d-dcb1-54d0-9764-b9756c5f4a28</t>
-  </si>
-  <si>
-    <t>05/16/2026 9:21:16 PM</t>
-  </si>
-  <si>
-    <t>Construction, Moderate Traffic, Night</t>
-  </si>
-  <si>
-    <t>I 10;US 90, Vidor, TX, 77662</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544533bc-e027-5557-b78e-89930845d14b</t>
-  </si>
-  <si>
-    <t>05/15/2026 11:50:46 AM</t>
-  </si>
-  <si>
-    <t>634 - Heavy</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54452c8c-35cb-5042-8396-5318d3f2fd79</t>
-  </si>
-  <si>
-    <t>05/08/2026 1:47:14 AM</t>
-  </si>
-  <si>
-    <t>7282 Garth Street, Cheek, TX, 77705</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54450657-2264-540c-a356-04b8b65790a7</t>
-  </si>
-  <si>
-    <t>05/06/2026 6:15:28 PM</t>
-  </si>
-  <si>
-    <t>Professional Drive, Port Arthur, TX, 77627</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ff93-2bc8-5ff4-87de-ffed8bce9121</t>
-  </si>
-  <si>
-    <t>05/06/2026 10:49:01 AM</t>
-  </si>
-  <si>
-    <t>Very Drowsy, Light Traffic</t>
-  </si>
-  <si>
-    <t>I 10, Eminence, TX, 77597</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445fdfa-6df8-54f7-bf4a-fab794afbe08</t>
-  </si>
-  <si>
-    <t>05/04/2026 2:55:02 PM</t>
-  </si>
-  <si>
-    <t>West Cardinal Drive, Beaumont, TX, 77710</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f48e-f389-50f8-87be-6562e2798e54</t>
-  </si>
-  <si>
-    <t>05/04/2026 11:04:48 AM</t>
-  </si>
-  <si>
-    <t>5269 Mustang-Chocolate Bayou Road, Liverpool, TX, 77511</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f3bc-29ec-5cbd-8282-0b221781d62e</t>
-  </si>
-  <si>
-    <t>05/03/2026 7:49:58 PM</t>
-  </si>
-  <si>
-    <t>362 Simmons Road, 1.9 mi N Vidor, Orange County, TX, 77662</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445f076-9dc7-55a8-867a-6a41fd2b62ac</t>
-  </si>
-  <si>
-    <t>05/02/2026 7:49:16 AM</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e8bc-6e70-5526-87d9-b05bb8910029</t>
-  </si>
-  <si>
-    <t>05/01/2026 6:35:06 PM</t>
-  </si>
-  <si>
-    <t>6425 Highway 347, Beaumont, TX, 77705</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e5e5-5b1b-523d-ab9c-a26f380cefef</t>
-  </si>
-  <si>
-    <t>05/01/2026 6:20:21 PM</t>
-  </si>
-  <si>
-    <t>FM 366, Groves, TX, 77651</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e5d7-d728-50d0-8a79-285ccb21062a</t>
-  </si>
-  <si>
-    <t>05/01/2026 9:24:31 AM</t>
-  </si>
-  <si>
-    <t>Wet Road, Construction, Light Traffic</t>
-  </si>
-  <si>
-    <t>State Highway 124, Cheek, TX, 77705</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e3ed-47e7-5957-ba13-b0bea3bf1b0d</t>
-  </si>
-  <si>
-    <t>04/30/2026 10:24:39 PM</t>
-  </si>
-  <si>
-    <t>Very Drowsy, Wet Road, Light Traffic, Night</t>
-  </si>
-  <si>
-    <t>7743 TX 105, Beaumont, TX, 77713</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e191-28b2-53d4-beb2-41c48d1673bc</t>
-  </si>
-  <si>
-    <t>04/28/2026 2:56:41 PM</t>
-  </si>
-  <si>
-    <t>South Major Drive, Beaumont, TX, 77705</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d5aa-4dd2-5073-adcd-a728d6e756c6</t>
-  </si>
-  <si>
-    <t>04/28/2026 10:39:38 AM</t>
-  </si>
-  <si>
-    <t>I 10, Vinton, LA, 70668</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d4be-f767-5552-9776-eea7c53edc2d</t>
-  </si>
-  <si>
-    <t>04/27/2026 6:19:35 PM</t>
-  </si>
-  <si>
-    <t>12.8 mi SW Beaumont, Jefferson County, TX</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445d13d-b4f6-5a82-bd3b-3d99bfc16a01</t>
-  </si>
-  <si>
-    <t>04/27/2026 8:54:16 AM</t>
-  </si>
-  <si>
-    <t>272 5th Street, Sour Lake, TX, 77659</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cf38-25f0-54ef-8b24-354e43be286d</t>
-  </si>
-  <si>
-    <t>04/26/2026 3:30:04 PM</t>
-  </si>
-  <si>
-    <t>State Highway 73, Winnie, TX, 77665</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cb7c-286d-5c30-82b5-a900c5aaf727</t>
-  </si>
-  <si>
-    <t>04/24/2026 8:06:44 PM</t>
-  </si>
-  <si>
-    <t>7838 Fannett Road, Beaumont, TX, 77705</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c22c-b8a8-56e7-91dd-e75155840d5d</t>
-  </si>
-  <si>
-    <t>04/24/2026 1:19:55 PM</t>
-  </si>
-  <si>
-    <t>4039 Washington Boulevard, Beaumont, TX, 77705</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445c0b8-4808-566d-a30c-abb96659aacf</t>
-  </si>
-  <si>
-    <t>04/23/2026 1:47:25 PM</t>
-  </si>
-  <si>
-    <t>662 - Heavy</t>
-  </si>
-  <si>
-    <t>Drew Template</t>
-  </si>
-  <si>
-    <t>8401 Washington Boulevard, Beaumont, TX, 77707</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>0.61</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445bbab-17ef-5346-9a45-c49e8341e9be</t>
-  </si>
-  <si>
-    <t>04/22/2026 6:29:50 AM</t>
-  </si>
-  <si>
-    <t>Fred Hartman Bridge, Baytown, TX</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b4f4-1f22-5ef3-9175-aee791790b8b</t>
-  </si>
-  <si>
-    <t>04/21/2026 5:20:10 PM</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b221-27f0-520a-b7e1-6dca1413a74b</t>
-  </si>
-  <si>
-    <t>04/21/2026 2:19:20 PM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445b17b-997e-5ccd-9142-896d210e168f</t>
-  </si>
-  <si>
-    <t>04/20/2026 10:49:13 AM</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ab94-df4e-5e43-8f70-06189ab78268</t>
   </si>
   <si>
-    <t>04/18/2026 8:25:57 AM</t>
+    <t>04/18/2026 7:25:57 AM</t>
   </si>
   <si>
     <t>I 10, Beaumont, TX, 77702</t>
@@ -1127,7 +1310,7 @@
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a0c4-fdcf-57c3-b241-7891a9a8e817</t>
   </si>
   <si>
-    <t>04/16/2026 11:41:19 AM</t>
+    <t>04/16/2026 10:41:19 AM</t>
   </si>
   <si>
     <t>Eastex Freeway Frontage Road, Beaumont, TX, 77702</t>
@@ -1136,7 +1319,7 @@
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445972b-2023-520b-9311-2aa79edade29</t>
   </si>
   <si>
-    <t>04/15/2026 11:09:32 AM</t>
+    <t>04/15/2026 10:09:32 AM</t>
   </si>
   <si>
     <t>I 10;US 69;US 96;US 287, Beaumont, TX, 77702</t>
@@ -1145,13 +1328,13 @@
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544591e7-ac88-54d6-98a8-4bfe3fad16a5</t>
   </si>
   <si>
-    <t>04/14/2026 11:07:04 PM</t>
+    <t>04/14/2026 10:07:04 PM</t>
   </si>
   <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458f52-3b0b-50cb-bd6a-0400939c68f0</t>
   </si>
   <si>
-    <t>04/14/2026 5:40:17 PM</t>
+    <t>04/14/2026 4:40:17 PM</t>
   </si>
   <si>
     <t>693 - Heavy</t>
@@ -1166,7 +1349,7 @@
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458e27-0eb3-5dba-85fd-a0dce64314bb</t>
   </si>
   <si>
-    <t>04/14/2026 5:19:07 PM</t>
+    <t>04/14/2026 4:19:07 PM</t>
   </si>
   <si>
     <t>1193 US 90, Broussard, LA, 70518</t>
@@ -1178,7 +1361,7 @@
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458e13-abfc-5546-ba17-feaf5efdc4dd</t>
   </si>
   <si>
-    <t>04/14/2026 11:46:08 AM</t>
+    <t>04/14/2026 10:46:08 AM</t>
   </si>
   <si>
     <t>Eastex Freeway Frontage Road, Beaumont, TX, 77703</t>
@@ -1190,7 +1373,7 @@
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458ce2-d409-5c3c-aecb-b998a858ebbd</t>
   </si>
   <si>
-    <t>04/13/2026 1:57:32 PM</t>
+    <t>04/13/2026 12:57:32 PM</t>
   </si>
   <si>
     <t>21882 US 90, Nome, TX, 77713</t>
@@ -1202,79 +1385,13 @@
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458834-c18f-5646-beeb-dec2a1a762b7</t>
   </si>
   <si>
-    <t>04/13/2026 10:43:50 AM</t>
+    <t>04/13/2026 9:43:50 AM</t>
   </si>
   <si>
     <t>East Freeway, Houston, TX, 77020</t>
   </si>
   <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458783-6b27-5c61-8273-549c16680488</t>
-  </si>
-  <si>
-    <t>04/11/2026 7:55:26 PM</t>
-  </si>
-  <si>
-    <t>FM 105, 7.6 mi ESE Silsbee, Jasper County, TX, 77615</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457f2f-b767-58bc-a524-ffc617afdb32</t>
-  </si>
-  <si>
-    <t>04/10/2026 6:09:04 AM</t>
-  </si>
-  <si>
-    <t>Jason Leleaux</t>
-  </si>
-  <si>
-    <t>TX 35, Alvin, TX, 77511</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457714-cb5e-5acc-94bb-e56eaeea5d26</t>
-  </si>
-  <si>
-    <t>04/10/2026 5:18:57 AM</t>
-  </si>
-  <si>
-    <t>East Freeway, Baytown, TX, 77523</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544576e6-e8fe-5378-987e-f6a0db6cddf7</t>
-  </si>
-  <si>
-    <t>04/09/2026 2:37:19 PM</t>
-  </si>
-  <si>
-    <t>7360 Garth Street, Cheek, TX, 77705</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544573bf-bf1e-52f1-a30e-4d7de5d4ff54</t>
-  </si>
-  <si>
-    <t>04/07/2026 10:15:48 PM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456b16-c772-5c6b-bb09-e92039e34f7c</t>
-  </si>
-  <si>
-    <t>04/06/2026 5:30:46 PM</t>
-  </si>
-  <si>
-    <t>East Freeway, 5.0 mi N Baytown, Harris County, TX, 77521</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544564eb-79d0-5e02-bdcb-46a38e6bc3b1</t>
-  </si>
-  <si>
-    <t>04/06/2026 9:54:40 AM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456349-e5b4-55ac-a43b-944299eef0c4</t>
   </si>
 </sst>
 </file>
@@ -1651,7 +1768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O100"/>
+  <dimension ref="A1:O112"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -1756,131 +1873,131 @@
         <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
         <v>31</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
         <v>32</v>
       </c>
-      <c r="H3" t="s">
+      <c r="K3" t="s">
         <v>33</v>
       </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" t="s">
         <v>34</v>
-      </c>
-      <c r="K3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" t="s">
-        <v>26</v>
-      </c>
-      <c r="N3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
         <v>37</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
         <v>38</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>39</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>41</v>
-      </c>
-      <c r="G4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" t="s">
-        <v>33</v>
       </c>
       <c r="I4" t="s">
         <v>23</v>
       </c>
       <c r="J4" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" t="s">
         <v>43</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" t="s">
         <v>44</v>
-      </c>
-      <c r="L4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
         <v>46</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>47</v>
-      </c>
-      <c r="C5" t="s">
-        <v>48</v>
       </c>
       <c r="D5" t="s">
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" t="s">
         <v>31</v>
       </c>
-      <c r="G5" t="s">
-        <v>42</v>
-      </c>
       <c r="H5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I5" t="s">
         <v>23</v>
       </c>
       <c r="J5" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" t="s">
         <v>50</v>
       </c>
-      <c r="K5" t="s">
+      <c r="M5" t="s">
         <v>51</v>
-      </c>
-      <c r="L5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" t="s">
-        <v>26</v>
       </c>
       <c r="N5" t="s">
         <v>26</v>
@@ -1894,10 +2011,10 @@
         <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
@@ -1906,163 +2023,163 @@
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H6" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I6" t="s">
         <v>23</v>
       </c>
       <c r="J6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M6" t="s">
         <v>55</v>
       </c>
-      <c r="K6" t="s">
+      <c r="N6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O6" t="s">
         <v>56</v>
-      </c>
-      <c r="L6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O6" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H7" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I7" t="s">
         <v>23</v>
       </c>
       <c r="J7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K7" t="s">
+        <v>60</v>
+      </c>
+      <c r="L7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" t="s">
+        <v>61</v>
+      </c>
+      <c r="O7" t="s">
         <v>62</v>
-      </c>
-      <c r="K7" t="s">
-        <v>51</v>
-      </c>
-      <c r="L7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="G8" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="H8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" t="s">
         <v>33</v>
       </c>
-      <c r="I8" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" t="s">
-        <v>67</v>
-      </c>
-      <c r="K8" t="s">
-        <v>68</v>
-      </c>
       <c r="L8" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="M8" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="N8" t="s">
         <v>26</v>
       </c>
       <c r="O8" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
         <v>31</v>
       </c>
-      <c r="G9" t="s">
-        <v>26</v>
-      </c>
       <c r="H9" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I9" t="s">
         <v>23</v>
       </c>
       <c r="J9" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="K9" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="L9" t="s">
         <v>26</v>
@@ -2074,183 +2191,183 @@
         <v>26</v>
       </c>
       <c r="O9" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="G10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" t="s">
+        <v>49</v>
+      </c>
+      <c r="K10" t="s">
+        <v>76</v>
+      </c>
+      <c r="L10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N10" t="s">
+        <v>26</v>
+      </c>
+      <c r="O10" t="s">
         <v>77</v>
-      </c>
-      <c r="H10" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" t="s">
-        <v>26</v>
-      </c>
-      <c r="J10" t="s">
-        <v>78</v>
-      </c>
-      <c r="K10" t="s">
-        <v>79</v>
-      </c>
-      <c r="L10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O10" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" t="s">
         <v>81</v>
       </c>
-      <c r="B11" t="s">
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" t="s">
         <v>82</v>
       </c>
-      <c r="C11" t="s">
+      <c r="K11" t="s">
         <v>83</v>
       </c>
-      <c r="D11" t="s">
+      <c r="L11" t="s">
+        <v>26</v>
+      </c>
+      <c r="M11" t="s">
+        <v>26</v>
+      </c>
+      <c r="N11" t="s">
+        <v>26</v>
+      </c>
+      <c r="O11" t="s">
         <v>84</v>
-      </c>
-      <c r="E11" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" t="s">
-        <v>85</v>
-      </c>
-      <c r="G11" t="s">
-        <v>86</v>
-      </c>
-      <c r="H11" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J11" t="s">
-        <v>87</v>
-      </c>
-      <c r="K11" t="s">
-        <v>88</v>
-      </c>
-      <c r="L11" t="s">
-        <v>26</v>
-      </c>
-      <c r="M11" t="s">
-        <v>26</v>
-      </c>
-      <c r="N11" t="s">
-        <v>26</v>
-      </c>
-      <c r="O11" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="G12" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H12" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I12" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J12" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="K12" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="L12" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="M12" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="N12" t="s">
         <v>26</v>
       </c>
       <c r="O12" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G13" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="H13" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I13" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J13" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="K13" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="L13" t="s">
         <v>26</v>
@@ -2262,18 +2379,18 @@
         <v>26</v>
       </c>
       <c r="O13" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
@@ -2282,22 +2399,22 @@
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="H14" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I14" t="s">
         <v>23</v>
       </c>
       <c r="J14" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="K14" t="s">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="L14" t="s">
         <v>26</v>
@@ -2309,42 +2426,42 @@
         <v>26</v>
       </c>
       <c r="O14" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="H15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I15" t="s">
         <v>23</v>
       </c>
       <c r="J15" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="K15" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="L15" t="s">
         <v>26</v>
@@ -2356,42 +2473,42 @@
         <v>26</v>
       </c>
       <c r="O15" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="E16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" t="s">
+        <v>41</v>
+      </c>
+      <c r="I16" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" t="s">
         <v>49</v>
       </c>
-      <c r="F16" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16" t="s">
-        <v>66</v>
-      </c>
-      <c r="H16" t="s">
-        <v>33</v>
-      </c>
-      <c r="I16" t="s">
-        <v>26</v>
-      </c>
-      <c r="J16" t="s">
-        <v>112</v>
-      </c>
       <c r="K16" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="L16" t="s">
         <v>26</v>
@@ -2403,42 +2520,42 @@
         <v>26</v>
       </c>
       <c r="O16" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B17" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E17" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="H17" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I17" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="J17" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="K17" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="L17" t="s">
         <v>26</v>
@@ -2450,89 +2567,89 @@
         <v>26</v>
       </c>
       <c r="O17" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="B18" t="s">
-        <v>122</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
       </c>
       <c r="E18" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>124</v>
+        <v>30</v>
       </c>
       <c r="G18" t="s">
-        <v>103</v>
+        <v>31</v>
       </c>
       <c r="H18" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I18" t="s">
         <v>23</v>
       </c>
       <c r="J18" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="K18" t="s">
-        <v>125</v>
+        <v>33</v>
       </c>
       <c r="L18" t="s">
         <v>26</v>
       </c>
       <c r="M18" t="s">
-        <v>126</v>
+        <v>26</v>
       </c>
       <c r="N18" t="s">
         <v>26</v>
       </c>
       <c r="O18" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="B19" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="E19" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G19" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H19" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="I19" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J19" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="K19" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="L19" t="s">
         <v>26</v>
@@ -2544,42 +2661,42 @@
         <v>26</v>
       </c>
       <c r="O19" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B20" t="s">
-        <v>122</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
       </c>
       <c r="E20" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" t="s">
         <v>31</v>
       </c>
-      <c r="G20" t="s">
-        <v>103</v>
-      </c>
       <c r="H20" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I20" t="s">
         <v>23</v>
       </c>
       <c r="J20" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="K20" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="L20" t="s">
         <v>26</v>
@@ -2591,42 +2708,42 @@
         <v>26</v>
       </c>
       <c r="O20" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
       </c>
       <c r="F21" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" t="s">
         <v>31</v>
       </c>
-      <c r="G21" t="s">
-        <v>66</v>
-      </c>
       <c r="H21" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I21" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J21" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="K21" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L21" t="s">
         <v>26</v>
@@ -2638,42 +2755,42 @@
         <v>26</v>
       </c>
       <c r="O21" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
       </c>
       <c r="E22" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F22" t="s">
-        <v>20</v>
+        <v>129</v>
       </c>
       <c r="G22" t="s">
         <v>21</v>
       </c>
       <c r="H22" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I22" t="s">
         <v>23</v>
       </c>
       <c r="J22" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="K22" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="L22" t="s">
         <v>26</v>
@@ -2685,42 +2802,42 @@
         <v>26</v>
       </c>
       <c r="O22" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="C23" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F23" t="s">
-        <v>144</v>
+        <v>30</v>
       </c>
       <c r="G23" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="H23" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I23" t="s">
         <v>23</v>
       </c>
       <c r="J23" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="K23" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="L23" t="s">
         <v>26</v>
@@ -2729,45 +2846,45 @@
         <v>26</v>
       </c>
       <c r="N23" t="s">
-        <v>146</v>
+        <v>26</v>
       </c>
       <c r="O23" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="B24" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C24" t="s">
-        <v>26</v>
+        <v>139</v>
       </c>
       <c r="D24" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E24" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F24" t="s">
+        <v>30</v>
+      </c>
+      <c r="G24" t="s">
         <v>31</v>
       </c>
-      <c r="G24" t="s">
-        <v>32</v>
-      </c>
       <c r="H24" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="I24" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J24" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K24" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="L24" t="s">
         <v>26</v>
@@ -2779,42 +2896,42 @@
         <v>26</v>
       </c>
       <c r="O24" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>127</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>128</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
       </c>
       <c r="E25" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F25" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>42</v>
+        <v>144</v>
       </c>
       <c r="H25" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I25" t="s">
         <v>23</v>
       </c>
       <c r="J25" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K25" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="L25" t="s">
         <v>26</v>
@@ -2826,42 +2943,42 @@
         <v>26</v>
       </c>
       <c r="O25" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C26" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="E26" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F26" t="s">
-        <v>144</v>
+        <v>74</v>
       </c>
       <c r="G26" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="H26" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I26" t="s">
         <v>23</v>
       </c>
       <c r="J26" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="K26" t="s">
-        <v>157</v>
+        <v>76</v>
       </c>
       <c r="L26" t="s">
         <v>26</v>
@@ -2870,45 +2987,45 @@
         <v>26</v>
       </c>
       <c r="N26" t="s">
-        <v>158</v>
+        <v>26</v>
       </c>
       <c r="O26" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B27" t="s">
-        <v>161</v>
+        <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="D27" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
       </c>
       <c r="F27" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" t="s">
+        <v>75</v>
+      </c>
+      <c r="H27" t="s">
         <v>41</v>
       </c>
-      <c r="G27" t="s">
-        <v>42</v>
-      </c>
-      <c r="H27" t="s">
-        <v>22</v>
-      </c>
       <c r="I27" t="s">
-        <v>23</v>
+        <v>153</v>
       </c>
       <c r="J27" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="K27" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="L27" t="s">
         <v>26</v>
@@ -2920,42 +3037,42 @@
         <v>26</v>
       </c>
       <c r="O27" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" t="s">
         <v>47</v>
-      </c>
-      <c r="C28" t="s">
-        <v>123</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
       </c>
       <c r="E28" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>66</v>
+        <v>158</v>
       </c>
       <c r="H28" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I28" t="s">
         <v>23</v>
       </c>
       <c r="J28" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="K28" t="s">
-        <v>74</v>
+        <v>155</v>
       </c>
       <c r="L28" t="s">
         <v>26</v>
@@ -2967,42 +3084,42 @@
         <v>26</v>
       </c>
       <c r="O28" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="C29" t="s">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
       </c>
       <c r="E29" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F29" t="s">
-        <v>54</v>
+        <v>129</v>
       </c>
       <c r="G29" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H29" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I29" t="s">
         <v>23</v>
       </c>
       <c r="J29" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="K29" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="L29" t="s">
         <v>26</v>
@@ -3014,89 +3131,89 @@
         <v>26</v>
       </c>
       <c r="O29" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C30" t="s">
-        <v>173</v>
+        <v>108</v>
       </c>
       <c r="D30" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="E30" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F30" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="G30" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H30" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I30" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J30" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="K30" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="L30" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="M30" t="s">
-        <v>174</v>
+        <v>26</v>
       </c>
       <c r="N30" t="s">
         <v>26</v>
       </c>
       <c r="O30" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B31" t="s">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="C31" t="s">
-        <v>177</v>
+        <v>80</v>
       </c>
       <c r="D31" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>31</v>
+        <v>170</v>
       </c>
       <c r="G31" t="s">
-        <v>66</v>
+        <v>171</v>
       </c>
       <c r="H31" t="s">
         <v>22</v>
       </c>
       <c r="I31" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J31" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="K31" t="s">
-        <v>68</v>
+        <v>173</v>
       </c>
       <c r="L31" t="s">
         <v>26</v>
@@ -3108,89 +3225,89 @@
         <v>26</v>
       </c>
       <c r="O31" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B32" t="s">
-        <v>122</v>
+        <v>46</v>
       </c>
       <c r="C32" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="D32" t="s">
         <v>18</v>
       </c>
       <c r="E32" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F32" t="s">
-        <v>124</v>
+        <v>48</v>
       </c>
       <c r="G32" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="H32" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I32" t="s">
         <v>23</v>
       </c>
       <c r="J32" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="K32" t="s">
-        <v>182</v>
+        <v>33</v>
       </c>
       <c r="L32" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="M32" t="s">
-        <v>126</v>
+        <v>55</v>
       </c>
       <c r="N32" t="s">
         <v>26</v>
       </c>
       <c r="O32" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B33" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="C33" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
       </c>
       <c r="E33" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F33" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="G33" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="H33" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I33" t="s">
         <v>23</v>
       </c>
       <c r="J33" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="K33" t="s">
-        <v>35</v>
+        <v>180</v>
       </c>
       <c r="L33" t="s">
         <v>26</v>
@@ -3202,42 +3319,42 @@
         <v>26</v>
       </c>
       <c r="O33" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B34" t="s">
-        <v>29</v>
+        <v>127</v>
       </c>
       <c r="C34" t="s">
-        <v>30</v>
+        <v>128</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
       </c>
       <c r="E34" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F34" t="s">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="G34" t="s">
-        <v>188</v>
+        <v>58</v>
       </c>
       <c r="H34" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I34" t="s">
         <v>23</v>
       </c>
       <c r="J34" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="K34" t="s">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="L34" t="s">
         <v>26</v>
@@ -3249,30 +3366,30 @@
         <v>26</v>
       </c>
       <c r="O34" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B35" t="s">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="C35" t="s">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E35" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F35" t="s">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="G35" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="H35" t="s">
         <v>22</v>
@@ -3281,10 +3398,10 @@
         <v>26</v>
       </c>
       <c r="J35" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="K35" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="L35" t="s">
         <v>26</v>
@@ -3296,42 +3413,42 @@
         <v>26</v>
       </c>
       <c r="O35" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="B36" t="s">
-        <v>197</v>
+        <v>102</v>
       </c>
       <c r="C36" t="s">
-        <v>123</v>
+        <v>190</v>
       </c>
       <c r="D36" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="E36" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F36" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G36" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="H36" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I36" t="s">
-        <v>23</v>
+        <v>191</v>
       </c>
       <c r="J36" t="s">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="K36" t="s">
-        <v>68</v>
+        <v>193</v>
       </c>
       <c r="L36" t="s">
         <v>26</v>
@@ -3343,142 +3460,142 @@
         <v>26</v>
       </c>
       <c r="O36" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B37" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
       </c>
       <c r="E37" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F37" t="s">
-        <v>91</v>
+        <v>196</v>
       </c>
       <c r="G37" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="H37" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I37" t="s">
         <v>23</v>
       </c>
       <c r="J37" t="s">
-        <v>200</v>
+        <v>166</v>
       </c>
       <c r="K37" t="s">
-        <v>93</v>
+        <v>197</v>
       </c>
       <c r="L37" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="M37" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="N37" t="s">
         <v>26</v>
       </c>
       <c r="O37" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>200</v>
+      </c>
+      <c r="B38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38" t="s">
+        <v>30</v>
+      </c>
+      <c r="G38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H38" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" t="s">
+        <v>23</v>
+      </c>
+      <c r="J38" t="s">
+        <v>201</v>
+      </c>
+      <c r="K38" t="s">
         <v>202</v>
       </c>
-      <c r="B38" t="s">
-        <v>122</v>
-      </c>
-      <c r="C38" t="s">
-        <v>173</v>
-      </c>
-      <c r="D38" t="s">
-        <v>84</v>
-      </c>
-      <c r="E38" t="s">
-        <v>49</v>
-      </c>
-      <c r="F38" t="s">
-        <v>31</v>
-      </c>
-      <c r="G38" t="s">
-        <v>66</v>
-      </c>
-      <c r="H38" t="s">
-        <v>22</v>
-      </c>
-      <c r="I38" t="s">
-        <v>26</v>
-      </c>
-      <c r="J38" t="s">
+      <c r="L38" t="s">
+        <v>26</v>
+      </c>
+      <c r="M38" t="s">
+        <v>26</v>
+      </c>
+      <c r="N38" t="s">
+        <v>26</v>
+      </c>
+      <c r="O38" t="s">
         <v>203</v>
-      </c>
-      <c r="K38" t="s">
-        <v>170</v>
-      </c>
-      <c r="L38" t="s">
-        <v>26</v>
-      </c>
-      <c r="M38" t="s">
-        <v>26</v>
-      </c>
-      <c r="N38" t="s">
-        <v>26</v>
-      </c>
-      <c r="O38" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>204</v>
+      </c>
+      <c r="B39" t="s">
+        <v>72</v>
+      </c>
+      <c r="C39" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" t="s">
+        <v>20</v>
+      </c>
+      <c r="G39" t="s">
+        <v>58</v>
+      </c>
+      <c r="H39" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" t="s">
+        <v>23</v>
+      </c>
+      <c r="J39" t="s">
+        <v>166</v>
+      </c>
+      <c r="K39" t="s">
         <v>205</v>
       </c>
-      <c r="B39" t="s">
-        <v>122</v>
-      </c>
-      <c r="C39" t="s">
-        <v>173</v>
-      </c>
-      <c r="D39" t="s">
-        <v>84</v>
-      </c>
-      <c r="E39" t="s">
-        <v>49</v>
-      </c>
-      <c r="F39" t="s">
-        <v>124</v>
-      </c>
-      <c r="G39" t="s">
-        <v>42</v>
-      </c>
-      <c r="H39" t="s">
-        <v>22</v>
-      </c>
-      <c r="I39" t="s">
-        <v>26</v>
-      </c>
-      <c r="J39" t="s">
-        <v>50</v>
-      </c>
-      <c r="K39" t="s">
-        <v>137</v>
-      </c>
       <c r="L39" t="s">
         <v>26</v>
       </c>
       <c r="M39" t="s">
-        <v>126</v>
+        <v>26</v>
       </c>
       <c r="N39" t="s">
         <v>26</v>
@@ -3492,34 +3609,34 @@
         <v>207</v>
       </c>
       <c r="B40" t="s">
-        <v>197</v>
+        <v>138</v>
       </c>
       <c r="C40" t="s">
-        <v>123</v>
+        <v>26</v>
       </c>
       <c r="D40" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E40" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F40" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G40" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="H40" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I40" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J40" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="K40" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="L40" t="s">
         <v>26</v>
@@ -3531,42 +3648,42 @@
         <v>26</v>
       </c>
       <c r="O40" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="C41" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
       </c>
       <c r="E41" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="G41" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H41" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I41" t="s">
         <v>23</v>
       </c>
       <c r="J41" t="s">
-        <v>210</v>
+        <v>49</v>
       </c>
       <c r="K41" t="s">
-        <v>35</v>
+        <v>211</v>
       </c>
       <c r="L41" t="s">
         <v>26</v>
@@ -3578,136 +3695,136 @@
         <v>26</v>
       </c>
       <c r="O41" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B42" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="C42" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
       </c>
       <c r="E42" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>91</v>
+        <v>214</v>
       </c>
       <c r="G42" t="s">
         <v>21</v>
       </c>
       <c r="H42" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I42" t="s">
         <v>23</v>
       </c>
       <c r="J42" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K42" t="s">
-        <v>93</v>
+        <v>54</v>
       </c>
       <c r="L42" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="M42" t="s">
-        <v>174</v>
+        <v>26</v>
       </c>
       <c r="N42" t="s">
-        <v>26</v>
+        <v>216</v>
       </c>
       <c r="O42" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B43" t="s">
+        <v>219</v>
+      </c>
+      <c r="C43" t="s">
+        <v>26</v>
+      </c>
+      <c r="D43" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43" t="s">
+        <v>20</v>
+      </c>
+      <c r="G43" t="s">
+        <v>144</v>
+      </c>
+      <c r="H43" t="s">
+        <v>22</v>
+      </c>
+      <c r="I43" t="s">
+        <v>26</v>
+      </c>
+      <c r="J43" t="s">
+        <v>109</v>
+      </c>
+      <c r="K43" t="s">
         <v>197</v>
       </c>
-      <c r="C43" t="s">
-        <v>26</v>
-      </c>
-      <c r="D43" t="s">
-        <v>26</v>
-      </c>
-      <c r="E43" t="s">
-        <v>49</v>
-      </c>
-      <c r="F43" t="s">
-        <v>91</v>
-      </c>
-      <c r="G43" t="s">
-        <v>21</v>
-      </c>
-      <c r="H43" t="s">
-        <v>33</v>
-      </c>
-      <c r="I43" t="s">
-        <v>26</v>
-      </c>
-      <c r="J43" t="s">
-        <v>73</v>
-      </c>
-      <c r="K43" t="s">
-        <v>93</v>
-      </c>
       <c r="L43" t="s">
-        <v>94</v>
+        <v>26</v>
       </c>
       <c r="M43" t="s">
-        <v>174</v>
+        <v>26</v>
       </c>
       <c r="N43" t="s">
         <v>26</v>
       </c>
       <c r="O43" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B44" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="C44" t="s">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
       </c>
       <c r="E44" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F44" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="G44" t="s">
-        <v>218</v>
+        <v>75</v>
       </c>
       <c r="H44" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I44" t="s">
         <v>23</v>
       </c>
       <c r="J44" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="K44" t="s">
-        <v>182</v>
+        <v>222</v>
       </c>
       <c r="L44" t="s">
         <v>26</v>
@@ -3719,89 +3836,89 @@
         <v>26</v>
       </c>
       <c r="O44" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B45" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="C45" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
       </c>
       <c r="E45" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>91</v>
+        <v>214</v>
       </c>
       <c r="G45" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H45" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I45" t="s">
         <v>23</v>
       </c>
       <c r="J45" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="K45" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="L45" t="s">
-        <v>223</v>
+        <v>26</v>
       </c>
       <c r="M45" t="s">
-        <v>174</v>
+        <v>26</v>
       </c>
       <c r="N45" t="s">
-        <v>26</v>
+        <v>227</v>
       </c>
       <c r="O45" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>230</v>
       </c>
       <c r="C46" t="s">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="D46" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="E46" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F46" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="G46" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="H46" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="I46" t="s">
         <v>23</v>
       </c>
       <c r="J46" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="K46" t="s">
-        <v>227</v>
+        <v>83</v>
       </c>
       <c r="L46" t="s">
         <v>26</v>
@@ -3813,42 +3930,42 @@
         <v>26</v>
       </c>
       <c r="O46" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B47" t="s">
-        <v>230</v>
+        <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="E47" t="s">
         <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G47" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="H47" t="s">
         <v>22</v>
       </c>
       <c r="I47" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="J47" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="K47" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="L47" t="s">
         <v>26</v>
@@ -3860,189 +3977,189 @@
         <v>26</v>
       </c>
       <c r="O47" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B48" t="s">
-        <v>236</v>
+        <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>237</v>
+        <v>47</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
       </c>
       <c r="E48" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F48" t="s">
-        <v>31</v>
+        <v>237</v>
       </c>
       <c r="G48" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="H48" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I48" t="s">
         <v>23</v>
       </c>
       <c r="J48" t="s">
+        <v>59</v>
+      </c>
+      <c r="K48" t="s">
+        <v>25</v>
+      </c>
+      <c r="L48" t="s">
+        <v>26</v>
+      </c>
+      <c r="M48" t="s">
+        <v>26</v>
+      </c>
+      <c r="N48" t="s">
+        <v>26</v>
+      </c>
+      <c r="O48" t="s">
         <v>238</v>
-      </c>
-      <c r="K48" t="s">
-        <v>239</v>
-      </c>
-      <c r="L48" t="s">
-        <v>26</v>
-      </c>
-      <c r="M48" t="s">
-        <v>26</v>
-      </c>
-      <c r="N48" t="s">
-        <v>26</v>
-      </c>
-      <c r="O48" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>239</v>
+      </c>
+      <c r="B49" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" t="s">
+        <v>240</v>
+      </c>
+      <c r="D49" t="s">
+        <v>81</v>
+      </c>
+      <c r="E49" t="s">
+        <v>19</v>
+      </c>
+      <c r="F49" t="s">
+        <v>48</v>
+      </c>
+      <c r="G49" t="s">
+        <v>31</v>
+      </c>
+      <c r="H49" t="s">
+        <v>22</v>
+      </c>
+      <c r="I49" t="s">
+        <v>26</v>
+      </c>
+      <c r="J49" t="s">
+        <v>49</v>
+      </c>
+      <c r="K49" t="s">
+        <v>33</v>
+      </c>
+      <c r="L49" t="s">
+        <v>54</v>
+      </c>
+      <c r="M49" t="s">
+        <v>51</v>
+      </c>
+      <c r="N49" t="s">
+        <v>26</v>
+      </c>
+      <c r="O49" t="s">
         <v>241</v>
-      </c>
-      <c r="B49" t="s">
-        <v>197</v>
-      </c>
-      <c r="C49" t="s">
-        <v>26</v>
-      </c>
-      <c r="D49" t="s">
-        <v>26</v>
-      </c>
-      <c r="E49" t="s">
-        <v>49</v>
-      </c>
-      <c r="F49" t="s">
-        <v>31</v>
-      </c>
-      <c r="G49" t="s">
-        <v>32</v>
-      </c>
-      <c r="H49" t="s">
-        <v>33</v>
-      </c>
-      <c r="I49" t="s">
-        <v>26</v>
-      </c>
-      <c r="J49" t="s">
-        <v>203</v>
-      </c>
-      <c r="K49" t="s">
-        <v>68</v>
-      </c>
-      <c r="L49" t="s">
-        <v>26</v>
-      </c>
-      <c r="M49" t="s">
-        <v>26</v>
-      </c>
-      <c r="N49" t="s">
-        <v>26</v>
-      </c>
-      <c r="O49" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>242</v>
+      </c>
+      <c r="B50" t="s">
+        <v>102</v>
+      </c>
+      <c r="C50" t="s">
         <v>243</v>
       </c>
-      <c r="B50" t="s">
+      <c r="D50" t="s">
+        <v>68</v>
+      </c>
+      <c r="E50" t="s">
+        <v>38</v>
+      </c>
+      <c r="F50" t="s">
+        <v>20</v>
+      </c>
+      <c r="G50" t="s">
+        <v>21</v>
+      </c>
+      <c r="H50" t="s">
+        <v>41</v>
+      </c>
+      <c r="I50" t="s">
+        <v>23</v>
+      </c>
+      <c r="J50" t="s">
         <v>244</v>
       </c>
-      <c r="C50" t="s">
-        <v>116</v>
-      </c>
-      <c r="D50" t="s">
-        <v>40</v>
-      </c>
-      <c r="E50" t="s">
-        <v>19</v>
-      </c>
-      <c r="F50" t="s">
-        <v>65</v>
-      </c>
-      <c r="G50" t="s">
-        <v>66</v>
-      </c>
-      <c r="H50" t="s">
-        <v>33</v>
-      </c>
-      <c r="I50" t="s">
-        <v>117</v>
-      </c>
-      <c r="J50" t="s">
+      <c r="K50" t="s">
+        <v>163</v>
+      </c>
+      <c r="L50" t="s">
+        <v>26</v>
+      </c>
+      <c r="M50" t="s">
+        <v>26</v>
+      </c>
+      <c r="N50" t="s">
+        <v>26</v>
+      </c>
+      <c r="O50" t="s">
         <v>245</v>
-      </c>
-      <c r="K50" t="s">
-        <v>227</v>
-      </c>
-      <c r="L50" t="s">
-        <v>26</v>
-      </c>
-      <c r="M50" t="s">
-        <v>26</v>
-      </c>
-      <c r="N50" t="s">
-        <v>26</v>
-      </c>
-      <c r="O50" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B51" t="s">
-        <v>161</v>
+        <v>72</v>
       </c>
       <c r="C51" t="s">
-        <v>231</v>
+        <v>47</v>
       </c>
       <c r="D51" t="s">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="E51" t="s">
         <v>19</v>
       </c>
       <c r="F51" t="s">
-        <v>124</v>
+        <v>196</v>
       </c>
       <c r="G51" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="H51" t="s">
         <v>22</v>
       </c>
       <c r="I51" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="J51" t="s">
+        <v>247</v>
+      </c>
+      <c r="K51" t="s">
         <v>248</v>
       </c>
-      <c r="K51" t="s">
-        <v>133</v>
-      </c>
       <c r="L51" t="s">
         <v>26</v>
       </c>
       <c r="M51" t="s">
-        <v>26</v>
+        <v>198</v>
       </c>
       <c r="N51" t="s">
         <v>26</v>
@@ -4056,34 +4173,34 @@
         <v>250</v>
       </c>
       <c r="B52" t="s">
-        <v>244</v>
+        <v>46</v>
       </c>
       <c r="C52" t="s">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="D52" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E52" t="s">
         <v>19</v>
       </c>
       <c r="F52" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="G52" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="H52" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I52" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="J52" t="s">
-        <v>181</v>
+        <v>251</v>
       </c>
       <c r="K52" t="s">
-        <v>251</v>
+        <v>146</v>
       </c>
       <c r="L52" t="s">
         <v>26</v>
@@ -4103,34 +4220,34 @@
         <v>253</v>
       </c>
       <c r="B53" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" t="s">
+        <v>128</v>
+      </c>
+      <c r="D53" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F53" t="s">
+        <v>20</v>
+      </c>
+      <c r="G53" t="s">
         <v>254</v>
       </c>
-      <c r="C53" t="s">
+      <c r="H53" t="s">
+        <v>22</v>
+      </c>
+      <c r="I53" t="s">
+        <v>23</v>
+      </c>
+      <c r="J53" t="s">
         <v>255</v>
       </c>
-      <c r="D53" t="s">
+      <c r="K53" t="s">
         <v>256</v>
-      </c>
-      <c r="E53" t="s">
-        <v>19</v>
-      </c>
-      <c r="F53" t="s">
-        <v>41</v>
-      </c>
-      <c r="G53" t="s">
-        <v>66</v>
-      </c>
-      <c r="H53" t="s">
-        <v>22</v>
-      </c>
-      <c r="I53" t="s">
-        <v>26</v>
-      </c>
-      <c r="J53" t="s">
-        <v>233</v>
-      </c>
-      <c r="K53" t="s">
-        <v>44</v>
       </c>
       <c r="L53" t="s">
         <v>26</v>
@@ -4150,34 +4267,34 @@
         <v>258</v>
       </c>
       <c r="B54" t="s">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="C54" t="s">
-        <v>173</v>
+        <v>240</v>
       </c>
       <c r="D54" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E54" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F54" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G54" t="s">
+        <v>21</v>
+      </c>
+      <c r="H54" t="s">
+        <v>41</v>
+      </c>
+      <c r="I54" t="s">
+        <v>26</v>
+      </c>
+      <c r="J54" t="s">
         <v>259</v>
       </c>
-      <c r="H54" t="s">
-        <v>22</v>
-      </c>
-      <c r="I54" t="s">
-        <v>26</v>
-      </c>
-      <c r="J54" t="s">
+      <c r="K54" t="s">
         <v>260</v>
-      </c>
-      <c r="K54" t="s">
-        <v>227</v>
       </c>
       <c r="L54" t="s">
         <v>26</v>
@@ -4197,10 +4314,10 @@
         <v>262</v>
       </c>
       <c r="B55" t="s">
-        <v>29</v>
+        <v>263</v>
       </c>
       <c r="C55" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D55" t="s">
         <v>18</v>
@@ -4209,22 +4326,22 @@
         <v>19</v>
       </c>
       <c r="F55" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="G55" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H55" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I55" t="s">
         <v>23</v>
       </c>
       <c r="J55" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="K55" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="L55" t="s">
         <v>26</v>
@@ -4236,89 +4353,89 @@
         <v>26</v>
       </c>
       <c r="O55" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B56" t="s">
-        <v>122</v>
+        <v>46</v>
       </c>
       <c r="C56" t="s">
-        <v>173</v>
+        <v>47</v>
       </c>
       <c r="D56" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="E56" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F56" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="G56" t="s">
-        <v>259</v>
+        <v>26</v>
       </c>
       <c r="H56" t="s">
         <v>22</v>
       </c>
       <c r="I56" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J56" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K56" t="s">
-        <v>190</v>
+        <v>33</v>
       </c>
       <c r="L56" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="M56" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="N56" t="s">
         <v>26</v>
       </c>
       <c r="O56" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B57" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C57" t="s">
-        <v>72</v>
+        <v>240</v>
       </c>
       <c r="D57" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="E57" t="s">
         <v>19</v>
       </c>
       <c r="F57" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="G57" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H57" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="I57" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J57" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K57" t="s">
-        <v>269</v>
+        <v>25</v>
       </c>
       <c r="L57" t="s">
         <v>26</v>
@@ -4338,81 +4455,81 @@
         <v>271</v>
       </c>
       <c r="B58" t="s">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="C58" t="s">
-        <v>173</v>
+        <v>240</v>
       </c>
       <c r="D58" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E58" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F58" t="s">
-        <v>124</v>
+        <v>196</v>
       </c>
       <c r="G58" t="s">
-        <v>259</v>
+        <v>75</v>
       </c>
       <c r="H58" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="I58" t="s">
         <v>26</v>
       </c>
       <c r="J58" t="s">
+        <v>154</v>
+      </c>
+      <c r="K58" t="s">
+        <v>208</v>
+      </c>
+      <c r="L58" t="s">
+        <v>26</v>
+      </c>
+      <c r="M58" t="s">
+        <v>198</v>
+      </c>
+      <c r="N58" t="s">
+        <v>26</v>
+      </c>
+      <c r="O58" t="s">
         <v>272</v>
-      </c>
-      <c r="K58" t="s">
-        <v>273</v>
-      </c>
-      <c r="L58" t="s">
-        <v>26</v>
-      </c>
-      <c r="M58" t="s">
-        <v>126</v>
-      </c>
-      <c r="N58" t="s">
-        <v>26</v>
-      </c>
-      <c r="O58" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B59" t="s">
-        <v>122</v>
+        <v>263</v>
       </c>
       <c r="C59" t="s">
-        <v>173</v>
+        <v>17</v>
       </c>
       <c r="D59" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="E59" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F59" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="G59" t="s">
-        <v>276</v>
+        <v>21</v>
       </c>
       <c r="H59" t="s">
         <v>22</v>
       </c>
       <c r="I59" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J59" t="s">
-        <v>277</v>
+        <v>183</v>
       </c>
       <c r="K59" t="s">
-        <v>278</v>
+        <v>187</v>
       </c>
       <c r="L59" t="s">
         <v>26</v>
@@ -4424,42 +4541,42 @@
         <v>26</v>
       </c>
       <c r="O59" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B60" t="s">
-        <v>122</v>
+        <v>46</v>
       </c>
       <c r="C60" t="s">
-        <v>173</v>
+        <v>47</v>
       </c>
       <c r="D60" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="E60" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F60" t="s">
-        <v>65</v>
+        <v>237</v>
       </c>
       <c r="G60" t="s">
-        <v>281</v>
+        <v>26</v>
       </c>
       <c r="H60" t="s">
         <v>22</v>
       </c>
       <c r="I60" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J60" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="K60" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="L60" t="s">
         <v>26</v>
@@ -4471,230 +4588,230 @@
         <v>26</v>
       </c>
       <c r="O60" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="B61" t="s">
-        <v>285</v>
+        <v>46</v>
       </c>
       <c r="C61" t="s">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="D61" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E61" t="s">
         <v>19</v>
       </c>
       <c r="F61" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="G61" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="H61" t="s">
         <v>22</v>
       </c>
       <c r="I61" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="J61" t="s">
-        <v>118</v>
+        <v>279</v>
       </c>
       <c r="K61" t="s">
-        <v>286</v>
+        <v>33</v>
       </c>
       <c r="L61" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="M61" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="N61" t="s">
         <v>26</v>
       </c>
       <c r="O61" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B62" t="s">
-        <v>59</v>
+        <v>263</v>
       </c>
       <c r="C62" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="D62" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E62" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F62" t="s">
-        <v>124</v>
+        <v>48</v>
       </c>
       <c r="G62" t="s">
-        <v>259</v>
+        <v>31</v>
       </c>
       <c r="H62" t="s">
+        <v>22</v>
+      </c>
+      <c r="I62" t="s">
+        <v>26</v>
+      </c>
+      <c r="J62" t="s">
+        <v>166</v>
+      </c>
+      <c r="K62" t="s">
         <v>33</v>
       </c>
-      <c r="I62" t="s">
-        <v>23</v>
-      </c>
-      <c r="J62" t="s">
-        <v>289</v>
-      </c>
-      <c r="K62" t="s">
-        <v>290</v>
-      </c>
       <c r="L62" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="M62" t="s">
-        <v>126</v>
+        <v>51</v>
       </c>
       <c r="N62" t="s">
         <v>26</v>
       </c>
       <c r="O62" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B63" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="C63" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="D63" t="s">
         <v>18</v>
       </c>
       <c r="E63" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F63" t="s">
-        <v>124</v>
+        <v>170</v>
       </c>
       <c r="G63" t="s">
-        <v>32</v>
+        <v>284</v>
       </c>
       <c r="H63" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I63" t="s">
         <v>23</v>
       </c>
       <c r="J63" t="s">
-        <v>293</v>
+        <v>109</v>
       </c>
       <c r="K63" t="s">
-        <v>278</v>
+        <v>248</v>
       </c>
       <c r="L63" t="s">
         <v>26</v>
       </c>
       <c r="M63" t="s">
-        <v>126</v>
+        <v>26</v>
       </c>
       <c r="N63" t="s">
         <v>26</v>
       </c>
       <c r="O63" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="B64" t="s">
-        <v>230</v>
+        <v>46</v>
       </c>
       <c r="C64" t="s">
-        <v>231</v>
+        <v>47</v>
       </c>
       <c r="D64" t="s">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="E64" t="s">
         <v>19</v>
       </c>
       <c r="F64" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="G64" t="s">
-        <v>296</v>
+        <v>26</v>
       </c>
       <c r="H64" t="s">
         <v>22</v>
       </c>
       <c r="I64" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="J64" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="K64" t="s">
-        <v>44</v>
+        <v>288</v>
       </c>
       <c r="L64" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="M64" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="N64" t="s">
         <v>26</v>
       </c>
       <c r="O64" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B65" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="C65" t="s">
-        <v>30</v>
+        <v>108</v>
       </c>
       <c r="D65" t="s">
         <v>18</v>
       </c>
       <c r="E65" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F65" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="G65" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="H65" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I65" t="s">
         <v>23</v>
       </c>
       <c r="J65" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="K65" t="s">
-        <v>109</v>
+        <v>292</v>
       </c>
       <c r="L65" t="s">
         <v>26</v>
@@ -4706,42 +4823,42 @@
         <v>26</v>
       </c>
       <c r="O65" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="B66" t="s">
-        <v>244</v>
+        <v>295</v>
       </c>
       <c r="C66" t="s">
-        <v>116</v>
+        <v>296</v>
       </c>
       <c r="D66" t="s">
-        <v>40</v>
+        <v>297</v>
       </c>
       <c r="E66" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F66" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="G66" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="H66" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="I66" t="s">
-        <v>117</v>
+        <v>191</v>
       </c>
       <c r="J66" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="K66" t="s">
-        <v>273</v>
+        <v>83</v>
       </c>
       <c r="L66" t="s">
         <v>26</v>
@@ -4753,42 +4870,42 @@
         <v>26</v>
       </c>
       <c r="O66" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B67" t="s">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="C67" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D67" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="E67" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F67" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="G67" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="H67" t="s">
         <v>22</v>
       </c>
       <c r="I67" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J67" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="K67" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="L67" t="s">
         <v>26</v>
@@ -4800,42 +4917,42 @@
         <v>26</v>
       </c>
       <c r="O67" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B68" t="s">
-        <v>47</v>
+        <v>263</v>
       </c>
       <c r="C68" t="s">
-        <v>123</v>
+        <v>26</v>
       </c>
       <c r="D68" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E68" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F68" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G68" t="s">
-        <v>66</v>
+        <v>144</v>
       </c>
       <c r="H68" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I68" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J68" t="s">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="K68" t="s">
-        <v>310</v>
+        <v>163</v>
       </c>
       <c r="L68" t="s">
         <v>26</v>
@@ -4847,42 +4964,42 @@
         <v>26</v>
       </c>
       <c r="O68" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B69" t="s">
-        <v>122</v>
+        <v>308</v>
       </c>
       <c r="C69" t="s">
-        <v>48</v>
+        <v>190</v>
       </c>
       <c r="D69" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="E69" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F69" t="s">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="G69" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H69" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I69" t="s">
-        <v>23</v>
+        <v>191</v>
       </c>
       <c r="J69" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K69" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="L69" t="s">
         <v>26</v>
@@ -4894,42 +5011,42 @@
         <v>26</v>
       </c>
       <c r="O69" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B70" t="s">
-        <v>122</v>
+        <v>230</v>
       </c>
       <c r="C70" t="s">
-        <v>48</v>
+        <v>296</v>
       </c>
       <c r="D70" t="s">
-        <v>18</v>
+        <v>297</v>
       </c>
       <c r="E70" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F70" t="s">
-        <v>65</v>
+        <v>196</v>
       </c>
       <c r="G70" t="s">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="H70" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="I70" t="s">
-        <v>23</v>
+        <v>191</v>
       </c>
       <c r="J70" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="K70" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
       <c r="L70" t="s">
         <v>26</v>
@@ -4941,42 +5058,42 @@
         <v>26</v>
       </c>
       <c r="O70" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B71" t="s">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="C71" t="s">
-        <v>116</v>
+        <v>190</v>
       </c>
       <c r="D71" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="E71" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F71" t="s">
-        <v>65</v>
+        <v>129</v>
       </c>
       <c r="G71" t="s">
-        <v>320</v>
+        <v>75</v>
       </c>
       <c r="H71" t="s">
         <v>22</v>
       </c>
       <c r="I71" t="s">
-        <v>117</v>
+        <v>191</v>
       </c>
       <c r="J71" t="s">
-        <v>321</v>
+        <v>247</v>
       </c>
       <c r="K71" t="s">
-        <v>190</v>
+        <v>315</v>
       </c>
       <c r="L71" t="s">
         <v>26</v>
@@ -4988,42 +5105,42 @@
         <v>26</v>
       </c>
       <c r="O71" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B72" t="s">
-        <v>47</v>
+        <v>318</v>
       </c>
       <c r="C72" t="s">
-        <v>123</v>
+        <v>319</v>
       </c>
       <c r="D72" t="s">
-        <v>18</v>
+        <v>320</v>
       </c>
       <c r="E72" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F72" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="G72" t="s">
-        <v>324</v>
+        <v>21</v>
       </c>
       <c r="H72" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="I72" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J72" t="s">
-        <v>325</v>
+        <v>298</v>
       </c>
       <c r="K72" t="s">
-        <v>223</v>
+        <v>76</v>
       </c>
       <c r="L72" t="s">
         <v>26</v>
@@ -5035,42 +5152,42 @@
         <v>26</v>
       </c>
       <c r="O72" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B73" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="C73" t="s">
-        <v>48</v>
+        <v>240</v>
       </c>
       <c r="D73" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="E73" t="s">
         <v>19</v>
       </c>
       <c r="F73" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G73" t="s">
-        <v>66</v>
+        <v>323</v>
       </c>
       <c r="H73" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="I73" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J73" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="K73" t="s">
-        <v>51</v>
+        <v>292</v>
       </c>
       <c r="L73" t="s">
         <v>26</v>
@@ -5082,42 +5199,42 @@
         <v>26</v>
       </c>
       <c r="O73" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B74" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="C74" t="s">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
       </c>
       <c r="E74" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F74" t="s">
-        <v>65</v>
+        <v>129</v>
       </c>
       <c r="G74" t="s">
-        <v>276</v>
+        <v>144</v>
       </c>
       <c r="H74" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I74" t="s">
         <v>23</v>
       </c>
       <c r="J74" t="s">
-        <v>331</v>
+        <v>109</v>
       </c>
       <c r="K74" t="s">
-        <v>273</v>
+        <v>208</v>
       </c>
       <c r="L74" t="s">
         <v>26</v>
@@ -5129,42 +5246,42 @@
         <v>26</v>
       </c>
       <c r="O74" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="B75" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="C75" t="s">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="D75" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="E75" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F75" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="G75" t="s">
-        <v>66</v>
+        <v>323</v>
       </c>
       <c r="H75" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="I75" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J75" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="K75" t="s">
-        <v>94</v>
+        <v>256</v>
       </c>
       <c r="L75" t="s">
         <v>26</v>
@@ -5176,42 +5293,42 @@
         <v>26</v>
       </c>
       <c r="O75" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B76" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="C76" t="s">
-        <v>30</v>
+        <v>108</v>
       </c>
       <c r="D76" t="s">
         <v>18</v>
       </c>
       <c r="E76" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F76" t="s">
-        <v>65</v>
+        <v>129</v>
       </c>
       <c r="G76" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="H76" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I76" t="s">
         <v>23</v>
       </c>
       <c r="J76" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="K76" t="s">
-        <v>68</v>
+        <v>333</v>
       </c>
       <c r="L76" t="s">
         <v>26</v>
@@ -5223,89 +5340,89 @@
         <v>26</v>
       </c>
       <c r="O76" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B77" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="C77" t="s">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="D77" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="E77" t="s">
         <v>19</v>
       </c>
       <c r="F77" t="s">
-        <v>65</v>
+        <v>196</v>
       </c>
       <c r="G77" t="s">
-        <v>66</v>
+        <v>323</v>
       </c>
       <c r="H77" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="I77" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J77" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="K77" t="s">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="L77" t="s">
         <v>26</v>
       </c>
       <c r="M77" t="s">
-        <v>26</v>
+        <v>198</v>
       </c>
       <c r="N77" t="s">
         <v>26</v>
       </c>
       <c r="O77" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B78" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="C78" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="D78" t="s">
-        <v>232</v>
+        <v>81</v>
       </c>
       <c r="E78" t="s">
         <v>19</v>
       </c>
       <c r="F78" t="s">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="G78" t="s">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="H78" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="I78" t="s">
-        <v>117</v>
+        <v>26</v>
       </c>
       <c r="J78" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="K78" t="s">
-        <v>286</v>
+        <v>340</v>
       </c>
       <c r="L78" t="s">
         <v>26</v>
@@ -5317,42 +5434,42 @@
         <v>26</v>
       </c>
       <c r="O78" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B79" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="C79" t="s">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="D79" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="E79" t="s">
         <v>19</v>
       </c>
       <c r="F79" t="s">
-        <v>65</v>
+        <v>129</v>
       </c>
       <c r="G79" t="s">
-        <v>66</v>
+        <v>343</v>
       </c>
       <c r="H79" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="I79" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J79" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="K79" t="s">
-        <v>286</v>
+        <v>345</v>
       </c>
       <c r="L79" t="s">
         <v>26</v>
@@ -5364,112 +5481,112 @@
         <v>26</v>
       </c>
       <c r="O79" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>347</v>
+      </c>
+      <c r="B80" t="s">
+        <v>348</v>
+      </c>
+      <c r="C80" t="s">
+        <v>190</v>
+      </c>
+      <c r="D80" t="s">
+        <v>68</v>
+      </c>
+      <c r="E80" t="s">
+        <v>38</v>
+      </c>
+      <c r="F80" t="s">
+        <v>129</v>
+      </c>
+      <c r="G80" t="s">
+        <v>21</v>
+      </c>
+      <c r="H80" t="s">
+        <v>41</v>
+      </c>
+      <c r="I80" t="s">
+        <v>191</v>
+      </c>
+      <c r="J80" t="s">
+        <v>192</v>
+      </c>
+      <c r="K80" t="s">
         <v>349</v>
       </c>
-      <c r="B80" t="s">
+      <c r="L80" t="s">
+        <v>26</v>
+      </c>
+      <c r="M80" t="s">
+        <v>26</v>
+      </c>
+      <c r="N80" t="s">
+        <v>26</v>
+      </c>
+      <c r="O80" t="s">
         <v>350</v>
-      </c>
-      <c r="C80" t="s">
-        <v>351</v>
-      </c>
-      <c r="D80" t="s">
-        <v>40</v>
-      </c>
-      <c r="E80" t="s">
-        <v>19</v>
-      </c>
-      <c r="F80" t="s">
-        <v>144</v>
-      </c>
-      <c r="G80" t="s">
-        <v>42</v>
-      </c>
-      <c r="H80" t="s">
-        <v>22</v>
-      </c>
-      <c r="I80" t="s">
-        <v>26</v>
-      </c>
-      <c r="J80" t="s">
-        <v>352</v>
-      </c>
-      <c r="K80" t="s">
-        <v>353</v>
-      </c>
-      <c r="L80" t="s">
-        <v>26</v>
-      </c>
-      <c r="M80" t="s">
-        <v>26</v>
-      </c>
-      <c r="N80" t="s">
-        <v>354</v>
-      </c>
-      <c r="O80" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B81" t="s">
-        <v>244</v>
+        <v>46</v>
       </c>
       <c r="C81" t="s">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="D81" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E81" t="s">
         <v>19</v>
       </c>
       <c r="F81" t="s">
-        <v>65</v>
+        <v>196</v>
       </c>
       <c r="G81" t="s">
-        <v>42</v>
+        <v>323</v>
       </c>
       <c r="H81" t="s">
         <v>22</v>
       </c>
       <c r="I81" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="J81" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="K81" t="s">
-        <v>164</v>
+        <v>353</v>
       </c>
       <c r="L81" t="s">
         <v>26</v>
       </c>
       <c r="M81" t="s">
-        <v>26</v>
+        <v>198</v>
       </c>
       <c r="N81" t="s">
         <v>26</v>
       </c>
       <c r="O81" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B82" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="C82" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="D82" t="s">
         <v>18</v>
@@ -5478,69 +5595,69 @@
         <v>19</v>
       </c>
       <c r="F82" t="s">
-        <v>31</v>
+        <v>196</v>
       </c>
       <c r="G82" t="s">
-        <v>188</v>
+        <v>144</v>
       </c>
       <c r="H82" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I82" t="s">
         <v>23</v>
       </c>
       <c r="J82" t="s">
-        <v>297</v>
+        <v>356</v>
       </c>
       <c r="K82" t="s">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="L82" t="s">
         <v>26</v>
       </c>
       <c r="M82" t="s">
-        <v>26</v>
+        <v>198</v>
       </c>
       <c r="N82" t="s">
         <v>26</v>
       </c>
       <c r="O82" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B83" t="s">
-        <v>244</v>
+        <v>295</v>
       </c>
       <c r="C83" t="s">
-        <v>116</v>
+        <v>296</v>
       </c>
       <c r="D83" t="s">
-        <v>40</v>
+        <v>297</v>
       </c>
       <c r="E83" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F83" t="s">
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="G83" t="s">
-        <v>32</v>
+        <v>359</v>
       </c>
       <c r="H83" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="I83" t="s">
-        <v>117</v>
+        <v>191</v>
       </c>
       <c r="J83" t="s">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="K83" t="s">
-        <v>227</v>
+        <v>76</v>
       </c>
       <c r="L83" t="s">
         <v>26</v>
@@ -5552,42 +5669,42 @@
         <v>26</v>
       </c>
       <c r="O83" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B84" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="C84" t="s">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="D84" t="s">
         <v>18</v>
       </c>
       <c r="E84" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F84" t="s">
-        <v>54</v>
+        <v>129</v>
       </c>
       <c r="G84" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H84" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I84" t="s">
         <v>23</v>
       </c>
       <c r="J84" t="s">
-        <v>321</v>
+        <v>363</v>
       </c>
       <c r="K84" t="s">
-        <v>79</v>
+        <v>345</v>
       </c>
       <c r="L84" t="s">
         <v>26</v>
@@ -5599,112 +5716,112 @@
         <v>26</v>
       </c>
       <c r="O84" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
+        <v>365</v>
+      </c>
+      <c r="B85" t="s">
+        <v>308</v>
+      </c>
+      <c r="C85" t="s">
+        <v>190</v>
+      </c>
+      <c r="D85" t="s">
+        <v>68</v>
+      </c>
+      <c r="E85" t="s">
+        <v>38</v>
+      </c>
+      <c r="F85" t="s">
+        <v>129</v>
+      </c>
+      <c r="G85" t="s">
+        <v>21</v>
+      </c>
+      <c r="H85" t="s">
+        <v>41</v>
+      </c>
+      <c r="I85" t="s">
+        <v>191</v>
+      </c>
+      <c r="J85" t="s">
         <v>366</v>
       </c>
-      <c r="B85" t="s">
-        <v>47</v>
-      </c>
-      <c r="C85" t="s">
-        <v>123</v>
-      </c>
-      <c r="D85" t="s">
-        <v>18</v>
-      </c>
-      <c r="E85" t="s">
-        <v>49</v>
-      </c>
-      <c r="F85" t="s">
-        <v>31</v>
-      </c>
-      <c r="G85" t="s">
-        <v>103</v>
-      </c>
-      <c r="H85" t="s">
-        <v>33</v>
-      </c>
-      <c r="I85" t="s">
-        <v>23</v>
-      </c>
-      <c r="J85" t="s">
+      <c r="K85" t="s">
+        <v>131</v>
+      </c>
+      <c r="L85" t="s">
+        <v>26</v>
+      </c>
+      <c r="M85" t="s">
+        <v>26</v>
+      </c>
+      <c r="N85" t="s">
+        <v>26</v>
+      </c>
+      <c r="O85" t="s">
         <v>367</v>
-      </c>
-      <c r="K85" t="s">
-        <v>368</v>
-      </c>
-      <c r="L85" t="s">
-        <v>26</v>
-      </c>
-      <c r="M85" t="s">
-        <v>26</v>
-      </c>
-      <c r="N85" t="s">
-        <v>26</v>
-      </c>
-      <c r="O85" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
+        <v>368</v>
+      </c>
+      <c r="B86" t="s">
+        <v>79</v>
+      </c>
+      <c r="C86" t="s">
+        <v>80</v>
+      </c>
+      <c r="D86" t="s">
+        <v>81</v>
+      </c>
+      <c r="E86" t="s">
+        <v>19</v>
+      </c>
+      <c r="F86" t="s">
+        <v>129</v>
+      </c>
+      <c r="G86" t="s">
+        <v>21</v>
+      </c>
+      <c r="H86" t="s">
+        <v>41</v>
+      </c>
+      <c r="I86" t="s">
+        <v>26</v>
+      </c>
+      <c r="J86" t="s">
+        <v>369</v>
+      </c>
+      <c r="K86" t="s">
+        <v>110</v>
+      </c>
+      <c r="L86" t="s">
+        <v>26</v>
+      </c>
+      <c r="M86" t="s">
+        <v>26</v>
+      </c>
+      <c r="N86" t="s">
+        <v>26</v>
+      </c>
+      <c r="O86" t="s">
         <v>370</v>
-      </c>
-      <c r="B86" t="s">
-        <v>59</v>
-      </c>
-      <c r="C86" t="s">
-        <v>60</v>
-      </c>
-      <c r="D86" t="s">
-        <v>18</v>
-      </c>
-      <c r="E86" t="s">
-        <v>49</v>
-      </c>
-      <c r="F86" t="s">
-        <v>54</v>
-      </c>
-      <c r="G86" t="s">
-        <v>26</v>
-      </c>
-      <c r="H86" t="s">
-        <v>33</v>
-      </c>
-      <c r="I86" t="s">
-        <v>23</v>
-      </c>
-      <c r="J86" t="s">
-        <v>371</v>
-      </c>
-      <c r="K86" t="s">
-        <v>269</v>
-      </c>
-      <c r="L86" t="s">
-        <v>26</v>
-      </c>
-      <c r="M86" t="s">
-        <v>26</v>
-      </c>
-      <c r="N86" t="s">
-        <v>26</v>
-      </c>
-      <c r="O86" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B87" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C87" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D87" t="s">
         <v>18</v>
@@ -5713,22 +5830,22 @@
         <v>19</v>
       </c>
       <c r="F87" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="G87" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="H87" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I87" t="s">
         <v>23</v>
       </c>
       <c r="J87" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="K87" t="s">
-        <v>109</v>
+        <v>372</v>
       </c>
       <c r="L87" t="s">
         <v>26</v>
@@ -5740,42 +5857,42 @@
         <v>26</v>
       </c>
       <c r="O87" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B88" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C88" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="D88" t="s">
         <v>18</v>
       </c>
       <c r="E88" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F88" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G88" t="s">
-        <v>259</v>
+        <v>144</v>
       </c>
       <c r="H88" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I88" t="s">
         <v>23</v>
       </c>
       <c r="J88" t="s">
-        <v>136</v>
+        <v>375</v>
       </c>
       <c r="K88" t="s">
-        <v>94</v>
+        <v>376</v>
       </c>
       <c r="L88" t="s">
         <v>26</v>
@@ -5795,175 +5912,175 @@
         <v>378</v>
       </c>
       <c r="B89" t="s">
-        <v>379</v>
+        <v>72</v>
       </c>
       <c r="C89" t="s">
-        <v>351</v>
+        <v>152</v>
       </c>
       <c r="D89" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E89" t="s">
         <v>19</v>
       </c>
       <c r="F89" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="G89" t="s">
-        <v>66</v>
+        <v>254</v>
       </c>
       <c r="H89" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I89" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J89" t="s">
+        <v>379</v>
+      </c>
+      <c r="K89" t="s">
+        <v>146</v>
+      </c>
+      <c r="L89" t="s">
+        <v>26</v>
+      </c>
+      <c r="M89" t="s">
+        <v>26</v>
+      </c>
+      <c r="N89" t="s">
+        <v>26</v>
+      </c>
+      <c r="O89" t="s">
         <v>380</v>
-      </c>
-      <c r="K89" t="s">
-        <v>174</v>
-      </c>
-      <c r="L89" t="s">
-        <v>26</v>
-      </c>
-      <c r="M89" t="s">
-        <v>26</v>
-      </c>
-      <c r="N89" t="s">
-        <v>381</v>
-      </c>
-      <c r="O89" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
+        <v>381</v>
+      </c>
+      <c r="B90" t="s">
+        <v>308</v>
+      </c>
+      <c r="C90" t="s">
+        <v>190</v>
+      </c>
+      <c r="D90" t="s">
+        <v>68</v>
+      </c>
+      <c r="E90" t="s">
+        <v>38</v>
+      </c>
+      <c r="F90" t="s">
+        <v>129</v>
+      </c>
+      <c r="G90" t="s">
+        <v>382</v>
+      </c>
+      <c r="H90" t="s">
+        <v>41</v>
+      </c>
+      <c r="I90" t="s">
+        <v>191</v>
+      </c>
+      <c r="J90" t="s">
         <v>383</v>
       </c>
-      <c r="B90" t="s">
-        <v>379</v>
-      </c>
-      <c r="C90" t="s">
-        <v>351</v>
-      </c>
-      <c r="D90" t="s">
-        <v>40</v>
-      </c>
-      <c r="E90" t="s">
-        <v>19</v>
-      </c>
-      <c r="F90" t="s">
-        <v>144</v>
-      </c>
-      <c r="G90" t="s">
-        <v>66</v>
-      </c>
-      <c r="H90" t="s">
-        <v>22</v>
-      </c>
-      <c r="I90" t="s">
-        <v>26</v>
-      </c>
-      <c r="J90" t="s">
+      <c r="K90" t="s">
+        <v>256</v>
+      </c>
+      <c r="L90" t="s">
+        <v>26</v>
+      </c>
+      <c r="M90" t="s">
+        <v>26</v>
+      </c>
+      <c r="N90" t="s">
+        <v>26</v>
+      </c>
+      <c r="O90" t="s">
         <v>384</v>
-      </c>
-      <c r="K90" t="s">
-        <v>223</v>
-      </c>
-      <c r="L90" t="s">
-        <v>26</v>
-      </c>
-      <c r="M90" t="s">
-        <v>26</v>
-      </c>
-      <c r="N90" t="s">
-        <v>385</v>
-      </c>
-      <c r="O90" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B91" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="C91" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="D91" t="s">
         <v>18</v>
       </c>
       <c r="E91" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F91" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="G91" t="s">
-        <v>26</v>
+        <v>386</v>
       </c>
       <c r="H91" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I91" t="s">
         <v>23</v>
       </c>
       <c r="J91" t="s">
+        <v>387</v>
+      </c>
+      <c r="K91" t="s">
+        <v>50</v>
+      </c>
+      <c r="L91" t="s">
+        <v>26</v>
+      </c>
+      <c r="M91" t="s">
+        <v>26</v>
+      </c>
+      <c r="N91" t="s">
+        <v>26</v>
+      </c>
+      <c r="O91" t="s">
         <v>388</v>
-      </c>
-      <c r="K91" t="s">
-        <v>389</v>
-      </c>
-      <c r="L91" t="s">
-        <v>26</v>
-      </c>
-      <c r="M91" t="s">
-        <v>26</v>
-      </c>
-      <c r="N91" t="s">
-        <v>26</v>
-      </c>
-      <c r="O91" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B92" t="s">
-        <v>29</v>
+        <v>138</v>
       </c>
       <c r="C92" t="s">
-        <v>30</v>
+        <v>152</v>
       </c>
       <c r="D92" t="s">
         <v>18</v>
       </c>
       <c r="E92" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F92" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="G92" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="H92" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I92" t="s">
         <v>23</v>
       </c>
       <c r="J92" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="K92" t="s">
-        <v>393</v>
+        <v>155</v>
       </c>
       <c r="L92" t="s">
         <v>26</v>
@@ -5975,30 +6092,30 @@
         <v>26</v>
       </c>
       <c r="O92" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B93" t="s">
-        <v>149</v>
+        <v>46</v>
       </c>
       <c r="C93" t="s">
-        <v>177</v>
+        <v>47</v>
       </c>
       <c r="D93" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E93" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F93" t="s">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="G93" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="H93" t="s">
         <v>22</v>
@@ -6007,10 +6124,10 @@
         <v>23</v>
       </c>
       <c r="J93" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="K93" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="L93" t="s">
         <v>26</v>
@@ -6022,42 +6139,42 @@
         <v>26</v>
       </c>
       <c r="O93" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B94" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="C94" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="D94" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="E94" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F94" t="s">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="G94" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="H94" t="s">
         <v>22</v>
       </c>
       <c r="I94" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J94" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="K94" t="s">
-        <v>153</v>
+        <v>54</v>
       </c>
       <c r="L94" t="s">
         <v>26</v>
@@ -6069,42 +6186,42 @@
         <v>26</v>
       </c>
       <c r="O94" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B95" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="C95" t="s">
-        <v>402</v>
+        <v>128</v>
       </c>
       <c r="D95" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E95" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F95" t="s">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="G95" t="s">
-        <v>66</v>
+        <v>144</v>
       </c>
       <c r="H95" t="s">
         <v>22</v>
       </c>
       <c r="I95" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J95" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="K95" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="L95" t="s">
         <v>26</v>
@@ -6116,42 +6233,42 @@
         <v>26</v>
       </c>
       <c r="O95" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B96" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="C96" t="s">
+        <v>128</v>
+      </c>
+      <c r="D96" t="s">
+        <v>18</v>
+      </c>
+      <c r="E96" t="s">
+        <v>38</v>
+      </c>
+      <c r="F96" t="s">
+        <v>129</v>
+      </c>
+      <c r="G96" t="s">
+        <v>21</v>
+      </c>
+      <c r="H96" t="s">
+        <v>22</v>
+      </c>
+      <c r="I96" t="s">
+        <v>23</v>
+      </c>
+      <c r="J96" t="s">
         <v>402</v>
       </c>
-      <c r="D96" t="s">
-        <v>19</v>
-      </c>
-      <c r="E96" t="s">
-        <v>19</v>
-      </c>
-      <c r="F96" t="s">
-        <v>65</v>
-      </c>
-      <c r="G96" t="s">
-        <v>259</v>
-      </c>
-      <c r="H96" t="s">
-        <v>22</v>
-      </c>
-      <c r="I96" t="s">
-        <v>26</v>
-      </c>
-      <c r="J96" t="s">
-        <v>406</v>
-      </c>
       <c r="K96" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="L96" t="s">
         <v>26</v>
@@ -6163,42 +6280,42 @@
         <v>26</v>
       </c>
       <c r="O96" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B97" t="s">
+        <v>138</v>
+      </c>
+      <c r="C97" t="s">
+        <v>296</v>
+      </c>
+      <c r="D97" t="s">
+        <v>297</v>
+      </c>
+      <c r="E97" t="s">
         <v>38</v>
       </c>
-      <c r="C97" t="s">
-        <v>39</v>
-      </c>
-      <c r="D97" t="s">
-        <v>40</v>
-      </c>
-      <c r="E97" t="s">
-        <v>19</v>
-      </c>
       <c r="F97" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="G97" t="s">
-        <v>26</v>
+        <v>144</v>
       </c>
       <c r="H97" t="s">
         <v>22</v>
       </c>
       <c r="I97" t="s">
-        <v>23</v>
+        <v>191</v>
       </c>
       <c r="J97" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="K97" t="s">
-        <v>411</v>
+        <v>349</v>
       </c>
       <c r="L97" t="s">
         <v>26</v>
@@ -6210,42 +6327,42 @@
         <v>26</v>
       </c>
       <c r="O97" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B98" t="s">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="C98" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D98" t="s">
         <v>18</v>
       </c>
       <c r="E98" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F98" t="s">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="G98" t="s">
-        <v>259</v>
+        <v>21</v>
       </c>
       <c r="H98" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="I98" t="s">
         <v>23</v>
       </c>
       <c r="J98" t="s">
-        <v>73</v>
+        <v>409</v>
       </c>
       <c r="K98" t="s">
-        <v>137</v>
+        <v>349</v>
       </c>
       <c r="L98" t="s">
         <v>26</v>
@@ -6257,101 +6374,665 @@
         <v>26</v>
       </c>
       <c r="O98" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
+        <v>411</v>
+      </c>
+      <c r="B99" t="s">
+        <v>116</v>
+      </c>
+      <c r="C99" t="s">
+        <v>117</v>
+      </c>
+      <c r="D99" t="s">
+        <v>68</v>
+      </c>
+      <c r="E99" t="s">
+        <v>38</v>
+      </c>
+      <c r="F99" t="s">
+        <v>214</v>
+      </c>
+      <c r="G99" t="s">
+        <v>75</v>
+      </c>
+      <c r="H99" t="s">
+        <v>41</v>
+      </c>
+      <c r="I99" t="s">
+        <v>26</v>
+      </c>
+      <c r="J99" t="s">
+        <v>412</v>
+      </c>
+      <c r="K99" t="s">
+        <v>413</v>
+      </c>
+      <c r="L99" t="s">
+        <v>26</v>
+      </c>
+      <c r="M99" t="s">
+        <v>26</v>
+      </c>
+      <c r="N99" t="s">
+        <v>414</v>
+      </c>
+      <c r="O99" t="s">
         <v>415</v>
-      </c>
-      <c r="B99" t="s">
-        <v>29</v>
-      </c>
-      <c r="C99" t="s">
-        <v>30</v>
-      </c>
-      <c r="D99" t="s">
-        <v>18</v>
-      </c>
-      <c r="E99" t="s">
-        <v>19</v>
-      </c>
-      <c r="F99" t="s">
-        <v>41</v>
-      </c>
-      <c r="G99" t="s">
-        <v>66</v>
-      </c>
-      <c r="H99" t="s">
-        <v>33</v>
-      </c>
-      <c r="I99" t="s">
-        <v>23</v>
-      </c>
-      <c r="J99" t="s">
-        <v>416</v>
-      </c>
-      <c r="K99" t="s">
-        <v>74</v>
-      </c>
-      <c r="L99" t="s">
-        <v>26</v>
-      </c>
-      <c r="M99" t="s">
-        <v>26</v>
-      </c>
-      <c r="N99" t="s">
-        <v>26</v>
-      </c>
-      <c r="O99" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
+        <v>416</v>
+      </c>
+      <c r="B100" t="s">
+        <v>308</v>
+      </c>
+      <c r="C100" t="s">
+        <v>190</v>
+      </c>
+      <c r="D100" t="s">
+        <v>68</v>
+      </c>
+      <c r="E100" t="s">
+        <v>38</v>
+      </c>
+      <c r="F100" t="s">
+        <v>129</v>
+      </c>
+      <c r="G100" t="s">
+        <v>75</v>
+      </c>
+      <c r="H100" t="s">
+        <v>41</v>
+      </c>
+      <c r="I100" t="s">
+        <v>191</v>
+      </c>
+      <c r="J100" t="s">
+        <v>417</v>
+      </c>
+      <c r="K100" t="s">
+        <v>83</v>
+      </c>
+      <c r="L100" t="s">
+        <v>26</v>
+      </c>
+      <c r="M100" t="s">
+        <v>26</v>
+      </c>
+      <c r="N100" t="s">
+        <v>26</v>
+      </c>
+      <c r="O100" t="s">
         <v>418</v>
       </c>
-      <c r="B100" t="s">
-        <v>149</v>
-      </c>
-      <c r="C100" t="s">
-        <v>26</v>
-      </c>
-      <c r="D100" t="s">
-        <v>26</v>
-      </c>
-      <c r="E100" t="s">
-        <v>49</v>
-      </c>
-      <c r="F100" t="s">
-        <v>31</v>
-      </c>
-      <c r="G100" t="s">
-        <v>66</v>
-      </c>
-      <c r="H100" t="s">
-        <v>33</v>
-      </c>
-      <c r="I100" t="s">
-        <v>26</v>
-      </c>
-      <c r="J100" t="s">
-        <v>321</v>
-      </c>
-      <c r="K100" t="s">
-        <v>393</v>
-      </c>
-      <c r="L100" t="s">
-        <v>26</v>
-      </c>
-      <c r="M100" t="s">
-        <v>26</v>
-      </c>
-      <c r="N100" t="s">
-        <v>26</v>
-      </c>
-      <c r="O100" t="s">
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
         <v>419</v>
+      </c>
+      <c r="B101" t="s">
+        <v>127</v>
+      </c>
+      <c r="C101" t="s">
+        <v>128</v>
+      </c>
+      <c r="D101" t="s">
+        <v>18</v>
+      </c>
+      <c r="E101" t="s">
+        <v>38</v>
+      </c>
+      <c r="F101" t="s">
+        <v>20</v>
+      </c>
+      <c r="G101" t="s">
+        <v>254</v>
+      </c>
+      <c r="H101" t="s">
+        <v>22</v>
+      </c>
+      <c r="I101" t="s">
+        <v>23</v>
+      </c>
+      <c r="J101" t="s">
+        <v>360</v>
+      </c>
+      <c r="K101" t="s">
+        <v>420</v>
+      </c>
+      <c r="L101" t="s">
+        <v>26</v>
+      </c>
+      <c r="M101" t="s">
+        <v>26</v>
+      </c>
+      <c r="N101" t="s">
+        <v>26</v>
+      </c>
+      <c r="O101" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>422</v>
+      </c>
+      <c r="B102" t="s">
+        <v>308</v>
+      </c>
+      <c r="C102" t="s">
+        <v>190</v>
+      </c>
+      <c r="D102" t="s">
+        <v>68</v>
+      </c>
+      <c r="E102" t="s">
+        <v>38</v>
+      </c>
+      <c r="F102" t="s">
+        <v>129</v>
+      </c>
+      <c r="G102" t="s">
+        <v>144</v>
+      </c>
+      <c r="H102" t="s">
+        <v>41</v>
+      </c>
+      <c r="I102" t="s">
+        <v>191</v>
+      </c>
+      <c r="J102" t="s">
+        <v>363</v>
+      </c>
+      <c r="K102" t="s">
+        <v>292</v>
+      </c>
+      <c r="L102" t="s">
+        <v>26</v>
+      </c>
+      <c r="M102" t="s">
+        <v>26</v>
+      </c>
+      <c r="N102" t="s">
+        <v>26</v>
+      </c>
+      <c r="O102" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>424</v>
+      </c>
+      <c r="B103" t="s">
+        <v>46</v>
+      </c>
+      <c r="C103" t="s">
+        <v>47</v>
+      </c>
+      <c r="D103" t="s">
+        <v>18</v>
+      </c>
+      <c r="E103" t="s">
+        <v>19</v>
+      </c>
+      <c r="F103" t="s">
+        <v>237</v>
+      </c>
+      <c r="G103" t="s">
+        <v>26</v>
+      </c>
+      <c r="H103" t="s">
+        <v>22</v>
+      </c>
+      <c r="I103" t="s">
+        <v>23</v>
+      </c>
+      <c r="J103" t="s">
+        <v>383</v>
+      </c>
+      <c r="K103" t="s">
+        <v>425</v>
+      </c>
+      <c r="L103" t="s">
+        <v>26</v>
+      </c>
+      <c r="M103" t="s">
+        <v>26</v>
+      </c>
+      <c r="N103" t="s">
+        <v>26</v>
+      </c>
+      <c r="O103" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>427</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="s">
+        <v>17</v>
+      </c>
+      <c r="D104" t="s">
+        <v>18</v>
+      </c>
+      <c r="E104" t="s">
+        <v>19</v>
+      </c>
+      <c r="F104" t="s">
+        <v>20</v>
+      </c>
+      <c r="G104" t="s">
+        <v>58</v>
+      </c>
+      <c r="H104" t="s">
+        <v>22</v>
+      </c>
+      <c r="I104" t="s">
+        <v>23</v>
+      </c>
+      <c r="J104" t="s">
+        <v>428</v>
+      </c>
+      <c r="K104" t="s">
+        <v>429</v>
+      </c>
+      <c r="L104" t="s">
+        <v>26</v>
+      </c>
+      <c r="M104" t="s">
+        <v>26</v>
+      </c>
+      <c r="N104" t="s">
+        <v>26</v>
+      </c>
+      <c r="O104" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>431</v>
+      </c>
+      <c r="B105" t="s">
+        <v>46</v>
+      </c>
+      <c r="C105" t="s">
+        <v>47</v>
+      </c>
+      <c r="D105" t="s">
+        <v>18</v>
+      </c>
+      <c r="E105" t="s">
+        <v>19</v>
+      </c>
+      <c r="F105" t="s">
+        <v>237</v>
+      </c>
+      <c r="G105" t="s">
+        <v>26</v>
+      </c>
+      <c r="H105" t="s">
+        <v>22</v>
+      </c>
+      <c r="I105" t="s">
+        <v>23</v>
+      </c>
+      <c r="J105" t="s">
+        <v>432</v>
+      </c>
+      <c r="K105" t="s">
+        <v>333</v>
+      </c>
+      <c r="L105" t="s">
+        <v>26</v>
+      </c>
+      <c r="M105" t="s">
+        <v>26</v>
+      </c>
+      <c r="N105" t="s">
+        <v>26</v>
+      </c>
+      <c r="O105" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>434</v>
+      </c>
+      <c r="B106" t="s">
+        <v>127</v>
+      </c>
+      <c r="C106" t="s">
+        <v>128</v>
+      </c>
+      <c r="D106" t="s">
+        <v>18</v>
+      </c>
+      <c r="E106" t="s">
+        <v>38</v>
+      </c>
+      <c r="F106" t="s">
+        <v>129</v>
+      </c>
+      <c r="G106" t="s">
+        <v>58</v>
+      </c>
+      <c r="H106" t="s">
+        <v>22</v>
+      </c>
+      <c r="I106" t="s">
+        <v>23</v>
+      </c>
+      <c r="J106" t="s">
+        <v>435</v>
+      </c>
+      <c r="K106" t="s">
+        <v>345</v>
+      </c>
+      <c r="L106" t="s">
+        <v>26</v>
+      </c>
+      <c r="M106" t="s">
+        <v>26</v>
+      </c>
+      <c r="N106" t="s">
+        <v>26</v>
+      </c>
+      <c r="O106" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>437</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="s">
+        <v>17</v>
+      </c>
+      <c r="D107" t="s">
+        <v>18</v>
+      </c>
+      <c r="E107" t="s">
+        <v>19</v>
+      </c>
+      <c r="F107" t="s">
+        <v>20</v>
+      </c>
+      <c r="G107" t="s">
+        <v>323</v>
+      </c>
+      <c r="H107" t="s">
+        <v>22</v>
+      </c>
+      <c r="I107" t="s">
+        <v>23</v>
+      </c>
+      <c r="J107" t="s">
+        <v>109</v>
+      </c>
+      <c r="K107" t="s">
+        <v>54</v>
+      </c>
+      <c r="L107" t="s">
+        <v>26</v>
+      </c>
+      <c r="M107" t="s">
+        <v>26</v>
+      </c>
+      <c r="N107" t="s">
+        <v>26</v>
+      </c>
+      <c r="O107" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>439</v>
+      </c>
+      <c r="B108" t="s">
+        <v>440</v>
+      </c>
+      <c r="C108" t="s">
+        <v>117</v>
+      </c>
+      <c r="D108" t="s">
+        <v>68</v>
+      </c>
+      <c r="E108" t="s">
+        <v>38</v>
+      </c>
+      <c r="F108" t="s">
+        <v>214</v>
+      </c>
+      <c r="G108" t="s">
+        <v>21</v>
+      </c>
+      <c r="H108" t="s">
+        <v>22</v>
+      </c>
+      <c r="I108" t="s">
+        <v>26</v>
+      </c>
+      <c r="J108" t="s">
+        <v>441</v>
+      </c>
+      <c r="K108" t="s">
+        <v>51</v>
+      </c>
+      <c r="L108" t="s">
+        <v>26</v>
+      </c>
+      <c r="M108" t="s">
+        <v>26</v>
+      </c>
+      <c r="N108" t="s">
+        <v>442</v>
+      </c>
+      <c r="O108" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>444</v>
+      </c>
+      <c r="B109" t="s">
+        <v>440</v>
+      </c>
+      <c r="C109" t="s">
+        <v>117</v>
+      </c>
+      <c r="D109" t="s">
+        <v>68</v>
+      </c>
+      <c r="E109" t="s">
+        <v>38</v>
+      </c>
+      <c r="F109" t="s">
+        <v>214</v>
+      </c>
+      <c r="G109" t="s">
+        <v>21</v>
+      </c>
+      <c r="H109" t="s">
+        <v>41</v>
+      </c>
+      <c r="I109" t="s">
+        <v>26</v>
+      </c>
+      <c r="J109" t="s">
+        <v>445</v>
+      </c>
+      <c r="K109" t="s">
+        <v>50</v>
+      </c>
+      <c r="L109" t="s">
+        <v>26</v>
+      </c>
+      <c r="M109" t="s">
+        <v>26</v>
+      </c>
+      <c r="N109" t="s">
+        <v>446</v>
+      </c>
+      <c r="O109" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>448</v>
+      </c>
+      <c r="B110" t="s">
+        <v>46</v>
+      </c>
+      <c r="C110" t="s">
+        <v>47</v>
+      </c>
+      <c r="D110" t="s">
+        <v>18</v>
+      </c>
+      <c r="E110" t="s">
+        <v>19</v>
+      </c>
+      <c r="F110" t="s">
+        <v>237</v>
+      </c>
+      <c r="G110" t="s">
+        <v>26</v>
+      </c>
+      <c r="H110" t="s">
+        <v>22</v>
+      </c>
+      <c r="I110" t="s">
+        <v>23</v>
+      </c>
+      <c r="J110" t="s">
+        <v>449</v>
+      </c>
+      <c r="K110" t="s">
+        <v>450</v>
+      </c>
+      <c r="L110" t="s">
+        <v>26</v>
+      </c>
+      <c r="M110" t="s">
+        <v>26</v>
+      </c>
+      <c r="N110" t="s">
+        <v>26</v>
+      </c>
+      <c r="O110" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>452</v>
+      </c>
+      <c r="B111" t="s">
+        <v>127</v>
+      </c>
+      <c r="C111" t="s">
+        <v>128</v>
+      </c>
+      <c r="D111" t="s">
+        <v>18</v>
+      </c>
+      <c r="E111" t="s">
+        <v>38</v>
+      </c>
+      <c r="F111" t="s">
+        <v>129</v>
+      </c>
+      <c r="G111" t="s">
+        <v>58</v>
+      </c>
+      <c r="H111" t="s">
+        <v>22</v>
+      </c>
+      <c r="I111" t="s">
+        <v>23</v>
+      </c>
+      <c r="J111" t="s">
+        <v>453</v>
+      </c>
+      <c r="K111" t="s">
+        <v>454</v>
+      </c>
+      <c r="L111" t="s">
+        <v>26</v>
+      </c>
+      <c r="M111" t="s">
+        <v>26</v>
+      </c>
+      <c r="N111" t="s">
+        <v>26</v>
+      </c>
+      <c r="O111" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>456</v>
+      </c>
+      <c r="B112" t="s">
+        <v>219</v>
+      </c>
+      <c r="C112" t="s">
+        <v>243</v>
+      </c>
+      <c r="D112" t="s">
+        <v>68</v>
+      </c>
+      <c r="E112" t="s">
+        <v>19</v>
+      </c>
+      <c r="F112" t="s">
+        <v>20</v>
+      </c>
+      <c r="G112" t="s">
+        <v>21</v>
+      </c>
+      <c r="H112" t="s">
+        <v>41</v>
+      </c>
+      <c r="I112" t="s">
+        <v>23</v>
+      </c>
+      <c r="J112" t="s">
+        <v>457</v>
+      </c>
+      <c r="K112" t="s">
+        <v>208</v>
+      </c>
+      <c r="L112" t="s">
+        <v>26</v>
+      </c>
+      <c r="M112" t="s">
+        <v>26</v>
+      </c>
+      <c r="N112" t="s">
+        <v>26</v>
+      </c>
+      <c r="O112" t="s">
+        <v>458</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE101934-9FA6-4A56-803A-2DD22EA1927E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{07801934-09CD-417F-B1BB-6198BF9A1211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1680" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="466">
   <si>
     <t>Time</t>
   </si>
@@ -62,42 +62,264 @@
     <t>Event URL</t>
   </si>
   <si>
+    <t>07/16/2026 4:36:25 PM</t>
+  </si>
+  <si>
+    <t>658 - Medium</t>
+  </si>
+  <si>
+    <t>Paul Kunze Jr</t>
+  </si>
+  <si>
+    <t>Active Drivers, Towing and Recovery</t>
+  </si>
+  <si>
+    <t>HAAS Alert, Towing and Recovery</t>
+  </si>
+  <si>
+    <t>Mobile Usage</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Needs Coaching</t>
+  </si>
+  <si>
+    <t>Tim Neff Jr.</t>
+  </si>
+  <si>
+    <t>I 10;US 90, Orange, TX</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456d12-f12b-5291-9f65-04d5400ba4ff</t>
+  </si>
+  <si>
+    <t>07/16/2026 2:55:40 PM</t>
+  </si>
+  <si>
+    <t>680 - Medium</t>
+  </si>
+  <si>
+    <t>Jesus Carbajal</t>
+  </si>
+  <si>
+    <t>Severe Speeding</t>
+  </si>
+  <si>
+    <t>Speed Sign Verified</t>
+  </si>
+  <si>
+    <t>I 10, Winnie, TX</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456cb6-b2d3-53ff-9b1c-cfacfb120d97</t>
+  </si>
+  <si>
+    <t>07/16/2026 11:12:35 AM</t>
+  </si>
+  <si>
+    <t>Obstructed Camera</t>
+  </si>
+  <si>
+    <t>Creole Nature Trail All-American Road, Vinton, LA, 70668</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456bea-774d-5d24-8ff1-7a175394f335</t>
+  </si>
+  <si>
+    <t>07/16/2026 11:10:17 AM</t>
+  </si>
+  <si>
+    <t>694 - Heavy</t>
+  </si>
+  <si>
+    <t>Dwayne Manuel</t>
+  </si>
+  <si>
+    <t>Active Drivers, Heavy Haul</t>
+  </si>
+  <si>
+    <t>HAAS Alert, Heavy Haul</t>
+  </si>
+  <si>
+    <t>Heavy Speeding</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456be8-5aa7-5277-801b-bdbbde16e640</t>
+  </si>
+  <si>
+    <t>07/16/2026 8:50:11 AM</t>
+  </si>
+  <si>
+    <t>North Linscomb Road, Vidor, TX, 77662</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456b68-1575-5c4e-a71c-3a21d58af60a</t>
+  </si>
+  <si>
+    <t>07/15/2026 9:51:25 PM</t>
+  </si>
+  <si>
+    <t>667 - Medium</t>
+  </si>
+  <si>
+    <t>Jeremy Myers</t>
+  </si>
+  <si>
+    <t>Towing and Recovery</t>
+  </si>
+  <si>
+    <t>Coached</t>
+  </si>
+  <si>
+    <t>US 69;US 287, Lumberton, TX, 77657</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445690c-f853-5ca9-a74d-919836e17a1b</t>
+  </si>
+  <si>
+    <t>07/15/2026 5:27:17 PM</t>
+  </si>
+  <si>
+    <t>615 - Heavy</t>
+  </si>
+  <si>
+    <t>Joshua Barrow</t>
+  </si>
+  <si>
+    <t>Eddie Bowden</t>
+  </si>
+  <si>
+    <t>East Freeway, 12.4 mi ENE Baytown, Chambers County, TX, 77580</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445681b-2408-5a50-ba10-279f6d3cfb96</t>
+  </si>
+  <si>
+    <t>07/15/2026 3:29:30 PM</t>
+  </si>
+  <si>
+    <t>6701 Port Arthur Road, Port Arthur, TX, 77640</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544567af-5092-5b4b-98f8-2a06d3f0147c</t>
+  </si>
+  <si>
+    <t>07/15/2026 2:39:09 PM</t>
+  </si>
+  <si>
+    <t>Eastex Freeway Frontage Road, Beaumont, TX, 77703</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54456781-36ac-511e-91f5-dc21243fac9f</t>
+  </si>
+  <si>
+    <t>07/15/2026 12:05:54 PM</t>
+  </si>
+  <si>
+    <t>669 - Heavy</t>
+  </si>
+  <si>
+    <t>Jason Walker</t>
+  </si>
+  <si>
+    <t>FM 92, Town Bluff, TX</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544566f4-eb2e-57fb-853c-48816be6a5f8</t>
+  </si>
+  <si>
+    <t>07/13/2026 4:04:35 PM</t>
+  </si>
+  <si>
+    <t>668 - Light</t>
+  </si>
+  <si>
+    <t>Emergency Lights, Wet Road, Light Traffic</t>
+  </si>
+  <si>
+    <t>Interstate 10 South Frontage Road, Beaumont, TX, 77705</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455d82-b6e8-57e1-bd3e-c0328dca6f16</t>
+  </si>
+  <si>
+    <t>07/12/2026 7:30:57 PM</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54455919-4a6b-5a7e-953e-abb12501decc</t>
+  </si>
+  <si>
+    <t>07/12/2026 5:59:51 PM</t>
+  </si>
+  <si>
+    <t>Light Traffic</t>
+  </si>
+  <si>
+    <t>I-10 Frontage Road, Winnie, TX, 77665</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544558c5-e2d0-5de9-9a2f-ae3344ea4f99</t>
+  </si>
+  <si>
+    <t>07/10/2026 10:31:38 PM</t>
+  </si>
+  <si>
+    <t>635 - Heavy</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454f71-fe0c-5725-9667-b70d246bba9a</t>
+  </si>
+  <si>
     <t>07/09/2026 8:14:20 PM</t>
   </si>
   <si>
-    <t>658 - Medium</t>
-  </si>
-  <si>
-    <t>Paul Kunze Jr</t>
-  </si>
-  <si>
-    <t>Active Drivers, Towing and Recovery</t>
-  </si>
-  <si>
-    <t>HAAS Alert, Towing and Recovery</t>
-  </si>
-  <si>
-    <t>Mobile Usage</t>
-  </si>
-  <si>
-    <t>Light Traffic</t>
-  </si>
-  <si>
-    <t>Needs Coaching</t>
-  </si>
-  <si>
-    <t>Tim Neff Jr.</t>
-  </si>
-  <si>
     <t>Martin Luther King Junior Parkway, Beaumont, TX, 77701</t>
   </si>
   <si>
     <t>40</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544549cd-f00d-52ad-bb3e-9c69ddab7b28</t>
   </si>
   <si>
@@ -107,18 +329,9 @@
     <t>646 - Medium</t>
   </si>
   <si>
-    <t>Heavy Speeding</t>
-  </si>
-  <si>
-    <t>Speed Sign Verified</t>
-  </si>
-  <si>
     <t>US 69;US 96;US 287, Beaumont, TX, 77710</t>
   </si>
   <si>
-    <t>85</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454977-71c3-5f5a-bf2e-b3c5aa74eb3b</t>
   </si>
   <si>
@@ -131,18 +344,12 @@
     <t>Juan Ramirez</t>
   </si>
   <si>
-    <t>HAAS Alert, Heavy Haul</t>
-  </si>
-  <si>
     <t>Rolling Stop</t>
   </si>
   <si>
     <t>Wet Road, Parking Lot, Light Traffic</t>
   </si>
   <si>
-    <t>Coached</t>
-  </si>
-  <si>
     <t>East Cardinal Drive, Beaumont, TX, 77710</t>
   </si>
   <si>
@@ -155,24 +362,6 @@
     <t>07/09/2026 8:25:14 AM</t>
   </si>
   <si>
-    <t>680 - Medium</t>
-  </si>
-  <si>
-    <t>Jesus Carbajal</t>
-  </si>
-  <si>
-    <t>Severe Speeding</t>
-  </si>
-  <si>
-    <t>I 10, Winnie, TX</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454744-bb1a-5daa-9bcb-7e498329e50f</t>
   </si>
   <si>
@@ -221,9 +410,6 @@
     <t>Adam Johnson</t>
   </si>
   <si>
-    <t>Active Drivers, Heavy Haul</t>
-  </si>
-  <si>
     <t>79</t>
   </si>
   <si>
@@ -245,54 +431,24 @@
     <t>Moderate Traffic</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54454247-8d4f-5875-9229-50054cf58c0e</t>
   </si>
   <si>
     <t>07/07/2026 10:08:17 PM</t>
   </si>
   <si>
-    <t>667 - Medium</t>
-  </si>
-  <si>
-    <t>Jeremy Myers</t>
-  </si>
-  <si>
-    <t>Towing and Recovery</t>
-  </si>
-  <si>
-    <t>US 69;US 287, Lumberton, TX, 77657</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453fe9-896a-5edb-bea5-59308595e899</t>
   </si>
   <si>
-    <t>07/07/2026 8:40:51 PM</t>
-  </si>
-  <si>
-    <t>625 - Heavy</t>
-  </si>
-  <si>
-    <t>I 10, 18.8 mi SE Liberty, Chambers County, TX</t>
+    <t>07/07/2026 8:21:33 PM</t>
+  </si>
+  <si>
+    <t>US Highway 90, Felicia, TX</t>
   </si>
   <si>
     <t>77</t>
   </si>
   <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453f99-7d2f-53e3-befe-f1791d246378</t>
-  </si>
-  <si>
-    <t>07/07/2026 8:21:33 PM</t>
-  </si>
-  <si>
-    <t>US Highway 90, Felicia, TX</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453f87-d216-5e0f-a6e4-fa3a620e8365</t>
   </si>
   <si>
@@ -329,9 +485,6 @@
     <t>Jonathan Walters</t>
   </si>
   <si>
-    <t>75</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54453f1e-3a9d-576e-965e-f8c65f3564b0</t>
   </si>
   <si>
@@ -398,12 +551,6 @@
     <t>07/03/2026 1:40:22 PM</t>
   </si>
   <si>
-    <t>669 - Heavy</t>
-  </si>
-  <si>
-    <t>Jason Walker</t>
-  </si>
-  <si>
     <t>No Seat Belt</t>
   </si>
   <si>
@@ -482,9 +629,6 @@
     <t>East Freeway, Channelview, TX, 77530</t>
   </si>
   <si>
-    <t>27</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54451ec0-085f-56a4-bd8c-a28cd6a152aa</t>
   </si>
   <si>
@@ -590,9 +734,6 @@
     <t>Gary Worley</t>
   </si>
   <si>
-    <t>Eddie Bowden</t>
-  </si>
-  <si>
     <t>US 90, China, TX, 77613</t>
   </si>
   <si>
@@ -623,9 +764,6 @@
     <t>US 69;US 96;US 287, Beaumont, TX, 77701</t>
   </si>
   <si>
-    <t>84</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544505a0-0548-52df-90bb-6baf18f84b57</t>
   </si>
   <si>
@@ -641,9 +779,6 @@
     <t>06/25/2026 3:46:02 PM</t>
   </si>
   <si>
-    <t>57</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544500bf-4275-5ded-85e2-3ee8f4e6d92b</t>
   </si>
   <si>
@@ -674,9 +809,6 @@
     <t>06/25/2026 9:09:43 AM</t>
   </si>
   <si>
-    <t>668 - Light</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ff54-6b07-5d1d-8dc0-8053502f47ef</t>
   </si>
   <si>
@@ -728,9 +860,6 @@
     <t>06/18/2026 3:34:01 PM</t>
   </si>
   <si>
-    <t>Obstructed Camera</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445dca7-bd7e-50f6-b2da-d0e7f3669228</t>
   </si>
   <si>
@@ -746,9 +875,6 @@
     <t>06/17/2026 4:02:17 PM</t>
   </si>
   <si>
-    <t>Dwayne Manuel</t>
-  </si>
-  <si>
     <t>H O Mills Highway, Port Arthur, TX</t>
   </si>
   <si>
@@ -962,9 +1088,6 @@
     <t>05/28/2026 3:24:20 PM</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54457079-5686-54e8-8a42-3ea1c6f860e5</t>
   </si>
   <si>
@@ -1133,9 +1256,6 @@
     <t>05/02/2026 6:49:16 AM</t>
   </si>
   <si>
-    <t>44</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445e8bc-6e70-5526-87d9-b05bb8910029</t>
   </si>
   <si>
@@ -1226,9 +1346,6 @@
     <t>State Highway 73, Winnie, TX, 77665</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445cb7c-286d-5c30-82b5-a900c5aaf727</t>
   </si>
   <si>
@@ -1296,102 +1413,6 @@
   </si>
   <si>
     <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445ab94-df4e-5e43-8f70-06189ab78268</t>
-  </si>
-  <si>
-    <t>04/18/2026 7:25:57 AM</t>
-  </si>
-  <si>
-    <t>I 10, Beaumont, TX, 77702</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445a0c4-fdcf-57c3-b241-7891a9a8e817</t>
-  </si>
-  <si>
-    <t>04/16/2026 10:41:19 AM</t>
-  </si>
-  <si>
-    <t>Eastex Freeway Frontage Road, Beaumont, TX, 77702</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=5445972b-2023-520b-9311-2aa79edade29</t>
-  </si>
-  <si>
-    <t>04/15/2026 10:09:32 AM</t>
-  </si>
-  <si>
-    <t>I 10;US 69;US 96;US 287, Beaumont, TX, 77702</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=544591e7-ac88-54d6-98a8-4bfe3fad16a5</t>
-  </si>
-  <si>
-    <t>04/14/2026 10:07:04 PM</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458f52-3b0b-50cb-bd6a-0400939c68f0</t>
-  </si>
-  <si>
-    <t>04/14/2026 4:40:17 PM</t>
-  </si>
-  <si>
-    <t>693 - Heavy</t>
-  </si>
-  <si>
-    <t>401 Northeast Evangeline Thruway, Lafayette, LA, 70501</t>
-  </si>
-  <si>
-    <t>0.58</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458e27-0eb3-5dba-85fd-a0dce64314bb</t>
-  </si>
-  <si>
-    <t>04/14/2026 4:19:07 PM</t>
-  </si>
-  <si>
-    <t>1193 US 90, Broussard, LA, 70518</t>
-  </si>
-  <si>
-    <t>0.65</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458e13-abfc-5546-ba17-feaf5efdc4dd</t>
-  </si>
-  <si>
-    <t>04/14/2026 10:46:08 AM</t>
-  </si>
-  <si>
-    <t>Eastex Freeway Frontage Road, Beaumont, TX, 77703</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458ce2-d409-5c3c-aecb-b998a858ebbd</t>
-  </si>
-  <si>
-    <t>04/13/2026 12:57:32 PM</t>
-  </si>
-  <si>
-    <t>21882 US 90, Nome, TX, 77713</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458834-c18f-5646-beeb-dec2a1a762b7</t>
-  </si>
-  <si>
-    <t>04/13/2026 9:43:50 AM</t>
-  </si>
-  <si>
-    <t>East Freeway, Houston, TX, 77020</t>
-  </si>
-  <si>
-    <t>https://cloud.samsara.com/o/60990/fleet/reports/safety/inbox_feed?selectedAggregationKey=event&amp;uuid=54458783-6b27-5c61-8273-549c16680488</t>
   </si>
 </sst>
 </file>
@@ -1768,7 +1789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O112"/>
+  <dimension ref="A1:O116"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
@@ -1853,30 +1874,30 @@
         <v>25</v>
       </c>
       <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2" t="s">
         <v>26</v>
-      </c>
-      <c r="M2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>29</v>
       </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
@@ -1891,7 +1912,7 @@
         <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J3" t="s">
         <v>32</v>
@@ -1900,83 +1921,83 @@
         <v>33</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="M3" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="N3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
         <v>18</v>
       </c>
       <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
         <v>38</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" t="s">
         <v>39</v>
       </c>
-      <c r="G4" t="s">
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O4" t="s">
         <v>40</v>
-      </c>
-      <c r="H4" t="s">
-        <v>41</v>
-      </c>
-      <c r="I4" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K4" t="s">
-        <v>43</v>
-      </c>
-      <c r="L4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O4" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s">
         <v>45</v>
       </c>
-      <c r="B5" t="s">
+      <c r="F5" t="s">
         <v>46</v>
-      </c>
-      <c r="C5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>48</v>
       </c>
       <c r="G5" t="s">
         <v>31</v>
@@ -1988,33 +2009,33 @@
         <v>23</v>
       </c>
       <c r="J5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="K5" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="L5" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="M5" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="N5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
@@ -2023,10 +2044,10 @@
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H6" t="s">
         <v>22</v>
@@ -2035,89 +2056,89 @@
         <v>23</v>
       </c>
       <c r="J6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="L6" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="M6" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="N6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" t="s">
         <v>58</v>
       </c>
-      <c r="H7" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>59</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7" t="s">
         <v>60</v>
-      </c>
-      <c r="L7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" t="s">
-        <v>61</v>
-      </c>
-      <c r="O7" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" t="s">
         <v>63</v>
       </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G8" t="s">
         <v>31</v>
@@ -2126,45 +2147,45 @@
         <v>22</v>
       </c>
       <c r="I8" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="J8" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="K8" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="L8" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="M8" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="N8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G9" t="s">
         <v>31</v>
@@ -2176,19 +2197,19 @@
         <v>23</v>
       </c>
       <c r="J9" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="K9" t="s">
         <v>69</v>
       </c>
       <c r="L9" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M9" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N9" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O9" t="s">
         <v>70</v>
@@ -2199,10 +2220,10 @@
         <v>71</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
@@ -2211,142 +2232,142 @@
         <v>19</v>
       </c>
       <c r="F10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" t="s">
+        <v>72</v>
+      </c>
+      <c r="K10" t="s">
+        <v>73</v>
+      </c>
+      <c r="L10" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" t="s">
+        <v>21</v>
+      </c>
+      <c r="O10" t="s">
         <v>74</v>
-      </c>
-      <c r="G10" t="s">
-        <v>75</v>
-      </c>
-      <c r="H10" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" t="s">
-        <v>49</v>
-      </c>
-      <c r="K10" t="s">
-        <v>76</v>
-      </c>
-      <c r="L10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O10" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" t="s">
         <v>78</v>
       </c>
-      <c r="B11" t="s">
+      <c r="K11" t="s">
         <v>79</v>
       </c>
-      <c r="C11" t="s">
+      <c r="L11" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" t="s">
+        <v>21</v>
+      </c>
+      <c r="O11" t="s">
         <v>80</v>
-      </c>
-      <c r="D11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" t="s">
-        <v>31</v>
-      </c>
-      <c r="H11" t="s">
-        <v>41</v>
-      </c>
-      <c r="I11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J11" t="s">
-        <v>82</v>
-      </c>
-      <c r="K11" t="s">
-        <v>83</v>
-      </c>
-      <c r="L11" t="s">
-        <v>26</v>
-      </c>
-      <c r="M11" t="s">
-        <v>26</v>
-      </c>
-      <c r="N11" t="s">
-        <v>26</v>
-      </c>
-      <c r="O11" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" t="s">
+        <v>84</v>
+      </c>
+      <c r="K12" t="s">
+        <v>51</v>
+      </c>
+      <c r="L12" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N12" t="s">
+        <v>21</v>
+      </c>
+      <c r="O12" t="s">
         <v>85</v>
-      </c>
-      <c r="B12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J12" t="s">
-        <v>87</v>
-      </c>
-      <c r="K12" t="s">
-        <v>88</v>
-      </c>
-      <c r="L12" t="s">
-        <v>26</v>
-      </c>
-      <c r="M12" t="s">
-        <v>26</v>
-      </c>
-      <c r="N12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O12" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E13" t="s">
         <v>19</v>
@@ -2361,30 +2382,30 @@
         <v>22</v>
       </c>
       <c r="I13" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J13" t="s">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="K13" t="s">
+        <v>87</v>
+      </c>
+      <c r="L13" t="s">
+        <v>34</v>
+      </c>
+      <c r="M13" t="s">
+        <v>35</v>
+      </c>
+      <c r="N13" t="s">
+        <v>21</v>
+      </c>
+      <c r="O13" t="s">
         <v>88</v>
-      </c>
-      <c r="L13" t="s">
-        <v>26</v>
-      </c>
-      <c r="M13" t="s">
-        <v>26</v>
-      </c>
-      <c r="N13" t="s">
-        <v>26</v>
-      </c>
-      <c r="O13" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B14" t="s">
         <v>16</v>
@@ -2402,7 +2423,7 @@
         <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H14" t="s">
         <v>22</v>
@@ -2411,227 +2432,227 @@
         <v>23</v>
       </c>
       <c r="J14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="K14" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="L14" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M14" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N14" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O14" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" t="s">
+        <v>96</v>
+      </c>
+      <c r="L15" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" t="s">
+        <v>21</v>
+      </c>
+      <c r="O15" t="s">
         <v>97</v>
-      </c>
-      <c r="B15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" t="s">
-        <v>98</v>
-      </c>
-      <c r="H15" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" t="s">
-        <v>23</v>
-      </c>
-      <c r="J15" t="s">
-        <v>82</v>
-      </c>
-      <c r="K15" t="s">
-        <v>99</v>
-      </c>
-      <c r="L15" t="s">
-        <v>26</v>
-      </c>
-      <c r="M15" t="s">
-        <v>26</v>
-      </c>
-      <c r="N15" t="s">
-        <v>26</v>
-      </c>
-      <c r="O15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" t="s">
+        <v>99</v>
+      </c>
+      <c r="K16" t="s">
+        <v>100</v>
+      </c>
+      <c r="L16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" t="s">
+        <v>21</v>
+      </c>
+      <c r="O16" t="s">
         <v>101</v>
-      </c>
-      <c r="B16" t="s">
-        <v>102</v>
-      </c>
-      <c r="C16" t="s">
-        <v>103</v>
-      </c>
-      <c r="D16" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16" t="s">
-        <v>38</v>
-      </c>
-      <c r="F16" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" t="s">
-        <v>41</v>
-      </c>
-      <c r="I16" t="s">
-        <v>26</v>
-      </c>
-      <c r="J16" t="s">
-        <v>49</v>
-      </c>
-      <c r="K16" t="s">
-        <v>104</v>
-      </c>
-      <c r="L16" t="s">
-        <v>26</v>
-      </c>
-      <c r="M16" t="s">
-        <v>26</v>
-      </c>
-      <c r="N16" t="s">
-        <v>26</v>
-      </c>
-      <c r="O16" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G17" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H17" t="s">
         <v>22</v>
       </c>
       <c r="I17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J17" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="K17" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="L17" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M17" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N17" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O17" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
       </c>
       <c r="E18" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>30</v>
+        <v>109</v>
       </c>
       <c r="G18" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="H18" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="I18" t="s">
         <v>23</v>
       </c>
       <c r="J18" t="s">
+        <v>111</v>
+      </c>
+      <c r="K18" t="s">
+        <v>112</v>
+      </c>
+      <c r="L18" t="s">
+        <v>21</v>
+      </c>
+      <c r="M18" t="s">
+        <v>21</v>
+      </c>
+      <c r="N18" t="s">
+        <v>21</v>
+      </c>
+      <c r="O18" t="s">
         <v>113</v>
-      </c>
-      <c r="K18" t="s">
-        <v>33</v>
-      </c>
-      <c r="L18" t="s">
-        <v>26</v>
-      </c>
-      <c r="M18" t="s">
-        <v>26</v>
-      </c>
-      <c r="N18" t="s">
-        <v>26</v>
-      </c>
-      <c r="O18" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F19" t="s">
         <v>30</v>
@@ -2640,39 +2661,39 @@
         <v>31</v>
       </c>
       <c r="H19" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J19" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="K19" t="s">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="L19" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="M19" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="N19" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O19" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
@@ -2693,33 +2714,33 @@
         <v>23</v>
       </c>
       <c r="J20" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="K20" t="s">
-        <v>121</v>
+        <v>33</v>
       </c>
       <c r="L20" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="M20" t="s">
-        <v>26</v>
+        <v>118</v>
       </c>
       <c r="N20" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O20" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
@@ -2728,10 +2749,10 @@
         <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G21" t="s">
-        <v>31</v>
+        <v>121</v>
       </c>
       <c r="H21" t="s">
         <v>22</v>
@@ -2740,19 +2761,19 @@
         <v>23</v>
       </c>
       <c r="J21" t="s">
+        <v>122</v>
+      </c>
+      <c r="K21" t="s">
+        <v>123</v>
+      </c>
+      <c r="L21" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N21" t="s">
         <v>124</v>
-      </c>
-      <c r="K21" t="s">
-        <v>104</v>
-      </c>
-      <c r="L21" t="s">
-        <v>26</v>
-      </c>
-      <c r="M21" t="s">
-        <v>26</v>
-      </c>
-      <c r="N21" t="s">
-        <v>26</v>
       </c>
       <c r="O21" t="s">
         <v>125</v>
@@ -2763,66 +2784,66 @@
         <v>126</v>
       </c>
       <c r="B22" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s">
+        <v>32</v>
+      </c>
+      <c r="K22" t="s">
+        <v>33</v>
+      </c>
+      <c r="L22" t="s">
+        <v>34</v>
+      </c>
+      <c r="M22" t="s">
+        <v>35</v>
+      </c>
+      <c r="N22" t="s">
+        <v>21</v>
+      </c>
+      <c r="O22" t="s">
         <v>127</v>
-      </c>
-      <c r="C22" t="s">
-        <v>128</v>
-      </c>
-      <c r="D22" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" t="s">
-        <v>129</v>
-      </c>
-      <c r="G22" t="s">
-        <v>21</v>
-      </c>
-      <c r="H22" t="s">
-        <v>22</v>
-      </c>
-      <c r="I22" t="s">
-        <v>23</v>
-      </c>
-      <c r="J22" t="s">
-        <v>130</v>
-      </c>
-      <c r="K22" t="s">
-        <v>131</v>
-      </c>
-      <c r="L22" t="s">
-        <v>26</v>
-      </c>
-      <c r="M22" t="s">
-        <v>26</v>
-      </c>
-      <c r="N22" t="s">
-        <v>26</v>
-      </c>
-      <c r="O22" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="D23" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G23" t="s">
         <v>31</v>
@@ -2834,174 +2855,174 @@
         <v>23</v>
       </c>
       <c r="J23" t="s">
-        <v>134</v>
+        <v>32</v>
       </c>
       <c r="K23" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L23" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M23" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N23" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O23" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B24" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C24" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
       </c>
       <c r="E24" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>30</v>
+        <v>136</v>
       </c>
       <c r="G24" t="s">
-        <v>31</v>
+        <v>137</v>
       </c>
       <c r="H24" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I24" t="s">
         <v>23</v>
       </c>
       <c r="J24" t="s">
-        <v>140</v>
+        <v>32</v>
       </c>
       <c r="K24" t="s">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="L24" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M24" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N24" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O24" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B25" t="s">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>128</v>
+        <v>55</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="E25" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G25" t="s">
-        <v>144</v>
+        <v>31</v>
       </c>
       <c r="H25" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="I25" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J25" t="s">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="K25" t="s">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="L25" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M25" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N25" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O25" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="D26" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="E26" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F26" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="H26" t="s">
         <v>22</v>
       </c>
       <c r="I26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J26" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K26" t="s">
-        <v>76</v>
+        <v>143</v>
       </c>
       <c r="L26" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M26" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N26" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O26" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B27" t="s">
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
@@ -3013,42 +3034,42 @@
         <v>20</v>
       </c>
       <c r="G27" t="s">
-        <v>75</v>
+        <v>146</v>
       </c>
       <c r="H27" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I27" t="s">
-        <v>153</v>
+        <v>23</v>
       </c>
       <c r="J27" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="K27" t="s">
-        <v>155</v>
+        <v>25</v>
       </c>
       <c r="L27" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M27" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N27" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O27" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C28" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -3060,7 +3081,7 @@
         <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="H28" t="s">
         <v>22</v>
@@ -3069,92 +3090,92 @@
         <v>23</v>
       </c>
       <c r="J28" t="s">
-        <v>159</v>
+        <v>58</v>
       </c>
       <c r="K28" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="L28" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M28" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N28" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O28" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B29" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="C29" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="D29" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="E29" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F29" t="s">
-        <v>129</v>
+        <v>46</v>
       </c>
       <c r="G29" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H29" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="I29" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J29" t="s">
-        <v>162</v>
+        <v>32</v>
       </c>
       <c r="K29" t="s">
-        <v>163</v>
+        <v>96</v>
       </c>
       <c r="L29" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M29" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N29" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O29" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B30" t="s">
-        <v>107</v>
+        <v>158</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>159</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
       </c>
       <c r="E30" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F30" t="s">
         <v>20</v>
       </c>
       <c r="G30" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s">
         <v>22</v>
@@ -3163,127 +3184,127 @@
         <v>23</v>
       </c>
       <c r="J30" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="K30" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="L30" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M30" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N30" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O30" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="D31" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>170</v>
+        <v>46</v>
       </c>
       <c r="G31" t="s">
-        <v>171</v>
+        <v>31</v>
       </c>
       <c r="H31" t="s">
         <v>22</v>
       </c>
       <c r="I31" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J31" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="K31" t="s">
-        <v>173</v>
+        <v>33</v>
       </c>
       <c r="L31" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M31" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N31" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O31" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B32" t="s">
+        <v>167</v>
+      </c>
+      <c r="C32" t="s">
+        <v>168</v>
+      </c>
+      <c r="D32" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" t="s">
+        <v>45</v>
+      </c>
+      <c r="F32" t="s">
         <v>46</v>
-      </c>
-      <c r="C32" t="s">
-        <v>47</v>
-      </c>
-      <c r="D32" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" t="s">
-        <v>19</v>
-      </c>
-      <c r="F32" t="s">
-        <v>48</v>
       </c>
       <c r="G32" t="s">
         <v>31</v>
       </c>
       <c r="H32" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="I32" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J32" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="K32" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="L32" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="M32" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="N32" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O32" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B33" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" t="s">
         <v>29</v>
-      </c>
-      <c r="C33" t="s">
-        <v>139</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
@@ -3292,10 +3313,10 @@
         <v>19</v>
       </c>
       <c r="F33" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G33" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H33" t="s">
         <v>22</v>
@@ -3304,45 +3325,45 @@
         <v>23</v>
       </c>
       <c r="J33" t="s">
-        <v>179</v>
+        <v>32</v>
       </c>
       <c r="K33" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="L33" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M33" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N33" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O33" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="B34" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="C34" t="s">
-        <v>128</v>
+        <v>29</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
       </c>
       <c r="E34" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F34" t="s">
-        <v>129</v>
+        <v>46</v>
       </c>
       <c r="G34" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="H34" t="s">
         <v>22</v>
@@ -3351,186 +3372,186 @@
         <v>23</v>
       </c>
       <c r="J34" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="K34" t="s">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="L34" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M34" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N34" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O34" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C35" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D35" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="E35" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F35" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="G35" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s">
         <v>22</v>
       </c>
       <c r="I35" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J35" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="K35" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="L35" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M35" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N35" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O35" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B36" t="s">
-        <v>102</v>
+        <v>158</v>
       </c>
       <c r="C36" t="s">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="D36" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="E36" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F36" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G36" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H36" t="s">
         <v>22</v>
       </c>
       <c r="I36" t="s">
-        <v>191</v>
+        <v>23</v>
       </c>
       <c r="J36" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="K36" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="L36" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M36" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N36" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O36" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B37" t="s">
-        <v>72</v>
+        <v>187</v>
       </c>
       <c r="C37" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
       </c>
       <c r="E37" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F37" t="s">
-        <v>196</v>
+        <v>46</v>
       </c>
       <c r="G37" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="H37" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="I37" t="s">
         <v>23</v>
       </c>
       <c r="J37" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="K37" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="L37" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M37" t="s">
-        <v>198</v>
+        <v>21</v>
       </c>
       <c r="N37" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O37" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C38" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
       </c>
       <c r="E38" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F38" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G38" t="s">
-        <v>31</v>
+        <v>193</v>
       </c>
       <c r="H38" t="s">
         <v>22</v>
@@ -3539,45 +3560,45 @@
         <v>23</v>
       </c>
       <c r="J38" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="K38" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="L38" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M38" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N38" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O38" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B39" t="s">
-        <v>72</v>
+        <v>129</v>
       </c>
       <c r="C39" t="s">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="D39" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="E39" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F39" t="s">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="G39" t="s">
-        <v>58</v>
+        <v>137</v>
       </c>
       <c r="H39" t="s">
         <v>22</v>
@@ -3586,80 +3607,80 @@
         <v>23</v>
       </c>
       <c r="J39" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="K39" t="s">
-        <v>205</v>
+        <v>25</v>
       </c>
       <c r="L39" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M39" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N39" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O39" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="B40" t="s">
-        <v>138</v>
+        <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>26</v>
+        <v>201</v>
       </c>
       <c r="D40" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E40" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F40" t="s">
         <v>20</v>
       </c>
       <c r="G40" t="s">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="H40" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="I40" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="J40" t="s">
-        <v>109</v>
+        <v>203</v>
       </c>
       <c r="K40" t="s">
-        <v>208</v>
+        <v>51</v>
       </c>
       <c r="L40" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M40" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N40" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O40" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B41" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C41" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
@@ -3668,10 +3689,10 @@
         <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G41" t="s">
-        <v>31</v>
+        <v>206</v>
       </c>
       <c r="H41" t="s">
         <v>22</v>
@@ -3680,45 +3701,45 @@
         <v>23</v>
       </c>
       <c r="J41" t="s">
-        <v>49</v>
+        <v>207</v>
       </c>
       <c r="K41" t="s">
-        <v>211</v>
+        <v>51</v>
       </c>
       <c r="L41" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M41" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N41" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O41" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C42" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
       </c>
       <c r="E42" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F42" t="s">
-        <v>214</v>
+        <v>178</v>
       </c>
       <c r="G42" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s">
         <v>22</v>
@@ -3727,127 +3748,127 @@
         <v>23</v>
       </c>
       <c r="J42" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K42" t="s">
-        <v>54</v>
+        <v>211</v>
       </c>
       <c r="L42" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M42" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N42" t="s">
-        <v>216</v>
+        <v>21</v>
       </c>
       <c r="O42" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B43" t="s">
-        <v>219</v>
+        <v>158</v>
       </c>
       <c r="C43" t="s">
-        <v>26</v>
+        <v>159</v>
       </c>
       <c r="D43" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E43" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F43" t="s">
         <v>20</v>
       </c>
       <c r="G43" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="H43" t="s">
         <v>22</v>
       </c>
       <c r="I43" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J43" t="s">
-        <v>109</v>
+        <v>214</v>
       </c>
       <c r="K43" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="L43" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M43" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N43" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O43" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>217</v>
+      </c>
+      <c r="B44" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" t="s">
+        <v>55</v>
+      </c>
+      <c r="D44" t="s">
+        <v>56</v>
+      </c>
+      <c r="E44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" t="s">
+        <v>218</v>
+      </c>
+      <c r="G44" t="s">
+        <v>219</v>
+      </c>
+      <c r="H44" t="s">
+        <v>22</v>
+      </c>
+      <c r="I44" t="s">
+        <v>21</v>
+      </c>
+      <c r="J44" t="s">
+        <v>220</v>
+      </c>
+      <c r="K44" t="s">
         <v>221</v>
       </c>
-      <c r="B44" t="s">
-        <v>127</v>
-      </c>
-      <c r="C44" t="s">
-        <v>128</v>
-      </c>
-      <c r="D44" t="s">
-        <v>18</v>
-      </c>
-      <c r="E44" t="s">
-        <v>38</v>
-      </c>
-      <c r="F44" t="s">
-        <v>74</v>
-      </c>
-      <c r="G44" t="s">
-        <v>75</v>
-      </c>
-      <c r="H44" t="s">
-        <v>22</v>
-      </c>
-      <c r="I44" t="s">
-        <v>23</v>
-      </c>
-      <c r="J44" t="s">
-        <v>113</v>
-      </c>
-      <c r="K44" t="s">
+      <c r="L44" t="s">
+        <v>21</v>
+      </c>
+      <c r="M44" t="s">
+        <v>21</v>
+      </c>
+      <c r="N44" t="s">
+        <v>21</v>
+      </c>
+      <c r="O44" t="s">
         <v>222</v>
-      </c>
-      <c r="L44" t="s">
-        <v>26</v>
-      </c>
-      <c r="M44" t="s">
-        <v>26</v>
-      </c>
-      <c r="N44" t="s">
-        <v>26</v>
-      </c>
-      <c r="O44" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B45" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C45" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
@@ -3856,10 +3877,10 @@
         <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>214</v>
+        <v>30</v>
       </c>
       <c r="G45" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H45" t="s">
         <v>22</v>
@@ -3868,92 +3889,92 @@
         <v>23</v>
       </c>
       <c r="J45" t="s">
+        <v>224</v>
+      </c>
+      <c r="K45" t="s">
+        <v>33</v>
+      </c>
+      <c r="L45" t="s">
+        <v>117</v>
+      </c>
+      <c r="M45" t="s">
+        <v>118</v>
+      </c>
+      <c r="N45" t="s">
+        <v>21</v>
+      </c>
+      <c r="O45" t="s">
         <v>225</v>
-      </c>
-      <c r="K45" t="s">
-        <v>226</v>
-      </c>
-      <c r="L45" t="s">
-        <v>26</v>
-      </c>
-      <c r="M45" t="s">
-        <v>26</v>
-      </c>
-      <c r="N45" t="s">
-        <v>227</v>
-      </c>
-      <c r="O45" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>226</v>
+      </c>
+      <c r="B46" t="s">
+        <v>103</v>
+      </c>
+      <c r="C46" t="s">
+        <v>188</v>
+      </c>
+      <c r="D46" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" t="s">
+        <v>136</v>
+      </c>
+      <c r="G46" t="s">
+        <v>90</v>
+      </c>
+      <c r="H46" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" t="s">
+        <v>23</v>
+      </c>
+      <c r="J46" t="s">
+        <v>227</v>
+      </c>
+      <c r="K46" t="s">
+        <v>228</v>
+      </c>
+      <c r="L46" t="s">
+        <v>21</v>
+      </c>
+      <c r="M46" t="s">
+        <v>21</v>
+      </c>
+      <c r="N46" t="s">
+        <v>21</v>
+      </c>
+      <c r="O46" t="s">
         <v>229</v>
-      </c>
-      <c r="B46" t="s">
-        <v>230</v>
-      </c>
-      <c r="C46" t="s">
-        <v>231</v>
-      </c>
-      <c r="D46" t="s">
-        <v>68</v>
-      </c>
-      <c r="E46" t="s">
-        <v>38</v>
-      </c>
-      <c r="F46" t="s">
-        <v>74</v>
-      </c>
-      <c r="G46" t="s">
-        <v>75</v>
-      </c>
-      <c r="H46" t="s">
-        <v>41</v>
-      </c>
-      <c r="I46" t="s">
-        <v>23</v>
-      </c>
-      <c r="J46" t="s">
-        <v>232</v>
-      </c>
-      <c r="K46" t="s">
-        <v>83</v>
-      </c>
-      <c r="L46" t="s">
-        <v>26</v>
-      </c>
-      <c r="M46" t="s">
-        <v>26</v>
-      </c>
-      <c r="N46" t="s">
-        <v>26</v>
-      </c>
-      <c r="O46" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B47" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="C47" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
       </c>
       <c r="E47" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F47" t="s">
-        <v>20</v>
+        <v>178</v>
       </c>
       <c r="G47" t="s">
-        <v>21</v>
+        <v>121</v>
       </c>
       <c r="H47" t="s">
         <v>22</v>
@@ -3962,113 +3983,113 @@
         <v>23</v>
       </c>
       <c r="J47" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="K47" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="L47" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M47" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N47" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O47" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B48" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C48" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D48" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="E48" t="s">
         <v>19</v>
       </c>
       <c r="F48" t="s">
-        <v>237</v>
+        <v>178</v>
       </c>
       <c r="G48" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s">
         <v>22</v>
       </c>
       <c r="I48" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J48" t="s">
-        <v>59</v>
+        <v>234</v>
       </c>
       <c r="K48" t="s">
-        <v>25</v>
+        <v>235</v>
       </c>
       <c r="L48" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M48" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N48" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O48" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>237</v>
+      </c>
+      <c r="B49" t="s">
+        <v>154</v>
+      </c>
+      <c r="C49" t="s">
+        <v>238</v>
+      </c>
+      <c r="D49" t="s">
+        <v>44</v>
+      </c>
+      <c r="E49" t="s">
+        <v>45</v>
+      </c>
+      <c r="F49" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" t="s">
+        <v>90</v>
+      </c>
+      <c r="H49" t="s">
+        <v>22</v>
+      </c>
+      <c r="I49" t="s">
+        <v>64</v>
+      </c>
+      <c r="J49" t="s">
         <v>239</v>
       </c>
-      <c r="B49" t="s">
-        <v>72</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="K49" t="s">
         <v>240</v>
       </c>
-      <c r="D49" t="s">
-        <v>81</v>
-      </c>
-      <c r="E49" t="s">
-        <v>19</v>
-      </c>
-      <c r="F49" t="s">
-        <v>48</v>
-      </c>
-      <c r="G49" t="s">
-        <v>31</v>
-      </c>
-      <c r="H49" t="s">
-        <v>22</v>
-      </c>
-      <c r="I49" t="s">
-        <v>26</v>
-      </c>
-      <c r="J49" t="s">
-        <v>49</v>
-      </c>
-      <c r="K49" t="s">
-        <v>33</v>
-      </c>
       <c r="L49" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="M49" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="N49" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O49" t="s">
         <v>241</v>
@@ -4079,57 +4100,57 @@
         <v>242</v>
       </c>
       <c r="B50" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="C50" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50" t="s">
+        <v>19</v>
+      </c>
+      <c r="F50" t="s">
         <v>243</v>
       </c>
-      <c r="D50" t="s">
-        <v>68</v>
-      </c>
-      <c r="E50" t="s">
-        <v>38</v>
-      </c>
-      <c r="F50" t="s">
-        <v>20</v>
-      </c>
       <c r="G50" t="s">
-        <v>21</v>
+        <v>121</v>
       </c>
       <c r="H50" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I50" t="s">
         <v>23</v>
       </c>
       <c r="J50" t="s">
+        <v>214</v>
+      </c>
+      <c r="K50" t="s">
         <v>244</v>
       </c>
-      <c r="K50" t="s">
-        <v>163</v>
-      </c>
       <c r="L50" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M50" t="s">
-        <v>26</v>
+        <v>245</v>
       </c>
       <c r="N50" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O50" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B51" t="s">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="C51" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
@@ -4138,10 +4159,10 @@
         <v>19</v>
       </c>
       <c r="F51" t="s">
-        <v>196</v>
+        <v>46</v>
       </c>
       <c r="G51" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H51" t="s">
         <v>22</v>
@@ -4150,19 +4171,19 @@
         <v>23</v>
       </c>
       <c r="J51" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K51" t="s">
-        <v>248</v>
+        <v>87</v>
       </c>
       <c r="L51" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M51" t="s">
-        <v>198</v>
+        <v>21</v>
       </c>
       <c r="N51" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O51" t="s">
         <v>249</v>
@@ -4173,10 +4194,10 @@
         <v>250</v>
       </c>
       <c r="B52" t="s">
-        <v>46</v>
+        <v>134</v>
       </c>
       <c r="C52" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
@@ -4188,7 +4209,7 @@
         <v>20</v>
       </c>
       <c r="G52" t="s">
-        <v>21</v>
+        <v>121</v>
       </c>
       <c r="H52" t="s">
         <v>22</v>
@@ -4197,19 +4218,19 @@
         <v>23</v>
       </c>
       <c r="J52" t="s">
+        <v>214</v>
+      </c>
+      <c r="K52" t="s">
         <v>251</v>
       </c>
-      <c r="K52" t="s">
-        <v>146</v>
-      </c>
       <c r="L52" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M52" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N52" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O52" t="s">
         <v>252</v>
@@ -4220,104 +4241,104 @@
         <v>253</v>
       </c>
       <c r="B53" t="s">
-        <v>127</v>
+        <v>187</v>
       </c>
       <c r="C53" t="s">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="D53" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E53" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F53" t="s">
         <v>20</v>
       </c>
       <c r="G53" t="s">
+        <v>90</v>
+      </c>
+      <c r="H53" t="s">
+        <v>22</v>
+      </c>
+      <c r="I53" t="s">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s">
+        <v>160</v>
+      </c>
+      <c r="K53" t="s">
+        <v>69</v>
+      </c>
+      <c r="L53" t="s">
+        <v>21</v>
+      </c>
+      <c r="M53" t="s">
+        <v>21</v>
+      </c>
+      <c r="N53" t="s">
+        <v>21</v>
+      </c>
+      <c r="O53" t="s">
         <v>254</v>
-      </c>
-      <c r="H53" t="s">
-        <v>22</v>
-      </c>
-      <c r="I53" t="s">
-        <v>23</v>
-      </c>
-      <c r="J53" t="s">
-        <v>255</v>
-      </c>
-      <c r="K53" t="s">
-        <v>256</v>
-      </c>
-      <c r="L53" t="s">
-        <v>26</v>
-      </c>
-      <c r="M53" t="s">
-        <v>26</v>
-      </c>
-      <c r="N53" t="s">
-        <v>26</v>
-      </c>
-      <c r="O53" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B54" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="C54" t="s">
-        <v>240</v>
+        <v>29</v>
       </c>
       <c r="D54" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="E54" t="s">
         <v>19</v>
       </c>
       <c r="F54" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="G54" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H54" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I54" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J54" t="s">
-        <v>259</v>
+        <v>32</v>
       </c>
       <c r="K54" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="L54" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M54" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N54" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O54" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B55" t="s">
-        <v>263</v>
+        <v>28</v>
       </c>
       <c r="C55" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D55" t="s">
         <v>18</v>
@@ -4326,10 +4347,10 @@
         <v>19</v>
       </c>
       <c r="F55" t="s">
-        <v>20</v>
+        <v>259</v>
       </c>
       <c r="G55" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s">
         <v>22</v>
@@ -4338,160 +4359,160 @@
         <v>23</v>
       </c>
       <c r="J55" t="s">
-        <v>109</v>
+        <v>260</v>
       </c>
       <c r="K55" t="s">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="L55" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M55" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N55" t="s">
-        <v>26</v>
+        <v>261</v>
       </c>
       <c r="O55" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B56" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="C56" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D56" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E56" t="s">
         <v>19</v>
       </c>
       <c r="F56" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="G56" t="s">
-        <v>26</v>
+        <v>193</v>
       </c>
       <c r="H56" t="s">
         <v>22</v>
       </c>
       <c r="I56" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J56" t="s">
-        <v>266</v>
+        <v>160</v>
       </c>
       <c r="K56" t="s">
-        <v>33</v>
+        <v>244</v>
       </c>
       <c r="L56" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="M56" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="N56" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O56" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B57" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C57" t="s">
-        <v>240</v>
+        <v>77</v>
       </c>
       <c r="D57" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="E57" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F57" t="s">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="G57" t="s">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="H57" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I57" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J57" t="s">
-        <v>269</v>
+        <v>164</v>
       </c>
       <c r="K57" t="s">
-        <v>25</v>
+        <v>266</v>
       </c>
       <c r="L57" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M57" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N57" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O57" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B58" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="C58" t="s">
-        <v>240</v>
+        <v>29</v>
       </c>
       <c r="D58" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="E58" t="s">
         <v>19</v>
       </c>
       <c r="F58" t="s">
-        <v>196</v>
+        <v>259</v>
       </c>
       <c r="G58" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="H58" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I58" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J58" t="s">
-        <v>154</v>
+        <v>269</v>
       </c>
       <c r="K58" t="s">
-        <v>208</v>
+        <v>270</v>
       </c>
       <c r="L58" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M58" t="s">
-        <v>198</v>
+        <v>21</v>
       </c>
       <c r="N58" t="s">
-        <v>26</v>
+        <v>271</v>
       </c>
       <c r="O58" t="s">
         <v>272</v>
@@ -4502,57 +4523,57 @@
         <v>273</v>
       </c>
       <c r="B59" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="C59" t="s">
-        <v>17</v>
+        <v>275</v>
       </c>
       <c r="D59" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="E59" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F59" t="s">
-        <v>20</v>
+        <v>136</v>
       </c>
       <c r="G59" t="s">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="H59" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="I59" t="s">
         <v>23</v>
       </c>
       <c r="J59" t="s">
-        <v>183</v>
+        <v>276</v>
       </c>
       <c r="K59" t="s">
-        <v>187</v>
+        <v>59</v>
       </c>
       <c r="L59" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M59" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N59" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O59" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B60" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="C60" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="D60" t="s">
         <v>18</v>
@@ -4561,10 +4582,10 @@
         <v>19</v>
       </c>
       <c r="F60" t="s">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="G60" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="H60" t="s">
         <v>22</v>
@@ -4573,33 +4594,33 @@
         <v>23</v>
       </c>
       <c r="J60" t="s">
-        <v>276</v>
+        <v>248</v>
       </c>
       <c r="K60" t="s">
-        <v>146</v>
+        <v>215</v>
       </c>
       <c r="L60" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M60" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N60" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O60" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B61" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C61" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D61" t="s">
         <v>18</v>
@@ -4608,10 +4629,10 @@
         <v>19</v>
       </c>
       <c r="F61" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G61" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H61" t="s">
         <v>22</v>
@@ -4620,42 +4641,42 @@
         <v>23</v>
       </c>
       <c r="J61" t="s">
-        <v>279</v>
+        <v>122</v>
       </c>
       <c r="K61" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="L61" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="M61" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="N61" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O61" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B62" t="s">
-        <v>263</v>
+        <v>134</v>
       </c>
       <c r="C62" t="s">
-        <v>26</v>
+        <v>283</v>
       </c>
       <c r="D62" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="E62" t="s">
         <v>19</v>
       </c>
       <c r="F62" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="G62" t="s">
         <v>31</v>
@@ -4664,83 +4685,83 @@
         <v>22</v>
       </c>
       <c r="I62" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J62" t="s">
-        <v>166</v>
+        <v>32</v>
       </c>
       <c r="K62" t="s">
         <v>33</v>
       </c>
       <c r="L62" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="M62" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="N62" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O62" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B63" t="s">
-        <v>46</v>
+        <v>154</v>
       </c>
       <c r="C63" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D63" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="E63" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F63" t="s">
-        <v>170</v>
+        <v>20</v>
       </c>
       <c r="G63" t="s">
-        <v>284</v>
+        <v>90</v>
       </c>
       <c r="H63" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="I63" t="s">
         <v>23</v>
       </c>
       <c r="J63" t="s">
-        <v>109</v>
+        <v>286</v>
       </c>
       <c r="K63" t="s">
-        <v>248</v>
+        <v>211</v>
       </c>
       <c r="L63" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M63" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N63" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O63" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B64" t="s">
-        <v>46</v>
+        <v>134</v>
       </c>
       <c r="C64" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D64" t="s">
         <v>18</v>
@@ -4749,10 +4770,10 @@
         <v>19</v>
       </c>
       <c r="F64" t="s">
-        <v>48</v>
+        <v>243</v>
       </c>
       <c r="G64" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="H64" t="s">
         <v>22</v>
@@ -4761,45 +4782,45 @@
         <v>23</v>
       </c>
       <c r="J64" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K64" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L64" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="M64" t="s">
-        <v>51</v>
+        <v>245</v>
       </c>
       <c r="N64" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O64" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B65" t="s">
-        <v>107</v>
+        <v>28</v>
       </c>
       <c r="C65" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="D65" t="s">
         <v>18</v>
       </c>
       <c r="E65" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F65" t="s">
         <v>20</v>
       </c>
       <c r="G65" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="H65" t="s">
         <v>22</v>
@@ -4808,66 +4829,66 @@
         <v>23</v>
       </c>
       <c r="J65" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K65" t="s">
-        <v>292</v>
+        <v>195</v>
       </c>
       <c r="L65" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M65" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N65" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O65" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B66" t="s">
-        <v>295</v>
+        <v>76</v>
       </c>
       <c r="C66" t="s">
+        <v>77</v>
+      </c>
+      <c r="D66" t="s">
+        <v>18</v>
+      </c>
+      <c r="E66" t="s">
+        <v>45</v>
+      </c>
+      <c r="F66" t="s">
+        <v>20</v>
+      </c>
+      <c r="G66" t="s">
         <v>296</v>
       </c>
-      <c r="D66" t="s">
+      <c r="H66" t="s">
+        <v>22</v>
+      </c>
+      <c r="I66" t="s">
+        <v>23</v>
+      </c>
+      <c r="J66" t="s">
         <v>297</v>
       </c>
-      <c r="E66" t="s">
-        <v>38</v>
-      </c>
-      <c r="F66" t="s">
-        <v>74</v>
-      </c>
-      <c r="G66" t="s">
-        <v>75</v>
-      </c>
-      <c r="H66" t="s">
-        <v>41</v>
-      </c>
-      <c r="I66" t="s">
-        <v>191</v>
-      </c>
-      <c r="J66" t="s">
+      <c r="K66" t="s">
         <v>298</v>
       </c>
-      <c r="K66" t="s">
-        <v>83</v>
-      </c>
       <c r="L66" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M66" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N66" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O66" t="s">
         <v>299</v>
@@ -4878,13 +4899,13 @@
         <v>300</v>
       </c>
       <c r="B67" t="s">
-        <v>301</v>
+        <v>134</v>
       </c>
       <c r="C67" t="s">
-        <v>73</v>
+        <v>283</v>
       </c>
       <c r="D67" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="E67" t="s">
         <v>19</v>
@@ -4893,45 +4914,45 @@
         <v>20</v>
       </c>
       <c r="G67" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="H67" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="I67" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J67" t="s">
+        <v>301</v>
+      </c>
+      <c r="K67" t="s">
         <v>302</v>
       </c>
-      <c r="K67" t="s">
+      <c r="L67" t="s">
+        <v>21</v>
+      </c>
+      <c r="M67" t="s">
+        <v>21</v>
+      </c>
+      <c r="N67" t="s">
+        <v>21</v>
+      </c>
+      <c r="O67" t="s">
         <v>303</v>
-      </c>
-      <c r="L67" t="s">
-        <v>26</v>
-      </c>
-      <c r="M67" t="s">
-        <v>26</v>
-      </c>
-      <c r="N67" t="s">
-        <v>26</v>
-      </c>
-      <c r="O67" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>304</v>
+      </c>
+      <c r="B68" t="s">
         <v>305</v>
       </c>
-      <c r="B68" t="s">
-        <v>263</v>
-      </c>
       <c r="C68" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D68" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E68" t="s">
         <v>19</v>
@@ -4940,28 +4961,28 @@
         <v>20</v>
       </c>
       <c r="G68" t="s">
-        <v>144</v>
+        <v>90</v>
       </c>
       <c r="H68" t="s">
         <v>22</v>
       </c>
       <c r="I68" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J68" t="s">
-        <v>269</v>
+        <v>160</v>
       </c>
       <c r="K68" t="s">
-        <v>163</v>
+        <v>211</v>
       </c>
       <c r="L68" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M68" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N68" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O68" t="s">
         <v>306</v>
@@ -4972,257 +4993,257 @@
         <v>307</v>
       </c>
       <c r="B69" t="s">
+        <v>28</v>
+      </c>
+      <c r="C69" t="s">
+        <v>29</v>
+      </c>
+      <c r="D69" t="s">
+        <v>18</v>
+      </c>
+      <c r="E69" t="s">
+        <v>19</v>
+      </c>
+      <c r="F69" t="s">
+        <v>30</v>
+      </c>
+      <c r="G69" t="s">
+        <v>21</v>
+      </c>
+      <c r="H69" t="s">
+        <v>22</v>
+      </c>
+      <c r="I69" t="s">
+        <v>23</v>
+      </c>
+      <c r="J69" t="s">
         <v>308</v>
       </c>
-      <c r="C69" t="s">
-        <v>190</v>
-      </c>
-      <c r="D69" t="s">
-        <v>68</v>
-      </c>
-      <c r="E69" t="s">
-        <v>38</v>
-      </c>
-      <c r="F69" t="s">
-        <v>129</v>
-      </c>
-      <c r="G69" t="s">
-        <v>21</v>
-      </c>
-      <c r="H69" t="s">
-        <v>22</v>
-      </c>
-      <c r="I69" t="s">
-        <v>191</v>
-      </c>
-      <c r="J69" t="s">
+      <c r="K69" t="s">
+        <v>33</v>
+      </c>
+      <c r="L69" t="s">
+        <v>117</v>
+      </c>
+      <c r="M69" t="s">
+        <v>35</v>
+      </c>
+      <c r="N69" t="s">
+        <v>21</v>
+      </c>
+      <c r="O69" t="s">
         <v>309</v>
-      </c>
-      <c r="K69" t="s">
-        <v>292</v>
-      </c>
-      <c r="L69" t="s">
-        <v>26</v>
-      </c>
-      <c r="M69" t="s">
-        <v>26</v>
-      </c>
-      <c r="N69" t="s">
-        <v>26</v>
-      </c>
-      <c r="O69" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>310</v>
+      </c>
+      <c r="B70" t="s">
+        <v>134</v>
+      </c>
+      <c r="C70" t="s">
+        <v>283</v>
+      </c>
+      <c r="D70" t="s">
+        <v>56</v>
+      </c>
+      <c r="E70" t="s">
+        <v>19</v>
+      </c>
+      <c r="F70" t="s">
+        <v>20</v>
+      </c>
+      <c r="G70" t="s">
+        <v>90</v>
+      </c>
+      <c r="H70" t="s">
+        <v>57</v>
+      </c>
+      <c r="I70" t="s">
+        <v>21</v>
+      </c>
+      <c r="J70" t="s">
         <v>311</v>
       </c>
-      <c r="B70" t="s">
-        <v>230</v>
-      </c>
-      <c r="C70" t="s">
-        <v>296</v>
-      </c>
-      <c r="D70" t="s">
-        <v>297</v>
-      </c>
-      <c r="E70" t="s">
-        <v>38</v>
-      </c>
-      <c r="F70" t="s">
-        <v>196</v>
-      </c>
-      <c r="G70" t="s">
-        <v>21</v>
-      </c>
-      <c r="H70" t="s">
-        <v>41</v>
-      </c>
-      <c r="I70" t="s">
-        <v>191</v>
-      </c>
-      <c r="J70" t="s">
+      <c r="K70" t="s">
+        <v>100</v>
+      </c>
+      <c r="L70" t="s">
+        <v>21</v>
+      </c>
+      <c r="M70" t="s">
+        <v>21</v>
+      </c>
+      <c r="N70" t="s">
+        <v>21</v>
+      </c>
+      <c r="O70" t="s">
         <v>312</v>
-      </c>
-      <c r="K70" t="s">
-        <v>205</v>
-      </c>
-      <c r="L70" t="s">
-        <v>26</v>
-      </c>
-      <c r="M70" t="s">
-        <v>26</v>
-      </c>
-      <c r="N70" t="s">
-        <v>26</v>
-      </c>
-      <c r="O70" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>313</v>
+      </c>
+      <c r="B71" t="s">
+        <v>134</v>
+      </c>
+      <c r="C71" t="s">
+        <v>283</v>
+      </c>
+      <c r="D71" t="s">
+        <v>56</v>
+      </c>
+      <c r="E71" t="s">
+        <v>19</v>
+      </c>
+      <c r="F71" t="s">
+        <v>243</v>
+      </c>
+      <c r="G71" t="s">
+        <v>137</v>
+      </c>
+      <c r="H71" t="s">
+        <v>57</v>
+      </c>
+      <c r="I71" t="s">
+        <v>21</v>
+      </c>
+      <c r="J71" t="s">
+        <v>203</v>
+      </c>
+      <c r="K71" t="s">
+        <v>69</v>
+      </c>
+      <c r="L71" t="s">
+        <v>21</v>
+      </c>
+      <c r="M71" t="s">
+        <v>245</v>
+      </c>
+      <c r="N71" t="s">
+        <v>21</v>
+      </c>
+      <c r="O71" t="s">
         <v>314</v>
-      </c>
-      <c r="B71" t="s">
-        <v>308</v>
-      </c>
-      <c r="C71" t="s">
-        <v>190</v>
-      </c>
-      <c r="D71" t="s">
-        <v>68</v>
-      </c>
-      <c r="E71" t="s">
-        <v>38</v>
-      </c>
-      <c r="F71" t="s">
-        <v>129</v>
-      </c>
-      <c r="G71" t="s">
-        <v>75</v>
-      </c>
-      <c r="H71" t="s">
-        <v>22</v>
-      </c>
-      <c r="I71" t="s">
-        <v>191</v>
-      </c>
-      <c r="J71" t="s">
-        <v>247</v>
-      </c>
-      <c r="K71" t="s">
-        <v>315</v>
-      </c>
-      <c r="L71" t="s">
-        <v>26</v>
-      </c>
-      <c r="M71" t="s">
-        <v>26</v>
-      </c>
-      <c r="N71" t="s">
-        <v>26</v>
-      </c>
-      <c r="O71" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B72" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="C72" t="s">
-        <v>319</v>
+        <v>17</v>
       </c>
       <c r="D72" t="s">
-        <v>320</v>
+        <v>18</v>
       </c>
       <c r="E72" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F72" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="G72" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="H72" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I72" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J72" t="s">
-        <v>298</v>
+        <v>231</v>
       </c>
       <c r="K72" t="s">
-        <v>76</v>
+        <v>235</v>
       </c>
       <c r="L72" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M72" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N72" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O72" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="B73" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="C73" t="s">
-        <v>240</v>
+        <v>29</v>
       </c>
       <c r="D73" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="E73" t="s">
         <v>19</v>
       </c>
       <c r="F73" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="G73" t="s">
-        <v>323</v>
+        <v>21</v>
       </c>
       <c r="H73" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I73" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J73" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="K73" t="s">
-        <v>292</v>
+        <v>195</v>
       </c>
       <c r="L73" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M73" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N73" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O73" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B74" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="C74" t="s">
-        <v>128</v>
+        <v>29</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
       </c>
       <c r="E74" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F74" t="s">
-        <v>129</v>
+        <v>30</v>
       </c>
       <c r="G74" t="s">
-        <v>144</v>
+        <v>31</v>
       </c>
       <c r="H74" t="s">
         <v>22</v>
@@ -5231,92 +5252,92 @@
         <v>23</v>
       </c>
       <c r="J74" t="s">
-        <v>109</v>
+        <v>321</v>
       </c>
       <c r="K74" t="s">
-        <v>208</v>
+        <v>33</v>
       </c>
       <c r="L74" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="M74" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="N74" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O74" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B75" t="s">
-        <v>72</v>
+        <v>305</v>
       </c>
       <c r="C75" t="s">
-        <v>240</v>
+        <v>21</v>
       </c>
       <c r="D75" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="E75" t="s">
         <v>19</v>
       </c>
       <c r="F75" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G75" t="s">
-        <v>323</v>
+        <v>31</v>
       </c>
       <c r="H75" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I75" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J75" t="s">
-        <v>329</v>
+        <v>214</v>
       </c>
       <c r="K75" t="s">
-        <v>256</v>
+        <v>33</v>
       </c>
       <c r="L75" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="M75" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="N75" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O75" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B76" t="s">
-        <v>107</v>
+        <v>28</v>
       </c>
       <c r="C76" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="D76" t="s">
         <v>18</v>
       </c>
       <c r="E76" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F76" t="s">
-        <v>129</v>
+        <v>218</v>
       </c>
       <c r="G76" t="s">
-        <v>144</v>
+        <v>326</v>
       </c>
       <c r="H76" t="s">
         <v>22</v>
@@ -5325,515 +5346,515 @@
         <v>23</v>
       </c>
       <c r="J76" t="s">
-        <v>332</v>
+        <v>160</v>
       </c>
       <c r="K76" t="s">
-        <v>333</v>
+        <v>290</v>
       </c>
       <c r="L76" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M76" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N76" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O76" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="B77" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="C77" t="s">
-        <v>240</v>
+        <v>29</v>
       </c>
       <c r="D77" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="E77" t="s">
         <v>19</v>
       </c>
       <c r="F77" t="s">
-        <v>196</v>
+        <v>30</v>
       </c>
       <c r="G77" t="s">
-        <v>323</v>
+        <v>21</v>
       </c>
       <c r="H77" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I77" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J77" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="K77" t="s">
-        <v>131</v>
+        <v>330</v>
       </c>
       <c r="L77" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="M77" t="s">
-        <v>198</v>
+        <v>35</v>
       </c>
       <c r="N77" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O77" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B78" t="s">
-        <v>72</v>
+        <v>158</v>
       </c>
       <c r="C78" t="s">
-        <v>240</v>
+        <v>159</v>
       </c>
       <c r="D78" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="E78" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F78" t="s">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="G78" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H78" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I78" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J78" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="K78" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="L78" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M78" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N78" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O78" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B79" t="s">
-        <v>72</v>
+        <v>337</v>
       </c>
       <c r="C79" t="s">
-        <v>240</v>
+        <v>338</v>
       </c>
       <c r="D79" t="s">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="E79" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F79" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G79" t="s">
-        <v>343</v>
+        <v>137</v>
       </c>
       <c r="H79" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="I79" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="J79" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="K79" t="s">
-        <v>345</v>
+        <v>59</v>
       </c>
       <c r="L79" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M79" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N79" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O79" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B80" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="C80" t="s">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="D80" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="E80" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F80" t="s">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="G80" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="H80" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I80" t="s">
-        <v>191</v>
+        <v>23</v>
       </c>
       <c r="J80" t="s">
-        <v>192</v>
+        <v>344</v>
       </c>
       <c r="K80" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="L80" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M80" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N80" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O80" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B81" t="s">
-        <v>46</v>
+        <v>305</v>
       </c>
       <c r="C81" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D81" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E81" t="s">
         <v>19</v>
       </c>
       <c r="F81" t="s">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="G81" t="s">
-        <v>323</v>
+        <v>193</v>
       </c>
       <c r="H81" t="s">
         <v>22</v>
       </c>
       <c r="I81" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J81" t="s">
-        <v>352</v>
+        <v>311</v>
       </c>
       <c r="K81" t="s">
-        <v>353</v>
+        <v>211</v>
       </c>
       <c r="L81" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M81" t="s">
-        <v>198</v>
+        <v>21</v>
       </c>
       <c r="N81" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O81" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B82" t="s">
-        <v>46</v>
+        <v>350</v>
       </c>
       <c r="C82" t="s">
-        <v>47</v>
+        <v>238</v>
       </c>
       <c r="D82" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="E82" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F82" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G82" t="s">
-        <v>144</v>
+        <v>90</v>
       </c>
       <c r="H82" t="s">
         <v>22</v>
       </c>
       <c r="I82" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="J82" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="K82" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="L82" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M82" t="s">
-        <v>198</v>
+        <v>21</v>
       </c>
       <c r="N82" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O82" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B83" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="C83" t="s">
-        <v>296</v>
+        <v>338</v>
       </c>
       <c r="D83" t="s">
-        <v>297</v>
+        <v>339</v>
       </c>
       <c r="E83" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F83" t="s">
-        <v>170</v>
+        <v>243</v>
       </c>
       <c r="G83" t="s">
-        <v>359</v>
+        <v>90</v>
       </c>
       <c r="H83" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="I83" t="s">
-        <v>191</v>
+        <v>64</v>
       </c>
       <c r="J83" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="K83" t="s">
-        <v>76</v>
+        <v>251</v>
       </c>
       <c r="L83" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M83" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N83" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O83" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="B84" t="s">
-        <v>127</v>
+        <v>350</v>
       </c>
       <c r="C84" t="s">
-        <v>128</v>
+        <v>238</v>
       </c>
       <c r="D84" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="E84" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F84" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="G84" t="s">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="H84" t="s">
         <v>22</v>
       </c>
       <c r="I84" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="J84" t="s">
-        <v>363</v>
+        <v>289</v>
       </c>
       <c r="K84" t="s">
-        <v>345</v>
+        <v>92</v>
       </c>
       <c r="L84" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M84" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N84" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O84" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="B85" t="s">
-        <v>308</v>
+        <v>359</v>
       </c>
       <c r="C85" t="s">
-        <v>190</v>
+        <v>360</v>
       </c>
       <c r="D85" t="s">
-        <v>68</v>
+        <v>361</v>
       </c>
       <c r="E85" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F85" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G85" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="H85" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="I85" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J85" t="s">
-        <v>366</v>
+        <v>340</v>
       </c>
       <c r="K85" t="s">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="L85" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M85" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N85" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O85" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B86" t="s">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="C86" t="s">
-        <v>80</v>
+        <v>283</v>
       </c>
       <c r="D86" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="E86" t="s">
         <v>19</v>
       </c>
       <c r="F86" t="s">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="G86" t="s">
-        <v>21</v>
+        <v>364</v>
       </c>
       <c r="H86" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="I86" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J86" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="K86" t="s">
-        <v>110</v>
+        <v>334</v>
       </c>
       <c r="L86" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M86" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N86" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O86" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B87" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="C87" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="D87" t="s">
         <v>18</v>
       </c>
       <c r="E87" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F87" t="s">
-        <v>20</v>
+        <v>178</v>
       </c>
       <c r="G87" t="s">
-        <v>21</v>
+        <v>193</v>
       </c>
       <c r="H87" t="s">
         <v>22</v>
@@ -5842,36 +5863,36 @@
         <v>23</v>
       </c>
       <c r="J87" t="s">
-        <v>363</v>
+        <v>160</v>
       </c>
       <c r="K87" t="s">
-        <v>372</v>
+        <v>69</v>
       </c>
       <c r="L87" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M87" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N87" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O87" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B88" t="s">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="C88" t="s">
-        <v>152</v>
+        <v>283</v>
       </c>
       <c r="D88" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="E88" t="s">
         <v>19</v>
@@ -5880,54 +5901,54 @@
         <v>20</v>
       </c>
       <c r="G88" t="s">
-        <v>144</v>
+        <v>364</v>
       </c>
       <c r="H88" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="I88" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J88" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="K88" t="s">
-        <v>376</v>
+        <v>298</v>
       </c>
       <c r="L88" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M88" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N88" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O88" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="B89" t="s">
-        <v>72</v>
+        <v>158</v>
       </c>
       <c r="C89" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D89" t="s">
         <v>18</v>
       </c>
       <c r="E89" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F89" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="G89" t="s">
-        <v>254</v>
+        <v>193</v>
       </c>
       <c r="H89" t="s">
         <v>22</v>
@@ -5936,221 +5957,221 @@
         <v>23</v>
       </c>
       <c r="J89" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="K89" t="s">
-        <v>146</v>
+        <v>374</v>
       </c>
       <c r="L89" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M89" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N89" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O89" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B90" t="s">
-        <v>308</v>
+        <v>134</v>
       </c>
       <c r="C90" t="s">
-        <v>190</v>
+        <v>283</v>
       </c>
       <c r="D90" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E90" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F90" t="s">
-        <v>129</v>
+        <v>243</v>
       </c>
       <c r="G90" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="H90" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="I90" t="s">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="J90" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="K90" t="s">
-        <v>256</v>
+        <v>180</v>
       </c>
       <c r="L90" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M90" t="s">
-        <v>26</v>
+        <v>245</v>
       </c>
       <c r="N90" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O90" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B91" t="s">
-        <v>16</v>
+        <v>134</v>
       </c>
       <c r="C91" t="s">
-        <v>17</v>
+        <v>283</v>
       </c>
       <c r="D91" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="E91" t="s">
         <v>19</v>
       </c>
       <c r="F91" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="G91" t="s">
-        <v>386</v>
+        <v>146</v>
       </c>
       <c r="H91" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="I91" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J91" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="K91" t="s">
-        <v>50</v>
+        <v>381</v>
       </c>
       <c r="L91" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M91" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N91" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O91" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="B92" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C92" t="s">
-        <v>152</v>
+        <v>283</v>
       </c>
       <c r="D92" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="E92" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F92" t="s">
-        <v>20</v>
+        <v>178</v>
       </c>
       <c r="G92" t="s">
-        <v>21</v>
+        <v>384</v>
       </c>
       <c r="H92" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="I92" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J92" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="K92" t="s">
-        <v>155</v>
+        <v>386</v>
       </c>
       <c r="L92" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M92" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N92" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O92" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B93" t="s">
-        <v>46</v>
+        <v>389</v>
       </c>
       <c r="C93" t="s">
-        <v>47</v>
+        <v>238</v>
       </c>
       <c r="D93" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="E93" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F93" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="G93" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H93" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="I93" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="J93" t="s">
-        <v>393</v>
+        <v>239</v>
       </c>
       <c r="K93" t="s">
-        <v>131</v>
+        <v>390</v>
       </c>
       <c r="L93" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M93" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N93" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O93" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B94" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C94" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D94" t="s">
         <v>18</v>
@@ -6159,10 +6180,10 @@
         <v>19</v>
       </c>
       <c r="F94" t="s">
-        <v>129</v>
+        <v>243</v>
       </c>
       <c r="G94" t="s">
-        <v>21</v>
+        <v>364</v>
       </c>
       <c r="H94" t="s">
         <v>22</v>
@@ -6171,45 +6192,45 @@
         <v>23</v>
       </c>
       <c r="J94" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="K94" t="s">
-        <v>54</v>
+        <v>394</v>
       </c>
       <c r="L94" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M94" t="s">
-        <v>26</v>
+        <v>245</v>
       </c>
       <c r="N94" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O94" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B95" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="C95" t="s">
-        <v>128</v>
+        <v>29</v>
       </c>
       <c r="D95" t="s">
         <v>18</v>
       </c>
       <c r="E95" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F95" t="s">
-        <v>129</v>
+        <v>243</v>
       </c>
       <c r="G95" t="s">
-        <v>144</v>
+        <v>193</v>
       </c>
       <c r="H95" t="s">
         <v>22</v>
@@ -6218,280 +6239,280 @@
         <v>23</v>
       </c>
       <c r="J95" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="K95" t="s">
-        <v>163</v>
+        <v>381</v>
       </c>
       <c r="L95" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M95" t="s">
-        <v>26</v>
+        <v>245</v>
       </c>
       <c r="N95" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O95" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
+        <v>399</v>
+      </c>
+      <c r="B96" t="s">
+        <v>337</v>
+      </c>
+      <c r="C96" t="s">
+        <v>338</v>
+      </c>
+      <c r="D96" t="s">
+        <v>339</v>
+      </c>
+      <c r="E96" t="s">
+        <v>45</v>
+      </c>
+      <c r="F96" t="s">
+        <v>218</v>
+      </c>
+      <c r="G96" t="s">
+        <v>400</v>
+      </c>
+      <c r="H96" t="s">
+        <v>57</v>
+      </c>
+      <c r="I96" t="s">
+        <v>64</v>
+      </c>
+      <c r="J96" t="s">
         <v>401</v>
       </c>
-      <c r="B96" t="s">
-        <v>127</v>
-      </c>
-      <c r="C96" t="s">
-        <v>128</v>
-      </c>
-      <c r="D96" t="s">
-        <v>18</v>
-      </c>
-      <c r="E96" t="s">
-        <v>38</v>
-      </c>
-      <c r="F96" t="s">
-        <v>129</v>
-      </c>
-      <c r="G96" t="s">
-        <v>21</v>
-      </c>
-      <c r="H96" t="s">
-        <v>22</v>
-      </c>
-      <c r="I96" t="s">
-        <v>23</v>
-      </c>
-      <c r="J96" t="s">
+      <c r="K96" t="s">
+        <v>25</v>
+      </c>
+      <c r="L96" t="s">
+        <v>21</v>
+      </c>
+      <c r="M96" t="s">
+        <v>21</v>
+      </c>
+      <c r="N96" t="s">
+        <v>21</v>
+      </c>
+      <c r="O96" t="s">
         <v>402</v>
-      </c>
-      <c r="K96" t="s">
-        <v>403</v>
-      </c>
-      <c r="L96" t="s">
-        <v>26</v>
-      </c>
-      <c r="M96" t="s">
-        <v>26</v>
-      </c>
-      <c r="N96" t="s">
-        <v>26</v>
-      </c>
-      <c r="O96" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
+        <v>403</v>
+      </c>
+      <c r="B97" t="s">
+        <v>76</v>
+      </c>
+      <c r="C97" t="s">
+        <v>77</v>
+      </c>
+      <c r="D97" t="s">
+        <v>18</v>
+      </c>
+      <c r="E97" t="s">
+        <v>45</v>
+      </c>
+      <c r="F97" t="s">
+        <v>178</v>
+      </c>
+      <c r="G97" t="s">
+        <v>90</v>
+      </c>
+      <c r="H97" t="s">
+        <v>22</v>
+      </c>
+      <c r="I97" t="s">
+        <v>23</v>
+      </c>
+      <c r="J97" t="s">
+        <v>404</v>
+      </c>
+      <c r="K97" t="s">
+        <v>386</v>
+      </c>
+      <c r="L97" t="s">
+        <v>21</v>
+      </c>
+      <c r="M97" t="s">
+        <v>21</v>
+      </c>
+      <c r="N97" t="s">
+        <v>21</v>
+      </c>
+      <c r="O97" t="s">
         <v>405</v>
-      </c>
-      <c r="B97" t="s">
-        <v>138</v>
-      </c>
-      <c r="C97" t="s">
-        <v>296</v>
-      </c>
-      <c r="D97" t="s">
-        <v>297</v>
-      </c>
-      <c r="E97" t="s">
-        <v>38</v>
-      </c>
-      <c r="F97" t="s">
-        <v>20</v>
-      </c>
-      <c r="G97" t="s">
-        <v>144</v>
-      </c>
-      <c r="H97" t="s">
-        <v>22</v>
-      </c>
-      <c r="I97" t="s">
-        <v>191</v>
-      </c>
-      <c r="J97" t="s">
-        <v>406</v>
-      </c>
-      <c r="K97" t="s">
-        <v>349</v>
-      </c>
-      <c r="L97" t="s">
-        <v>26</v>
-      </c>
-      <c r="M97" t="s">
-        <v>26</v>
-      </c>
-      <c r="N97" t="s">
-        <v>26</v>
-      </c>
-      <c r="O97" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
+        <v>406</v>
+      </c>
+      <c r="B98" t="s">
+        <v>350</v>
+      </c>
+      <c r="C98" t="s">
+        <v>238</v>
+      </c>
+      <c r="D98" t="s">
+        <v>44</v>
+      </c>
+      <c r="E98" t="s">
+        <v>45</v>
+      </c>
+      <c r="F98" t="s">
+        <v>178</v>
+      </c>
+      <c r="G98" t="s">
+        <v>90</v>
+      </c>
+      <c r="H98" t="s">
+        <v>57</v>
+      </c>
+      <c r="I98" t="s">
+        <v>64</v>
+      </c>
+      <c r="J98" t="s">
+        <v>407</v>
+      </c>
+      <c r="K98" t="s">
+        <v>180</v>
+      </c>
+      <c r="L98" t="s">
+        <v>21</v>
+      </c>
+      <c r="M98" t="s">
+        <v>21</v>
+      </c>
+      <c r="N98" t="s">
+        <v>21</v>
+      </c>
+      <c r="O98" t="s">
         <v>408</v>
-      </c>
-      <c r="B98" t="s">
-        <v>127</v>
-      </c>
-      <c r="C98" t="s">
-        <v>128</v>
-      </c>
-      <c r="D98" t="s">
-        <v>18</v>
-      </c>
-      <c r="E98" t="s">
-        <v>38</v>
-      </c>
-      <c r="F98" t="s">
-        <v>129</v>
-      </c>
-      <c r="G98" t="s">
-        <v>21</v>
-      </c>
-      <c r="H98" t="s">
-        <v>22</v>
-      </c>
-      <c r="I98" t="s">
-        <v>23</v>
-      </c>
-      <c r="J98" t="s">
-        <v>409</v>
-      </c>
-      <c r="K98" t="s">
-        <v>349</v>
-      </c>
-      <c r="L98" t="s">
-        <v>26</v>
-      </c>
-      <c r="M98" t="s">
-        <v>26</v>
-      </c>
-      <c r="N98" t="s">
-        <v>26</v>
-      </c>
-      <c r="O98" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
+        <v>409</v>
+      </c>
+      <c r="B99" t="s">
+        <v>54</v>
+      </c>
+      <c r="C99" t="s">
+        <v>55</v>
+      </c>
+      <c r="D99" t="s">
+        <v>56</v>
+      </c>
+      <c r="E99" t="s">
+        <v>19</v>
+      </c>
+      <c r="F99" t="s">
+        <v>178</v>
+      </c>
+      <c r="G99" t="s">
+        <v>90</v>
+      </c>
+      <c r="H99" t="s">
+        <v>57</v>
+      </c>
+      <c r="I99" t="s">
+        <v>21</v>
+      </c>
+      <c r="J99" t="s">
+        <v>410</v>
+      </c>
+      <c r="K99" t="s">
+        <v>161</v>
+      </c>
+      <c r="L99" t="s">
+        <v>21</v>
+      </c>
+      <c r="M99" t="s">
+        <v>21</v>
+      </c>
+      <c r="N99" t="s">
+        <v>21</v>
+      </c>
+      <c r="O99" t="s">
         <v>411</v>
-      </c>
-      <c r="B99" t="s">
-        <v>116</v>
-      </c>
-      <c r="C99" t="s">
-        <v>117</v>
-      </c>
-      <c r="D99" t="s">
-        <v>68</v>
-      </c>
-      <c r="E99" t="s">
-        <v>38</v>
-      </c>
-      <c r="F99" t="s">
-        <v>214</v>
-      </c>
-      <c r="G99" t="s">
-        <v>75</v>
-      </c>
-      <c r="H99" t="s">
-        <v>41</v>
-      </c>
-      <c r="I99" t="s">
-        <v>26</v>
-      </c>
-      <c r="J99" t="s">
-        <v>412</v>
-      </c>
-      <c r="K99" t="s">
-        <v>413</v>
-      </c>
-      <c r="L99" t="s">
-        <v>26</v>
-      </c>
-      <c r="M99" t="s">
-        <v>26</v>
-      </c>
-      <c r="N99" t="s">
-        <v>414</v>
-      </c>
-      <c r="O99" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B100" t="s">
-        <v>308</v>
+        <v>16</v>
       </c>
       <c r="C100" t="s">
-        <v>190</v>
+        <v>17</v>
       </c>
       <c r="D100" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="E100" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F100" t="s">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="G100" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="H100" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I100" t="s">
-        <v>191</v>
+        <v>23</v>
       </c>
       <c r="J100" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="K100" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="L100" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M100" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N100" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O100" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B101" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C101" t="s">
-        <v>128</v>
+        <v>201</v>
       </c>
       <c r="D101" t="s">
         <v>18</v>
       </c>
       <c r="E101" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F101" t="s">
         <v>20</v>
       </c>
       <c r="G101" t="s">
-        <v>254</v>
+        <v>193</v>
       </c>
       <c r="H101" t="s">
         <v>22</v>
@@ -6500,121 +6521,121 @@
         <v>23</v>
       </c>
       <c r="J101" t="s">
-        <v>360</v>
+        <v>415</v>
       </c>
       <c r="K101" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="L101" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M101" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N101" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O101" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="B102" t="s">
-        <v>308</v>
+        <v>134</v>
       </c>
       <c r="C102" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="D102" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="E102" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F102" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="G102" t="s">
-        <v>144</v>
+        <v>296</v>
       </c>
       <c r="H102" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I102" t="s">
-        <v>191</v>
+        <v>23</v>
       </c>
       <c r="J102" t="s">
-        <v>363</v>
+        <v>419</v>
       </c>
       <c r="K102" t="s">
-        <v>292</v>
+        <v>195</v>
       </c>
       <c r="L102" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M102" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N102" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O102" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
+        <v>421</v>
+      </c>
+      <c r="B103" t="s">
+        <v>350</v>
+      </c>
+      <c r="C103" t="s">
+        <v>238</v>
+      </c>
+      <c r="D103" t="s">
+        <v>44</v>
+      </c>
+      <c r="E103" t="s">
+        <v>45</v>
+      </c>
+      <c r="F103" t="s">
+        <v>178</v>
+      </c>
+      <c r="G103" t="s">
+        <v>422</v>
+      </c>
+      <c r="H103" t="s">
+        <v>57</v>
+      </c>
+      <c r="I103" t="s">
+        <v>64</v>
+      </c>
+      <c r="J103" t="s">
+        <v>423</v>
+      </c>
+      <c r="K103" t="s">
+        <v>298</v>
+      </c>
+      <c r="L103" t="s">
+        <v>21</v>
+      </c>
+      <c r="M103" t="s">
+        <v>21</v>
+      </c>
+      <c r="N103" t="s">
+        <v>21</v>
+      </c>
+      <c r="O103" t="s">
         <v>424</v>
-      </c>
-      <c r="B103" t="s">
-        <v>46</v>
-      </c>
-      <c r="C103" t="s">
-        <v>47</v>
-      </c>
-      <c r="D103" t="s">
-        <v>18</v>
-      </c>
-      <c r="E103" t="s">
-        <v>19</v>
-      </c>
-      <c r="F103" t="s">
-        <v>237</v>
-      </c>
-      <c r="G103" t="s">
-        <v>26</v>
-      </c>
-      <c r="H103" t="s">
-        <v>22</v>
-      </c>
-      <c r="I103" t="s">
-        <v>23</v>
-      </c>
-      <c r="J103" t="s">
-        <v>383</v>
-      </c>
-      <c r="K103" t="s">
-        <v>425</v>
-      </c>
-      <c r="L103" t="s">
-        <v>26</v>
-      </c>
-      <c r="M103" t="s">
-        <v>26</v>
-      </c>
-      <c r="N103" t="s">
-        <v>26</v>
-      </c>
-      <c r="O103" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B104" t="s">
         <v>16</v>
@@ -6629,10 +6650,10 @@
         <v>19</v>
       </c>
       <c r="F104" t="s">
-        <v>20</v>
+        <v>218</v>
       </c>
       <c r="G104" t="s">
-        <v>58</v>
+        <v>426</v>
       </c>
       <c r="H104" t="s">
         <v>22</v>
@@ -6641,45 +6662,45 @@
         <v>23</v>
       </c>
       <c r="J104" t="s">
+        <v>427</v>
+      </c>
+      <c r="K104" t="s">
+        <v>34</v>
+      </c>
+      <c r="L104" t="s">
+        <v>21</v>
+      </c>
+      <c r="M104" t="s">
+        <v>21</v>
+      </c>
+      <c r="N104" t="s">
+        <v>21</v>
+      </c>
+      <c r="O104" t="s">
         <v>428</v>
-      </c>
-      <c r="K104" t="s">
-        <v>429</v>
-      </c>
-      <c r="L104" t="s">
-        <v>26</v>
-      </c>
-      <c r="M104" t="s">
-        <v>26</v>
-      </c>
-      <c r="N104" t="s">
-        <v>26</v>
-      </c>
-      <c r="O104" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B105" t="s">
-        <v>46</v>
+        <v>187</v>
       </c>
       <c r="C105" t="s">
-        <v>47</v>
+        <v>201</v>
       </c>
       <c r="D105" t="s">
         <v>18</v>
       </c>
       <c r="E105" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F105" t="s">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="G105" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="H105" t="s">
         <v>22</v>
@@ -6688,45 +6709,45 @@
         <v>23</v>
       </c>
       <c r="J105" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="K105" t="s">
-        <v>333</v>
+        <v>51</v>
       </c>
       <c r="L105" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M105" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N105" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O105" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B106" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="C106" t="s">
-        <v>128</v>
+        <v>29</v>
       </c>
       <c r="D106" t="s">
         <v>18</v>
       </c>
       <c r="E106" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F106" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="G106" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="H106" t="s">
         <v>22</v>
@@ -6735,33 +6756,33 @@
         <v>23</v>
       </c>
       <c r="J106" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="K106" t="s">
-        <v>345</v>
+        <v>180</v>
       </c>
       <c r="L106" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M106" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N106" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O106" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B107" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C107" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D107" t="s">
         <v>18</v>
@@ -6770,10 +6791,10 @@
         <v>19</v>
       </c>
       <c r="F107" t="s">
-        <v>20</v>
+        <v>178</v>
       </c>
       <c r="G107" t="s">
-        <v>323</v>
+        <v>90</v>
       </c>
       <c r="H107" t="s">
         <v>22</v>
@@ -6782,186 +6803,186 @@
         <v>23</v>
       </c>
       <c r="J107" t="s">
-        <v>109</v>
+        <v>436</v>
       </c>
       <c r="K107" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="L107" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M107" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N107" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O107" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
+        <v>438</v>
+      </c>
+      <c r="B108" t="s">
+        <v>76</v>
+      </c>
+      <c r="C108" t="s">
+        <v>77</v>
+      </c>
+      <c r="D108" t="s">
+        <v>18</v>
+      </c>
+      <c r="E108" t="s">
+        <v>45</v>
+      </c>
+      <c r="F108" t="s">
+        <v>178</v>
+      </c>
+      <c r="G108" t="s">
+        <v>193</v>
+      </c>
+      <c r="H108" t="s">
+        <v>22</v>
+      </c>
+      <c r="I108" t="s">
+        <v>23</v>
+      </c>
+      <c r="J108" t="s">
         <v>439</v>
       </c>
-      <c r="B108" t="s">
+      <c r="K108" t="s">
+        <v>211</v>
+      </c>
+      <c r="L108" t="s">
+        <v>21</v>
+      </c>
+      <c r="M108" t="s">
+        <v>21</v>
+      </c>
+      <c r="N108" t="s">
+        <v>21</v>
+      </c>
+      <c r="O108" t="s">
         <v>440</v>
-      </c>
-      <c r="C108" t="s">
-        <v>117</v>
-      </c>
-      <c r="D108" t="s">
-        <v>68</v>
-      </c>
-      <c r="E108" t="s">
-        <v>38</v>
-      </c>
-      <c r="F108" t="s">
-        <v>214</v>
-      </c>
-      <c r="G108" t="s">
-        <v>21</v>
-      </c>
-      <c r="H108" t="s">
-        <v>22</v>
-      </c>
-      <c r="I108" t="s">
-        <v>26</v>
-      </c>
-      <c r="J108" t="s">
-        <v>441</v>
-      </c>
-      <c r="K108" t="s">
-        <v>51</v>
-      </c>
-      <c r="L108" t="s">
-        <v>26</v>
-      </c>
-      <c r="M108" t="s">
-        <v>26</v>
-      </c>
-      <c r="N108" t="s">
-        <v>442</v>
-      </c>
-      <c r="O108" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B109" t="s">
-        <v>440</v>
+        <v>76</v>
       </c>
       <c r="C109" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="D109" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="E109" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F109" t="s">
-        <v>214</v>
+        <v>178</v>
       </c>
       <c r="G109" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="H109" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I109" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J109" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="K109" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="L109" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M109" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N109" t="s">
-        <v>446</v>
+        <v>21</v>
       </c>
       <c r="O109" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B110" t="s">
-        <v>46</v>
+        <v>187</v>
       </c>
       <c r="C110" t="s">
-        <v>47</v>
+        <v>338</v>
       </c>
       <c r="D110" t="s">
-        <v>18</v>
+        <v>339</v>
       </c>
       <c r="E110" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F110" t="s">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="G110" t="s">
-        <v>26</v>
+        <v>193</v>
       </c>
       <c r="H110" t="s">
         <v>22</v>
       </c>
       <c r="I110" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="J110" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="K110" t="s">
-        <v>450</v>
+        <v>390</v>
       </c>
       <c r="L110" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M110" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N110" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O110" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="B111" t="s">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="C111" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="D111" t="s">
         <v>18</v>
       </c>
       <c r="E111" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="F111" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="G111" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="H111" t="s">
         <v>22</v>
@@ -6970,69 +6991,257 @@
         <v>23</v>
       </c>
       <c r="J111" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="K111" t="s">
-        <v>454</v>
+        <v>390</v>
       </c>
       <c r="L111" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="M111" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N111" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O111" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
+        <v>450</v>
+      </c>
+      <c r="B112" t="s">
+        <v>167</v>
+      </c>
+      <c r="C112" t="s">
+        <v>168</v>
+      </c>
+      <c r="D112" t="s">
+        <v>44</v>
+      </c>
+      <c r="E112" t="s">
+        <v>45</v>
+      </c>
+      <c r="F112" t="s">
+        <v>259</v>
+      </c>
+      <c r="G112" t="s">
+        <v>137</v>
+      </c>
+      <c r="H112" t="s">
+        <v>57</v>
+      </c>
+      <c r="I112" t="s">
+        <v>21</v>
+      </c>
+      <c r="J112" t="s">
+        <v>451</v>
+      </c>
+      <c r="K112" t="s">
+        <v>452</v>
+      </c>
+      <c r="L112" t="s">
+        <v>21</v>
+      </c>
+      <c r="M112" t="s">
+        <v>21</v>
+      </c>
+      <c r="N112" t="s">
+        <v>453</v>
+      </c>
+      <c r="O112" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>455</v>
+      </c>
+      <c r="B113" t="s">
+        <v>350</v>
+      </c>
+      <c r="C113" t="s">
+        <v>238</v>
+      </c>
+      <c r="D113" t="s">
+        <v>44</v>
+      </c>
+      <c r="E113" t="s">
+        <v>45</v>
+      </c>
+      <c r="F113" t="s">
+        <v>178</v>
+      </c>
+      <c r="G113" t="s">
+        <v>137</v>
+      </c>
+      <c r="H113" t="s">
+        <v>57</v>
+      </c>
+      <c r="I113" t="s">
+        <v>64</v>
+      </c>
+      <c r="J113" t="s">
         <v>456</v>
       </c>
-      <c r="B112" t="s">
-        <v>219</v>
-      </c>
-      <c r="C112" t="s">
-        <v>243</v>
-      </c>
-      <c r="D112" t="s">
-        <v>68</v>
-      </c>
-      <c r="E112" t="s">
+      <c r="K113" t="s">
+        <v>59</v>
+      </c>
+      <c r="L113" t="s">
+        <v>21</v>
+      </c>
+      <c r="M113" t="s">
+        <v>21</v>
+      </c>
+      <c r="N113" t="s">
+        <v>21</v>
+      </c>
+      <c r="O113" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>458</v>
+      </c>
+      <c r="B114" t="s">
+        <v>76</v>
+      </c>
+      <c r="C114" t="s">
+        <v>77</v>
+      </c>
+      <c r="D114" t="s">
+        <v>18</v>
+      </c>
+      <c r="E114" t="s">
+        <v>45</v>
+      </c>
+      <c r="F114" t="s">
+        <v>20</v>
+      </c>
+      <c r="G114" t="s">
+        <v>296</v>
+      </c>
+      <c r="H114" t="s">
+        <v>22</v>
+      </c>
+      <c r="I114" t="s">
+        <v>23</v>
+      </c>
+      <c r="J114" t="s">
+        <v>401</v>
+      </c>
+      <c r="K114" t="s">
+        <v>459</v>
+      </c>
+      <c r="L114" t="s">
+        <v>21</v>
+      </c>
+      <c r="M114" t="s">
+        <v>21</v>
+      </c>
+      <c r="N114" t="s">
+        <v>21</v>
+      </c>
+      <c r="O114" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>461</v>
+      </c>
+      <c r="B115" t="s">
+        <v>350</v>
+      </c>
+      <c r="C115" t="s">
+        <v>238</v>
+      </c>
+      <c r="D115" t="s">
+        <v>44</v>
+      </c>
+      <c r="E115" t="s">
+        <v>45</v>
+      </c>
+      <c r="F115" t="s">
+        <v>178</v>
+      </c>
+      <c r="G115" t="s">
+        <v>193</v>
+      </c>
+      <c r="H115" t="s">
+        <v>57</v>
+      </c>
+      <c r="I115" t="s">
+        <v>64</v>
+      </c>
+      <c r="J115" t="s">
+        <v>404</v>
+      </c>
+      <c r="K115" t="s">
+        <v>334</v>
+      </c>
+      <c r="L115" t="s">
+        <v>21</v>
+      </c>
+      <c r="M115" t="s">
+        <v>21</v>
+      </c>
+      <c r="N115" t="s">
+        <v>21</v>
+      </c>
+      <c r="O115" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>463</v>
+      </c>
+      <c r="B116" t="s">
+        <v>28</v>
+      </c>
+      <c r="C116" t="s">
+        <v>29</v>
+      </c>
+      <c r="D116" t="s">
+        <v>18</v>
+      </c>
+      <c r="E116" t="s">
         <v>19</v>
       </c>
-      <c r="F112" t="s">
-        <v>20</v>
-      </c>
-      <c r="G112" t="s">
-        <v>21</v>
-      </c>
-      <c r="H112" t="s">
-        <v>41</v>
-      </c>
-      <c r="I112" t="s">
-        <v>23</v>
-      </c>
-      <c r="J112" t="s">
-        <v>457</v>
-      </c>
-      <c r="K112" t="s">
-        <v>208</v>
-      </c>
-      <c r="L112" t="s">
-        <v>26</v>
-      </c>
-      <c r="M112" t="s">
-        <v>26</v>
-      </c>
-      <c r="N112" t="s">
-        <v>26</v>
-      </c>
-      <c r="O112" t="s">
-        <v>458</v>
+      <c r="F116" t="s">
+        <v>38</v>
+      </c>
+      <c r="G116" t="s">
+        <v>21</v>
+      </c>
+      <c r="H116" t="s">
+        <v>22</v>
+      </c>
+      <c r="I116" t="s">
+        <v>23</v>
+      </c>
+      <c r="J116" t="s">
+        <v>423</v>
+      </c>
+      <c r="K116" t="s">
+        <v>464</v>
+      </c>
+      <c r="L116" t="s">
+        <v>21</v>
+      </c>
+      <c r="M116" t="s">
+        <v>21</v>
+      </c>
+      <c r="N116" t="s">
+        <v>21</v>
+      </c>
+      <c r="O116" t="s">
+        <v>465</v>
       </c>
     </row>
   </sheetData>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O93"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,17 +496,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07/31/2026 5:19:49 PM</t>
+          <t>08/06/2026 2:18:16 PM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -545,38 +545,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>07/31/2026 1:16:01 PM</t>
+          <t>08/06/2026 8:19:00 AM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>662 - Heavy</t>
+          <t>696 - Medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Drew Template</t>
+          <t>Jammie Singleton</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -594,38 +594,38 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>07/31/2026 1:02:24 PM</t>
+          <t>08/05/2026 5:42:28 PM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jeremy Myers</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -643,17 +643,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/30/2026 6:11:26 PM</t>
+          <t>08/05/2026 3:33:14 PM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -692,17 +692,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07/30/2026 5:19:23 PM</t>
+          <t>08/04/2026 2:28:07 PM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,12 +712,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -741,17 +741,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07/27/2026 3:31:40 PM</t>
+          <t>08/04/2026 12:31:14 PM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>696 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -761,12 +761,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -790,22 +790,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07/27/2026 10:23:43 AM</t>
+          <t>08/03/2026 2:39:43 PM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>693 - Heavy</t>
+          <t>649 - Heavy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jonathan Dubose</t>
+          <t>Juan Ramirez</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -815,13 +815,13 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -839,17 +839,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07/27/2026 8:16:05 AM</t>
+          <t>08/03/2026 2:36:38 PM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>649 - Heavy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Juan Ramirez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -888,38 +888,38 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/24/2026 6:37:41 PM</t>
+          <t>07/31/2026 1:16:01 PM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>662 - Heavy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Drew Template</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -927,30 +927,32 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
-        <v>0.5610000000000001</v>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/24/2026 5:53:45 PM</t>
+          <t>07/31/2026 1:02:24 PM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jeremy Myers</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Towing and Recovery</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -960,13 +962,13 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -984,17 +986,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/24/2026 10:43:08 AM</t>
+          <t>07/30/2026 6:11:26 PM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1009,7 +1011,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1033,17 +1035,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/23/2026 12:53:44 PM</t>
+          <t>07/30/2026 5:19:23 PM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>693 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1053,7 +1055,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1082,12 +1084,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/23/2026 12:28:42 PM</t>
+          <t>07/27/2026 3:31:40 PM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>696 - Medium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1107,7 +1109,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1131,30 +1133,38 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/23/2026 5:35:45 AM</t>
+          <t>07/27/2026 10:23:43 AM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>693 - Heavy</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Jonathan Dubose</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Active Drivers, Heavy Haul</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1172,17 +1182,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/22/2026 5:03:30 PM</t>
+          <t>07/27/2026 8:16:05 AM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1192,7 +1202,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1221,7 +1231,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/21/2026 5:20:15 PM</t>
+          <t>07/24/2026 6:37:41 PM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1246,7 +1256,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1260,27 +1270,25 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N17" t="n">
+        <v>0.5610000000000001</v>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/21/2026 4:39:25 PM</t>
+          <t>07/24/2026 5:53:45 PM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1295,7 +1303,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1319,17 +1327,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/21/2026 4:37:50 PM</t>
+          <t>07/24/2026 10:43:08 AM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1339,12 +1347,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1368,38 +1376,38 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/21/2026 3:29:43 PM</t>
+          <t>07/23/2026 12:53:44 PM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>693 - Heavy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jeremy Myers</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1417,38 +1425,38 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/21/2026 11:16:15 AM</t>
+          <t>07/23/2026 12:28:42 PM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>693 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Adam Johnson</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1456,27 +1464,25 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="n">
-        <v>0.606</v>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/21/2026 10:51:17 AM</t>
+          <t>07/23/2026 5:35:45 AM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>668 - Light</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Joshua Barrow</t>
-        </is>
-      </c>
+          <t>685 - Medium</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
@@ -1485,13 +1491,13 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1509,17 +1515,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/20/2026 4:04:35 PM</t>
+          <t>07/22/2026 5:03:30 PM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1529,7 +1535,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1558,17 +1564,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/20/2026 6:42:29 AM</t>
+          <t>07/21/2026 5:20:15 PM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1607,7 +1613,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/19/2026 8:59:02 PM</t>
+          <t>07/21/2026 4:39:25 PM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1632,7 +1638,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1656,22 +1662,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/18/2026 7:39:22 AM</t>
+          <t>07/21/2026 4:37:50 PM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>683 - Heavy</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dwayne Manuel</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1705,22 +1711,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/17/2026 10:14:38 PM</t>
+          <t>07/21/2026 3:29:43 PM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jeremy Myers</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Towing and Recovery</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1730,13 +1736,13 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -1754,20 +1760,24 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/17/2026 12:31:29 PM</t>
+          <t>07/21/2026 11:16:15 AM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>683 - Heavy</t>
+          <t>693 - Heavy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Gary Worley</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Adam Johnson</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Active Drivers, Heavy Haul</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>HAAS Alert, Heavy Haul</t>
@@ -1775,13 +1785,13 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -1789,34 +1799,28 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N28" t="n">
+        <v>0.606</v>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/17/2026 6:43:14 AM</t>
+          <t>07/21/2026 10:51:17 AM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>668 - Light</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Joshua Barrow</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -1824,13 +1828,13 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -1838,25 +1842,27 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="n">
-        <v>0.621</v>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/16/2026 5:36:25 PM</t>
+          <t>07/20/2026 4:04:35 PM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1895,17 +1901,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/16/2026 12:12:35 PM</t>
+          <t>07/20/2026 6:42:29 AM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1920,7 +1926,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -1944,7 +1950,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/16/2026 9:50:11 AM</t>
+          <t>07/19/2026 8:59:02 PM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1993,32 +1999,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/15/2026 3:39:09 PM</t>
+          <t>07/18/2026 7:39:22 AM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>683 - Heavy</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Dwayne Manuel</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -2042,17 +2048,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/15/2026 1:05:54 PM</t>
+          <t>07/17/2026 10:14:38 PM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2062,7 +2068,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2091,27 +2097,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/13/2026 5:04:35 PM</t>
+          <t>07/17/2026 12:31:29 PM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>668 - Light</t>
+          <t>683 - Heavy</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Gary Worley</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2140,7 +2142,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/12/2026 6:59:51 PM</t>
+          <t>07/17/2026 6:43:14 AM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2165,7 +2167,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2179,17 +2181,15 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N36" t="n">
+        <v>0.621</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/09/2026 9:14:20 PM</t>
+          <t>07/16/2026 5:36:25 PM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2238,17 +2238,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/09/2026 1:48:10 PM</t>
+          <t>07/16/2026 12:12:35 PM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>649 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Juan Ramirez</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2258,18 +2258,18 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -2287,17 +2287,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/08/2026 8:35:24 PM</t>
+          <t>07/16/2026 9:50:11 AM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2326,25 +2326,27 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="n">
-        <v>0.52</v>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/08/2026 10:10:13 AM</t>
+          <t>07/15/2026 3:39:09 PM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jammie Singleton</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2359,7 +2361,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -2383,17 +2385,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/07/2026 7:49:42 PM</t>
+          <t>07/15/2026 1:05:54 PM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2403,7 +2405,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2432,17 +2434,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/07/2026 7:36:21 PM</t>
+          <t>07/13/2026 5:04:35 PM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>668 - Light</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2481,17 +2483,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/07/2026 1:55:40 PM</t>
+          <t>07/12/2026 6:59:51 PM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2501,7 +2503,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2530,17 +2532,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/03/2026 2:40:22 PM</t>
+          <t>07/09/2026 9:14:20 PM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2550,12 +2552,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -2579,17 +2581,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/02/2026 4:49:00 PM</t>
+          <t>07/09/2026 1:48:10 PM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>649 - Heavy</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Juan Ramirez</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2604,13 +2606,13 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -2628,38 +2630,38 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/02/2026 2:57:58 PM</t>
+          <t>07/08/2026 8:35:24 PM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>641 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Adam Johnson</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -2667,30 +2669,32 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N46" t="n">
+        <v>0.52</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/01/2026 12:35:29 PM</t>
+          <t>07/08/2026 10:10:13 AM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Phillip Metz</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Jammie Singleton</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -2698,13 +2702,13 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -2722,17 +2726,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/01/2026 11:01:54 AM</t>
+          <t>07/07/2026 7:49:42 PM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2771,17 +2775,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06/30/2026 6:33:35 PM</t>
+          <t>07/07/2026 7:36:21 PM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2791,12 +2795,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -2820,7 +2824,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06/30/2026 3:45:32 PM</t>
+          <t>07/07/2026 1:55:40 PM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2869,32 +2873,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/30/2026 2:25:53 AM</t>
+          <t>07/03/2026 2:40:22 PM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jeremy Myers</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -2918,28 +2922,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06/29/2026 11:23:34 AM</t>
+          <t>07/02/2026 4:49:00 PM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>646 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Harley Tidwell</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>Jason Walker</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -2963,22 +2971,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/29/2026 10:19:27 AM</t>
+          <t>07/02/2026 2:57:58 PM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>641 - Heavy</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Adam Johnson</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2988,13 +2996,13 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -3012,24 +3020,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06/29/2026 8:54:50 AM</t>
+          <t>07/01/2026 12:35:29 PM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jeremy Myers</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Phillip Metz</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -3037,13 +3041,13 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -3061,23 +3065,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06/28/2026 8:19:03 PM</t>
+          <t>07/01/2026 11:01:54 AM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>683 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Gary Worley</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3106,17 +3114,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/27/2026 5:25:06 PM</t>
+          <t>06/30/2026 6:33:35 PM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3126,12 +3134,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -3155,17 +3163,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/26/2026 3:27:58 PM</t>
+          <t>06/30/2026 3:45:32 PM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3175,7 +3183,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3204,24 +3212,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/25/2026 4:46:02 PM</t>
+          <t>06/30/2026 2:25:53 AM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>629 - Heavy</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+          <t>667 - Medium</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Jeremy Myers</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -3245,24 +3261,20 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/25/2026 11:15:11 AM</t>
+          <t>06/29/2026 11:23:34 AM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>646 - Medium</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Harley Tidwell</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -3270,7 +3282,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -3284,32 +3296,42 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="n">
-        <v>0.673</v>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/25/2026 10:09:43 AM</t>
+          <t>06/29/2026 10:19:27 AM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>668 - Light</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+          <t>669 - Heavy</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Jason Walker</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -3333,32 +3355,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/24/2026 1:15:17 PM</t>
+          <t>06/29/2026 8:54:50 AM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Jeremy Myers</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Towing and Recovery</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -3382,32 +3404,28 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06/23/2026 11:02:05 AM</t>
+          <t>06/28/2026 8:19:03 PM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>683 - Heavy</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Gary Worley</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -3421,46 +3439,48 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="n">
-        <v>0.55</v>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06/22/2026 11:26:05 AM</t>
+          <t>06/27/2026 5:25:06 PM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>692 - Heavy</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>William Foley</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -3478,12 +3498,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06/19/2026 4:15:44 PM</t>
+          <t>06/26/2026 3:27:58 PM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3527,24 +3547,16 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06/17/2026 5:02:17 PM</t>
+          <t>06/25/2026 4:46:02 PM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>683 - Heavy</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Dwayne Manuel</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Active Drivers, Heavy Haul</t>
-        </is>
-      </c>
+          <t>629 - Heavy</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>HAAS Alert, Heavy Haul</t>
@@ -3558,7 +3570,7 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -3576,12 +3588,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06/17/2026 11:28:09 AM</t>
+          <t>06/25/2026 11:15:11 AM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3601,7 +3613,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -3615,34 +3627,24 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N66" t="n">
+        <v>0.673</v>
       </c>
       <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06/15/2026 5:53:31 PM</t>
+          <t>06/25/2026 10:09:43 AM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Jesus Carbajal</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>668 - Light</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -3674,7 +3676,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06/15/2026 1:23:54 PM</t>
+          <t>06/24/2026 1:15:17 PM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3699,7 +3701,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -3723,20 +3725,24 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>06/14/2026 11:39:04 AM</t>
+          <t>06/23/2026 11:02:05 AM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -3744,13 +3750,13 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -3758,48 +3764,46 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N69" t="n">
+        <v>0.55</v>
       </c>
       <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>06/14/2026 9:48:42 AM</t>
+          <t>06/22/2026 11:26:05 AM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>644 - Medium</t>
+          <t>692 - Heavy</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>William Foley</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -3817,20 +3821,24 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>06/13/2026 5:24:44 PM</t>
+          <t>06/19/2026 4:15:44 PM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>Paul Kunze Jr</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -3844,7 +3852,7 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -3862,28 +3870,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>06/13/2026 4:18:06 PM</t>
+          <t>06/17/2026 5:02:17 PM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>683 - Heavy</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Dwayne Manuel</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Active Drivers, Heavy Haul</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -3907,17 +3919,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>06/12/2026 9:27:53 AM</t>
+          <t>06/17/2026 11:28:09 AM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>644 - Medium</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3932,7 +3944,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -3956,7 +3968,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>06/11/2026 10:09:35 PM</t>
+          <t>06/15/2026 5:53:31 PM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3981,7 +3993,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -4005,17 +4017,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>06/10/2026 10:04:03 AM</t>
+          <t>06/15/2026 1:23:54 PM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4054,32 +4066,28 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>06/07/2026 2:14:46 PM</t>
+          <t>06/14/2026 11:39:04 AM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>673 - Heavy</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Kyle Ray</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Christopher Marcantel</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -4103,17 +4111,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>06/06/2026 8:18:21 AM</t>
+          <t>06/14/2026 9:48:42 AM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>696 - Medium</t>
+          <t>644 - Medium</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Jammie Singleton</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4152,15 +4160,19 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>06/04/2026 2:15:03 PM</t>
+          <t>06/13/2026 5:24:44 PM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>644 - Medium</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>685 - Medium</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Christopher Marcantel</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
@@ -4175,7 +4187,7 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -4193,34 +4205,34 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>06/03/2026 10:10:14 AM</t>
+          <t>06/13/2026 4:18:06 PM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>632 - Heavy</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Gary Worley</t>
+          <t>Christopher Marcantel</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -4238,38 +4250,38 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>05/29/2026 12:42:54 PM</t>
+          <t>06/12/2026 9:27:53 AM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>692 - Heavy</t>
+          <t>644 - Medium</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kyle Ray</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -4287,28 +4299,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>05/28/2026 4:24:20 PM</t>
+          <t>06/11/2026 10:09:35 PM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>632 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Gary Worley</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -4332,22 +4348,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>05/28/2026 1:48:42 PM</t>
+          <t>06/10/2026 10:04:03 AM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>660 - Heavy</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Billy Johnson</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Active Drivers, HAAS Alert, Heavy Haul, Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4357,13 +4373,13 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -4381,28 +4397,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>05/28/2026 12:14:01 AM</t>
+          <t>06/07/2026 2:14:46 PM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>673 - Heavy</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>Kyle Ray</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -4426,17 +4446,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>05/23/2026 10:35:24 AM</t>
+          <t>06/06/2026 8:18:21 AM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>696 - Medium</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Jammie Singleton</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4446,12 +4466,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -4475,19 +4495,15 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>05/20/2026 10:02:55 PM</t>
+          <t>06/04/2026 2:15:03 PM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
+          <t>644 - Medium</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
@@ -4502,7 +4518,7 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -4520,24 +4536,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>05/20/2026 5:13:08 PM</t>
+          <t>06/03/2026 10:10:14 AM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>632 - Heavy</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Gary Worley</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>HAAS Alert, Heavy Haul</t>
@@ -4569,23 +4581,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>05/19/2026 9:16:41 PM</t>
+          <t>05/29/2026 12:42:54 PM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>692 - Heavy</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
+          <t>Kyle Ray</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4614,23 +4630,23 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>05/17/2026 12:48:35 PM</t>
+          <t>05/28/2026 4:24:20 PM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>632 - Heavy</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
+          <t>Gary Worley</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4641,7 +4657,7 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -4659,28 +4675,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>05/16/2026 9:21:16 PM</t>
+          <t>05/28/2026 1:48:42 PM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>660 - Heavy</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
+          <t>Billy Johnson</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Active Drivers, HAAS Alert, Heavy Haul, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -4704,28 +4724,28 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>05/15/2026 11:50:46 AM</t>
+          <t>05/28/2026 12:14:01 AM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>634 - Heavy</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Gary Worley</t>
+          <t>Christopher Marcantel</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -4749,17 +4769,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>05/08/2026 1:47:14 AM</t>
+          <t>05/23/2026 10:35:24 AM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4769,12 +4789,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -4798,24 +4818,20 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>05/06/2026 6:15:28 PM</t>
+          <t>05/20/2026 10:02:55 PM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Christopher Marcantel</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -4823,13 +4839,13 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -4847,22 +4863,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>05/06/2026 10:49:01 AM</t>
+          <t>05/20/2026 5:13:08 PM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>673 - Heavy</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kyle Ray</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4872,13 +4888,13 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -4893,6 +4909,186 @@
       </c>
       <c r="O93" t="inlineStr"/>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>05/19/2026 9:16:41 PM</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>685 - Medium</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Christopher Marcantel</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Inattentive Driving</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>05/17/2026 12:48:35 PM</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>685 - Medium</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Christopher Marcantel</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>05/16/2026 9:21:16 PM</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>685 - Medium</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Christopher Marcantel</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>05/15/2026 11:50:46 AM</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>634 - Heavy</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Gary Worley</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Heavy Haul</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,24 +496,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/06/2026 2:18:16 PM</t>
+          <t>08/14/2026 6:11:59 PM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Jason Walker</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>629 - Heavy</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>HAAS Alert, Heavy Haul</t>
@@ -521,7 +513,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -545,17 +537,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/06/2026 8:19:00 AM</t>
+          <t>08/14/2026 2:51:01 PM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>696 - Medium</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jammie Singleton</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -565,7 +557,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -594,17 +586,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/05/2026 5:42:28 PM</t>
+          <t>08/14/2026 7:46:37 AM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -614,7 +606,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -643,17 +635,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/05/2026 3:33:14 PM</t>
+          <t>08/13/2026 6:33:21 PM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -692,24 +684,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/04/2026 2:28:07 PM</t>
+          <t>08/13/2026 11:59:27 AM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Jason Walker</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>694 - Heavy</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>HAAS Alert, Heavy Haul</t>
@@ -717,7 +701,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -741,17 +725,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/04/2026 12:31:14 PM</t>
+          <t>08/11/2026 4:41:04 PM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>649 - Heavy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Juan Ramirez</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -766,13 +750,13 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -790,17 +774,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/03/2026 2:39:43 PM</t>
+          <t>08/11/2026 4:04:10 PM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>649 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Juan Ramirez</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -810,12 +794,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -839,38 +823,38 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/03/2026 2:36:38 PM</t>
+          <t>08/11/2026 10:56:24 AM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>649 - Heavy</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Juan Ramirez</t>
+          <t>Jeremy Myers</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Towing and Recovery</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -878,42 +862,40 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N9" t="n">
+        <v>0.672</v>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07/31/2026 1:16:01 PM</t>
+          <t>08/10/2026 5:26:28 PM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>662 - Heavy</t>
+          <t>668 - Light</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Drew Template</t>
+          <t>Jonathan Walters</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -937,22 +919,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07/31/2026 1:02:24 PM</t>
+          <t>08/09/2026 12:17:56 PM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jeremy Myers</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -962,13 +944,13 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -986,7 +968,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07/30/2026 6:11:26 PM</t>
+          <t>08/09/2026 7:57:46 AM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1011,7 +993,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1025,27 +1007,25 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N12" t="n">
+        <v>0.489</v>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/30/2026 5:19:23 PM</t>
+          <t>08/07/2026 6:45:51 PM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1084,17 +1064,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/27/2026 3:31:40 PM</t>
+          <t>08/06/2026 2:18:16 PM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>696 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1104,12 +1084,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1133,27 +1113,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/27/2026 10:23:43 AM</t>
+          <t>08/06/2026 8:19:00 AM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>693 - Heavy</t>
+          <t>696 - Medium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jonathan Dubose</t>
+          <t>Jammie Singleton</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1164,7 +1144,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1182,17 +1162,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/27/2026 8:16:05 AM</t>
+          <t>08/05/2026 5:42:28 PM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1202,7 +1182,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1231,7 +1211,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/24/2026 6:37:41 PM</t>
+          <t>08/05/2026 3:33:14 PM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1256,7 +1236,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1270,25 +1250,27 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
-        <v>0.5610000000000001</v>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/24/2026 5:53:45 PM</t>
+          <t>08/04/2026 2:28:07 PM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1298,12 +1280,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1327,17 +1309,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/24/2026 10:43:08 AM</t>
+          <t>08/04/2026 12:31:14 PM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1347,12 +1329,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1376,17 +1358,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/23/2026 12:53:44 PM</t>
+          <t>08/03/2026 2:39:43 PM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>693 - Heavy</t>
+          <t>649 - Heavy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Juan Ramirez</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1401,7 +1383,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1425,17 +1407,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/23/2026 12:28:42 PM</t>
+          <t>08/03/2026 2:36:38 PM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>649 - Heavy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Juan Ramirez</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1445,12 +1427,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1474,30 +1456,38 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/23/2026 5:35:45 AM</t>
+          <t>07/31/2026 1:16:01 PM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+          <t>662 - Heavy</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Drew Template</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Active Drivers, Heavy Haul</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1515,38 +1505,38 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/22/2026 5:03:30 PM</t>
+          <t>07/31/2026 1:02:24 PM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Jeremy Myers</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Towing and Recovery</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1564,17 +1554,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/21/2026 5:20:15 PM</t>
+          <t>07/30/2026 6:11:26 PM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1613,7 +1603,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/21/2026 4:39:25 PM</t>
+          <t>07/30/2026 5:19:23 PM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1638,7 +1628,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1662,17 +1652,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/21/2026 4:37:50 PM</t>
+          <t>07/27/2026 3:31:40 PM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>696 - Medium</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1682,7 +1672,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1711,32 +1701,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/21/2026 3:29:43 PM</t>
+          <t>07/27/2026 10:23:43 AM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>693 - Heavy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jeremy Myers</t>
+          <t>Jonathan Dubose</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1760,38 +1750,38 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/21/2026 11:16:15 AM</t>
+          <t>07/27/2026 8:16:05 AM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>693 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Adam Johnson</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -1799,28 +1789,34 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="n">
-        <v>0.606</v>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/21/2026 10:51:17 AM</t>
+          <t>07/24/2026 6:37:41 PM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>668 - Light</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Joshua Barrow</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -1828,13 +1824,13 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -1842,27 +1838,25 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N29" t="n">
+        <v>0.5610000000000001</v>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/20/2026 4:04:35 PM</t>
+          <t>07/24/2026 5:53:45 PM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1901,17 +1895,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/20/2026 6:42:29 AM</t>
+          <t>07/24/2026 10:43:08 AM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1926,7 +1920,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -1950,17 +1944,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/19/2026 8:59:02 PM</t>
+          <t>07/23/2026 12:53:44 PM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>693 - Heavy</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1970,7 +1964,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1999,32 +1993,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/18/2026 7:39:22 AM</t>
+          <t>07/23/2026 12:28:42 PM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>683 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dwayne Manuel</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -2048,24 +2042,16 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/17/2026 10:14:38 PM</t>
+          <t>07/23/2026 5:35:45 AM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>685 - Medium</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -2073,7 +2059,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -2097,20 +2083,24 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/17/2026 12:31:29 PM</t>
+          <t>07/22/2026 5:03:30 PM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>683 - Heavy</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Gary Worley</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Thomas Neff III</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>HAAS Alert, Heavy Haul</t>
@@ -2142,17 +2132,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/17/2026 6:43:14 AM</t>
+          <t>07/21/2026 5:20:15 PM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2167,7 +2157,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2181,25 +2171,27 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="n">
-        <v>0.621</v>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/16/2026 5:36:25 PM</t>
+          <t>07/21/2026 4:39:25 PM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2214,7 +2206,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -2238,17 +2230,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/16/2026 12:12:35 PM</t>
+          <t>07/21/2026 4:37:50 PM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2258,12 +2250,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -2287,22 +2279,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/16/2026 9:50:11 AM</t>
+          <t>07/21/2026 3:29:43 PM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Jeremy Myers</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Towing and Recovery</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2312,13 +2304,13 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -2336,38 +2328,38 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/15/2026 3:39:09 PM</t>
+          <t>07/21/2026 11:16:15 AM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>693 - Heavy</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Adam Johnson</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -2375,37 +2367,31 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N40" t="n">
+        <v>0.606</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/15/2026 1:05:54 PM</t>
+          <t>07/21/2026 10:51:17 AM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>668 - Light</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Joshua Barrow</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2416,7 +2402,7 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -2434,17 +2420,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/13/2026 5:04:35 PM</t>
+          <t>07/20/2026 4:04:35 PM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>668 - Light</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2483,7 +2469,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/12/2026 6:59:51 PM</t>
+          <t>07/20/2026 6:42:29 AM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2532,17 +2518,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/09/2026 9:14:20 PM</t>
+          <t>07/19/2026 8:59:02 PM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2581,22 +2567,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/09/2026 1:48:10 PM</t>
+          <t>07/18/2026 7:39:22 AM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>649 - Heavy</t>
+          <t>683 - Heavy</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Juan Ramirez</t>
+          <t>Dwayne Manuel</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2606,7 +2592,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -2630,7 +2616,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/08/2026 8:35:24 PM</t>
+          <t>07/17/2026 10:14:38 PM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2669,40 +2655,38 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="n">
-        <v>0.52</v>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/08/2026 10:10:13 AM</t>
+          <t>07/17/2026 12:31:29 PM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>683 - Heavy</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jammie Singleton</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Gary Worley</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -2726,7 +2710,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/07/2026 7:49:42 PM</t>
+          <t>07/17/2026 6:43:14 AM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2751,7 +2735,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -2765,27 +2749,25 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N48" t="n">
+        <v>0.621</v>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/07/2026 7:36:21 PM</t>
+          <t>07/16/2026 5:36:25 PM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2824,17 +2806,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/07/2026 1:55:40 PM</t>
+          <t>07/16/2026 9:50:11 AM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2844,7 +2826,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2873,7 +2855,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/03/2026 2:40:22 PM</t>
+          <t>07/15/2026 1:05:54 PM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2898,7 +2880,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -2922,17 +2904,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/02/2026 4:49:00 PM</t>
+          <t>07/13/2026 5:04:35 PM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>668 - Light</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2942,7 +2924,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2971,38 +2953,38 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/02/2026 2:57:58 PM</t>
+          <t>07/12/2026 6:59:51 PM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>641 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Adam Johnson</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -3020,7 +3002,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/01/2026 12:35:29 PM</t>
+          <t>07/09/2026 9:14:20 PM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3030,10 +3012,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Phillip Metz</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>Paul Kunze Jr</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -3047,7 +3033,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -3065,17 +3051,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/01/2026 11:01:54 AM</t>
+          <t>07/09/2026 1:48:10 PM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>649 - Heavy</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Juan Ramirez</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3085,18 +3071,18 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -3114,17 +3100,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06/30/2026 6:33:35 PM</t>
+          <t>07/08/2026 8:35:24 PM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3134,12 +3120,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -3153,27 +3139,25 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N56" t="n">
+        <v>0.52</v>
       </c>
       <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06/30/2026 3:45:32 PM</t>
+          <t>07/08/2026 10:10:13 AM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Jammie Singleton</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3183,12 +3167,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -3212,22 +3196,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06/30/2026 2:25:53 AM</t>
+          <t>07/07/2026 7:49:42 PM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jeremy Myers</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3237,7 +3221,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -3261,20 +3245,24 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06/29/2026 11:23:34 AM</t>
+          <t>07/07/2026 7:36:21 PM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>646 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Harley Tidwell</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -3282,7 +3270,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -3306,17 +3294,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06/29/2026 10:19:27 AM</t>
+          <t>07/07/2026 1:55:40 PM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3331,7 +3319,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -3355,27 +3343,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06/29/2026 8:54:50 AM</t>
+          <t>07/03/2026 2:40:22 PM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jeremy Myers</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3404,20 +3392,24 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06/28/2026 8:19:03 PM</t>
+          <t>07/02/2026 4:49:00 PM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>683 - Heavy</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Gary Worley</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>Jason Walker</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>HAAS Alert, Heavy Haul</t>
@@ -3449,38 +3441,38 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06/27/2026 5:25:06 PM</t>
+          <t>07/02/2026 2:57:58 PM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>641 - Heavy</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Adam Johnson</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -3498,24 +3490,20 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06/26/2026 3:27:58 PM</t>
+          <t>07/01/2026 12:35:29 PM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Phillip Metz</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -3529,7 +3517,7 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -3547,19 +3535,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06/25/2026 4:46:02 PM</t>
+          <t>07/01/2026 11:01:54 AM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>629 - Heavy</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+          <t>680 - Medium</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3588,17 +3584,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06/25/2026 11:15:11 AM</t>
+          <t>06/30/2026 6:33:35 PM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3608,12 +3604,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -3627,27 +3623,37 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="n">
-        <v>0.673</v>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06/25/2026 10:09:43 AM</t>
+          <t>06/30/2026 3:45:32 PM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>668 - Light</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
+          <t>659 - Heavy</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Thomas Neff III</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3676,32 +3682,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06/24/2026 1:15:17 PM</t>
+          <t>06/30/2026 2:25:53 AM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Jeremy Myers</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Towing and Recovery</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -3725,24 +3731,20 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>06/23/2026 11:02:05 AM</t>
+          <t>06/29/2026 11:23:34 AM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>646 - Medium</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Harley Tidwell</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -3750,7 +3752,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3764,30 +3766,32 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="n">
-        <v>0.55</v>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>06/22/2026 11:26:05 AM</t>
+          <t>06/29/2026 10:19:27 AM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>692 - Heavy</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>William Foley</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3797,13 +3801,13 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -3821,22 +3825,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>06/19/2026 4:15:44 PM</t>
+          <t>06/29/2026 8:54:50 AM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jeremy Myers</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Towing and Recovery</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3846,7 +3850,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3870,7 +3874,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>06/17/2026 5:02:17 PM</t>
+          <t>06/28/2026 8:19:03 PM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3880,14 +3884,10 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dwayne Manuel</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Active Drivers, Heavy Haul</t>
-        </is>
-      </c>
+          <t>Gary Worley</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>HAAS Alert, Heavy Haul</t>
@@ -3901,7 +3901,7 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -3919,7 +3919,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>06/17/2026 11:28:09 AM</t>
+          <t>06/27/2026 5:25:06 PM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3968,17 +3968,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>06/15/2026 5:53:31 PM</t>
+          <t>06/26/2026 3:27:58 PM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4017,24 +4017,16 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>06/15/2026 1:23:54 PM</t>
+          <t>06/25/2026 4:46:02 PM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Jason Walker</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>629 - Heavy</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>HAAS Alert, Heavy Haul</t>
@@ -4066,20 +4058,24 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>06/14/2026 11:39:04 AM</t>
+          <t>06/25/2026 11:15:11 AM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -4087,13 +4083,13 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -4101,34 +4097,24 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N76" t="n">
+        <v>0.673</v>
       </c>
       <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>06/14/2026 9:48:42 AM</t>
+          <t>06/25/2026 10:09:43 AM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>644 - Medium</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>668 - Light</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -4160,34 +4146,38 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>06/13/2026 5:24:44 PM</t>
+          <t>06/24/2026 1:15:17 PM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>Jason Walker</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -4205,20 +4195,24 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>06/13/2026 4:18:06 PM</t>
+          <t>06/23/2026 11:02:05 AM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -4226,13 +4220,13 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -4240,48 +4234,46 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N79" t="n">
+        <v>0.55</v>
       </c>
       <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>06/12/2026 9:27:53 AM</t>
+          <t>06/22/2026 11:26:05 AM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>644 - Medium</t>
+          <t>692 - Heavy</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>William Foley</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -4299,17 +4291,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>06/11/2026 10:09:35 PM</t>
+          <t>06/19/2026 4:15:44 PM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4324,7 +4316,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -4348,22 +4340,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>06/10/2026 10:04:03 AM</t>
+          <t>06/17/2026 5:02:17 PM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>683 - Heavy</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Dwayne Manuel</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4379,7 +4371,7 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -4397,38 +4389,38 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>06/07/2026 2:14:46 PM</t>
+          <t>06/17/2026 11:28:09 AM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>673 - Heavy</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Kyle Ray</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -4446,17 +4438,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>06/06/2026 8:18:21 AM</t>
+          <t>06/15/2026 5:53:31 PM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>696 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jammie Singleton</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4495,19 +4487,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>06/04/2026 2:15:03 PM</t>
+          <t>06/15/2026 1:23:54 PM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>644 - Medium</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
+          <t>669 - Heavy</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Jason Walker</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4536,34 +4536,34 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>06/03/2026 10:10:14 AM</t>
+          <t>06/14/2026 11:39:04 AM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>632 - Heavy</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Gary Worley</t>
+          <t>Christopher Marcantel</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -4581,38 +4581,38 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>05/29/2026 12:42:54 PM</t>
+          <t>06/14/2026 9:48:42 AM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>692 - Heavy</t>
+          <t>644 - Medium</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kyle Ray</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -4630,34 +4630,34 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>05/28/2026 4:24:20 PM</t>
+          <t>06/13/2026 5:24:44 PM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>632 - Heavy</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Gary Worley</t>
+          <t>Christopher Marcantel</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -4675,32 +4675,28 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>05/28/2026 1:48:42 PM</t>
+          <t>06/13/2026 4:18:06 PM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>660 - Heavy</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Billy Johnson</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Active Drivers, HAAS Alert, Heavy Haul, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Christopher Marcantel</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -4724,20 +4720,24 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>05/28/2026 12:14:01 AM</t>
+          <t>06/12/2026 9:27:53 AM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>644 - Medium</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>Paul Kunze Jr</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -4751,7 +4751,7 @@
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -4769,17 +4769,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>05/23/2026 10:35:24 AM</t>
+          <t>06/11/2026 10:09:35 PM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -4818,23 +4818,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>05/20/2026 10:02:55 PM</t>
+          <t>06/10/2026 10:04:03 AM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
+          <t>Thomas Neff III</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4845,7 +4849,7 @@
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -4863,22 +4867,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>05/20/2026 5:13:08 PM</t>
+          <t>06/07/2026 2:14:46 PM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>673 - Heavy</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Kyle Ray</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4888,13 +4892,13 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -4912,20 +4916,24 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>05/19/2026 9:16:41 PM</t>
+          <t>06/06/2026 8:18:21 AM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>696 - Medium</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>Jammie Singleton</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -4933,13 +4941,13 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -4957,19 +4965,15 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>05/17/2026 12:48:35 PM</t>
+          <t>06/04/2026 2:15:03 PM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
+          <t>644 - Medium</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
@@ -4978,13 +4982,13 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -5002,23 +5006,23 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>05/16/2026 9:21:16 PM</t>
+          <t>06/03/2026 10:10:14 AM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>632 - Heavy</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
+          <t>Gary Worley</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5029,7 +5033,7 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -5047,20 +5051,24 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>05/15/2026 11:50:46 AM</t>
+          <t>05/29/2026 12:42:54 PM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>634 - Heavy</t>
+          <t>692 - Heavy</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Gary Worley</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
+          <t>Kyle Ray</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>HAAS Alert, Heavy Haul</t>
@@ -5068,7 +5076,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -5089,6 +5097,333 @@
       </c>
       <c r="O97" t="inlineStr"/>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>05/28/2026 4:24:20 PM</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>632 - Heavy</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Gary Worley</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Heavy Haul</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>05/28/2026 1:48:42 PM</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>660 - Heavy</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Billy Johnson</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Active Drivers, HAAS Alert, Heavy Haul, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Heavy Haul</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Following Distance</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>05/28/2026 12:14:01 AM</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>685 - Medium</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Christopher Marcantel</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Mobile Usage</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>05/23/2026 10:35:24 AM</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>669 - Heavy</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Jason Walker</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Heavy Haul</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>05/20/2026 10:02:55 PM</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>685 - Medium</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Christopher Marcantel</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Mobile Usage</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>05/20/2026 5:13:08 PM</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>659 - Heavy</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Thomas Neff III</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Heavy Haul</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>05/19/2026 9:16:41 PM</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>685 - Medium</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Christopher Marcantel</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Inattentive Driving</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -496,24 +496,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/14/2026 6:11:59 PM</t>
+          <t>08/20/2026 12:54:58 PM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>629 - Heavy</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+          <t>680 - Medium</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -537,17 +545,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/14/2026 2:51:01 PM</t>
+          <t>08/20/2026 12:25:18 PM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -557,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -586,22 +594,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/14/2026 7:46:37 AM</t>
+          <t>08/20/2026 10:30:15 AM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>668 - Light</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Adam Johnson</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -611,7 +619,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -635,27 +643,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/13/2026 6:33:21 PM</t>
+          <t>08/18/2026 7:41:40 AM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>629 - Heavy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t xml:space="preserve">Clint Winwood </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Towing and Recovery</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -666,7 +674,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -684,16 +692,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/13/2026 11:59:27 AM</t>
+          <t>08/17/2026 2:57:01 PM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>694 - Heavy</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+          <t>629 - Heavy</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clint Winwood </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>HAAS Alert, Heavy Haul</t>
@@ -707,7 +723,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -725,17 +741,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/11/2026 4:41:04 PM</t>
+          <t>08/17/2026 2:08:31 PM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>649 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Juan Ramirez</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -745,18 +761,18 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -774,17 +790,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/11/2026 4:04:10 PM</t>
+          <t>08/17/2026 11:09:15 AM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -799,7 +815,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -823,38 +839,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/11/2026 10:56:24 AM</t>
+          <t>08/14/2026 6:11:59 PM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Jeremy Myers</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Towing and Recovery</t>
-        </is>
-      </c>
+          <t>629 - Heavy</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -862,35 +870,37 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
-        <v>0.672</v>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/10/2026 5:26:28 PM</t>
+          <t>08/14/2026 2:51:01 PM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>668 - Light</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jonathan Walters</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>HAAS Alert, Heavy Haul</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -901,7 +911,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -919,17 +929,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/09/2026 12:17:56 PM</t>
+          <t>08/14/2026 7:46:37 AM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -968,7 +978,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/09/2026 7:57:46 AM</t>
+          <t>08/13/2026 6:33:21 PM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -993,7 +1003,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1007,35 +1017,29 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
-        <v>0.489</v>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/07/2026 6:45:51 PM</t>
+          <t>08/13/2026 11:59:27 AM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>694 - Heavy</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1064,17 +1068,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/06/2026 2:18:16 PM</t>
+          <t>08/11/2026 4:41:04 PM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>649 - Heavy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Juan Ramirez</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1089,13 +1093,13 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1113,17 +1117,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/06/2026 8:19:00 AM</t>
+          <t>08/11/2026 4:04:10 PM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>696 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jammie Singleton</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1162,38 +1166,34 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/05/2026 5:42:28 PM</t>
+          <t>08/11/2026 10:56:24 AM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Jeremy Myers</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1201,32 +1201,30 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N16" t="n">
+        <v>0.672</v>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/05/2026 3:33:14 PM</t>
+          <t>08/10/2026 5:26:28 PM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>668 - Light</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Jonathan Walters</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1242,7 +1240,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1260,17 +1258,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/04/2026 2:28:07 PM</t>
+          <t>08/09/2026 12:17:56 PM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1280,12 +1278,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1309,17 +1307,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/04/2026 12:31:14 PM</t>
+          <t>08/09/2026 7:57:46 AM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1329,12 +1327,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1348,27 +1346,25 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N19" t="n">
+        <v>0.489</v>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/03/2026 2:39:43 PM</t>
+          <t>08/07/2026 6:45:51 PM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>649 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Juan Ramirez</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1378,12 +1374,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1407,17 +1403,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/03/2026 2:36:38 PM</t>
+          <t>08/06/2026 2:18:16 PM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>649 - Heavy</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Juan Ramirez</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1432,7 +1428,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1456,38 +1452,38 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/31/2026 1:16:01 PM</t>
+          <t>08/06/2026 8:19:00 AM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>662 - Heavy</t>
+          <t>696 - Medium</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Drew Template</t>
+          <t>Jammie Singleton</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1505,38 +1501,38 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/31/2026 1:02:24 PM</t>
+          <t>08/05/2026 5:42:28 PM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jeremy Myers</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1554,17 +1550,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/30/2026 6:11:26 PM</t>
+          <t>08/05/2026 3:33:14 PM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1603,17 +1599,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/30/2026 5:19:23 PM</t>
+          <t>08/04/2026 2:28:07 PM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1623,12 +1619,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1652,17 +1648,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/27/2026 3:31:40 PM</t>
+          <t>08/04/2026 12:31:14 PM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>696 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1672,12 +1668,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -1701,22 +1697,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/27/2026 10:23:43 AM</t>
+          <t>08/03/2026 2:39:43 PM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>693 - Heavy</t>
+          <t>649 - Heavy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jonathan Dubose</t>
+          <t>Juan Ramirez</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1726,13 +1722,13 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -1750,17 +1746,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/27/2026 8:16:05 AM</t>
+          <t>08/03/2026 2:36:38 PM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>649 - Heavy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Juan Ramirez</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1770,12 +1766,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1799,38 +1795,38 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/24/2026 6:37:41 PM</t>
+          <t>07/31/2026 1:16:01 PM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>662 - Heavy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Drew Template</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -1838,32 +1834,30 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="n">
-        <v>0.5610000000000001</v>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/24/2026 5:53:45 PM</t>
+          <t>07/31/2026 1:02:24 PM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Jeremy Myers</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -1871,13 +1865,13 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -1895,17 +1889,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/24/2026 10:43:08 AM</t>
+          <t>07/30/2026 6:11:26 PM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1920,7 +1914,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -1944,17 +1938,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/23/2026 12:53:44 PM</t>
+          <t>07/30/2026 5:19:23 PM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>693 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1964,7 +1958,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1993,12 +1987,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/23/2026 12:28:42 PM</t>
+          <t>07/27/2026 3:31:40 PM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>696 - Medium</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2018,7 +2012,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -2042,30 +2036,38 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/23/2026 5:35:45 AM</t>
+          <t>07/27/2026 10:23:43 AM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+          <t>693 - Heavy</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Jonathan Dubose</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Active Drivers, Heavy Haul</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -2083,17 +2085,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/22/2026 5:03:30 PM</t>
+          <t>07/27/2026 8:16:05 AM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2103,7 +2105,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2132,7 +2134,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/21/2026 5:20:15 PM</t>
+          <t>07/24/2026 6:37:41 PM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2157,7 +2159,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2171,27 +2173,25 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N36" t="n">
+        <v>0.5610000000000001</v>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/21/2026 4:39:25 PM</t>
+          <t>07/24/2026 5:53:45 PM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -2230,12 +2230,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/21/2026 4:37:50 PM</t>
+          <t>07/23/2026 12:53:44 PM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>693 - Heavy</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2279,24 +2279,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/21/2026 3:29:43 PM</t>
+          <t>07/23/2026 5:35:45 AM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Jeremy Myers</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Towing and Recovery</t>
-        </is>
-      </c>
+          <t>685 - Medium</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -2304,13 +2296,13 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -2328,22 +2320,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/21/2026 11:16:15 AM</t>
+          <t>07/22/2026 5:03:30 PM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>693 - Heavy</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Adam Johnson</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2353,13 +2345,13 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -2367,28 +2359,34 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="n">
-        <v>0.606</v>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/21/2026 10:51:17 AM</t>
+          <t>07/21/2026 5:20:15 PM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>668 - Light</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Joshua Barrow</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -2402,7 +2400,7 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -2420,17 +2418,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/20/2026 4:04:35 PM</t>
+          <t>07/21/2026 4:37:50 PM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2440,7 +2438,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2469,24 +2467,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/20/2026 6:42:29 AM</t>
+          <t>07/21/2026 3:29:43 PM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Jeremy Myers</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -2494,13 +2488,13 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -2518,38 +2512,38 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/19/2026 8:59:02 PM</t>
+          <t>07/21/2026 11:16:15 AM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>693 - Heavy</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Adam Johnson</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -2557,37 +2551,31 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N44" t="n">
+        <v>0.606</v>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/18/2026 7:39:22 AM</t>
+          <t>07/21/2026 10:51:17 AM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>683 - Heavy</t>
+          <t>668 - Light</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dwayne Manuel</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Active Drivers, Heavy Haul</t>
-        </is>
-      </c>
+          <t>Joshua Barrow</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2616,17 +2604,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/17/2026 10:14:38 PM</t>
+          <t>07/20/2026 4:04:35 PM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2665,23 +2653,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/17/2026 12:31:29 PM</t>
+          <t>07/20/2026 6:42:29 AM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>683 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Gary Worley</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Paul Kunze Jr</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2710,17 +2702,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/17/2026 6:43:14 AM</t>
+          <t>07/19/2026 8:59:02 PM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2735,7 +2727,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -2749,35 +2741,37 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="n">
-        <v>0.621</v>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/16/2026 5:36:25 PM</t>
+          <t>07/18/2026 7:39:22 AM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>683 - Heavy</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Dwayne Manuel</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2788,7 +2782,7 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -2806,17 +2800,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/16/2026 9:50:11 AM</t>
+          <t>07/17/2026 10:14:38 PM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2855,24 +2849,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/15/2026 1:05:54 PM</t>
+          <t>07/17/2026 12:31:29 PM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>683 - Heavy</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Gary Worley</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>HAAS Alert, Heavy Haul</t>
@@ -2904,12 +2894,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/13/2026 5:04:35 PM</t>
+          <t>07/17/2026 6:43:14 AM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>668 - Light</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2929,7 +2919,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -2943,17 +2933,15 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N52" t="n">
+        <v>0.621</v>
       </c>
       <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/12/2026 6:59:51 PM</t>
+          <t>07/16/2026 5:36:25 PM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3002,17 +2990,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/09/2026 9:14:20 PM</t>
+          <t>07/16/2026 9:50:11 AM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3051,17 +3039,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/09/2026 1:48:10 PM</t>
+          <t>07/15/2026 1:05:54 PM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>649 - Heavy</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Juan Ramirez</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3076,13 +3064,13 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -3100,12 +3088,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/08/2026 8:35:24 PM</t>
+          <t>07/13/2026 5:04:35 PM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>668 - Light</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3139,25 +3127,27 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="n">
-        <v>0.52</v>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/08/2026 10:10:13 AM</t>
+          <t>07/12/2026 6:59:51 PM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jammie Singleton</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3172,7 +3162,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -3196,7 +3186,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/07/2026 7:49:42 PM</t>
+          <t>07/09/2026 9:14:20 PM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3245,17 +3235,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/07/2026 7:36:21 PM</t>
+          <t>07/09/2026 1:48:10 PM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>649 - Heavy</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Juan Ramirez</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3265,18 +3255,18 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -3294,17 +3284,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/07/2026 1:55:40 PM</t>
+          <t>07/08/2026 8:35:24 PM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3314,7 +3304,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3333,27 +3323,25 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N60" t="n">
+        <v>0.52</v>
       </c>
       <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/03/2026 2:40:22 PM</t>
+          <t>07/08/2026 10:10:13 AM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Jammie Singleton</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3363,12 +3351,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -3392,17 +3380,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/02/2026 4:49:00 PM</t>
+          <t>07/07/2026 7:49:42 PM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3412,7 +3400,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3441,38 +3429,38 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/02/2026 2:57:58 PM</t>
+          <t>07/07/2026 7:36:21 PM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>641 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Adam Johnson</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -3490,23 +3478,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/01/2026 12:35:29 PM</t>
+          <t>07/07/2026 1:55:40 PM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Phillip Metz</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Thomas Neff III</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3517,7 +3509,7 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -3535,17 +3527,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/01/2026 11:01:54 AM</t>
+          <t>07/03/2026 2:40:22 PM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3555,12 +3547,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -3584,7 +3576,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06/30/2026 6:33:35 PM</t>
+          <t>07/02/2026 4:49:00 PM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3609,7 +3601,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -3633,22 +3625,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06/30/2026 3:45:32 PM</t>
+          <t>07/02/2026 2:57:58 PM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>641 - Heavy</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Adam Johnson</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3658,13 +3650,13 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -3682,24 +3674,20 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06/30/2026 2:25:53 AM</t>
+          <t>07/01/2026 12:35:29 PM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jeremy Myers</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Phillip Metz</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -3707,13 +3695,13 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -3731,20 +3719,24 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>06/29/2026 11:23:34 AM</t>
+          <t>07/01/2026 11:01:54 AM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>646 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Harley Tidwell</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -3752,7 +3744,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3776,7 +3768,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>06/29/2026 10:19:27 AM</t>
+          <t>06/30/2026 6:33:35 PM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3825,32 +3817,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>06/29/2026 8:54:50 AM</t>
+          <t>06/30/2026 3:45:32 PM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Jeremy Myers</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3874,28 +3866,28 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>06/28/2026 8:19:03 PM</t>
+          <t>06/30/2026 2:25:53 AM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>683 - Heavy</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Gary Worley</t>
+          <t>Jeremy Myers</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -3919,24 +3911,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>06/27/2026 5:25:06 PM</t>
+          <t>06/29/2026 11:23:34 AM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>646 - Medium</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Harley Tidwell</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -3944,7 +3932,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -3968,17 +3956,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>06/26/2026 3:27:58 PM</t>
+          <t>06/29/2026 10:19:27 AM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3988,12 +3976,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -4017,24 +4005,28 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>06/25/2026 4:46:02 PM</t>
+          <t>06/29/2026 8:54:50 AM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>629 - Heavy</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>667 - Medium</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Jeremy Myers</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -4058,32 +4050,28 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>06/25/2026 11:15:11 AM</t>
+          <t>06/28/2026 8:19:03 PM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>683 - Heavy</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Gary Worley</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -4097,24 +4085,34 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="n">
-        <v>0.673</v>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>06/25/2026 10:09:43 AM</t>
+          <t>06/27/2026 5:25:06 PM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>668 - Light</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
+          <t>685 - Medium</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Paul Kunze Jr</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -4122,7 +4120,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -4146,17 +4144,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>06/24/2026 1:15:17 PM</t>
+          <t>06/26/2026 3:27:58 PM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4166,12 +4164,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -4195,32 +4193,24 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>06/23/2026 11:02:05 AM</t>
+          <t>06/25/2026 4:46:02 PM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Jesus Carbajal</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>629 - Heavy</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -4234,46 +4224,48 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="n">
-        <v>0.55</v>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>06/22/2026 11:26:05 AM</t>
+          <t>06/25/2026 11:15:11 AM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>692 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>William Foley</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -4281,34 +4273,24 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N80" t="n">
+        <v>0.673</v>
       </c>
       <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>06/19/2026 4:15:44 PM</t>
+          <t>06/25/2026 10:09:43 AM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>668 - Light</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -4340,22 +4322,22 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>06/17/2026 5:02:17 PM</t>
+          <t>06/24/2026 1:15:17 PM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>683 - Heavy</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dwayne Manuel</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4365,13 +4347,13 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -4389,12 +4371,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>06/17/2026 11:28:09 AM</t>
+          <t>06/23/2026 11:02:05 AM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4414,7 +4396,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -4428,48 +4410,46 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N83" t="n">
+        <v>0.55</v>
       </c>
       <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>06/15/2026 5:53:31 PM</t>
+          <t>06/22/2026 11:26:05 AM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>692 - Heavy</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>William Foley</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -4487,17 +4467,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>06/15/2026 1:23:54 PM</t>
+          <t>06/19/2026 4:15:44 PM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4507,7 +4487,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4536,23 +4516,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>06/14/2026 11:39:04 AM</t>
+          <t>06/17/2026 5:02:17 PM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>683 - Heavy</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>Dwayne Manuel</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Active Drivers, Heavy Haul</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4581,17 +4565,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>06/14/2026 9:48:42 AM</t>
+          <t>06/17/2026 11:28:09 AM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>644 - Medium</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4606,7 +4590,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -4630,20 +4614,24 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>06/13/2026 5:24:44 PM</t>
+          <t>06/15/2026 5:53:31 PM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -4657,7 +4645,7 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -4675,34 +4663,38 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>06/13/2026 4:18:06 PM</t>
+          <t>06/15/2026 1:23:54 PM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
+          <t>Jason Walker</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -4720,24 +4712,20 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>06/12/2026 9:27:53 AM</t>
+          <t>06/14/2026 11:39:04 AM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>644 - Medium</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Christopher Marcantel</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -4751,7 +4739,7 @@
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -4769,17 +4757,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>06/11/2026 10:09:35 PM</t>
+          <t>06/14/2026 9:48:42 AM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>644 - Medium</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4794,7 +4782,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -4818,27 +4806,23 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>06/10/2026 10:04:03 AM</t>
+          <t>06/13/2026 5:24:44 PM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Christopher Marcantel</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4849,7 +4833,7 @@
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -4867,32 +4851,28 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>06/07/2026 2:14:46 PM</t>
+          <t>06/13/2026 4:18:06 PM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>673 - Heavy</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kyle Ray</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Christopher Marcantel</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -4916,17 +4896,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>06/06/2026 8:18:21 AM</t>
+          <t>06/12/2026 9:27:53 AM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>696 - Medium</t>
+          <t>644 - Medium</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jammie Singleton</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4965,16 +4945,24 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>06/04/2026 2:15:03 PM</t>
+          <t>06/11/2026 10:09:35 PM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>644 - Medium</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
+          <t>680 - Medium</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -4982,7 +4970,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -5006,20 +4994,24 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>06/03/2026 10:10:14 AM</t>
+          <t>06/10/2026 10:04:03 AM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>632 - Heavy</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Gary Worley</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>Thomas Neff III</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>HAAS Alert, Heavy Haul</t>
@@ -5027,7 +5019,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -5051,12 +5043,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>05/29/2026 12:42:54 PM</t>
+          <t>06/07/2026 2:14:46 PM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>692 - Heavy</t>
+          <t>673 - Heavy</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5076,7 +5068,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -5100,28 +5092,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>05/28/2026 4:24:20 PM</t>
+          <t>06/06/2026 8:18:21 AM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>632 - Heavy</t>
+          <t>696 - Medium</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Gary Worley</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
+          <t>Jammie Singleton</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -5145,38 +5141,30 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>05/28/2026 1:48:42 PM</t>
+          <t>06/04/2026 2:15:03 PM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>660 - Heavy</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Billy Johnson</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Active Drivers, HAAS Alert, Heavy Haul, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>644 - Medium</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -5194,34 +5182,34 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>05/28/2026 12:14:01 AM</t>
+          <t>06/03/2026 10:10:14 AM</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>632 - Heavy</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
+          <t>Gary Worley</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -5239,22 +5227,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>05/23/2026 10:35:24 AM</t>
+          <t>05/29/2026 12:42:54 PM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>692 - Heavy</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Kyle Ray</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5264,13 +5252,13 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -5288,34 +5276,34 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>05/20/2026 10:02:55 PM</t>
+          <t>05/28/2026 4:24:20 PM</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>632 - Heavy</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
+          <t>Gary Worley</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -5333,22 +5321,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>05/20/2026 5:13:08 PM</t>
+          <t>05/28/2026 1:48:42 PM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>660 - Heavy</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Billy Johnson</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, HAAS Alert, Heavy Haul, Towing and Recovery</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5358,13 +5346,13 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -5382,7 +5370,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>05/19/2026 9:16:41 PM</t>
+          <t>05/28/2026 12:14:01 AM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5403,7 +5391,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O104"/>
+  <dimension ref="A1:O109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,38 +496,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/20/2026 12:54:58 PM</t>
+          <t>08/23/2026 12:28:49 AM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>629 - Heavy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t xml:space="preserve">Clint Winwood </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Towing and Recovery</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -545,17 +545,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/20/2026 12:25:18 PM</t>
+          <t>08/21/2026 9:34:11 PM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -594,32 +594,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/20/2026 10:30:15 AM</t>
+          <t>08/21/2026 8:37:13 PM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>668 - Light</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Adam Johnson</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -643,17 +643,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/18/2026 7:41:40 AM</t>
+          <t>08/21/2026 6:17:21 PM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>629 - Heavy</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clint Winwood </t>
+          <t>Kody Addison</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -674,7 +674,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -692,17 +692,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/17/2026 2:57:01 PM</t>
+          <t>08/21/2026 12:33:22 PM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>629 - Heavy</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clint Winwood </t>
+          <t>Kody Addison</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -712,18 +712,18 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -741,17 +741,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/17/2026 2:08:31 PM</t>
+          <t>08/20/2026 12:54:58 PM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -790,7 +790,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/17/2026 11:09:15 AM</t>
+          <t>08/20/2026 12:25:18 PM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -839,24 +839,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/14/2026 6:11:59 PM</t>
+          <t>08/20/2026 10:30:15 AM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>629 - Heavy</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>668 - Light</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Adam Johnson</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Active Drivers, Heavy Haul</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -880,22 +888,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/14/2026 2:51:01 PM</t>
+          <t>08/18/2026 7:41:40 AM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>629 - Heavy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t xml:space="preserve">Clint Winwood </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Towing and Recovery</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -911,7 +919,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -929,27 +937,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/14/2026 7:46:37 AM</t>
+          <t>08/17/2026 2:57:01 PM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>629 - Heavy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t xml:space="preserve">Clint Winwood </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Towing and Recovery</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -960,7 +968,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -978,7 +986,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/13/2026 6:33:21 PM</t>
+          <t>08/17/2026 2:08:31 PM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1027,24 +1035,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/13/2026 11:59:27 AM</t>
+          <t>08/17/2026 11:09:15 AM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>694 - Heavy</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>680 - Medium</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1068,24 +1084,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/11/2026 4:41:04 PM</t>
+          <t>08/14/2026 6:11:59 PM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>649 - Heavy</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Juan Ramirez</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>629 - Heavy</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>HAAS Alert, Heavy Haul</t>
@@ -1093,13 +1101,13 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1117,17 +1125,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/11/2026 4:04:10 PM</t>
+          <t>08/14/2026 2:51:01 PM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1137,7 +1145,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1166,20 +1174,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/11/2026 10:56:24 AM</t>
+          <t>08/14/2026 7:46:37 AM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jeremy Myers</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Paul Kunze Jr</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -1187,13 +1199,13 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1201,30 +1213,32 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
-        <v>0.672</v>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/10/2026 5:26:28 PM</t>
+          <t>08/13/2026 6:33:21 PM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>668 - Light</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jonathan Walters</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1240,7 +1254,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1258,27 +1272,19 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/09/2026 12:17:56 PM</t>
+          <t>08/13/2026 11:59:27 AM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Jesus Carbajal</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>694 - Heavy</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1307,17 +1313,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/09/2026 7:57:46 AM</t>
+          <t>08/11/2026 4:41:04 PM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>649 - Heavy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Juan Ramirez</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1327,18 +1333,18 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1346,15 +1352,17 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="n">
-        <v>0.489</v>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/07/2026 6:45:51 PM</t>
+          <t>08/11/2026 4:04:10 PM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1403,38 +1411,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/06/2026 2:18:16 PM</t>
+          <t>08/11/2026 10:56:24 AM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Jeremy Myers</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1442,32 +1446,30 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N21" t="n">
+        <v>0.672</v>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/06/2026 8:19:00 AM</t>
+          <t>08/10/2026 5:26:28 PM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>696 - Medium</t>
+          <t>668 - Light</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jammie Singleton</t>
+          <t>Jonathan Walters</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1483,7 +1485,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1501,17 +1503,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/05/2026 5:42:28 PM</t>
+          <t>08/09/2026 12:17:56 PM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1521,7 +1523,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1550,17 +1552,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/05/2026 3:33:14 PM</t>
+          <t>08/09/2026 7:57:46 AM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1575,7 +1577,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1589,27 +1591,25 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N24" t="n">
+        <v>0.489</v>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/04/2026 2:28:07 PM</t>
+          <t>08/07/2026 6:45:51 PM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1648,7 +1648,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/04/2026 12:31:14 PM</t>
+          <t>08/06/2026 2:18:16 PM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1697,17 +1697,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/03/2026 2:39:43 PM</t>
+          <t>08/06/2026 8:19:00 AM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>649 - Heavy</t>
+          <t>696 - Medium</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Juan Ramirez</t>
+          <t>Jammie Singleton</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1746,17 +1746,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/03/2026 2:36:38 PM</t>
+          <t>08/05/2026 5:42:28 PM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>649 - Heavy</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Juan Ramirez</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1795,38 +1795,38 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/31/2026 1:16:01 PM</t>
+          <t>08/05/2026 3:33:14 PM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>662 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Drew Template</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -1844,34 +1844,38 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/31/2026 1:02:24 PM</t>
+          <t>08/04/2026 2:28:07 PM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jeremy Myers</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>Jason Walker</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -1889,17 +1893,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/30/2026 6:11:26 PM</t>
+          <t>08/04/2026 12:31:14 PM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1909,12 +1913,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -1938,17 +1942,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/30/2026 5:19:23 PM</t>
+          <t>08/03/2026 2:39:43 PM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>649 - Heavy</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Juan Ramirez</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1958,12 +1962,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -1987,17 +1991,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/27/2026 3:31:40 PM</t>
+          <t>08/03/2026 2:36:38 PM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>696 - Medium</t>
+          <t>649 - Heavy</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Juan Ramirez</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2007,12 +2011,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -2036,17 +2040,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/27/2026 10:23:43 AM</t>
+          <t>07/31/2026 1:16:01 PM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>693 - Heavy</t>
+          <t>662 - Heavy</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jonathan Dubose</t>
+          <t>Drew Template</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2061,7 +2065,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -2085,24 +2089,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/27/2026 8:16:05 AM</t>
+          <t>07/31/2026 1:02:24 PM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Jeremy Myers</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -2110,13 +2110,13 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -2134,17 +2134,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/24/2026 6:37:41 PM</t>
+          <t>07/30/2026 6:11:26 PM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -2173,25 +2173,27 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="n">
-        <v>0.5610000000000001</v>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/24/2026 5:53:45 PM</t>
+          <t>07/30/2026 5:19:23 PM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2230,17 +2232,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/23/2026 12:53:44 PM</t>
+          <t>07/27/2026 3:31:40 PM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>693 - Heavy</t>
+          <t>696 - Medium</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2250,7 +2252,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2279,30 +2281,38 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/23/2026 5:35:45 AM</t>
+          <t>07/27/2026 10:23:43 AM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+          <t>693 - Heavy</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Jonathan Dubose</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Active Drivers, Heavy Haul</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -2320,17 +2330,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/22/2026 5:03:30 PM</t>
+          <t>07/27/2026 8:16:05 AM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2340,7 +2350,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2369,7 +2379,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/21/2026 5:20:15 PM</t>
+          <t>07/24/2026 6:37:41 PM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2394,7 +2404,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -2408,27 +2418,25 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N41" t="n">
+        <v>0.5610000000000001</v>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/21/2026 4:37:50 PM</t>
+          <t>07/24/2026 5:53:45 PM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2438,7 +2446,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2467,34 +2475,38 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/21/2026 3:29:43 PM</t>
+          <t>07/23/2026 12:53:44 PM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>693 - Heavy</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jeremy Myers</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>Thomas Neff III</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -2512,38 +2524,30 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/21/2026 11:16:15 AM</t>
+          <t>07/23/2026 5:35:45 AM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>693 - Heavy</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Adam Johnson</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Active Drivers, Heavy Haul</t>
-        </is>
-      </c>
+          <t>685 - Medium</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -2551,31 +2555,37 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="n">
-        <v>0.606</v>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/21/2026 10:51:17 AM</t>
+          <t>07/22/2026 5:03:30 PM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>668 - Light</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Joshua Barrow</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>Thomas Neff III</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2586,7 +2596,7 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -2604,7 +2614,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/20/2026 4:04:35 PM</t>
+          <t>07/21/2026 5:20:15 PM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2653,17 +2663,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/20/2026 6:42:29 AM</t>
+          <t>07/21/2026 4:37:50 PM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2673,7 +2683,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2702,24 +2712,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/19/2026 8:59:02 PM</t>
+          <t>07/21/2026 3:29:43 PM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Jeremy Myers</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -2727,13 +2733,13 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -2751,17 +2757,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/18/2026 7:39:22 AM</t>
+          <t>07/21/2026 11:16:15 AM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>683 - Heavy</t>
+          <t>693 - Heavy</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dwayne Manuel</t>
+          <t>Adam Johnson</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2776,7 +2782,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -2790,34 +2796,28 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N49" t="n">
+        <v>0.606</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/17/2026 10:14:38 PM</t>
+          <t>07/21/2026 10:51:17 AM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>668 - Light</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Joshua Barrow</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -2831,7 +2831,7 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -2849,23 +2849,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/17/2026 12:31:29 PM</t>
+          <t>07/20/2026 4:04:35 PM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>683 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Gary Worley</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2894,7 +2898,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/17/2026 6:43:14 AM</t>
+          <t>07/20/2026 6:42:29 AM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2919,7 +2923,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -2933,25 +2937,27 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="n">
-        <v>0.621</v>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/16/2026 5:36:25 PM</t>
+          <t>07/19/2026 8:59:02 PM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2990,27 +2996,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/16/2026 9:50:11 AM</t>
+          <t>07/18/2026 7:39:22 AM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>683 - Heavy</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Dwayne Manuel</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3021,7 +3027,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -3039,17 +3045,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/15/2026 1:05:54 PM</t>
+          <t>07/17/2026 10:14:38 PM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3059,7 +3065,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3088,27 +3094,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/13/2026 5:04:35 PM</t>
+          <t>07/17/2026 12:31:29 PM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>668 - Light</t>
+          <t>683 - Heavy</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Gary Worley</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3137,7 +3139,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/12/2026 6:59:51 PM</t>
+          <t>07/17/2026 6:43:14 AM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3162,7 +3164,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -3176,17 +3178,15 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N57" t="n">
+        <v>0.621</v>
       </c>
       <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/09/2026 9:14:20 PM</t>
+          <t>07/16/2026 5:36:25 PM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3235,17 +3235,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/09/2026 1:48:10 PM</t>
+          <t>07/16/2026 9:50:11 AM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>649 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Juan Ramirez</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3255,18 +3255,18 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -3284,17 +3284,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/08/2026 8:35:24 PM</t>
+          <t>07/15/2026 1:05:54 PM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3323,25 +3323,27 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="n">
-        <v>0.52</v>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/08/2026 10:10:13 AM</t>
+          <t>07/13/2026 5:04:35 PM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>668 - Light</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jammie Singleton</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3356,7 +3358,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -3380,7 +3382,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/07/2026 7:49:42 PM</t>
+          <t>07/12/2026 6:59:51 PM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3429,17 +3431,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/07/2026 7:36:21 PM</t>
+          <t>07/09/2026 9:14:20 PM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3478,17 +3480,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/07/2026 1:55:40 PM</t>
+          <t>07/09/2026 1:48:10 PM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>649 - Heavy</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Juan Ramirez</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3503,13 +3505,13 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -3527,17 +3529,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/03/2026 2:40:22 PM</t>
+          <t>07/08/2026 8:35:24 PM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3547,12 +3549,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -3566,27 +3568,25 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N65" t="n">
+        <v>0.52</v>
       </c>
       <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/02/2026 4:49:00 PM</t>
+          <t>07/08/2026 10:10:13 AM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Jammie Singleton</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -3625,38 +3625,38 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/02/2026 2:57:58 PM</t>
+          <t>07/07/2026 7:49:42 PM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>641 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Adam Johnson</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -3674,20 +3674,24 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/01/2026 12:35:29 PM</t>
+          <t>07/07/2026 7:36:21 PM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Phillip Metz</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -3701,7 +3705,7 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -3719,17 +3723,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/01/2026 11:01:54 AM</t>
+          <t>07/07/2026 1:55:40 PM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3739,7 +3743,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3768,7 +3772,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>06/30/2026 6:33:35 PM</t>
+          <t>07/03/2026 2:40:22 PM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3817,17 +3821,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>06/30/2026 3:45:32 PM</t>
+          <t>07/02/2026 4:49:00 PM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3866,34 +3870,38 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>06/30/2026 2:25:53 AM</t>
+          <t>07/02/2026 2:57:58 PM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>641 - Heavy</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Jeremy Myers</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Adam Johnson</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Active Drivers, Heavy Haul</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -3911,17 +3919,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>06/29/2026 11:23:34 AM</t>
+          <t>07/01/2026 12:35:29 PM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>646 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Harley Tidwell</t>
+          <t>Phillip Metz</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -3932,13 +3940,13 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -3956,17 +3964,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>06/29/2026 10:19:27 AM</t>
+          <t>07/01/2026 11:01:54 AM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3976,12 +3984,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -4005,23 +4013,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>06/29/2026 8:54:50 AM</t>
+          <t>06/30/2026 6:33:35 PM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jeremy Myers</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>Jason Walker</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4050,20 +4062,24 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>06/28/2026 8:19:03 PM</t>
+          <t>06/30/2026 3:45:32 PM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>683 - Heavy</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Gary Worley</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>Thomas Neff III</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>HAAS Alert, Heavy Haul</t>
@@ -4095,24 +4111,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>06/27/2026 5:25:06 PM</t>
+          <t>06/30/2026 2:25:53 AM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Jeremy Myers</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -4120,7 +4132,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -4144,24 +4156,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>06/26/2026 3:27:58 PM</t>
+          <t>06/29/2026 11:23:34 AM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>646 - Medium</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Harley Tidwell</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -4169,7 +4177,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -4193,16 +4201,24 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>06/25/2026 4:46:02 PM</t>
+          <t>06/29/2026 10:19:27 AM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>629 - Heavy</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
+          <t>669 - Heavy</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Jason Walker</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>HAAS Alert, Heavy Haul</t>
@@ -4210,7 +4226,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -4234,24 +4250,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>06/25/2026 11:15:11 AM</t>
+          <t>06/29/2026 8:54:50 AM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Jeremy Myers</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -4259,7 +4271,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -4273,27 +4285,33 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" t="n">
-        <v>0.673</v>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>06/25/2026 10:09:43 AM</t>
+          <t>06/28/2026 8:19:03 PM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>668 - Light</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>683 - Heavy</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Gary Worley</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4322,17 +4340,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>06/24/2026 1:15:17 PM</t>
+          <t>06/27/2026 5:25:06 PM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4342,12 +4360,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -4371,17 +4389,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>06/23/2026 11:02:05 AM</t>
+          <t>06/26/2026 3:27:58 PM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4396,7 +4414,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -4410,32 +4428,26 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" t="n">
-        <v>0.55</v>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>06/22/2026 11:26:05 AM</t>
+          <t>06/25/2026 4:46:02 PM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>692 - Heavy</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>William Foley</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Active Drivers, Heavy Haul</t>
-        </is>
-      </c>
+          <t>629 - Heavy</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>HAAS Alert, Heavy Haul</t>
@@ -4443,13 +4455,13 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -4467,17 +4479,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>06/19/2026 4:15:44 PM</t>
+          <t>06/25/2026 11:15:11 AM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4492,7 +4504,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -4506,37 +4518,27 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N85" t="n">
+        <v>0.673</v>
       </c>
       <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>06/17/2026 5:02:17 PM</t>
+          <t>06/25/2026 10:09:43 AM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>683 - Heavy</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Dwayne Manuel</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Active Drivers, Heavy Haul</t>
-        </is>
-      </c>
+          <t>668 - Light</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4547,7 +4549,7 @@
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -4565,17 +4567,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>06/17/2026 11:28:09 AM</t>
+          <t>06/24/2026 1:15:17 PM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4585,12 +4587,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -4614,7 +4616,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>06/15/2026 5:53:31 PM</t>
+          <t>06/23/2026 11:02:05 AM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4639,7 +4641,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -4653,32 +4655,30 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N88" t="n">
+        <v>0.55</v>
       </c>
       <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>06/15/2026 1:23:54 PM</t>
+          <t>06/22/2026 11:26:05 AM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>692 - Heavy</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>William Foley</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4688,13 +4688,13 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -4712,20 +4712,24 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>06/14/2026 11:39:04 AM</t>
+          <t>06/19/2026 4:15:44 PM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>Paul Kunze Jr</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -4739,7 +4743,7 @@
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -4757,27 +4761,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>06/14/2026 9:48:42 AM</t>
+          <t>06/17/2026 5:02:17 PM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>644 - Medium</t>
+          <t>683 - Heavy</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Dwayne Manuel</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4788,7 +4792,7 @@
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -4806,7 +4810,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>06/13/2026 5:24:44 PM</t>
+          <t>06/17/2026 11:28:09 AM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4816,10 +4820,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -4827,13 +4835,13 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -4851,20 +4859,24 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>06/13/2026 4:18:06 PM</t>
+          <t>06/15/2026 5:53:31 PM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -4872,13 +4884,13 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -4896,17 +4908,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>06/12/2026 9:27:53 AM</t>
+          <t>06/15/2026 1:23:54 PM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>644 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4916,7 +4928,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4945,24 +4957,20 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>06/11/2026 10:09:35 PM</t>
+          <t>06/14/2026 11:39:04 AM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Christopher Marcantel</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -4970,13 +4978,13 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -4994,17 +5002,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>06/10/2026 10:04:03 AM</t>
+          <t>06/14/2026 9:48:42 AM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>644 - Medium</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5014,7 +5022,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5043,32 +5051,28 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>06/07/2026 2:14:46 PM</t>
+          <t>06/13/2026 5:24:44 PM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>673 - Heavy</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Kyle Ray</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Christopher Marcantel</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -5092,24 +5096,20 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>06/06/2026 8:18:21 AM</t>
+          <t>06/13/2026 4:18:06 PM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>696 - Medium</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jammie Singleton</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Christopher Marcantel</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -5117,13 +5117,13 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -5141,7 +5141,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>06/04/2026 2:15:03 PM</t>
+          <t>06/12/2026 9:27:53 AM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5149,8 +5149,16 @@
           <t>644 - Medium</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Paul Kunze Jr</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -5182,28 +5190,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>06/03/2026 10:10:14 AM</t>
+          <t>06/11/2026 10:09:35 PM</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>632 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Gary Worley</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -5227,22 +5239,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>05/29/2026 12:42:54 PM</t>
+          <t>06/10/2026 10:04:03 AM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>692 - Heavy</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kyle Ray</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5252,13 +5264,13 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -5276,20 +5288,24 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>05/28/2026 4:24:20 PM</t>
+          <t>06/07/2026 2:14:46 PM</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>632 - Heavy</t>
+          <t>673 - Heavy</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Gary Worley</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>Kyle Ray</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>HAAS Alert, Heavy Haul</t>
@@ -5297,13 +5313,13 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -5321,38 +5337,38 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>05/28/2026 1:48:42 PM</t>
+          <t>06/06/2026 8:18:21 AM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>660 - Heavy</t>
+          <t>696 - Medium</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Billy Johnson</t>
+          <t>Jammie Singleton</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Active Drivers, HAAS Alert, Heavy Haul, Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -5370,19 +5386,15 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>05/28/2026 12:14:01 AM</t>
+          <t>06/04/2026 2:15:03 PM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
+          <t>644 - Medium</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
@@ -5397,7 +5409,7 @@
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -5412,6 +5424,239 @@
       </c>
       <c r="O104" t="inlineStr"/>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>06/03/2026 10:10:14 AM</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>632 - Heavy</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Gary Worley</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Heavy Haul</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>05/29/2026 12:42:54 PM</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>692 - Heavy</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Kyle Ray</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Heavy Haul</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Inattentive Driving</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>05/28/2026 4:24:20 PM</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>632 - Heavy</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Gary Worley</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Heavy Haul</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>05/28/2026 1:48:42 PM</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>660 - Heavy</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Billy Johnson</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Active Drivers, HAAS Alert, Heavy Haul, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Heavy Haul</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Following Distance</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>05/28/2026 12:14:01 AM</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>685 - Medium</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Christopher Marcantel</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Mobile Usage</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O109"/>
+  <dimension ref="A1:O124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,38 +496,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/23/2026 12:28:49 AM</t>
+          <t>08/29/2026 8:03:37 PM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>629 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clint Winwood </t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -545,17 +545,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/21/2026 9:34:11 PM</t>
+          <t>08/29/2026 9:56:26 AM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -594,27 +594,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/21/2026 8:37:13 PM</t>
+          <t>08/28/2026 6:21:26 PM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Thomas Neff III</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>651 - Light</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -643,27 +635,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/21/2026 6:17:21 PM</t>
+          <t>08/28/2026 3:49:32 PM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kody Addison</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -692,38 +684,38 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/21/2026 12:33:22 PM</t>
+          <t>08/28/2026 2:08:42 PM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>607 - Heavy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kody Addison</t>
+          <t xml:space="preserve">Tommy Scott </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -741,17 +733,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/20/2026 12:54:58 PM</t>
+          <t>08/28/2026 11:41:17 AM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>649 - Heavy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Juan Ramirez</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -761,18 +753,18 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -790,27 +782,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/20/2026 12:25:18 PM</t>
+          <t>08/28/2026 8:56:53 AM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>683 - Heavy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Jonathan Walters</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -821,7 +813,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -839,22 +831,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/20/2026 10:30:15 AM</t>
+          <t>08/27/2026 6:48:52 PM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>668 - Light</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Adam Johnson</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -864,7 +856,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -888,38 +880,38 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/18/2026 7:41:40 AM</t>
+          <t>08/27/2026 2:12:13 PM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>629 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clint Winwood </t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -937,27 +929,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/17/2026 2:57:01 PM</t>
+          <t>08/26/2026 2:26:37 PM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>629 - Heavy</t>
+          <t>696 - Medium</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clint Winwood </t>
+          <t>Jammie Singleton</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -968,7 +960,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -986,7 +978,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/17/2026 2:08:31 PM</t>
+          <t>08/26/2026 10:36:47 AM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1035,7 +1027,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/17/2026 11:09:15 AM</t>
+          <t>08/26/2026 8:11:59 AM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1060,7 +1052,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1084,16 +1076,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/14/2026 6:11:59 PM</t>
+          <t>08/25/2026 11:30:08 AM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>629 - Heavy</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>641 - Heavy</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Adam Johnson</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Active Drivers, Heavy Haul</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>HAAS Alert, Heavy Haul</t>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1125,17 +1125,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/14/2026 2:51:01 PM</t>
+          <t>08/25/2026 7:10:36 AM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1174,32 +1174,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/14/2026 7:46:37 AM</t>
+          <t>08/24/2026 11:01:42 PM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>635 - Heavy</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1223,7 +1215,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/13/2026 6:33:21 PM</t>
+          <t>08/24/2026 9:48:53 PM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1272,16 +1264,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/13/2026 11:59:27 AM</t>
+          <t>08/24/2026 11:28:18 AM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>694 - Heavy</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>662 - Heavy</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Drew Template</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Active Drivers, Heavy Haul</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>HAAS Alert, Heavy Haul</t>
@@ -1289,13 +1289,13 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1313,17 +1313,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/11/2026 4:41:04 PM</t>
+          <t>08/24/2026 11:07:41 AM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>649 - Heavy</t>
+          <t>696 - Medium</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Juan Ramirez</t>
+          <t>Jammie Singleton</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1333,18 +1333,18 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1362,17 +1362,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/11/2026 4:04:10 PM</t>
+          <t>08/24/2026 8:54:18 AM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1411,28 +1411,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/11/2026 10:56:24 AM</t>
+          <t>08/23/2026 12:28:49 AM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>629 - Heavy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jeremy Myers</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t xml:space="preserve">Clint Winwood </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1446,30 +1450,32 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="n">
-        <v>0.672</v>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/10/2026 5:26:28 PM</t>
+          <t>08/21/2026 9:34:11 PM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>668 - Light</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jonathan Walters</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1485,7 +1491,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1503,17 +1509,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/09/2026 12:17:56 PM</t>
+          <t>08/21/2026 8:37:13 PM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1523,7 +1529,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1552,24 +1558,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/09/2026 7:57:46 AM</t>
+          <t>08/21/2026 6:17:21 PM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Kody Addison</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -1577,7 +1579,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1591,32 +1593,30 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="n">
-        <v>0.489</v>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/07/2026 6:45:51 PM</t>
+          <t>08/21/2026 12:33:22 PM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Kody Addison</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1648,17 +1648,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/06/2026 2:18:16 PM</t>
+          <t>08/20/2026 12:54:58 PM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -1697,17 +1697,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/06/2026 8:19:00 AM</t>
+          <t>08/20/2026 12:25:18 PM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>696 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jammie Singleton</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1746,32 +1746,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/05/2026 5:42:28 PM</t>
+          <t>08/20/2026 10:30:15 AM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>668 - Light</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Adam Johnson</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1795,27 +1795,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/05/2026 3:33:14 PM</t>
+          <t>08/18/2026 7:41:40 AM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>629 - Heavy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t xml:space="preserve">Clint Winwood </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Towing and Recovery</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1826,7 +1826,7 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -1844,22 +1844,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/04/2026 2:28:07 PM</t>
+          <t>08/17/2026 2:57:01 PM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>629 - Heavy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t xml:space="preserve">Clint Winwood </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Towing and Recovery</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1869,13 +1869,13 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -1893,17 +1893,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/04/2026 12:31:14 PM</t>
+          <t>08/17/2026 2:08:31 PM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -1942,17 +1942,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/03/2026 2:39:43 PM</t>
+          <t>08/17/2026 11:09:15 AM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>649 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Juan Ramirez</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1962,12 +1962,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -1991,24 +1991,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/03/2026 2:36:38 PM</t>
+          <t>08/14/2026 6:11:59 PM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>649 - Heavy</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Juan Ramirez</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>629 - Heavy</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>HAAS Alert, Heavy Haul</t>
@@ -2016,7 +2008,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -2040,22 +2032,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/31/2026 1:16:01 PM</t>
+          <t>08/14/2026 2:51:01 PM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>662 - Heavy</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Drew Template</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2065,13 +2057,13 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -2089,20 +2081,24 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/31/2026 1:02:24 PM</t>
+          <t>08/14/2026 7:46:37 AM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jeremy Myers</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Paul Kunze Jr</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -2110,13 +2106,13 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -2134,7 +2130,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/30/2026 6:11:26 PM</t>
+          <t>08/13/2026 6:33:21 PM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2183,27 +2179,19 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/30/2026 5:19:23 PM</t>
+          <t>08/13/2026 11:59:27 AM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Jesus Carbajal</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>694 - Heavy</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2232,17 +2220,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/27/2026 3:31:40 PM</t>
+          <t>08/11/2026 4:41:04 PM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>696 - Medium</t>
+          <t>649 - Heavy</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Juan Ramirez</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2252,18 +2240,18 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -2281,27 +2269,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/27/2026 10:23:43 AM</t>
+          <t>08/11/2026 4:04:10 PM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>693 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jonathan Dubose</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2312,7 +2300,7 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -2330,24 +2318,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/27/2026 8:16:05 AM</t>
+          <t>08/11/2026 10:56:24 AM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Jeremy Myers</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -2355,13 +2339,13 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -2369,32 +2353,30 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N40" t="n">
+        <v>0.672</v>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/24/2026 6:37:41 PM</t>
+          <t>08/10/2026 5:26:28 PM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>668 - Light</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Jonathan Walters</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2404,13 +2386,13 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -2418,25 +2400,27 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="n">
-        <v>0.5610000000000001</v>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/24/2026 5:53:45 PM</t>
+          <t>08/09/2026 12:17:56 PM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2475,17 +2459,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/23/2026 12:53:44 PM</t>
+          <t>08/09/2026 7:57:46 AM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>693 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2495,12 +2479,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -2514,26 +2498,32 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N43" t="n">
+        <v>0.489</v>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/23/2026 5:35:45 AM</t>
+          <t>08/07/2026 6:45:51 PM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+          <t>658 - Medium</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Paul Kunze Jr</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -2541,7 +2531,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -2565,17 +2555,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/22/2026 5:03:30 PM</t>
+          <t>08/06/2026 2:18:16 PM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2590,7 +2580,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -2614,17 +2604,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/21/2026 5:20:15 PM</t>
+          <t>08/06/2026 8:19:00 AM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>696 - Medium</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Jammie Singleton</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2663,17 +2653,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/21/2026 4:37:50 PM</t>
+          <t>08/05/2026 5:42:28 PM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2712,20 +2702,24 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/21/2026 3:29:43 PM</t>
+          <t>08/05/2026 3:33:14 PM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jeremy Myers</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -2733,13 +2727,13 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -2757,22 +2751,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/21/2026 11:16:15 AM</t>
+          <t>08/04/2026 2:28:07 PM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>693 - Heavy</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Adam Johnson</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2782,13 +2776,13 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -2796,42 +2790,48 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="n">
-        <v>0.606</v>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/21/2026 10:51:17 AM</t>
+          <t>08/04/2026 12:31:14 PM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>668 - Light</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Joshua Barrow</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Jason Walker</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -2849,17 +2849,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/20/2026 4:04:35 PM</t>
+          <t>08/03/2026 2:39:43 PM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>649 - Heavy</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Juan Ramirez</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2869,12 +2869,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -2898,17 +2898,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/20/2026 6:42:29 AM</t>
+          <t>08/03/2026 2:36:38 PM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>649 - Heavy</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Juan Ramirez</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -2947,38 +2947,38 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/19/2026 8:59:02 PM</t>
+          <t>07/31/2026 1:16:01 PM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>662 - Heavy</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Drew Template</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -2996,32 +2996,28 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/18/2026 7:39:22 AM</t>
+          <t>07/31/2026 1:02:24 PM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>683 - Heavy</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dwayne Manuel</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Active Drivers, Heavy Haul</t>
-        </is>
-      </c>
+          <t>Jeremy Myers</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -3045,7 +3041,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/17/2026 10:14:38 PM</t>
+          <t>07/30/2026 6:11:26 PM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3094,23 +3090,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/17/2026 12:31:29 PM</t>
+          <t>07/30/2026 5:19:23 PM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>683 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Gary Worley</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3139,17 +3139,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/17/2026 6:43:14 AM</t>
+          <t>07/27/2026 3:31:40 PM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>696 - Medium</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -3178,35 +3178,37 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" t="n">
-        <v>0.621</v>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/16/2026 5:36:25 PM</t>
+          <t>07/27/2026 10:23:43 AM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>693 - Heavy</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jonathan Dubose</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3217,7 +3219,7 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -3235,17 +3237,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/16/2026 9:50:11 AM</t>
+          <t>07/27/2026 8:16:05 AM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3284,17 +3286,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/15/2026 1:05:54 PM</t>
+          <t>07/24/2026 6:37:41 PM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3304,12 +3306,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -3323,22 +3325,20 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N60" t="n">
+        <v>0.5610000000000001</v>
       </c>
       <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/13/2026 5:04:35 PM</t>
+          <t>07/24/2026 5:53:45 PM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>668 - Light</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3382,17 +3382,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/12/2026 6:59:51 PM</t>
+          <t>07/23/2026 12:53:44 PM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>693 - Heavy</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3431,24 +3431,16 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/09/2026 9:14:20 PM</t>
+          <t>07/23/2026 5:35:45 AM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>685 - Medium</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -3456,7 +3448,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -3480,17 +3472,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/09/2026 1:48:10 PM</t>
+          <t>07/22/2026 5:03:30 PM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>649 - Heavy</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Juan Ramirez</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3505,13 +3497,13 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -3529,17 +3521,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/08/2026 8:35:24 PM</t>
+          <t>07/21/2026 5:20:15 PM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3568,25 +3560,27 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="n">
-        <v>0.52</v>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/08/2026 10:10:13 AM</t>
+          <t>07/21/2026 4:37:50 PM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jammie Singleton</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3596,12 +3590,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -3625,24 +3619,20 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07/07/2026 7:49:42 PM</t>
+          <t>07/21/2026 3:29:43 PM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Jeremy Myers</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -3650,13 +3640,13 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -3674,38 +3664,38 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07/07/2026 7:36:21 PM</t>
+          <t>07/21/2026 11:16:15 AM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>693 - Heavy</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Adam Johnson</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -3713,37 +3703,31 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N68" t="n">
+        <v>0.606</v>
       </c>
       <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07/07/2026 1:55:40 PM</t>
+          <t>07/21/2026 10:51:17 AM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>668 - Light</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Joshua Barrow</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3754,7 +3738,7 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -3772,17 +3756,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07/03/2026 2:40:22 PM</t>
+          <t>07/20/2026 4:04:35 PM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3792,12 +3776,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -3821,17 +3805,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07/02/2026 4:49:00 PM</t>
+          <t>07/20/2026 6:42:29 AM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3841,7 +3825,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3870,38 +3854,38 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07/02/2026 2:57:58 PM</t>
+          <t>07/19/2026 8:59:02 PM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>641 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Adam Johnson</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -3919,23 +3903,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07/01/2026 12:35:29 PM</t>
+          <t>07/18/2026 7:39:22 AM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>683 - Heavy</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Phillip Metz</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>Dwayne Manuel</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Active Drivers, Heavy Haul</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3964,17 +3952,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07/01/2026 11:01:54 AM</t>
+          <t>07/17/2026 10:14:38 PM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4013,24 +4001,20 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>06/30/2026 6:33:35 PM</t>
+          <t>07/17/2026 12:31:29 PM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>683 - Heavy</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Gary Worley</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>HAAS Alert, Heavy Haul</t>
@@ -4038,7 +4022,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -4062,17 +4046,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>06/30/2026 3:45:32 PM</t>
+          <t>07/17/2026 6:43:14 AM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4082,12 +4066,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -4101,30 +4085,32 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N76" t="n">
+        <v>0.621</v>
       </c>
       <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>06/30/2026 2:25:53 AM</t>
+          <t>07/16/2026 5:36:25 PM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Jeremy Myers</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>Paul Kunze Jr</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -4132,7 +4118,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -4156,20 +4142,24 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>06/29/2026 11:23:34 AM</t>
+          <t>07/16/2026 9:50:11 AM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>646 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Harley Tidwell</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -4177,7 +4167,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -4201,7 +4191,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>06/29/2026 10:19:27 AM</t>
+          <t>07/15/2026 1:05:54 PM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4226,7 +4216,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -4250,20 +4240,24 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>06/29/2026 8:54:50 AM</t>
+          <t>07/13/2026 5:04:35 PM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>668 - Light</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Jeremy Myers</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>Paul Kunze Jr</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -4271,7 +4265,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -4295,23 +4289,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>06/28/2026 8:19:03 PM</t>
+          <t>07/12/2026 6:59:51 PM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>683 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Gary Worley</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>Paul Kunze Jr</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4340,12 +4338,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>06/27/2026 5:25:06 PM</t>
+          <t>07/09/2026 9:14:20 PM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4365,7 +4363,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -4389,17 +4387,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>06/26/2026 3:27:58 PM</t>
+          <t>07/09/2026 1:48:10 PM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>649 - Heavy</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Juan Ramirez</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4409,18 +4407,18 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -4438,19 +4436,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>06/25/2026 4:46:02 PM</t>
+          <t>07/08/2026 8:35:24 PM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>629 - Heavy</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
+          <t>658 - Medium</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Paul Kunze Jr</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4469,27 +4475,25 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N84" t="n">
+        <v>0.52</v>
       </c>
       <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>06/25/2026 11:15:11 AM</t>
+          <t>07/08/2026 10:10:13 AM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Jammie Singleton</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4504,7 +4508,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -4518,24 +4522,34 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" t="n">
-        <v>0.673</v>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>06/25/2026 10:09:43 AM</t>
+          <t>07/07/2026 7:49:42 PM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>668 - Light</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
+          <t>658 - Medium</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Paul Kunze Jr</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -4567,17 +4581,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>06/24/2026 1:15:17 PM</t>
+          <t>07/07/2026 7:36:21 PM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4587,12 +4601,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -4616,17 +4630,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>06/23/2026 11:02:05 AM</t>
+          <t>07/07/2026 1:55:40 PM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4636,12 +4650,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -4655,30 +4669,32 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" t="n">
-        <v>0.55</v>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>06/22/2026 11:26:05 AM</t>
+          <t>07/03/2026 2:40:22 PM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>692 - Heavy</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>William Foley</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4688,13 +4704,13 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -4712,17 +4728,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>06/19/2026 4:15:44 PM</t>
+          <t>07/02/2026 4:49:00 PM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4732,7 +4748,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4761,17 +4777,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>06/17/2026 5:02:17 PM</t>
+          <t>07/02/2026 2:57:58 PM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>683 - Heavy</t>
+          <t>641 - Heavy</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dwayne Manuel</t>
+          <t>Adam Johnson</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4786,7 +4802,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -4810,24 +4826,20 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>06/17/2026 11:28:09 AM</t>
+          <t>07/01/2026 12:35:29 PM</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Phillip Metz</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -4835,13 +4847,13 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -4859,7 +4871,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>06/15/2026 5:53:31 PM</t>
+          <t>07/01/2026 11:01:54 AM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4908,7 +4920,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>06/15/2026 1:23:54 PM</t>
+          <t>06/30/2026 6:33:35 PM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4933,7 +4945,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -4957,23 +4969,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>06/14/2026 11:39:04 AM</t>
+          <t>06/30/2026 3:45:32 PM</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
+          <t>Thomas Neff III</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4984,7 +5000,7 @@
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -5002,24 +5018,20 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>06/14/2026 9:48:42 AM</t>
+          <t>06/30/2026 2:25:53 AM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>644 - Medium</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Jeremy Myers</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -5027,7 +5039,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -5051,17 +5063,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>06/13/2026 5:24:44 PM</t>
+          <t>06/29/2026 11:23:34 AM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>646 - Medium</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
+          <t>Harley Tidwell</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -5072,13 +5084,13 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -5096,34 +5108,38 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>06/13/2026 4:18:06 PM</t>
+          <t>06/29/2026 10:19:27 AM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
+          <t>Jason Walker</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -5141,24 +5157,20 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>06/12/2026 9:27:53 AM</t>
+          <t>06/29/2026 8:54:50 AM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>644 - Medium</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Jeremy Myers</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -5166,7 +5178,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -5190,32 +5202,28 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>06/11/2026 10:09:35 PM</t>
+          <t>06/28/2026 8:19:03 PM</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>683 - Heavy</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Gary Worley</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -5239,17 +5247,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>06/10/2026 10:04:03 AM</t>
+          <t>06/27/2026 5:25:06 PM</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5259,12 +5267,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -5288,38 +5296,38 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>06/07/2026 2:14:46 PM</t>
+          <t>06/26/2026 3:27:58 PM</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>673 - Heavy</t>
+          <t>685 - Medium</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Kyle Ray</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -5337,27 +5345,19 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>06/06/2026 8:18:21 AM</t>
+          <t>06/25/2026 4:46:02 PM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>696 - Medium</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Jammie Singleton</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>629 - Heavy</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5386,16 +5386,24 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>06/04/2026 2:15:03 PM</t>
+          <t>06/25/2026 11:15:11 AM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>644 - Medium</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
+          <t>680 - Medium</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -5403,7 +5411,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -5417,38 +5425,32 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N104" t="n">
+        <v>0.673</v>
       </c>
       <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>06/03/2026 10:10:14 AM</t>
+          <t>06/25/2026 10:09:43 AM</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>632 - Heavy</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Gary Worley</t>
-        </is>
-      </c>
+          <t>668 - Light</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -5472,22 +5474,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>05/29/2026 12:42:54 PM</t>
+          <t>06/24/2026 1:15:17 PM</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>692 - Heavy</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Kyle Ray</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5497,13 +5499,13 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -5521,28 +5523,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>05/28/2026 4:24:20 PM</t>
+          <t>06/23/2026 11:02:05 AM</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>632 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Gary Worley</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -5556,32 +5562,30 @@
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N107" t="n">
+        <v>0.55</v>
       </c>
       <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>05/28/2026 1:48:42 PM</t>
+          <t>06/22/2026 11:26:05 AM</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>660 - Heavy</t>
+          <t>692 - Heavy</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Billy Johnson</t>
+          <t>William Foley</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Active Drivers, HAAS Alert, Heavy Haul, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5615,20 +5619,24 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>05/28/2026 12:14:01 AM</t>
+          <t>06/19/2026 4:15:44 PM</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>685 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Christopher Marcantel</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>Paul Kunze Jr</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -5642,7 +5650,7 @@
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -5657,6 +5665,717 @@
       </c>
       <c r="O109" t="inlineStr"/>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>06/17/2026 5:02:17 PM</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>683 - Heavy</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Dwayne Manuel</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Active Drivers, Heavy Haul</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Heavy Haul</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Mobile Usage</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>06/17/2026 11:28:09 AM</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>685 - Medium</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Inattentive Driving</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>06/15/2026 5:53:31 PM</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>680 - Medium</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Mobile Usage</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>06/15/2026 1:23:54 PM</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>669 - Heavy</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Jason Walker</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Heavy Haul</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Mobile Usage</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>06/14/2026 11:39:04 AM</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>685 - Medium</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Christopher Marcantel</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Mobile Usage</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>06/14/2026 9:48:42 AM</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>644 - Medium</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Paul Kunze Jr</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Mobile Usage</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>06/13/2026 5:24:44 PM</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>685 - Medium</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Christopher Marcantel</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Mobile Usage</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>06/13/2026 4:18:06 PM</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>685 - Medium</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Christopher Marcantel</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Inattentive Driving</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>06/12/2026 9:27:53 AM</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>644 - Medium</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Paul Kunze Jr</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Mobile Usage</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>06/11/2026 10:09:35 PM</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>680 - Medium</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Drowsy</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>06/10/2026 10:04:03 AM</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>659 - Heavy</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Thomas Neff III</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Heavy Haul</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Mobile Usage</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>06/07/2026 2:14:46 PM</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>673 - Heavy</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Kyle Ray</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Active Drivers, Heavy Haul, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Heavy Haul</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Following Distance</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Coached</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>06/06/2026 8:18:21 AM</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>696 - Medium</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Jammie Singleton</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Mobile Usage</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>06/04/2026 2:15:03 PM</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>644 - Medium</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Towing and Recovery</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Mobile Usage</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>06/03/2026 10:10:14 AM</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>632 - Heavy</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Gary Worley</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>HAAS Alert, Heavy Haul</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>No Seat Belt</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Needs Coaching</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/camera_events.xlsx
+++ b/camera_events.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O124"/>
+  <dimension ref="A1:O126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08/29/2026 8:03:37 PM</t>
+          <t>09/03/2026 9:45:53 PM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -545,17 +545,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08/29/2026 9:56:26 AM</t>
+          <t>09/02/2026 3:54:44 PM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -594,19 +594,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08/28/2026 6:21:26 PM</t>
+          <t>09/01/2026 5:51:03 PM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>651 - Light</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+          <t>659 - Heavy</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Thomas Neff III</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -635,22 +643,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/28/2026 3:49:32 PM</t>
+          <t>09/01/2026 5:20:48 PM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>662 - Heavy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Dwayne Manuel</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -666,7 +674,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -684,17 +692,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/28/2026 2:08:42 PM</t>
+          <t>09/01/2026 4:44:08 PM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>607 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tommy Scott </t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -704,7 +712,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -715,7 +723,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -733,17 +741,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/28/2026 11:41:17 AM</t>
+          <t>08/31/2026 3:21:00 PM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>649 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Juan Ramirez</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -753,7 +761,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -764,7 +772,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -782,27 +790,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/28/2026 8:56:53 AM</t>
+          <t>08/29/2026 8:03:37 PM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>683 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jonathan Walters</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -813,7 +821,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -831,17 +839,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/27/2026 6:48:52 PM</t>
+          <t>08/29/2026 9:56:26 AM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -880,24 +888,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/27/2026 2:12:13 PM</t>
+          <t>08/28/2026 6:21:26 PM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Jesus Carbajal</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>651 - Light</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -905,7 +905,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Inattentive Driving</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/26/2026 2:26:37 PM</t>
+          <t>08/28/2026 3:49:32 PM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>696 - Medium</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jammie Singleton</t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -978,17 +978,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/26/2026 10:36:47 AM</t>
+          <t>08/28/2026 2:08:42 PM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>607 - Heavy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t xml:space="preserve">Tommy Scott </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1009,7 +1009,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1027,17 +1027,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/26/2026 8:11:59 AM</t>
+          <t>08/28/2026 11:41:17 AM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>649 - Heavy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Juan Ramirez</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1058,7 +1058,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1076,22 +1076,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08/25/2026 11:30:08 AM</t>
+          <t>08/28/2026 8:56:53 AM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>641 - Heavy</t>
+          <t>683 - Heavy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Adam Johnson</t>
+          <t>Jonathan Walters</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1101,13 +1101,13 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Camera Obstruction</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1125,7 +1125,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08/25/2026 7:10:36 AM</t>
+          <t>08/27/2026 6:48:52 PM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1174,24 +1174,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08/24/2026 11:01:42 PM</t>
+          <t>08/27/2026 2:12:13 PM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>635 - Heavy</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>680 - Medium</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Inattentive Driving</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1215,17 +1223,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08/24/2026 9:48:53 PM</t>
+          <t>08/26/2026 2:26:37 PM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>696 - Medium</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Jammie Singleton</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1264,38 +1272,38 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08/24/2026 11:28:18 AM</t>
+          <t>08/26/2026 10:36:47 AM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>662 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Drew Template</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -1313,17 +1321,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08/24/2026 11:07:41 AM</t>
+          <t>08/26/2026 8:11:59 AM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>696 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jammie Singleton</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1362,27 +1370,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08/24/2026 8:54:18 AM</t>
+          <t>08/25/2026 11:30:08 AM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>641 - Heavy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Adam Johnson</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1411,38 +1419,38 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08/23/2026 12:28:49 AM</t>
+          <t>08/25/2026 7:10:36 AM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>629 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clint Winwood </t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1460,32 +1468,24 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08/21/2026 9:34:11 PM</t>
+          <t>08/24/2026 11:01:42 PM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>635 - Heavy</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1509,17 +1509,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08/21/2026 8:37:13 PM</t>
+          <t>08/24/2026 9:48:53 PM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1558,34 +1558,38 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08/21/2026 6:17:21 PM</t>
+          <t>08/24/2026 11:28:18 AM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>662 - Heavy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kody Addison</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Drew Template</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Active Drivers, Heavy Haul</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -1603,20 +1607,24 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08/21/2026 12:33:22 PM</t>
+          <t>08/24/2026 11:07:41 AM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>696 - Medium</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kody Addison</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Jammie Singleton</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -1624,7 +1632,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1648,7 +1656,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08/20/2026 12:54:58 PM</t>
+          <t>08/24/2026 8:54:18 AM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1697,38 +1705,38 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08/20/2026 12:25:18 PM</t>
+          <t>08/23/2026 12:28:49 AM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>629 - Heavy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t xml:space="preserve">Clint Winwood </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Towing and Recovery</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -1746,22 +1754,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08/20/2026 10:30:15 AM</t>
+          <t>08/21/2026 9:34:11 PM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>668 - Light</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Adam Johnson</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1771,7 +1779,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1795,22 +1803,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08/18/2026 7:41:40 AM</t>
+          <t>08/21/2026 8:37:13 PM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>629 - Heavy</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clint Winwood </t>
+          <t>Thomas Neff III</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Towing and Recovery</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1826,7 +1834,7 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -1844,27 +1852,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08/17/2026 2:57:01 PM</t>
+          <t>08/21/2026 6:17:21 PM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>629 - Heavy</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clint Winwood </t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Kody Addison</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1875,7 +1879,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -1893,24 +1897,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08/17/2026 2:08:31 PM</t>
+          <t>08/21/2026 12:33:22 PM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Kody Addison</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -1942,7 +1942,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08/17/2026 11:09:15 AM</t>
+          <t>08/20/2026 12:54:58 PM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1991,19 +1991,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08/14/2026 6:11:59 PM</t>
+          <t>08/20/2026 12:25:18 PM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>629 - Heavy</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+          <t>680 - Medium</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2032,32 +2040,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08/14/2026 2:51:01 PM</t>
+          <t>08/20/2026 10:30:15 AM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>659 - Heavy</t>
+          <t>668 - Light</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Thomas Neff III</t>
+          <t>Adam Johnson</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Active Drivers, Heavy Haul</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Following Distance</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -2081,27 +2089,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/14/2026 7:46:37 AM</t>
+          <t>08/18/2026 7:41:40 AM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>629 - Heavy</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t xml:space="preserve">Clint Winwood </t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Towing and Recovery</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2112,7 +2120,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -2130,27 +2138,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08/13/2026 6:33:21 PM</t>
+          <t>08/17/2026 2:57:01 PM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>629 - Heavy</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t xml:space="preserve">Clint Winwood </t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>Towing and Recovery</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2161,7 +2169,7 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -2179,19 +2187,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08/13/2026 11:59:27 AM</t>
+          <t>08/17/2026 2:08:31 PM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>694 - Heavy</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+          <t>658 - Medium</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Paul Kunze Jr</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2220,17 +2236,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08/11/2026 4:41:04 PM</t>
+          <t>08/17/2026 11:09:15 AM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>649 - Heavy</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Juan Ramirez</t>
+          <t>Jesus Carbajal</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2240,18 +2256,18 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Camera Obstruction</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -2269,27 +2285,19 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08/11/2026 4:04:10 PM</t>
+          <t>08/14/2026 6:11:59 PM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>629 - Heavy</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2318,34 +2326,38 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08/11/2026 10:56:24 AM</t>
+          <t>08/14/2026 2:51:01 PM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>659 - Heavy</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jeremy Myers</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>Thomas Neff III</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -2353,30 +2365,32 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="n">
-        <v>0.672</v>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08/10/2026 5:26:28 PM</t>
+          <t>08/14/2026 7:46:37 AM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>668 - Light</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jonathan Walters</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2392,7 +2406,7 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -2410,17 +2424,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08/09/2026 12:17:56 PM</t>
+          <t>08/13/2026 6:33:21 PM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>680 - Medium</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jesus Carbajal</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2459,32 +2473,24 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08/09/2026 7:57:46 AM</t>
+          <t>08/13/2026 11:59:27 AM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Paul Kunze Jr</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>694 - Heavy</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harsh Brake</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -2498,25 +2504,27 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="n">
-        <v>0.489</v>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08/07/2026 6:45:51 PM</t>
+          <t>08/11/2026 4:41:04 PM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>658 - Medium</t>
+          <t>649 - Heavy</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Paul Kunze Jr</t>
+          <t>Juan Ramirez</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2526,18 +2534,18 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>HAAS Alert, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Rolling Stop</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -2555,17 +2563,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08/06/2026 2:18:16 PM</t>
+          <t>08/11/2026 4:04:10 PM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2575,12 +2583,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -2604,24 +2612,20 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08/06/2026 8:19:00 AM</t>
+          <t>08/11/2026 10:56:24 AM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>696 - Medium</t>
+          <t>667 - Medium</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jammie Singleton</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Active Drivers, Towing and Recovery</t>
-        </is>
-      </c>
+          <t>Jeremy Myers</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -2629,13 +2633,13 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mobile Usage</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -2643,37 +2647,35 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N46" t="n">
+        <v>0.672</v>
       </c>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08/05/2026 5:42:28 PM</t>
+          <t>08/10/2026 5:26:28 PM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>668 - Light</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Jonathan Walters</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Active Drivers, Towing and Recovery</t>
+          <t>HAAS Alert, Heavy Haul</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2684,7 +2686,7 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Needs Coaching</t>
+          <t>Coached</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -2702,7 +2704,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08/05/2026 3:33:14 PM</t>
+          <t>08/09/2026 12:17:56 PM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2751,17 +2753,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08/04/2026 2:28:07 PM</t>
+          <t>08/09/2026 7:57:46 AM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2771,12 +2773,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Harsh Brake</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -2790,27 +2792,25 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N49" t="n">
+        <v>0.489</v>
       </c>
       <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08/04/2026 12:31:14 PM</t>
+          <t>08/07/2026 6:45:51 PM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>669 - Heavy</t>
+          <t>658 - Medium</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jason Walker</t>
+          <t>Paul Kunze Jr</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2820,12 +2820,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>No Seat Belt</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -2849,17 +2849,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08/03/2026 2:39:43 PM</t>
+          <t>08/06/2026 2:18:16 PM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>649 - Heavy</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Juan Ramirez</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>No Seat Belt</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -2898,17 +2898,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08/03/2026 2:36:38 PM</t>
+          <t>08/06/2026 8:19:00 AM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>649 - Heavy</t>
+          <t>696 - Medium</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Juan Ramirez</t>
+          <t>Jammie Singleton</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>HAAS Alert, Heavy Haul</t>
+          <t>HAAS Alert, Towing and Recovery</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rolling Stop</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -2947,22 +2947,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/31/2026 1:16:01 PM</t>
+          <t>08/05/2026 5:42:28 PM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>662 - Heavy</t>
+          <t>669 - Heavy</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Drew Template</t>
+          <t>Jason Walker</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Active Drivers, Heavy Haul</t>
+          <t>Active Drivers, Towing and Recovery</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2972,13 +2972,13 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -2996,20 +2996,24 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/31/2026 1:02:24 PM</t>
+          <t>08/05/2026 3:33:14 PM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>667 - Medium</t>
+          <t>680 - Medium</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jeremy Myers</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>Jesus Carbajal</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Active Drivers, Towing and Recovery</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>HAAS Alert, Towing and Recovery</t>
@@ -3017,13 +3021,13 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Following Distance</t>
+          <t>Mobile Usage</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Coached</t>
+          <t>Needs Coaching</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -3041,17 +3045,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <i